--- a/artfynd/A 36363-2024 artfynd.xlsx
+++ b/artfynd/A 36363-2024 artfynd.xlsx
@@ -37002,10 +37002,10 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>122254341</v>
+        <v>122254588</v>
       </c>
       <c r="B272" t="n">
-        <v>56280</v>
+        <v>56285</v>
       </c>
       <c r="C272" t="inlineStr">
         <is>
@@ -37018,21 +37018,21 @@
         </is>
       </c>
       <c r="E272" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
@@ -37059,7 +37059,7 @@
         <v>586415</v>
       </c>
       <c r="R272" t="n">
-        <v>6311146</v>
+        <v>6311196</v>
       </c>
       <c r="S272" t="n">
         <v>5</v>
@@ -37091,7 +37091,7 @@
       </c>
       <c r="Z272" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>23:22</t>
         </is>
       </c>
       <c r="AA272" t="inlineStr">
@@ -37101,7 +37101,7 @@
       </c>
       <c r="AB272" t="inlineStr">
         <is>
-          <t>23:03</t>
+          <t>23:23</t>
         </is>
       </c>
       <c r="AC272" t="inlineStr">
@@ -37146,10 +37146,10 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>122254394</v>
+        <v>122254648</v>
       </c>
       <c r="B273" t="n">
-        <v>56280</v>
+        <v>56285</v>
       </c>
       <c r="C273" t="inlineStr">
         <is>
@@ -37162,21 +37162,21 @@
         </is>
       </c>
       <c r="E273" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
@@ -37200,10 +37200,10 @@
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>586419</v>
+        <v>586418</v>
       </c>
       <c r="R273" t="n">
-        <v>6311142</v>
+        <v>6311107</v>
       </c>
       <c r="S273" t="n">
         <v>5</v>
@@ -37235,7 +37235,7 @@
       </c>
       <c r="Z273" t="inlineStr">
         <is>
-          <t>22:43</t>
+          <t>22:36</t>
         </is>
       </c>
       <c r="AA273" t="inlineStr">
@@ -37245,7 +37245,7 @@
       </c>
       <c r="AB273" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AC273" t="inlineStr">
@@ -37290,10 +37290,10 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>122254314</v>
+        <v>122254633</v>
       </c>
       <c r="B274" t="n">
-        <v>56280</v>
+        <v>56285</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>
@@ -37306,21 +37306,21 @@
         </is>
       </c>
       <c r="E274" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
@@ -37344,10 +37344,10 @@
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>586443</v>
+        <v>586396</v>
       </c>
       <c r="R274" t="n">
-        <v>6311164</v>
+        <v>6311146</v>
       </c>
       <c r="S274" t="n">
         <v>5</v>
@@ -37379,7 +37379,7 @@
       </c>
       <c r="Z274" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AA274" t="inlineStr">
@@ -37389,7 +37389,7 @@
       </c>
       <c r="AB274" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AC274" t="inlineStr">
@@ -37434,7 +37434,7 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>122254306</v>
+        <v>122254342</v>
       </c>
       <c r="B275" t="n">
         <v>56280</v>
@@ -37488,10 +37488,10 @@
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>586473</v>
+        <v>586389</v>
       </c>
       <c r="R275" t="n">
-        <v>6311192</v>
+        <v>6311142</v>
       </c>
       <c r="S275" t="n">
         <v>5</v>
@@ -37523,7 +37523,7 @@
       </c>
       <c r="Z275" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA275" t="inlineStr">
@@ -37533,7 +37533,7 @@
       </c>
       <c r="AB275" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AC275" t="inlineStr">
@@ -37578,10 +37578,10 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>122254649</v>
+        <v>122254316</v>
       </c>
       <c r="B276" t="n">
-        <v>56285</v>
+        <v>56280</v>
       </c>
       <c r="C276" t="inlineStr">
         <is>
@@ -37594,21 +37594,21 @@
         </is>
       </c>
       <c r="E276" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
@@ -37632,10 +37632,10 @@
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>586422</v>
+        <v>586423</v>
       </c>
       <c r="R276" t="n">
-        <v>6311100</v>
+        <v>6311166</v>
       </c>
       <c r="S276" t="n">
         <v>5</v>
@@ -37667,7 +37667,7 @@
       </c>
       <c r="Z276" t="inlineStr">
         <is>
-          <t>22:35</t>
+          <t>23:23</t>
         </is>
       </c>
       <c r="AA276" t="inlineStr">
@@ -37677,7 +37677,7 @@
       </c>
       <c r="AB276" t="inlineStr">
         <is>
-          <t>22:36</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="AC276" t="inlineStr">
@@ -37722,10 +37722,10 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>122254650</v>
+        <v>122254371</v>
       </c>
       <c r="B277" t="n">
-        <v>56285</v>
+        <v>56280</v>
       </c>
       <c r="C277" t="inlineStr">
         <is>
@@ -37738,21 +37738,21 @@
         </is>
       </c>
       <c r="E277" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
@@ -37776,10 +37776,10 @@
         </is>
       </c>
       <c r="Q277" t="n">
-        <v>586422</v>
+        <v>586308</v>
       </c>
       <c r="R277" t="n">
-        <v>6311105</v>
+        <v>6311132</v>
       </c>
       <c r="S277" t="n">
         <v>5</v>
@@ -37811,7 +37811,7 @@
       </c>
       <c r="Z277" t="inlineStr">
         <is>
-          <t>22:35</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AA277" t="inlineStr">
@@ -37821,7 +37821,7 @@
       </c>
       <c r="AB277" t="inlineStr">
         <is>
-          <t>22:36</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AC277" t="inlineStr">
@@ -37866,10 +37866,10 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>122254659</v>
+        <v>122254957</v>
       </c>
       <c r="B278" t="n">
-        <v>56285</v>
+        <v>56273</v>
       </c>
       <c r="C278" t="inlineStr">
         <is>
@@ -37882,21 +37882,21 @@
         </is>
       </c>
       <c r="E278" t="n">
-        <v>205995</v>
+        <v>205992</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
@@ -37920,10 +37920,10 @@
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>586489</v>
+        <v>586444</v>
       </c>
       <c r="R278" t="n">
-        <v>6311181</v>
+        <v>6311160</v>
       </c>
       <c r="S278" t="n">
         <v>5</v>
@@ -37955,7 +37955,7 @@
       </c>
       <c r="Z278" t="inlineStr">
         <is>
-          <t>22:31</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="AA278" t="inlineStr">
@@ -37965,7 +37965,7 @@
       </c>
       <c r="AB278" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AC278" t="inlineStr">
@@ -38010,7 +38010,7 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>122254652</v>
+        <v>122254644</v>
       </c>
       <c r="B279" t="n">
         <v>56285</v>
@@ -38064,10 +38064,10 @@
         </is>
       </c>
       <c r="Q279" t="n">
-        <v>586432</v>
+        <v>586429</v>
       </c>
       <c r="R279" t="n">
-        <v>6311118</v>
+        <v>6311115</v>
       </c>
       <c r="S279" t="n">
         <v>5</v>
@@ -38099,7 +38099,7 @@
       </c>
       <c r="Z279" t="inlineStr">
         <is>
-          <t>22:34</t>
+          <t>22:36</t>
         </is>
       </c>
       <c r="AA279" t="inlineStr">
@@ -38109,7 +38109,7 @@
       </c>
       <c r="AB279" t="inlineStr">
         <is>
-          <t>22:35</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AC279" t="inlineStr">
@@ -38154,10 +38154,10 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>122254657</v>
+        <v>122254845</v>
       </c>
       <c r="B280" t="n">
-        <v>56285</v>
+        <v>56283</v>
       </c>
       <c r="C280" t="inlineStr">
         <is>
@@ -38170,21 +38170,21 @@
         </is>
       </c>
       <c r="E280" t="n">
-        <v>205995</v>
+        <v>100111</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
@@ -38208,10 +38208,10 @@
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>586488</v>
+        <v>586370</v>
       </c>
       <c r="R280" t="n">
-        <v>6311184</v>
+        <v>6311139</v>
       </c>
       <c r="S280" t="n">
         <v>5</v>
@@ -38243,7 +38243,7 @@
       </c>
       <c r="Z280" t="inlineStr">
         <is>
-          <t>22:31</t>
+          <t>22:59</t>
         </is>
       </c>
       <c r="AA280" t="inlineStr">
@@ -38253,7 +38253,7 @@
       </c>
       <c r="AB280" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AC280" t="inlineStr">
@@ -38298,10 +38298,10 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>122254317</v>
+        <v>122254862</v>
       </c>
       <c r="B281" t="n">
-        <v>56280</v>
+        <v>56283</v>
       </c>
       <c r="C281" t="inlineStr">
         <is>
@@ -38314,21 +38314,21 @@
         </is>
       </c>
       <c r="E281" t="n">
-        <v>100092</v>
+        <v>100111</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
@@ -38352,10 +38352,10 @@
         </is>
       </c>
       <c r="Q281" t="n">
-        <v>586438</v>
+        <v>586288</v>
       </c>
       <c r="R281" t="n">
-        <v>6311222</v>
+        <v>6311100</v>
       </c>
       <c r="S281" t="n">
         <v>5</v>
@@ -38387,7 +38387,7 @@
       </c>
       <c r="Z281" t="inlineStr">
         <is>
-          <t>23:22</t>
+          <t>22:55</t>
         </is>
       </c>
       <c r="AA281" t="inlineStr">
@@ -38397,7 +38397,7 @@
       </c>
       <c r="AB281" t="inlineStr">
         <is>
-          <t>23:23</t>
+          <t>22:56</t>
         </is>
       </c>
       <c r="AC281" t="inlineStr">
@@ -38442,32 +38442,32 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>122254342</v>
+        <v>122254173</v>
       </c>
       <c r="B282" t="n">
-        <v>56280</v>
+        <v>56264</v>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Dokumentation efterfrågas</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E282" t="n">
-        <v>100092</v>
+        <v>100015</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Barbastell</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Barbastella barbastellus</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -38496,10 +38496,10 @@
         </is>
       </c>
       <c r="Q282" t="n">
-        <v>586389</v>
+        <v>586415</v>
       </c>
       <c r="R282" t="n">
-        <v>6311142</v>
+        <v>6311149</v>
       </c>
       <c r="S282" t="n">
         <v>5</v>
@@ -38531,7 +38531,7 @@
       </c>
       <c r="Z282" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AA282" t="inlineStr">
@@ -38541,7 +38541,7 @@
       </c>
       <c r="AB282" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>23:03</t>
         </is>
       </c>
       <c r="AC282" t="inlineStr">
@@ -38586,7 +38586,7 @@
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>122254411</v>
+        <v>122254413</v>
       </c>
       <c r="B283" t="n">
         <v>56280</v>
@@ -38640,10 +38640,10 @@
         </is>
       </c>
       <c r="Q283" t="n">
-        <v>586414</v>
+        <v>586423</v>
       </c>
       <c r="R283" t="n">
-        <v>6311126</v>
+        <v>6311137</v>
       </c>
       <c r="S283" t="n">
         <v>5</v>
@@ -38730,7 +38730,7 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>122254313</v>
+        <v>122254350</v>
       </c>
       <c r="B284" t="n">
         <v>56280</v>
@@ -38784,10 +38784,10 @@
         </is>
       </c>
       <c r="Q284" t="n">
-        <v>586449</v>
+        <v>586330</v>
       </c>
       <c r="R284" t="n">
-        <v>6311155</v>
+        <v>6311120</v>
       </c>
       <c r="S284" t="n">
         <v>5</v>
@@ -38819,7 +38819,7 @@
       </c>
       <c r="Z284" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>22:57</t>
         </is>
       </c>
       <c r="AA284" t="inlineStr">
@@ -38829,7 +38829,7 @@
       </c>
       <c r="AB284" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>22:58</t>
         </is>
       </c>
       <c r="AC284" t="inlineStr">
@@ -38874,10 +38874,10 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>122254610</v>
+        <v>122254953</v>
       </c>
       <c r="B285" t="n">
-        <v>56285</v>
+        <v>56273</v>
       </c>
       <c r="C285" t="inlineStr">
         <is>
@@ -38890,21 +38890,21 @@
         </is>
       </c>
       <c r="E285" t="n">
-        <v>205995</v>
+        <v>205992</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
@@ -38928,10 +38928,10 @@
         </is>
       </c>
       <c r="Q285" t="n">
-        <v>586389</v>
+        <v>586449</v>
       </c>
       <c r="R285" t="n">
-        <v>6311141</v>
+        <v>6311155</v>
       </c>
       <c r="S285" t="n">
         <v>5</v>
@@ -38963,7 +38963,7 @@
       </c>
       <c r="Z285" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA285" t="inlineStr">
@@ -38973,7 +38973,7 @@
       </c>
       <c r="AB285" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC285" t="inlineStr">
@@ -39018,10 +39018,10 @@
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>122254636</v>
+        <v>122254472</v>
       </c>
       <c r="B286" t="n">
-        <v>56285</v>
+        <v>56266</v>
       </c>
       <c r="C286" t="inlineStr">
         <is>
@@ -39030,25 +39030,25 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E286" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
@@ -39072,10 +39072,10 @@
         </is>
       </c>
       <c r="Q286" t="n">
-        <v>586418</v>
+        <v>586455</v>
       </c>
       <c r="R286" t="n">
-        <v>6311145</v>
+        <v>6311159</v>
       </c>
       <c r="S286" t="n">
         <v>5</v>
@@ -39107,7 +39107,7 @@
       </c>
       <c r="Z286" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AA286" t="inlineStr">
@@ -39117,7 +39117,7 @@
       </c>
       <c r="AB286" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AC286" t="inlineStr">
@@ -39162,10 +39162,10 @@
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>122254308</v>
+        <v>122254650</v>
       </c>
       <c r="B287" t="n">
-        <v>56280</v>
+        <v>56285</v>
       </c>
       <c r="C287" t="inlineStr">
         <is>
@@ -39178,21 +39178,21 @@
         </is>
       </c>
       <c r="E287" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
@@ -39216,10 +39216,10 @@
         </is>
       </c>
       <c r="Q287" t="n">
-        <v>586455</v>
+        <v>586422</v>
       </c>
       <c r="R287" t="n">
-        <v>6311159</v>
+        <v>6311105</v>
       </c>
       <c r="S287" t="n">
         <v>5</v>
@@ -39251,7 +39251,7 @@
       </c>
       <c r="Z287" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="AA287" t="inlineStr">
@@ -39261,7 +39261,7 @@
       </c>
       <c r="AB287" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>22:36</t>
         </is>
       </c>
       <c r="AC287" t="inlineStr">
@@ -39306,10 +39306,10 @@
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>122254844</v>
+        <v>122254514</v>
       </c>
       <c r="B288" t="n">
-        <v>56283</v>
+        <v>56266</v>
       </c>
       <c r="C288" t="inlineStr">
         <is>
@@ -39318,25 +39318,25 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E288" t="n">
-        <v>100111</v>
+        <v>205998</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
@@ -39360,10 +39360,10 @@
         </is>
       </c>
       <c r="Q288" t="n">
-        <v>586387</v>
+        <v>586408</v>
       </c>
       <c r="R288" t="n">
-        <v>6311141</v>
+        <v>6311124</v>
       </c>
       <c r="S288" t="n">
         <v>5</v>
@@ -39395,7 +39395,7 @@
       </c>
       <c r="Z288" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:43</t>
         </is>
       </c>
       <c r="AA288" t="inlineStr">
@@ -39405,7 +39405,7 @@
       </c>
       <c r="AB288" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AC288" t="inlineStr">
@@ -39450,10 +39450,10 @@
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>122254837</v>
+        <v>122254341</v>
       </c>
       <c r="B289" t="n">
-        <v>56283</v>
+        <v>56280</v>
       </c>
       <c r="C289" t="inlineStr">
         <is>
@@ -39466,21 +39466,21 @@
         </is>
       </c>
       <c r="E289" t="n">
-        <v>100111</v>
+        <v>100092</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
@@ -39504,10 +39504,10 @@
         </is>
       </c>
       <c r="Q289" t="n">
-        <v>586448</v>
+        <v>586415</v>
       </c>
       <c r="R289" t="n">
-        <v>6311154</v>
+        <v>6311146</v>
       </c>
       <c r="S289" t="n">
         <v>5</v>
@@ -39539,7 +39539,7 @@
       </c>
       <c r="Z289" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AA289" t="inlineStr">
@@ -39549,7 +39549,7 @@
       </c>
       <c r="AB289" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>23:03</t>
         </is>
       </c>
       <c r="AC289" t="inlineStr">
@@ -39594,10 +39594,10 @@
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>122254586</v>
+        <v>122254415</v>
       </c>
       <c r="B290" t="n">
-        <v>56285</v>
+        <v>56280</v>
       </c>
       <c r="C290" t="inlineStr">
         <is>
@@ -39610,21 +39610,21 @@
         </is>
       </c>
       <c r="E290" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
@@ -39648,10 +39648,10 @@
         </is>
       </c>
       <c r="Q290" t="n">
-        <v>586446</v>
+        <v>586425</v>
       </c>
       <c r="R290" t="n">
-        <v>6311158</v>
+        <v>6311135</v>
       </c>
       <c r="S290" t="n">
         <v>5</v>
@@ -39683,7 +39683,7 @@
       </c>
       <c r="Z290" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AA290" t="inlineStr">
@@ -39693,7 +39693,7 @@
       </c>
       <c r="AB290" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>22:38</t>
         </is>
       </c>
       <c r="AC290" t="inlineStr">
@@ -39738,10 +39738,10 @@
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>122254519</v>
+        <v>122254343</v>
       </c>
       <c r="B291" t="n">
-        <v>56266</v>
+        <v>56280</v>
       </c>
       <c r="C291" t="inlineStr">
         <is>
@@ -39750,25 +39750,25 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E291" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
@@ -39792,10 +39792,10 @@
         </is>
       </c>
       <c r="Q291" t="n">
-        <v>586424</v>
+        <v>586388</v>
       </c>
       <c r="R291" t="n">
-        <v>6311135</v>
+        <v>6311142</v>
       </c>
       <c r="S291" t="n">
         <v>5</v>
@@ -39827,7 +39827,7 @@
       </c>
       <c r="Z291" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA291" t="inlineStr">
@@ -39837,7 +39837,7 @@
       </c>
       <c r="AB291" t="inlineStr">
         <is>
-          <t>22:38</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AC291" t="inlineStr">
@@ -39882,10 +39882,10 @@
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>122254956</v>
+        <v>122254370</v>
       </c>
       <c r="B292" t="n">
-        <v>56273</v>
+        <v>56280</v>
       </c>
       <c r="C292" t="inlineStr">
         <is>
@@ -39898,21 +39898,21 @@
         </is>
       </c>
       <c r="E292" t="n">
-        <v>205992</v>
+        <v>100092</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
@@ -39936,10 +39936,10 @@
         </is>
       </c>
       <c r="Q292" t="n">
-        <v>586441</v>
+        <v>586309</v>
       </c>
       <c r="R292" t="n">
-        <v>6311152</v>
+        <v>6311119</v>
       </c>
       <c r="S292" t="n">
         <v>5</v>
@@ -39971,7 +39971,7 @@
       </c>
       <c r="Z292" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AA292" t="inlineStr">
@@ -39981,7 +39981,7 @@
       </c>
       <c r="AB292" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AC292" t="inlineStr">
@@ -40026,10 +40026,10 @@
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>122254307</v>
+        <v>122254625</v>
       </c>
       <c r="B293" t="n">
-        <v>56280</v>
+        <v>56285</v>
       </c>
       <c r="C293" t="inlineStr">
         <is>
@@ -40042,21 +40042,21 @@
         </is>
       </c>
       <c r="E293" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
@@ -40080,10 +40080,10 @@
         </is>
       </c>
       <c r="Q293" t="n">
-        <v>586477</v>
+        <v>586309</v>
       </c>
       <c r="R293" t="n">
-        <v>6311186</v>
+        <v>6311119</v>
       </c>
       <c r="S293" t="n">
         <v>5</v>
@@ -40115,7 +40115,7 @@
       </c>
       <c r="Z293" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AA293" t="inlineStr">
@@ -40125,7 +40125,7 @@
       </c>
       <c r="AB293" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AC293" t="inlineStr">
@@ -40170,10 +40170,10 @@
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>122254588</v>
+        <v>122254519</v>
       </c>
       <c r="B294" t="n">
-        <v>56285</v>
+        <v>56266</v>
       </c>
       <c r="C294" t="inlineStr">
         <is>
@@ -40182,25 +40182,25 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E294" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
@@ -40224,10 +40224,10 @@
         </is>
       </c>
       <c r="Q294" t="n">
-        <v>586415</v>
+        <v>586424</v>
       </c>
       <c r="R294" t="n">
-        <v>6311196</v>
+        <v>6311135</v>
       </c>
       <c r="S294" t="n">
         <v>5</v>
@@ -40259,7 +40259,7 @@
       </c>
       <c r="Z294" t="inlineStr">
         <is>
-          <t>23:22</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AA294" t="inlineStr">
@@ -40269,7 +40269,7 @@
       </c>
       <c r="AB294" t="inlineStr">
         <is>
-          <t>23:23</t>
+          <t>22:38</t>
         </is>
       </c>
       <c r="AC294" t="inlineStr">
@@ -40314,7 +40314,7 @@
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>122254658</v>
+        <v>122254646</v>
       </c>
       <c r="B295" t="n">
         <v>56285</v>
@@ -40368,10 +40368,10 @@
         </is>
       </c>
       <c r="Q295" t="n">
-        <v>586491</v>
+        <v>586422</v>
       </c>
       <c r="R295" t="n">
-        <v>6311181</v>
+        <v>6311111</v>
       </c>
       <c r="S295" t="n">
         <v>5</v>
@@ -40403,7 +40403,7 @@
       </c>
       <c r="Z295" t="inlineStr">
         <is>
-          <t>22:31</t>
+          <t>22:36</t>
         </is>
       </c>
       <c r="AA295" t="inlineStr">
@@ -40413,7 +40413,7 @@
       </c>
       <c r="AB295" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AC295" t="inlineStr">
@@ -40458,10 +40458,10 @@
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>122254953</v>
+        <v>122254626</v>
       </c>
       <c r="B296" t="n">
-        <v>56273</v>
+        <v>56285</v>
       </c>
       <c r="C296" t="inlineStr">
         <is>
@@ -40474,21 +40474,21 @@
         </is>
       </c>
       <c r="E296" t="n">
-        <v>205992</v>
+        <v>205995</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
@@ -40512,10 +40512,10 @@
         </is>
       </c>
       <c r="Q296" t="n">
-        <v>586449</v>
+        <v>586313</v>
       </c>
       <c r="R296" t="n">
-        <v>6311155</v>
+        <v>6311124</v>
       </c>
       <c r="S296" t="n">
         <v>5</v>
@@ -40547,7 +40547,7 @@
       </c>
       <c r="Z296" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AA296" t="inlineStr">
@@ -40557,7 +40557,7 @@
       </c>
       <c r="AB296" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AC296" t="inlineStr">
@@ -40746,10 +40746,10 @@
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>122254609</v>
+        <v>122254365</v>
       </c>
       <c r="B298" t="n">
-        <v>56285</v>
+        <v>56280</v>
       </c>
       <c r="C298" t="inlineStr">
         <is>
@@ -40762,21 +40762,21 @@
         </is>
       </c>
       <c r="E298" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
@@ -40800,10 +40800,10 @@
         </is>
       </c>
       <c r="Q298" t="n">
-        <v>586392</v>
+        <v>586276</v>
       </c>
       <c r="R298" t="n">
-        <v>6311147</v>
+        <v>6311100</v>
       </c>
       <c r="S298" t="n">
         <v>5</v>
@@ -40835,7 +40835,7 @@
       </c>
       <c r="Z298" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AA298" t="inlineStr">
@@ -40845,7 +40845,7 @@
       </c>
       <c r="AB298" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>22:52</t>
         </is>
       </c>
       <c r="AC298" t="inlineStr">
@@ -40890,10 +40890,10 @@
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>122254857</v>
+        <v>122254312</v>
       </c>
       <c r="B299" t="n">
-        <v>56283</v>
+        <v>56280</v>
       </c>
       <c r="C299" t="inlineStr">
         <is>
@@ -40906,21 +40906,21 @@
         </is>
       </c>
       <c r="E299" t="n">
-        <v>100111</v>
+        <v>100092</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
@@ -40944,10 +40944,10 @@
         </is>
       </c>
       <c r="Q299" t="n">
-        <v>586317</v>
+        <v>586452</v>
       </c>
       <c r="R299" t="n">
-        <v>6311115</v>
+        <v>6311152</v>
       </c>
       <c r="S299" t="n">
         <v>5</v>
@@ -40979,7 +40979,7 @@
       </c>
       <c r="Z299" t="inlineStr">
         <is>
-          <t>22:57</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA299" t="inlineStr">
@@ -40989,7 +40989,7 @@
       </c>
       <c r="AB299" t="inlineStr">
         <is>
-          <t>22:58</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC299" t="inlineStr">
@@ -41034,7 +41034,7 @@
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>122254350</v>
+        <v>122254306</v>
       </c>
       <c r="B300" t="n">
         <v>56280</v>
@@ -41088,10 +41088,10 @@
         </is>
       </c>
       <c r="Q300" t="n">
-        <v>586330</v>
+        <v>586473</v>
       </c>
       <c r="R300" t="n">
-        <v>6311120</v>
+        <v>6311192</v>
       </c>
       <c r="S300" t="n">
         <v>5</v>
@@ -41123,7 +41123,7 @@
       </c>
       <c r="Z300" t="inlineStr">
         <is>
-          <t>22:57</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AA300" t="inlineStr">
@@ -41133,7 +41133,7 @@
       </c>
       <c r="AB300" t="inlineStr">
         <is>
-          <t>22:58</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AC300" t="inlineStr">
@@ -41178,10 +41178,10 @@
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>122254396</v>
+        <v>122254475</v>
       </c>
       <c r="B301" t="n">
-        <v>56280</v>
+        <v>56266</v>
       </c>
       <c r="C301" t="inlineStr">
         <is>
@@ -41190,25 +41190,25 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E301" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
@@ -41232,10 +41232,10 @@
         </is>
       </c>
       <c r="Q301" t="n">
-        <v>586408</v>
+        <v>586420</v>
       </c>
       <c r="R301" t="n">
-        <v>6311124</v>
+        <v>6311166</v>
       </c>
       <c r="S301" t="n">
         <v>5</v>
@@ -41267,7 +41267,7 @@
       </c>
       <c r="Z301" t="inlineStr">
         <is>
-          <t>22:43</t>
+          <t>23:23</t>
         </is>
       </c>
       <c r="AA301" t="inlineStr">
@@ -41277,7 +41277,7 @@
       </c>
       <c r="AB301" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="AC301" t="inlineStr">
@@ -41322,10 +41322,10 @@
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>122254963</v>
+        <v>122254474</v>
       </c>
       <c r="B302" t="n">
-        <v>56273</v>
+        <v>56266</v>
       </c>
       <c r="C302" t="inlineStr">
         <is>
@@ -41334,25 +41334,25 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E302" t="n">
-        <v>205992</v>
+        <v>205998</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
@@ -41376,10 +41376,10 @@
         </is>
       </c>
       <c r="Q302" t="n">
-        <v>586374</v>
+        <v>586443</v>
       </c>
       <c r="R302" t="n">
-        <v>6311140</v>
+        <v>6311164</v>
       </c>
       <c r="S302" t="n">
         <v>5</v>
@@ -41411,7 +41411,7 @@
       </c>
       <c r="Z302" t="inlineStr">
         <is>
-          <t>22:46</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AA302" t="inlineStr">
@@ -41421,7 +41421,7 @@
       </c>
       <c r="AB302" t="inlineStr">
         <is>
-          <t>22:47</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AC302" t="inlineStr">
@@ -41466,10 +41466,10 @@
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>122254633</v>
+        <v>122254964</v>
       </c>
       <c r="B303" t="n">
-        <v>56285</v>
+        <v>56273</v>
       </c>
       <c r="C303" t="inlineStr">
         <is>
@@ -41482,21 +41482,21 @@
         </is>
       </c>
       <c r="E303" t="n">
-        <v>205995</v>
+        <v>205992</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
@@ -41520,10 +41520,10 @@
         </is>
       </c>
       <c r="Q303" t="n">
-        <v>586396</v>
+        <v>586430</v>
       </c>
       <c r="R303" t="n">
-        <v>6311146</v>
+        <v>6311142</v>
       </c>
       <c r="S303" t="n">
         <v>5</v>
@@ -41555,7 +41555,7 @@
       </c>
       <c r="Z303" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="AA303" t="inlineStr">
@@ -41565,7 +41565,7 @@
       </c>
       <c r="AB303" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>22:34</t>
         </is>
       </c>
       <c r="AC303" t="inlineStr">
@@ -41610,10 +41610,10 @@
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>122254472</v>
+        <v>122254952</v>
       </c>
       <c r="B304" t="n">
-        <v>56266</v>
+        <v>56273</v>
       </c>
       <c r="C304" t="inlineStr">
         <is>
@@ -41622,25 +41622,25 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E304" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
@@ -41667,7 +41667,7 @@
         <v>586455</v>
       </c>
       <c r="R304" t="n">
-        <v>6311159</v>
+        <v>6311156</v>
       </c>
       <c r="S304" t="n">
         <v>5</v>
@@ -41754,7 +41754,7 @@
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>122254880</v>
+        <v>122254878</v>
       </c>
       <c r="B305" t="n">
         <v>56283</v>
@@ -41808,10 +41808,10 @@
         </is>
       </c>
       <c r="Q305" t="n">
-        <v>586303</v>
+        <v>586280</v>
       </c>
       <c r="R305" t="n">
-        <v>6311115</v>
+        <v>6311103</v>
       </c>
       <c r="S305" t="n">
         <v>5</v>
@@ -41843,7 +41843,7 @@
       </c>
       <c r="Z305" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AA305" t="inlineStr">
@@ -41853,7 +41853,7 @@
       </c>
       <c r="AB305" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>22:52</t>
         </is>
       </c>
       <c r="AC305" t="inlineStr">
@@ -41898,7 +41898,7 @@
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>122254343</v>
+        <v>122254393</v>
       </c>
       <c r="B306" t="n">
         <v>56280</v>
@@ -41952,10 +41952,10 @@
         </is>
       </c>
       <c r="Q306" t="n">
-        <v>586388</v>
+        <v>586396</v>
       </c>
       <c r="R306" t="n">
-        <v>6311142</v>
+        <v>6311146</v>
       </c>
       <c r="S306" t="n">
         <v>5</v>
@@ -41987,7 +41987,7 @@
       </c>
       <c r="Z306" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AA306" t="inlineStr">
@@ -41997,7 +41997,7 @@
       </c>
       <c r="AB306" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AC306" t="inlineStr">
@@ -42042,10 +42042,10 @@
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>122254627</v>
+        <v>122254416</v>
       </c>
       <c r="B307" t="n">
-        <v>56285</v>
+        <v>56280</v>
       </c>
       <c r="C307" t="inlineStr">
         <is>
@@ -42058,21 +42058,21 @@
         </is>
       </c>
       <c r="E307" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
@@ -42096,10 +42096,10 @@
         </is>
       </c>
       <c r="Q307" t="n">
-        <v>586306</v>
+        <v>586410</v>
       </c>
       <c r="R307" t="n">
-        <v>6311131</v>
+        <v>6311140</v>
       </c>
       <c r="S307" t="n">
         <v>5</v>
@@ -42131,7 +42131,7 @@
       </c>
       <c r="Z307" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="AA307" t="inlineStr">
@@ -42141,7 +42141,7 @@
       </c>
       <c r="AB307" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>22:34</t>
         </is>
       </c>
       <c r="AC307" t="inlineStr">
@@ -42186,10 +42186,10 @@
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>122254845</v>
+        <v>122254649</v>
       </c>
       <c r="B308" t="n">
-        <v>56283</v>
+        <v>56285</v>
       </c>
       <c r="C308" t="inlineStr">
         <is>
@@ -42202,21 +42202,21 @@
         </is>
       </c>
       <c r="E308" t="n">
-        <v>100111</v>
+        <v>205995</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
@@ -42240,10 +42240,10 @@
         </is>
       </c>
       <c r="Q308" t="n">
-        <v>586370</v>
+        <v>586422</v>
       </c>
       <c r="R308" t="n">
-        <v>6311139</v>
+        <v>6311100</v>
       </c>
       <c r="S308" t="n">
         <v>5</v>
@@ -42275,7 +42275,7 @@
       </c>
       <c r="Z308" t="inlineStr">
         <is>
-          <t>22:59</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="AA308" t="inlineStr">
@@ -42285,7 +42285,7 @@
       </c>
       <c r="AB308" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:36</t>
         </is>
       </c>
       <c r="AC308" t="inlineStr">
@@ -42330,10 +42330,10 @@
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>122254413</v>
+        <v>122254585</v>
       </c>
       <c r="B309" t="n">
-        <v>56280</v>
+        <v>56285</v>
       </c>
       <c r="C309" t="inlineStr">
         <is>
@@ -42346,21 +42346,21 @@
         </is>
       </c>
       <c r="E309" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
@@ -42384,10 +42384,10 @@
         </is>
       </c>
       <c r="Q309" t="n">
-        <v>586423</v>
+        <v>586455</v>
       </c>
       <c r="R309" t="n">
-        <v>6311137</v>
+        <v>6311156</v>
       </c>
       <c r="S309" t="n">
         <v>5</v>
@@ -42419,7 +42419,7 @@
       </c>
       <c r="Z309" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AA309" t="inlineStr">
@@ -42429,7 +42429,7 @@
       </c>
       <c r="AB309" t="inlineStr">
         <is>
-          <t>22:38</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AC309" t="inlineStr">
@@ -42474,10 +42474,10 @@
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>122254371</v>
+        <v>122254496</v>
       </c>
       <c r="B310" t="n">
-        <v>56280</v>
+        <v>56266</v>
       </c>
       <c r="C310" t="inlineStr">
         <is>
@@ -42486,25 +42486,25 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E310" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
@@ -42528,10 +42528,10 @@
         </is>
       </c>
       <c r="Q310" t="n">
-        <v>586308</v>
+        <v>586415</v>
       </c>
       <c r="R310" t="n">
-        <v>6311132</v>
+        <v>6311146</v>
       </c>
       <c r="S310" t="n">
         <v>5</v>
@@ -42563,7 +42563,7 @@
       </c>
       <c r="Z310" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AA310" t="inlineStr">
@@ -42573,7 +42573,7 @@
       </c>
       <c r="AB310" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>23:03</t>
         </is>
       </c>
       <c r="AC310" t="inlineStr">
@@ -42618,10 +42618,10 @@
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>122254475</v>
+        <v>122254586</v>
       </c>
       <c r="B311" t="n">
-        <v>56266</v>
+        <v>56285</v>
       </c>
       <c r="C311" t="inlineStr">
         <is>
@@ -42630,25 +42630,25 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E311" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
@@ -42672,10 +42672,10 @@
         </is>
       </c>
       <c r="Q311" t="n">
-        <v>586420</v>
+        <v>586446</v>
       </c>
       <c r="R311" t="n">
-        <v>6311166</v>
+        <v>6311158</v>
       </c>
       <c r="S311" t="n">
         <v>5</v>
@@ -42707,7 +42707,7 @@
       </c>
       <c r="Z311" t="inlineStr">
         <is>
-          <t>23:23</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AA311" t="inlineStr">
@@ -42717,7 +42717,7 @@
       </c>
       <c r="AB311" t="inlineStr">
         <is>
-          <t>23:24</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AC311" t="inlineStr">
@@ -42762,10 +42762,10 @@
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>122254959</v>
+        <v>122254617</v>
       </c>
       <c r="B312" t="n">
-        <v>56273</v>
+        <v>56285</v>
       </c>
       <c r="C312" t="inlineStr">
         <is>
@@ -42778,21 +42778,21 @@
         </is>
       </c>
       <c r="E312" t="n">
-        <v>205992</v>
+        <v>205995</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
@@ -42816,10 +42816,10 @@
         </is>
       </c>
       <c r="Q312" t="n">
-        <v>586370</v>
+        <v>586317</v>
       </c>
       <c r="R312" t="n">
-        <v>6311139</v>
+        <v>6311115</v>
       </c>
       <c r="S312" t="n">
         <v>5</v>
@@ -42851,7 +42851,7 @@
       </c>
       <c r="Z312" t="inlineStr">
         <is>
-          <t>22:59</t>
+          <t>22:57</t>
         </is>
       </c>
       <c r="AA312" t="inlineStr">
@@ -42861,7 +42861,7 @@
       </c>
       <c r="AB312" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:58</t>
         </is>
       </c>
       <c r="AC312" t="inlineStr">
@@ -42906,10 +42906,10 @@
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>122254950</v>
+        <v>122254643</v>
       </c>
       <c r="B313" t="n">
-        <v>56273</v>
+        <v>56285</v>
       </c>
       <c r="C313" t="inlineStr">
         <is>
@@ -42922,21 +42922,21 @@
         </is>
       </c>
       <c r="E313" t="n">
-        <v>205992</v>
+        <v>205995</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
@@ -42960,10 +42960,10 @@
         </is>
       </c>
       <c r="Q313" t="n">
-        <v>586482</v>
+        <v>586424</v>
       </c>
       <c r="R313" t="n">
-        <v>6311185</v>
+        <v>6311135</v>
       </c>
       <c r="S313" t="n">
         <v>5</v>
@@ -42995,7 +42995,7 @@
       </c>
       <c r="Z313" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AA313" t="inlineStr">
@@ -43005,7 +43005,7 @@
       </c>
       <c r="AB313" t="inlineStr">
         <is>
-          <t>23:31</t>
+          <t>22:38</t>
         </is>
       </c>
       <c r="AC313" t="inlineStr">
@@ -43050,10 +43050,10 @@
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>122254653</v>
+        <v>122254307</v>
       </c>
       <c r="B314" t="n">
-        <v>56285</v>
+        <v>56280</v>
       </c>
       <c r="C314" t="inlineStr">
         <is>
@@ -43066,21 +43066,21 @@
         </is>
       </c>
       <c r="E314" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
@@ -43104,10 +43104,10 @@
         </is>
       </c>
       <c r="Q314" t="n">
-        <v>586430</v>
+        <v>586477</v>
       </c>
       <c r="R314" t="n">
-        <v>6311142</v>
+        <v>6311186</v>
       </c>
       <c r="S314" t="n">
         <v>5</v>
@@ -43139,7 +43139,7 @@
       </c>
       <c r="Z314" t="inlineStr">
         <is>
-          <t>22:33</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AA314" t="inlineStr">
@@ -43149,7 +43149,7 @@
       </c>
       <c r="AB314" t="inlineStr">
         <is>
-          <t>22:34</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AC314" t="inlineStr">
@@ -43194,7 +43194,7 @@
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>122254412</v>
+        <v>122254420</v>
       </c>
       <c r="B315" t="n">
         <v>56280</v>
@@ -43248,10 +43248,10 @@
         </is>
       </c>
       <c r="Q315" t="n">
-        <v>586424</v>
+        <v>586467</v>
       </c>
       <c r="R315" t="n">
-        <v>6311135</v>
+        <v>6311178</v>
       </c>
       <c r="S315" t="n">
         <v>5</v>
@@ -43283,7 +43283,7 @@
       </c>
       <c r="Z315" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AA315" t="inlineStr">
@@ -43293,7 +43293,7 @@
       </c>
       <c r="AB315" t="inlineStr">
         <is>
-          <t>22:38</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="AC315" t="inlineStr">
@@ -43338,10 +43338,10 @@
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>122254418</v>
+        <v>122254843</v>
       </c>
       <c r="B316" t="n">
-        <v>56280</v>
+        <v>56283</v>
       </c>
       <c r="C316" t="inlineStr">
         <is>
@@ -43354,21 +43354,21 @@
         </is>
       </c>
       <c r="E316" t="n">
-        <v>100092</v>
+        <v>100111</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
@@ -43392,10 +43392,10 @@
         </is>
       </c>
       <c r="Q316" t="n">
-        <v>586467</v>
+        <v>586389</v>
       </c>
       <c r="R316" t="n">
-        <v>6311178</v>
+        <v>6311142</v>
       </c>
       <c r="S316" t="n">
         <v>5</v>
@@ -43427,7 +43427,7 @@
       </c>
       <c r="Z316" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA316" t="inlineStr">
@@ -43437,7 +43437,7 @@
       </c>
       <c r="AB316" t="inlineStr">
         <is>
-          <t>22:33</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AC316" t="inlineStr">
@@ -43482,10 +43482,10 @@
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>122254318</v>
+        <v>122254836</v>
       </c>
       <c r="B317" t="n">
-        <v>56280</v>
+        <v>56283</v>
       </c>
       <c r="C317" t="inlineStr">
         <is>
@@ -43498,21 +43498,21 @@
         </is>
       </c>
       <c r="E317" t="n">
-        <v>100092</v>
+        <v>100111</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
@@ -43536,10 +43536,10 @@
         </is>
       </c>
       <c r="Q317" t="n">
-        <v>586455</v>
+        <v>586474</v>
       </c>
       <c r="R317" t="n">
-        <v>6311228</v>
+        <v>6311176</v>
       </c>
       <c r="S317" t="n">
         <v>5</v>
@@ -43571,7 +43571,7 @@
       </c>
       <c r="Z317" t="inlineStr">
         <is>
-          <t>23:22</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AA317" t="inlineStr">
@@ -43581,7 +43581,7 @@
       </c>
       <c r="AB317" t="inlineStr">
         <is>
-          <t>23:23</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AC317" t="inlineStr">
@@ -43770,10 +43770,10 @@
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>122254416</v>
+        <v>122254951</v>
       </c>
       <c r="B319" t="n">
-        <v>56280</v>
+        <v>56273</v>
       </c>
       <c r="C319" t="inlineStr">
         <is>
@@ -43786,21 +43786,21 @@
         </is>
       </c>
       <c r="E319" t="n">
-        <v>100092</v>
+        <v>205992</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
@@ -43824,10 +43824,10 @@
         </is>
       </c>
       <c r="Q319" t="n">
-        <v>586410</v>
+        <v>586459</v>
       </c>
       <c r="R319" t="n">
-        <v>6311140</v>
+        <v>6311154</v>
       </c>
       <c r="S319" t="n">
         <v>5</v>
@@ -43859,7 +43859,7 @@
       </c>
       <c r="Z319" t="inlineStr">
         <is>
-          <t>22:33</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AA319" t="inlineStr">
@@ -43869,7 +43869,7 @@
       </c>
       <c r="AB319" t="inlineStr">
         <is>
-          <t>22:34</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AC319" t="inlineStr">
@@ -43914,10 +43914,10 @@
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>122254393</v>
+        <v>122254963</v>
       </c>
       <c r="B320" t="n">
-        <v>56280</v>
+        <v>56273</v>
       </c>
       <c r="C320" t="inlineStr">
         <is>
@@ -43930,21 +43930,21 @@
         </is>
       </c>
       <c r="E320" t="n">
-        <v>100092</v>
+        <v>205992</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
@@ -43968,10 +43968,10 @@
         </is>
       </c>
       <c r="Q320" t="n">
-        <v>586396</v>
+        <v>586374</v>
       </c>
       <c r="R320" t="n">
-        <v>6311146</v>
+        <v>6311140</v>
       </c>
       <c r="S320" t="n">
         <v>5</v>
@@ -44003,7 +44003,7 @@
       </c>
       <c r="Z320" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>22:46</t>
         </is>
       </c>
       <c r="AA320" t="inlineStr">
@@ -44013,7 +44013,7 @@
       </c>
       <c r="AB320" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>22:47</t>
         </is>
       </c>
       <c r="AC320" t="inlineStr">
@@ -44058,10 +44058,10 @@
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>122254310</v>
+        <v>122254615</v>
       </c>
       <c r="B321" t="n">
-        <v>56280</v>
+        <v>56285</v>
       </c>
       <c r="C321" t="inlineStr">
         <is>
@@ -44074,21 +44074,21 @@
         </is>
       </c>
       <c r="E321" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
@@ -44112,10 +44112,10 @@
         </is>
       </c>
       <c r="Q321" t="n">
-        <v>586452</v>
+        <v>586329</v>
       </c>
       <c r="R321" t="n">
-        <v>6311156</v>
+        <v>6311120</v>
       </c>
       <c r="S321" t="n">
         <v>5</v>
@@ -44147,7 +44147,7 @@
       </c>
       <c r="Z321" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>22:57</t>
         </is>
       </c>
       <c r="AA321" t="inlineStr">
@@ -44157,7 +44157,7 @@
       </c>
       <c r="AB321" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>22:58</t>
         </is>
       </c>
       <c r="AC321" t="inlineStr">
@@ -44202,10 +44202,10 @@
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>122254309</v>
+        <v>122254503</v>
       </c>
       <c r="B322" t="n">
-        <v>56280</v>
+        <v>56266</v>
       </c>
       <c r="C322" t="inlineStr">
         <is>
@@ -44214,25 +44214,25 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E322" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
@@ -44256,10 +44256,10 @@
         </is>
       </c>
       <c r="Q322" t="n">
-        <v>586456</v>
+        <v>586313</v>
       </c>
       <c r="R322" t="n">
-        <v>6311158</v>
+        <v>6311124</v>
       </c>
       <c r="S322" t="n">
         <v>5</v>
@@ -44291,7 +44291,7 @@
       </c>
       <c r="Z322" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AA322" t="inlineStr">
@@ -44301,7 +44301,7 @@
       </c>
       <c r="AB322" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AC322" t="inlineStr">
@@ -44346,10 +44346,10 @@
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>122254615</v>
+        <v>122254512</v>
       </c>
       <c r="B323" t="n">
-        <v>56285</v>
+        <v>56266</v>
       </c>
       <c r="C323" t="inlineStr">
         <is>
@@ -44358,25 +44358,25 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E323" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
@@ -44400,10 +44400,10 @@
         </is>
       </c>
       <c r="Q323" t="n">
-        <v>586329</v>
+        <v>586379</v>
       </c>
       <c r="R323" t="n">
-        <v>6311120</v>
+        <v>6311136</v>
       </c>
       <c r="S323" t="n">
         <v>5</v>
@@ -44435,7 +44435,7 @@
       </c>
       <c r="Z323" t="inlineStr">
         <is>
-          <t>22:57</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AA323" t="inlineStr">
@@ -44445,7 +44445,7 @@
       </c>
       <c r="AB323" t="inlineStr">
         <is>
-          <t>22:58</t>
+          <t>22:46</t>
         </is>
       </c>
       <c r="AC323" t="inlineStr">
@@ -44490,10 +44490,10 @@
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>122254957</v>
+        <v>122254499</v>
       </c>
       <c r="B324" t="n">
-        <v>56273</v>
+        <v>56266</v>
       </c>
       <c r="C324" t="inlineStr">
         <is>
@@ -44502,25 +44502,25 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E324" t="n">
-        <v>205992</v>
+        <v>205998</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
@@ -44544,10 +44544,10 @@
         </is>
       </c>
       <c r="Q324" t="n">
-        <v>586444</v>
+        <v>586392</v>
       </c>
       <c r="R324" t="n">
-        <v>6311160</v>
+        <v>6311147</v>
       </c>
       <c r="S324" t="n">
         <v>5</v>
@@ -44579,7 +44579,7 @@
       </c>
       <c r="Z324" t="inlineStr">
         <is>
-          <t>23:24</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AA324" t="inlineStr">
@@ -44589,7 +44589,7 @@
       </c>
       <c r="AB324" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AC324" t="inlineStr">
@@ -44634,10 +44634,10 @@
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>122254585</v>
+        <v>122254308</v>
       </c>
       <c r="B325" t="n">
-        <v>56285</v>
+        <v>56280</v>
       </c>
       <c r="C325" t="inlineStr">
         <is>
@@ -44650,21 +44650,21 @@
         </is>
       </c>
       <c r="E325" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
@@ -44691,7 +44691,7 @@
         <v>586455</v>
       </c>
       <c r="R325" t="n">
-        <v>6311156</v>
+        <v>6311159</v>
       </c>
       <c r="S325" t="n">
         <v>5</v>
@@ -44778,10 +44778,10 @@
     </row>
     <row r="326">
       <c r="A326" t="n">
-        <v>122254655</v>
+        <v>122254309</v>
       </c>
       <c r="B326" t="n">
-        <v>56285</v>
+        <v>56280</v>
       </c>
       <c r="C326" t="inlineStr">
         <is>
@@ -44794,21 +44794,21 @@
         </is>
       </c>
       <c r="E326" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
@@ -44832,10 +44832,10 @@
         </is>
       </c>
       <c r="Q326" t="n">
-        <v>586475</v>
+        <v>586456</v>
       </c>
       <c r="R326" t="n">
-        <v>6311187</v>
+        <v>6311158</v>
       </c>
       <c r="S326" t="n">
         <v>5</v>
@@ -44867,7 +44867,7 @@
       </c>
       <c r="Z326" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AA326" t="inlineStr">
@@ -44877,7 +44877,7 @@
       </c>
       <c r="AB326" t="inlineStr">
         <is>
-          <t>22:33</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AC326" t="inlineStr">
@@ -44922,10 +44922,10 @@
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>122254474</v>
+        <v>122254396</v>
       </c>
       <c r="B327" t="n">
-        <v>56266</v>
+        <v>56280</v>
       </c>
       <c r="C327" t="inlineStr">
         <is>
@@ -44934,25 +44934,25 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E327" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
@@ -44976,10 +44976,10 @@
         </is>
       </c>
       <c r="Q327" t="n">
-        <v>586443</v>
+        <v>586408</v>
       </c>
       <c r="R327" t="n">
-        <v>6311164</v>
+        <v>6311124</v>
       </c>
       <c r="S327" t="n">
         <v>5</v>
@@ -45011,7 +45011,7 @@
       </c>
       <c r="Z327" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>22:43</t>
         </is>
       </c>
       <c r="AA327" t="inlineStr">
@@ -45021,7 +45021,7 @@
       </c>
       <c r="AB327" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AC327" t="inlineStr">
@@ -45066,10 +45066,10 @@
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>122254500</v>
+        <v>122254651</v>
       </c>
       <c r="B328" t="n">
-        <v>56266</v>
+        <v>56285</v>
       </c>
       <c r="C328" t="inlineStr">
         <is>
@@ -45078,25 +45078,25 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E328" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
@@ -45120,10 +45120,10 @@
         </is>
       </c>
       <c r="Q328" t="n">
-        <v>586388</v>
+        <v>586425</v>
       </c>
       <c r="R328" t="n">
-        <v>6311142</v>
+        <v>6311113</v>
       </c>
       <c r="S328" t="n">
         <v>5</v>
@@ -45155,7 +45155,7 @@
       </c>
       <c r="Z328" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="AA328" t="inlineStr">
@@ -45165,7 +45165,7 @@
       </c>
       <c r="AB328" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>22:36</t>
         </is>
       </c>
       <c r="AC328" t="inlineStr">
@@ -45210,10 +45210,10 @@
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>122254656</v>
+        <v>122254498</v>
       </c>
       <c r="B329" t="n">
-        <v>56285</v>
+        <v>56266</v>
       </c>
       <c r="C329" t="inlineStr">
         <is>
@@ -45222,25 +45222,25 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E329" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
@@ -45264,10 +45264,10 @@
         </is>
       </c>
       <c r="Q329" t="n">
-        <v>586483</v>
+        <v>586393</v>
       </c>
       <c r="R329" t="n">
-        <v>6311186</v>
+        <v>6311147</v>
       </c>
       <c r="S329" t="n">
         <v>5</v>
@@ -45299,7 +45299,7 @@
       </c>
       <c r="Z329" t="inlineStr">
         <is>
-          <t>22:31</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AA329" t="inlineStr">
@@ -45309,7 +45309,7 @@
       </c>
       <c r="AB329" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AC329" t="inlineStr">
@@ -45354,10 +45354,10 @@
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>122254503</v>
+        <v>122254857</v>
       </c>
       <c r="B330" t="n">
-        <v>56266</v>
+        <v>56283</v>
       </c>
       <c r="C330" t="inlineStr">
         <is>
@@ -45366,25 +45366,25 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E330" t="n">
-        <v>205998</v>
+        <v>100111</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
@@ -45408,10 +45408,10 @@
         </is>
       </c>
       <c r="Q330" t="n">
-        <v>586313</v>
+        <v>586317</v>
       </c>
       <c r="R330" t="n">
-        <v>6311124</v>
+        <v>6311115</v>
       </c>
       <c r="S330" t="n">
         <v>5</v>
@@ -45443,7 +45443,7 @@
       </c>
       <c r="Z330" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>22:57</t>
         </is>
       </c>
       <c r="AA330" t="inlineStr">
@@ -45453,7 +45453,7 @@
       </c>
       <c r="AB330" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>22:58</t>
         </is>
       </c>
       <c r="AC330" t="inlineStr">
@@ -45498,10 +45498,10 @@
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>122254473</v>
+        <v>122254394</v>
       </c>
       <c r="B331" t="n">
-        <v>56266</v>
+        <v>56280</v>
       </c>
       <c r="C331" t="inlineStr">
         <is>
@@ -45510,25 +45510,25 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E331" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I331" t="inlineStr">
@@ -45552,10 +45552,10 @@
         </is>
       </c>
       <c r="Q331" t="n">
-        <v>586450</v>
+        <v>586419</v>
       </c>
       <c r="R331" t="n">
-        <v>6311152</v>
+        <v>6311142</v>
       </c>
       <c r="S331" t="n">
         <v>5</v>
@@ -45587,7 +45587,7 @@
       </c>
       <c r="Z331" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>22:43</t>
         </is>
       </c>
       <c r="AA331" t="inlineStr">
@@ -45597,7 +45597,7 @@
       </c>
       <c r="AB331" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AC331" t="inlineStr">
@@ -45642,32 +45642,32 @@
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>122254173</v>
+        <v>122254313</v>
       </c>
       <c r="B332" t="n">
-        <v>56264</v>
+        <v>56280</v>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Dokumentation efterfrågas</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E332" t="n">
-        <v>100015</v>
+        <v>100092</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>Barbastell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>Barbastella barbastellus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
@@ -45696,10 +45696,10 @@
         </is>
       </c>
       <c r="Q332" t="n">
-        <v>586415</v>
+        <v>586449</v>
       </c>
       <c r="R332" t="n">
-        <v>6311149</v>
+        <v>6311155</v>
       </c>
       <c r="S332" t="n">
         <v>5</v>
@@ -45731,7 +45731,7 @@
       </c>
       <c r="Z332" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA332" t="inlineStr">
@@ -45741,7 +45741,7 @@
       </c>
       <c r="AB332" t="inlineStr">
         <is>
-          <t>23:03</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC332" t="inlineStr">
@@ -45786,10 +45786,10 @@
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>122254312</v>
+        <v>122254658</v>
       </c>
       <c r="B333" t="n">
-        <v>56280</v>
+        <v>56285</v>
       </c>
       <c r="C333" t="inlineStr">
         <is>
@@ -45802,21 +45802,21 @@
         </is>
       </c>
       <c r="E333" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
@@ -45840,10 +45840,10 @@
         </is>
       </c>
       <c r="Q333" t="n">
-        <v>586452</v>
+        <v>586491</v>
       </c>
       <c r="R333" t="n">
-        <v>6311152</v>
+        <v>6311181</v>
       </c>
       <c r="S333" t="n">
         <v>5</v>
@@ -45875,7 +45875,7 @@
       </c>
       <c r="Z333" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>22:31</t>
         </is>
       </c>
       <c r="AA333" t="inlineStr">
@@ -45885,7 +45885,7 @@
       </c>
       <c r="AB333" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AC333" t="inlineStr">
@@ -45930,10 +45930,10 @@
     </row>
     <row r="334">
       <c r="A334" t="n">
-        <v>122254612</v>
+        <v>122254473</v>
       </c>
       <c r="B334" t="n">
-        <v>56285</v>
+        <v>56266</v>
       </c>
       <c r="C334" t="inlineStr">
         <is>
@@ -45942,25 +45942,25 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E334" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
@@ -45984,10 +45984,10 @@
         </is>
       </c>
       <c r="Q334" t="n">
-        <v>586371</v>
+        <v>586450</v>
       </c>
       <c r="R334" t="n">
-        <v>6311135</v>
+        <v>6311152</v>
       </c>
       <c r="S334" t="n">
         <v>5</v>
@@ -46019,7 +46019,7 @@
       </c>
       <c r="Z334" t="inlineStr">
         <is>
-          <t>22:59</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA334" t="inlineStr">
@@ -46029,7 +46029,7 @@
       </c>
       <c r="AB334" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC334" t="inlineStr">
@@ -46074,10 +46074,10 @@
     </row>
     <row r="335">
       <c r="A335" t="n">
-        <v>122254644</v>
+        <v>122254317</v>
       </c>
       <c r="B335" t="n">
-        <v>56285</v>
+        <v>56280</v>
       </c>
       <c r="C335" t="inlineStr">
         <is>
@@ -46090,21 +46090,21 @@
         </is>
       </c>
       <c r="E335" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I335" t="inlineStr">
@@ -46128,10 +46128,10 @@
         </is>
       </c>
       <c r="Q335" t="n">
-        <v>586429</v>
+        <v>586438</v>
       </c>
       <c r="R335" t="n">
-        <v>6311115</v>
+        <v>6311222</v>
       </c>
       <c r="S335" t="n">
         <v>5</v>
@@ -46163,7 +46163,7 @@
       </c>
       <c r="Z335" t="inlineStr">
         <is>
-          <t>22:36</t>
+          <t>23:22</t>
         </is>
       </c>
       <c r="AA335" t="inlineStr">
@@ -46173,7 +46173,7 @@
       </c>
       <c r="AB335" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>23:23</t>
         </is>
       </c>
       <c r="AC335" t="inlineStr">
@@ -46218,7 +46218,7 @@
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>122254646</v>
+        <v>122254653</v>
       </c>
       <c r="B336" t="n">
         <v>56285</v>
@@ -46272,10 +46272,10 @@
         </is>
       </c>
       <c r="Q336" t="n">
-        <v>586422</v>
+        <v>586430</v>
       </c>
       <c r="R336" t="n">
-        <v>6311111</v>
+        <v>6311142</v>
       </c>
       <c r="S336" t="n">
         <v>5</v>
@@ -46307,7 +46307,7 @@
       </c>
       <c r="Z336" t="inlineStr">
         <is>
-          <t>22:36</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="AA336" t="inlineStr">
@@ -46317,7 +46317,7 @@
       </c>
       <c r="AB336" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>22:34</t>
         </is>
       </c>
       <c r="AC336" t="inlineStr">
@@ -46362,7 +46362,7 @@
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>122254616</v>
+        <v>122254632</v>
       </c>
       <c r="B337" t="n">
         <v>56285</v>
@@ -46416,10 +46416,10 @@
         </is>
       </c>
       <c r="Q337" t="n">
-        <v>586327</v>
+        <v>586374</v>
       </c>
       <c r="R337" t="n">
-        <v>6311118</v>
+        <v>6311140</v>
       </c>
       <c r="S337" t="n">
         <v>5</v>
@@ -46451,7 +46451,7 @@
       </c>
       <c r="Z337" t="inlineStr">
         <is>
-          <t>22:57</t>
+          <t>22:46</t>
         </is>
       </c>
       <c r="AA337" t="inlineStr">
@@ -46461,7 +46461,7 @@
       </c>
       <c r="AB337" t="inlineStr">
         <is>
-          <t>22:58</t>
+          <t>22:47</t>
         </is>
       </c>
       <c r="AC337" t="inlineStr">
@@ -46506,7 +46506,7 @@
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>122254654</v>
+        <v>122254657</v>
       </c>
       <c r="B338" t="n">
         <v>56285</v>
@@ -46560,10 +46560,10 @@
         </is>
       </c>
       <c r="Q338" t="n">
-        <v>586467</v>
+        <v>586488</v>
       </c>
       <c r="R338" t="n">
-        <v>6311178</v>
+        <v>6311184</v>
       </c>
       <c r="S338" t="n">
         <v>5</v>
@@ -46595,17 +46595,17 @@
       </c>
       <c r="Z338" t="inlineStr">
         <is>
+          <t>22:31</t>
+        </is>
+      </c>
+      <c r="AA338" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AB338" t="inlineStr">
+        <is>
           <t>22:32</t>
-        </is>
-      </c>
-      <c r="AA338" t="inlineStr">
-        <is>
-          <t>2024-06-26</t>
-        </is>
-      </c>
-      <c r="AB338" t="inlineStr">
-        <is>
-          <t>22:33</t>
         </is>
       </c>
       <c r="AC338" t="inlineStr">
@@ -46650,7 +46650,7 @@
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>122254606</v>
+        <v>122254652</v>
       </c>
       <c r="B339" t="n">
         <v>56285</v>
@@ -46704,10 +46704,10 @@
         </is>
       </c>
       <c r="Q339" t="n">
-        <v>586415</v>
+        <v>586432</v>
       </c>
       <c r="R339" t="n">
-        <v>6311146</v>
+        <v>6311118</v>
       </c>
       <c r="S339" t="n">
         <v>5</v>
@@ -46739,7 +46739,7 @@
       </c>
       <c r="Z339" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>22:34</t>
         </is>
       </c>
       <c r="AA339" t="inlineStr">
@@ -46749,7 +46749,7 @@
       </c>
       <c r="AB339" t="inlineStr">
         <is>
-          <t>23:03</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="AC339" t="inlineStr">
@@ -46794,10 +46794,10 @@
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>122254499</v>
+        <v>122254608</v>
       </c>
       <c r="B340" t="n">
-        <v>56266</v>
+        <v>56285</v>
       </c>
       <c r="C340" t="inlineStr">
         <is>
@@ -46806,25 +46806,25 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E340" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
@@ -46848,7 +46848,7 @@
         </is>
       </c>
       <c r="Q340" t="n">
-        <v>586392</v>
+        <v>586393</v>
       </c>
       <c r="R340" t="n">
         <v>6311147</v>
@@ -46938,10 +46938,10 @@
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>122254421</v>
+        <v>122254634</v>
       </c>
       <c r="B341" t="n">
-        <v>56280</v>
+        <v>56285</v>
       </c>
       <c r="C341" t="inlineStr">
         <is>
@@ -46954,21 +46954,21 @@
         </is>
       </c>
       <c r="E341" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I341" t="inlineStr">
@@ -46992,10 +46992,10 @@
         </is>
       </c>
       <c r="Q341" t="n">
-        <v>586468</v>
+        <v>586415</v>
       </c>
       <c r="R341" t="n">
-        <v>6311181</v>
+        <v>6311148</v>
       </c>
       <c r="S341" t="n">
         <v>5</v>
@@ -47027,7 +47027,7 @@
       </c>
       <c r="Z341" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AA341" t="inlineStr">
@@ -47037,7 +47037,7 @@
       </c>
       <c r="AB341" t="inlineStr">
         <is>
-          <t>22:33</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AC341" t="inlineStr">
@@ -47082,10 +47082,10 @@
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>122254952</v>
+        <v>122254606</v>
       </c>
       <c r="B342" t="n">
-        <v>56273</v>
+        <v>56285</v>
       </c>
       <c r="C342" t="inlineStr">
         <is>
@@ -47098,21 +47098,21 @@
         </is>
       </c>
       <c r="E342" t="n">
-        <v>205992</v>
+        <v>205995</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
@@ -47136,10 +47136,10 @@
         </is>
       </c>
       <c r="Q342" t="n">
-        <v>586455</v>
+        <v>586415</v>
       </c>
       <c r="R342" t="n">
-        <v>6311156</v>
+        <v>6311146</v>
       </c>
       <c r="S342" t="n">
         <v>5</v>
@@ -47171,7 +47171,7 @@
       </c>
       <c r="Z342" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AA342" t="inlineStr">
@@ -47181,7 +47181,7 @@
       </c>
       <c r="AB342" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>23:03</t>
         </is>
       </c>
       <c r="AC342" t="inlineStr">
@@ -47226,10 +47226,10 @@
     </row>
     <row r="343">
       <c r="A343" t="n">
-        <v>122254514</v>
+        <v>122254391</v>
       </c>
       <c r="B343" t="n">
-        <v>56266</v>
+        <v>56280</v>
       </c>
       <c r="C343" t="inlineStr">
         <is>
@@ -47238,25 +47238,25 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E343" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
@@ -47280,10 +47280,10 @@
         </is>
       </c>
       <c r="Q343" t="n">
-        <v>586408</v>
+        <v>586379</v>
       </c>
       <c r="R343" t="n">
-        <v>6311124</v>
+        <v>6311136</v>
       </c>
       <c r="S343" t="n">
         <v>5</v>
@@ -47315,7 +47315,7 @@
       </c>
       <c r="Z343" t="inlineStr">
         <is>
-          <t>22:43</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AA343" t="inlineStr">
@@ -47325,7 +47325,7 @@
       </c>
       <c r="AB343" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>22:46</t>
         </is>
       </c>
       <c r="AC343" t="inlineStr">
@@ -47370,10 +47370,10 @@
     </row>
     <row r="344">
       <c r="A344" t="n">
-        <v>122254496</v>
+        <v>122254855</v>
       </c>
       <c r="B344" t="n">
-        <v>56266</v>
+        <v>56283</v>
       </c>
       <c r="C344" t="inlineStr">
         <is>
@@ -47382,25 +47382,25 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E344" t="n">
-        <v>205998</v>
+        <v>100111</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
@@ -47424,10 +47424,10 @@
         </is>
       </c>
       <c r="Q344" t="n">
-        <v>586415</v>
+        <v>586330</v>
       </c>
       <c r="R344" t="n">
-        <v>6311146</v>
+        <v>6311120</v>
       </c>
       <c r="S344" t="n">
         <v>5</v>
@@ -47459,7 +47459,7 @@
       </c>
       <c r="Z344" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>22:57</t>
         </is>
       </c>
       <c r="AA344" t="inlineStr">
@@ -47469,7 +47469,7 @@
       </c>
       <c r="AB344" t="inlineStr">
         <is>
-          <t>23:03</t>
+          <t>22:58</t>
         </is>
       </c>
       <c r="AC344" t="inlineStr">
@@ -47514,10 +47514,10 @@
     </row>
     <row r="345">
       <c r="A345" t="n">
-        <v>122254660</v>
+        <v>122254837</v>
       </c>
       <c r="B345" t="n">
-        <v>56285</v>
+        <v>56283</v>
       </c>
       <c r="C345" t="inlineStr">
         <is>
@@ -47530,21 +47530,21 @@
         </is>
       </c>
       <c r="E345" t="n">
-        <v>205995</v>
+        <v>100111</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
@@ -47568,10 +47568,10 @@
         </is>
       </c>
       <c r="Q345" t="n">
-        <v>586488</v>
+        <v>586448</v>
       </c>
       <c r="R345" t="n">
-        <v>6311183</v>
+        <v>6311154</v>
       </c>
       <c r="S345" t="n">
         <v>5</v>
@@ -47603,7 +47603,7 @@
       </c>
       <c r="Z345" t="inlineStr">
         <is>
-          <t>22:31</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA345" t="inlineStr">
@@ -47613,7 +47613,7 @@
       </c>
       <c r="AB345" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC345" t="inlineStr">
@@ -47658,10 +47658,10 @@
     </row>
     <row r="346">
       <c r="A346" t="n">
-        <v>122254651</v>
+        <v>122254412</v>
       </c>
       <c r="B346" t="n">
-        <v>56285</v>
+        <v>56280</v>
       </c>
       <c r="C346" t="inlineStr">
         <is>
@@ -47674,21 +47674,21 @@
         </is>
       </c>
       <c r="E346" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
@@ -47712,10 +47712,10 @@
         </is>
       </c>
       <c r="Q346" t="n">
-        <v>586425</v>
+        <v>586424</v>
       </c>
       <c r="R346" t="n">
-        <v>6311113</v>
+        <v>6311135</v>
       </c>
       <c r="S346" t="n">
         <v>5</v>
@@ -47747,7 +47747,7 @@
       </c>
       <c r="Z346" t="inlineStr">
         <is>
-          <t>22:35</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AA346" t="inlineStr">
@@ -47757,7 +47757,7 @@
       </c>
       <c r="AB346" t="inlineStr">
         <is>
-          <t>22:36</t>
+          <t>22:38</t>
         </is>
       </c>
       <c r="AC346" t="inlineStr">
@@ -47946,10 +47946,10 @@
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>122254878</v>
+        <v>122254318</v>
       </c>
       <c r="B348" t="n">
-        <v>56283</v>
+        <v>56280</v>
       </c>
       <c r="C348" t="inlineStr">
         <is>
@@ -47962,21 +47962,21 @@
         </is>
       </c>
       <c r="E348" t="n">
-        <v>100111</v>
+        <v>100092</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I348" t="inlineStr">
@@ -48000,10 +48000,10 @@
         </is>
       </c>
       <c r="Q348" t="n">
-        <v>586280</v>
+        <v>586455</v>
       </c>
       <c r="R348" t="n">
-        <v>6311103</v>
+        <v>6311228</v>
       </c>
       <c r="S348" t="n">
         <v>5</v>
@@ -48035,7 +48035,7 @@
       </c>
       <c r="Z348" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>23:22</t>
         </is>
       </c>
       <c r="AA348" t="inlineStr">
@@ -48045,7 +48045,7 @@
       </c>
       <c r="AB348" t="inlineStr">
         <is>
-          <t>22:52</t>
+          <t>23:23</t>
         </is>
       </c>
       <c r="AC348" t="inlineStr">
@@ -48090,10 +48090,10 @@
     </row>
     <row r="349">
       <c r="A349" t="n">
-        <v>122254584</v>
+        <v>122254310</v>
       </c>
       <c r="B349" t="n">
-        <v>56285</v>
+        <v>56280</v>
       </c>
       <c r="C349" t="inlineStr">
         <is>
@@ -48106,21 +48106,21 @@
         </is>
       </c>
       <c r="E349" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I349" t="inlineStr">
@@ -48144,10 +48144,10 @@
         </is>
       </c>
       <c r="Q349" t="n">
-        <v>586473</v>
+        <v>586452</v>
       </c>
       <c r="R349" t="n">
-        <v>6311192</v>
+        <v>6311156</v>
       </c>
       <c r="S349" t="n">
         <v>5</v>
@@ -48179,7 +48179,7 @@
       </c>
       <c r="Z349" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA349" t="inlineStr">
@@ -48189,7 +48189,7 @@
       </c>
       <c r="AB349" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC349" t="inlineStr">
@@ -48234,7 +48234,7 @@
     </row>
     <row r="350">
       <c r="A350" t="n">
-        <v>122254617</v>
+        <v>122254655</v>
       </c>
       <c r="B350" t="n">
         <v>56285</v>
@@ -48288,10 +48288,10 @@
         </is>
       </c>
       <c r="Q350" t="n">
-        <v>586317</v>
+        <v>586475</v>
       </c>
       <c r="R350" t="n">
-        <v>6311115</v>
+        <v>6311187</v>
       </c>
       <c r="S350" t="n">
         <v>5</v>
@@ -48323,7 +48323,7 @@
       </c>
       <c r="Z350" t="inlineStr">
         <is>
-          <t>22:57</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AA350" t="inlineStr">
@@ -48333,7 +48333,7 @@
       </c>
       <c r="AB350" t="inlineStr">
         <is>
-          <t>22:58</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="AC350" t="inlineStr">
@@ -48378,7 +48378,7 @@
     </row>
     <row r="351">
       <c r="A351" t="n">
-        <v>122254611</v>
+        <v>122254654</v>
       </c>
       <c r="B351" t="n">
         <v>56285</v>
@@ -48432,10 +48432,10 @@
         </is>
       </c>
       <c r="Q351" t="n">
-        <v>586370</v>
+        <v>586467</v>
       </c>
       <c r="R351" t="n">
-        <v>6311139</v>
+        <v>6311178</v>
       </c>
       <c r="S351" t="n">
         <v>5</v>
@@ -48467,7 +48467,7 @@
       </c>
       <c r="Z351" t="inlineStr">
         <is>
-          <t>22:59</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AA351" t="inlineStr">
@@ -48477,7 +48477,7 @@
       </c>
       <c r="AB351" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="AC351" t="inlineStr">
@@ -48522,10 +48522,10 @@
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>122254511</v>
+        <v>122254627</v>
       </c>
       <c r="B352" t="n">
-        <v>56266</v>
+        <v>56285</v>
       </c>
       <c r="C352" t="inlineStr">
         <is>
@@ -48534,25 +48534,25 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E352" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I352" t="inlineStr">
@@ -48576,10 +48576,10 @@
         </is>
       </c>
       <c r="Q352" t="n">
-        <v>586374</v>
+        <v>586306</v>
       </c>
       <c r="R352" t="n">
-        <v>6311139</v>
+        <v>6311131</v>
       </c>
       <c r="S352" t="n">
         <v>5</v>
@@ -48611,7 +48611,7 @@
       </c>
       <c r="Z352" t="inlineStr">
         <is>
-          <t>22:46</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AA352" t="inlineStr">
@@ -48621,7 +48621,7 @@
       </c>
       <c r="AB352" t="inlineStr">
         <is>
-          <t>22:47</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AC352" t="inlineStr">
@@ -48666,10 +48666,10 @@
     </row>
     <row r="353">
       <c r="A353" t="n">
-        <v>122254513</v>
+        <v>122254959</v>
       </c>
       <c r="B353" t="n">
-        <v>56266</v>
+        <v>56273</v>
       </c>
       <c r="C353" t="inlineStr">
         <is>
@@ -48678,25 +48678,25 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E353" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I353" t="inlineStr">
@@ -48720,10 +48720,10 @@
         </is>
       </c>
       <c r="Q353" t="n">
-        <v>586396</v>
+        <v>586370</v>
       </c>
       <c r="R353" t="n">
-        <v>6311146</v>
+        <v>6311139</v>
       </c>
       <c r="S353" t="n">
         <v>5</v>
@@ -48755,7 +48755,7 @@
       </c>
       <c r="Z353" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>22:59</t>
         </is>
       </c>
       <c r="AA353" t="inlineStr">
@@ -48765,7 +48765,7 @@
       </c>
       <c r="AB353" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AC353" t="inlineStr">
@@ -48810,10 +48810,10 @@
     </row>
     <row r="354">
       <c r="A354" t="n">
-        <v>122254476</v>
+        <v>122254372</v>
       </c>
       <c r="B354" t="n">
-        <v>56266</v>
+        <v>56280</v>
       </c>
       <c r="C354" t="inlineStr">
         <is>
@@ -48822,25 +48822,25 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E354" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I354" t="inlineStr">
@@ -48864,10 +48864,10 @@
         </is>
       </c>
       <c r="Q354" t="n">
-        <v>586418</v>
+        <v>586306</v>
       </c>
       <c r="R354" t="n">
-        <v>6311167</v>
+        <v>6311131</v>
       </c>
       <c r="S354" t="n">
         <v>5</v>
@@ -48899,7 +48899,7 @@
       </c>
       <c r="Z354" t="inlineStr">
         <is>
-          <t>23:23</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AA354" t="inlineStr">
@@ -48909,7 +48909,7 @@
       </c>
       <c r="AB354" t="inlineStr">
         <is>
-          <t>23:24</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AC354" t="inlineStr">
@@ -48954,10 +48954,10 @@
     </row>
     <row r="355">
       <c r="A355" t="n">
-        <v>122254854</v>
+        <v>122254352</v>
       </c>
       <c r="B355" t="n">
-        <v>56283</v>
+        <v>56280</v>
       </c>
       <c r="C355" t="inlineStr">
         <is>
@@ -48970,21 +48970,21 @@
         </is>
       </c>
       <c r="E355" t="n">
-        <v>100111</v>
+        <v>100092</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I355" t="inlineStr">
@@ -49008,10 +49008,10 @@
         </is>
       </c>
       <c r="Q355" t="n">
-        <v>586329</v>
+        <v>586288</v>
       </c>
       <c r="R355" t="n">
-        <v>6311120</v>
+        <v>6311100</v>
       </c>
       <c r="S355" t="n">
         <v>5</v>
@@ -49043,7 +49043,7 @@
       </c>
       <c r="Z355" t="inlineStr">
         <is>
-          <t>22:57</t>
+          <t>22:55</t>
         </is>
       </c>
       <c r="AA355" t="inlineStr">
@@ -49053,7 +49053,7 @@
       </c>
       <c r="AB355" t="inlineStr">
         <is>
-          <t>22:58</t>
+          <t>22:56</t>
         </is>
       </c>
       <c r="AC355" t="inlineStr">
@@ -49098,7 +49098,7 @@
     </row>
     <row r="356">
       <c r="A356" t="n">
-        <v>122254373</v>
+        <v>122254392</v>
       </c>
       <c r="B356" t="n">
         <v>56280</v>
@@ -49152,10 +49152,10 @@
         </is>
       </c>
       <c r="Q356" t="n">
-        <v>586307</v>
+        <v>586384</v>
       </c>
       <c r="R356" t="n">
-        <v>6311133</v>
+        <v>6311139</v>
       </c>
       <c r="S356" t="n">
         <v>5</v>
@@ -49187,7 +49187,7 @@
       </c>
       <c r="Z356" t="inlineStr">
         <is>
-          <t>22:49</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AA356" t="inlineStr">
@@ -49197,7 +49197,7 @@
       </c>
       <c r="AB356" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>22:46</t>
         </is>
       </c>
       <c r="AC356" t="inlineStr">
@@ -49242,7 +49242,7 @@
     </row>
     <row r="357">
       <c r="A357" t="n">
-        <v>122254391</v>
+        <v>122254315</v>
       </c>
       <c r="B357" t="n">
         <v>56280</v>
@@ -49296,10 +49296,10 @@
         </is>
       </c>
       <c r="Q357" t="n">
-        <v>586379</v>
+        <v>586441</v>
       </c>
       <c r="R357" t="n">
-        <v>6311136</v>
+        <v>6311155</v>
       </c>
       <c r="S357" t="n">
         <v>5</v>
@@ -49331,7 +49331,7 @@
       </c>
       <c r="Z357" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AA357" t="inlineStr">
@@ -49341,7 +49341,7 @@
       </c>
       <c r="AB357" t="inlineStr">
         <is>
-          <t>22:46</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AC357" t="inlineStr">
@@ -49386,10 +49386,10 @@
     </row>
     <row r="358">
       <c r="A358" t="n">
-        <v>122254369</v>
+        <v>122254513</v>
       </c>
       <c r="B358" t="n">
-        <v>56280</v>
+        <v>56266</v>
       </c>
       <c r="C358" t="inlineStr">
         <is>
@@ -49398,25 +49398,25 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E358" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H358" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I358" t="inlineStr">
@@ -49440,10 +49440,10 @@
         </is>
       </c>
       <c r="Q358" t="n">
-        <v>586300</v>
+        <v>586396</v>
       </c>
       <c r="R358" t="n">
-        <v>6311112</v>
+        <v>6311146</v>
       </c>
       <c r="S358" t="n">
         <v>5</v>
@@ -49475,7 +49475,7 @@
       </c>
       <c r="Z358" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AA358" t="inlineStr">
@@ -49485,7 +49485,7 @@
       </c>
       <c r="AB358" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AC358" t="inlineStr">
@@ -49530,10 +49530,10 @@
     </row>
     <row r="359">
       <c r="A359" t="n">
-        <v>122254877</v>
+        <v>122254511</v>
       </c>
       <c r="B359" t="n">
-        <v>56283</v>
+        <v>56266</v>
       </c>
       <c r="C359" t="inlineStr">
         <is>
@@ -49542,25 +49542,25 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E359" t="n">
-        <v>100111</v>
+        <v>205998</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I359" t="inlineStr">
@@ -49584,10 +49584,10 @@
         </is>
       </c>
       <c r="Q359" t="n">
-        <v>586276</v>
+        <v>586374</v>
       </c>
       <c r="R359" t="n">
-        <v>6311100</v>
+        <v>6311139</v>
       </c>
       <c r="S359" t="n">
         <v>5</v>
@@ -49619,7 +49619,7 @@
       </c>
       <c r="Z359" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>22:46</t>
         </is>
       </c>
       <c r="AA359" t="inlineStr">
@@ -49629,7 +49629,7 @@
       </c>
       <c r="AB359" t="inlineStr">
         <is>
-          <t>22:52</t>
+          <t>22:47</t>
         </is>
       </c>
       <c r="AC359" t="inlineStr">
@@ -49674,10 +49674,10 @@
     </row>
     <row r="360">
       <c r="A360" t="n">
-        <v>122254392</v>
+        <v>122254609</v>
       </c>
       <c r="B360" t="n">
-        <v>56280</v>
+        <v>56285</v>
       </c>
       <c r="C360" t="inlineStr">
         <is>
@@ -49690,21 +49690,21 @@
         </is>
       </c>
       <c r="E360" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I360" t="inlineStr">
@@ -49728,10 +49728,10 @@
         </is>
       </c>
       <c r="Q360" t="n">
-        <v>586384</v>
+        <v>586392</v>
       </c>
       <c r="R360" t="n">
-        <v>6311139</v>
+        <v>6311147</v>
       </c>
       <c r="S360" t="n">
         <v>5</v>
@@ -49763,7 +49763,7 @@
       </c>
       <c r="Z360" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AA360" t="inlineStr">
@@ -49773,7 +49773,7 @@
       </c>
       <c r="AB360" t="inlineStr">
         <is>
-          <t>22:46</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AC360" t="inlineStr">
@@ -49818,10 +49818,10 @@
     </row>
     <row r="361">
       <c r="A361" t="n">
-        <v>122254951</v>
+        <v>122254656</v>
       </c>
       <c r="B361" t="n">
-        <v>56273</v>
+        <v>56285</v>
       </c>
       <c r="C361" t="inlineStr">
         <is>
@@ -49834,21 +49834,21 @@
         </is>
       </c>
       <c r="E361" t="n">
-        <v>205992</v>
+        <v>205995</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I361" t="inlineStr">
@@ -49872,10 +49872,10 @@
         </is>
       </c>
       <c r="Q361" t="n">
-        <v>586459</v>
+        <v>586483</v>
       </c>
       <c r="R361" t="n">
-        <v>6311154</v>
+        <v>6311186</v>
       </c>
       <c r="S361" t="n">
         <v>5</v>
@@ -49907,7 +49907,7 @@
       </c>
       <c r="Z361" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>22:31</t>
         </is>
       </c>
       <c r="AA361" t="inlineStr">
@@ -49917,7 +49917,7 @@
       </c>
       <c r="AB361" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AC361" t="inlineStr">
@@ -49962,7 +49962,7 @@
     </row>
     <row r="362">
       <c r="A362" t="n">
-        <v>122254626</v>
+        <v>122254616</v>
       </c>
       <c r="B362" t="n">
         <v>56285</v>
@@ -50016,10 +50016,10 @@
         </is>
       </c>
       <c r="Q362" t="n">
-        <v>586313</v>
+        <v>586327</v>
       </c>
       <c r="R362" t="n">
-        <v>6311124</v>
+        <v>6311118</v>
       </c>
       <c r="S362" t="n">
         <v>5</v>
@@ -50051,7 +50051,7 @@
       </c>
       <c r="Z362" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>22:57</t>
         </is>
       </c>
       <c r="AA362" t="inlineStr">
@@ -50061,7 +50061,7 @@
       </c>
       <c r="AB362" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>22:58</t>
         </is>
       </c>
       <c r="AC362" t="inlineStr">
@@ -50106,10 +50106,10 @@
     </row>
     <row r="363">
       <c r="A363" t="n">
-        <v>122254637</v>
+        <v>122254421</v>
       </c>
       <c r="B363" t="n">
-        <v>56285</v>
+        <v>56280</v>
       </c>
       <c r="C363" t="inlineStr">
         <is>
@@ -50122,21 +50122,21 @@
         </is>
       </c>
       <c r="E363" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I363" t="inlineStr">
@@ -50160,10 +50160,10 @@
         </is>
       </c>
       <c r="Q363" t="n">
-        <v>586408</v>
+        <v>586468</v>
       </c>
       <c r="R363" t="n">
-        <v>6311124</v>
+        <v>6311181</v>
       </c>
       <c r="S363" t="n">
         <v>5</v>
@@ -50195,7 +50195,7 @@
       </c>
       <c r="Z363" t="inlineStr">
         <is>
-          <t>22:43</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AA363" t="inlineStr">
@@ -50205,7 +50205,7 @@
       </c>
       <c r="AB363" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="AC363" t="inlineStr">
@@ -50250,10 +50250,10 @@
     </row>
     <row r="364">
       <c r="A364" t="n">
-        <v>122254512</v>
+        <v>122254373</v>
       </c>
       <c r="B364" t="n">
-        <v>56266</v>
+        <v>56280</v>
       </c>
       <c r="C364" t="inlineStr">
         <is>
@@ -50262,25 +50262,25 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E364" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I364" t="inlineStr">
@@ -50304,10 +50304,10 @@
         </is>
       </c>
       <c r="Q364" t="n">
-        <v>586379</v>
+        <v>586307</v>
       </c>
       <c r="R364" t="n">
-        <v>6311136</v>
+        <v>6311133</v>
       </c>
       <c r="S364" t="n">
         <v>5</v>
@@ -50339,7 +50339,7 @@
       </c>
       <c r="Z364" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>22:49</t>
         </is>
       </c>
       <c r="AA364" t="inlineStr">
@@ -50349,7 +50349,7 @@
       </c>
       <c r="AB364" t="inlineStr">
         <is>
-          <t>22:46</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AC364" t="inlineStr">
@@ -50394,7 +50394,7 @@
     </row>
     <row r="365">
       <c r="A365" t="n">
-        <v>122254352</v>
+        <v>122254314</v>
       </c>
       <c r="B365" t="n">
         <v>56280</v>
@@ -50448,10 +50448,10 @@
         </is>
       </c>
       <c r="Q365" t="n">
-        <v>586288</v>
+        <v>586443</v>
       </c>
       <c r="R365" t="n">
-        <v>6311100</v>
+        <v>6311164</v>
       </c>
       <c r="S365" t="n">
         <v>5</v>
@@ -50483,7 +50483,7 @@
       </c>
       <c r="Z365" t="inlineStr">
         <is>
-          <t>22:55</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AA365" t="inlineStr">
@@ -50493,7 +50493,7 @@
       </c>
       <c r="AB365" t="inlineStr">
         <is>
-          <t>22:56</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AC365" t="inlineStr">
@@ -50538,10 +50538,10 @@
     </row>
     <row r="366">
       <c r="A366" t="n">
-        <v>122254367</v>
+        <v>122254954</v>
       </c>
       <c r="B366" t="n">
-        <v>56280</v>
+        <v>56273</v>
       </c>
       <c r="C366" t="inlineStr">
         <is>
@@ -50554,21 +50554,21 @@
         </is>
       </c>
       <c r="E366" t="n">
-        <v>100092</v>
+        <v>205992</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I366" t="inlineStr">
@@ -50592,10 +50592,10 @@
         </is>
       </c>
       <c r="Q366" t="n">
-        <v>586280</v>
+        <v>586442</v>
       </c>
       <c r="R366" t="n">
-        <v>6311103</v>
+        <v>6311152</v>
       </c>
       <c r="S366" t="n">
         <v>5</v>
@@ -50627,7 +50627,7 @@
       </c>
       <c r="Z366" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AA366" t="inlineStr">
@@ -50637,7 +50637,7 @@
       </c>
       <c r="AB366" t="inlineStr">
         <is>
-          <t>22:52</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AC366" t="inlineStr">
@@ -50682,10 +50682,10 @@
     </row>
     <row r="367">
       <c r="A367" t="n">
-        <v>122254843</v>
+        <v>122254500</v>
       </c>
       <c r="B367" t="n">
-        <v>56283</v>
+        <v>56266</v>
       </c>
       <c r="C367" t="inlineStr">
         <is>
@@ -50694,25 +50694,25 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E367" t="n">
-        <v>100111</v>
+        <v>205998</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I367" t="inlineStr">
@@ -50736,7 +50736,7 @@
         </is>
       </c>
       <c r="Q367" t="n">
-        <v>586389</v>
+        <v>586388</v>
       </c>
       <c r="R367" t="n">
         <v>6311142</v>
@@ -50826,7 +50826,7 @@
     </row>
     <row r="368">
       <c r="A368" t="n">
-        <v>122254632</v>
+        <v>122254607</v>
       </c>
       <c r="B368" t="n">
         <v>56285</v>
@@ -50880,10 +50880,10 @@
         </is>
       </c>
       <c r="Q368" t="n">
-        <v>586374</v>
+        <v>586415</v>
       </c>
       <c r="R368" t="n">
-        <v>6311140</v>
+        <v>6311149</v>
       </c>
       <c r="S368" t="n">
         <v>5</v>
@@ -50915,7 +50915,7 @@
       </c>
       <c r="Z368" t="inlineStr">
         <is>
-          <t>22:46</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AA368" t="inlineStr">
@@ -50925,7 +50925,7 @@
       </c>
       <c r="AB368" t="inlineStr">
         <is>
-          <t>22:47</t>
+          <t>23:03</t>
         </is>
       </c>
       <c r="AC368" t="inlineStr">
@@ -50970,10 +50970,10 @@
     </row>
     <row r="369">
       <c r="A369" t="n">
-        <v>122254966</v>
+        <v>122254880</v>
       </c>
       <c r="B369" t="n">
-        <v>56273</v>
+        <v>56283</v>
       </c>
       <c r="C369" t="inlineStr">
         <is>
@@ -50986,21 +50986,21 @@
         </is>
       </c>
       <c r="E369" t="n">
-        <v>205992</v>
+        <v>100111</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I369" t="inlineStr">
@@ -51024,10 +51024,10 @@
         </is>
       </c>
       <c r="Q369" t="n">
-        <v>586467</v>
+        <v>586303</v>
       </c>
       <c r="R369" t="n">
-        <v>6311178</v>
+        <v>6311115</v>
       </c>
       <c r="S369" t="n">
         <v>5</v>
@@ -51059,7 +51059,7 @@
       </c>
       <c r="Z369" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AA369" t="inlineStr">
@@ -51069,7 +51069,7 @@
       </c>
       <c r="AB369" t="inlineStr">
         <is>
-          <t>22:33</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AC369" t="inlineStr">
@@ -51114,10 +51114,10 @@
     </row>
     <row r="370">
       <c r="A370" t="n">
-        <v>122254415</v>
+        <v>122254835</v>
       </c>
       <c r="B370" t="n">
-        <v>56280</v>
+        <v>56283</v>
       </c>
       <c r="C370" t="inlineStr">
         <is>
@@ -51130,21 +51130,21 @@
         </is>
       </c>
       <c r="E370" t="n">
-        <v>100092</v>
+        <v>100111</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I370" t="inlineStr">
@@ -51168,10 +51168,10 @@
         </is>
       </c>
       <c r="Q370" t="n">
-        <v>586425</v>
+        <v>586473</v>
       </c>
       <c r="R370" t="n">
-        <v>6311135</v>
+        <v>6311192</v>
       </c>
       <c r="S370" t="n">
         <v>5</v>
@@ -51203,7 +51203,7 @@
       </c>
       <c r="Z370" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AA370" t="inlineStr">
@@ -51213,7 +51213,7 @@
       </c>
       <c r="AB370" t="inlineStr">
         <is>
-          <t>22:38</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AC370" t="inlineStr">
@@ -51258,7 +51258,7 @@
     </row>
     <row r="371">
       <c r="A371" t="n">
-        <v>122254836</v>
+        <v>122254844</v>
       </c>
       <c r="B371" t="n">
         <v>56283</v>
@@ -51312,10 +51312,10 @@
         </is>
       </c>
       <c r="Q371" t="n">
-        <v>586474</v>
+        <v>586387</v>
       </c>
       <c r="R371" t="n">
-        <v>6311176</v>
+        <v>6311141</v>
       </c>
       <c r="S371" t="n">
         <v>5</v>
@@ -51347,7 +51347,7 @@
       </c>
       <c r="Z371" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA371" t="inlineStr">
@@ -51357,7 +51357,7 @@
       </c>
       <c r="AB371" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AC371" t="inlineStr">
@@ -51402,7 +51402,7 @@
     </row>
     <row r="372">
       <c r="A372" t="n">
-        <v>122254625</v>
+        <v>122254584</v>
       </c>
       <c r="B372" t="n">
         <v>56285</v>
@@ -51456,10 +51456,10 @@
         </is>
       </c>
       <c r="Q372" t="n">
-        <v>586309</v>
+        <v>586473</v>
       </c>
       <c r="R372" t="n">
-        <v>6311119</v>
+        <v>6311192</v>
       </c>
       <c r="S372" t="n">
         <v>5</v>
@@ -51491,7 +51491,7 @@
       </c>
       <c r="Z372" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AA372" t="inlineStr">
@@ -51501,7 +51501,7 @@
       </c>
       <c r="AB372" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AC372" t="inlineStr">
@@ -51546,7 +51546,7 @@
     </row>
     <row r="373">
       <c r="A373" t="n">
-        <v>122254607</v>
+        <v>122254612</v>
       </c>
       <c r="B373" t="n">
         <v>56285</v>
@@ -51600,10 +51600,10 @@
         </is>
       </c>
       <c r="Q373" t="n">
-        <v>586415</v>
+        <v>586371</v>
       </c>
       <c r="R373" t="n">
-        <v>6311149</v>
+        <v>6311135</v>
       </c>
       <c r="S373" t="n">
         <v>5</v>
@@ -51635,7 +51635,7 @@
       </c>
       <c r="Z373" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>22:59</t>
         </is>
       </c>
       <c r="AA373" t="inlineStr">
@@ -51645,7 +51645,7 @@
       </c>
       <c r="AB373" t="inlineStr">
         <is>
-          <t>23:03</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AC373" t="inlineStr">
@@ -51690,10 +51690,10 @@
     </row>
     <row r="374">
       <c r="A374" t="n">
-        <v>122254587</v>
+        <v>122254956</v>
       </c>
       <c r="B374" t="n">
-        <v>56285</v>
+        <v>56273</v>
       </c>
       <c r="C374" t="inlineStr">
         <is>
@@ -51706,21 +51706,21 @@
         </is>
       </c>
       <c r="E374" t="n">
-        <v>205995</v>
+        <v>205992</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I374" t="inlineStr">
@@ -51744,10 +51744,10 @@
         </is>
       </c>
       <c r="Q374" t="n">
-        <v>586443</v>
+        <v>586441</v>
       </c>
       <c r="R374" t="n">
-        <v>6311163</v>
+        <v>6311152</v>
       </c>
       <c r="S374" t="n">
         <v>5</v>
@@ -51779,17 +51779,17 @@
       </c>
       <c r="Z374" t="inlineStr">
         <is>
+          <t>23:25</t>
+        </is>
+      </c>
+      <c r="AA374" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AB374" t="inlineStr">
+        <is>
           <t>23:26</t>
-        </is>
-      </c>
-      <c r="AA374" t="inlineStr">
-        <is>
-          <t>2024-06-26</t>
-        </is>
-      </c>
-      <c r="AB374" t="inlineStr">
-        <is>
-          <t>23:27</t>
         </is>
       </c>
       <c r="AC374" t="inlineStr">
@@ -51978,7 +51978,7 @@
     </row>
     <row r="376">
       <c r="A376" t="n">
-        <v>122254608</v>
+        <v>122254611</v>
       </c>
       <c r="B376" t="n">
         <v>56285</v>
@@ -52032,10 +52032,10 @@
         </is>
       </c>
       <c r="Q376" t="n">
-        <v>586393</v>
+        <v>586370</v>
       </c>
       <c r="R376" t="n">
-        <v>6311147</v>
+        <v>6311139</v>
       </c>
       <c r="S376" t="n">
         <v>5</v>
@@ -52067,7 +52067,7 @@
       </c>
       <c r="Z376" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>22:59</t>
         </is>
       </c>
       <c r="AA376" t="inlineStr">
@@ -52077,7 +52077,7 @@
       </c>
       <c r="AB376" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AC376" t="inlineStr">
@@ -52122,10 +52122,10 @@
     </row>
     <row r="377">
       <c r="A377" t="n">
-        <v>122254498</v>
+        <v>122254367</v>
       </c>
       <c r="B377" t="n">
-        <v>56266</v>
+        <v>56280</v>
       </c>
       <c r="C377" t="inlineStr">
         <is>
@@ -52134,25 +52134,25 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E377" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H377" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I377" t="inlineStr">
@@ -52176,10 +52176,10 @@
         </is>
       </c>
       <c r="Q377" t="n">
-        <v>586393</v>
+        <v>586280</v>
       </c>
       <c r="R377" t="n">
-        <v>6311147</v>
+        <v>6311103</v>
       </c>
       <c r="S377" t="n">
         <v>5</v>
@@ -52211,7 +52211,7 @@
       </c>
       <c r="Z377" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AA377" t="inlineStr">
@@ -52221,7 +52221,7 @@
       </c>
       <c r="AB377" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>22:52</t>
         </is>
       </c>
       <c r="AC377" t="inlineStr">
@@ -52266,10 +52266,10 @@
     </row>
     <row r="378">
       <c r="A378" t="n">
-        <v>122254372</v>
+        <v>122254877</v>
       </c>
       <c r="B378" t="n">
-        <v>56280</v>
+        <v>56283</v>
       </c>
       <c r="C378" t="inlineStr">
         <is>
@@ -52282,21 +52282,21 @@
         </is>
       </c>
       <c r="E378" t="n">
-        <v>100092</v>
+        <v>100111</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I378" t="inlineStr">
@@ -52320,10 +52320,10 @@
         </is>
       </c>
       <c r="Q378" t="n">
-        <v>586306</v>
+        <v>586276</v>
       </c>
       <c r="R378" t="n">
-        <v>6311131</v>
+        <v>6311100</v>
       </c>
       <c r="S378" t="n">
         <v>5</v>
@@ -52355,7 +52355,7 @@
       </c>
       <c r="Z378" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AA378" t="inlineStr">
@@ -52365,7 +52365,7 @@
       </c>
       <c r="AB378" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>22:52</t>
         </is>
       </c>
       <c r="AC378" t="inlineStr">
@@ -52410,10 +52410,10 @@
     </row>
     <row r="379">
       <c r="A379" t="n">
-        <v>122254835</v>
+        <v>122254966</v>
       </c>
       <c r="B379" t="n">
-        <v>56283</v>
+        <v>56273</v>
       </c>
       <c r="C379" t="inlineStr">
         <is>
@@ -52426,21 +52426,21 @@
         </is>
       </c>
       <c r="E379" t="n">
-        <v>100111</v>
+        <v>205992</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H379" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I379" t="inlineStr">
@@ -52464,10 +52464,10 @@
         </is>
       </c>
       <c r="Q379" t="n">
-        <v>586473</v>
+        <v>586467</v>
       </c>
       <c r="R379" t="n">
-        <v>6311192</v>
+        <v>6311178</v>
       </c>
       <c r="S379" t="n">
         <v>5</v>
@@ -52499,7 +52499,7 @@
       </c>
       <c r="Z379" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AA379" t="inlineStr">
@@ -52509,7 +52509,7 @@
       </c>
       <c r="AB379" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="AC379" t="inlineStr">
@@ -52554,10 +52554,10 @@
     </row>
     <row r="380">
       <c r="A380" t="n">
-        <v>122254862</v>
+        <v>122254660</v>
       </c>
       <c r="B380" t="n">
-        <v>56283</v>
+        <v>56285</v>
       </c>
       <c r="C380" t="inlineStr">
         <is>
@@ -52570,21 +52570,21 @@
         </is>
       </c>
       <c r="E380" t="n">
-        <v>100111</v>
+        <v>205995</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H380" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I380" t="inlineStr">
@@ -52608,10 +52608,10 @@
         </is>
       </c>
       <c r="Q380" t="n">
-        <v>586288</v>
+        <v>586488</v>
       </c>
       <c r="R380" t="n">
-        <v>6311100</v>
+        <v>6311183</v>
       </c>
       <c r="S380" t="n">
         <v>5</v>
@@ -52643,7 +52643,7 @@
       </c>
       <c r="Z380" t="inlineStr">
         <is>
-          <t>22:55</t>
+          <t>22:31</t>
         </is>
       </c>
       <c r="AA380" t="inlineStr">
@@ -52653,7 +52653,7 @@
       </c>
       <c r="AB380" t="inlineStr">
         <is>
-          <t>22:56</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AC380" t="inlineStr">
@@ -52698,10 +52698,10 @@
     </row>
     <row r="381">
       <c r="A381" t="n">
-        <v>122254365</v>
+        <v>122254610</v>
       </c>
       <c r="B381" t="n">
-        <v>56280</v>
+        <v>56285</v>
       </c>
       <c r="C381" t="inlineStr">
         <is>
@@ -52714,21 +52714,21 @@
         </is>
       </c>
       <c r="E381" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I381" t="inlineStr">
@@ -52752,10 +52752,10 @@
         </is>
       </c>
       <c r="Q381" t="n">
-        <v>586276</v>
+        <v>586389</v>
       </c>
       <c r="R381" t="n">
-        <v>6311100</v>
+        <v>6311141</v>
       </c>
       <c r="S381" t="n">
         <v>5</v>
@@ -52787,7 +52787,7 @@
       </c>
       <c r="Z381" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA381" t="inlineStr">
@@ -52797,7 +52797,7 @@
       </c>
       <c r="AB381" t="inlineStr">
         <is>
-          <t>22:52</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AC381" t="inlineStr">
@@ -52842,7 +52842,7 @@
     </row>
     <row r="382">
       <c r="A382" t="n">
-        <v>122254315</v>
+        <v>122254411</v>
       </c>
       <c r="B382" t="n">
         <v>56280</v>
@@ -52896,10 +52896,10 @@
         </is>
       </c>
       <c r="Q382" t="n">
-        <v>586441</v>
+        <v>586414</v>
       </c>
       <c r="R382" t="n">
-        <v>6311155</v>
+        <v>6311126</v>
       </c>
       <c r="S382" t="n">
         <v>5</v>
@@ -52931,7 +52931,7 @@
       </c>
       <c r="Z382" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AA382" t="inlineStr">
@@ -52941,7 +52941,7 @@
       </c>
       <c r="AB382" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>22:38</t>
         </is>
       </c>
       <c r="AC382" t="inlineStr">
@@ -52986,7 +52986,7 @@
     </row>
     <row r="383">
       <c r="A383" t="n">
-        <v>122254954</v>
+        <v>122254950</v>
       </c>
       <c r="B383" t="n">
         <v>56273</v>
@@ -53040,10 +53040,10 @@
         </is>
       </c>
       <c r="Q383" t="n">
-        <v>586442</v>
+        <v>586482</v>
       </c>
       <c r="R383" t="n">
-        <v>6311152</v>
+        <v>6311185</v>
       </c>
       <c r="S383" t="n">
         <v>5</v>
@@ -53075,7 +53075,7 @@
       </c>
       <c r="Z383" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AA383" t="inlineStr">
@@ -53085,7 +53085,7 @@
       </c>
       <c r="AB383" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>23:31</t>
         </is>
       </c>
       <c r="AC383" t="inlineStr">
@@ -53130,10 +53130,10 @@
     </row>
     <row r="384">
       <c r="A384" t="n">
-        <v>122254855</v>
+        <v>122254636</v>
       </c>
       <c r="B384" t="n">
-        <v>56283</v>
+        <v>56285</v>
       </c>
       <c r="C384" t="inlineStr">
         <is>
@@ -53146,21 +53146,21 @@
         </is>
       </c>
       <c r="E384" t="n">
-        <v>100111</v>
+        <v>205995</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I384" t="inlineStr">
@@ -53184,10 +53184,10 @@
         </is>
       </c>
       <c r="Q384" t="n">
-        <v>586330</v>
+        <v>586418</v>
       </c>
       <c r="R384" t="n">
-        <v>6311120</v>
+        <v>6311145</v>
       </c>
       <c r="S384" t="n">
         <v>5</v>
@@ -53219,7 +53219,7 @@
       </c>
       <c r="Z384" t="inlineStr">
         <is>
-          <t>22:57</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AA384" t="inlineStr">
@@ -53229,7 +53229,7 @@
       </c>
       <c r="AB384" t="inlineStr">
         <is>
-          <t>22:58</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AC384" t="inlineStr">
@@ -53274,10 +53274,10 @@
     </row>
     <row r="385">
       <c r="A385" t="n">
-        <v>122254370</v>
+        <v>122254659</v>
       </c>
       <c r="B385" t="n">
-        <v>56280</v>
+        <v>56285</v>
       </c>
       <c r="C385" t="inlineStr">
         <is>
@@ -53290,21 +53290,21 @@
         </is>
       </c>
       <c r="E385" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H385" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I385" t="inlineStr">
@@ -53328,10 +53328,10 @@
         </is>
       </c>
       <c r="Q385" t="n">
-        <v>586309</v>
+        <v>586489</v>
       </c>
       <c r="R385" t="n">
-        <v>6311119</v>
+        <v>6311181</v>
       </c>
       <c r="S385" t="n">
         <v>5</v>
@@ -53363,7 +53363,7 @@
       </c>
       <c r="Z385" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>22:31</t>
         </is>
       </c>
       <c r="AA385" t="inlineStr">
@@ -53373,7 +53373,7 @@
       </c>
       <c r="AB385" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AC385" t="inlineStr">
@@ -53418,10 +53418,10 @@
     </row>
     <row r="386">
       <c r="A386" t="n">
-        <v>122254316</v>
+        <v>122254587</v>
       </c>
       <c r="B386" t="n">
-        <v>56280</v>
+        <v>56285</v>
       </c>
       <c r="C386" t="inlineStr">
         <is>
@@ -53434,21 +53434,21 @@
         </is>
       </c>
       <c r="E386" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H386" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I386" t="inlineStr">
@@ -53472,10 +53472,10 @@
         </is>
       </c>
       <c r="Q386" t="n">
-        <v>586423</v>
+        <v>586443</v>
       </c>
       <c r="R386" t="n">
-        <v>6311166</v>
+        <v>6311163</v>
       </c>
       <c r="S386" t="n">
         <v>5</v>
@@ -53507,7 +53507,7 @@
       </c>
       <c r="Z386" t="inlineStr">
         <is>
-          <t>23:23</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AA386" t="inlineStr">
@@ -53517,7 +53517,7 @@
       </c>
       <c r="AB386" t="inlineStr">
         <is>
-          <t>23:24</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AC386" t="inlineStr">
@@ -53562,10 +53562,10 @@
     </row>
     <row r="387">
       <c r="A387" t="n">
-        <v>122254648</v>
+        <v>122254369</v>
       </c>
       <c r="B387" t="n">
-        <v>56285</v>
+        <v>56280</v>
       </c>
       <c r="C387" t="inlineStr">
         <is>
@@ -53578,21 +53578,21 @@
         </is>
       </c>
       <c r="E387" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I387" t="inlineStr">
@@ -53616,10 +53616,10 @@
         </is>
       </c>
       <c r="Q387" t="n">
-        <v>586418</v>
+        <v>586300</v>
       </c>
       <c r="R387" t="n">
-        <v>6311107</v>
+        <v>6311112</v>
       </c>
       <c r="S387" t="n">
         <v>5</v>
@@ -53651,7 +53651,7 @@
       </c>
       <c r="Z387" t="inlineStr">
         <is>
-          <t>22:36</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AA387" t="inlineStr">
@@ -53661,7 +53661,7 @@
       </c>
       <c r="AB387" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AC387" t="inlineStr">
@@ -53706,10 +53706,10 @@
     </row>
     <row r="388">
       <c r="A388" t="n">
-        <v>122254634</v>
+        <v>122254476</v>
       </c>
       <c r="B388" t="n">
-        <v>56285</v>
+        <v>56266</v>
       </c>
       <c r="C388" t="inlineStr">
         <is>
@@ -53718,25 +53718,25 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E388" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H388" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I388" t="inlineStr">
@@ -53760,10 +53760,10 @@
         </is>
       </c>
       <c r="Q388" t="n">
-        <v>586415</v>
+        <v>586418</v>
       </c>
       <c r="R388" t="n">
-        <v>6311148</v>
+        <v>6311167</v>
       </c>
       <c r="S388" t="n">
         <v>5</v>
@@ -53795,7 +53795,7 @@
       </c>
       <c r="Z388" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>23:23</t>
         </is>
       </c>
       <c r="AA388" t="inlineStr">
@@ -53805,7 +53805,7 @@
       </c>
       <c r="AB388" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="AC388" t="inlineStr">
@@ -53850,10 +53850,10 @@
     </row>
     <row r="389">
       <c r="A389" t="n">
-        <v>122254964</v>
+        <v>122254637</v>
       </c>
       <c r="B389" t="n">
-        <v>56273</v>
+        <v>56285</v>
       </c>
       <c r="C389" t="inlineStr">
         <is>
@@ -53866,21 +53866,21 @@
         </is>
       </c>
       <c r="E389" t="n">
-        <v>205992</v>
+        <v>205995</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I389" t="inlineStr">
@@ -53904,10 +53904,10 @@
         </is>
       </c>
       <c r="Q389" t="n">
-        <v>586430</v>
+        <v>586408</v>
       </c>
       <c r="R389" t="n">
-        <v>6311142</v>
+        <v>6311124</v>
       </c>
       <c r="S389" t="n">
         <v>5</v>
@@ -53939,7 +53939,7 @@
       </c>
       <c r="Z389" t="inlineStr">
         <is>
-          <t>22:33</t>
+          <t>22:43</t>
         </is>
       </c>
       <c r="AA389" t="inlineStr">
@@ -53949,7 +53949,7 @@
       </c>
       <c r="AB389" t="inlineStr">
         <is>
-          <t>22:34</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AC389" t="inlineStr">
@@ -53994,10 +53994,10 @@
     </row>
     <row r="390">
       <c r="A390" t="n">
-        <v>122254643</v>
+        <v>122254854</v>
       </c>
       <c r="B390" t="n">
-        <v>56285</v>
+        <v>56283</v>
       </c>
       <c r="C390" t="inlineStr">
         <is>
@@ -54010,21 +54010,21 @@
         </is>
       </c>
       <c r="E390" t="n">
-        <v>205995</v>
+        <v>100111</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I390" t="inlineStr">
@@ -54048,10 +54048,10 @@
         </is>
       </c>
       <c r="Q390" t="n">
-        <v>586424</v>
+        <v>586329</v>
       </c>
       <c r="R390" t="n">
-        <v>6311135</v>
+        <v>6311120</v>
       </c>
       <c r="S390" t="n">
         <v>5</v>
@@ -54083,7 +54083,7 @@
       </c>
       <c r="Z390" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>22:57</t>
         </is>
       </c>
       <c r="AA390" t="inlineStr">
@@ -54093,7 +54093,7 @@
       </c>
       <c r="AB390" t="inlineStr">
         <is>
-          <t>22:38</t>
+          <t>22:58</t>
         </is>
       </c>
       <c r="AC390" t="inlineStr">

--- a/artfynd/A 36363-2024 artfynd.xlsx
+++ b/artfynd/A 36363-2024 artfynd.xlsx
@@ -43770,10 +43770,10 @@
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>122254951</v>
+        <v>122254615</v>
       </c>
       <c r="B319" t="n">
-        <v>56273</v>
+        <v>56285</v>
       </c>
       <c r="C319" t="inlineStr">
         <is>
@@ -43786,21 +43786,21 @@
         </is>
       </c>
       <c r="E319" t="n">
-        <v>205992</v>
+        <v>205995</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
@@ -43824,10 +43824,10 @@
         </is>
       </c>
       <c r="Q319" t="n">
-        <v>586459</v>
+        <v>586329</v>
       </c>
       <c r="R319" t="n">
-        <v>6311154</v>
+        <v>6311120</v>
       </c>
       <c r="S319" t="n">
         <v>5</v>
@@ -43859,7 +43859,7 @@
       </c>
       <c r="Z319" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>22:57</t>
         </is>
       </c>
       <c r="AA319" t="inlineStr">
@@ -43869,7 +43869,7 @@
       </c>
       <c r="AB319" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>22:58</t>
         </is>
       </c>
       <c r="AC319" t="inlineStr">
@@ -43914,10 +43914,10 @@
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>122254963</v>
+        <v>122254503</v>
       </c>
       <c r="B320" t="n">
-        <v>56273</v>
+        <v>56266</v>
       </c>
       <c r="C320" t="inlineStr">
         <is>
@@ -43926,25 +43926,25 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E320" t="n">
-        <v>205992</v>
+        <v>205998</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
@@ -43968,10 +43968,10 @@
         </is>
       </c>
       <c r="Q320" t="n">
-        <v>586374</v>
+        <v>586313</v>
       </c>
       <c r="R320" t="n">
-        <v>6311140</v>
+        <v>6311124</v>
       </c>
       <c r="S320" t="n">
         <v>5</v>
@@ -44003,7 +44003,7 @@
       </c>
       <c r="Z320" t="inlineStr">
         <is>
-          <t>22:46</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AA320" t="inlineStr">
@@ -44013,7 +44013,7 @@
       </c>
       <c r="AB320" t="inlineStr">
         <is>
-          <t>22:47</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AC320" t="inlineStr">
@@ -44058,10 +44058,10 @@
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>122254615</v>
+        <v>122254499</v>
       </c>
       <c r="B321" t="n">
-        <v>56285</v>
+        <v>56266</v>
       </c>
       <c r="C321" t="inlineStr">
         <is>
@@ -44070,25 +44070,25 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E321" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
@@ -44112,10 +44112,10 @@
         </is>
       </c>
       <c r="Q321" t="n">
-        <v>586329</v>
+        <v>586392</v>
       </c>
       <c r="R321" t="n">
-        <v>6311120</v>
+        <v>6311147</v>
       </c>
       <c r="S321" t="n">
         <v>5</v>
@@ -44147,7 +44147,7 @@
       </c>
       <c r="Z321" t="inlineStr">
         <is>
-          <t>22:57</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AA321" t="inlineStr">
@@ -44157,7 +44157,7 @@
       </c>
       <c r="AB321" t="inlineStr">
         <is>
-          <t>22:58</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AC321" t="inlineStr">
@@ -44202,7 +44202,7 @@
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>122254503</v>
+        <v>122254512</v>
       </c>
       <c r="B322" t="n">
         <v>56266</v>
@@ -44256,10 +44256,10 @@
         </is>
       </c>
       <c r="Q322" t="n">
-        <v>586313</v>
+        <v>586379</v>
       </c>
       <c r="R322" t="n">
-        <v>6311124</v>
+        <v>6311136</v>
       </c>
       <c r="S322" t="n">
         <v>5</v>
@@ -44291,7 +44291,7 @@
       </c>
       <c r="Z322" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AA322" t="inlineStr">
@@ -44301,7 +44301,7 @@
       </c>
       <c r="AB322" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>22:46</t>
         </is>
       </c>
       <c r="AC322" t="inlineStr">
@@ -44346,10 +44346,10 @@
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>122254512</v>
+        <v>122254951</v>
       </c>
       <c r="B323" t="n">
-        <v>56266</v>
+        <v>56273</v>
       </c>
       <c r="C323" t="inlineStr">
         <is>
@@ -44358,25 +44358,25 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E323" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
@@ -44400,10 +44400,10 @@
         </is>
       </c>
       <c r="Q323" t="n">
-        <v>586379</v>
+        <v>586459</v>
       </c>
       <c r="R323" t="n">
-        <v>6311136</v>
+        <v>6311154</v>
       </c>
       <c r="S323" t="n">
         <v>5</v>
@@ -44435,7 +44435,7 @@
       </c>
       <c r="Z323" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AA323" t="inlineStr">
@@ -44445,7 +44445,7 @@
       </c>
       <c r="AB323" t="inlineStr">
         <is>
-          <t>22:46</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AC323" t="inlineStr">
@@ -44490,10 +44490,10 @@
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>122254499</v>
+        <v>122254963</v>
       </c>
       <c r="B324" t="n">
-        <v>56266</v>
+        <v>56273</v>
       </c>
       <c r="C324" t="inlineStr">
         <is>
@@ -44502,25 +44502,25 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E324" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
@@ -44544,10 +44544,10 @@
         </is>
       </c>
       <c r="Q324" t="n">
-        <v>586392</v>
+        <v>586374</v>
       </c>
       <c r="R324" t="n">
-        <v>6311147</v>
+        <v>6311140</v>
       </c>
       <c r="S324" t="n">
         <v>5</v>
@@ -44579,7 +44579,7 @@
       </c>
       <c r="Z324" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>22:46</t>
         </is>
       </c>
       <c r="AA324" t="inlineStr">
@@ -44589,7 +44589,7 @@
       </c>
       <c r="AB324" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>22:47</t>
         </is>
       </c>
       <c r="AC324" t="inlineStr">
@@ -45354,10 +45354,10 @@
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>122254857</v>
+        <v>122254394</v>
       </c>
       <c r="B330" t="n">
-        <v>56283</v>
+        <v>56280</v>
       </c>
       <c r="C330" t="inlineStr">
         <is>
@@ -45370,21 +45370,21 @@
         </is>
       </c>
       <c r="E330" t="n">
-        <v>100111</v>
+        <v>100092</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
@@ -45408,10 +45408,10 @@
         </is>
       </c>
       <c r="Q330" t="n">
-        <v>586317</v>
+        <v>586419</v>
       </c>
       <c r="R330" t="n">
-        <v>6311115</v>
+        <v>6311142</v>
       </c>
       <c r="S330" t="n">
         <v>5</v>
@@ -45443,7 +45443,7 @@
       </c>
       <c r="Z330" t="inlineStr">
         <is>
-          <t>22:57</t>
+          <t>22:43</t>
         </is>
       </c>
       <c r="AA330" t="inlineStr">
@@ -45453,7 +45453,7 @@
       </c>
       <c r="AB330" t="inlineStr">
         <is>
-          <t>22:58</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AC330" t="inlineStr">
@@ -45498,7 +45498,7 @@
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>122254394</v>
+        <v>122254313</v>
       </c>
       <c r="B331" t="n">
         <v>56280</v>
@@ -45552,10 +45552,10 @@
         </is>
       </c>
       <c r="Q331" t="n">
-        <v>586419</v>
+        <v>586449</v>
       </c>
       <c r="R331" t="n">
-        <v>6311142</v>
+        <v>6311155</v>
       </c>
       <c r="S331" t="n">
         <v>5</v>
@@ -45587,7 +45587,7 @@
       </c>
       <c r="Z331" t="inlineStr">
         <is>
-          <t>22:43</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA331" t="inlineStr">
@@ -45597,7 +45597,7 @@
       </c>
       <c r="AB331" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC331" t="inlineStr">
@@ -45642,10 +45642,10 @@
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>122254313</v>
+        <v>122254857</v>
       </c>
       <c r="B332" t="n">
-        <v>56280</v>
+        <v>56283</v>
       </c>
       <c r="C332" t="inlineStr">
         <is>
@@ -45658,21 +45658,21 @@
         </is>
       </c>
       <c r="E332" t="n">
-        <v>100092</v>
+        <v>100111</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
@@ -45696,10 +45696,10 @@
         </is>
       </c>
       <c r="Q332" t="n">
-        <v>586449</v>
+        <v>586317</v>
       </c>
       <c r="R332" t="n">
-        <v>6311155</v>
+        <v>6311115</v>
       </c>
       <c r="S332" t="n">
         <v>5</v>
@@ -45731,7 +45731,7 @@
       </c>
       <c r="Z332" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>22:57</t>
         </is>
       </c>
       <c r="AA332" t="inlineStr">
@@ -45741,7 +45741,7 @@
       </c>
       <c r="AB332" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>22:58</t>
         </is>
       </c>
       <c r="AC332" t="inlineStr">
@@ -46794,10 +46794,10 @@
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>122254608</v>
+        <v>122254391</v>
       </c>
       <c r="B340" t="n">
-        <v>56285</v>
+        <v>56280</v>
       </c>
       <c r="C340" t="inlineStr">
         <is>
@@ -46810,21 +46810,21 @@
         </is>
       </c>
       <c r="E340" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
@@ -46848,10 +46848,10 @@
         </is>
       </c>
       <c r="Q340" t="n">
-        <v>586393</v>
+        <v>586379</v>
       </c>
       <c r="R340" t="n">
-        <v>6311147</v>
+        <v>6311136</v>
       </c>
       <c r="S340" t="n">
         <v>5</v>
@@ -46883,7 +46883,7 @@
       </c>
       <c r="Z340" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AA340" t="inlineStr">
@@ -46893,7 +46893,7 @@
       </c>
       <c r="AB340" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>22:46</t>
         </is>
       </c>
       <c r="AC340" t="inlineStr">
@@ -46938,7 +46938,7 @@
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>122254634</v>
+        <v>122254608</v>
       </c>
       <c r="B341" t="n">
         <v>56285</v>
@@ -46992,10 +46992,10 @@
         </is>
       </c>
       <c r="Q341" t="n">
-        <v>586415</v>
+        <v>586393</v>
       </c>
       <c r="R341" t="n">
-        <v>6311148</v>
+        <v>6311147</v>
       </c>
       <c r="S341" t="n">
         <v>5</v>
@@ -47027,7 +47027,7 @@
       </c>
       <c r="Z341" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AA341" t="inlineStr">
@@ -47037,7 +47037,7 @@
       </c>
       <c r="AB341" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AC341" t="inlineStr">
@@ -47082,7 +47082,7 @@
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>122254606</v>
+        <v>122254634</v>
       </c>
       <c r="B342" t="n">
         <v>56285</v>
@@ -47139,7 +47139,7 @@
         <v>586415</v>
       </c>
       <c r="R342" t="n">
-        <v>6311146</v>
+        <v>6311148</v>
       </c>
       <c r="S342" t="n">
         <v>5</v>
@@ -47171,7 +47171,7 @@
       </c>
       <c r="Z342" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AA342" t="inlineStr">
@@ -47181,7 +47181,7 @@
       </c>
       <c r="AB342" t="inlineStr">
         <is>
-          <t>23:03</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AC342" t="inlineStr">
@@ -47226,10 +47226,10 @@
     </row>
     <row r="343">
       <c r="A343" t="n">
-        <v>122254391</v>
+        <v>122254606</v>
       </c>
       <c r="B343" t="n">
-        <v>56280</v>
+        <v>56285</v>
       </c>
       <c r="C343" t="inlineStr">
         <is>
@@ -47242,21 +47242,21 @@
         </is>
       </c>
       <c r="E343" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
@@ -47280,10 +47280,10 @@
         </is>
       </c>
       <c r="Q343" t="n">
-        <v>586379</v>
+        <v>586415</v>
       </c>
       <c r="R343" t="n">
-        <v>6311136</v>
+        <v>6311146</v>
       </c>
       <c r="S343" t="n">
         <v>5</v>
@@ -47315,7 +47315,7 @@
       </c>
       <c r="Z343" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AA343" t="inlineStr">
@@ -47325,7 +47325,7 @@
       </c>
       <c r="AB343" t="inlineStr">
         <is>
-          <t>22:46</t>
+          <t>23:03</t>
         </is>
       </c>
       <c r="AC343" t="inlineStr">
@@ -48666,10 +48666,10 @@
     </row>
     <row r="353">
       <c r="A353" t="n">
-        <v>122254959</v>
+        <v>122254372</v>
       </c>
       <c r="B353" t="n">
-        <v>56273</v>
+        <v>56280</v>
       </c>
       <c r="C353" t="inlineStr">
         <is>
@@ -48682,21 +48682,21 @@
         </is>
       </c>
       <c r="E353" t="n">
-        <v>205992</v>
+        <v>100092</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I353" t="inlineStr">
@@ -48720,10 +48720,10 @@
         </is>
       </c>
       <c r="Q353" t="n">
-        <v>586370</v>
+        <v>586306</v>
       </c>
       <c r="R353" t="n">
-        <v>6311139</v>
+        <v>6311131</v>
       </c>
       <c r="S353" t="n">
         <v>5</v>
@@ -48755,7 +48755,7 @@
       </c>
       <c r="Z353" t="inlineStr">
         <is>
-          <t>22:59</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AA353" t="inlineStr">
@@ -48765,7 +48765,7 @@
       </c>
       <c r="AB353" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AC353" t="inlineStr">
@@ -48810,7 +48810,7 @@
     </row>
     <row r="354">
       <c r="A354" t="n">
-        <v>122254372</v>
+        <v>122254392</v>
       </c>
       <c r="B354" t="n">
         <v>56280</v>
@@ -48864,10 +48864,10 @@
         </is>
       </c>
       <c r="Q354" t="n">
-        <v>586306</v>
+        <v>586384</v>
       </c>
       <c r="R354" t="n">
-        <v>6311131</v>
+        <v>6311139</v>
       </c>
       <c r="S354" t="n">
         <v>5</v>
@@ -48899,7 +48899,7 @@
       </c>
       <c r="Z354" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AA354" t="inlineStr">
@@ -48909,7 +48909,7 @@
       </c>
       <c r="AB354" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>22:46</t>
         </is>
       </c>
       <c r="AC354" t="inlineStr">
@@ -49098,7 +49098,7 @@
     </row>
     <row r="356">
       <c r="A356" t="n">
-        <v>122254392</v>
+        <v>122254315</v>
       </c>
       <c r="B356" t="n">
         <v>56280</v>
@@ -49152,10 +49152,10 @@
         </is>
       </c>
       <c r="Q356" t="n">
-        <v>586384</v>
+        <v>586441</v>
       </c>
       <c r="R356" t="n">
-        <v>6311139</v>
+        <v>6311155</v>
       </c>
       <c r="S356" t="n">
         <v>5</v>
@@ -49187,7 +49187,7 @@
       </c>
       <c r="Z356" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AA356" t="inlineStr">
@@ -49197,7 +49197,7 @@
       </c>
       <c r="AB356" t="inlineStr">
         <is>
-          <t>22:46</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AC356" t="inlineStr">
@@ -49242,10 +49242,10 @@
     </row>
     <row r="357">
       <c r="A357" t="n">
-        <v>122254315</v>
+        <v>122254959</v>
       </c>
       <c r="B357" t="n">
-        <v>56280</v>
+        <v>56273</v>
       </c>
       <c r="C357" t="inlineStr">
         <is>
@@ -49258,21 +49258,21 @@
         </is>
       </c>
       <c r="E357" t="n">
-        <v>100092</v>
+        <v>205992</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I357" t="inlineStr">
@@ -49296,10 +49296,10 @@
         </is>
       </c>
       <c r="Q357" t="n">
-        <v>586441</v>
+        <v>586370</v>
       </c>
       <c r="R357" t="n">
-        <v>6311155</v>
+        <v>6311139</v>
       </c>
       <c r="S357" t="n">
         <v>5</v>
@@ -49331,7 +49331,7 @@
       </c>
       <c r="Z357" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>22:59</t>
         </is>
       </c>
       <c r="AA357" t="inlineStr">
@@ -49341,7 +49341,7 @@
       </c>
       <c r="AB357" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AC357" t="inlineStr">
@@ -50106,10 +50106,10 @@
     </row>
     <row r="363">
       <c r="A363" t="n">
-        <v>122254421</v>
+        <v>122254880</v>
       </c>
       <c r="B363" t="n">
-        <v>56280</v>
+        <v>56283</v>
       </c>
       <c r="C363" t="inlineStr">
         <is>
@@ -50122,21 +50122,21 @@
         </is>
       </c>
       <c r="E363" t="n">
-        <v>100092</v>
+        <v>100111</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I363" t="inlineStr">
@@ -50160,10 +50160,10 @@
         </is>
       </c>
       <c r="Q363" t="n">
-        <v>586468</v>
+        <v>586303</v>
       </c>
       <c r="R363" t="n">
-        <v>6311181</v>
+        <v>6311115</v>
       </c>
       <c r="S363" t="n">
         <v>5</v>
@@ -50195,7 +50195,7 @@
       </c>
       <c r="Z363" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AA363" t="inlineStr">
@@ -50205,7 +50205,7 @@
       </c>
       <c r="AB363" t="inlineStr">
         <is>
-          <t>22:33</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AC363" t="inlineStr">
@@ -50250,10 +50250,10 @@
     </row>
     <row r="364">
       <c r="A364" t="n">
-        <v>122254373</v>
+        <v>122254835</v>
       </c>
       <c r="B364" t="n">
-        <v>56280</v>
+        <v>56283</v>
       </c>
       <c r="C364" t="inlineStr">
         <is>
@@ -50266,21 +50266,21 @@
         </is>
       </c>
       <c r="E364" t="n">
-        <v>100092</v>
+        <v>100111</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I364" t="inlineStr">
@@ -50304,10 +50304,10 @@
         </is>
       </c>
       <c r="Q364" t="n">
-        <v>586307</v>
+        <v>586473</v>
       </c>
       <c r="R364" t="n">
-        <v>6311133</v>
+        <v>6311192</v>
       </c>
       <c r="S364" t="n">
         <v>5</v>
@@ -50339,7 +50339,7 @@
       </c>
       <c r="Z364" t="inlineStr">
         <is>
-          <t>22:49</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AA364" t="inlineStr">
@@ -50349,7 +50349,7 @@
       </c>
       <c r="AB364" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AC364" t="inlineStr">
@@ -50394,7 +50394,7 @@
     </row>
     <row r="365">
       <c r="A365" t="n">
-        <v>122254314</v>
+        <v>122254421</v>
       </c>
       <c r="B365" t="n">
         <v>56280</v>
@@ -50448,10 +50448,10 @@
         </is>
       </c>
       <c r="Q365" t="n">
-        <v>586443</v>
+        <v>586468</v>
       </c>
       <c r="R365" t="n">
-        <v>6311164</v>
+        <v>6311181</v>
       </c>
       <c r="S365" t="n">
         <v>5</v>
@@ -50483,7 +50483,7 @@
       </c>
       <c r="Z365" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AA365" t="inlineStr">
@@ -50493,7 +50493,7 @@
       </c>
       <c r="AB365" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="AC365" t="inlineStr">
@@ -50538,10 +50538,10 @@
     </row>
     <row r="366">
       <c r="A366" t="n">
-        <v>122254954</v>
+        <v>122254373</v>
       </c>
       <c r="B366" t="n">
-        <v>56273</v>
+        <v>56280</v>
       </c>
       <c r="C366" t="inlineStr">
         <is>
@@ -50554,21 +50554,21 @@
         </is>
       </c>
       <c r="E366" t="n">
-        <v>205992</v>
+        <v>100092</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I366" t="inlineStr">
@@ -50592,10 +50592,10 @@
         </is>
       </c>
       <c r="Q366" t="n">
-        <v>586442</v>
+        <v>586307</v>
       </c>
       <c r="R366" t="n">
-        <v>6311152</v>
+        <v>6311133</v>
       </c>
       <c r="S366" t="n">
         <v>5</v>
@@ -50627,7 +50627,7 @@
       </c>
       <c r="Z366" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>22:49</t>
         </is>
       </c>
       <c r="AA366" t="inlineStr">
@@ -50637,7 +50637,7 @@
       </c>
       <c r="AB366" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AC366" t="inlineStr">
@@ -50682,10 +50682,10 @@
     </row>
     <row r="367">
       <c r="A367" t="n">
-        <v>122254500</v>
+        <v>122254314</v>
       </c>
       <c r="B367" t="n">
-        <v>56266</v>
+        <v>56280</v>
       </c>
       <c r="C367" t="inlineStr">
         <is>
@@ -50694,25 +50694,25 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E367" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I367" t="inlineStr">
@@ -50736,10 +50736,10 @@
         </is>
       </c>
       <c r="Q367" t="n">
-        <v>586388</v>
+        <v>586443</v>
       </c>
       <c r="R367" t="n">
-        <v>6311142</v>
+        <v>6311164</v>
       </c>
       <c r="S367" t="n">
         <v>5</v>
@@ -50771,7 +50771,7 @@
       </c>
       <c r="Z367" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AA367" t="inlineStr">
@@ -50781,7 +50781,7 @@
       </c>
       <c r="AB367" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AC367" t="inlineStr">
@@ -50826,10 +50826,10 @@
     </row>
     <row r="368">
       <c r="A368" t="n">
-        <v>122254607</v>
+        <v>122254954</v>
       </c>
       <c r="B368" t="n">
-        <v>56285</v>
+        <v>56273</v>
       </c>
       <c r="C368" t="inlineStr">
         <is>
@@ -50842,21 +50842,21 @@
         </is>
       </c>
       <c r="E368" t="n">
-        <v>205995</v>
+        <v>205992</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H368" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I368" t="inlineStr">
@@ -50880,10 +50880,10 @@
         </is>
       </c>
       <c r="Q368" t="n">
-        <v>586415</v>
+        <v>586442</v>
       </c>
       <c r="R368" t="n">
-        <v>6311149</v>
+        <v>6311152</v>
       </c>
       <c r="S368" t="n">
         <v>5</v>
@@ -50915,7 +50915,7 @@
       </c>
       <c r="Z368" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AA368" t="inlineStr">
@@ -50925,7 +50925,7 @@
       </c>
       <c r="AB368" t="inlineStr">
         <is>
-          <t>23:03</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AC368" t="inlineStr">
@@ -50970,10 +50970,10 @@
     </row>
     <row r="369">
       <c r="A369" t="n">
-        <v>122254880</v>
+        <v>122254500</v>
       </c>
       <c r="B369" t="n">
-        <v>56283</v>
+        <v>56266</v>
       </c>
       <c r="C369" t="inlineStr">
         <is>
@@ -50982,25 +50982,25 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E369" t="n">
-        <v>100111</v>
+        <v>205998</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I369" t="inlineStr">
@@ -51024,10 +51024,10 @@
         </is>
       </c>
       <c r="Q369" t="n">
-        <v>586303</v>
+        <v>586388</v>
       </c>
       <c r="R369" t="n">
-        <v>6311115</v>
+        <v>6311142</v>
       </c>
       <c r="S369" t="n">
         <v>5</v>
@@ -51059,7 +51059,7 @@
       </c>
       <c r="Z369" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA369" t="inlineStr">
@@ -51069,7 +51069,7 @@
       </c>
       <c r="AB369" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AC369" t="inlineStr">
@@ -51114,10 +51114,10 @@
     </row>
     <row r="370">
       <c r="A370" t="n">
-        <v>122254835</v>
+        <v>122254607</v>
       </c>
       <c r="B370" t="n">
-        <v>56283</v>
+        <v>56285</v>
       </c>
       <c r="C370" t="inlineStr">
         <is>
@@ -51130,21 +51130,21 @@
         </is>
       </c>
       <c r="E370" t="n">
-        <v>100111</v>
+        <v>205995</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I370" t="inlineStr">
@@ -51168,10 +51168,10 @@
         </is>
       </c>
       <c r="Q370" t="n">
-        <v>586473</v>
+        <v>586415</v>
       </c>
       <c r="R370" t="n">
-        <v>6311192</v>
+        <v>6311149</v>
       </c>
       <c r="S370" t="n">
         <v>5</v>
@@ -51203,7 +51203,7 @@
       </c>
       <c r="Z370" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AA370" t="inlineStr">
@@ -51213,7 +51213,7 @@
       </c>
       <c r="AB370" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:03</t>
         </is>
       </c>
       <c r="AC370" t="inlineStr">
@@ -51690,10 +51690,10 @@
     </row>
     <row r="374">
       <c r="A374" t="n">
-        <v>122254956</v>
+        <v>122254635</v>
       </c>
       <c r="B374" t="n">
-        <v>56273</v>
+        <v>56285</v>
       </c>
       <c r="C374" t="inlineStr">
         <is>
@@ -51706,21 +51706,21 @@
         </is>
       </c>
       <c r="E374" t="n">
-        <v>205992</v>
+        <v>205995</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I374" t="inlineStr">
@@ -51744,10 +51744,10 @@
         </is>
       </c>
       <c r="Q374" t="n">
-        <v>586441</v>
+        <v>586417</v>
       </c>
       <c r="R374" t="n">
-        <v>6311152</v>
+        <v>6311145</v>
       </c>
       <c r="S374" t="n">
         <v>5</v>
@@ -51779,7 +51779,7 @@
       </c>
       <c r="Z374" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AA374" t="inlineStr">
@@ -51789,7 +51789,7 @@
       </c>
       <c r="AB374" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AC374" t="inlineStr">
@@ -51834,7 +51834,7 @@
     </row>
     <row r="375">
       <c r="A375" t="n">
-        <v>122254635</v>
+        <v>122254611</v>
       </c>
       <c r="B375" t="n">
         <v>56285</v>
@@ -51888,10 +51888,10 @@
         </is>
       </c>
       <c r="Q375" t="n">
-        <v>586417</v>
+        <v>586370</v>
       </c>
       <c r="R375" t="n">
-        <v>6311145</v>
+        <v>6311139</v>
       </c>
       <c r="S375" t="n">
         <v>5</v>
@@ -51923,7 +51923,7 @@
       </c>
       <c r="Z375" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>22:59</t>
         </is>
       </c>
       <c r="AA375" t="inlineStr">
@@ -51933,7 +51933,7 @@
       </c>
       <c r="AB375" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AC375" t="inlineStr">
@@ -51978,10 +51978,10 @@
     </row>
     <row r="376">
       <c r="A376" t="n">
-        <v>122254611</v>
+        <v>122254367</v>
       </c>
       <c r="B376" t="n">
-        <v>56285</v>
+        <v>56280</v>
       </c>
       <c r="C376" t="inlineStr">
         <is>
@@ -51994,21 +51994,21 @@
         </is>
       </c>
       <c r="E376" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H376" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I376" t="inlineStr">
@@ -52032,10 +52032,10 @@
         </is>
       </c>
       <c r="Q376" t="n">
-        <v>586370</v>
+        <v>586280</v>
       </c>
       <c r="R376" t="n">
-        <v>6311139</v>
+        <v>6311103</v>
       </c>
       <c r="S376" t="n">
         <v>5</v>
@@ -52067,7 +52067,7 @@
       </c>
       <c r="Z376" t="inlineStr">
         <is>
-          <t>22:59</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AA376" t="inlineStr">
@@ -52077,7 +52077,7 @@
       </c>
       <c r="AB376" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:52</t>
         </is>
       </c>
       <c r="AC376" t="inlineStr">
@@ -52122,10 +52122,10 @@
     </row>
     <row r="377">
       <c r="A377" t="n">
-        <v>122254367</v>
+        <v>122254956</v>
       </c>
       <c r="B377" t="n">
-        <v>56280</v>
+        <v>56273</v>
       </c>
       <c r="C377" t="inlineStr">
         <is>
@@ -52138,21 +52138,21 @@
         </is>
       </c>
       <c r="E377" t="n">
-        <v>100092</v>
+        <v>205992</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H377" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I377" t="inlineStr">
@@ -52176,10 +52176,10 @@
         </is>
       </c>
       <c r="Q377" t="n">
-        <v>586280</v>
+        <v>586441</v>
       </c>
       <c r="R377" t="n">
-        <v>6311103</v>
+        <v>6311152</v>
       </c>
       <c r="S377" t="n">
         <v>5</v>
@@ -52211,7 +52211,7 @@
       </c>
       <c r="Z377" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AA377" t="inlineStr">
@@ -52221,7 +52221,7 @@
       </c>
       <c r="AB377" t="inlineStr">
         <is>
-          <t>22:52</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AC377" t="inlineStr">
@@ -53562,10 +53562,10 @@
     </row>
     <row r="387">
       <c r="A387" t="n">
-        <v>122254369</v>
+        <v>122254476</v>
       </c>
       <c r="B387" t="n">
-        <v>56280</v>
+        <v>56266</v>
       </c>
       <c r="C387" t="inlineStr">
         <is>
@@ -53574,25 +53574,25 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E387" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I387" t="inlineStr">
@@ -53616,10 +53616,10 @@
         </is>
       </c>
       <c r="Q387" t="n">
-        <v>586300</v>
+        <v>586418</v>
       </c>
       <c r="R387" t="n">
-        <v>6311112</v>
+        <v>6311167</v>
       </c>
       <c r="S387" t="n">
         <v>5</v>
@@ -53651,7 +53651,7 @@
       </c>
       <c r="Z387" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>23:23</t>
         </is>
       </c>
       <c r="AA387" t="inlineStr">
@@ -53661,7 +53661,7 @@
       </c>
       <c r="AB387" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="AC387" t="inlineStr">
@@ -53706,10 +53706,10 @@
     </row>
     <row r="388">
       <c r="A388" t="n">
-        <v>122254476</v>
+        <v>122254637</v>
       </c>
       <c r="B388" t="n">
-        <v>56266</v>
+        <v>56285</v>
       </c>
       <c r="C388" t="inlineStr">
         <is>
@@ -53718,25 +53718,25 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E388" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H388" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I388" t="inlineStr">
@@ -53760,10 +53760,10 @@
         </is>
       </c>
       <c r="Q388" t="n">
-        <v>586418</v>
+        <v>586408</v>
       </c>
       <c r="R388" t="n">
-        <v>6311167</v>
+        <v>6311124</v>
       </c>
       <c r="S388" t="n">
         <v>5</v>
@@ -53795,7 +53795,7 @@
       </c>
       <c r="Z388" t="inlineStr">
         <is>
-          <t>23:23</t>
+          <t>22:43</t>
         </is>
       </c>
       <c r="AA388" t="inlineStr">
@@ -53805,7 +53805,7 @@
       </c>
       <c r="AB388" t="inlineStr">
         <is>
-          <t>23:24</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AC388" t="inlineStr">
@@ -53850,10 +53850,10 @@
     </row>
     <row r="389">
       <c r="A389" t="n">
-        <v>122254637</v>
+        <v>122254854</v>
       </c>
       <c r="B389" t="n">
-        <v>56285</v>
+        <v>56283</v>
       </c>
       <c r="C389" t="inlineStr">
         <is>
@@ -53866,21 +53866,21 @@
         </is>
       </c>
       <c r="E389" t="n">
-        <v>205995</v>
+        <v>100111</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I389" t="inlineStr">
@@ -53904,10 +53904,10 @@
         </is>
       </c>
       <c r="Q389" t="n">
-        <v>586408</v>
+        <v>586329</v>
       </c>
       <c r="R389" t="n">
-        <v>6311124</v>
+        <v>6311120</v>
       </c>
       <c r="S389" t="n">
         <v>5</v>
@@ -53939,7 +53939,7 @@
       </c>
       <c r="Z389" t="inlineStr">
         <is>
-          <t>22:43</t>
+          <t>22:57</t>
         </is>
       </c>
       <c r="AA389" t="inlineStr">
@@ -53949,7 +53949,7 @@
       </c>
       <c r="AB389" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>22:58</t>
         </is>
       </c>
       <c r="AC389" t="inlineStr">
@@ -53994,10 +53994,10 @@
     </row>
     <row r="390">
       <c r="A390" t="n">
-        <v>122254854</v>
+        <v>122254369</v>
       </c>
       <c r="B390" t="n">
-        <v>56283</v>
+        <v>56280</v>
       </c>
       <c r="C390" t="inlineStr">
         <is>
@@ -54010,21 +54010,21 @@
         </is>
       </c>
       <c r="E390" t="n">
-        <v>100111</v>
+        <v>100092</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I390" t="inlineStr">
@@ -54048,10 +54048,10 @@
         </is>
       </c>
       <c r="Q390" t="n">
-        <v>586329</v>
+        <v>586300</v>
       </c>
       <c r="R390" t="n">
-        <v>6311120</v>
+        <v>6311112</v>
       </c>
       <c r="S390" t="n">
         <v>5</v>
@@ -54083,7 +54083,7 @@
       </c>
       <c r="Z390" t="inlineStr">
         <is>
-          <t>22:57</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AA390" t="inlineStr">
@@ -54093,7 +54093,7 @@
       </c>
       <c r="AB390" t="inlineStr">
         <is>
-          <t>22:58</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AC390" t="inlineStr">

--- a/artfynd/A 36363-2024 artfynd.xlsx
+++ b/artfynd/A 36363-2024 artfynd.xlsx
@@ -37002,7 +37002,7 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>122254588</v>
+        <v>122254660</v>
       </c>
       <c r="B272" t="n">
         <v>56285</v>
@@ -37056,10 +37056,10 @@
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>586415</v>
+        <v>586488</v>
       </c>
       <c r="R272" t="n">
-        <v>6311196</v>
+        <v>6311183</v>
       </c>
       <c r="S272" t="n">
         <v>5</v>
@@ -37091,7 +37091,7 @@
       </c>
       <c r="Z272" t="inlineStr">
         <is>
-          <t>23:22</t>
+          <t>22:31</t>
         </is>
       </c>
       <c r="AA272" t="inlineStr">
@@ -37101,7 +37101,7 @@
       </c>
       <c r="AB272" t="inlineStr">
         <is>
-          <t>23:23</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AC272" t="inlineStr">
@@ -37146,10 +37146,10 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>122254648</v>
+        <v>122254950</v>
       </c>
       <c r="B273" t="n">
-        <v>56285</v>
+        <v>56273</v>
       </c>
       <c r="C273" t="inlineStr">
         <is>
@@ -37162,21 +37162,21 @@
         </is>
       </c>
       <c r="E273" t="n">
-        <v>205995</v>
+        <v>205992</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
@@ -37200,10 +37200,10 @@
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>586418</v>
+        <v>586482</v>
       </c>
       <c r="R273" t="n">
-        <v>6311107</v>
+        <v>6311185</v>
       </c>
       <c r="S273" t="n">
         <v>5</v>
@@ -37235,7 +37235,7 @@
       </c>
       <c r="Z273" t="inlineStr">
         <is>
-          <t>22:36</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AA273" t="inlineStr">
@@ -37245,7 +37245,7 @@
       </c>
       <c r="AB273" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>23:31</t>
         </is>
       </c>
       <c r="AC273" t="inlineStr">
@@ -37290,7 +37290,7 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>122254633</v>
+        <v>122254659</v>
       </c>
       <c r="B274" t="n">
         <v>56285</v>
@@ -37344,10 +37344,10 @@
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>586396</v>
+        <v>586489</v>
       </c>
       <c r="R274" t="n">
-        <v>6311146</v>
+        <v>6311181</v>
       </c>
       <c r="S274" t="n">
         <v>5</v>
@@ -37379,7 +37379,7 @@
       </c>
       <c r="Z274" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>22:31</t>
         </is>
       </c>
       <c r="AA274" t="inlineStr">
@@ -37389,7 +37389,7 @@
       </c>
       <c r="AB274" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AC274" t="inlineStr">
@@ -37434,7 +37434,7 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>122254342</v>
+        <v>122254411</v>
       </c>
       <c r="B275" t="n">
         <v>56280</v>
@@ -37488,10 +37488,10 @@
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>586389</v>
+        <v>586414</v>
       </c>
       <c r="R275" t="n">
-        <v>6311142</v>
+        <v>6311126</v>
       </c>
       <c r="S275" t="n">
         <v>5</v>
@@ -37523,7 +37523,7 @@
       </c>
       <c r="Z275" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AA275" t="inlineStr">
@@ -37533,7 +37533,7 @@
       </c>
       <c r="AB275" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>22:38</t>
         </is>
       </c>
       <c r="AC275" t="inlineStr">
@@ -37578,7 +37578,7 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>122254316</v>
+        <v>122254307</v>
       </c>
       <c r="B276" t="n">
         <v>56280</v>
@@ -37632,10 +37632,10 @@
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>586423</v>
+        <v>586477</v>
       </c>
       <c r="R276" t="n">
-        <v>6311166</v>
+        <v>6311186</v>
       </c>
       <c r="S276" t="n">
         <v>5</v>
@@ -37667,7 +37667,7 @@
       </c>
       <c r="Z276" t="inlineStr">
         <is>
-          <t>23:23</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AA276" t="inlineStr">
@@ -37677,7 +37677,7 @@
       </c>
       <c r="AB276" t="inlineStr">
         <is>
-          <t>23:24</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AC276" t="inlineStr">
@@ -37722,7 +37722,7 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>122254371</v>
+        <v>122254420</v>
       </c>
       <c r="B277" t="n">
         <v>56280</v>
@@ -37776,10 +37776,10 @@
         </is>
       </c>
       <c r="Q277" t="n">
-        <v>586308</v>
+        <v>586467</v>
       </c>
       <c r="R277" t="n">
-        <v>6311132</v>
+        <v>6311178</v>
       </c>
       <c r="S277" t="n">
         <v>5</v>
@@ -37811,7 +37811,7 @@
       </c>
       <c r="Z277" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AA277" t="inlineStr">
@@ -37821,7 +37821,7 @@
       </c>
       <c r="AB277" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="AC277" t="inlineStr">
@@ -37866,10 +37866,10 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>122254957</v>
+        <v>122254417</v>
       </c>
       <c r="B278" t="n">
-        <v>56273</v>
+        <v>56280</v>
       </c>
       <c r="C278" t="inlineStr">
         <is>
@@ -37882,21 +37882,21 @@
         </is>
       </c>
       <c r="E278" t="n">
-        <v>205992</v>
+        <v>100092</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
@@ -37920,10 +37920,10 @@
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>586444</v>
+        <v>586426</v>
       </c>
       <c r="R278" t="n">
-        <v>6311160</v>
+        <v>6311145</v>
       </c>
       <c r="S278" t="n">
         <v>5</v>
@@ -37955,7 +37955,7 @@
       </c>
       <c r="Z278" t="inlineStr">
         <is>
-          <t>23:24</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="AA278" t="inlineStr">
@@ -37965,7 +37965,7 @@
       </c>
       <c r="AB278" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>22:34</t>
         </is>
       </c>
       <c r="AC278" t="inlineStr">
@@ -38010,10 +38010,10 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>122254644</v>
+        <v>122254316</v>
       </c>
       <c r="B279" t="n">
-        <v>56285</v>
+        <v>56280</v>
       </c>
       <c r="C279" t="inlineStr">
         <is>
@@ -38026,21 +38026,21 @@
         </is>
       </c>
       <c r="E279" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
@@ -38064,10 +38064,10 @@
         </is>
       </c>
       <c r="Q279" t="n">
-        <v>586429</v>
+        <v>586423</v>
       </c>
       <c r="R279" t="n">
-        <v>6311115</v>
+        <v>6311166</v>
       </c>
       <c r="S279" t="n">
         <v>5</v>
@@ -38099,7 +38099,7 @@
       </c>
       <c r="Z279" t="inlineStr">
         <is>
-          <t>22:36</t>
+          <t>23:23</t>
         </is>
       </c>
       <c r="AA279" t="inlineStr">
@@ -38109,7 +38109,7 @@
       </c>
       <c r="AB279" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="AC279" t="inlineStr">
@@ -38154,10 +38154,10 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>122254845</v>
+        <v>122254415</v>
       </c>
       <c r="B280" t="n">
-        <v>56283</v>
+        <v>56280</v>
       </c>
       <c r="C280" t="inlineStr">
         <is>
@@ -38170,21 +38170,21 @@
         </is>
       </c>
       <c r="E280" t="n">
-        <v>100111</v>
+        <v>100092</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
@@ -38208,10 +38208,10 @@
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>586370</v>
+        <v>586425</v>
       </c>
       <c r="R280" t="n">
-        <v>6311139</v>
+        <v>6311135</v>
       </c>
       <c r="S280" t="n">
         <v>5</v>
@@ -38243,7 +38243,7 @@
       </c>
       <c r="Z280" t="inlineStr">
         <is>
-          <t>22:59</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AA280" t="inlineStr">
@@ -38253,7 +38253,7 @@
       </c>
       <c r="AB280" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:38</t>
         </is>
       </c>
       <c r="AC280" t="inlineStr">
@@ -38298,10 +38298,10 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>122254862</v>
+        <v>122254315</v>
       </c>
       <c r="B281" t="n">
-        <v>56283</v>
+        <v>56280</v>
       </c>
       <c r="C281" t="inlineStr">
         <is>
@@ -38314,21 +38314,21 @@
         </is>
       </c>
       <c r="E281" t="n">
-        <v>100111</v>
+        <v>100092</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
@@ -38352,10 +38352,10 @@
         </is>
       </c>
       <c r="Q281" t="n">
-        <v>586288</v>
+        <v>586441</v>
       </c>
       <c r="R281" t="n">
-        <v>6311100</v>
+        <v>6311155</v>
       </c>
       <c r="S281" t="n">
         <v>5</v>
@@ -38387,7 +38387,7 @@
       </c>
       <c r="Z281" t="inlineStr">
         <is>
-          <t>22:55</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AA281" t="inlineStr">
@@ -38397,7 +38397,7 @@
       </c>
       <c r="AB281" t="inlineStr">
         <is>
-          <t>22:56</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AC281" t="inlineStr">
@@ -38442,37 +38442,37 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>122254173</v>
+        <v>122254846</v>
       </c>
       <c r="B282" t="n">
-        <v>56264</v>
+        <v>56283</v>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Dokumentation efterfrågas</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E282" t="n">
-        <v>100015</v>
+        <v>100111</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Barbastell</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Barbastella barbastellus</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
@@ -38496,10 +38496,10 @@
         </is>
       </c>
       <c r="Q282" t="n">
-        <v>586415</v>
+        <v>586370</v>
       </c>
       <c r="R282" t="n">
-        <v>6311149</v>
+        <v>6311139</v>
       </c>
       <c r="S282" t="n">
         <v>5</v>
@@ -38531,7 +38531,7 @@
       </c>
       <c r="Z282" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>22:59</t>
         </is>
       </c>
       <c r="AA282" t="inlineStr">
@@ -38541,7 +38541,7 @@
       </c>
       <c r="AB282" t="inlineStr">
         <is>
-          <t>23:03</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AC282" t="inlineStr">
@@ -38586,10 +38586,10 @@
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>122254413</v>
+        <v>122254609</v>
       </c>
       <c r="B283" t="n">
-        <v>56280</v>
+        <v>56285</v>
       </c>
       <c r="C283" t="inlineStr">
         <is>
@@ -38602,21 +38602,21 @@
         </is>
       </c>
       <c r="E283" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
@@ -38640,10 +38640,10 @@
         </is>
       </c>
       <c r="Q283" t="n">
-        <v>586423</v>
+        <v>586392</v>
       </c>
       <c r="R283" t="n">
-        <v>6311137</v>
+        <v>6311147</v>
       </c>
       <c r="S283" t="n">
         <v>5</v>
@@ -38675,7 +38675,7 @@
       </c>
       <c r="Z283" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AA283" t="inlineStr">
@@ -38685,7 +38685,7 @@
       </c>
       <c r="AB283" t="inlineStr">
         <is>
-          <t>22:38</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AC283" t="inlineStr">
@@ -38730,7 +38730,7 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>122254350</v>
+        <v>122254421</v>
       </c>
       <c r="B284" t="n">
         <v>56280</v>
@@ -38784,10 +38784,10 @@
         </is>
       </c>
       <c r="Q284" t="n">
-        <v>586330</v>
+        <v>586468</v>
       </c>
       <c r="R284" t="n">
-        <v>6311120</v>
+        <v>6311181</v>
       </c>
       <c r="S284" t="n">
         <v>5</v>
@@ -38819,7 +38819,7 @@
       </c>
       <c r="Z284" t="inlineStr">
         <is>
-          <t>22:57</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AA284" t="inlineStr">
@@ -38829,7 +38829,7 @@
       </c>
       <c r="AB284" t="inlineStr">
         <is>
-          <t>22:58</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="AC284" t="inlineStr">
@@ -38874,10 +38874,10 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>122254953</v>
+        <v>122254372</v>
       </c>
       <c r="B285" t="n">
-        <v>56273</v>
+        <v>56280</v>
       </c>
       <c r="C285" t="inlineStr">
         <is>
@@ -38890,21 +38890,21 @@
         </is>
       </c>
       <c r="E285" t="n">
-        <v>205992</v>
+        <v>100092</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
@@ -38928,10 +38928,10 @@
         </is>
       </c>
       <c r="Q285" t="n">
-        <v>586449</v>
+        <v>586306</v>
       </c>
       <c r="R285" t="n">
-        <v>6311155</v>
+        <v>6311131</v>
       </c>
       <c r="S285" t="n">
         <v>5</v>
@@ -38963,7 +38963,7 @@
       </c>
       <c r="Z285" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AA285" t="inlineStr">
@@ -38973,7 +38973,7 @@
       </c>
       <c r="AB285" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AC285" t="inlineStr">
@@ -39018,10 +39018,10 @@
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>122254472</v>
+        <v>122254313</v>
       </c>
       <c r="B286" t="n">
-        <v>56266</v>
+        <v>56280</v>
       </c>
       <c r="C286" t="inlineStr">
         <is>
@@ -39030,25 +39030,25 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E286" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
@@ -39072,10 +39072,10 @@
         </is>
       </c>
       <c r="Q286" t="n">
-        <v>586455</v>
+        <v>586449</v>
       </c>
       <c r="R286" t="n">
-        <v>6311159</v>
+        <v>6311155</v>
       </c>
       <c r="S286" t="n">
         <v>5</v>
@@ -39107,17 +39107,17 @@
       </c>
       <c r="Z286" t="inlineStr">
         <is>
+          <t>23:27</t>
+        </is>
+      </c>
+      <c r="AA286" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AB286" t="inlineStr">
+        <is>
           <t>23:28</t>
-        </is>
-      </c>
-      <c r="AA286" t="inlineStr">
-        <is>
-          <t>2024-06-26</t>
-        </is>
-      </c>
-      <c r="AB286" t="inlineStr">
-        <is>
-          <t>23:29</t>
         </is>
       </c>
       <c r="AC286" t="inlineStr">
@@ -39162,10 +39162,10 @@
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>122254650</v>
+        <v>122254310</v>
       </c>
       <c r="B287" t="n">
-        <v>56285</v>
+        <v>56280</v>
       </c>
       <c r="C287" t="inlineStr">
         <is>
@@ -39178,21 +39178,21 @@
         </is>
       </c>
       <c r="E287" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
@@ -39216,10 +39216,10 @@
         </is>
       </c>
       <c r="Q287" t="n">
-        <v>586422</v>
+        <v>586452</v>
       </c>
       <c r="R287" t="n">
-        <v>6311105</v>
+        <v>6311156</v>
       </c>
       <c r="S287" t="n">
         <v>5</v>
@@ -39251,7 +39251,7 @@
       </c>
       <c r="Z287" t="inlineStr">
         <is>
-          <t>22:35</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA287" t="inlineStr">
@@ -39261,7 +39261,7 @@
       </c>
       <c r="AB287" t="inlineStr">
         <is>
-          <t>22:36</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC287" t="inlineStr">
@@ -39306,10 +39306,10 @@
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>122254514</v>
+        <v>122254371</v>
       </c>
       <c r="B288" t="n">
-        <v>56266</v>
+        <v>56280</v>
       </c>
       <c r="C288" t="inlineStr">
         <is>
@@ -39318,25 +39318,25 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E288" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
@@ -39360,10 +39360,10 @@
         </is>
       </c>
       <c r="Q288" t="n">
-        <v>586408</v>
+        <v>586308</v>
       </c>
       <c r="R288" t="n">
-        <v>6311124</v>
+        <v>6311132</v>
       </c>
       <c r="S288" t="n">
         <v>5</v>
@@ -39395,7 +39395,7 @@
       </c>
       <c r="Z288" t="inlineStr">
         <is>
-          <t>22:43</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AA288" t="inlineStr">
@@ -39405,7 +39405,7 @@
       </c>
       <c r="AB288" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AC288" t="inlineStr">
@@ -39450,10 +39450,10 @@
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>122254341</v>
+        <v>122254626</v>
       </c>
       <c r="B289" t="n">
-        <v>56280</v>
+        <v>56285</v>
       </c>
       <c r="C289" t="inlineStr">
         <is>
@@ -39466,21 +39466,21 @@
         </is>
       </c>
       <c r="E289" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
@@ -39504,10 +39504,10 @@
         </is>
       </c>
       <c r="Q289" t="n">
-        <v>586415</v>
+        <v>586313</v>
       </c>
       <c r="R289" t="n">
-        <v>6311146</v>
+        <v>6311124</v>
       </c>
       <c r="S289" t="n">
         <v>5</v>
@@ -39539,7 +39539,7 @@
       </c>
       <c r="Z289" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AA289" t="inlineStr">
@@ -39549,7 +39549,7 @@
       </c>
       <c r="AB289" t="inlineStr">
         <is>
-          <t>23:03</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AC289" t="inlineStr">
@@ -39594,10 +39594,10 @@
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>122254415</v>
+        <v>122254606</v>
       </c>
       <c r="B290" t="n">
-        <v>56280</v>
+        <v>56285</v>
       </c>
       <c r="C290" t="inlineStr">
         <is>
@@ -39610,21 +39610,21 @@
         </is>
       </c>
       <c r="E290" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
@@ -39648,10 +39648,10 @@
         </is>
       </c>
       <c r="Q290" t="n">
-        <v>586425</v>
+        <v>586415</v>
       </c>
       <c r="R290" t="n">
-        <v>6311135</v>
+        <v>6311146</v>
       </c>
       <c r="S290" t="n">
         <v>5</v>
@@ -39683,7 +39683,7 @@
       </c>
       <c r="Z290" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AA290" t="inlineStr">
@@ -39693,7 +39693,7 @@
       </c>
       <c r="AB290" t="inlineStr">
         <is>
-          <t>22:38</t>
+          <t>23:03</t>
         </is>
       </c>
       <c r="AC290" t="inlineStr">
@@ -39738,10 +39738,10 @@
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>122254343</v>
+        <v>122254656</v>
       </c>
       <c r="B291" t="n">
-        <v>56280</v>
+        <v>56285</v>
       </c>
       <c r="C291" t="inlineStr">
         <is>
@@ -39754,21 +39754,21 @@
         </is>
       </c>
       <c r="E291" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
@@ -39792,10 +39792,10 @@
         </is>
       </c>
       <c r="Q291" t="n">
-        <v>586388</v>
+        <v>586483</v>
       </c>
       <c r="R291" t="n">
-        <v>6311142</v>
+        <v>6311186</v>
       </c>
       <c r="S291" t="n">
         <v>5</v>
@@ -39827,7 +39827,7 @@
       </c>
       <c r="Z291" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:31</t>
         </is>
       </c>
       <c r="AA291" t="inlineStr">
@@ -39837,7 +39837,7 @@
       </c>
       <c r="AB291" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AC291" t="inlineStr">
@@ -39882,7 +39882,7 @@
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>122254370</v>
+        <v>122254343</v>
       </c>
       <c r="B292" t="n">
         <v>56280</v>
@@ -39936,10 +39936,10 @@
         </is>
       </c>
       <c r="Q292" t="n">
-        <v>586309</v>
+        <v>586388</v>
       </c>
       <c r="R292" t="n">
-        <v>6311119</v>
+        <v>6311142</v>
       </c>
       <c r="S292" t="n">
         <v>5</v>
@@ -39971,7 +39971,7 @@
       </c>
       <c r="Z292" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA292" t="inlineStr">
@@ -39981,7 +39981,7 @@
       </c>
       <c r="AB292" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AC292" t="inlineStr">
@@ -40026,10 +40026,10 @@
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>122254625</v>
+        <v>122254370</v>
       </c>
       <c r="B293" t="n">
-        <v>56285</v>
+        <v>56280</v>
       </c>
       <c r="C293" t="inlineStr">
         <is>
@@ -40042,21 +40042,21 @@
         </is>
       </c>
       <c r="E293" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
@@ -40170,7 +40170,7 @@
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>122254519</v>
+        <v>122254472</v>
       </c>
       <c r="B294" t="n">
         <v>56266</v>
@@ -40224,10 +40224,10 @@
         </is>
       </c>
       <c r="Q294" t="n">
-        <v>586424</v>
+        <v>586455</v>
       </c>
       <c r="R294" t="n">
-        <v>6311135</v>
+        <v>6311159</v>
       </c>
       <c r="S294" t="n">
         <v>5</v>
@@ -40259,7 +40259,7 @@
       </c>
       <c r="Z294" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AA294" t="inlineStr">
@@ -40269,7 +40269,7 @@
       </c>
       <c r="AB294" t="inlineStr">
         <is>
-          <t>22:38</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AC294" t="inlineStr">
@@ -40314,7 +40314,7 @@
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>122254646</v>
+        <v>122254610</v>
       </c>
       <c r="B295" t="n">
         <v>56285</v>
@@ -40368,10 +40368,10 @@
         </is>
       </c>
       <c r="Q295" t="n">
-        <v>586422</v>
+        <v>586389</v>
       </c>
       <c r="R295" t="n">
-        <v>6311111</v>
+        <v>6311141</v>
       </c>
       <c r="S295" t="n">
         <v>5</v>
@@ -40403,7 +40403,7 @@
       </c>
       <c r="Z295" t="inlineStr">
         <is>
-          <t>22:36</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA295" t="inlineStr">
@@ -40413,7 +40413,7 @@
       </c>
       <c r="AB295" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AC295" t="inlineStr">
@@ -40458,10 +40458,10 @@
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>122254626</v>
+        <v>122254877</v>
       </c>
       <c r="B296" t="n">
-        <v>56285</v>
+        <v>56283</v>
       </c>
       <c r="C296" t="inlineStr">
         <is>
@@ -40474,21 +40474,21 @@
         </is>
       </c>
       <c r="E296" t="n">
-        <v>205995</v>
+        <v>100111</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
@@ -40512,10 +40512,10 @@
         </is>
       </c>
       <c r="Q296" t="n">
-        <v>586313</v>
+        <v>586276</v>
       </c>
       <c r="R296" t="n">
-        <v>6311124</v>
+        <v>6311100</v>
       </c>
       <c r="S296" t="n">
         <v>5</v>
@@ -40547,7 +40547,7 @@
       </c>
       <c r="Z296" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AA296" t="inlineStr">
@@ -40557,7 +40557,7 @@
       </c>
       <c r="AB296" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>22:52</t>
         </is>
       </c>
       <c r="AC296" t="inlineStr">
@@ -40602,10 +40602,10 @@
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>122254856</v>
+        <v>122254367</v>
       </c>
       <c r="B297" t="n">
-        <v>56283</v>
+        <v>56280</v>
       </c>
       <c r="C297" t="inlineStr">
         <is>
@@ -40618,21 +40618,21 @@
         </is>
       </c>
       <c r="E297" t="n">
-        <v>100111</v>
+        <v>100092</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
@@ -40656,10 +40656,10 @@
         </is>
       </c>
       <c r="Q297" t="n">
-        <v>586327</v>
+        <v>586280</v>
       </c>
       <c r="R297" t="n">
-        <v>6311118</v>
+        <v>6311103</v>
       </c>
       <c r="S297" t="n">
         <v>5</v>
@@ -40691,7 +40691,7 @@
       </c>
       <c r="Z297" t="inlineStr">
         <is>
-          <t>22:57</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AA297" t="inlineStr">
@@ -40701,7 +40701,7 @@
       </c>
       <c r="AB297" t="inlineStr">
         <is>
-          <t>22:58</t>
+          <t>22:52</t>
         </is>
       </c>
       <c r="AC297" t="inlineStr">
@@ -40746,7 +40746,7 @@
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>122254365</v>
+        <v>122254391</v>
       </c>
       <c r="B298" t="n">
         <v>56280</v>
@@ -40800,10 +40800,10 @@
         </is>
       </c>
       <c r="Q298" t="n">
-        <v>586276</v>
+        <v>586379</v>
       </c>
       <c r="R298" t="n">
-        <v>6311100</v>
+        <v>6311136</v>
       </c>
       <c r="S298" t="n">
         <v>5</v>
@@ -40835,7 +40835,7 @@
       </c>
       <c r="Z298" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AA298" t="inlineStr">
@@ -40845,7 +40845,7 @@
       </c>
       <c r="AB298" t="inlineStr">
         <is>
-          <t>22:52</t>
+          <t>22:46</t>
         </is>
       </c>
       <c r="AC298" t="inlineStr">
@@ -40890,10 +40890,10 @@
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>122254312</v>
+        <v>122254514</v>
       </c>
       <c r="B299" t="n">
-        <v>56280</v>
+        <v>56266</v>
       </c>
       <c r="C299" t="inlineStr">
         <is>
@@ -40902,25 +40902,25 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E299" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
@@ -40944,10 +40944,10 @@
         </is>
       </c>
       <c r="Q299" t="n">
-        <v>586452</v>
+        <v>586408</v>
       </c>
       <c r="R299" t="n">
-        <v>6311152</v>
+        <v>6311124</v>
       </c>
       <c r="S299" t="n">
         <v>5</v>
@@ -40979,7 +40979,7 @@
       </c>
       <c r="Z299" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>22:43</t>
         </is>
       </c>
       <c r="AA299" t="inlineStr">
@@ -40989,7 +40989,7 @@
       </c>
       <c r="AB299" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AC299" t="inlineStr">
@@ -41034,10 +41034,10 @@
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>122254306</v>
+        <v>122254959</v>
       </c>
       <c r="B300" t="n">
-        <v>56280</v>
+        <v>56273</v>
       </c>
       <c r="C300" t="inlineStr">
         <is>
@@ -41050,21 +41050,21 @@
         </is>
       </c>
       <c r="E300" t="n">
-        <v>100092</v>
+        <v>205992</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
@@ -41088,10 +41088,10 @@
         </is>
       </c>
       <c r="Q300" t="n">
-        <v>586473</v>
+        <v>586370</v>
       </c>
       <c r="R300" t="n">
-        <v>6311192</v>
+        <v>6311139</v>
       </c>
       <c r="S300" t="n">
         <v>5</v>
@@ -41123,7 +41123,7 @@
       </c>
       <c r="Z300" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>22:59</t>
         </is>
       </c>
       <c r="AA300" t="inlineStr">
@@ -41133,7 +41133,7 @@
       </c>
       <c r="AB300" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AC300" t="inlineStr">
@@ -41178,10 +41178,10 @@
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>122254475</v>
+        <v>122254615</v>
       </c>
       <c r="B301" t="n">
-        <v>56266</v>
+        <v>56285</v>
       </c>
       <c r="C301" t="inlineStr">
         <is>
@@ -41190,25 +41190,25 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E301" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
@@ -41232,10 +41232,10 @@
         </is>
       </c>
       <c r="Q301" t="n">
-        <v>586420</v>
+        <v>586329</v>
       </c>
       <c r="R301" t="n">
-        <v>6311166</v>
+        <v>6311120</v>
       </c>
       <c r="S301" t="n">
         <v>5</v>
@@ -41267,7 +41267,7 @@
       </c>
       <c r="Z301" t="inlineStr">
         <is>
-          <t>23:23</t>
+          <t>22:57</t>
         </is>
       </c>
       <c r="AA301" t="inlineStr">
@@ -41277,7 +41277,7 @@
       </c>
       <c r="AB301" t="inlineStr">
         <is>
-          <t>23:24</t>
+          <t>22:58</t>
         </is>
       </c>
       <c r="AC301" t="inlineStr">
@@ -41322,10 +41322,10 @@
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>122254474</v>
+        <v>122254651</v>
       </c>
       <c r="B302" t="n">
-        <v>56266</v>
+        <v>56285</v>
       </c>
       <c r="C302" t="inlineStr">
         <is>
@@ -41334,25 +41334,25 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E302" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
@@ -41376,10 +41376,10 @@
         </is>
       </c>
       <c r="Q302" t="n">
-        <v>586443</v>
+        <v>586425</v>
       </c>
       <c r="R302" t="n">
-        <v>6311164</v>
+        <v>6311113</v>
       </c>
       <c r="S302" t="n">
         <v>5</v>
@@ -41411,7 +41411,7 @@
       </c>
       <c r="Z302" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="AA302" t="inlineStr">
@@ -41421,7 +41421,7 @@
       </c>
       <c r="AB302" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>22:36</t>
         </is>
       </c>
       <c r="AC302" t="inlineStr">
@@ -41466,10 +41466,10 @@
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>122254964</v>
+        <v>122254655</v>
       </c>
       <c r="B303" t="n">
-        <v>56273</v>
+        <v>56285</v>
       </c>
       <c r="C303" t="inlineStr">
         <is>
@@ -41482,21 +41482,21 @@
         </is>
       </c>
       <c r="E303" t="n">
-        <v>205992</v>
+        <v>205995</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
@@ -41520,10 +41520,10 @@
         </is>
       </c>
       <c r="Q303" t="n">
-        <v>586430</v>
+        <v>586475</v>
       </c>
       <c r="R303" t="n">
-        <v>6311142</v>
+        <v>6311187</v>
       </c>
       <c r="S303" t="n">
         <v>5</v>
@@ -41555,17 +41555,17 @@
       </c>
       <c r="Z303" t="inlineStr">
         <is>
+          <t>22:32</t>
+        </is>
+      </c>
+      <c r="AA303" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AB303" t="inlineStr">
+        <is>
           <t>22:33</t>
-        </is>
-      </c>
-      <c r="AA303" t="inlineStr">
-        <is>
-          <t>2024-06-26</t>
-        </is>
-      </c>
-      <c r="AB303" t="inlineStr">
-        <is>
-          <t>22:34</t>
         </is>
       </c>
       <c r="AC303" t="inlineStr">
@@ -41610,7 +41610,7 @@
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>122254952</v>
+        <v>122254951</v>
       </c>
       <c r="B304" t="n">
         <v>56273</v>
@@ -41664,10 +41664,10 @@
         </is>
       </c>
       <c r="Q304" t="n">
-        <v>586455</v>
+        <v>586459</v>
       </c>
       <c r="R304" t="n">
-        <v>6311156</v>
+        <v>6311154</v>
       </c>
       <c r="S304" t="n">
         <v>5</v>
@@ -41754,10 +41754,10 @@
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>122254878</v>
+        <v>122254586</v>
       </c>
       <c r="B305" t="n">
-        <v>56283</v>
+        <v>56285</v>
       </c>
       <c r="C305" t="inlineStr">
         <is>
@@ -41770,21 +41770,21 @@
         </is>
       </c>
       <c r="E305" t="n">
-        <v>100111</v>
+        <v>205995</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
@@ -41808,10 +41808,10 @@
         </is>
       </c>
       <c r="Q305" t="n">
-        <v>586280</v>
+        <v>586446</v>
       </c>
       <c r="R305" t="n">
-        <v>6311103</v>
+        <v>6311158</v>
       </c>
       <c r="S305" t="n">
         <v>5</v>
@@ -41843,7 +41843,7 @@
       </c>
       <c r="Z305" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AA305" t="inlineStr">
@@ -41853,7 +41853,7 @@
       </c>
       <c r="AB305" t="inlineStr">
         <is>
-          <t>22:52</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AC305" t="inlineStr">
@@ -41898,10 +41898,10 @@
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>122254393</v>
+        <v>122254956</v>
       </c>
       <c r="B306" t="n">
-        <v>56280</v>
+        <v>56273</v>
       </c>
       <c r="C306" t="inlineStr">
         <is>
@@ -41914,21 +41914,21 @@
         </is>
       </c>
       <c r="E306" t="n">
-        <v>100092</v>
+        <v>205992</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
@@ -41952,10 +41952,10 @@
         </is>
       </c>
       <c r="Q306" t="n">
-        <v>586396</v>
+        <v>586441</v>
       </c>
       <c r="R306" t="n">
-        <v>6311146</v>
+        <v>6311152</v>
       </c>
       <c r="S306" t="n">
         <v>5</v>
@@ -41987,7 +41987,7 @@
       </c>
       <c r="Z306" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AA306" t="inlineStr">
@@ -41997,7 +41997,7 @@
       </c>
       <c r="AB306" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AC306" t="inlineStr">
@@ -42042,10 +42042,10 @@
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>122254416</v>
+        <v>122254966</v>
       </c>
       <c r="B307" t="n">
-        <v>56280</v>
+        <v>56273</v>
       </c>
       <c r="C307" t="inlineStr">
         <is>
@@ -42058,21 +42058,21 @@
         </is>
       </c>
       <c r="E307" t="n">
-        <v>100092</v>
+        <v>205992</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
@@ -42096,10 +42096,10 @@
         </is>
       </c>
       <c r="Q307" t="n">
-        <v>586410</v>
+        <v>586467</v>
       </c>
       <c r="R307" t="n">
-        <v>6311140</v>
+        <v>6311178</v>
       </c>
       <c r="S307" t="n">
         <v>5</v>
@@ -42131,17 +42131,17 @@
       </c>
       <c r="Z307" t="inlineStr">
         <is>
+          <t>22:32</t>
+        </is>
+      </c>
+      <c r="AA307" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AB307" t="inlineStr">
+        <is>
           <t>22:33</t>
-        </is>
-      </c>
-      <c r="AA307" t="inlineStr">
-        <is>
-          <t>2024-06-26</t>
-        </is>
-      </c>
-      <c r="AB307" t="inlineStr">
-        <is>
-          <t>22:34</t>
         </is>
       </c>
       <c r="AC307" t="inlineStr">
@@ -42186,10 +42186,10 @@
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>122254649</v>
+        <v>122254317</v>
       </c>
       <c r="B308" t="n">
-        <v>56285</v>
+        <v>56280</v>
       </c>
       <c r="C308" t="inlineStr">
         <is>
@@ -42202,21 +42202,21 @@
         </is>
       </c>
       <c r="E308" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
@@ -42240,10 +42240,10 @@
         </is>
       </c>
       <c r="Q308" t="n">
-        <v>586422</v>
+        <v>586438</v>
       </c>
       <c r="R308" t="n">
-        <v>6311100</v>
+        <v>6311222</v>
       </c>
       <c r="S308" t="n">
         <v>5</v>
@@ -42275,7 +42275,7 @@
       </c>
       <c r="Z308" t="inlineStr">
         <is>
-          <t>22:35</t>
+          <t>23:22</t>
         </is>
       </c>
       <c r="AA308" t="inlineStr">
@@ -42285,7 +42285,7 @@
       </c>
       <c r="AB308" t="inlineStr">
         <is>
-          <t>22:36</t>
+          <t>23:23</t>
         </is>
       </c>
       <c r="AC308" t="inlineStr">
@@ -42330,10 +42330,10 @@
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>122254585</v>
+        <v>122254390</v>
       </c>
       <c r="B309" t="n">
-        <v>56285</v>
+        <v>56280</v>
       </c>
       <c r="C309" t="inlineStr">
         <is>
@@ -42346,21 +42346,21 @@
         </is>
       </c>
       <c r="E309" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
@@ -42384,10 +42384,10 @@
         </is>
       </c>
       <c r="Q309" t="n">
-        <v>586455</v>
+        <v>586374</v>
       </c>
       <c r="R309" t="n">
-        <v>6311156</v>
+        <v>6311139</v>
       </c>
       <c r="S309" t="n">
         <v>5</v>
@@ -42419,7 +42419,7 @@
       </c>
       <c r="Z309" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>22:46</t>
         </is>
       </c>
       <c r="AA309" t="inlineStr">
@@ -42429,7 +42429,7 @@
       </c>
       <c r="AB309" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>22:47</t>
         </is>
       </c>
       <c r="AC309" t="inlineStr">
@@ -42474,10 +42474,10 @@
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>122254496</v>
+        <v>122254414</v>
       </c>
       <c r="B310" t="n">
-        <v>56266</v>
+        <v>56280</v>
       </c>
       <c r="C310" t="inlineStr">
         <is>
@@ -42486,25 +42486,25 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E310" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
@@ -42528,10 +42528,10 @@
         </is>
       </c>
       <c r="Q310" t="n">
-        <v>586415</v>
+        <v>586423</v>
       </c>
       <c r="R310" t="n">
-        <v>6311146</v>
+        <v>6311137</v>
       </c>
       <c r="S310" t="n">
         <v>5</v>
@@ -42563,7 +42563,7 @@
       </c>
       <c r="Z310" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AA310" t="inlineStr">
@@ -42573,7 +42573,7 @@
       </c>
       <c r="AB310" t="inlineStr">
         <is>
-          <t>23:03</t>
+          <t>22:38</t>
         </is>
       </c>
       <c r="AC310" t="inlineStr">
@@ -42618,10 +42618,10 @@
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>122254586</v>
+        <v>122254416</v>
       </c>
       <c r="B311" t="n">
-        <v>56285</v>
+        <v>56280</v>
       </c>
       <c r="C311" t="inlineStr">
         <is>
@@ -42634,21 +42634,21 @@
         </is>
       </c>
       <c r="E311" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
@@ -42672,10 +42672,10 @@
         </is>
       </c>
       <c r="Q311" t="n">
-        <v>586446</v>
+        <v>586410</v>
       </c>
       <c r="R311" t="n">
-        <v>6311158</v>
+        <v>6311140</v>
       </c>
       <c r="S311" t="n">
         <v>5</v>
@@ -42707,7 +42707,7 @@
       </c>
       <c r="Z311" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="AA311" t="inlineStr">
@@ -42717,7 +42717,7 @@
       </c>
       <c r="AB311" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>22:34</t>
         </is>
       </c>
       <c r="AC311" t="inlineStr">
@@ -42762,10 +42762,10 @@
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>122254617</v>
+        <v>122254350</v>
       </c>
       <c r="B312" t="n">
-        <v>56285</v>
+        <v>56280</v>
       </c>
       <c r="C312" t="inlineStr">
         <is>
@@ -42778,21 +42778,21 @@
         </is>
       </c>
       <c r="E312" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
@@ -42816,10 +42816,10 @@
         </is>
       </c>
       <c r="Q312" t="n">
-        <v>586317</v>
+        <v>586330</v>
       </c>
       <c r="R312" t="n">
-        <v>6311115</v>
+        <v>6311120</v>
       </c>
       <c r="S312" t="n">
         <v>5</v>
@@ -42906,7 +42906,7 @@
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>122254643</v>
+        <v>122254634</v>
       </c>
       <c r="B313" t="n">
         <v>56285</v>
@@ -42960,10 +42960,10 @@
         </is>
       </c>
       <c r="Q313" t="n">
-        <v>586424</v>
+        <v>586415</v>
       </c>
       <c r="R313" t="n">
-        <v>6311135</v>
+        <v>6311148</v>
       </c>
       <c r="S313" t="n">
         <v>5</v>
@@ -42995,7 +42995,7 @@
       </c>
       <c r="Z313" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AA313" t="inlineStr">
@@ -43005,7 +43005,7 @@
       </c>
       <c r="AB313" t="inlineStr">
         <is>
-          <t>22:38</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AC313" t="inlineStr">
@@ -43050,10 +43050,10 @@
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>122254307</v>
+        <v>122254496</v>
       </c>
       <c r="B314" t="n">
-        <v>56280</v>
+        <v>56266</v>
       </c>
       <c r="C314" t="inlineStr">
         <is>
@@ -43062,25 +43062,25 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E314" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
@@ -43104,10 +43104,10 @@
         </is>
       </c>
       <c r="Q314" t="n">
-        <v>586477</v>
+        <v>586415</v>
       </c>
       <c r="R314" t="n">
-        <v>6311186</v>
+        <v>6311146</v>
       </c>
       <c r="S314" t="n">
         <v>5</v>
@@ -43139,7 +43139,7 @@
       </c>
       <c r="Z314" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AA314" t="inlineStr">
@@ -43149,7 +43149,7 @@
       </c>
       <c r="AB314" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:03</t>
         </is>
       </c>
       <c r="AC314" t="inlineStr">
@@ -43194,10 +43194,10 @@
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>122254420</v>
+        <v>122254632</v>
       </c>
       <c r="B315" t="n">
-        <v>56280</v>
+        <v>56285</v>
       </c>
       <c r="C315" t="inlineStr">
         <is>
@@ -43210,21 +43210,21 @@
         </is>
       </c>
       <c r="E315" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
@@ -43248,10 +43248,10 @@
         </is>
       </c>
       <c r="Q315" t="n">
-        <v>586467</v>
+        <v>586374</v>
       </c>
       <c r="R315" t="n">
-        <v>6311178</v>
+        <v>6311140</v>
       </c>
       <c r="S315" t="n">
         <v>5</v>
@@ -43283,7 +43283,7 @@
       </c>
       <c r="Z315" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>22:46</t>
         </is>
       </c>
       <c r="AA315" t="inlineStr">
@@ -43293,7 +43293,7 @@
       </c>
       <c r="AB315" t="inlineStr">
         <is>
-          <t>22:33</t>
+          <t>22:47</t>
         </is>
       </c>
       <c r="AC315" t="inlineStr">
@@ -43338,7 +43338,7 @@
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>122254843</v>
+        <v>122254855</v>
       </c>
       <c r="B316" t="n">
         <v>56283</v>
@@ -43392,10 +43392,10 @@
         </is>
       </c>
       <c r="Q316" t="n">
-        <v>586389</v>
+        <v>586330</v>
       </c>
       <c r="R316" t="n">
-        <v>6311142</v>
+        <v>6311120</v>
       </c>
       <c r="S316" t="n">
         <v>5</v>
@@ -43427,7 +43427,7 @@
       </c>
       <c r="Z316" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:57</t>
         </is>
       </c>
       <c r="AA316" t="inlineStr">
@@ -43437,7 +43437,7 @@
       </c>
       <c r="AB316" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>22:58</t>
         </is>
       </c>
       <c r="AC316" t="inlineStr">
@@ -43482,7 +43482,7 @@
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>122254836</v>
+        <v>122254843</v>
       </c>
       <c r="B317" t="n">
         <v>56283</v>
@@ -43536,10 +43536,10 @@
         </is>
       </c>
       <c r="Q317" t="n">
-        <v>586474</v>
+        <v>586389</v>
       </c>
       <c r="R317" t="n">
-        <v>6311176</v>
+        <v>6311142</v>
       </c>
       <c r="S317" t="n">
         <v>5</v>
@@ -43571,7 +43571,7 @@
       </c>
       <c r="Z317" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA317" t="inlineStr">
@@ -43581,7 +43581,7 @@
       </c>
       <c r="AB317" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AC317" t="inlineStr">
@@ -43626,10 +43626,10 @@
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>122254417</v>
+        <v>122254837</v>
       </c>
       <c r="B318" t="n">
-        <v>56280</v>
+        <v>56283</v>
       </c>
       <c r="C318" t="inlineStr">
         <is>
@@ -43642,21 +43642,21 @@
         </is>
       </c>
       <c r="E318" t="n">
-        <v>100092</v>
+        <v>100111</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
@@ -43680,10 +43680,10 @@
         </is>
       </c>
       <c r="Q318" t="n">
-        <v>586426</v>
+        <v>586448</v>
       </c>
       <c r="R318" t="n">
-        <v>6311145</v>
+        <v>6311154</v>
       </c>
       <c r="S318" t="n">
         <v>5</v>
@@ -43715,7 +43715,7 @@
       </c>
       <c r="Z318" t="inlineStr">
         <is>
-          <t>22:33</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA318" t="inlineStr">
@@ -43725,7 +43725,7 @@
       </c>
       <c r="AB318" t="inlineStr">
         <is>
-          <t>22:34</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC318" t="inlineStr">
@@ -43770,10 +43770,10 @@
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>122254615</v>
+        <v>122254312</v>
       </c>
       <c r="B319" t="n">
-        <v>56285</v>
+        <v>56280</v>
       </c>
       <c r="C319" t="inlineStr">
         <is>
@@ -43786,21 +43786,21 @@
         </is>
       </c>
       <c r="E319" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
@@ -43824,10 +43824,10 @@
         </is>
       </c>
       <c r="Q319" t="n">
-        <v>586329</v>
+        <v>586452</v>
       </c>
       <c r="R319" t="n">
-        <v>6311120</v>
+        <v>6311152</v>
       </c>
       <c r="S319" t="n">
         <v>5</v>
@@ -43859,7 +43859,7 @@
       </c>
       <c r="Z319" t="inlineStr">
         <is>
-          <t>22:57</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA319" t="inlineStr">
@@ -43869,7 +43869,7 @@
       </c>
       <c r="AB319" t="inlineStr">
         <is>
-          <t>22:58</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC319" t="inlineStr">
@@ -43914,10 +43914,10 @@
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>122254503</v>
+        <v>122254627</v>
       </c>
       <c r="B320" t="n">
-        <v>56266</v>
+        <v>56285</v>
       </c>
       <c r="C320" t="inlineStr">
         <is>
@@ -43926,25 +43926,25 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E320" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
@@ -43968,10 +43968,10 @@
         </is>
       </c>
       <c r="Q320" t="n">
-        <v>586313</v>
+        <v>586306</v>
       </c>
       <c r="R320" t="n">
-        <v>6311124</v>
+        <v>6311131</v>
       </c>
       <c r="S320" t="n">
         <v>5</v>
@@ -44202,10 +44202,10 @@
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>122254512</v>
+        <v>122254588</v>
       </c>
       <c r="B322" t="n">
-        <v>56266</v>
+        <v>56285</v>
       </c>
       <c r="C322" t="inlineStr">
         <is>
@@ -44214,25 +44214,25 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E322" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
@@ -44256,10 +44256,10 @@
         </is>
       </c>
       <c r="Q322" t="n">
-        <v>586379</v>
+        <v>586415</v>
       </c>
       <c r="R322" t="n">
-        <v>6311136</v>
+        <v>6311196</v>
       </c>
       <c r="S322" t="n">
         <v>5</v>
@@ -44291,7 +44291,7 @@
       </c>
       <c r="Z322" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>23:22</t>
         </is>
       </c>
       <c r="AA322" t="inlineStr">
@@ -44301,7 +44301,7 @@
       </c>
       <c r="AB322" t="inlineStr">
         <is>
-          <t>22:46</t>
+          <t>23:23</t>
         </is>
       </c>
       <c r="AC322" t="inlineStr">
@@ -44346,10 +44346,10 @@
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>122254951</v>
+        <v>122254608</v>
       </c>
       <c r="B323" t="n">
-        <v>56273</v>
+        <v>56285</v>
       </c>
       <c r="C323" t="inlineStr">
         <is>
@@ -44362,21 +44362,21 @@
         </is>
       </c>
       <c r="E323" t="n">
-        <v>205992</v>
+        <v>205995</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
@@ -44400,10 +44400,10 @@
         </is>
       </c>
       <c r="Q323" t="n">
-        <v>586459</v>
+        <v>586393</v>
       </c>
       <c r="R323" t="n">
-        <v>6311154</v>
+        <v>6311147</v>
       </c>
       <c r="S323" t="n">
         <v>5</v>
@@ -44435,7 +44435,7 @@
       </c>
       <c r="Z323" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AA323" t="inlineStr">
@@ -44445,7 +44445,7 @@
       </c>
       <c r="AB323" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AC323" t="inlineStr">
@@ -44490,10 +44490,10 @@
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>122254963</v>
+        <v>122254513</v>
       </c>
       <c r="B324" t="n">
-        <v>56273</v>
+        <v>56266</v>
       </c>
       <c r="C324" t="inlineStr">
         <is>
@@ -44502,25 +44502,25 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E324" t="n">
-        <v>205992</v>
+        <v>205998</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
@@ -44544,10 +44544,10 @@
         </is>
       </c>
       <c r="Q324" t="n">
-        <v>586374</v>
+        <v>586396</v>
       </c>
       <c r="R324" t="n">
-        <v>6311140</v>
+        <v>6311146</v>
       </c>
       <c r="S324" t="n">
         <v>5</v>
@@ -44579,7 +44579,7 @@
       </c>
       <c r="Z324" t="inlineStr">
         <is>
-          <t>22:46</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AA324" t="inlineStr">
@@ -44589,7 +44589,7 @@
       </c>
       <c r="AB324" t="inlineStr">
         <is>
-          <t>22:47</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AC324" t="inlineStr">
@@ -44634,7 +44634,7 @@
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>122254308</v>
+        <v>122254318</v>
       </c>
       <c r="B325" t="n">
         <v>56280</v>
@@ -44691,7 +44691,7 @@
         <v>586455</v>
       </c>
       <c r="R325" t="n">
-        <v>6311159</v>
+        <v>6311228</v>
       </c>
       <c r="S325" t="n">
         <v>5</v>
@@ -44723,7 +44723,7 @@
       </c>
       <c r="Z325" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>23:22</t>
         </is>
       </c>
       <c r="AA325" t="inlineStr">
@@ -44733,7 +44733,7 @@
       </c>
       <c r="AB325" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>23:23</t>
         </is>
       </c>
       <c r="AC325" t="inlineStr">
@@ -44778,7 +44778,7 @@
     </row>
     <row r="326">
       <c r="A326" t="n">
-        <v>122254309</v>
+        <v>122254369</v>
       </c>
       <c r="B326" t="n">
         <v>56280</v>
@@ -44832,10 +44832,10 @@
         </is>
       </c>
       <c r="Q326" t="n">
-        <v>586456</v>
+        <v>586300</v>
       </c>
       <c r="R326" t="n">
-        <v>6311158</v>
+        <v>6311112</v>
       </c>
       <c r="S326" t="n">
         <v>5</v>
@@ -44867,7 +44867,7 @@
       </c>
       <c r="Z326" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AA326" t="inlineStr">
@@ -44877,7 +44877,7 @@
       </c>
       <c r="AB326" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AC326" t="inlineStr">
@@ -44922,10 +44922,10 @@
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>122254396</v>
+        <v>122254475</v>
       </c>
       <c r="B327" t="n">
-        <v>56280</v>
+        <v>56266</v>
       </c>
       <c r="C327" t="inlineStr">
         <is>
@@ -44934,25 +44934,25 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E327" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
@@ -44976,10 +44976,10 @@
         </is>
       </c>
       <c r="Q327" t="n">
-        <v>586408</v>
+        <v>586420</v>
       </c>
       <c r="R327" t="n">
-        <v>6311124</v>
+        <v>6311166</v>
       </c>
       <c r="S327" t="n">
         <v>5</v>
@@ -45011,7 +45011,7 @@
       </c>
       <c r="Z327" t="inlineStr">
         <is>
-          <t>22:43</t>
+          <t>23:23</t>
         </is>
       </c>
       <c r="AA327" t="inlineStr">
@@ -45021,7 +45021,7 @@
       </c>
       <c r="AB327" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="AC327" t="inlineStr">
@@ -45066,10 +45066,10 @@
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>122254651</v>
+        <v>122254500</v>
       </c>
       <c r="B328" t="n">
-        <v>56285</v>
+        <v>56266</v>
       </c>
       <c r="C328" t="inlineStr">
         <is>
@@ -45078,25 +45078,25 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E328" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
@@ -45120,10 +45120,10 @@
         </is>
       </c>
       <c r="Q328" t="n">
-        <v>586425</v>
+        <v>586388</v>
       </c>
       <c r="R328" t="n">
-        <v>6311113</v>
+        <v>6311142</v>
       </c>
       <c r="S328" t="n">
         <v>5</v>
@@ -45155,7 +45155,7 @@
       </c>
       <c r="Z328" t="inlineStr">
         <is>
-          <t>22:35</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA328" t="inlineStr">
@@ -45165,7 +45165,7 @@
       </c>
       <c r="AB328" t="inlineStr">
         <is>
-          <t>22:36</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AC328" t="inlineStr">
@@ -45210,10 +45210,10 @@
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>122254498</v>
+        <v>122254952</v>
       </c>
       <c r="B329" t="n">
-        <v>56266</v>
+        <v>56273</v>
       </c>
       <c r="C329" t="inlineStr">
         <is>
@@ -45222,25 +45222,25 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E329" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
@@ -45264,10 +45264,10 @@
         </is>
       </c>
       <c r="Q329" t="n">
-        <v>586393</v>
+        <v>586455</v>
       </c>
       <c r="R329" t="n">
-        <v>6311147</v>
+        <v>6311156</v>
       </c>
       <c r="S329" t="n">
         <v>5</v>
@@ -45299,7 +45299,7 @@
       </c>
       <c r="Z329" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AA329" t="inlineStr">
@@ -45309,7 +45309,7 @@
       </c>
       <c r="AB329" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AC329" t="inlineStr">
@@ -45354,10 +45354,10 @@
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>122254394</v>
+        <v>122254512</v>
       </c>
       <c r="B330" t="n">
-        <v>56280</v>
+        <v>56266</v>
       </c>
       <c r="C330" t="inlineStr">
         <is>
@@ -45366,25 +45366,25 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E330" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
@@ -45408,10 +45408,10 @@
         </is>
       </c>
       <c r="Q330" t="n">
-        <v>586419</v>
+        <v>586379</v>
       </c>
       <c r="R330" t="n">
-        <v>6311142</v>
+        <v>6311136</v>
       </c>
       <c r="S330" t="n">
         <v>5</v>
@@ -45443,7 +45443,7 @@
       </c>
       <c r="Z330" t="inlineStr">
         <is>
-          <t>22:43</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AA330" t="inlineStr">
@@ -45453,7 +45453,7 @@
       </c>
       <c r="AB330" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>22:46</t>
         </is>
       </c>
       <c r="AC330" t="inlineStr">
@@ -45498,10 +45498,10 @@
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>122254313</v>
+        <v>122254498</v>
       </c>
       <c r="B331" t="n">
-        <v>56280</v>
+        <v>56266</v>
       </c>
       <c r="C331" t="inlineStr">
         <is>
@@ -45510,25 +45510,25 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E331" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I331" t="inlineStr">
@@ -45552,10 +45552,10 @@
         </is>
       </c>
       <c r="Q331" t="n">
-        <v>586449</v>
+        <v>586393</v>
       </c>
       <c r="R331" t="n">
-        <v>6311155</v>
+        <v>6311147</v>
       </c>
       <c r="S331" t="n">
         <v>5</v>
@@ -45587,7 +45587,7 @@
       </c>
       <c r="Z331" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AA331" t="inlineStr">
@@ -45597,7 +45597,7 @@
       </c>
       <c r="AB331" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AC331" t="inlineStr">
@@ -45642,10 +45642,10 @@
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>122254857</v>
+        <v>122254393</v>
       </c>
       <c r="B332" t="n">
-        <v>56283</v>
+        <v>56280</v>
       </c>
       <c r="C332" t="inlineStr">
         <is>
@@ -45658,21 +45658,21 @@
         </is>
       </c>
       <c r="E332" t="n">
-        <v>100111</v>
+        <v>100092</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
@@ -45696,10 +45696,10 @@
         </is>
       </c>
       <c r="Q332" t="n">
-        <v>586317</v>
+        <v>586396</v>
       </c>
       <c r="R332" t="n">
-        <v>6311115</v>
+        <v>6311146</v>
       </c>
       <c r="S332" t="n">
         <v>5</v>
@@ -45731,7 +45731,7 @@
       </c>
       <c r="Z332" t="inlineStr">
         <is>
-          <t>22:57</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AA332" t="inlineStr">
@@ -45741,7 +45741,7 @@
       </c>
       <c r="AB332" t="inlineStr">
         <is>
-          <t>22:58</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AC332" t="inlineStr">
@@ -45786,10 +45786,10 @@
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>122254658</v>
+        <v>122254373</v>
       </c>
       <c r="B333" t="n">
-        <v>56285</v>
+        <v>56280</v>
       </c>
       <c r="C333" t="inlineStr">
         <is>
@@ -45802,21 +45802,21 @@
         </is>
       </c>
       <c r="E333" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
@@ -45840,10 +45840,10 @@
         </is>
       </c>
       <c r="Q333" t="n">
-        <v>586491</v>
+        <v>586307</v>
       </c>
       <c r="R333" t="n">
-        <v>6311181</v>
+        <v>6311133</v>
       </c>
       <c r="S333" t="n">
         <v>5</v>
@@ -45875,7 +45875,7 @@
       </c>
       <c r="Z333" t="inlineStr">
         <is>
-          <t>22:31</t>
+          <t>22:49</t>
         </is>
       </c>
       <c r="AA333" t="inlineStr">
@@ -45885,7 +45885,7 @@
       </c>
       <c r="AB333" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AC333" t="inlineStr">
@@ -45930,10 +45930,10 @@
     </row>
     <row r="334">
       <c r="A334" t="n">
-        <v>122254473</v>
+        <v>122254964</v>
       </c>
       <c r="B334" t="n">
-        <v>56266</v>
+        <v>56273</v>
       </c>
       <c r="C334" t="inlineStr">
         <is>
@@ -45942,25 +45942,25 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E334" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
@@ -45984,10 +45984,10 @@
         </is>
       </c>
       <c r="Q334" t="n">
-        <v>586450</v>
+        <v>586430</v>
       </c>
       <c r="R334" t="n">
-        <v>6311152</v>
+        <v>6311142</v>
       </c>
       <c r="S334" t="n">
         <v>5</v>
@@ -46019,7 +46019,7 @@
       </c>
       <c r="Z334" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="AA334" t="inlineStr">
@@ -46029,7 +46029,7 @@
       </c>
       <c r="AB334" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>22:34</t>
         </is>
       </c>
       <c r="AC334" t="inlineStr">
@@ -46074,10 +46074,10 @@
     </row>
     <row r="335">
       <c r="A335" t="n">
-        <v>122254317</v>
+        <v>122254474</v>
       </c>
       <c r="B335" t="n">
-        <v>56280</v>
+        <v>56266</v>
       </c>
       <c r="C335" t="inlineStr">
         <is>
@@ -46086,25 +46086,25 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E335" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I335" t="inlineStr">
@@ -46128,10 +46128,10 @@
         </is>
       </c>
       <c r="Q335" t="n">
-        <v>586438</v>
+        <v>586443</v>
       </c>
       <c r="R335" t="n">
-        <v>6311222</v>
+        <v>6311164</v>
       </c>
       <c r="S335" t="n">
         <v>5</v>
@@ -46163,7 +46163,7 @@
       </c>
       <c r="Z335" t="inlineStr">
         <is>
-          <t>23:22</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AA335" t="inlineStr">
@@ -46173,7 +46173,7 @@
       </c>
       <c r="AB335" t="inlineStr">
         <is>
-          <t>23:23</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AC335" t="inlineStr">
@@ -46218,7 +46218,7 @@
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>122254653</v>
+        <v>122254658</v>
       </c>
       <c r="B336" t="n">
         <v>56285</v>
@@ -46272,10 +46272,10 @@
         </is>
       </c>
       <c r="Q336" t="n">
-        <v>586430</v>
+        <v>586491</v>
       </c>
       <c r="R336" t="n">
-        <v>6311142</v>
+        <v>6311181</v>
       </c>
       <c r="S336" t="n">
         <v>5</v>
@@ -46307,7 +46307,7 @@
       </c>
       <c r="Z336" t="inlineStr">
         <is>
-          <t>22:33</t>
+          <t>22:31</t>
         </is>
       </c>
       <c r="AA336" t="inlineStr">
@@ -46317,7 +46317,7 @@
       </c>
       <c r="AB336" t="inlineStr">
         <is>
-          <t>22:34</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AC336" t="inlineStr">
@@ -46362,10 +46362,10 @@
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>122254632</v>
+        <v>122254954</v>
       </c>
       <c r="B337" t="n">
-        <v>56285</v>
+        <v>56273</v>
       </c>
       <c r="C337" t="inlineStr">
         <is>
@@ -46378,21 +46378,21 @@
         </is>
       </c>
       <c r="E337" t="n">
-        <v>205995</v>
+        <v>205992</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
@@ -46416,10 +46416,10 @@
         </is>
       </c>
       <c r="Q337" t="n">
-        <v>586374</v>
+        <v>586442</v>
       </c>
       <c r="R337" t="n">
-        <v>6311140</v>
+        <v>6311152</v>
       </c>
       <c r="S337" t="n">
         <v>5</v>
@@ -46451,7 +46451,7 @@
       </c>
       <c r="Z337" t="inlineStr">
         <is>
-          <t>22:46</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AA337" t="inlineStr">
@@ -46461,7 +46461,7 @@
       </c>
       <c r="AB337" t="inlineStr">
         <is>
-          <t>22:47</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AC337" t="inlineStr">
@@ -46506,7 +46506,7 @@
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>122254657</v>
+        <v>122254612</v>
       </c>
       <c r="B338" t="n">
         <v>56285</v>
@@ -46560,10 +46560,10 @@
         </is>
       </c>
       <c r="Q338" t="n">
-        <v>586488</v>
+        <v>586371</v>
       </c>
       <c r="R338" t="n">
-        <v>6311184</v>
+        <v>6311135</v>
       </c>
       <c r="S338" t="n">
         <v>5</v>
@@ -46595,7 +46595,7 @@
       </c>
       <c r="Z338" t="inlineStr">
         <is>
-          <t>22:31</t>
+          <t>22:59</t>
         </is>
       </c>
       <c r="AA338" t="inlineStr">
@@ -46605,7 +46605,7 @@
       </c>
       <c r="AB338" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AC338" t="inlineStr">
@@ -46650,7 +46650,7 @@
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>122254652</v>
+        <v>122254611</v>
       </c>
       <c r="B339" t="n">
         <v>56285</v>
@@ -46704,10 +46704,10 @@
         </is>
       </c>
       <c r="Q339" t="n">
-        <v>586432</v>
+        <v>586370</v>
       </c>
       <c r="R339" t="n">
-        <v>6311118</v>
+        <v>6311139</v>
       </c>
       <c r="S339" t="n">
         <v>5</v>
@@ -46739,7 +46739,7 @@
       </c>
       <c r="Z339" t="inlineStr">
         <is>
-          <t>22:34</t>
+          <t>22:59</t>
         </is>
       </c>
       <c r="AA339" t="inlineStr">
@@ -46749,7 +46749,7 @@
       </c>
       <c r="AB339" t="inlineStr">
         <is>
-          <t>22:35</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AC339" t="inlineStr">
@@ -46794,10 +46794,10 @@
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>122254391</v>
+        <v>122254648</v>
       </c>
       <c r="B340" t="n">
-        <v>56280</v>
+        <v>56285</v>
       </c>
       <c r="C340" t="inlineStr">
         <is>
@@ -46810,21 +46810,21 @@
         </is>
       </c>
       <c r="E340" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
@@ -46848,10 +46848,10 @@
         </is>
       </c>
       <c r="Q340" t="n">
-        <v>586379</v>
+        <v>586418</v>
       </c>
       <c r="R340" t="n">
-        <v>6311136</v>
+        <v>6311107</v>
       </c>
       <c r="S340" t="n">
         <v>5</v>
@@ -46883,7 +46883,7 @@
       </c>
       <c r="Z340" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>22:36</t>
         </is>
       </c>
       <c r="AA340" t="inlineStr">
@@ -46893,7 +46893,7 @@
       </c>
       <c r="AB340" t="inlineStr">
         <is>
-          <t>22:46</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AC340" t="inlineStr">
@@ -46938,10 +46938,10 @@
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>122254608</v>
+        <v>122254957</v>
       </c>
       <c r="B341" t="n">
-        <v>56285</v>
+        <v>56273</v>
       </c>
       <c r="C341" t="inlineStr">
         <is>
@@ -46954,21 +46954,21 @@
         </is>
       </c>
       <c r="E341" t="n">
-        <v>205995</v>
+        <v>205992</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I341" t="inlineStr">
@@ -46992,10 +46992,10 @@
         </is>
       </c>
       <c r="Q341" t="n">
-        <v>586393</v>
+        <v>586444</v>
       </c>
       <c r="R341" t="n">
-        <v>6311147</v>
+        <v>6311160</v>
       </c>
       <c r="S341" t="n">
         <v>5</v>
@@ -47027,7 +47027,7 @@
       </c>
       <c r="Z341" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="AA341" t="inlineStr">
@@ -47037,7 +47037,7 @@
       </c>
       <c r="AB341" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AC341" t="inlineStr">
@@ -47082,7 +47082,7 @@
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>122254634</v>
+        <v>122254584</v>
       </c>
       <c r="B342" t="n">
         <v>56285</v>
@@ -47136,10 +47136,10 @@
         </is>
       </c>
       <c r="Q342" t="n">
-        <v>586415</v>
+        <v>586473</v>
       </c>
       <c r="R342" t="n">
-        <v>6311148</v>
+        <v>6311192</v>
       </c>
       <c r="S342" t="n">
         <v>5</v>
@@ -47171,7 +47171,7 @@
       </c>
       <c r="Z342" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AA342" t="inlineStr">
@@ -47181,7 +47181,7 @@
       </c>
       <c r="AB342" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AC342" t="inlineStr">
@@ -47226,7 +47226,7 @@
     </row>
     <row r="343">
       <c r="A343" t="n">
-        <v>122254606</v>
+        <v>122254617</v>
       </c>
       <c r="B343" t="n">
         <v>56285</v>
@@ -47280,10 +47280,10 @@
         </is>
       </c>
       <c r="Q343" t="n">
-        <v>586415</v>
+        <v>586317</v>
       </c>
       <c r="R343" t="n">
-        <v>6311146</v>
+        <v>6311115</v>
       </c>
       <c r="S343" t="n">
         <v>5</v>
@@ -47315,7 +47315,7 @@
       </c>
       <c r="Z343" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>22:57</t>
         </is>
       </c>
       <c r="AA343" t="inlineStr">
@@ -47325,7 +47325,7 @@
       </c>
       <c r="AB343" t="inlineStr">
         <is>
-          <t>23:03</t>
+          <t>22:58</t>
         </is>
       </c>
       <c r="AC343" t="inlineStr">
@@ -47370,10 +47370,10 @@
     </row>
     <row r="344">
       <c r="A344" t="n">
-        <v>122254855</v>
+        <v>122254511</v>
       </c>
       <c r="B344" t="n">
-        <v>56283</v>
+        <v>56266</v>
       </c>
       <c r="C344" t="inlineStr">
         <is>
@@ -47382,25 +47382,25 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E344" t="n">
-        <v>100111</v>
+        <v>205998</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
@@ -47424,10 +47424,10 @@
         </is>
       </c>
       <c r="Q344" t="n">
-        <v>586330</v>
+        <v>586374</v>
       </c>
       <c r="R344" t="n">
-        <v>6311120</v>
+        <v>6311139</v>
       </c>
       <c r="S344" t="n">
         <v>5</v>
@@ -47459,7 +47459,7 @@
       </c>
       <c r="Z344" t="inlineStr">
         <is>
-          <t>22:57</t>
+          <t>22:46</t>
         </is>
       </c>
       <c r="AA344" t="inlineStr">
@@ -47469,7 +47469,7 @@
       </c>
       <c r="AB344" t="inlineStr">
         <is>
-          <t>22:58</t>
+          <t>22:47</t>
         </is>
       </c>
       <c r="AC344" t="inlineStr">
@@ -47514,37 +47514,37 @@
     </row>
     <row r="345">
       <c r="A345" t="n">
-        <v>122254837</v>
+        <v>122254173</v>
       </c>
       <c r="B345" t="n">
-        <v>56283</v>
+        <v>56264</v>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Dokumentation efterfrågas</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E345" t="n">
-        <v>100111</v>
+        <v>100015</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Barbastell</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Barbastella barbastellus</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
@@ -47568,10 +47568,10 @@
         </is>
       </c>
       <c r="Q345" t="n">
-        <v>586448</v>
+        <v>586415</v>
       </c>
       <c r="R345" t="n">
-        <v>6311154</v>
+        <v>6311149</v>
       </c>
       <c r="S345" t="n">
         <v>5</v>
@@ -47603,7 +47603,7 @@
       </c>
       <c r="Z345" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AA345" t="inlineStr">
@@ -47613,7 +47613,7 @@
       </c>
       <c r="AB345" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>23:03</t>
         </is>
       </c>
       <c r="AC345" t="inlineStr">
@@ -47658,10 +47658,10 @@
     </row>
     <row r="346">
       <c r="A346" t="n">
-        <v>122254412</v>
+        <v>122254854</v>
       </c>
       <c r="B346" t="n">
-        <v>56280</v>
+        <v>56283</v>
       </c>
       <c r="C346" t="inlineStr">
         <is>
@@ -47674,21 +47674,21 @@
         </is>
       </c>
       <c r="E346" t="n">
-        <v>100092</v>
+        <v>100111</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
@@ -47712,10 +47712,10 @@
         </is>
       </c>
       <c r="Q346" t="n">
-        <v>586424</v>
+        <v>586329</v>
       </c>
       <c r="R346" t="n">
-        <v>6311135</v>
+        <v>6311120</v>
       </c>
       <c r="S346" t="n">
         <v>5</v>
@@ -47747,7 +47747,7 @@
       </c>
       <c r="Z346" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>22:57</t>
         </is>
       </c>
       <c r="AA346" t="inlineStr">
@@ -47757,7 +47757,7 @@
       </c>
       <c r="AB346" t="inlineStr">
         <is>
-          <t>22:38</t>
+          <t>22:58</t>
         </is>
       </c>
       <c r="AC346" t="inlineStr">
@@ -47802,10 +47802,10 @@
     </row>
     <row r="347">
       <c r="A347" t="n">
-        <v>122254390</v>
+        <v>122254857</v>
       </c>
       <c r="B347" t="n">
-        <v>56280</v>
+        <v>56283</v>
       </c>
       <c r="C347" t="inlineStr">
         <is>
@@ -47818,21 +47818,21 @@
         </is>
       </c>
       <c r="E347" t="n">
-        <v>100092</v>
+        <v>100111</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I347" t="inlineStr">
@@ -47856,10 +47856,10 @@
         </is>
       </c>
       <c r="Q347" t="n">
-        <v>586374</v>
+        <v>586317</v>
       </c>
       <c r="R347" t="n">
-        <v>6311139</v>
+        <v>6311115</v>
       </c>
       <c r="S347" t="n">
         <v>5</v>
@@ -47891,7 +47891,7 @@
       </c>
       <c r="Z347" t="inlineStr">
         <is>
-          <t>22:46</t>
+          <t>22:57</t>
         </is>
       </c>
       <c r="AA347" t="inlineStr">
@@ -47901,7 +47901,7 @@
       </c>
       <c r="AB347" t="inlineStr">
         <is>
-          <t>22:47</t>
+          <t>22:58</t>
         </is>
       </c>
       <c r="AC347" t="inlineStr">
@@ -47946,10 +47946,10 @@
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>122254318</v>
+        <v>122254654</v>
       </c>
       <c r="B348" t="n">
-        <v>56280</v>
+        <v>56285</v>
       </c>
       <c r="C348" t="inlineStr">
         <is>
@@ -47962,21 +47962,21 @@
         </is>
       </c>
       <c r="E348" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I348" t="inlineStr">
@@ -48000,10 +48000,10 @@
         </is>
       </c>
       <c r="Q348" t="n">
-        <v>586455</v>
+        <v>586467</v>
       </c>
       <c r="R348" t="n">
-        <v>6311228</v>
+        <v>6311178</v>
       </c>
       <c r="S348" t="n">
         <v>5</v>
@@ -48035,7 +48035,7 @@
       </c>
       <c r="Z348" t="inlineStr">
         <is>
-          <t>23:22</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AA348" t="inlineStr">
@@ -48045,7 +48045,7 @@
       </c>
       <c r="AB348" t="inlineStr">
         <is>
-          <t>23:23</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="AC348" t="inlineStr">
@@ -48090,10 +48090,10 @@
     </row>
     <row r="349">
       <c r="A349" t="n">
-        <v>122254310</v>
+        <v>122254880</v>
       </c>
       <c r="B349" t="n">
-        <v>56280</v>
+        <v>56283</v>
       </c>
       <c r="C349" t="inlineStr">
         <is>
@@ -48106,21 +48106,21 @@
         </is>
       </c>
       <c r="E349" t="n">
-        <v>100092</v>
+        <v>100111</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I349" t="inlineStr">
@@ -48144,10 +48144,10 @@
         </is>
       </c>
       <c r="Q349" t="n">
-        <v>586452</v>
+        <v>586303</v>
       </c>
       <c r="R349" t="n">
-        <v>6311156</v>
+        <v>6311115</v>
       </c>
       <c r="S349" t="n">
         <v>5</v>
@@ -48179,7 +48179,7 @@
       </c>
       <c r="Z349" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AA349" t="inlineStr">
@@ -48189,7 +48189,7 @@
       </c>
       <c r="AB349" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AC349" t="inlineStr">
@@ -48234,10 +48234,10 @@
     </row>
     <row r="350">
       <c r="A350" t="n">
-        <v>122254655</v>
+        <v>122254844</v>
       </c>
       <c r="B350" t="n">
-        <v>56285</v>
+        <v>56283</v>
       </c>
       <c r="C350" t="inlineStr">
         <is>
@@ -48250,21 +48250,21 @@
         </is>
       </c>
       <c r="E350" t="n">
-        <v>205995</v>
+        <v>100111</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I350" t="inlineStr">
@@ -48288,10 +48288,10 @@
         </is>
       </c>
       <c r="Q350" t="n">
-        <v>586475</v>
+        <v>586387</v>
       </c>
       <c r="R350" t="n">
-        <v>6311187</v>
+        <v>6311141</v>
       </c>
       <c r="S350" t="n">
         <v>5</v>
@@ -48323,7 +48323,7 @@
       </c>
       <c r="Z350" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA350" t="inlineStr">
@@ -48333,7 +48333,7 @@
       </c>
       <c r="AB350" t="inlineStr">
         <is>
-          <t>22:33</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AC350" t="inlineStr">
@@ -48378,10 +48378,10 @@
     </row>
     <row r="351">
       <c r="A351" t="n">
-        <v>122254654</v>
+        <v>122254342</v>
       </c>
       <c r="B351" t="n">
-        <v>56285</v>
+        <v>56280</v>
       </c>
       <c r="C351" t="inlineStr">
         <is>
@@ -48394,21 +48394,21 @@
         </is>
       </c>
       <c r="E351" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I351" t="inlineStr">
@@ -48432,10 +48432,10 @@
         </is>
       </c>
       <c r="Q351" t="n">
-        <v>586467</v>
+        <v>586389</v>
       </c>
       <c r="R351" t="n">
-        <v>6311178</v>
+        <v>6311142</v>
       </c>
       <c r="S351" t="n">
         <v>5</v>
@@ -48467,7 +48467,7 @@
       </c>
       <c r="Z351" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA351" t="inlineStr">
@@ -48477,7 +48477,7 @@
       </c>
       <c r="AB351" t="inlineStr">
         <is>
-          <t>22:33</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AC351" t="inlineStr">
@@ -48522,10 +48522,10 @@
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>122254627</v>
+        <v>122254396</v>
       </c>
       <c r="B352" t="n">
-        <v>56285</v>
+        <v>56280</v>
       </c>
       <c r="C352" t="inlineStr">
         <is>
@@ -48538,21 +48538,21 @@
         </is>
       </c>
       <c r="E352" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I352" t="inlineStr">
@@ -48576,10 +48576,10 @@
         </is>
       </c>
       <c r="Q352" t="n">
-        <v>586306</v>
+        <v>586408</v>
       </c>
       <c r="R352" t="n">
-        <v>6311131</v>
+        <v>6311124</v>
       </c>
       <c r="S352" t="n">
         <v>5</v>
@@ -48611,7 +48611,7 @@
       </c>
       <c r="Z352" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>22:43</t>
         </is>
       </c>
       <c r="AA352" t="inlineStr">
@@ -48621,7 +48621,7 @@
       </c>
       <c r="AB352" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AC352" t="inlineStr">
@@ -48666,10 +48666,10 @@
     </row>
     <row r="353">
       <c r="A353" t="n">
-        <v>122254372</v>
+        <v>122254878</v>
       </c>
       <c r="B353" t="n">
-        <v>56280</v>
+        <v>56283</v>
       </c>
       <c r="C353" t="inlineStr">
         <is>
@@ -48682,21 +48682,21 @@
         </is>
       </c>
       <c r="E353" t="n">
-        <v>100092</v>
+        <v>100111</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I353" t="inlineStr">
@@ -48720,10 +48720,10 @@
         </is>
       </c>
       <c r="Q353" t="n">
-        <v>586306</v>
+        <v>586280</v>
       </c>
       <c r="R353" t="n">
-        <v>6311131</v>
+        <v>6311103</v>
       </c>
       <c r="S353" t="n">
         <v>5</v>
@@ -48755,7 +48755,7 @@
       </c>
       <c r="Z353" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AA353" t="inlineStr">
@@ -48765,7 +48765,7 @@
       </c>
       <c r="AB353" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>22:52</t>
         </is>
       </c>
       <c r="AC353" t="inlineStr">
@@ -48810,7 +48810,7 @@
     </row>
     <row r="354">
       <c r="A354" t="n">
-        <v>122254392</v>
+        <v>122254314</v>
       </c>
       <c r="B354" t="n">
         <v>56280</v>
@@ -48864,10 +48864,10 @@
         </is>
       </c>
       <c r="Q354" t="n">
-        <v>586384</v>
+        <v>586443</v>
       </c>
       <c r="R354" t="n">
-        <v>6311139</v>
+        <v>6311164</v>
       </c>
       <c r="S354" t="n">
         <v>5</v>
@@ -48899,7 +48899,7 @@
       </c>
       <c r="Z354" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AA354" t="inlineStr">
@@ -48909,7 +48909,7 @@
       </c>
       <c r="AB354" t="inlineStr">
         <is>
-          <t>22:46</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AC354" t="inlineStr">
@@ -48954,7 +48954,7 @@
     </row>
     <row r="355">
       <c r="A355" t="n">
-        <v>122254352</v>
+        <v>122254306</v>
       </c>
       <c r="B355" t="n">
         <v>56280</v>
@@ -49008,10 +49008,10 @@
         </is>
       </c>
       <c r="Q355" t="n">
-        <v>586288</v>
+        <v>586473</v>
       </c>
       <c r="R355" t="n">
-        <v>6311100</v>
+        <v>6311192</v>
       </c>
       <c r="S355" t="n">
         <v>5</v>
@@ -49043,7 +49043,7 @@
       </c>
       <c r="Z355" t="inlineStr">
         <is>
-          <t>22:55</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AA355" t="inlineStr">
@@ -49053,7 +49053,7 @@
       </c>
       <c r="AB355" t="inlineStr">
         <is>
-          <t>22:56</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AC355" t="inlineStr">
@@ -49098,10 +49098,10 @@
     </row>
     <row r="356">
       <c r="A356" t="n">
-        <v>122254315</v>
+        <v>122254633</v>
       </c>
       <c r="B356" t="n">
-        <v>56280</v>
+        <v>56285</v>
       </c>
       <c r="C356" t="inlineStr">
         <is>
@@ -49114,21 +49114,21 @@
         </is>
       </c>
       <c r="E356" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I356" t="inlineStr">
@@ -49152,10 +49152,10 @@
         </is>
       </c>
       <c r="Q356" t="n">
-        <v>586441</v>
+        <v>586396</v>
       </c>
       <c r="R356" t="n">
-        <v>6311155</v>
+        <v>6311146</v>
       </c>
       <c r="S356" t="n">
         <v>5</v>
@@ -49187,7 +49187,7 @@
       </c>
       <c r="Z356" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AA356" t="inlineStr">
@@ -49197,7 +49197,7 @@
       </c>
       <c r="AB356" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AC356" t="inlineStr">
@@ -49242,10 +49242,10 @@
     </row>
     <row r="357">
       <c r="A357" t="n">
-        <v>122254959</v>
+        <v>122254657</v>
       </c>
       <c r="B357" t="n">
-        <v>56273</v>
+        <v>56285</v>
       </c>
       <c r="C357" t="inlineStr">
         <is>
@@ -49258,21 +49258,21 @@
         </is>
       </c>
       <c r="E357" t="n">
-        <v>205992</v>
+        <v>205995</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I357" t="inlineStr">
@@ -49296,10 +49296,10 @@
         </is>
       </c>
       <c r="Q357" t="n">
-        <v>586370</v>
+        <v>586488</v>
       </c>
       <c r="R357" t="n">
-        <v>6311139</v>
+        <v>6311184</v>
       </c>
       <c r="S357" t="n">
         <v>5</v>
@@ -49331,7 +49331,7 @@
       </c>
       <c r="Z357" t="inlineStr">
         <is>
-          <t>22:59</t>
+          <t>22:31</t>
         </is>
       </c>
       <c r="AA357" t="inlineStr">
@@ -49341,7 +49341,7 @@
       </c>
       <c r="AB357" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AC357" t="inlineStr">
@@ -49386,10 +49386,10 @@
     </row>
     <row r="358">
       <c r="A358" t="n">
-        <v>122254513</v>
+        <v>122254652</v>
       </c>
       <c r="B358" t="n">
-        <v>56266</v>
+        <v>56285</v>
       </c>
       <c r="C358" t="inlineStr">
         <is>
@@ -49398,25 +49398,25 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E358" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H358" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I358" t="inlineStr">
@@ -49440,10 +49440,10 @@
         </is>
       </c>
       <c r="Q358" t="n">
-        <v>586396</v>
+        <v>586432</v>
       </c>
       <c r="R358" t="n">
-        <v>6311146</v>
+        <v>6311118</v>
       </c>
       <c r="S358" t="n">
         <v>5</v>
@@ -49475,7 +49475,7 @@
       </c>
       <c r="Z358" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>22:34</t>
         </is>
       </c>
       <c r="AA358" t="inlineStr">
@@ -49485,7 +49485,7 @@
       </c>
       <c r="AB358" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="AC358" t="inlineStr">
@@ -49530,10 +49530,10 @@
     </row>
     <row r="359">
       <c r="A359" t="n">
-        <v>122254511</v>
+        <v>122254308</v>
       </c>
       <c r="B359" t="n">
-        <v>56266</v>
+        <v>56280</v>
       </c>
       <c r="C359" t="inlineStr">
         <is>
@@ -49542,25 +49542,25 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E359" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I359" t="inlineStr">
@@ -49584,10 +49584,10 @@
         </is>
       </c>
       <c r="Q359" t="n">
-        <v>586374</v>
+        <v>586455</v>
       </c>
       <c r="R359" t="n">
-        <v>6311139</v>
+        <v>6311159</v>
       </c>
       <c r="S359" t="n">
         <v>5</v>
@@ -49619,7 +49619,7 @@
       </c>
       <c r="Z359" t="inlineStr">
         <is>
-          <t>22:46</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AA359" t="inlineStr">
@@ -49629,7 +49629,7 @@
       </c>
       <c r="AB359" t="inlineStr">
         <is>
-          <t>22:47</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AC359" t="inlineStr">
@@ -49674,10 +49674,10 @@
     </row>
     <row r="360">
       <c r="A360" t="n">
-        <v>122254609</v>
+        <v>122254476</v>
       </c>
       <c r="B360" t="n">
-        <v>56285</v>
+        <v>56266</v>
       </c>
       <c r="C360" t="inlineStr">
         <is>
@@ -49686,25 +49686,25 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E360" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I360" t="inlineStr">
@@ -49728,10 +49728,10 @@
         </is>
       </c>
       <c r="Q360" t="n">
-        <v>586392</v>
+        <v>586418</v>
       </c>
       <c r="R360" t="n">
-        <v>6311147</v>
+        <v>6311167</v>
       </c>
       <c r="S360" t="n">
         <v>5</v>
@@ -49763,7 +49763,7 @@
       </c>
       <c r="Z360" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>23:23</t>
         </is>
       </c>
       <c r="AA360" t="inlineStr">
@@ -49773,7 +49773,7 @@
       </c>
       <c r="AB360" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="AC360" t="inlineStr">
@@ -49818,7 +49818,7 @@
     </row>
     <row r="361">
       <c r="A361" t="n">
-        <v>122254656</v>
+        <v>122254649</v>
       </c>
       <c r="B361" t="n">
         <v>56285</v>
@@ -49872,10 +49872,10 @@
         </is>
       </c>
       <c r="Q361" t="n">
-        <v>586483</v>
+        <v>586422</v>
       </c>
       <c r="R361" t="n">
-        <v>6311186</v>
+        <v>6311100</v>
       </c>
       <c r="S361" t="n">
         <v>5</v>
@@ -49907,7 +49907,7 @@
       </c>
       <c r="Z361" t="inlineStr">
         <is>
-          <t>22:31</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="AA361" t="inlineStr">
@@ -49917,7 +49917,7 @@
       </c>
       <c r="AB361" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>22:36</t>
         </is>
       </c>
       <c r="AC361" t="inlineStr">
@@ -49962,7 +49962,7 @@
     </row>
     <row r="362">
       <c r="A362" t="n">
-        <v>122254616</v>
+        <v>122254643</v>
       </c>
       <c r="B362" t="n">
         <v>56285</v>
@@ -50016,10 +50016,10 @@
         </is>
       </c>
       <c r="Q362" t="n">
-        <v>586327</v>
+        <v>586424</v>
       </c>
       <c r="R362" t="n">
-        <v>6311118</v>
+        <v>6311135</v>
       </c>
       <c r="S362" t="n">
         <v>5</v>
@@ -50051,7 +50051,7 @@
       </c>
       <c r="Z362" t="inlineStr">
         <is>
-          <t>22:57</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AA362" t="inlineStr">
@@ -50061,7 +50061,7 @@
       </c>
       <c r="AB362" t="inlineStr">
         <is>
-          <t>22:58</t>
+          <t>22:38</t>
         </is>
       </c>
       <c r="AC362" t="inlineStr">
@@ -50106,10 +50106,10 @@
     </row>
     <row r="363">
       <c r="A363" t="n">
-        <v>122254880</v>
+        <v>122254953</v>
       </c>
       <c r="B363" t="n">
-        <v>56283</v>
+        <v>56273</v>
       </c>
       <c r="C363" t="inlineStr">
         <is>
@@ -50122,21 +50122,21 @@
         </is>
       </c>
       <c r="E363" t="n">
-        <v>100111</v>
+        <v>205992</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I363" t="inlineStr">
@@ -50160,10 +50160,10 @@
         </is>
       </c>
       <c r="Q363" t="n">
-        <v>586303</v>
+        <v>586449</v>
       </c>
       <c r="R363" t="n">
-        <v>6311115</v>
+        <v>6311155</v>
       </c>
       <c r="S363" t="n">
         <v>5</v>
@@ -50195,7 +50195,7 @@
       </c>
       <c r="Z363" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA363" t="inlineStr">
@@ -50205,7 +50205,7 @@
       </c>
       <c r="AB363" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC363" t="inlineStr">
@@ -50394,7 +50394,7 @@
     </row>
     <row r="365">
       <c r="A365" t="n">
-        <v>122254421</v>
+        <v>122254309</v>
       </c>
       <c r="B365" t="n">
         <v>56280</v>
@@ -50448,10 +50448,10 @@
         </is>
       </c>
       <c r="Q365" t="n">
-        <v>586468</v>
+        <v>586456</v>
       </c>
       <c r="R365" t="n">
-        <v>6311181</v>
+        <v>6311158</v>
       </c>
       <c r="S365" t="n">
         <v>5</v>
@@ -50483,7 +50483,7 @@
       </c>
       <c r="Z365" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AA365" t="inlineStr">
@@ -50493,7 +50493,7 @@
       </c>
       <c r="AB365" t="inlineStr">
         <is>
-          <t>22:33</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AC365" t="inlineStr">
@@ -50538,7 +50538,7 @@
     </row>
     <row r="366">
       <c r="A366" t="n">
-        <v>122254373</v>
+        <v>122254352</v>
       </c>
       <c r="B366" t="n">
         <v>56280</v>
@@ -50592,10 +50592,10 @@
         </is>
       </c>
       <c r="Q366" t="n">
-        <v>586307</v>
+        <v>586288</v>
       </c>
       <c r="R366" t="n">
-        <v>6311133</v>
+        <v>6311100</v>
       </c>
       <c r="S366" t="n">
         <v>5</v>
@@ -50627,7 +50627,7 @@
       </c>
       <c r="Z366" t="inlineStr">
         <is>
-          <t>22:49</t>
+          <t>22:55</t>
         </is>
       </c>
       <c r="AA366" t="inlineStr">
@@ -50637,7 +50637,7 @@
       </c>
       <c r="AB366" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>22:56</t>
         </is>
       </c>
       <c r="AC366" t="inlineStr">
@@ -50682,7 +50682,7 @@
     </row>
     <row r="367">
       <c r="A367" t="n">
-        <v>122254314</v>
+        <v>122254394</v>
       </c>
       <c r="B367" t="n">
         <v>56280</v>
@@ -50736,10 +50736,10 @@
         </is>
       </c>
       <c r="Q367" t="n">
-        <v>586443</v>
+        <v>586419</v>
       </c>
       <c r="R367" t="n">
-        <v>6311164</v>
+        <v>6311142</v>
       </c>
       <c r="S367" t="n">
         <v>5</v>
@@ -50771,7 +50771,7 @@
       </c>
       <c r="Z367" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>22:43</t>
         </is>
       </c>
       <c r="AA367" t="inlineStr">
@@ -50781,7 +50781,7 @@
       </c>
       <c r="AB367" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AC367" t="inlineStr">
@@ -50826,10 +50826,10 @@
     </row>
     <row r="368">
       <c r="A368" t="n">
-        <v>122254954</v>
+        <v>122254392</v>
       </c>
       <c r="B368" t="n">
-        <v>56273</v>
+        <v>56280</v>
       </c>
       <c r="C368" t="inlineStr">
         <is>
@@ -50842,21 +50842,21 @@
         </is>
       </c>
       <c r="E368" t="n">
-        <v>205992</v>
+        <v>100092</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H368" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I368" t="inlineStr">
@@ -50880,10 +50880,10 @@
         </is>
       </c>
       <c r="Q368" t="n">
-        <v>586442</v>
+        <v>586384</v>
       </c>
       <c r="R368" t="n">
-        <v>6311152</v>
+        <v>6311139</v>
       </c>
       <c r="S368" t="n">
         <v>5</v>
@@ -50915,7 +50915,7 @@
       </c>
       <c r="Z368" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AA368" t="inlineStr">
@@ -50925,7 +50925,7 @@
       </c>
       <c r="AB368" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>22:46</t>
         </is>
       </c>
       <c r="AC368" t="inlineStr">
@@ -50970,10 +50970,10 @@
     </row>
     <row r="369">
       <c r="A369" t="n">
-        <v>122254500</v>
+        <v>122254650</v>
       </c>
       <c r="B369" t="n">
-        <v>56266</v>
+        <v>56285</v>
       </c>
       <c r="C369" t="inlineStr">
         <is>
@@ -50982,25 +50982,25 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E369" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I369" t="inlineStr">
@@ -51024,10 +51024,10 @@
         </is>
       </c>
       <c r="Q369" t="n">
-        <v>586388</v>
+        <v>586422</v>
       </c>
       <c r="R369" t="n">
-        <v>6311142</v>
+        <v>6311105</v>
       </c>
       <c r="S369" t="n">
         <v>5</v>
@@ -51059,7 +51059,7 @@
       </c>
       <c r="Z369" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="AA369" t="inlineStr">
@@ -51069,7 +51069,7 @@
       </c>
       <c r="AB369" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>22:36</t>
         </is>
       </c>
       <c r="AC369" t="inlineStr">
@@ -51114,7 +51114,7 @@
     </row>
     <row r="370">
       <c r="A370" t="n">
-        <v>122254607</v>
+        <v>122254646</v>
       </c>
       <c r="B370" t="n">
         <v>56285</v>
@@ -51168,10 +51168,10 @@
         </is>
       </c>
       <c r="Q370" t="n">
-        <v>586415</v>
+        <v>586422</v>
       </c>
       <c r="R370" t="n">
-        <v>6311149</v>
+        <v>6311111</v>
       </c>
       <c r="S370" t="n">
         <v>5</v>
@@ -51203,7 +51203,7 @@
       </c>
       <c r="Z370" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>22:36</t>
         </is>
       </c>
       <c r="AA370" t="inlineStr">
@@ -51213,7 +51213,7 @@
       </c>
       <c r="AB370" t="inlineStr">
         <is>
-          <t>23:03</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AC370" t="inlineStr">
@@ -51258,10 +51258,10 @@
     </row>
     <row r="371">
       <c r="A371" t="n">
-        <v>122254844</v>
+        <v>122254607</v>
       </c>
       <c r="B371" t="n">
-        <v>56283</v>
+        <v>56285</v>
       </c>
       <c r="C371" t="inlineStr">
         <is>
@@ -51274,21 +51274,21 @@
         </is>
       </c>
       <c r="E371" t="n">
-        <v>100111</v>
+        <v>205995</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I371" t="inlineStr">
@@ -51312,10 +51312,10 @@
         </is>
       </c>
       <c r="Q371" t="n">
-        <v>586387</v>
+        <v>586415</v>
       </c>
       <c r="R371" t="n">
-        <v>6311141</v>
+        <v>6311149</v>
       </c>
       <c r="S371" t="n">
         <v>5</v>
@@ -51347,7 +51347,7 @@
       </c>
       <c r="Z371" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AA371" t="inlineStr">
@@ -51357,7 +51357,7 @@
       </c>
       <c r="AB371" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>23:03</t>
         </is>
       </c>
       <c r="AC371" t="inlineStr">
@@ -51402,7 +51402,7 @@
     </row>
     <row r="372">
       <c r="A372" t="n">
-        <v>122254584</v>
+        <v>122254616</v>
       </c>
       <c r="B372" t="n">
         <v>56285</v>
@@ -51456,10 +51456,10 @@
         </is>
       </c>
       <c r="Q372" t="n">
-        <v>586473</v>
+        <v>586327</v>
       </c>
       <c r="R372" t="n">
-        <v>6311192</v>
+        <v>6311118</v>
       </c>
       <c r="S372" t="n">
         <v>5</v>
@@ -51491,7 +51491,7 @@
       </c>
       <c r="Z372" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>22:57</t>
         </is>
       </c>
       <c r="AA372" t="inlineStr">
@@ -51501,7 +51501,7 @@
       </c>
       <c r="AB372" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>22:58</t>
         </is>
       </c>
       <c r="AC372" t="inlineStr">
@@ -51546,10 +51546,10 @@
     </row>
     <row r="373">
       <c r="A373" t="n">
-        <v>122254612</v>
+        <v>122254365</v>
       </c>
       <c r="B373" t="n">
-        <v>56285</v>
+        <v>56280</v>
       </c>
       <c r="C373" t="inlineStr">
         <is>
@@ -51562,21 +51562,21 @@
         </is>
       </c>
       <c r="E373" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H373" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I373" t="inlineStr">
@@ -51600,10 +51600,10 @@
         </is>
       </c>
       <c r="Q373" t="n">
-        <v>586371</v>
+        <v>586276</v>
       </c>
       <c r="R373" t="n">
-        <v>6311135</v>
+        <v>6311100</v>
       </c>
       <c r="S373" t="n">
         <v>5</v>
@@ -51635,7 +51635,7 @@
       </c>
       <c r="Z373" t="inlineStr">
         <is>
-          <t>22:59</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AA373" t="inlineStr">
@@ -51645,7 +51645,7 @@
       </c>
       <c r="AB373" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:52</t>
         </is>
       </c>
       <c r="AC373" t="inlineStr">
@@ -51690,7 +51690,7 @@
     </row>
     <row r="374">
       <c r="A374" t="n">
-        <v>122254635</v>
+        <v>122254644</v>
       </c>
       <c r="B374" t="n">
         <v>56285</v>
@@ -51744,10 +51744,10 @@
         </is>
       </c>
       <c r="Q374" t="n">
-        <v>586417</v>
+        <v>586429</v>
       </c>
       <c r="R374" t="n">
-        <v>6311145</v>
+        <v>6311115</v>
       </c>
       <c r="S374" t="n">
         <v>5</v>
@@ -51779,7 +51779,7 @@
       </c>
       <c r="Z374" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>22:36</t>
         </is>
       </c>
       <c r="AA374" t="inlineStr">
@@ -51789,7 +51789,7 @@
       </c>
       <c r="AB374" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AC374" t="inlineStr">
@@ -51834,10 +51834,10 @@
     </row>
     <row r="375">
       <c r="A375" t="n">
-        <v>122254611</v>
+        <v>122254862</v>
       </c>
       <c r="B375" t="n">
-        <v>56285</v>
+        <v>56283</v>
       </c>
       <c r="C375" t="inlineStr">
         <is>
@@ -51850,21 +51850,21 @@
         </is>
       </c>
       <c r="E375" t="n">
-        <v>205995</v>
+        <v>100111</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I375" t="inlineStr">
@@ -51888,10 +51888,10 @@
         </is>
       </c>
       <c r="Q375" t="n">
-        <v>586370</v>
+        <v>586288</v>
       </c>
       <c r="R375" t="n">
-        <v>6311139</v>
+        <v>6311100</v>
       </c>
       <c r="S375" t="n">
         <v>5</v>
@@ -51923,7 +51923,7 @@
       </c>
       <c r="Z375" t="inlineStr">
         <is>
-          <t>22:59</t>
+          <t>22:55</t>
         </is>
       </c>
       <c r="AA375" t="inlineStr">
@@ -51933,7 +51933,7 @@
       </c>
       <c r="AB375" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:56</t>
         </is>
       </c>
       <c r="AC375" t="inlineStr">
@@ -51978,10 +51978,10 @@
     </row>
     <row r="376">
       <c r="A376" t="n">
-        <v>122254367</v>
+        <v>122254856</v>
       </c>
       <c r="B376" t="n">
-        <v>56280</v>
+        <v>56283</v>
       </c>
       <c r="C376" t="inlineStr">
         <is>
@@ -51994,21 +51994,21 @@
         </is>
       </c>
       <c r="E376" t="n">
-        <v>100092</v>
+        <v>100111</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H376" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I376" t="inlineStr">
@@ -52032,10 +52032,10 @@
         </is>
       </c>
       <c r="Q376" t="n">
-        <v>586280</v>
+        <v>586327</v>
       </c>
       <c r="R376" t="n">
-        <v>6311103</v>
+        <v>6311118</v>
       </c>
       <c r="S376" t="n">
         <v>5</v>
@@ -52067,7 +52067,7 @@
       </c>
       <c r="Z376" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>22:57</t>
         </is>
       </c>
       <c r="AA376" t="inlineStr">
@@ -52077,7 +52077,7 @@
       </c>
       <c r="AB376" t="inlineStr">
         <is>
-          <t>22:52</t>
+          <t>22:58</t>
         </is>
       </c>
       <c r="AC376" t="inlineStr">
@@ -52122,10 +52122,10 @@
     </row>
     <row r="377">
       <c r="A377" t="n">
-        <v>122254956</v>
+        <v>122254625</v>
       </c>
       <c r="B377" t="n">
-        <v>56273</v>
+        <v>56285</v>
       </c>
       <c r="C377" t="inlineStr">
         <is>
@@ -52138,21 +52138,21 @@
         </is>
       </c>
       <c r="E377" t="n">
-        <v>205992</v>
+        <v>205995</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H377" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I377" t="inlineStr">
@@ -52176,10 +52176,10 @@
         </is>
       </c>
       <c r="Q377" t="n">
-        <v>586441</v>
+        <v>586309</v>
       </c>
       <c r="R377" t="n">
-        <v>6311152</v>
+        <v>6311119</v>
       </c>
       <c r="S377" t="n">
         <v>5</v>
@@ -52211,7 +52211,7 @@
       </c>
       <c r="Z377" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AA377" t="inlineStr">
@@ -52221,7 +52221,7 @@
       </c>
       <c r="AB377" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AC377" t="inlineStr">
@@ -52266,10 +52266,10 @@
     </row>
     <row r="378">
       <c r="A378" t="n">
-        <v>122254877</v>
+        <v>122254653</v>
       </c>
       <c r="B378" t="n">
-        <v>56283</v>
+        <v>56285</v>
       </c>
       <c r="C378" t="inlineStr">
         <is>
@@ -52282,21 +52282,21 @@
         </is>
       </c>
       <c r="E378" t="n">
-        <v>100111</v>
+        <v>205995</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I378" t="inlineStr">
@@ -52320,10 +52320,10 @@
         </is>
       </c>
       <c r="Q378" t="n">
-        <v>586276</v>
+        <v>586430</v>
       </c>
       <c r="R378" t="n">
-        <v>6311100</v>
+        <v>6311142</v>
       </c>
       <c r="S378" t="n">
         <v>5</v>
@@ -52355,7 +52355,7 @@
       </c>
       <c r="Z378" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="AA378" t="inlineStr">
@@ -52365,7 +52365,7 @@
       </c>
       <c r="AB378" t="inlineStr">
         <is>
-          <t>22:52</t>
+          <t>22:34</t>
         </is>
       </c>
       <c r="AC378" t="inlineStr">
@@ -52410,10 +52410,10 @@
     </row>
     <row r="379">
       <c r="A379" t="n">
-        <v>122254966</v>
+        <v>122254637</v>
       </c>
       <c r="B379" t="n">
-        <v>56273</v>
+        <v>56285</v>
       </c>
       <c r="C379" t="inlineStr">
         <is>
@@ -52426,21 +52426,21 @@
         </is>
       </c>
       <c r="E379" t="n">
-        <v>205992</v>
+        <v>205995</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H379" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I379" t="inlineStr">
@@ -52464,10 +52464,10 @@
         </is>
       </c>
       <c r="Q379" t="n">
-        <v>586467</v>
+        <v>586408</v>
       </c>
       <c r="R379" t="n">
-        <v>6311178</v>
+        <v>6311124</v>
       </c>
       <c r="S379" t="n">
         <v>5</v>
@@ -52499,7 +52499,7 @@
       </c>
       <c r="Z379" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>22:43</t>
         </is>
       </c>
       <c r="AA379" t="inlineStr">
@@ -52509,7 +52509,7 @@
       </c>
       <c r="AB379" t="inlineStr">
         <is>
-          <t>22:33</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AC379" t="inlineStr">
@@ -52554,10 +52554,10 @@
     </row>
     <row r="380">
       <c r="A380" t="n">
-        <v>122254660</v>
+        <v>122254412</v>
       </c>
       <c r="B380" t="n">
-        <v>56285</v>
+        <v>56280</v>
       </c>
       <c r="C380" t="inlineStr">
         <is>
@@ -52570,21 +52570,21 @@
         </is>
       </c>
       <c r="E380" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H380" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I380" t="inlineStr">
@@ -52608,10 +52608,10 @@
         </is>
       </c>
       <c r="Q380" t="n">
-        <v>586488</v>
+        <v>586424</v>
       </c>
       <c r="R380" t="n">
-        <v>6311183</v>
+        <v>6311135</v>
       </c>
       <c r="S380" t="n">
         <v>5</v>
@@ -52643,7 +52643,7 @@
       </c>
       <c r="Z380" t="inlineStr">
         <is>
-          <t>22:31</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AA380" t="inlineStr">
@@ -52653,7 +52653,7 @@
       </c>
       <c r="AB380" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>22:38</t>
         </is>
       </c>
       <c r="AC380" t="inlineStr">
@@ -52698,7 +52698,7 @@
     </row>
     <row r="381">
       <c r="A381" t="n">
-        <v>122254610</v>
+        <v>122254635</v>
       </c>
       <c r="B381" t="n">
         <v>56285</v>
@@ -52752,10 +52752,10 @@
         </is>
       </c>
       <c r="Q381" t="n">
-        <v>586389</v>
+        <v>586417</v>
       </c>
       <c r="R381" t="n">
-        <v>6311141</v>
+        <v>6311145</v>
       </c>
       <c r="S381" t="n">
         <v>5</v>
@@ -52787,7 +52787,7 @@
       </c>
       <c r="Z381" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AA381" t="inlineStr">
@@ -52797,7 +52797,7 @@
       </c>
       <c r="AB381" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AC381" t="inlineStr">
@@ -52842,10 +52842,10 @@
     </row>
     <row r="382">
       <c r="A382" t="n">
-        <v>122254411</v>
+        <v>122254963</v>
       </c>
       <c r="B382" t="n">
-        <v>56280</v>
+        <v>56273</v>
       </c>
       <c r="C382" t="inlineStr">
         <is>
@@ -52858,21 +52858,21 @@
         </is>
       </c>
       <c r="E382" t="n">
-        <v>100092</v>
+        <v>205992</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H382" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I382" t="inlineStr">
@@ -52896,10 +52896,10 @@
         </is>
       </c>
       <c r="Q382" t="n">
-        <v>586414</v>
+        <v>586374</v>
       </c>
       <c r="R382" t="n">
-        <v>6311126</v>
+        <v>6311140</v>
       </c>
       <c r="S382" t="n">
         <v>5</v>
@@ -52931,7 +52931,7 @@
       </c>
       <c r="Z382" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>22:46</t>
         </is>
       </c>
       <c r="AA382" t="inlineStr">
@@ -52941,7 +52941,7 @@
       </c>
       <c r="AB382" t="inlineStr">
         <is>
-          <t>22:38</t>
+          <t>22:47</t>
         </is>
       </c>
       <c r="AC382" t="inlineStr">
@@ -52986,10 +52986,10 @@
     </row>
     <row r="383">
       <c r="A383" t="n">
-        <v>122254950</v>
+        <v>122254473</v>
       </c>
       <c r="B383" t="n">
-        <v>56273</v>
+        <v>56266</v>
       </c>
       <c r="C383" t="inlineStr">
         <is>
@@ -52998,25 +52998,25 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E383" t="n">
-        <v>205992</v>
+        <v>205998</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I383" t="inlineStr">
@@ -53040,10 +53040,10 @@
         </is>
       </c>
       <c r="Q383" t="n">
-        <v>586482</v>
+        <v>586450</v>
       </c>
       <c r="R383" t="n">
-        <v>6311185</v>
+        <v>6311152</v>
       </c>
       <c r="S383" t="n">
         <v>5</v>
@@ -53075,7 +53075,7 @@
       </c>
       <c r="Z383" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA383" t="inlineStr">
@@ -53085,7 +53085,7 @@
       </c>
       <c r="AB383" t="inlineStr">
         <is>
-          <t>23:31</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC383" t="inlineStr">
@@ -53130,7 +53130,7 @@
     </row>
     <row r="384">
       <c r="A384" t="n">
-        <v>122254636</v>
+        <v>122254587</v>
       </c>
       <c r="B384" t="n">
         <v>56285</v>
@@ -53184,10 +53184,10 @@
         </is>
       </c>
       <c r="Q384" t="n">
-        <v>586418</v>
+        <v>586443</v>
       </c>
       <c r="R384" t="n">
-        <v>6311145</v>
+        <v>6311163</v>
       </c>
       <c r="S384" t="n">
         <v>5</v>
@@ -53219,7 +53219,7 @@
       </c>
       <c r="Z384" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AA384" t="inlineStr">
@@ -53229,7 +53229,7 @@
       </c>
       <c r="AB384" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AC384" t="inlineStr">
@@ -53274,10 +53274,10 @@
     </row>
     <row r="385">
       <c r="A385" t="n">
-        <v>122254659</v>
+        <v>122254341</v>
       </c>
       <c r="B385" t="n">
-        <v>56285</v>
+        <v>56280</v>
       </c>
       <c r="C385" t="inlineStr">
         <is>
@@ -53290,21 +53290,21 @@
         </is>
       </c>
       <c r="E385" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H385" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I385" t="inlineStr">
@@ -53328,10 +53328,10 @@
         </is>
       </c>
       <c r="Q385" t="n">
-        <v>586489</v>
+        <v>586415</v>
       </c>
       <c r="R385" t="n">
-        <v>6311181</v>
+        <v>6311146</v>
       </c>
       <c r="S385" t="n">
         <v>5</v>
@@ -53363,7 +53363,7 @@
       </c>
       <c r="Z385" t="inlineStr">
         <is>
-          <t>22:31</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AA385" t="inlineStr">
@@ -53373,7 +53373,7 @@
       </c>
       <c r="AB385" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>23:03</t>
         </is>
       </c>
       <c r="AC385" t="inlineStr">
@@ -53418,10 +53418,10 @@
     </row>
     <row r="386">
       <c r="A386" t="n">
-        <v>122254587</v>
+        <v>122254503</v>
       </c>
       <c r="B386" t="n">
-        <v>56285</v>
+        <v>56266</v>
       </c>
       <c r="C386" t="inlineStr">
         <is>
@@ -53430,25 +53430,25 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E386" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H386" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I386" t="inlineStr">
@@ -53472,10 +53472,10 @@
         </is>
       </c>
       <c r="Q386" t="n">
-        <v>586443</v>
+        <v>586313</v>
       </c>
       <c r="R386" t="n">
-        <v>6311163</v>
+        <v>6311124</v>
       </c>
       <c r="S386" t="n">
         <v>5</v>
@@ -53507,7 +53507,7 @@
       </c>
       <c r="Z386" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AA386" t="inlineStr">
@@ -53517,7 +53517,7 @@
       </c>
       <c r="AB386" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AC386" t="inlineStr">
@@ -53562,7 +53562,7 @@
     </row>
     <row r="387">
       <c r="A387" t="n">
-        <v>122254476</v>
+        <v>122254519</v>
       </c>
       <c r="B387" t="n">
         <v>56266</v>
@@ -53616,10 +53616,10 @@
         </is>
       </c>
       <c r="Q387" t="n">
-        <v>586418</v>
+        <v>586424</v>
       </c>
       <c r="R387" t="n">
-        <v>6311167</v>
+        <v>6311135</v>
       </c>
       <c r="S387" t="n">
         <v>5</v>
@@ -53651,7 +53651,7 @@
       </c>
       <c r="Z387" t="inlineStr">
         <is>
-          <t>23:23</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AA387" t="inlineStr">
@@ -53661,7 +53661,7 @@
       </c>
       <c r="AB387" t="inlineStr">
         <is>
-          <t>23:24</t>
+          <t>22:38</t>
         </is>
       </c>
       <c r="AC387" t="inlineStr">
@@ -53706,7 +53706,7 @@
     </row>
     <row r="388">
       <c r="A388" t="n">
-        <v>122254637</v>
+        <v>122254585</v>
       </c>
       <c r="B388" t="n">
         <v>56285</v>
@@ -53760,10 +53760,10 @@
         </is>
       </c>
       <c r="Q388" t="n">
-        <v>586408</v>
+        <v>586455</v>
       </c>
       <c r="R388" t="n">
-        <v>6311124</v>
+        <v>6311156</v>
       </c>
       <c r="S388" t="n">
         <v>5</v>
@@ -53795,7 +53795,7 @@
       </c>
       <c r="Z388" t="inlineStr">
         <is>
-          <t>22:43</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AA388" t="inlineStr">
@@ -53805,7 +53805,7 @@
       </c>
       <c r="AB388" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AC388" t="inlineStr">
@@ -53850,10 +53850,10 @@
     </row>
     <row r="389">
       <c r="A389" t="n">
-        <v>122254854</v>
+        <v>122254636</v>
       </c>
       <c r="B389" t="n">
-        <v>56283</v>
+        <v>56285</v>
       </c>
       <c r="C389" t="inlineStr">
         <is>
@@ -53866,21 +53866,21 @@
         </is>
       </c>
       <c r="E389" t="n">
-        <v>100111</v>
+        <v>205995</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I389" t="inlineStr">
@@ -53904,10 +53904,10 @@
         </is>
       </c>
       <c r="Q389" t="n">
-        <v>586329</v>
+        <v>586418</v>
       </c>
       <c r="R389" t="n">
-        <v>6311120</v>
+        <v>6311145</v>
       </c>
       <c r="S389" t="n">
         <v>5</v>
@@ -53939,7 +53939,7 @@
       </c>
       <c r="Z389" t="inlineStr">
         <is>
-          <t>22:57</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AA389" t="inlineStr">
@@ -53949,7 +53949,7 @@
       </c>
       <c r="AB389" t="inlineStr">
         <is>
-          <t>22:58</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AC389" t="inlineStr">
@@ -53994,10 +53994,10 @@
     </row>
     <row r="390">
       <c r="A390" t="n">
-        <v>122254369</v>
+        <v>122254836</v>
       </c>
       <c r="B390" t="n">
-        <v>56280</v>
+        <v>56283</v>
       </c>
       <c r="C390" t="inlineStr">
         <is>
@@ -54010,21 +54010,21 @@
         </is>
       </c>
       <c r="E390" t="n">
-        <v>100092</v>
+        <v>100111</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I390" t="inlineStr">
@@ -54048,10 +54048,10 @@
         </is>
       </c>
       <c r="Q390" t="n">
-        <v>586300</v>
+        <v>586474</v>
       </c>
       <c r="R390" t="n">
-        <v>6311112</v>
+        <v>6311176</v>
       </c>
       <c r="S390" t="n">
         <v>5</v>
@@ -54083,7 +54083,7 @@
       </c>
       <c r="Z390" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AA390" t="inlineStr">
@@ -54093,7 +54093,7 @@
       </c>
       <c r="AB390" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AC390" t="inlineStr">

--- a/artfynd/A 36363-2024 artfynd.xlsx
+++ b/artfynd/A 36363-2024 artfynd.xlsx
@@ -37002,10 +37002,10 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>122254660</v>
+        <v>122254844</v>
       </c>
       <c r="B272" t="n">
-        <v>56285</v>
+        <v>56283</v>
       </c>
       <c r="C272" t="inlineStr">
         <is>
@@ -37018,21 +37018,21 @@
         </is>
       </c>
       <c r="E272" t="n">
-        <v>205995</v>
+        <v>100111</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
@@ -37056,10 +37056,10 @@
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>586488</v>
+        <v>586387</v>
       </c>
       <c r="R272" t="n">
-        <v>6311183</v>
+        <v>6311141</v>
       </c>
       <c r="S272" t="n">
         <v>5</v>
@@ -37091,7 +37091,7 @@
       </c>
       <c r="Z272" t="inlineStr">
         <is>
-          <t>22:31</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA272" t="inlineStr">
@@ -37101,7 +37101,7 @@
       </c>
       <c r="AB272" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AC272" t="inlineStr">
@@ -37146,10 +37146,10 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>122254950</v>
+        <v>122254837</v>
       </c>
       <c r="B273" t="n">
-        <v>56273</v>
+        <v>56283</v>
       </c>
       <c r="C273" t="inlineStr">
         <is>
@@ -37162,21 +37162,21 @@
         </is>
       </c>
       <c r="E273" t="n">
-        <v>205992</v>
+        <v>100111</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
@@ -37200,10 +37200,10 @@
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>586482</v>
+        <v>586448</v>
       </c>
       <c r="R273" t="n">
-        <v>6311185</v>
+        <v>6311154</v>
       </c>
       <c r="S273" t="n">
         <v>5</v>
@@ -37235,7 +37235,7 @@
       </c>
       <c r="Z273" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA273" t="inlineStr">
@@ -37245,7 +37245,7 @@
       </c>
       <c r="AB273" t="inlineStr">
         <is>
-          <t>23:31</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC273" t="inlineStr">
@@ -37290,10 +37290,10 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>122254659</v>
+        <v>122254394</v>
       </c>
       <c r="B274" t="n">
-        <v>56285</v>
+        <v>56280</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>
@@ -37306,21 +37306,21 @@
         </is>
       </c>
       <c r="E274" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
@@ -37344,10 +37344,10 @@
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>586489</v>
+        <v>586419</v>
       </c>
       <c r="R274" t="n">
-        <v>6311181</v>
+        <v>6311142</v>
       </c>
       <c r="S274" t="n">
         <v>5</v>
@@ -37379,7 +37379,7 @@
       </c>
       <c r="Z274" t="inlineStr">
         <is>
-          <t>22:31</t>
+          <t>22:43</t>
         </is>
       </c>
       <c r="AA274" t="inlineStr">
@@ -37389,7 +37389,7 @@
       </c>
       <c r="AB274" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AC274" t="inlineStr">
@@ -37434,7 +37434,7 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>122254411</v>
+        <v>122254373</v>
       </c>
       <c r="B275" t="n">
         <v>56280</v>
@@ -37488,10 +37488,10 @@
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>586414</v>
+        <v>586307</v>
       </c>
       <c r="R275" t="n">
-        <v>6311126</v>
+        <v>6311133</v>
       </c>
       <c r="S275" t="n">
         <v>5</v>
@@ -37523,7 +37523,7 @@
       </c>
       <c r="Z275" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>22:49</t>
         </is>
       </c>
       <c r="AA275" t="inlineStr">
@@ -37533,7 +37533,7 @@
       </c>
       <c r="AB275" t="inlineStr">
         <is>
-          <t>22:38</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AC275" t="inlineStr">
@@ -37578,10 +37578,10 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>122254307</v>
+        <v>122254643</v>
       </c>
       <c r="B276" t="n">
-        <v>56280</v>
+        <v>56285</v>
       </c>
       <c r="C276" t="inlineStr">
         <is>
@@ -37594,21 +37594,21 @@
         </is>
       </c>
       <c r="E276" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
@@ -37632,10 +37632,10 @@
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>586477</v>
+        <v>586424</v>
       </c>
       <c r="R276" t="n">
-        <v>6311186</v>
+        <v>6311135</v>
       </c>
       <c r="S276" t="n">
         <v>5</v>
@@ -37667,7 +37667,7 @@
       </c>
       <c r="Z276" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AA276" t="inlineStr">
@@ -37677,7 +37677,7 @@
       </c>
       <c r="AB276" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>22:38</t>
         </is>
       </c>
       <c r="AC276" t="inlineStr">
@@ -37722,10 +37722,10 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>122254420</v>
+        <v>122254659</v>
       </c>
       <c r="B277" t="n">
-        <v>56280</v>
+        <v>56285</v>
       </c>
       <c r="C277" t="inlineStr">
         <is>
@@ -37738,21 +37738,21 @@
         </is>
       </c>
       <c r="E277" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
@@ -37776,10 +37776,10 @@
         </is>
       </c>
       <c r="Q277" t="n">
-        <v>586467</v>
+        <v>586489</v>
       </c>
       <c r="R277" t="n">
-        <v>6311178</v>
+        <v>6311181</v>
       </c>
       <c r="S277" t="n">
         <v>5</v>
@@ -37811,17 +37811,17 @@
       </c>
       <c r="Z277" t="inlineStr">
         <is>
+          <t>22:31</t>
+        </is>
+      </c>
+      <c r="AA277" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AB277" t="inlineStr">
+        <is>
           <t>22:32</t>
-        </is>
-      </c>
-      <c r="AA277" t="inlineStr">
-        <is>
-          <t>2024-06-26</t>
-        </is>
-      </c>
-      <c r="AB277" t="inlineStr">
-        <is>
-          <t>22:33</t>
         </is>
       </c>
       <c r="AC277" t="inlineStr">
@@ -37866,10 +37866,10 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>122254417</v>
+        <v>122254625</v>
       </c>
       <c r="B278" t="n">
-        <v>56280</v>
+        <v>56285</v>
       </c>
       <c r="C278" t="inlineStr">
         <is>
@@ -37882,21 +37882,21 @@
         </is>
       </c>
       <c r="E278" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
@@ -37920,10 +37920,10 @@
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>586426</v>
+        <v>586309</v>
       </c>
       <c r="R278" t="n">
-        <v>6311145</v>
+        <v>6311119</v>
       </c>
       <c r="S278" t="n">
         <v>5</v>
@@ -37955,7 +37955,7 @@
       </c>
       <c r="Z278" t="inlineStr">
         <is>
-          <t>22:33</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AA278" t="inlineStr">
@@ -37965,7 +37965,7 @@
       </c>
       <c r="AB278" t="inlineStr">
         <is>
-          <t>22:34</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AC278" t="inlineStr">
@@ -38010,10 +38010,10 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>122254316</v>
+        <v>122254585</v>
       </c>
       <c r="B279" t="n">
-        <v>56280</v>
+        <v>56285</v>
       </c>
       <c r="C279" t="inlineStr">
         <is>
@@ -38026,21 +38026,21 @@
         </is>
       </c>
       <c r="E279" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
@@ -38064,10 +38064,10 @@
         </is>
       </c>
       <c r="Q279" t="n">
-        <v>586423</v>
+        <v>586455</v>
       </c>
       <c r="R279" t="n">
-        <v>6311166</v>
+        <v>6311156</v>
       </c>
       <c r="S279" t="n">
         <v>5</v>
@@ -38099,7 +38099,7 @@
       </c>
       <c r="Z279" t="inlineStr">
         <is>
-          <t>23:23</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AA279" t="inlineStr">
@@ -38109,7 +38109,7 @@
       </c>
       <c r="AB279" t="inlineStr">
         <is>
-          <t>23:24</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AC279" t="inlineStr">
@@ -38154,7 +38154,7 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>122254415</v>
+        <v>122254315</v>
       </c>
       <c r="B280" t="n">
         <v>56280</v>
@@ -38208,10 +38208,10 @@
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>586425</v>
+        <v>586441</v>
       </c>
       <c r="R280" t="n">
-        <v>6311135</v>
+        <v>6311155</v>
       </c>
       <c r="S280" t="n">
         <v>5</v>
@@ -38243,7 +38243,7 @@
       </c>
       <c r="Z280" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AA280" t="inlineStr">
@@ -38253,7 +38253,7 @@
       </c>
       <c r="AB280" t="inlineStr">
         <is>
-          <t>22:38</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AC280" t="inlineStr">
@@ -38298,10 +38298,10 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>122254315</v>
+        <v>122254964</v>
       </c>
       <c r="B281" t="n">
-        <v>56280</v>
+        <v>56273</v>
       </c>
       <c r="C281" t="inlineStr">
         <is>
@@ -38314,21 +38314,21 @@
         </is>
       </c>
       <c r="E281" t="n">
-        <v>100092</v>
+        <v>205992</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
@@ -38352,10 +38352,10 @@
         </is>
       </c>
       <c r="Q281" t="n">
-        <v>586441</v>
+        <v>586430</v>
       </c>
       <c r="R281" t="n">
-        <v>6311155</v>
+        <v>6311142</v>
       </c>
       <c r="S281" t="n">
         <v>5</v>
@@ -38387,7 +38387,7 @@
       </c>
       <c r="Z281" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="AA281" t="inlineStr">
@@ -38397,7 +38397,7 @@
       </c>
       <c r="AB281" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>22:34</t>
         </is>
       </c>
       <c r="AC281" t="inlineStr">
@@ -38442,10 +38442,10 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>122254846</v>
+        <v>122254586</v>
       </c>
       <c r="B282" t="n">
-        <v>56283</v>
+        <v>56285</v>
       </c>
       <c r="C282" t="inlineStr">
         <is>
@@ -38458,21 +38458,21 @@
         </is>
       </c>
       <c r="E282" t="n">
-        <v>100111</v>
+        <v>205995</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
@@ -38496,10 +38496,10 @@
         </is>
       </c>
       <c r="Q282" t="n">
-        <v>586370</v>
+        <v>586446</v>
       </c>
       <c r="R282" t="n">
-        <v>6311139</v>
+        <v>6311158</v>
       </c>
       <c r="S282" t="n">
         <v>5</v>
@@ -38531,7 +38531,7 @@
       </c>
       <c r="Z282" t="inlineStr">
         <is>
-          <t>22:59</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AA282" t="inlineStr">
@@ -38541,7 +38541,7 @@
       </c>
       <c r="AB282" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AC282" t="inlineStr">
@@ -38586,10 +38586,10 @@
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>122254609</v>
+        <v>122254499</v>
       </c>
       <c r="B283" t="n">
-        <v>56285</v>
+        <v>56266</v>
       </c>
       <c r="C283" t="inlineStr">
         <is>
@@ -38598,25 +38598,25 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E283" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
@@ -38730,10 +38730,10 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>122254421</v>
+        <v>122254649</v>
       </c>
       <c r="B284" t="n">
-        <v>56280</v>
+        <v>56285</v>
       </c>
       <c r="C284" t="inlineStr">
         <is>
@@ -38746,21 +38746,21 @@
         </is>
       </c>
       <c r="E284" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
@@ -38784,10 +38784,10 @@
         </is>
       </c>
       <c r="Q284" t="n">
-        <v>586468</v>
+        <v>586422</v>
       </c>
       <c r="R284" t="n">
-        <v>6311181</v>
+        <v>6311100</v>
       </c>
       <c r="S284" t="n">
         <v>5</v>
@@ -38819,7 +38819,7 @@
       </c>
       <c r="Z284" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="AA284" t="inlineStr">
@@ -38829,7 +38829,7 @@
       </c>
       <c r="AB284" t="inlineStr">
         <is>
-          <t>22:33</t>
+          <t>22:36</t>
         </is>
       </c>
       <c r="AC284" t="inlineStr">
@@ -38874,10 +38874,10 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>122254372</v>
+        <v>122254637</v>
       </c>
       <c r="B285" t="n">
-        <v>56280</v>
+        <v>56285</v>
       </c>
       <c r="C285" t="inlineStr">
         <is>
@@ -38890,21 +38890,21 @@
         </is>
       </c>
       <c r="E285" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
@@ -38928,10 +38928,10 @@
         </is>
       </c>
       <c r="Q285" t="n">
-        <v>586306</v>
+        <v>586408</v>
       </c>
       <c r="R285" t="n">
-        <v>6311131</v>
+        <v>6311124</v>
       </c>
       <c r="S285" t="n">
         <v>5</v>
@@ -38963,7 +38963,7 @@
       </c>
       <c r="Z285" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>22:43</t>
         </is>
       </c>
       <c r="AA285" t="inlineStr">
@@ -38973,7 +38973,7 @@
       </c>
       <c r="AB285" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AC285" t="inlineStr">
@@ -39018,7 +39018,7 @@
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>122254313</v>
+        <v>122254418</v>
       </c>
       <c r="B286" t="n">
         <v>56280</v>
@@ -39072,10 +39072,10 @@
         </is>
       </c>
       <c r="Q286" t="n">
-        <v>586449</v>
+        <v>586467</v>
       </c>
       <c r="R286" t="n">
-        <v>6311155</v>
+        <v>6311178</v>
       </c>
       <c r="S286" t="n">
         <v>5</v>
@@ -39107,7 +39107,7 @@
       </c>
       <c r="Z286" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AA286" t="inlineStr">
@@ -39117,7 +39117,7 @@
       </c>
       <c r="AB286" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="AC286" t="inlineStr">
@@ -39306,7 +39306,7 @@
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>122254371</v>
+        <v>122254412</v>
       </c>
       <c r="B288" t="n">
         <v>56280</v>
@@ -39360,10 +39360,10 @@
         </is>
       </c>
       <c r="Q288" t="n">
-        <v>586308</v>
+        <v>586424</v>
       </c>
       <c r="R288" t="n">
-        <v>6311132</v>
+        <v>6311135</v>
       </c>
       <c r="S288" t="n">
         <v>5</v>
@@ -39395,7 +39395,7 @@
       </c>
       <c r="Z288" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AA288" t="inlineStr">
@@ -39405,7 +39405,7 @@
       </c>
       <c r="AB288" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>22:38</t>
         </is>
       </c>
       <c r="AC288" t="inlineStr">
@@ -39450,10 +39450,10 @@
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>122254626</v>
+        <v>122254392</v>
       </c>
       <c r="B289" t="n">
-        <v>56285</v>
+        <v>56280</v>
       </c>
       <c r="C289" t="inlineStr">
         <is>
@@ -39466,21 +39466,21 @@
         </is>
       </c>
       <c r="E289" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
@@ -39504,10 +39504,10 @@
         </is>
       </c>
       <c r="Q289" t="n">
-        <v>586313</v>
+        <v>586384</v>
       </c>
       <c r="R289" t="n">
-        <v>6311124</v>
+        <v>6311139</v>
       </c>
       <c r="S289" t="n">
         <v>5</v>
@@ -39539,7 +39539,7 @@
       </c>
       <c r="Z289" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AA289" t="inlineStr">
@@ -39549,7 +39549,7 @@
       </c>
       <c r="AB289" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>22:46</t>
         </is>
       </c>
       <c r="AC289" t="inlineStr">
@@ -39594,7 +39594,7 @@
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>122254606</v>
+        <v>122254608</v>
       </c>
       <c r="B290" t="n">
         <v>56285</v>
@@ -39648,10 +39648,10 @@
         </is>
       </c>
       <c r="Q290" t="n">
-        <v>586415</v>
+        <v>586393</v>
       </c>
       <c r="R290" t="n">
-        <v>6311146</v>
+        <v>6311147</v>
       </c>
       <c r="S290" t="n">
         <v>5</v>
@@ -39683,17 +39683,17 @@
       </c>
       <c r="Z290" t="inlineStr">
         <is>
+          <t>23:01</t>
+        </is>
+      </c>
+      <c r="AA290" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AB290" t="inlineStr">
+        <is>
           <t>23:02</t>
-        </is>
-      </c>
-      <c r="AA290" t="inlineStr">
-        <is>
-          <t>2024-06-26</t>
-        </is>
-      </c>
-      <c r="AB290" t="inlineStr">
-        <is>
-          <t>23:03</t>
         </is>
       </c>
       <c r="AC290" t="inlineStr">
@@ -39738,10 +39738,10 @@
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>122254656</v>
+        <v>122254957</v>
       </c>
       <c r="B291" t="n">
-        <v>56285</v>
+        <v>56273</v>
       </c>
       <c r="C291" t="inlineStr">
         <is>
@@ -39754,21 +39754,21 @@
         </is>
       </c>
       <c r="E291" t="n">
-        <v>205995</v>
+        <v>205992</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
@@ -39792,10 +39792,10 @@
         </is>
       </c>
       <c r="Q291" t="n">
-        <v>586483</v>
+        <v>586444</v>
       </c>
       <c r="R291" t="n">
-        <v>6311186</v>
+        <v>6311160</v>
       </c>
       <c r="S291" t="n">
         <v>5</v>
@@ -39827,7 +39827,7 @@
       </c>
       <c r="Z291" t="inlineStr">
         <is>
-          <t>22:31</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="AA291" t="inlineStr">
@@ -39837,7 +39837,7 @@
       </c>
       <c r="AB291" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AC291" t="inlineStr">
@@ -39882,10 +39882,10 @@
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>122254343</v>
+        <v>122254954</v>
       </c>
       <c r="B292" t="n">
-        <v>56280</v>
+        <v>56273</v>
       </c>
       <c r="C292" t="inlineStr">
         <is>
@@ -39898,21 +39898,21 @@
         </is>
       </c>
       <c r="E292" t="n">
-        <v>100092</v>
+        <v>205992</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
@@ -39936,10 +39936,10 @@
         </is>
       </c>
       <c r="Q292" t="n">
-        <v>586388</v>
+        <v>586442</v>
       </c>
       <c r="R292" t="n">
-        <v>6311142</v>
+        <v>6311152</v>
       </c>
       <c r="S292" t="n">
         <v>5</v>
@@ -39971,7 +39971,7 @@
       </c>
       <c r="Z292" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AA292" t="inlineStr">
@@ -39981,7 +39981,7 @@
       </c>
       <c r="AB292" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AC292" t="inlineStr">
@@ -40026,10 +40026,10 @@
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>122254370</v>
+        <v>122254634</v>
       </c>
       <c r="B293" t="n">
-        <v>56280</v>
+        <v>56285</v>
       </c>
       <c r="C293" t="inlineStr">
         <is>
@@ -40042,21 +40042,21 @@
         </is>
       </c>
       <c r="E293" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
@@ -40080,10 +40080,10 @@
         </is>
       </c>
       <c r="Q293" t="n">
-        <v>586309</v>
+        <v>586415</v>
       </c>
       <c r="R293" t="n">
-        <v>6311119</v>
+        <v>6311148</v>
       </c>
       <c r="S293" t="n">
         <v>5</v>
@@ -40115,7 +40115,7 @@
       </c>
       <c r="Z293" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AA293" t="inlineStr">
@@ -40125,7 +40125,7 @@
       </c>
       <c r="AB293" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AC293" t="inlineStr">
@@ -40170,10 +40170,10 @@
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>122254472</v>
+        <v>122254616</v>
       </c>
       <c r="B294" t="n">
-        <v>56266</v>
+        <v>56285</v>
       </c>
       <c r="C294" t="inlineStr">
         <is>
@@ -40182,25 +40182,25 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E294" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
@@ -40224,10 +40224,10 @@
         </is>
       </c>
       <c r="Q294" t="n">
-        <v>586455</v>
+        <v>586327</v>
       </c>
       <c r="R294" t="n">
-        <v>6311159</v>
+        <v>6311118</v>
       </c>
       <c r="S294" t="n">
         <v>5</v>
@@ -40259,7 +40259,7 @@
       </c>
       <c r="Z294" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>22:57</t>
         </is>
       </c>
       <c r="AA294" t="inlineStr">
@@ -40269,7 +40269,7 @@
       </c>
       <c r="AB294" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>22:58</t>
         </is>
       </c>
       <c r="AC294" t="inlineStr">
@@ -40314,7 +40314,7 @@
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>122254610</v>
+        <v>122254646</v>
       </c>
       <c r="B295" t="n">
         <v>56285</v>
@@ -40368,10 +40368,10 @@
         </is>
       </c>
       <c r="Q295" t="n">
-        <v>586389</v>
+        <v>586422</v>
       </c>
       <c r="R295" t="n">
-        <v>6311141</v>
+        <v>6311111</v>
       </c>
       <c r="S295" t="n">
         <v>5</v>
@@ -40403,7 +40403,7 @@
       </c>
       <c r="Z295" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:36</t>
         </is>
       </c>
       <c r="AA295" t="inlineStr">
@@ -40413,7 +40413,7 @@
       </c>
       <c r="AB295" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AC295" t="inlineStr">
@@ -40458,10 +40458,10 @@
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>122254877</v>
+        <v>122254607</v>
       </c>
       <c r="B296" t="n">
-        <v>56283</v>
+        <v>56285</v>
       </c>
       <c r="C296" t="inlineStr">
         <is>
@@ -40474,21 +40474,21 @@
         </is>
       </c>
       <c r="E296" t="n">
-        <v>100111</v>
+        <v>205995</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
@@ -40512,10 +40512,10 @@
         </is>
       </c>
       <c r="Q296" t="n">
-        <v>586276</v>
+        <v>586415</v>
       </c>
       <c r="R296" t="n">
-        <v>6311100</v>
+        <v>6311149</v>
       </c>
       <c r="S296" t="n">
         <v>5</v>
@@ -40547,7 +40547,7 @@
       </c>
       <c r="Z296" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AA296" t="inlineStr">
@@ -40557,7 +40557,7 @@
       </c>
       <c r="AB296" t="inlineStr">
         <is>
-          <t>22:52</t>
+          <t>23:03</t>
         </is>
       </c>
       <c r="AC296" t="inlineStr">
@@ -40602,10 +40602,10 @@
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>122254367</v>
+        <v>122254656</v>
       </c>
       <c r="B297" t="n">
-        <v>56280</v>
+        <v>56285</v>
       </c>
       <c r="C297" t="inlineStr">
         <is>
@@ -40618,21 +40618,21 @@
         </is>
       </c>
       <c r="E297" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
@@ -40656,10 +40656,10 @@
         </is>
       </c>
       <c r="Q297" t="n">
-        <v>586280</v>
+        <v>586483</v>
       </c>
       <c r="R297" t="n">
-        <v>6311103</v>
+        <v>6311186</v>
       </c>
       <c r="S297" t="n">
         <v>5</v>
@@ -40691,7 +40691,7 @@
       </c>
       <c r="Z297" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>22:31</t>
         </is>
       </c>
       <c r="AA297" t="inlineStr">
@@ -40701,7 +40701,7 @@
       </c>
       <c r="AB297" t="inlineStr">
         <is>
-          <t>22:52</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AC297" t="inlineStr">
@@ -40746,7 +40746,7 @@
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>122254391</v>
+        <v>122254318</v>
       </c>
       <c r="B298" t="n">
         <v>56280</v>
@@ -40800,10 +40800,10 @@
         </is>
       </c>
       <c r="Q298" t="n">
-        <v>586379</v>
+        <v>586455</v>
       </c>
       <c r="R298" t="n">
-        <v>6311136</v>
+        <v>6311228</v>
       </c>
       <c r="S298" t="n">
         <v>5</v>
@@ -40835,7 +40835,7 @@
       </c>
       <c r="Z298" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>23:22</t>
         </is>
       </c>
       <c r="AA298" t="inlineStr">
@@ -40845,7 +40845,7 @@
       </c>
       <c r="AB298" t="inlineStr">
         <is>
-          <t>22:46</t>
+          <t>23:23</t>
         </is>
       </c>
       <c r="AC298" t="inlineStr">
@@ -40890,10 +40890,10 @@
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>122254514</v>
+        <v>122254617</v>
       </c>
       <c r="B299" t="n">
-        <v>56266</v>
+        <v>56285</v>
       </c>
       <c r="C299" t="inlineStr">
         <is>
@@ -40902,25 +40902,25 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E299" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
@@ -40944,10 +40944,10 @@
         </is>
       </c>
       <c r="Q299" t="n">
-        <v>586408</v>
+        <v>586317</v>
       </c>
       <c r="R299" t="n">
-        <v>6311124</v>
+        <v>6311115</v>
       </c>
       <c r="S299" t="n">
         <v>5</v>
@@ -40979,7 +40979,7 @@
       </c>
       <c r="Z299" t="inlineStr">
         <is>
-          <t>22:43</t>
+          <t>22:57</t>
         </is>
       </c>
       <c r="AA299" t="inlineStr">
@@ -40989,7 +40989,7 @@
       </c>
       <c r="AB299" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>22:58</t>
         </is>
       </c>
       <c r="AC299" t="inlineStr">
@@ -41034,10 +41034,10 @@
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>122254959</v>
+        <v>122254475</v>
       </c>
       <c r="B300" t="n">
-        <v>56273</v>
+        <v>56266</v>
       </c>
       <c r="C300" t="inlineStr">
         <is>
@@ -41046,25 +41046,25 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E300" t="n">
-        <v>205992</v>
+        <v>205998</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
@@ -41088,10 +41088,10 @@
         </is>
       </c>
       <c r="Q300" t="n">
-        <v>586370</v>
+        <v>586420</v>
       </c>
       <c r="R300" t="n">
-        <v>6311139</v>
+        <v>6311166</v>
       </c>
       <c r="S300" t="n">
         <v>5</v>
@@ -41123,7 +41123,7 @@
       </c>
       <c r="Z300" t="inlineStr">
         <is>
-          <t>22:59</t>
+          <t>23:23</t>
         </is>
       </c>
       <c r="AA300" t="inlineStr">
@@ -41133,7 +41133,7 @@
       </c>
       <c r="AB300" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="AC300" t="inlineStr">
@@ -41178,10 +41178,10 @@
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>122254615</v>
+        <v>122254500</v>
       </c>
       <c r="B301" t="n">
-        <v>56285</v>
+        <v>56266</v>
       </c>
       <c r="C301" t="inlineStr">
         <is>
@@ -41190,25 +41190,25 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E301" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
@@ -41232,10 +41232,10 @@
         </is>
       </c>
       <c r="Q301" t="n">
-        <v>586329</v>
+        <v>586388</v>
       </c>
       <c r="R301" t="n">
-        <v>6311120</v>
+        <v>6311142</v>
       </c>
       <c r="S301" t="n">
         <v>5</v>
@@ -41267,7 +41267,7 @@
       </c>
       <c r="Z301" t="inlineStr">
         <is>
-          <t>22:57</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA301" t="inlineStr">
@@ -41277,7 +41277,7 @@
       </c>
       <c r="AB301" t="inlineStr">
         <is>
-          <t>22:58</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AC301" t="inlineStr">
@@ -41322,10 +41322,10 @@
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>122254651</v>
+        <v>122254343</v>
       </c>
       <c r="B302" t="n">
-        <v>56285</v>
+        <v>56280</v>
       </c>
       <c r="C302" t="inlineStr">
         <is>
@@ -41338,21 +41338,21 @@
         </is>
       </c>
       <c r="E302" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
@@ -41376,10 +41376,10 @@
         </is>
       </c>
       <c r="Q302" t="n">
-        <v>586425</v>
+        <v>586388</v>
       </c>
       <c r="R302" t="n">
-        <v>6311113</v>
+        <v>6311142</v>
       </c>
       <c r="S302" t="n">
         <v>5</v>
@@ -41411,7 +41411,7 @@
       </c>
       <c r="Z302" t="inlineStr">
         <is>
-          <t>22:35</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA302" t="inlineStr">
@@ -41421,7 +41421,7 @@
       </c>
       <c r="AB302" t="inlineStr">
         <is>
-          <t>22:36</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AC302" t="inlineStr">
@@ -41466,10 +41466,10 @@
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>122254655</v>
+        <v>122254313</v>
       </c>
       <c r="B303" t="n">
-        <v>56285</v>
+        <v>56280</v>
       </c>
       <c r="C303" t="inlineStr">
         <is>
@@ -41482,21 +41482,21 @@
         </is>
       </c>
       <c r="E303" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
@@ -41520,10 +41520,10 @@
         </is>
       </c>
       <c r="Q303" t="n">
-        <v>586475</v>
+        <v>586449</v>
       </c>
       <c r="R303" t="n">
-        <v>6311187</v>
+        <v>6311155</v>
       </c>
       <c r="S303" t="n">
         <v>5</v>
@@ -41555,7 +41555,7 @@
       </c>
       <c r="Z303" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA303" t="inlineStr">
@@ -41565,7 +41565,7 @@
       </c>
       <c r="AB303" t="inlineStr">
         <is>
-          <t>22:33</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC303" t="inlineStr">
@@ -41610,10 +41610,10 @@
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>122254951</v>
+        <v>122254341</v>
       </c>
       <c r="B304" t="n">
-        <v>56273</v>
+        <v>56280</v>
       </c>
       <c r="C304" t="inlineStr">
         <is>
@@ -41626,21 +41626,21 @@
         </is>
       </c>
       <c r="E304" t="n">
-        <v>205992</v>
+        <v>100092</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
@@ -41664,10 +41664,10 @@
         </is>
       </c>
       <c r="Q304" t="n">
-        <v>586459</v>
+        <v>586415</v>
       </c>
       <c r="R304" t="n">
-        <v>6311154</v>
+        <v>6311146</v>
       </c>
       <c r="S304" t="n">
         <v>5</v>
@@ -41699,7 +41699,7 @@
       </c>
       <c r="Z304" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AA304" t="inlineStr">
@@ -41709,7 +41709,7 @@
       </c>
       <c r="AB304" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>23:03</t>
         </is>
       </c>
       <c r="AC304" t="inlineStr">
@@ -41754,10 +41754,10 @@
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>122254586</v>
+        <v>122254472</v>
       </c>
       <c r="B305" t="n">
-        <v>56285</v>
+        <v>56266</v>
       </c>
       <c r="C305" t="inlineStr">
         <is>
@@ -41766,25 +41766,25 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E305" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
@@ -41808,10 +41808,10 @@
         </is>
       </c>
       <c r="Q305" t="n">
-        <v>586446</v>
+        <v>586455</v>
       </c>
       <c r="R305" t="n">
-        <v>6311158</v>
+        <v>6311159</v>
       </c>
       <c r="S305" t="n">
         <v>5</v>
@@ -41843,7 +41843,7 @@
       </c>
       <c r="Z305" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AA305" t="inlineStr">
@@ -41853,7 +41853,7 @@
       </c>
       <c r="AB305" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AC305" t="inlineStr">
@@ -41898,10 +41898,10 @@
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>122254956</v>
+        <v>122254496</v>
       </c>
       <c r="B306" t="n">
-        <v>56273</v>
+        <v>56266</v>
       </c>
       <c r="C306" t="inlineStr">
         <is>
@@ -41910,25 +41910,25 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E306" t="n">
-        <v>205992</v>
+        <v>205998</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
@@ -41952,10 +41952,10 @@
         </is>
       </c>
       <c r="Q306" t="n">
-        <v>586441</v>
+        <v>586415</v>
       </c>
       <c r="R306" t="n">
-        <v>6311152</v>
+        <v>6311146</v>
       </c>
       <c r="S306" t="n">
         <v>5</v>
@@ -41987,7 +41987,7 @@
       </c>
       <c r="Z306" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AA306" t="inlineStr">
@@ -41997,7 +41997,7 @@
       </c>
       <c r="AB306" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>23:03</t>
         </is>
       </c>
       <c r="AC306" t="inlineStr">
@@ -42042,10 +42042,10 @@
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>122254966</v>
+        <v>122254658</v>
       </c>
       <c r="B307" t="n">
-        <v>56273</v>
+        <v>56285</v>
       </c>
       <c r="C307" t="inlineStr">
         <is>
@@ -42058,21 +42058,21 @@
         </is>
       </c>
       <c r="E307" t="n">
-        <v>205992</v>
+        <v>205995</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
@@ -42096,10 +42096,10 @@
         </is>
       </c>
       <c r="Q307" t="n">
-        <v>586467</v>
+        <v>586491</v>
       </c>
       <c r="R307" t="n">
-        <v>6311178</v>
+        <v>6311181</v>
       </c>
       <c r="S307" t="n">
         <v>5</v>
@@ -42131,17 +42131,17 @@
       </c>
       <c r="Z307" t="inlineStr">
         <is>
+          <t>22:31</t>
+        </is>
+      </c>
+      <c r="AA307" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AB307" t="inlineStr">
+        <is>
           <t>22:32</t>
-        </is>
-      </c>
-      <c r="AA307" t="inlineStr">
-        <is>
-          <t>2024-06-26</t>
-        </is>
-      </c>
-      <c r="AB307" t="inlineStr">
-        <is>
-          <t>22:33</t>
         </is>
       </c>
       <c r="AC307" t="inlineStr">
@@ -42186,10 +42186,10 @@
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>122254317</v>
+        <v>122254513</v>
       </c>
       <c r="B308" t="n">
-        <v>56280</v>
+        <v>56266</v>
       </c>
       <c r="C308" t="inlineStr">
         <is>
@@ -42198,25 +42198,25 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E308" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
@@ -42240,10 +42240,10 @@
         </is>
       </c>
       <c r="Q308" t="n">
-        <v>586438</v>
+        <v>586396</v>
       </c>
       <c r="R308" t="n">
-        <v>6311222</v>
+        <v>6311146</v>
       </c>
       <c r="S308" t="n">
         <v>5</v>
@@ -42275,7 +42275,7 @@
       </c>
       <c r="Z308" t="inlineStr">
         <is>
-          <t>23:22</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AA308" t="inlineStr">
@@ -42285,7 +42285,7 @@
       </c>
       <c r="AB308" t="inlineStr">
         <is>
-          <t>23:23</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AC308" t="inlineStr">
@@ -42330,10 +42330,10 @@
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>122254390</v>
+        <v>122254966</v>
       </c>
       <c r="B309" t="n">
-        <v>56280</v>
+        <v>56273</v>
       </c>
       <c r="C309" t="inlineStr">
         <is>
@@ -42346,21 +42346,21 @@
         </is>
       </c>
       <c r="E309" t="n">
-        <v>100092</v>
+        <v>205992</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
@@ -42384,10 +42384,10 @@
         </is>
       </c>
       <c r="Q309" t="n">
-        <v>586374</v>
+        <v>586467</v>
       </c>
       <c r="R309" t="n">
-        <v>6311139</v>
+        <v>6311178</v>
       </c>
       <c r="S309" t="n">
         <v>5</v>
@@ -42419,7 +42419,7 @@
       </c>
       <c r="Z309" t="inlineStr">
         <is>
-          <t>22:46</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AA309" t="inlineStr">
@@ -42429,7 +42429,7 @@
       </c>
       <c r="AB309" t="inlineStr">
         <is>
-          <t>22:47</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="AC309" t="inlineStr">
@@ -42474,10 +42474,10 @@
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>122254414</v>
+        <v>122254632</v>
       </c>
       <c r="B310" t="n">
-        <v>56280</v>
+        <v>56285</v>
       </c>
       <c r="C310" t="inlineStr">
         <is>
@@ -42490,21 +42490,21 @@
         </is>
       </c>
       <c r="E310" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
@@ -42528,10 +42528,10 @@
         </is>
       </c>
       <c r="Q310" t="n">
-        <v>586423</v>
+        <v>586374</v>
       </c>
       <c r="R310" t="n">
-        <v>6311137</v>
+        <v>6311140</v>
       </c>
       <c r="S310" t="n">
         <v>5</v>
@@ -42563,7 +42563,7 @@
       </c>
       <c r="Z310" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>22:46</t>
         </is>
       </c>
       <c r="AA310" t="inlineStr">
@@ -42573,7 +42573,7 @@
       </c>
       <c r="AB310" t="inlineStr">
         <is>
-          <t>22:38</t>
+          <t>22:47</t>
         </is>
       </c>
       <c r="AC310" t="inlineStr">
@@ -42618,10 +42618,10 @@
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>122254416</v>
+        <v>122254651</v>
       </c>
       <c r="B311" t="n">
-        <v>56280</v>
+        <v>56285</v>
       </c>
       <c r="C311" t="inlineStr">
         <is>
@@ -42634,21 +42634,21 @@
         </is>
       </c>
       <c r="E311" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
@@ -42672,10 +42672,10 @@
         </is>
       </c>
       <c r="Q311" t="n">
-        <v>586410</v>
+        <v>586425</v>
       </c>
       <c r="R311" t="n">
-        <v>6311140</v>
+        <v>6311113</v>
       </c>
       <c r="S311" t="n">
         <v>5</v>
@@ -42707,7 +42707,7 @@
       </c>
       <c r="Z311" t="inlineStr">
         <is>
-          <t>22:33</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="AA311" t="inlineStr">
@@ -42717,7 +42717,7 @@
       </c>
       <c r="AB311" t="inlineStr">
         <is>
-          <t>22:34</t>
+          <t>22:36</t>
         </is>
       </c>
       <c r="AC311" t="inlineStr">
@@ -42762,7 +42762,7 @@
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>122254350</v>
+        <v>122254317</v>
       </c>
       <c r="B312" t="n">
         <v>56280</v>
@@ -42816,10 +42816,10 @@
         </is>
       </c>
       <c r="Q312" t="n">
-        <v>586330</v>
+        <v>586438</v>
       </c>
       <c r="R312" t="n">
-        <v>6311120</v>
+        <v>6311222</v>
       </c>
       <c r="S312" t="n">
         <v>5</v>
@@ -42851,7 +42851,7 @@
       </c>
       <c r="Z312" t="inlineStr">
         <is>
-          <t>22:57</t>
+          <t>23:22</t>
         </is>
       </c>
       <c r="AA312" t="inlineStr">
@@ -42861,7 +42861,7 @@
       </c>
       <c r="AB312" t="inlineStr">
         <is>
-          <t>22:58</t>
+          <t>23:23</t>
         </is>
       </c>
       <c r="AC312" t="inlineStr">
@@ -42906,10 +42906,10 @@
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>122254634</v>
+        <v>122254878</v>
       </c>
       <c r="B313" t="n">
-        <v>56285</v>
+        <v>56283</v>
       </c>
       <c r="C313" t="inlineStr">
         <is>
@@ -42922,21 +42922,21 @@
         </is>
       </c>
       <c r="E313" t="n">
-        <v>205995</v>
+        <v>100111</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
@@ -42960,10 +42960,10 @@
         </is>
       </c>
       <c r="Q313" t="n">
-        <v>586415</v>
+        <v>586280</v>
       </c>
       <c r="R313" t="n">
-        <v>6311148</v>
+        <v>6311103</v>
       </c>
       <c r="S313" t="n">
         <v>5</v>
@@ -42995,7 +42995,7 @@
       </c>
       <c r="Z313" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AA313" t="inlineStr">
@@ -43005,7 +43005,7 @@
       </c>
       <c r="AB313" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>22:52</t>
         </is>
       </c>
       <c r="AC313" t="inlineStr">
@@ -43050,10 +43050,10 @@
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>122254496</v>
+        <v>122254950</v>
       </c>
       <c r="B314" t="n">
-        <v>56266</v>
+        <v>56273</v>
       </c>
       <c r="C314" t="inlineStr">
         <is>
@@ -43062,25 +43062,25 @@
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E314" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
@@ -43104,10 +43104,10 @@
         </is>
       </c>
       <c r="Q314" t="n">
-        <v>586415</v>
+        <v>586482</v>
       </c>
       <c r="R314" t="n">
-        <v>6311146</v>
+        <v>6311185</v>
       </c>
       <c r="S314" t="n">
         <v>5</v>
@@ -43139,7 +43139,7 @@
       </c>
       <c r="Z314" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AA314" t="inlineStr">
@@ -43149,7 +43149,7 @@
       </c>
       <c r="AB314" t="inlineStr">
         <is>
-          <t>23:03</t>
+          <t>23:31</t>
         </is>
       </c>
       <c r="AC314" t="inlineStr">
@@ -43194,7 +43194,7 @@
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>122254632</v>
+        <v>122254606</v>
       </c>
       <c r="B315" t="n">
         <v>56285</v>
@@ -43248,10 +43248,10 @@
         </is>
       </c>
       <c r="Q315" t="n">
-        <v>586374</v>
+        <v>586415</v>
       </c>
       <c r="R315" t="n">
-        <v>6311140</v>
+        <v>6311146</v>
       </c>
       <c r="S315" t="n">
         <v>5</v>
@@ -43283,7 +43283,7 @@
       </c>
       <c r="Z315" t="inlineStr">
         <is>
-          <t>22:46</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AA315" t="inlineStr">
@@ -43293,7 +43293,7 @@
       </c>
       <c r="AB315" t="inlineStr">
         <is>
-          <t>22:47</t>
+          <t>23:03</t>
         </is>
       </c>
       <c r="AC315" t="inlineStr">
@@ -43338,7 +43338,7 @@
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>122254855</v>
+        <v>122254843</v>
       </c>
       <c r="B316" t="n">
         <v>56283</v>
@@ -43392,10 +43392,10 @@
         </is>
       </c>
       <c r="Q316" t="n">
-        <v>586330</v>
+        <v>586389</v>
       </c>
       <c r="R316" t="n">
-        <v>6311120</v>
+        <v>6311142</v>
       </c>
       <c r="S316" t="n">
         <v>5</v>
@@ -43427,7 +43427,7 @@
       </c>
       <c r="Z316" t="inlineStr">
         <is>
-          <t>22:57</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA316" t="inlineStr">
@@ -43437,7 +43437,7 @@
       </c>
       <c r="AB316" t="inlineStr">
         <is>
-          <t>22:58</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AC316" t="inlineStr">
@@ -43482,7 +43482,7 @@
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>122254843</v>
+        <v>122254836</v>
       </c>
       <c r="B317" t="n">
         <v>56283</v>
@@ -43536,10 +43536,10 @@
         </is>
       </c>
       <c r="Q317" t="n">
-        <v>586389</v>
+        <v>586474</v>
       </c>
       <c r="R317" t="n">
-        <v>6311142</v>
+        <v>6311176</v>
       </c>
       <c r="S317" t="n">
         <v>5</v>
@@ -43571,7 +43571,7 @@
       </c>
       <c r="Z317" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AA317" t="inlineStr">
@@ -43581,7 +43581,7 @@
       </c>
       <c r="AB317" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AC317" t="inlineStr">
@@ -43626,10 +43626,10 @@
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>122254837</v>
+        <v>122254390</v>
       </c>
       <c r="B318" t="n">
-        <v>56283</v>
+        <v>56280</v>
       </c>
       <c r="C318" t="inlineStr">
         <is>
@@ -43642,21 +43642,21 @@
         </is>
       </c>
       <c r="E318" t="n">
-        <v>100111</v>
+        <v>100092</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
@@ -43680,10 +43680,10 @@
         </is>
       </c>
       <c r="Q318" t="n">
-        <v>586448</v>
+        <v>586374</v>
       </c>
       <c r="R318" t="n">
-        <v>6311154</v>
+        <v>6311139</v>
       </c>
       <c r="S318" t="n">
         <v>5</v>
@@ -43715,7 +43715,7 @@
       </c>
       <c r="Z318" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>22:46</t>
         </is>
       </c>
       <c r="AA318" t="inlineStr">
@@ -43725,7 +43725,7 @@
       </c>
       <c r="AB318" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>22:47</t>
         </is>
       </c>
       <c r="AC318" t="inlineStr">
@@ -43770,10 +43770,10 @@
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>122254312</v>
+        <v>122254956</v>
       </c>
       <c r="B319" t="n">
-        <v>56280</v>
+        <v>56273</v>
       </c>
       <c r="C319" t="inlineStr">
         <is>
@@ -43786,21 +43786,21 @@
         </is>
       </c>
       <c r="E319" t="n">
-        <v>100092</v>
+        <v>205992</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
@@ -43824,7 +43824,7 @@
         </is>
       </c>
       <c r="Q319" t="n">
-        <v>586452</v>
+        <v>586441</v>
       </c>
       <c r="R319" t="n">
         <v>6311152</v>
@@ -43859,7 +43859,7 @@
       </c>
       <c r="Z319" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AA319" t="inlineStr">
@@ -43869,7 +43869,7 @@
       </c>
       <c r="AB319" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AC319" t="inlineStr">
@@ -43914,7 +43914,7 @@
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>122254627</v>
+        <v>122254615</v>
       </c>
       <c r="B320" t="n">
         <v>56285</v>
@@ -43968,10 +43968,10 @@
         </is>
       </c>
       <c r="Q320" t="n">
-        <v>586306</v>
+        <v>586329</v>
       </c>
       <c r="R320" t="n">
-        <v>6311131</v>
+        <v>6311120</v>
       </c>
       <c r="S320" t="n">
         <v>5</v>
@@ -44003,7 +44003,7 @@
       </c>
       <c r="Z320" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>22:57</t>
         </is>
       </c>
       <c r="AA320" t="inlineStr">
@@ -44013,7 +44013,7 @@
       </c>
       <c r="AB320" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>22:58</t>
         </is>
       </c>
       <c r="AC320" t="inlineStr">
@@ -44058,10 +44058,10 @@
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>122254499</v>
+        <v>122254660</v>
       </c>
       <c r="B321" t="n">
-        <v>56266</v>
+        <v>56285</v>
       </c>
       <c r="C321" t="inlineStr">
         <is>
@@ -44070,25 +44070,25 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E321" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
@@ -44112,10 +44112,10 @@
         </is>
       </c>
       <c r="Q321" t="n">
-        <v>586392</v>
+        <v>586488</v>
       </c>
       <c r="R321" t="n">
-        <v>6311147</v>
+        <v>6311183</v>
       </c>
       <c r="S321" t="n">
         <v>5</v>
@@ -44147,7 +44147,7 @@
       </c>
       <c r="Z321" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>22:31</t>
         </is>
       </c>
       <c r="AA321" t="inlineStr">
@@ -44157,7 +44157,7 @@
       </c>
       <c r="AB321" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AC321" t="inlineStr">
@@ -44202,10 +44202,10 @@
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>122254588</v>
+        <v>122254512</v>
       </c>
       <c r="B322" t="n">
-        <v>56285</v>
+        <v>56266</v>
       </c>
       <c r="C322" t="inlineStr">
         <is>
@@ -44214,25 +44214,25 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E322" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
@@ -44256,10 +44256,10 @@
         </is>
       </c>
       <c r="Q322" t="n">
-        <v>586415</v>
+        <v>586379</v>
       </c>
       <c r="R322" t="n">
-        <v>6311196</v>
+        <v>6311136</v>
       </c>
       <c r="S322" t="n">
         <v>5</v>
@@ -44291,7 +44291,7 @@
       </c>
       <c r="Z322" t="inlineStr">
         <is>
-          <t>23:22</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AA322" t="inlineStr">
@@ -44301,7 +44301,7 @@
       </c>
       <c r="AB322" t="inlineStr">
         <is>
-          <t>23:23</t>
+          <t>22:46</t>
         </is>
       </c>
       <c r="AC322" t="inlineStr">
@@ -44346,7 +44346,7 @@
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>122254608</v>
+        <v>122254611</v>
       </c>
       <c r="B323" t="n">
         <v>56285</v>
@@ -44400,10 +44400,10 @@
         </is>
       </c>
       <c r="Q323" t="n">
-        <v>586393</v>
+        <v>586370</v>
       </c>
       <c r="R323" t="n">
-        <v>6311147</v>
+        <v>6311139</v>
       </c>
       <c r="S323" t="n">
         <v>5</v>
@@ -44435,7 +44435,7 @@
       </c>
       <c r="Z323" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>22:59</t>
         </is>
       </c>
       <c r="AA323" t="inlineStr">
@@ -44445,7 +44445,7 @@
       </c>
       <c r="AB323" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AC323" t="inlineStr">
@@ -44490,10 +44490,10 @@
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>122254513</v>
+        <v>122254415</v>
       </c>
       <c r="B324" t="n">
-        <v>56266</v>
+        <v>56280</v>
       </c>
       <c r="C324" t="inlineStr">
         <is>
@@ -44502,25 +44502,25 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E324" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
@@ -44544,10 +44544,10 @@
         </is>
       </c>
       <c r="Q324" t="n">
-        <v>586396</v>
+        <v>586425</v>
       </c>
       <c r="R324" t="n">
-        <v>6311146</v>
+        <v>6311135</v>
       </c>
       <c r="S324" t="n">
         <v>5</v>
@@ -44579,7 +44579,7 @@
       </c>
       <c r="Z324" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AA324" t="inlineStr">
@@ -44589,7 +44589,7 @@
       </c>
       <c r="AB324" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>22:38</t>
         </is>
       </c>
       <c r="AC324" t="inlineStr">
@@ -44634,7 +44634,7 @@
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>122254318</v>
+        <v>122254413</v>
       </c>
       <c r="B325" t="n">
         <v>56280</v>
@@ -44688,10 +44688,10 @@
         </is>
       </c>
       <c r="Q325" t="n">
-        <v>586455</v>
+        <v>586423</v>
       </c>
       <c r="R325" t="n">
-        <v>6311228</v>
+        <v>6311137</v>
       </c>
       <c r="S325" t="n">
         <v>5</v>
@@ -44723,7 +44723,7 @@
       </c>
       <c r="Z325" t="inlineStr">
         <is>
-          <t>23:22</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AA325" t="inlineStr">
@@ -44733,7 +44733,7 @@
       </c>
       <c r="AB325" t="inlineStr">
         <is>
-          <t>23:23</t>
+          <t>22:38</t>
         </is>
       </c>
       <c r="AC325" t="inlineStr">
@@ -44778,7 +44778,7 @@
     </row>
     <row r="326">
       <c r="A326" t="n">
-        <v>122254369</v>
+        <v>122254416</v>
       </c>
       <c r="B326" t="n">
         <v>56280</v>
@@ -44832,10 +44832,10 @@
         </is>
       </c>
       <c r="Q326" t="n">
-        <v>586300</v>
+        <v>586410</v>
       </c>
       <c r="R326" t="n">
-        <v>6311112</v>
+        <v>6311140</v>
       </c>
       <c r="S326" t="n">
         <v>5</v>
@@ -44867,7 +44867,7 @@
       </c>
       <c r="Z326" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="AA326" t="inlineStr">
@@ -44877,7 +44877,7 @@
       </c>
       <c r="AB326" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>22:34</t>
         </is>
       </c>
       <c r="AC326" t="inlineStr">
@@ -44922,10 +44922,10 @@
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>122254475</v>
+        <v>122254367</v>
       </c>
       <c r="B327" t="n">
-        <v>56266</v>
+        <v>56280</v>
       </c>
       <c r="C327" t="inlineStr">
         <is>
@@ -44934,25 +44934,25 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E327" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
@@ -44976,10 +44976,10 @@
         </is>
       </c>
       <c r="Q327" t="n">
-        <v>586420</v>
+        <v>586280</v>
       </c>
       <c r="R327" t="n">
-        <v>6311166</v>
+        <v>6311103</v>
       </c>
       <c r="S327" t="n">
         <v>5</v>
@@ -45011,7 +45011,7 @@
       </c>
       <c r="Z327" t="inlineStr">
         <is>
-          <t>23:23</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AA327" t="inlineStr">
@@ -45021,7 +45021,7 @@
       </c>
       <c r="AB327" t="inlineStr">
         <is>
-          <t>23:24</t>
+          <t>22:52</t>
         </is>
       </c>
       <c r="AC327" t="inlineStr">
@@ -45066,10 +45066,10 @@
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>122254500</v>
+        <v>122254417</v>
       </c>
       <c r="B328" t="n">
-        <v>56266</v>
+        <v>56280</v>
       </c>
       <c r="C328" t="inlineStr">
         <is>
@@ -45078,25 +45078,25 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E328" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
@@ -45120,10 +45120,10 @@
         </is>
       </c>
       <c r="Q328" t="n">
-        <v>586388</v>
+        <v>586426</v>
       </c>
       <c r="R328" t="n">
-        <v>6311142</v>
+        <v>6311145</v>
       </c>
       <c r="S328" t="n">
         <v>5</v>
@@ -45155,7 +45155,7 @@
       </c>
       <c r="Z328" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="AA328" t="inlineStr">
@@ -45165,7 +45165,7 @@
       </c>
       <c r="AB328" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>22:34</t>
         </is>
       </c>
       <c r="AC328" t="inlineStr">
@@ -45210,10 +45210,10 @@
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>122254952</v>
+        <v>122254312</v>
       </c>
       <c r="B329" t="n">
-        <v>56273</v>
+        <v>56280</v>
       </c>
       <c r="C329" t="inlineStr">
         <is>
@@ -45226,21 +45226,21 @@
         </is>
       </c>
       <c r="E329" t="n">
-        <v>205992</v>
+        <v>100092</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
@@ -45264,10 +45264,10 @@
         </is>
       </c>
       <c r="Q329" t="n">
-        <v>586455</v>
+        <v>586452</v>
       </c>
       <c r="R329" t="n">
-        <v>6311156</v>
+        <v>6311152</v>
       </c>
       <c r="S329" t="n">
         <v>5</v>
@@ -45299,17 +45299,17 @@
       </c>
       <c r="Z329" t="inlineStr">
         <is>
+          <t>23:27</t>
+        </is>
+      </c>
+      <c r="AA329" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AB329" t="inlineStr">
+        <is>
           <t>23:28</t>
-        </is>
-      </c>
-      <c r="AA329" t="inlineStr">
-        <is>
-          <t>2024-06-26</t>
-        </is>
-      </c>
-      <c r="AB329" t="inlineStr">
-        <is>
-          <t>23:29</t>
         </is>
       </c>
       <c r="AC329" t="inlineStr">
@@ -45354,10 +45354,10 @@
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>122254512</v>
+        <v>122254633</v>
       </c>
       <c r="B330" t="n">
-        <v>56266</v>
+        <v>56285</v>
       </c>
       <c r="C330" t="inlineStr">
         <is>
@@ -45366,25 +45366,25 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E330" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
@@ -45408,10 +45408,10 @@
         </is>
       </c>
       <c r="Q330" t="n">
-        <v>586379</v>
+        <v>586396</v>
       </c>
       <c r="R330" t="n">
-        <v>6311136</v>
+        <v>6311146</v>
       </c>
       <c r="S330" t="n">
         <v>5</v>
@@ -45443,17 +45443,17 @@
       </c>
       <c r="Z330" t="inlineStr">
         <is>
+          <t>22:44</t>
+        </is>
+      </c>
+      <c r="AA330" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AB330" t="inlineStr">
+        <is>
           <t>22:45</t>
-        </is>
-      </c>
-      <c r="AA330" t="inlineStr">
-        <is>
-          <t>2024-06-26</t>
-        </is>
-      </c>
-      <c r="AB330" t="inlineStr">
-        <is>
-          <t>22:46</t>
         </is>
       </c>
       <c r="AC330" t="inlineStr">
@@ -45498,10 +45498,10 @@
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>122254498</v>
+        <v>122254587</v>
       </c>
       <c r="B331" t="n">
-        <v>56266</v>
+        <v>56285</v>
       </c>
       <c r="C331" t="inlineStr">
         <is>
@@ -45510,25 +45510,25 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E331" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I331" t="inlineStr">
@@ -45552,10 +45552,10 @@
         </is>
       </c>
       <c r="Q331" t="n">
-        <v>586393</v>
+        <v>586443</v>
       </c>
       <c r="R331" t="n">
-        <v>6311147</v>
+        <v>6311163</v>
       </c>
       <c r="S331" t="n">
         <v>5</v>
@@ -45587,7 +45587,7 @@
       </c>
       <c r="Z331" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AA331" t="inlineStr">
@@ -45597,7 +45597,7 @@
       </c>
       <c r="AB331" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AC331" t="inlineStr">
@@ -45642,10 +45642,10 @@
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>122254393</v>
+        <v>122254519</v>
       </c>
       <c r="B332" t="n">
-        <v>56280</v>
+        <v>56266</v>
       </c>
       <c r="C332" t="inlineStr">
         <is>
@@ -45654,25 +45654,25 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E332" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
@@ -45696,10 +45696,10 @@
         </is>
       </c>
       <c r="Q332" t="n">
-        <v>586396</v>
+        <v>586424</v>
       </c>
       <c r="R332" t="n">
-        <v>6311146</v>
+        <v>6311135</v>
       </c>
       <c r="S332" t="n">
         <v>5</v>
@@ -45731,7 +45731,7 @@
       </c>
       <c r="Z332" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AA332" t="inlineStr">
@@ -45741,7 +45741,7 @@
       </c>
       <c r="AB332" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>22:38</t>
         </is>
       </c>
       <c r="AC332" t="inlineStr">
@@ -45786,10 +45786,10 @@
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>122254373</v>
+        <v>122254644</v>
       </c>
       <c r="B333" t="n">
-        <v>56280</v>
+        <v>56285</v>
       </c>
       <c r="C333" t="inlineStr">
         <is>
@@ -45802,21 +45802,21 @@
         </is>
       </c>
       <c r="E333" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
@@ -45840,10 +45840,10 @@
         </is>
       </c>
       <c r="Q333" t="n">
-        <v>586307</v>
+        <v>586429</v>
       </c>
       <c r="R333" t="n">
-        <v>6311133</v>
+        <v>6311115</v>
       </c>
       <c r="S333" t="n">
         <v>5</v>
@@ -45875,7 +45875,7 @@
       </c>
       <c r="Z333" t="inlineStr">
         <is>
-          <t>22:49</t>
+          <t>22:36</t>
         </is>
       </c>
       <c r="AA333" t="inlineStr">
@@ -45885,7 +45885,7 @@
       </c>
       <c r="AB333" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AC333" t="inlineStr">
@@ -45930,10 +45930,10 @@
     </row>
     <row r="334">
       <c r="A334" t="n">
-        <v>122254964</v>
+        <v>122254652</v>
       </c>
       <c r="B334" t="n">
-        <v>56273</v>
+        <v>56285</v>
       </c>
       <c r="C334" t="inlineStr">
         <is>
@@ -45946,21 +45946,21 @@
         </is>
       </c>
       <c r="E334" t="n">
-        <v>205992</v>
+        <v>205995</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
@@ -45984,10 +45984,10 @@
         </is>
       </c>
       <c r="Q334" t="n">
-        <v>586430</v>
+        <v>586432</v>
       </c>
       <c r="R334" t="n">
-        <v>6311142</v>
+        <v>6311118</v>
       </c>
       <c r="S334" t="n">
         <v>5</v>
@@ -46019,7 +46019,7 @@
       </c>
       <c r="Z334" t="inlineStr">
         <is>
-          <t>22:33</t>
+          <t>22:34</t>
         </is>
       </c>
       <c r="AA334" t="inlineStr">
@@ -46029,7 +46029,7 @@
       </c>
       <c r="AB334" t="inlineStr">
         <is>
-          <t>22:34</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="AC334" t="inlineStr">
@@ -46074,10 +46074,10 @@
     </row>
     <row r="335">
       <c r="A335" t="n">
-        <v>122254474</v>
+        <v>122254854</v>
       </c>
       <c r="B335" t="n">
-        <v>56266</v>
+        <v>56283</v>
       </c>
       <c r="C335" t="inlineStr">
         <is>
@@ -46086,25 +46086,25 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E335" t="n">
-        <v>205998</v>
+        <v>100111</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I335" t="inlineStr">
@@ -46128,10 +46128,10 @@
         </is>
       </c>
       <c r="Q335" t="n">
-        <v>586443</v>
+        <v>586329</v>
       </c>
       <c r="R335" t="n">
-        <v>6311164</v>
+        <v>6311120</v>
       </c>
       <c r="S335" t="n">
         <v>5</v>
@@ -46163,7 +46163,7 @@
       </c>
       <c r="Z335" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>22:57</t>
         </is>
       </c>
       <c r="AA335" t="inlineStr">
@@ -46173,7 +46173,7 @@
       </c>
       <c r="AB335" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>22:58</t>
         </is>
       </c>
       <c r="AC335" t="inlineStr">
@@ -46218,10 +46218,10 @@
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>122254658</v>
+        <v>122254365</v>
       </c>
       <c r="B336" t="n">
-        <v>56285</v>
+        <v>56280</v>
       </c>
       <c r="C336" t="inlineStr">
         <is>
@@ -46234,21 +46234,21 @@
         </is>
       </c>
       <c r="E336" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
@@ -46272,10 +46272,10 @@
         </is>
       </c>
       <c r="Q336" t="n">
-        <v>586491</v>
+        <v>586276</v>
       </c>
       <c r="R336" t="n">
-        <v>6311181</v>
+        <v>6311100</v>
       </c>
       <c r="S336" t="n">
         <v>5</v>
@@ -46307,7 +46307,7 @@
       </c>
       <c r="Z336" t="inlineStr">
         <is>
-          <t>22:31</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AA336" t="inlineStr">
@@ -46317,7 +46317,7 @@
       </c>
       <c r="AB336" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>22:52</t>
         </is>
       </c>
       <c r="AC336" t="inlineStr">
@@ -46362,7 +46362,7 @@
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>122254954</v>
+        <v>122254953</v>
       </c>
       <c r="B337" t="n">
         <v>56273</v>
@@ -46416,10 +46416,10 @@
         </is>
       </c>
       <c r="Q337" t="n">
-        <v>586442</v>
+        <v>586449</v>
       </c>
       <c r="R337" t="n">
-        <v>6311152</v>
+        <v>6311155</v>
       </c>
       <c r="S337" t="n">
         <v>5</v>
@@ -46451,7 +46451,7 @@
       </c>
       <c r="Z337" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA337" t="inlineStr">
@@ -46461,7 +46461,7 @@
       </c>
       <c r="AB337" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC337" t="inlineStr">
@@ -46506,10 +46506,10 @@
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>122254612</v>
+        <v>122254514</v>
       </c>
       <c r="B338" t="n">
-        <v>56285</v>
+        <v>56266</v>
       </c>
       <c r="C338" t="inlineStr">
         <is>
@@ -46518,25 +46518,25 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E338" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
@@ -46560,10 +46560,10 @@
         </is>
       </c>
       <c r="Q338" t="n">
-        <v>586371</v>
+        <v>586408</v>
       </c>
       <c r="R338" t="n">
-        <v>6311135</v>
+        <v>6311124</v>
       </c>
       <c r="S338" t="n">
         <v>5</v>
@@ -46595,7 +46595,7 @@
       </c>
       <c r="Z338" t="inlineStr">
         <is>
-          <t>22:59</t>
+          <t>22:43</t>
         </is>
       </c>
       <c r="AA338" t="inlineStr">
@@ -46605,7 +46605,7 @@
       </c>
       <c r="AB338" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AC338" t="inlineStr">
@@ -46650,7 +46650,7 @@
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>122254611</v>
+        <v>122254588</v>
       </c>
       <c r="B339" t="n">
         <v>56285</v>
@@ -46704,10 +46704,10 @@
         </is>
       </c>
       <c r="Q339" t="n">
-        <v>586370</v>
+        <v>586415</v>
       </c>
       <c r="R339" t="n">
-        <v>6311139</v>
+        <v>6311196</v>
       </c>
       <c r="S339" t="n">
         <v>5</v>
@@ -46739,7 +46739,7 @@
       </c>
       <c r="Z339" t="inlineStr">
         <is>
-          <t>22:59</t>
+          <t>23:22</t>
         </is>
       </c>
       <c r="AA339" t="inlineStr">
@@ -46749,7 +46749,7 @@
       </c>
       <c r="AB339" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>23:23</t>
         </is>
       </c>
       <c r="AC339" t="inlineStr">
@@ -46794,10 +46794,10 @@
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>122254648</v>
+        <v>122254511</v>
       </c>
       <c r="B340" t="n">
-        <v>56285</v>
+        <v>56266</v>
       </c>
       <c r="C340" t="inlineStr">
         <is>
@@ -46806,25 +46806,25 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E340" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
@@ -46848,10 +46848,10 @@
         </is>
       </c>
       <c r="Q340" t="n">
-        <v>586418</v>
+        <v>586374</v>
       </c>
       <c r="R340" t="n">
-        <v>6311107</v>
+        <v>6311139</v>
       </c>
       <c r="S340" t="n">
         <v>5</v>
@@ -46883,7 +46883,7 @@
       </c>
       <c r="Z340" t="inlineStr">
         <is>
-          <t>22:36</t>
+          <t>22:46</t>
         </is>
       </c>
       <c r="AA340" t="inlineStr">
@@ -46893,7 +46893,7 @@
       </c>
       <c r="AB340" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>22:47</t>
         </is>
       </c>
       <c r="AC340" t="inlineStr">
@@ -46938,10 +46938,10 @@
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>122254957</v>
+        <v>122254342</v>
       </c>
       <c r="B341" t="n">
-        <v>56273</v>
+        <v>56280</v>
       </c>
       <c r="C341" t="inlineStr">
         <is>
@@ -46954,21 +46954,21 @@
         </is>
       </c>
       <c r="E341" t="n">
-        <v>205992</v>
+        <v>100092</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I341" t="inlineStr">
@@ -46992,10 +46992,10 @@
         </is>
       </c>
       <c r="Q341" t="n">
-        <v>586444</v>
+        <v>586389</v>
       </c>
       <c r="R341" t="n">
-        <v>6311160</v>
+        <v>6311142</v>
       </c>
       <c r="S341" t="n">
         <v>5</v>
@@ -47027,7 +47027,7 @@
       </c>
       <c r="Z341" t="inlineStr">
         <is>
-          <t>23:24</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA341" t="inlineStr">
@@ -47037,7 +47037,7 @@
       </c>
       <c r="AB341" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AC341" t="inlineStr">
@@ -47082,10 +47082,10 @@
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>122254584</v>
+        <v>122254421</v>
       </c>
       <c r="B342" t="n">
-        <v>56285</v>
+        <v>56280</v>
       </c>
       <c r="C342" t="inlineStr">
         <is>
@@ -47098,21 +47098,21 @@
         </is>
       </c>
       <c r="E342" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
@@ -47136,10 +47136,10 @@
         </is>
       </c>
       <c r="Q342" t="n">
-        <v>586473</v>
+        <v>586468</v>
       </c>
       <c r="R342" t="n">
-        <v>6311192</v>
+        <v>6311181</v>
       </c>
       <c r="S342" t="n">
         <v>5</v>
@@ -47171,7 +47171,7 @@
       </c>
       <c r="Z342" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AA342" t="inlineStr">
@@ -47181,7 +47181,7 @@
       </c>
       <c r="AB342" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="AC342" t="inlineStr">
@@ -47226,10 +47226,10 @@
     </row>
     <row r="343">
       <c r="A343" t="n">
-        <v>122254617</v>
+        <v>122254393</v>
       </c>
       <c r="B343" t="n">
-        <v>56285</v>
+        <v>56280</v>
       </c>
       <c r="C343" t="inlineStr">
         <is>
@@ -47242,21 +47242,21 @@
         </is>
       </c>
       <c r="E343" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
@@ -47280,10 +47280,10 @@
         </is>
       </c>
       <c r="Q343" t="n">
-        <v>586317</v>
+        <v>586396</v>
       </c>
       <c r="R343" t="n">
-        <v>6311115</v>
+        <v>6311146</v>
       </c>
       <c r="S343" t="n">
         <v>5</v>
@@ -47315,7 +47315,7 @@
       </c>
       <c r="Z343" t="inlineStr">
         <is>
-          <t>22:57</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AA343" t="inlineStr">
@@ -47325,7 +47325,7 @@
       </c>
       <c r="AB343" t="inlineStr">
         <is>
-          <t>22:58</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AC343" t="inlineStr">
@@ -47370,10 +47370,10 @@
     </row>
     <row r="344">
       <c r="A344" t="n">
-        <v>122254511</v>
+        <v>122254959</v>
       </c>
       <c r="B344" t="n">
-        <v>56266</v>
+        <v>56273</v>
       </c>
       <c r="C344" t="inlineStr">
         <is>
@@ -47382,25 +47382,25 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E344" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
@@ -47424,7 +47424,7 @@
         </is>
       </c>
       <c r="Q344" t="n">
-        <v>586374</v>
+        <v>586370</v>
       </c>
       <c r="R344" t="n">
         <v>6311139</v>
@@ -47459,7 +47459,7 @@
       </c>
       <c r="Z344" t="inlineStr">
         <is>
-          <t>22:46</t>
+          <t>22:59</t>
         </is>
       </c>
       <c r="AA344" t="inlineStr">
@@ -47469,7 +47469,7 @@
       </c>
       <c r="AB344" t="inlineStr">
         <is>
-          <t>22:47</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AC344" t="inlineStr">
@@ -47514,37 +47514,37 @@
     </row>
     <row r="345">
       <c r="A345" t="n">
-        <v>122254173</v>
+        <v>122254655</v>
       </c>
       <c r="B345" t="n">
-        <v>56264</v>
+        <v>56285</v>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Dokumentation efterfrågas</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E345" t="n">
-        <v>100015</v>
+        <v>205995</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>Barbastell</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>Barbastella barbastellus</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
@@ -47568,10 +47568,10 @@
         </is>
       </c>
       <c r="Q345" t="n">
-        <v>586415</v>
+        <v>586475</v>
       </c>
       <c r="R345" t="n">
-        <v>6311149</v>
+        <v>6311187</v>
       </c>
       <c r="S345" t="n">
         <v>5</v>
@@ -47603,7 +47603,7 @@
       </c>
       <c r="Z345" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AA345" t="inlineStr">
@@ -47613,7 +47613,7 @@
       </c>
       <c r="AB345" t="inlineStr">
         <is>
-          <t>23:03</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="AC345" t="inlineStr">
@@ -47658,10 +47658,10 @@
     </row>
     <row r="346">
       <c r="A346" t="n">
-        <v>122254854</v>
+        <v>122254314</v>
       </c>
       <c r="B346" t="n">
-        <v>56283</v>
+        <v>56280</v>
       </c>
       <c r="C346" t="inlineStr">
         <is>
@@ -47674,21 +47674,21 @@
         </is>
       </c>
       <c r="E346" t="n">
-        <v>100111</v>
+        <v>100092</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
@@ -47712,10 +47712,10 @@
         </is>
       </c>
       <c r="Q346" t="n">
-        <v>586329</v>
+        <v>586443</v>
       </c>
       <c r="R346" t="n">
-        <v>6311120</v>
+        <v>6311164</v>
       </c>
       <c r="S346" t="n">
         <v>5</v>
@@ -47747,7 +47747,7 @@
       </c>
       <c r="Z346" t="inlineStr">
         <is>
-          <t>22:57</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AA346" t="inlineStr">
@@ -47757,7 +47757,7 @@
       </c>
       <c r="AB346" t="inlineStr">
         <is>
-          <t>22:58</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AC346" t="inlineStr">
@@ -47802,7 +47802,7 @@
     </row>
     <row r="347">
       <c r="A347" t="n">
-        <v>122254857</v>
+        <v>122254862</v>
       </c>
       <c r="B347" t="n">
         <v>56283</v>
@@ -47856,10 +47856,10 @@
         </is>
       </c>
       <c r="Q347" t="n">
-        <v>586317</v>
+        <v>586288</v>
       </c>
       <c r="R347" t="n">
-        <v>6311115</v>
+        <v>6311100</v>
       </c>
       <c r="S347" t="n">
         <v>5</v>
@@ -47891,7 +47891,7 @@
       </c>
       <c r="Z347" t="inlineStr">
         <is>
-          <t>22:57</t>
+          <t>22:55</t>
         </is>
       </c>
       <c r="AA347" t="inlineStr">
@@ -47901,7 +47901,7 @@
       </c>
       <c r="AB347" t="inlineStr">
         <is>
-          <t>22:58</t>
+          <t>22:56</t>
         </is>
       </c>
       <c r="AC347" t="inlineStr">
@@ -47946,10 +47946,10 @@
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>122254654</v>
+        <v>122254391</v>
       </c>
       <c r="B348" t="n">
-        <v>56285</v>
+        <v>56280</v>
       </c>
       <c r="C348" t="inlineStr">
         <is>
@@ -47962,21 +47962,21 @@
         </is>
       </c>
       <c r="E348" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I348" t="inlineStr">
@@ -48000,10 +48000,10 @@
         </is>
       </c>
       <c r="Q348" t="n">
-        <v>586467</v>
+        <v>586379</v>
       </c>
       <c r="R348" t="n">
-        <v>6311178</v>
+        <v>6311136</v>
       </c>
       <c r="S348" t="n">
         <v>5</v>
@@ -48035,7 +48035,7 @@
       </c>
       <c r="Z348" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AA348" t="inlineStr">
@@ -48045,7 +48045,7 @@
       </c>
       <c r="AB348" t="inlineStr">
         <is>
-          <t>22:33</t>
+          <t>22:46</t>
         </is>
       </c>
       <c r="AC348" t="inlineStr">
@@ -48090,10 +48090,10 @@
     </row>
     <row r="349">
       <c r="A349" t="n">
-        <v>122254880</v>
+        <v>122254350</v>
       </c>
       <c r="B349" t="n">
-        <v>56283</v>
+        <v>56280</v>
       </c>
       <c r="C349" t="inlineStr">
         <is>
@@ -48106,21 +48106,21 @@
         </is>
       </c>
       <c r="E349" t="n">
-        <v>100111</v>
+        <v>100092</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I349" t="inlineStr">
@@ -48144,10 +48144,10 @@
         </is>
       </c>
       <c r="Q349" t="n">
-        <v>586303</v>
+        <v>586330</v>
       </c>
       <c r="R349" t="n">
-        <v>6311115</v>
+        <v>6311120</v>
       </c>
       <c r="S349" t="n">
         <v>5</v>
@@ -48179,7 +48179,7 @@
       </c>
       <c r="Z349" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>22:57</t>
         </is>
       </c>
       <c r="AA349" t="inlineStr">
@@ -48189,7 +48189,7 @@
       </c>
       <c r="AB349" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>22:58</t>
         </is>
       </c>
       <c r="AC349" t="inlineStr">
@@ -48234,10 +48234,10 @@
     </row>
     <row r="350">
       <c r="A350" t="n">
-        <v>122254844</v>
+        <v>122254411</v>
       </c>
       <c r="B350" t="n">
-        <v>56283</v>
+        <v>56280</v>
       </c>
       <c r="C350" t="inlineStr">
         <is>
@@ -48250,21 +48250,21 @@
         </is>
       </c>
       <c r="E350" t="n">
-        <v>100111</v>
+        <v>100092</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I350" t="inlineStr">
@@ -48288,10 +48288,10 @@
         </is>
       </c>
       <c r="Q350" t="n">
-        <v>586387</v>
+        <v>586414</v>
       </c>
       <c r="R350" t="n">
-        <v>6311141</v>
+        <v>6311126</v>
       </c>
       <c r="S350" t="n">
         <v>5</v>
@@ -48323,7 +48323,7 @@
       </c>
       <c r="Z350" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AA350" t="inlineStr">
@@ -48333,7 +48333,7 @@
       </c>
       <c r="AB350" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>22:38</t>
         </is>
       </c>
       <c r="AC350" t="inlineStr">
@@ -48378,10 +48378,10 @@
     </row>
     <row r="351">
       <c r="A351" t="n">
-        <v>122254342</v>
+        <v>122254584</v>
       </c>
       <c r="B351" t="n">
-        <v>56280</v>
+        <v>56285</v>
       </c>
       <c r="C351" t="inlineStr">
         <is>
@@ -48394,21 +48394,21 @@
         </is>
       </c>
       <c r="E351" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I351" t="inlineStr">
@@ -48432,10 +48432,10 @@
         </is>
       </c>
       <c r="Q351" t="n">
-        <v>586389</v>
+        <v>586473</v>
       </c>
       <c r="R351" t="n">
-        <v>6311142</v>
+        <v>6311192</v>
       </c>
       <c r="S351" t="n">
         <v>5</v>
@@ -48467,7 +48467,7 @@
       </c>
       <c r="Z351" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AA351" t="inlineStr">
@@ -48477,7 +48477,7 @@
       </c>
       <c r="AB351" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AC351" t="inlineStr">
@@ -48522,32 +48522,32 @@
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>122254396</v>
+        <v>122254173</v>
       </c>
       <c r="B352" t="n">
-        <v>56280</v>
+        <v>56264</v>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Dokumentation efterfrågas</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E352" t="n">
-        <v>100092</v>
+        <v>100015</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Barbastell</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Barbastella barbastellus</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
@@ -48576,10 +48576,10 @@
         </is>
       </c>
       <c r="Q352" t="n">
-        <v>586408</v>
+        <v>586415</v>
       </c>
       <c r="R352" t="n">
-        <v>6311124</v>
+        <v>6311149</v>
       </c>
       <c r="S352" t="n">
         <v>5</v>
@@ -48611,7 +48611,7 @@
       </c>
       <c r="Z352" t="inlineStr">
         <is>
-          <t>22:43</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AA352" t="inlineStr">
@@ -48621,7 +48621,7 @@
       </c>
       <c r="AB352" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>23:03</t>
         </is>
       </c>
       <c r="AC352" t="inlineStr">
@@ -48666,10 +48666,10 @@
     </row>
     <row r="353">
       <c r="A353" t="n">
-        <v>122254878</v>
+        <v>122254395</v>
       </c>
       <c r="B353" t="n">
-        <v>56283</v>
+        <v>56280</v>
       </c>
       <c r="C353" t="inlineStr">
         <is>
@@ -48682,21 +48682,21 @@
         </is>
       </c>
       <c r="E353" t="n">
-        <v>100111</v>
+        <v>100092</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I353" t="inlineStr">
@@ -48720,10 +48720,10 @@
         </is>
       </c>
       <c r="Q353" t="n">
-        <v>586280</v>
+        <v>586408</v>
       </c>
       <c r="R353" t="n">
-        <v>6311103</v>
+        <v>6311124</v>
       </c>
       <c r="S353" t="n">
         <v>5</v>
@@ -48755,7 +48755,7 @@
       </c>
       <c r="Z353" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>22:43</t>
         </is>
       </c>
       <c r="AA353" t="inlineStr">
@@ -48765,7 +48765,7 @@
       </c>
       <c r="AB353" t="inlineStr">
         <is>
-          <t>22:52</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AC353" t="inlineStr">
@@ -48810,10 +48810,10 @@
     </row>
     <row r="354">
       <c r="A354" t="n">
-        <v>122254314</v>
+        <v>122254476</v>
       </c>
       <c r="B354" t="n">
-        <v>56280</v>
+        <v>56266</v>
       </c>
       <c r="C354" t="inlineStr">
         <is>
@@ -48822,25 +48822,25 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E354" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I354" t="inlineStr">
@@ -48864,10 +48864,10 @@
         </is>
       </c>
       <c r="Q354" t="n">
-        <v>586443</v>
+        <v>586418</v>
       </c>
       <c r="R354" t="n">
-        <v>6311164</v>
+        <v>6311167</v>
       </c>
       <c r="S354" t="n">
         <v>5</v>
@@ -48899,7 +48899,7 @@
       </c>
       <c r="Z354" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>23:23</t>
         </is>
       </c>
       <c r="AA354" t="inlineStr">
@@ -48909,7 +48909,7 @@
       </c>
       <c r="AB354" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="AC354" t="inlineStr">
@@ -48954,10 +48954,10 @@
     </row>
     <row r="355">
       <c r="A355" t="n">
-        <v>122254306</v>
+        <v>122254503</v>
       </c>
       <c r="B355" t="n">
-        <v>56280</v>
+        <v>56266</v>
       </c>
       <c r="C355" t="inlineStr">
         <is>
@@ -48966,25 +48966,25 @@
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E355" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I355" t="inlineStr">
@@ -49008,10 +49008,10 @@
         </is>
       </c>
       <c r="Q355" t="n">
-        <v>586473</v>
+        <v>586313</v>
       </c>
       <c r="R355" t="n">
-        <v>6311192</v>
+        <v>6311124</v>
       </c>
       <c r="S355" t="n">
         <v>5</v>
@@ -49043,7 +49043,7 @@
       </c>
       <c r="Z355" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AA355" t="inlineStr">
@@ -49053,7 +49053,7 @@
       </c>
       <c r="AB355" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AC355" t="inlineStr">
@@ -49098,10 +49098,10 @@
     </row>
     <row r="356">
       <c r="A356" t="n">
-        <v>122254633</v>
+        <v>122254474</v>
       </c>
       <c r="B356" t="n">
-        <v>56285</v>
+        <v>56266</v>
       </c>
       <c r="C356" t="inlineStr">
         <is>
@@ -49110,25 +49110,25 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E356" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I356" t="inlineStr">
@@ -49152,10 +49152,10 @@
         </is>
       </c>
       <c r="Q356" t="n">
-        <v>586396</v>
+        <v>586443</v>
       </c>
       <c r="R356" t="n">
-        <v>6311146</v>
+        <v>6311164</v>
       </c>
       <c r="S356" t="n">
         <v>5</v>
@@ -49187,7 +49187,7 @@
       </c>
       <c r="Z356" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AA356" t="inlineStr">
@@ -49197,7 +49197,7 @@
       </c>
       <c r="AB356" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AC356" t="inlineStr">
@@ -49242,10 +49242,10 @@
     </row>
     <row r="357">
       <c r="A357" t="n">
-        <v>122254657</v>
+        <v>122254316</v>
       </c>
       <c r="B357" t="n">
-        <v>56285</v>
+        <v>56280</v>
       </c>
       <c r="C357" t="inlineStr">
         <is>
@@ -49258,21 +49258,21 @@
         </is>
       </c>
       <c r="E357" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I357" t="inlineStr">
@@ -49296,10 +49296,10 @@
         </is>
       </c>
       <c r="Q357" t="n">
-        <v>586488</v>
+        <v>586423</v>
       </c>
       <c r="R357" t="n">
-        <v>6311184</v>
+        <v>6311166</v>
       </c>
       <c r="S357" t="n">
         <v>5</v>
@@ -49331,7 +49331,7 @@
       </c>
       <c r="Z357" t="inlineStr">
         <is>
-          <t>22:31</t>
+          <t>23:23</t>
         </is>
       </c>
       <c r="AA357" t="inlineStr">
@@ -49341,7 +49341,7 @@
       </c>
       <c r="AB357" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="AC357" t="inlineStr">
@@ -49386,7 +49386,7 @@
     </row>
     <row r="358">
       <c r="A358" t="n">
-        <v>122254652</v>
+        <v>122254636</v>
       </c>
       <c r="B358" t="n">
         <v>56285</v>
@@ -49440,10 +49440,10 @@
         </is>
       </c>
       <c r="Q358" t="n">
-        <v>586432</v>
+        <v>586418</v>
       </c>
       <c r="R358" t="n">
-        <v>6311118</v>
+        <v>6311145</v>
       </c>
       <c r="S358" t="n">
         <v>5</v>
@@ -49475,7 +49475,7 @@
       </c>
       <c r="Z358" t="inlineStr">
         <is>
-          <t>22:34</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AA358" t="inlineStr">
@@ -49485,7 +49485,7 @@
       </c>
       <c r="AB358" t="inlineStr">
         <is>
-          <t>22:35</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AC358" t="inlineStr">
@@ -49530,10 +49530,10 @@
     </row>
     <row r="359">
       <c r="A359" t="n">
-        <v>122254308</v>
+        <v>122254963</v>
       </c>
       <c r="B359" t="n">
-        <v>56280</v>
+        <v>56273</v>
       </c>
       <c r="C359" t="inlineStr">
         <is>
@@ -49546,21 +49546,21 @@
         </is>
       </c>
       <c r="E359" t="n">
-        <v>100092</v>
+        <v>205992</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I359" t="inlineStr">
@@ -49584,10 +49584,10 @@
         </is>
       </c>
       <c r="Q359" t="n">
-        <v>586455</v>
+        <v>586374</v>
       </c>
       <c r="R359" t="n">
-        <v>6311159</v>
+        <v>6311140</v>
       </c>
       <c r="S359" t="n">
         <v>5</v>
@@ -49619,7 +49619,7 @@
       </c>
       <c r="Z359" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>22:46</t>
         </is>
       </c>
       <c r="AA359" t="inlineStr">
@@ -49629,7 +49629,7 @@
       </c>
       <c r="AB359" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>22:47</t>
         </is>
       </c>
       <c r="AC359" t="inlineStr">
@@ -49674,10 +49674,10 @@
     </row>
     <row r="360">
       <c r="A360" t="n">
-        <v>122254476</v>
+        <v>122254951</v>
       </c>
       <c r="B360" t="n">
-        <v>56266</v>
+        <v>56273</v>
       </c>
       <c r="C360" t="inlineStr">
         <is>
@@ -49686,25 +49686,25 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E360" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I360" t="inlineStr">
@@ -49728,10 +49728,10 @@
         </is>
       </c>
       <c r="Q360" t="n">
-        <v>586418</v>
+        <v>586459</v>
       </c>
       <c r="R360" t="n">
-        <v>6311167</v>
+        <v>6311154</v>
       </c>
       <c r="S360" t="n">
         <v>5</v>
@@ -49763,7 +49763,7 @@
       </c>
       <c r="Z360" t="inlineStr">
         <is>
-          <t>23:23</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AA360" t="inlineStr">
@@ -49773,7 +49773,7 @@
       </c>
       <c r="AB360" t="inlineStr">
         <is>
-          <t>23:24</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AC360" t="inlineStr">
@@ -49818,7 +49818,7 @@
     </row>
     <row r="361">
       <c r="A361" t="n">
-        <v>122254649</v>
+        <v>122254635</v>
       </c>
       <c r="B361" t="n">
         <v>56285</v>
@@ -49872,10 +49872,10 @@
         </is>
       </c>
       <c r="Q361" t="n">
-        <v>586422</v>
+        <v>586417</v>
       </c>
       <c r="R361" t="n">
-        <v>6311100</v>
+        <v>6311145</v>
       </c>
       <c r="S361" t="n">
         <v>5</v>
@@ -49907,7 +49907,7 @@
       </c>
       <c r="Z361" t="inlineStr">
         <is>
-          <t>22:35</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AA361" t="inlineStr">
@@ -49917,7 +49917,7 @@
       </c>
       <c r="AB361" t="inlineStr">
         <is>
-          <t>22:36</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AC361" t="inlineStr">
@@ -49962,7 +49962,7 @@
     </row>
     <row r="362">
       <c r="A362" t="n">
-        <v>122254643</v>
+        <v>122254626</v>
       </c>
       <c r="B362" t="n">
         <v>56285</v>
@@ -50016,10 +50016,10 @@
         </is>
       </c>
       <c r="Q362" t="n">
-        <v>586424</v>
+        <v>586313</v>
       </c>
       <c r="R362" t="n">
-        <v>6311135</v>
+        <v>6311124</v>
       </c>
       <c r="S362" t="n">
         <v>5</v>
@@ -50051,7 +50051,7 @@
       </c>
       <c r="Z362" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AA362" t="inlineStr">
@@ -50061,7 +50061,7 @@
       </c>
       <c r="AB362" t="inlineStr">
         <is>
-          <t>22:38</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AC362" t="inlineStr">
@@ -50106,10 +50106,10 @@
     </row>
     <row r="363">
       <c r="A363" t="n">
-        <v>122254953</v>
+        <v>122254845</v>
       </c>
       <c r="B363" t="n">
-        <v>56273</v>
+        <v>56283</v>
       </c>
       <c r="C363" t="inlineStr">
         <is>
@@ -50122,21 +50122,21 @@
         </is>
       </c>
       <c r="E363" t="n">
-        <v>205992</v>
+        <v>100111</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I363" t="inlineStr">
@@ -50160,10 +50160,10 @@
         </is>
       </c>
       <c r="Q363" t="n">
-        <v>586449</v>
+        <v>586370</v>
       </c>
       <c r="R363" t="n">
-        <v>6311155</v>
+        <v>6311139</v>
       </c>
       <c r="S363" t="n">
         <v>5</v>
@@ -50195,7 +50195,7 @@
       </c>
       <c r="Z363" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>22:59</t>
         </is>
       </c>
       <c r="AA363" t="inlineStr">
@@ -50205,7 +50205,7 @@
       </c>
       <c r="AB363" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AC363" t="inlineStr">
@@ -50250,10 +50250,10 @@
     </row>
     <row r="364">
       <c r="A364" t="n">
-        <v>122254835</v>
+        <v>122254308</v>
       </c>
       <c r="B364" t="n">
-        <v>56283</v>
+        <v>56280</v>
       </c>
       <c r="C364" t="inlineStr">
         <is>
@@ -50266,21 +50266,21 @@
         </is>
       </c>
       <c r="E364" t="n">
-        <v>100111</v>
+        <v>100092</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I364" t="inlineStr">
@@ -50304,10 +50304,10 @@
         </is>
       </c>
       <c r="Q364" t="n">
-        <v>586473</v>
+        <v>586455</v>
       </c>
       <c r="R364" t="n">
-        <v>6311192</v>
+        <v>6311159</v>
       </c>
       <c r="S364" t="n">
         <v>5</v>
@@ -50339,17 +50339,17 @@
       </c>
       <c r="Z364" t="inlineStr">
         <is>
+          <t>23:28</t>
+        </is>
+      </c>
+      <c r="AA364" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AB364" t="inlineStr">
+        <is>
           <t>23:29</t>
-        </is>
-      </c>
-      <c r="AA364" t="inlineStr">
-        <is>
-          <t>2024-06-26</t>
-        </is>
-      </c>
-      <c r="AB364" t="inlineStr">
-        <is>
-          <t>23:30</t>
         </is>
       </c>
       <c r="AC364" t="inlineStr">
@@ -50538,7 +50538,7 @@
     </row>
     <row r="366">
       <c r="A366" t="n">
-        <v>122254352</v>
+        <v>122254306</v>
       </c>
       <c r="B366" t="n">
         <v>56280</v>
@@ -50592,10 +50592,10 @@
         </is>
       </c>
       <c r="Q366" t="n">
-        <v>586288</v>
+        <v>586473</v>
       </c>
       <c r="R366" t="n">
-        <v>6311100</v>
+        <v>6311192</v>
       </c>
       <c r="S366" t="n">
         <v>5</v>
@@ -50627,7 +50627,7 @@
       </c>
       <c r="Z366" t="inlineStr">
         <is>
-          <t>22:55</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AA366" t="inlineStr">
@@ -50637,7 +50637,7 @@
       </c>
       <c r="AB366" t="inlineStr">
         <is>
-          <t>22:56</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AC366" t="inlineStr">
@@ -50682,10 +50682,10 @@
     </row>
     <row r="367">
       <c r="A367" t="n">
-        <v>122254394</v>
+        <v>122254835</v>
       </c>
       <c r="B367" t="n">
-        <v>56280</v>
+        <v>56283</v>
       </c>
       <c r="C367" t="inlineStr">
         <is>
@@ -50698,21 +50698,21 @@
         </is>
       </c>
       <c r="E367" t="n">
-        <v>100092</v>
+        <v>100111</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I367" t="inlineStr">
@@ -50736,10 +50736,10 @@
         </is>
       </c>
       <c r="Q367" t="n">
-        <v>586419</v>
+        <v>586473</v>
       </c>
       <c r="R367" t="n">
-        <v>6311142</v>
+        <v>6311192</v>
       </c>
       <c r="S367" t="n">
         <v>5</v>
@@ -50771,7 +50771,7 @@
       </c>
       <c r="Z367" t="inlineStr">
         <is>
-          <t>22:43</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AA367" t="inlineStr">
@@ -50781,7 +50781,7 @@
       </c>
       <c r="AB367" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AC367" t="inlineStr">
@@ -50826,10 +50826,10 @@
     </row>
     <row r="368">
       <c r="A368" t="n">
-        <v>122254392</v>
+        <v>122254609</v>
       </c>
       <c r="B368" t="n">
-        <v>56280</v>
+        <v>56285</v>
       </c>
       <c r="C368" t="inlineStr">
         <is>
@@ -50842,21 +50842,21 @@
         </is>
       </c>
       <c r="E368" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H368" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I368" t="inlineStr">
@@ -50880,10 +50880,10 @@
         </is>
       </c>
       <c r="Q368" t="n">
-        <v>586384</v>
+        <v>586392</v>
       </c>
       <c r="R368" t="n">
-        <v>6311139</v>
+        <v>6311147</v>
       </c>
       <c r="S368" t="n">
         <v>5</v>
@@ -50915,7 +50915,7 @@
       </c>
       <c r="Z368" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AA368" t="inlineStr">
@@ -50925,7 +50925,7 @@
       </c>
       <c r="AB368" t="inlineStr">
         <is>
-          <t>22:46</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AC368" t="inlineStr">
@@ -50970,10 +50970,10 @@
     </row>
     <row r="369">
       <c r="A369" t="n">
-        <v>122254650</v>
+        <v>122254352</v>
       </c>
       <c r="B369" t="n">
-        <v>56285</v>
+        <v>56280</v>
       </c>
       <c r="C369" t="inlineStr">
         <is>
@@ -50986,21 +50986,21 @@
         </is>
       </c>
       <c r="E369" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I369" t="inlineStr">
@@ -51024,10 +51024,10 @@
         </is>
       </c>
       <c r="Q369" t="n">
-        <v>586422</v>
+        <v>586288</v>
       </c>
       <c r="R369" t="n">
-        <v>6311105</v>
+        <v>6311100</v>
       </c>
       <c r="S369" t="n">
         <v>5</v>
@@ -51059,7 +51059,7 @@
       </c>
       <c r="Z369" t="inlineStr">
         <is>
-          <t>22:35</t>
+          <t>22:55</t>
         </is>
       </c>
       <c r="AA369" t="inlineStr">
@@ -51069,7 +51069,7 @@
       </c>
       <c r="AB369" t="inlineStr">
         <is>
-          <t>22:36</t>
+          <t>22:56</t>
         </is>
       </c>
       <c r="AC369" t="inlineStr">
@@ -51114,10 +51114,10 @@
     </row>
     <row r="370">
       <c r="A370" t="n">
-        <v>122254646</v>
+        <v>122254370</v>
       </c>
       <c r="B370" t="n">
-        <v>56285</v>
+        <v>56280</v>
       </c>
       <c r="C370" t="inlineStr">
         <is>
@@ -51130,21 +51130,21 @@
         </is>
       </c>
       <c r="E370" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I370" t="inlineStr">
@@ -51168,10 +51168,10 @@
         </is>
       </c>
       <c r="Q370" t="n">
-        <v>586422</v>
+        <v>586309</v>
       </c>
       <c r="R370" t="n">
-        <v>6311111</v>
+        <v>6311119</v>
       </c>
       <c r="S370" t="n">
         <v>5</v>
@@ -51203,7 +51203,7 @@
       </c>
       <c r="Z370" t="inlineStr">
         <is>
-          <t>22:36</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AA370" t="inlineStr">
@@ -51213,7 +51213,7 @@
       </c>
       <c r="AB370" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AC370" t="inlineStr">
@@ -51258,10 +51258,10 @@
     </row>
     <row r="371">
       <c r="A371" t="n">
-        <v>122254607</v>
+        <v>122254473</v>
       </c>
       <c r="B371" t="n">
-        <v>56285</v>
+        <v>56266</v>
       </c>
       <c r="C371" t="inlineStr">
         <is>
@@ -51270,25 +51270,25 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E371" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I371" t="inlineStr">
@@ -51312,10 +51312,10 @@
         </is>
       </c>
       <c r="Q371" t="n">
-        <v>586415</v>
+        <v>586450</v>
       </c>
       <c r="R371" t="n">
-        <v>6311149</v>
+        <v>6311152</v>
       </c>
       <c r="S371" t="n">
         <v>5</v>
@@ -51347,7 +51347,7 @@
       </c>
       <c r="Z371" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA371" t="inlineStr">
@@ -51357,7 +51357,7 @@
       </c>
       <c r="AB371" t="inlineStr">
         <is>
-          <t>23:03</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC371" t="inlineStr">
@@ -51402,10 +51402,10 @@
     </row>
     <row r="372">
       <c r="A372" t="n">
-        <v>122254616</v>
+        <v>122254498</v>
       </c>
       <c r="B372" t="n">
-        <v>56285</v>
+        <v>56266</v>
       </c>
       <c r="C372" t="inlineStr">
         <is>
@@ -51414,25 +51414,25 @@
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E372" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I372" t="inlineStr">
@@ -51456,10 +51456,10 @@
         </is>
       </c>
       <c r="Q372" t="n">
-        <v>586327</v>
+        <v>586393</v>
       </c>
       <c r="R372" t="n">
-        <v>6311118</v>
+        <v>6311147</v>
       </c>
       <c r="S372" t="n">
         <v>5</v>
@@ -51491,7 +51491,7 @@
       </c>
       <c r="Z372" t="inlineStr">
         <is>
-          <t>22:57</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AA372" t="inlineStr">
@@ -51501,7 +51501,7 @@
       </c>
       <c r="AB372" t="inlineStr">
         <is>
-          <t>22:58</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AC372" t="inlineStr">
@@ -51546,10 +51546,10 @@
     </row>
     <row r="373">
       <c r="A373" t="n">
-        <v>122254365</v>
+        <v>122254654</v>
       </c>
       <c r="B373" t="n">
-        <v>56280</v>
+        <v>56285</v>
       </c>
       <c r="C373" t="inlineStr">
         <is>
@@ -51562,21 +51562,21 @@
         </is>
       </c>
       <c r="E373" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H373" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I373" t="inlineStr">
@@ -51600,10 +51600,10 @@
         </is>
       </c>
       <c r="Q373" t="n">
-        <v>586276</v>
+        <v>586467</v>
       </c>
       <c r="R373" t="n">
-        <v>6311100</v>
+        <v>6311178</v>
       </c>
       <c r="S373" t="n">
         <v>5</v>
@@ -51635,7 +51635,7 @@
       </c>
       <c r="Z373" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AA373" t="inlineStr">
@@ -51645,7 +51645,7 @@
       </c>
       <c r="AB373" t="inlineStr">
         <is>
-          <t>22:52</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="AC373" t="inlineStr">
@@ -51690,7 +51690,7 @@
     </row>
     <row r="374">
       <c r="A374" t="n">
-        <v>122254644</v>
+        <v>122254653</v>
       </c>
       <c r="B374" t="n">
         <v>56285</v>
@@ -51744,10 +51744,10 @@
         </is>
       </c>
       <c r="Q374" t="n">
-        <v>586429</v>
+        <v>586430</v>
       </c>
       <c r="R374" t="n">
-        <v>6311115</v>
+        <v>6311142</v>
       </c>
       <c r="S374" t="n">
         <v>5</v>
@@ -51779,7 +51779,7 @@
       </c>
       <c r="Z374" t="inlineStr">
         <is>
-          <t>22:36</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="AA374" t="inlineStr">
@@ -51789,7 +51789,7 @@
       </c>
       <c r="AB374" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>22:34</t>
         </is>
       </c>
       <c r="AC374" t="inlineStr">
@@ -51834,10 +51834,10 @@
     </row>
     <row r="375">
       <c r="A375" t="n">
-        <v>122254862</v>
+        <v>122254307</v>
       </c>
       <c r="B375" t="n">
-        <v>56283</v>
+        <v>56280</v>
       </c>
       <c r="C375" t="inlineStr">
         <is>
@@ -51850,21 +51850,21 @@
         </is>
       </c>
       <c r="E375" t="n">
-        <v>100111</v>
+        <v>100092</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I375" t="inlineStr">
@@ -51888,10 +51888,10 @@
         </is>
       </c>
       <c r="Q375" t="n">
-        <v>586288</v>
+        <v>586477</v>
       </c>
       <c r="R375" t="n">
-        <v>6311100</v>
+        <v>6311186</v>
       </c>
       <c r="S375" t="n">
         <v>5</v>
@@ -51923,7 +51923,7 @@
       </c>
       <c r="Z375" t="inlineStr">
         <is>
-          <t>22:55</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AA375" t="inlineStr">
@@ -51933,7 +51933,7 @@
       </c>
       <c r="AB375" t="inlineStr">
         <is>
-          <t>22:56</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AC375" t="inlineStr">
@@ -51978,10 +51978,10 @@
     </row>
     <row r="376">
       <c r="A376" t="n">
-        <v>122254856</v>
+        <v>122254369</v>
       </c>
       <c r="B376" t="n">
-        <v>56283</v>
+        <v>56280</v>
       </c>
       <c r="C376" t="inlineStr">
         <is>
@@ -51994,21 +51994,21 @@
         </is>
       </c>
       <c r="E376" t="n">
-        <v>100111</v>
+        <v>100092</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H376" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I376" t="inlineStr">
@@ -52032,10 +52032,10 @@
         </is>
       </c>
       <c r="Q376" t="n">
-        <v>586327</v>
+        <v>586300</v>
       </c>
       <c r="R376" t="n">
-        <v>6311118</v>
+        <v>6311112</v>
       </c>
       <c r="S376" t="n">
         <v>5</v>
@@ -52067,7 +52067,7 @@
       </c>
       <c r="Z376" t="inlineStr">
         <is>
-          <t>22:57</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AA376" t="inlineStr">
@@ -52077,7 +52077,7 @@
       </c>
       <c r="AB376" t="inlineStr">
         <is>
-          <t>22:58</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AC376" t="inlineStr">
@@ -52122,10 +52122,10 @@
     </row>
     <row r="377">
       <c r="A377" t="n">
-        <v>122254625</v>
+        <v>122254877</v>
       </c>
       <c r="B377" t="n">
-        <v>56285</v>
+        <v>56283</v>
       </c>
       <c r="C377" t="inlineStr">
         <is>
@@ -52138,21 +52138,21 @@
         </is>
       </c>
       <c r="E377" t="n">
-        <v>205995</v>
+        <v>100111</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H377" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I377" t="inlineStr">
@@ -52176,10 +52176,10 @@
         </is>
       </c>
       <c r="Q377" t="n">
-        <v>586309</v>
+        <v>586276</v>
       </c>
       <c r="R377" t="n">
-        <v>6311119</v>
+        <v>6311100</v>
       </c>
       <c r="S377" t="n">
         <v>5</v>
@@ -52211,7 +52211,7 @@
       </c>
       <c r="Z377" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AA377" t="inlineStr">
@@ -52221,7 +52221,7 @@
       </c>
       <c r="AB377" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>22:52</t>
         </is>
       </c>
       <c r="AC377" t="inlineStr">
@@ -52266,10 +52266,10 @@
     </row>
     <row r="378">
       <c r="A378" t="n">
-        <v>122254653</v>
+        <v>122254855</v>
       </c>
       <c r="B378" t="n">
-        <v>56285</v>
+        <v>56283</v>
       </c>
       <c r="C378" t="inlineStr">
         <is>
@@ -52282,21 +52282,21 @@
         </is>
       </c>
       <c r="E378" t="n">
-        <v>205995</v>
+        <v>100111</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I378" t="inlineStr">
@@ -52320,10 +52320,10 @@
         </is>
       </c>
       <c r="Q378" t="n">
-        <v>586430</v>
+        <v>586330</v>
       </c>
       <c r="R378" t="n">
-        <v>6311142</v>
+        <v>6311120</v>
       </c>
       <c r="S378" t="n">
         <v>5</v>
@@ -52355,7 +52355,7 @@
       </c>
       <c r="Z378" t="inlineStr">
         <is>
-          <t>22:33</t>
+          <t>22:57</t>
         </is>
       </c>
       <c r="AA378" t="inlineStr">
@@ -52365,7 +52365,7 @@
       </c>
       <c r="AB378" t="inlineStr">
         <is>
-          <t>22:34</t>
+          <t>22:58</t>
         </is>
       </c>
       <c r="AC378" t="inlineStr">
@@ -52410,10 +52410,10 @@
     </row>
     <row r="379">
       <c r="A379" t="n">
-        <v>122254637</v>
+        <v>122254857</v>
       </c>
       <c r="B379" t="n">
-        <v>56285</v>
+        <v>56283</v>
       </c>
       <c r="C379" t="inlineStr">
         <is>
@@ -52426,21 +52426,21 @@
         </is>
       </c>
       <c r="E379" t="n">
-        <v>205995</v>
+        <v>100111</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H379" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I379" t="inlineStr">
@@ -52464,10 +52464,10 @@
         </is>
       </c>
       <c r="Q379" t="n">
-        <v>586408</v>
+        <v>586317</v>
       </c>
       <c r="R379" t="n">
-        <v>6311124</v>
+        <v>6311115</v>
       </c>
       <c r="S379" t="n">
         <v>5</v>
@@ -52499,7 +52499,7 @@
       </c>
       <c r="Z379" t="inlineStr">
         <is>
-          <t>22:43</t>
+          <t>22:57</t>
         </is>
       </c>
       <c r="AA379" t="inlineStr">
@@ -52509,7 +52509,7 @@
       </c>
       <c r="AB379" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>22:58</t>
         </is>
       </c>
       <c r="AC379" t="inlineStr">
@@ -52554,10 +52554,10 @@
     </row>
     <row r="380">
       <c r="A380" t="n">
-        <v>122254412</v>
+        <v>122254856</v>
       </c>
       <c r="B380" t="n">
-        <v>56280</v>
+        <v>56283</v>
       </c>
       <c r="C380" t="inlineStr">
         <is>
@@ -52570,21 +52570,21 @@
         </is>
       </c>
       <c r="E380" t="n">
-        <v>100092</v>
+        <v>100111</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H380" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I380" t="inlineStr">
@@ -52608,10 +52608,10 @@
         </is>
       </c>
       <c r="Q380" t="n">
-        <v>586424</v>
+        <v>586327</v>
       </c>
       <c r="R380" t="n">
-        <v>6311135</v>
+        <v>6311118</v>
       </c>
       <c r="S380" t="n">
         <v>5</v>
@@ -52643,7 +52643,7 @@
       </c>
       <c r="Z380" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>22:57</t>
         </is>
       </c>
       <c r="AA380" t="inlineStr">
@@ -52653,7 +52653,7 @@
       </c>
       <c r="AB380" t="inlineStr">
         <is>
-          <t>22:38</t>
+          <t>22:58</t>
         </is>
       </c>
       <c r="AC380" t="inlineStr">
@@ -52698,10 +52698,10 @@
     </row>
     <row r="381">
       <c r="A381" t="n">
-        <v>122254635</v>
+        <v>122254371</v>
       </c>
       <c r="B381" t="n">
-        <v>56285</v>
+        <v>56280</v>
       </c>
       <c r="C381" t="inlineStr">
         <is>
@@ -52714,21 +52714,21 @@
         </is>
       </c>
       <c r="E381" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I381" t="inlineStr">
@@ -52752,10 +52752,10 @@
         </is>
       </c>
       <c r="Q381" t="n">
-        <v>586417</v>
+        <v>586308</v>
       </c>
       <c r="R381" t="n">
-        <v>6311145</v>
+        <v>6311132</v>
       </c>
       <c r="S381" t="n">
         <v>5</v>
@@ -52787,7 +52787,7 @@
       </c>
       <c r="Z381" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AA381" t="inlineStr">
@@ -52797,7 +52797,7 @@
       </c>
       <c r="AB381" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AC381" t="inlineStr">
@@ -52842,10 +52842,10 @@
     </row>
     <row r="382">
       <c r="A382" t="n">
-        <v>122254963</v>
+        <v>122254627</v>
       </c>
       <c r="B382" t="n">
-        <v>56273</v>
+        <v>56285</v>
       </c>
       <c r="C382" t="inlineStr">
         <is>
@@ -52858,21 +52858,21 @@
         </is>
       </c>
       <c r="E382" t="n">
-        <v>205992</v>
+        <v>205995</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H382" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I382" t="inlineStr">
@@ -52896,10 +52896,10 @@
         </is>
       </c>
       <c r="Q382" t="n">
-        <v>586374</v>
+        <v>586306</v>
       </c>
       <c r="R382" t="n">
-        <v>6311140</v>
+        <v>6311131</v>
       </c>
       <c r="S382" t="n">
         <v>5</v>
@@ -52931,7 +52931,7 @@
       </c>
       <c r="Z382" t="inlineStr">
         <is>
-          <t>22:46</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AA382" t="inlineStr">
@@ -52941,7 +52941,7 @@
       </c>
       <c r="AB382" t="inlineStr">
         <is>
-          <t>22:47</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AC382" t="inlineStr">
@@ -52986,10 +52986,10 @@
     </row>
     <row r="383">
       <c r="A383" t="n">
-        <v>122254473</v>
+        <v>122254372</v>
       </c>
       <c r="B383" t="n">
-        <v>56266</v>
+        <v>56280</v>
       </c>
       <c r="C383" t="inlineStr">
         <is>
@@ -52998,25 +52998,25 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E383" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I383" t="inlineStr">
@@ -53040,10 +53040,10 @@
         </is>
       </c>
       <c r="Q383" t="n">
-        <v>586450</v>
+        <v>586306</v>
       </c>
       <c r="R383" t="n">
-        <v>6311152</v>
+        <v>6311131</v>
       </c>
       <c r="S383" t="n">
         <v>5</v>
@@ -53075,7 +53075,7 @@
       </c>
       <c r="Z383" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AA383" t="inlineStr">
@@ -53085,7 +53085,7 @@
       </c>
       <c r="AB383" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AC383" t="inlineStr">
@@ -53130,7 +53130,7 @@
     </row>
     <row r="384">
       <c r="A384" t="n">
-        <v>122254587</v>
+        <v>122254657</v>
       </c>
       <c r="B384" t="n">
         <v>56285</v>
@@ -53184,10 +53184,10 @@
         </is>
       </c>
       <c r="Q384" t="n">
-        <v>586443</v>
+        <v>586488</v>
       </c>
       <c r="R384" t="n">
-        <v>6311163</v>
+        <v>6311184</v>
       </c>
       <c r="S384" t="n">
         <v>5</v>
@@ -53219,7 +53219,7 @@
       </c>
       <c r="Z384" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>22:31</t>
         </is>
       </c>
       <c r="AA384" t="inlineStr">
@@ -53229,7 +53229,7 @@
       </c>
       <c r="AB384" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AC384" t="inlineStr">
@@ -53274,10 +53274,10 @@
     </row>
     <row r="385">
       <c r="A385" t="n">
-        <v>122254341</v>
+        <v>122254880</v>
       </c>
       <c r="B385" t="n">
-        <v>56280</v>
+        <v>56283</v>
       </c>
       <c r="C385" t="inlineStr">
         <is>
@@ -53290,21 +53290,21 @@
         </is>
       </c>
       <c r="E385" t="n">
-        <v>100092</v>
+        <v>100111</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H385" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I385" t="inlineStr">
@@ -53328,10 +53328,10 @@
         </is>
       </c>
       <c r="Q385" t="n">
-        <v>586415</v>
+        <v>586303</v>
       </c>
       <c r="R385" t="n">
-        <v>6311146</v>
+        <v>6311115</v>
       </c>
       <c r="S385" t="n">
         <v>5</v>
@@ -53363,7 +53363,7 @@
       </c>
       <c r="Z385" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AA385" t="inlineStr">
@@ -53373,7 +53373,7 @@
       </c>
       <c r="AB385" t="inlineStr">
         <is>
-          <t>23:03</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AC385" t="inlineStr">
@@ -53418,10 +53418,10 @@
     </row>
     <row r="386">
       <c r="A386" t="n">
-        <v>122254503</v>
+        <v>122254952</v>
       </c>
       <c r="B386" t="n">
-        <v>56266</v>
+        <v>56273</v>
       </c>
       <c r="C386" t="inlineStr">
         <is>
@@ -53430,25 +53430,25 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E386" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H386" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I386" t="inlineStr">
@@ -53472,10 +53472,10 @@
         </is>
       </c>
       <c r="Q386" t="n">
-        <v>586313</v>
+        <v>586455</v>
       </c>
       <c r="R386" t="n">
-        <v>6311124</v>
+        <v>6311156</v>
       </c>
       <c r="S386" t="n">
         <v>5</v>
@@ -53507,7 +53507,7 @@
       </c>
       <c r="Z386" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AA386" t="inlineStr">
@@ -53517,7 +53517,7 @@
       </c>
       <c r="AB386" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AC386" t="inlineStr">
@@ -53562,10 +53562,10 @@
     </row>
     <row r="387">
       <c r="A387" t="n">
-        <v>122254519</v>
+        <v>122254648</v>
       </c>
       <c r="B387" t="n">
-        <v>56266</v>
+        <v>56285</v>
       </c>
       <c r="C387" t="inlineStr">
         <is>
@@ -53574,25 +53574,25 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E387" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I387" t="inlineStr">
@@ -53616,10 +53616,10 @@
         </is>
       </c>
       <c r="Q387" t="n">
-        <v>586424</v>
+        <v>586418</v>
       </c>
       <c r="R387" t="n">
-        <v>6311135</v>
+        <v>6311107</v>
       </c>
       <c r="S387" t="n">
         <v>5</v>
@@ -53651,17 +53651,17 @@
       </c>
       <c r="Z387" t="inlineStr">
         <is>
+          <t>22:36</t>
+        </is>
+      </c>
+      <c r="AA387" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AB387" t="inlineStr">
+        <is>
           <t>22:37</t>
-        </is>
-      </c>
-      <c r="AA387" t="inlineStr">
-        <is>
-          <t>2024-06-26</t>
-        </is>
-      </c>
-      <c r="AB387" t="inlineStr">
-        <is>
-          <t>22:38</t>
         </is>
       </c>
       <c r="AC387" t="inlineStr">
@@ -53706,7 +53706,7 @@
     </row>
     <row r="388">
       <c r="A388" t="n">
-        <v>122254585</v>
+        <v>122254650</v>
       </c>
       <c r="B388" t="n">
         <v>56285</v>
@@ -53760,10 +53760,10 @@
         </is>
       </c>
       <c r="Q388" t="n">
-        <v>586455</v>
+        <v>586422</v>
       </c>
       <c r="R388" t="n">
-        <v>6311156</v>
+        <v>6311105</v>
       </c>
       <c r="S388" t="n">
         <v>5</v>
@@ -53795,7 +53795,7 @@
       </c>
       <c r="Z388" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="AA388" t="inlineStr">
@@ -53805,7 +53805,7 @@
       </c>
       <c r="AB388" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>22:36</t>
         </is>
       </c>
       <c r="AC388" t="inlineStr">
@@ -53850,7 +53850,7 @@
     </row>
     <row r="389">
       <c r="A389" t="n">
-        <v>122254636</v>
+        <v>122254610</v>
       </c>
       <c r="B389" t="n">
         <v>56285</v>
@@ -53904,10 +53904,10 @@
         </is>
       </c>
       <c r="Q389" t="n">
-        <v>586418</v>
+        <v>586389</v>
       </c>
       <c r="R389" t="n">
-        <v>6311145</v>
+        <v>6311141</v>
       </c>
       <c r="S389" t="n">
         <v>5</v>
@@ -53939,7 +53939,7 @@
       </c>
       <c r="Z389" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA389" t="inlineStr">
@@ -53949,7 +53949,7 @@
       </c>
       <c r="AB389" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AC389" t="inlineStr">
@@ -53994,10 +53994,10 @@
     </row>
     <row r="390">
       <c r="A390" t="n">
-        <v>122254836</v>
+        <v>122254612</v>
       </c>
       <c r="B390" t="n">
-        <v>56283</v>
+        <v>56285</v>
       </c>
       <c r="C390" t="inlineStr">
         <is>
@@ -54010,21 +54010,21 @@
         </is>
       </c>
       <c r="E390" t="n">
-        <v>100111</v>
+        <v>205995</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I390" t="inlineStr">
@@ -54048,10 +54048,10 @@
         </is>
       </c>
       <c r="Q390" t="n">
-        <v>586474</v>
+        <v>586371</v>
       </c>
       <c r="R390" t="n">
-        <v>6311176</v>
+        <v>6311135</v>
       </c>
       <c r="S390" t="n">
         <v>5</v>
@@ -54083,7 +54083,7 @@
       </c>
       <c r="Z390" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>22:59</t>
         </is>
       </c>
       <c r="AA390" t="inlineStr">
@@ -54093,7 +54093,7 @@
       </c>
       <c r="AB390" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AC390" t="inlineStr">

--- a/artfynd/A 36363-2024 artfynd.xlsx
+++ b/artfynd/A 36363-2024 artfynd.xlsx
@@ -39018,10 +39018,10 @@
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>122254418</v>
+        <v>122254957</v>
       </c>
       <c r="B286" t="n">
-        <v>56280</v>
+        <v>56273</v>
       </c>
       <c r="C286" t="inlineStr">
         <is>
@@ -39034,21 +39034,21 @@
         </is>
       </c>
       <c r="E286" t="n">
-        <v>100092</v>
+        <v>205992</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
@@ -39072,10 +39072,10 @@
         </is>
       </c>
       <c r="Q286" t="n">
-        <v>586467</v>
+        <v>586444</v>
       </c>
       <c r="R286" t="n">
-        <v>6311178</v>
+        <v>6311160</v>
       </c>
       <c r="S286" t="n">
         <v>5</v>
@@ -39107,7 +39107,7 @@
       </c>
       <c r="Z286" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="AA286" t="inlineStr">
@@ -39117,7 +39117,7 @@
       </c>
       <c r="AB286" t="inlineStr">
         <is>
-          <t>22:33</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AC286" t="inlineStr">
@@ -39162,10 +39162,10 @@
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>122254310</v>
+        <v>122254954</v>
       </c>
       <c r="B287" t="n">
-        <v>56280</v>
+        <v>56273</v>
       </c>
       <c r="C287" t="inlineStr">
         <is>
@@ -39178,21 +39178,21 @@
         </is>
       </c>
       <c r="E287" t="n">
-        <v>100092</v>
+        <v>205992</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
@@ -39216,10 +39216,10 @@
         </is>
       </c>
       <c r="Q287" t="n">
-        <v>586452</v>
+        <v>586442</v>
       </c>
       <c r="R287" t="n">
-        <v>6311156</v>
+        <v>6311152</v>
       </c>
       <c r="S287" t="n">
         <v>5</v>
@@ -39251,7 +39251,7 @@
       </c>
       <c r="Z287" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AA287" t="inlineStr">
@@ -39261,7 +39261,7 @@
       </c>
       <c r="AB287" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AC287" t="inlineStr">
@@ -39306,10 +39306,10 @@
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>122254412</v>
+        <v>122254616</v>
       </c>
       <c r="B288" t="n">
-        <v>56280</v>
+        <v>56285</v>
       </c>
       <c r="C288" t="inlineStr">
         <is>
@@ -39322,21 +39322,21 @@
         </is>
       </c>
       <c r="E288" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
@@ -39360,10 +39360,10 @@
         </is>
       </c>
       <c r="Q288" t="n">
-        <v>586424</v>
+        <v>586327</v>
       </c>
       <c r="R288" t="n">
-        <v>6311135</v>
+        <v>6311118</v>
       </c>
       <c r="S288" t="n">
         <v>5</v>
@@ -39395,7 +39395,7 @@
       </c>
       <c r="Z288" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>22:57</t>
         </is>
       </c>
       <c r="AA288" t="inlineStr">
@@ -39405,7 +39405,7 @@
       </c>
       <c r="AB288" t="inlineStr">
         <is>
-          <t>22:38</t>
+          <t>22:58</t>
         </is>
       </c>
       <c r="AC288" t="inlineStr">
@@ -39450,10 +39450,10 @@
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>122254392</v>
+        <v>122254634</v>
       </c>
       <c r="B289" t="n">
-        <v>56280</v>
+        <v>56285</v>
       </c>
       <c r="C289" t="inlineStr">
         <is>
@@ -39466,21 +39466,21 @@
         </is>
       </c>
       <c r="E289" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
@@ -39504,10 +39504,10 @@
         </is>
       </c>
       <c r="Q289" t="n">
-        <v>586384</v>
+        <v>586415</v>
       </c>
       <c r="R289" t="n">
-        <v>6311139</v>
+        <v>6311148</v>
       </c>
       <c r="S289" t="n">
         <v>5</v>
@@ -39539,17 +39539,17 @@
       </c>
       <c r="Z289" t="inlineStr">
         <is>
+          <t>22:44</t>
+        </is>
+      </c>
+      <c r="AA289" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AB289" t="inlineStr">
+        <is>
           <t>22:45</t>
-        </is>
-      </c>
-      <c r="AA289" t="inlineStr">
-        <is>
-          <t>2024-06-26</t>
-        </is>
-      </c>
-      <c r="AB289" t="inlineStr">
-        <is>
-          <t>22:46</t>
         </is>
       </c>
       <c r="AC289" t="inlineStr">
@@ -39594,10 +39594,10 @@
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>122254608</v>
+        <v>122254418</v>
       </c>
       <c r="B290" t="n">
-        <v>56285</v>
+        <v>56280</v>
       </c>
       <c r="C290" t="inlineStr">
         <is>
@@ -39610,21 +39610,21 @@
         </is>
       </c>
       <c r="E290" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
@@ -39648,10 +39648,10 @@
         </is>
       </c>
       <c r="Q290" t="n">
-        <v>586393</v>
+        <v>586467</v>
       </c>
       <c r="R290" t="n">
-        <v>6311147</v>
+        <v>6311178</v>
       </c>
       <c r="S290" t="n">
         <v>5</v>
@@ -39683,7 +39683,7 @@
       </c>
       <c r="Z290" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AA290" t="inlineStr">
@@ -39693,7 +39693,7 @@
       </c>
       <c r="AB290" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="AC290" t="inlineStr">
@@ -39738,10 +39738,10 @@
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>122254957</v>
+        <v>122254310</v>
       </c>
       <c r="B291" t="n">
-        <v>56273</v>
+        <v>56280</v>
       </c>
       <c r="C291" t="inlineStr">
         <is>
@@ -39754,21 +39754,21 @@
         </is>
       </c>
       <c r="E291" t="n">
-        <v>205992</v>
+        <v>100092</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
@@ -39792,10 +39792,10 @@
         </is>
       </c>
       <c r="Q291" t="n">
-        <v>586444</v>
+        <v>586452</v>
       </c>
       <c r="R291" t="n">
-        <v>6311160</v>
+        <v>6311156</v>
       </c>
       <c r="S291" t="n">
         <v>5</v>
@@ -39827,7 +39827,7 @@
       </c>
       <c r="Z291" t="inlineStr">
         <is>
-          <t>23:24</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA291" t="inlineStr">
@@ -39837,7 +39837,7 @@
       </c>
       <c r="AB291" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC291" t="inlineStr">
@@ -39882,10 +39882,10 @@
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>122254954</v>
+        <v>122254412</v>
       </c>
       <c r="B292" t="n">
-        <v>56273</v>
+        <v>56280</v>
       </c>
       <c r="C292" t="inlineStr">
         <is>
@@ -39898,21 +39898,21 @@
         </is>
       </c>
       <c r="E292" t="n">
-        <v>205992</v>
+        <v>100092</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
@@ -39936,10 +39936,10 @@
         </is>
       </c>
       <c r="Q292" t="n">
-        <v>586442</v>
+        <v>586424</v>
       </c>
       <c r="R292" t="n">
-        <v>6311152</v>
+        <v>6311135</v>
       </c>
       <c r="S292" t="n">
         <v>5</v>
@@ -39971,7 +39971,7 @@
       </c>
       <c r="Z292" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AA292" t="inlineStr">
@@ -39981,7 +39981,7 @@
       </c>
       <c r="AB292" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>22:38</t>
         </is>
       </c>
       <c r="AC292" t="inlineStr">
@@ -40026,10 +40026,10 @@
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>122254634</v>
+        <v>122254392</v>
       </c>
       <c r="B293" t="n">
-        <v>56285</v>
+        <v>56280</v>
       </c>
       <c r="C293" t="inlineStr">
         <is>
@@ -40042,21 +40042,21 @@
         </is>
       </c>
       <c r="E293" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
@@ -40080,10 +40080,10 @@
         </is>
       </c>
       <c r="Q293" t="n">
-        <v>586415</v>
+        <v>586384</v>
       </c>
       <c r="R293" t="n">
-        <v>6311148</v>
+        <v>6311139</v>
       </c>
       <c r="S293" t="n">
         <v>5</v>
@@ -40115,7 +40115,7 @@
       </c>
       <c r="Z293" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AA293" t="inlineStr">
@@ -40125,7 +40125,7 @@
       </c>
       <c r="AB293" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>22:46</t>
         </is>
       </c>
       <c r="AC293" t="inlineStr">
@@ -40170,7 +40170,7 @@
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>122254616</v>
+        <v>122254608</v>
       </c>
       <c r="B294" t="n">
         <v>56285</v>
@@ -40224,10 +40224,10 @@
         </is>
       </c>
       <c r="Q294" t="n">
-        <v>586327</v>
+        <v>586393</v>
       </c>
       <c r="R294" t="n">
-        <v>6311118</v>
+        <v>6311147</v>
       </c>
       <c r="S294" t="n">
         <v>5</v>
@@ -40259,7 +40259,7 @@
       </c>
       <c r="Z294" t="inlineStr">
         <is>
-          <t>22:57</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AA294" t="inlineStr">
@@ -40269,7 +40269,7 @@
       </c>
       <c r="AB294" t="inlineStr">
         <is>
-          <t>22:58</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AC294" t="inlineStr">
@@ -40314,7 +40314,7 @@
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>122254646</v>
+        <v>122254617</v>
       </c>
       <c r="B295" t="n">
         <v>56285</v>
@@ -40368,10 +40368,10 @@
         </is>
       </c>
       <c r="Q295" t="n">
-        <v>586422</v>
+        <v>586317</v>
       </c>
       <c r="R295" t="n">
-        <v>6311111</v>
+        <v>6311115</v>
       </c>
       <c r="S295" t="n">
         <v>5</v>
@@ -40403,7 +40403,7 @@
       </c>
       <c r="Z295" t="inlineStr">
         <is>
-          <t>22:36</t>
+          <t>22:57</t>
         </is>
       </c>
       <c r="AA295" t="inlineStr">
@@ -40413,7 +40413,7 @@
       </c>
       <c r="AB295" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>22:58</t>
         </is>
       </c>
       <c r="AC295" t="inlineStr">
@@ -40458,10 +40458,10 @@
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>122254607</v>
+        <v>122254475</v>
       </c>
       <c r="B296" t="n">
-        <v>56285</v>
+        <v>56266</v>
       </c>
       <c r="C296" t="inlineStr">
         <is>
@@ -40470,25 +40470,25 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E296" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
@@ -40512,10 +40512,10 @@
         </is>
       </c>
       <c r="Q296" t="n">
-        <v>586415</v>
+        <v>586420</v>
       </c>
       <c r="R296" t="n">
-        <v>6311149</v>
+        <v>6311166</v>
       </c>
       <c r="S296" t="n">
         <v>5</v>
@@ -40547,7 +40547,7 @@
       </c>
       <c r="Z296" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>23:23</t>
         </is>
       </c>
       <c r="AA296" t="inlineStr">
@@ -40557,7 +40557,7 @@
       </c>
       <c r="AB296" t="inlineStr">
         <is>
-          <t>23:03</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="AC296" t="inlineStr">
@@ -40602,10 +40602,10 @@
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>122254656</v>
+        <v>122254500</v>
       </c>
       <c r="B297" t="n">
-        <v>56285</v>
+        <v>56266</v>
       </c>
       <c r="C297" t="inlineStr">
         <is>
@@ -40614,25 +40614,25 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E297" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
@@ -40656,10 +40656,10 @@
         </is>
       </c>
       <c r="Q297" t="n">
-        <v>586483</v>
+        <v>586388</v>
       </c>
       <c r="R297" t="n">
-        <v>6311186</v>
+        <v>6311142</v>
       </c>
       <c r="S297" t="n">
         <v>5</v>
@@ -40691,7 +40691,7 @@
       </c>
       <c r="Z297" t="inlineStr">
         <is>
-          <t>22:31</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA297" t="inlineStr">
@@ -40701,7 +40701,7 @@
       </c>
       <c r="AB297" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AC297" t="inlineStr">
@@ -40890,7 +40890,7 @@
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>122254617</v>
+        <v>122254646</v>
       </c>
       <c r="B299" t="n">
         <v>56285</v>
@@ -40944,10 +40944,10 @@
         </is>
       </c>
       <c r="Q299" t="n">
-        <v>586317</v>
+        <v>586422</v>
       </c>
       <c r="R299" t="n">
-        <v>6311115</v>
+        <v>6311111</v>
       </c>
       <c r="S299" t="n">
         <v>5</v>
@@ -40979,7 +40979,7 @@
       </c>
       <c r="Z299" t="inlineStr">
         <is>
-          <t>22:57</t>
+          <t>22:36</t>
         </is>
       </c>
       <c r="AA299" t="inlineStr">
@@ -40989,7 +40989,7 @@
       </c>
       <c r="AB299" t="inlineStr">
         <is>
-          <t>22:58</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AC299" t="inlineStr">
@@ -41034,10 +41034,10 @@
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>122254475</v>
+        <v>122254607</v>
       </c>
       <c r="B300" t="n">
-        <v>56266</v>
+        <v>56285</v>
       </c>
       <c r="C300" t="inlineStr">
         <is>
@@ -41046,25 +41046,25 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E300" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
@@ -41088,10 +41088,10 @@
         </is>
       </c>
       <c r="Q300" t="n">
-        <v>586420</v>
+        <v>586415</v>
       </c>
       <c r="R300" t="n">
-        <v>6311166</v>
+        <v>6311149</v>
       </c>
       <c r="S300" t="n">
         <v>5</v>
@@ -41123,7 +41123,7 @@
       </c>
       <c r="Z300" t="inlineStr">
         <is>
-          <t>23:23</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AA300" t="inlineStr">
@@ -41133,7 +41133,7 @@
       </c>
       <c r="AB300" t="inlineStr">
         <is>
-          <t>23:24</t>
+          <t>23:03</t>
         </is>
       </c>
       <c r="AC300" t="inlineStr">
@@ -41178,10 +41178,10 @@
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>122254500</v>
+        <v>122254656</v>
       </c>
       <c r="B301" t="n">
-        <v>56266</v>
+        <v>56285</v>
       </c>
       <c r="C301" t="inlineStr">
         <is>
@@ -41190,25 +41190,25 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E301" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
@@ -41232,10 +41232,10 @@
         </is>
       </c>
       <c r="Q301" t="n">
-        <v>586388</v>
+        <v>586483</v>
       </c>
       <c r="R301" t="n">
-        <v>6311142</v>
+        <v>6311186</v>
       </c>
       <c r="S301" t="n">
         <v>5</v>
@@ -41267,7 +41267,7 @@
       </c>
       <c r="Z301" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:31</t>
         </is>
       </c>
       <c r="AA301" t="inlineStr">
@@ -41277,7 +41277,7 @@
       </c>
       <c r="AB301" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AC301" t="inlineStr">
@@ -41754,10 +41754,10 @@
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>122254472</v>
+        <v>122254658</v>
       </c>
       <c r="B305" t="n">
-        <v>56266</v>
+        <v>56285</v>
       </c>
       <c r="C305" t="inlineStr">
         <is>
@@ -41766,25 +41766,25 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E305" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
@@ -41808,10 +41808,10 @@
         </is>
       </c>
       <c r="Q305" t="n">
-        <v>586455</v>
+        <v>586491</v>
       </c>
       <c r="R305" t="n">
-        <v>6311159</v>
+        <v>6311181</v>
       </c>
       <c r="S305" t="n">
         <v>5</v>
@@ -41843,7 +41843,7 @@
       </c>
       <c r="Z305" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>22:31</t>
         </is>
       </c>
       <c r="AA305" t="inlineStr">
@@ -41853,7 +41853,7 @@
       </c>
       <c r="AB305" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AC305" t="inlineStr">
@@ -41898,7 +41898,7 @@
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>122254496</v>
+        <v>122254513</v>
       </c>
       <c r="B306" t="n">
         <v>56266</v>
@@ -41952,7 +41952,7 @@
         </is>
       </c>
       <c r="Q306" t="n">
-        <v>586415</v>
+        <v>586396</v>
       </c>
       <c r="R306" t="n">
         <v>6311146</v>
@@ -41987,7 +41987,7 @@
       </c>
       <c r="Z306" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AA306" t="inlineStr">
@@ -41997,7 +41997,7 @@
       </c>
       <c r="AB306" t="inlineStr">
         <is>
-          <t>23:03</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AC306" t="inlineStr">
@@ -42042,10 +42042,10 @@
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>122254658</v>
+        <v>122254472</v>
       </c>
       <c r="B307" t="n">
-        <v>56285</v>
+        <v>56266</v>
       </c>
       <c r="C307" t="inlineStr">
         <is>
@@ -42054,25 +42054,25 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E307" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
@@ -42096,10 +42096,10 @@
         </is>
       </c>
       <c r="Q307" t="n">
-        <v>586491</v>
+        <v>586455</v>
       </c>
       <c r="R307" t="n">
-        <v>6311181</v>
+        <v>6311159</v>
       </c>
       <c r="S307" t="n">
         <v>5</v>
@@ -42131,7 +42131,7 @@
       </c>
       <c r="Z307" t="inlineStr">
         <is>
-          <t>22:31</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AA307" t="inlineStr">
@@ -42141,7 +42141,7 @@
       </c>
       <c r="AB307" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AC307" t="inlineStr">
@@ -42186,7 +42186,7 @@
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>122254513</v>
+        <v>122254496</v>
       </c>
       <c r="B308" t="n">
         <v>56266</v>
@@ -42240,7 +42240,7 @@
         </is>
       </c>
       <c r="Q308" t="n">
-        <v>586396</v>
+        <v>586415</v>
       </c>
       <c r="R308" t="n">
         <v>6311146</v>
@@ -42275,7 +42275,7 @@
       </c>
       <c r="Z308" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AA308" t="inlineStr">
@@ -42285,7 +42285,7 @@
       </c>
       <c r="AB308" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>23:03</t>
         </is>
       </c>
       <c r="AC308" t="inlineStr">
@@ -46506,10 +46506,10 @@
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>122254514</v>
+        <v>122254588</v>
       </c>
       <c r="B338" t="n">
-        <v>56266</v>
+        <v>56285</v>
       </c>
       <c r="C338" t="inlineStr">
         <is>
@@ -46518,25 +46518,25 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E338" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
@@ -46560,10 +46560,10 @@
         </is>
       </c>
       <c r="Q338" t="n">
-        <v>586408</v>
+        <v>586415</v>
       </c>
       <c r="R338" t="n">
-        <v>6311124</v>
+        <v>6311196</v>
       </c>
       <c r="S338" t="n">
         <v>5</v>
@@ -46595,7 +46595,7 @@
       </c>
       <c r="Z338" t="inlineStr">
         <is>
-          <t>22:43</t>
+          <t>23:22</t>
         </is>
       </c>
       <c r="AA338" t="inlineStr">
@@ -46605,7 +46605,7 @@
       </c>
       <c r="AB338" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>23:23</t>
         </is>
       </c>
       <c r="AC338" t="inlineStr">
@@ -46650,10 +46650,10 @@
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>122254588</v>
+        <v>122254511</v>
       </c>
       <c r="B339" t="n">
-        <v>56285</v>
+        <v>56266</v>
       </c>
       <c r="C339" t="inlineStr">
         <is>
@@ -46662,25 +46662,25 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E339" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I339" t="inlineStr">
@@ -46704,10 +46704,10 @@
         </is>
       </c>
       <c r="Q339" t="n">
-        <v>586415</v>
+        <v>586374</v>
       </c>
       <c r="R339" t="n">
-        <v>6311196</v>
+        <v>6311139</v>
       </c>
       <c r="S339" t="n">
         <v>5</v>
@@ -46739,7 +46739,7 @@
       </c>
       <c r="Z339" t="inlineStr">
         <is>
-          <t>23:22</t>
+          <t>22:46</t>
         </is>
       </c>
       <c r="AA339" t="inlineStr">
@@ -46749,7 +46749,7 @@
       </c>
       <c r="AB339" t="inlineStr">
         <is>
-          <t>23:23</t>
+          <t>22:47</t>
         </is>
       </c>
       <c r="AC339" t="inlineStr">
@@ -46794,10 +46794,10 @@
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>122254511</v>
+        <v>122254342</v>
       </c>
       <c r="B340" t="n">
-        <v>56266</v>
+        <v>56280</v>
       </c>
       <c r="C340" t="inlineStr">
         <is>
@@ -46806,25 +46806,25 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E340" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
@@ -46848,10 +46848,10 @@
         </is>
       </c>
       <c r="Q340" t="n">
-        <v>586374</v>
+        <v>586389</v>
       </c>
       <c r="R340" t="n">
-        <v>6311139</v>
+        <v>6311142</v>
       </c>
       <c r="S340" t="n">
         <v>5</v>
@@ -46883,7 +46883,7 @@
       </c>
       <c r="Z340" t="inlineStr">
         <is>
-          <t>22:46</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA340" t="inlineStr">
@@ -46893,7 +46893,7 @@
       </c>
       <c r="AB340" t="inlineStr">
         <is>
-          <t>22:47</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AC340" t="inlineStr">
@@ -46938,7 +46938,7 @@
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>122254342</v>
+        <v>122254421</v>
       </c>
       <c r="B341" t="n">
         <v>56280</v>
@@ -46992,10 +46992,10 @@
         </is>
       </c>
       <c r="Q341" t="n">
-        <v>586389</v>
+        <v>586468</v>
       </c>
       <c r="R341" t="n">
-        <v>6311142</v>
+        <v>6311181</v>
       </c>
       <c r="S341" t="n">
         <v>5</v>
@@ -47027,7 +47027,7 @@
       </c>
       <c r="Z341" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AA341" t="inlineStr">
@@ -47037,7 +47037,7 @@
       </c>
       <c r="AB341" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="AC341" t="inlineStr">
@@ -47082,10 +47082,10 @@
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>122254421</v>
+        <v>122254514</v>
       </c>
       <c r="B342" t="n">
-        <v>56280</v>
+        <v>56266</v>
       </c>
       <c r="C342" t="inlineStr">
         <is>
@@ -47094,25 +47094,25 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E342" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
@@ -47136,10 +47136,10 @@
         </is>
       </c>
       <c r="Q342" t="n">
-        <v>586468</v>
+        <v>586408</v>
       </c>
       <c r="R342" t="n">
-        <v>6311181</v>
+        <v>6311124</v>
       </c>
       <c r="S342" t="n">
         <v>5</v>
@@ -47171,7 +47171,7 @@
       </c>
       <c r="Z342" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>22:43</t>
         </is>
       </c>
       <c r="AA342" t="inlineStr">
@@ -47181,7 +47181,7 @@
       </c>
       <c r="AB342" t="inlineStr">
         <is>
-          <t>22:33</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AC342" t="inlineStr">
@@ -49242,10 +49242,10 @@
     </row>
     <row r="357">
       <c r="A357" t="n">
-        <v>122254316</v>
+        <v>122254635</v>
       </c>
       <c r="B357" t="n">
-        <v>56280</v>
+        <v>56285</v>
       </c>
       <c r="C357" t="inlineStr">
         <is>
@@ -49258,21 +49258,21 @@
         </is>
       </c>
       <c r="E357" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I357" t="inlineStr">
@@ -49296,10 +49296,10 @@
         </is>
       </c>
       <c r="Q357" t="n">
-        <v>586423</v>
+        <v>586417</v>
       </c>
       <c r="R357" t="n">
-        <v>6311166</v>
+        <v>6311145</v>
       </c>
       <c r="S357" t="n">
         <v>5</v>
@@ -49331,7 +49331,7 @@
       </c>
       <c r="Z357" t="inlineStr">
         <is>
-          <t>23:23</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AA357" t="inlineStr">
@@ -49341,7 +49341,7 @@
       </c>
       <c r="AB357" t="inlineStr">
         <is>
-          <t>23:24</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AC357" t="inlineStr">
@@ -49530,10 +49530,10 @@
     </row>
     <row r="359">
       <c r="A359" t="n">
-        <v>122254963</v>
+        <v>122254316</v>
       </c>
       <c r="B359" t="n">
-        <v>56273</v>
+        <v>56280</v>
       </c>
       <c r="C359" t="inlineStr">
         <is>
@@ -49546,21 +49546,21 @@
         </is>
       </c>
       <c r="E359" t="n">
-        <v>205992</v>
+        <v>100092</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I359" t="inlineStr">
@@ -49584,10 +49584,10 @@
         </is>
       </c>
       <c r="Q359" t="n">
-        <v>586374</v>
+        <v>586423</v>
       </c>
       <c r="R359" t="n">
-        <v>6311140</v>
+        <v>6311166</v>
       </c>
       <c r="S359" t="n">
         <v>5</v>
@@ -49619,7 +49619,7 @@
       </c>
       <c r="Z359" t="inlineStr">
         <is>
-          <t>22:46</t>
+          <t>23:23</t>
         </is>
       </c>
       <c r="AA359" t="inlineStr">
@@ -49629,7 +49629,7 @@
       </c>
       <c r="AB359" t="inlineStr">
         <is>
-          <t>22:47</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="AC359" t="inlineStr">
@@ -49674,7 +49674,7 @@
     </row>
     <row r="360">
       <c r="A360" t="n">
-        <v>122254951</v>
+        <v>122254963</v>
       </c>
       <c r="B360" t="n">
         <v>56273</v>
@@ -49728,10 +49728,10 @@
         </is>
       </c>
       <c r="Q360" t="n">
-        <v>586459</v>
+        <v>586374</v>
       </c>
       <c r="R360" t="n">
-        <v>6311154</v>
+        <v>6311140</v>
       </c>
       <c r="S360" t="n">
         <v>5</v>
@@ -49763,7 +49763,7 @@
       </c>
       <c r="Z360" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>22:46</t>
         </is>
       </c>
       <c r="AA360" t="inlineStr">
@@ -49773,7 +49773,7 @@
       </c>
       <c r="AB360" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>22:47</t>
         </is>
       </c>
       <c r="AC360" t="inlineStr">
@@ -49818,10 +49818,10 @@
     </row>
     <row r="361">
       <c r="A361" t="n">
-        <v>122254635</v>
+        <v>122254951</v>
       </c>
       <c r="B361" t="n">
-        <v>56285</v>
+        <v>56273</v>
       </c>
       <c r="C361" t="inlineStr">
         <is>
@@ -49834,21 +49834,21 @@
         </is>
       </c>
       <c r="E361" t="n">
-        <v>205995</v>
+        <v>205992</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I361" t="inlineStr">
@@ -49872,10 +49872,10 @@
         </is>
       </c>
       <c r="Q361" t="n">
-        <v>586417</v>
+        <v>586459</v>
       </c>
       <c r="R361" t="n">
-        <v>6311145</v>
+        <v>6311154</v>
       </c>
       <c r="S361" t="n">
         <v>5</v>
@@ -49907,7 +49907,7 @@
       </c>
       <c r="Z361" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AA361" t="inlineStr">
@@ -49917,7 +49917,7 @@
       </c>
       <c r="AB361" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AC361" t="inlineStr">
@@ -49962,10 +49962,10 @@
     </row>
     <row r="362">
       <c r="A362" t="n">
-        <v>122254626</v>
+        <v>122254845</v>
       </c>
       <c r="B362" t="n">
-        <v>56285</v>
+        <v>56283</v>
       </c>
       <c r="C362" t="inlineStr">
         <is>
@@ -49978,21 +49978,21 @@
         </is>
       </c>
       <c r="E362" t="n">
-        <v>205995</v>
+        <v>100111</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I362" t="inlineStr">
@@ -50016,10 +50016,10 @@
         </is>
       </c>
       <c r="Q362" t="n">
-        <v>586313</v>
+        <v>586370</v>
       </c>
       <c r="R362" t="n">
-        <v>6311124</v>
+        <v>6311139</v>
       </c>
       <c r="S362" t="n">
         <v>5</v>
@@ -50051,7 +50051,7 @@
       </c>
       <c r="Z362" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>22:59</t>
         </is>
       </c>
       <c r="AA362" t="inlineStr">
@@ -50061,7 +50061,7 @@
       </c>
       <c r="AB362" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AC362" t="inlineStr">
@@ -50106,10 +50106,10 @@
     </row>
     <row r="363">
       <c r="A363" t="n">
-        <v>122254845</v>
+        <v>122254308</v>
       </c>
       <c r="B363" t="n">
-        <v>56283</v>
+        <v>56280</v>
       </c>
       <c r="C363" t="inlineStr">
         <is>
@@ -50122,21 +50122,21 @@
         </is>
       </c>
       <c r="E363" t="n">
-        <v>100111</v>
+        <v>100092</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I363" t="inlineStr">
@@ -50160,10 +50160,10 @@
         </is>
       </c>
       <c r="Q363" t="n">
-        <v>586370</v>
+        <v>586455</v>
       </c>
       <c r="R363" t="n">
-        <v>6311139</v>
+        <v>6311159</v>
       </c>
       <c r="S363" t="n">
         <v>5</v>
@@ -50195,7 +50195,7 @@
       </c>
       <c r="Z363" t="inlineStr">
         <is>
-          <t>22:59</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AA363" t="inlineStr">
@@ -50205,7 +50205,7 @@
       </c>
       <c r="AB363" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AC363" t="inlineStr">
@@ -50250,7 +50250,7 @@
     </row>
     <row r="364">
       <c r="A364" t="n">
-        <v>122254308</v>
+        <v>122254309</v>
       </c>
       <c r="B364" t="n">
         <v>56280</v>
@@ -50304,10 +50304,10 @@
         </is>
       </c>
       <c r="Q364" t="n">
-        <v>586455</v>
+        <v>586456</v>
       </c>
       <c r="R364" t="n">
-        <v>6311159</v>
+        <v>6311158</v>
       </c>
       <c r="S364" t="n">
         <v>5</v>
@@ -50394,7 +50394,7 @@
     </row>
     <row r="365">
       <c r="A365" t="n">
-        <v>122254309</v>
+        <v>122254306</v>
       </c>
       <c r="B365" t="n">
         <v>56280</v>
@@ -50448,10 +50448,10 @@
         </is>
       </c>
       <c r="Q365" t="n">
-        <v>586456</v>
+        <v>586473</v>
       </c>
       <c r="R365" t="n">
-        <v>6311158</v>
+        <v>6311192</v>
       </c>
       <c r="S365" t="n">
         <v>5</v>
@@ -50483,7 +50483,7 @@
       </c>
       <c r="Z365" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AA365" t="inlineStr">
@@ -50493,7 +50493,7 @@
       </c>
       <c r="AB365" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AC365" t="inlineStr">
@@ -50538,10 +50538,10 @@
     </row>
     <row r="366">
       <c r="A366" t="n">
-        <v>122254306</v>
+        <v>122254835</v>
       </c>
       <c r="B366" t="n">
-        <v>56280</v>
+        <v>56283</v>
       </c>
       <c r="C366" t="inlineStr">
         <is>
@@ -50554,21 +50554,21 @@
         </is>
       </c>
       <c r="E366" t="n">
-        <v>100092</v>
+        <v>100111</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I366" t="inlineStr">
@@ -50682,10 +50682,10 @@
     </row>
     <row r="367">
       <c r="A367" t="n">
-        <v>122254835</v>
+        <v>122254626</v>
       </c>
       <c r="B367" t="n">
-        <v>56283</v>
+        <v>56285</v>
       </c>
       <c r="C367" t="inlineStr">
         <is>
@@ -50698,21 +50698,21 @@
         </is>
       </c>
       <c r="E367" t="n">
-        <v>100111</v>
+        <v>205995</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I367" t="inlineStr">
@@ -50736,10 +50736,10 @@
         </is>
       </c>
       <c r="Q367" t="n">
-        <v>586473</v>
+        <v>586313</v>
       </c>
       <c r="R367" t="n">
-        <v>6311192</v>
+        <v>6311124</v>
       </c>
       <c r="S367" t="n">
         <v>5</v>
@@ -50771,7 +50771,7 @@
       </c>
       <c r="Z367" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AA367" t="inlineStr">
@@ -50781,7 +50781,7 @@
       </c>
       <c r="AB367" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AC367" t="inlineStr">
@@ -53418,10 +53418,10 @@
     </row>
     <row r="386">
       <c r="A386" t="n">
-        <v>122254952</v>
+        <v>122254648</v>
       </c>
       <c r="B386" t="n">
-        <v>56273</v>
+        <v>56285</v>
       </c>
       <c r="C386" t="inlineStr">
         <is>
@@ -53434,21 +53434,21 @@
         </is>
       </c>
       <c r="E386" t="n">
-        <v>205992</v>
+        <v>205995</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H386" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I386" t="inlineStr">
@@ -53472,10 +53472,10 @@
         </is>
       </c>
       <c r="Q386" t="n">
-        <v>586455</v>
+        <v>586418</v>
       </c>
       <c r="R386" t="n">
-        <v>6311156</v>
+        <v>6311107</v>
       </c>
       <c r="S386" t="n">
         <v>5</v>
@@ -53507,7 +53507,7 @@
       </c>
       <c r="Z386" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>22:36</t>
         </is>
       </c>
       <c r="AA386" t="inlineStr">
@@ -53517,7 +53517,7 @@
       </c>
       <c r="AB386" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AC386" t="inlineStr">
@@ -53562,7 +53562,7 @@
     </row>
     <row r="387">
       <c r="A387" t="n">
-        <v>122254648</v>
+        <v>122254650</v>
       </c>
       <c r="B387" t="n">
         <v>56285</v>
@@ -53616,10 +53616,10 @@
         </is>
       </c>
       <c r="Q387" t="n">
-        <v>586418</v>
+        <v>586422</v>
       </c>
       <c r="R387" t="n">
-        <v>6311107</v>
+        <v>6311105</v>
       </c>
       <c r="S387" t="n">
         <v>5</v>
@@ -53651,17 +53651,17 @@
       </c>
       <c r="Z387" t="inlineStr">
         <is>
+          <t>22:35</t>
+        </is>
+      </c>
+      <c r="AA387" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AB387" t="inlineStr">
+        <is>
           <t>22:36</t>
-        </is>
-      </c>
-      <c r="AA387" t="inlineStr">
-        <is>
-          <t>2024-06-26</t>
-        </is>
-      </c>
-      <c r="AB387" t="inlineStr">
-        <is>
-          <t>22:37</t>
         </is>
       </c>
       <c r="AC387" t="inlineStr">
@@ -53706,7 +53706,7 @@
     </row>
     <row r="388">
       <c r="A388" t="n">
-        <v>122254650</v>
+        <v>122254610</v>
       </c>
       <c r="B388" t="n">
         <v>56285</v>
@@ -53760,10 +53760,10 @@
         </is>
       </c>
       <c r="Q388" t="n">
-        <v>586422</v>
+        <v>586389</v>
       </c>
       <c r="R388" t="n">
-        <v>6311105</v>
+        <v>6311141</v>
       </c>
       <c r="S388" t="n">
         <v>5</v>
@@ -53795,7 +53795,7 @@
       </c>
       <c r="Z388" t="inlineStr">
         <is>
-          <t>22:35</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA388" t="inlineStr">
@@ -53805,7 +53805,7 @@
       </c>
       <c r="AB388" t="inlineStr">
         <is>
-          <t>22:36</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AC388" t="inlineStr">
@@ -53850,7 +53850,7 @@
     </row>
     <row r="389">
       <c r="A389" t="n">
-        <v>122254610</v>
+        <v>122254612</v>
       </c>
       <c r="B389" t="n">
         <v>56285</v>
@@ -53904,10 +53904,10 @@
         </is>
       </c>
       <c r="Q389" t="n">
-        <v>586389</v>
+        <v>586371</v>
       </c>
       <c r="R389" t="n">
-        <v>6311141</v>
+        <v>6311135</v>
       </c>
       <c r="S389" t="n">
         <v>5</v>
@@ -53939,17 +53939,17 @@
       </c>
       <c r="Z389" t="inlineStr">
         <is>
+          <t>22:59</t>
+        </is>
+      </c>
+      <c r="AA389" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AB389" t="inlineStr">
+        <is>
           <t>23:00</t>
-        </is>
-      </c>
-      <c r="AA389" t="inlineStr">
-        <is>
-          <t>2024-06-26</t>
-        </is>
-      </c>
-      <c r="AB389" t="inlineStr">
-        <is>
-          <t>23:01</t>
         </is>
       </c>
       <c r="AC389" t="inlineStr">
@@ -53994,10 +53994,10 @@
     </row>
     <row r="390">
       <c r="A390" t="n">
-        <v>122254612</v>
+        <v>122254952</v>
       </c>
       <c r="B390" t="n">
-        <v>56285</v>
+        <v>56273</v>
       </c>
       <c r="C390" t="inlineStr">
         <is>
@@ -54010,21 +54010,21 @@
         </is>
       </c>
       <c r="E390" t="n">
-        <v>205995</v>
+        <v>205992</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I390" t="inlineStr">
@@ -54048,10 +54048,10 @@
         </is>
       </c>
       <c r="Q390" t="n">
-        <v>586371</v>
+        <v>586455</v>
       </c>
       <c r="R390" t="n">
-        <v>6311135</v>
+        <v>6311156</v>
       </c>
       <c r="S390" t="n">
         <v>5</v>
@@ -54083,7 +54083,7 @@
       </c>
       <c r="Z390" t="inlineStr">
         <is>
-          <t>22:59</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AA390" t="inlineStr">
@@ -54093,7 +54093,7 @@
       </c>
       <c r="AB390" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AC390" t="inlineStr">

--- a/artfynd/A 36363-2024 artfynd.xlsx
+++ b/artfynd/A 36363-2024 artfynd.xlsx
@@ -37002,10 +37002,10 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>122254844</v>
+        <v>122254837</v>
       </c>
       <c r="B272" t="n">
-        <v>56283</v>
+        <v>56288</v>
       </c>
       <c r="C272" t="inlineStr">
         <is>
@@ -37056,10 +37056,10 @@
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>586387</v>
+        <v>586448</v>
       </c>
       <c r="R272" t="n">
-        <v>6311141</v>
+        <v>6311154</v>
       </c>
       <c r="S272" t="n">
         <v>5</v>
@@ -37091,7 +37091,7 @@
       </c>
       <c r="Z272" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA272" t="inlineStr">
@@ -37101,7 +37101,7 @@
       </c>
       <c r="AB272" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC272" t="inlineStr">
@@ -37146,10 +37146,10 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>122254837</v>
+        <v>122254420</v>
       </c>
       <c r="B273" t="n">
-        <v>56283</v>
+        <v>56285</v>
       </c>
       <c r="C273" t="inlineStr">
         <is>
@@ -37162,21 +37162,21 @@
         </is>
       </c>
       <c r="E273" t="n">
-        <v>100111</v>
+        <v>100092</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
@@ -37200,10 +37200,10 @@
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>586448</v>
+        <v>586467</v>
       </c>
       <c r="R273" t="n">
-        <v>6311154</v>
+        <v>6311178</v>
       </c>
       <c r="S273" t="n">
         <v>5</v>
@@ -37235,7 +37235,7 @@
       </c>
       <c r="Z273" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AA273" t="inlineStr">
@@ -37245,7 +37245,7 @@
       </c>
       <c r="AB273" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="AC273" t="inlineStr">
@@ -37290,10 +37290,10 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>122254394</v>
+        <v>122254413</v>
       </c>
       <c r="B274" t="n">
-        <v>56280</v>
+        <v>56285</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>
@@ -37344,10 +37344,10 @@
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>586419</v>
+        <v>586423</v>
       </c>
       <c r="R274" t="n">
-        <v>6311142</v>
+        <v>6311137</v>
       </c>
       <c r="S274" t="n">
         <v>5</v>
@@ -37379,7 +37379,7 @@
       </c>
       <c r="Z274" t="inlineStr">
         <is>
-          <t>22:43</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AA274" t="inlineStr">
@@ -37389,7 +37389,7 @@
       </c>
       <c r="AB274" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>22:38</t>
         </is>
       </c>
       <c r="AC274" t="inlineStr">
@@ -37434,10 +37434,10 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>122254373</v>
+        <v>122254395</v>
       </c>
       <c r="B275" t="n">
-        <v>56280</v>
+        <v>56285</v>
       </c>
       <c r="C275" t="inlineStr">
         <is>
@@ -37488,10 +37488,10 @@
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>586307</v>
+        <v>586408</v>
       </c>
       <c r="R275" t="n">
-        <v>6311133</v>
+        <v>6311124</v>
       </c>
       <c r="S275" t="n">
         <v>5</v>
@@ -37523,7 +37523,7 @@
       </c>
       <c r="Z275" t="inlineStr">
         <is>
-          <t>22:49</t>
+          <t>22:43</t>
         </is>
       </c>
       <c r="AA275" t="inlineStr">
@@ -37533,7 +37533,7 @@
       </c>
       <c r="AB275" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AC275" t="inlineStr">
@@ -37578,7 +37578,7 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>122254643</v>
+        <v>122254369</v>
       </c>
       <c r="B276" t="n">
         <v>56285</v>
@@ -37594,21 +37594,21 @@
         </is>
       </c>
       <c r="E276" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
@@ -37632,10 +37632,10 @@
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>586424</v>
+        <v>586300</v>
       </c>
       <c r="R276" t="n">
-        <v>6311135</v>
+        <v>6311112</v>
       </c>
       <c r="S276" t="n">
         <v>5</v>
@@ -37667,7 +37667,7 @@
       </c>
       <c r="Z276" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AA276" t="inlineStr">
@@ -37677,7 +37677,7 @@
       </c>
       <c r="AB276" t="inlineStr">
         <is>
-          <t>22:38</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AC276" t="inlineStr">
@@ -37722,7 +37722,7 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>122254659</v>
+        <v>122254371</v>
       </c>
       <c r="B277" t="n">
         <v>56285</v>
@@ -37738,21 +37738,21 @@
         </is>
       </c>
       <c r="E277" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
@@ -37776,10 +37776,10 @@
         </is>
       </c>
       <c r="Q277" t="n">
-        <v>586489</v>
+        <v>586308</v>
       </c>
       <c r="R277" t="n">
-        <v>6311181</v>
+        <v>6311132</v>
       </c>
       <c r="S277" t="n">
         <v>5</v>
@@ -37811,7 +37811,7 @@
       </c>
       <c r="Z277" t="inlineStr">
         <is>
-          <t>22:31</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AA277" t="inlineStr">
@@ -37821,7 +37821,7 @@
       </c>
       <c r="AB277" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AC277" t="inlineStr">
@@ -37866,10 +37866,10 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>122254625</v>
+        <v>122254612</v>
       </c>
       <c r="B278" t="n">
-        <v>56285</v>
+        <v>56290</v>
       </c>
       <c r="C278" t="inlineStr">
         <is>
@@ -37920,10 +37920,10 @@
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>586309</v>
+        <v>586371</v>
       </c>
       <c r="R278" t="n">
-        <v>6311119</v>
+        <v>6311135</v>
       </c>
       <c r="S278" t="n">
         <v>5</v>
@@ -37955,7 +37955,7 @@
       </c>
       <c r="Z278" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>22:59</t>
         </is>
       </c>
       <c r="AA278" t="inlineStr">
@@ -37965,7 +37965,7 @@
       </c>
       <c r="AB278" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AC278" t="inlineStr">
@@ -38010,10 +38010,10 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>122254585</v>
+        <v>122254643</v>
       </c>
       <c r="B279" t="n">
-        <v>56285</v>
+        <v>56290</v>
       </c>
       <c r="C279" t="inlineStr">
         <is>
@@ -38064,10 +38064,10 @@
         </is>
       </c>
       <c r="Q279" t="n">
-        <v>586455</v>
+        <v>586424</v>
       </c>
       <c r="R279" t="n">
-        <v>6311156</v>
+        <v>6311135</v>
       </c>
       <c r="S279" t="n">
         <v>5</v>
@@ -38099,7 +38099,7 @@
       </c>
       <c r="Z279" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AA279" t="inlineStr">
@@ -38109,7 +38109,7 @@
       </c>
       <c r="AB279" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>22:38</t>
         </is>
       </c>
       <c r="AC279" t="inlineStr">
@@ -38154,10 +38154,10 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>122254315</v>
+        <v>122254342</v>
       </c>
       <c r="B280" t="n">
-        <v>56280</v>
+        <v>56285</v>
       </c>
       <c r="C280" t="inlineStr">
         <is>
@@ -38208,10 +38208,10 @@
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>586441</v>
+        <v>586389</v>
       </c>
       <c r="R280" t="n">
-        <v>6311155</v>
+        <v>6311142</v>
       </c>
       <c r="S280" t="n">
         <v>5</v>
@@ -38243,7 +38243,7 @@
       </c>
       <c r="Z280" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA280" t="inlineStr">
@@ -38253,7 +38253,7 @@
       </c>
       <c r="AB280" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AC280" t="inlineStr">
@@ -38298,10 +38298,10 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>122254964</v>
+        <v>122254836</v>
       </c>
       <c r="B281" t="n">
-        <v>56273</v>
+        <v>56288</v>
       </c>
       <c r="C281" t="inlineStr">
         <is>
@@ -38314,21 +38314,21 @@
         </is>
       </c>
       <c r="E281" t="n">
-        <v>205992</v>
+        <v>100111</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
@@ -38352,10 +38352,10 @@
         </is>
       </c>
       <c r="Q281" t="n">
-        <v>586430</v>
+        <v>586474</v>
       </c>
       <c r="R281" t="n">
-        <v>6311142</v>
+        <v>6311176</v>
       </c>
       <c r="S281" t="n">
         <v>5</v>
@@ -38387,7 +38387,7 @@
       </c>
       <c r="Z281" t="inlineStr">
         <is>
-          <t>22:33</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AA281" t="inlineStr">
@@ -38397,7 +38397,7 @@
       </c>
       <c r="AB281" t="inlineStr">
         <is>
-          <t>22:34</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AC281" t="inlineStr">
@@ -38442,10 +38442,10 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>122254586</v>
+        <v>122254951</v>
       </c>
       <c r="B282" t="n">
-        <v>56285</v>
+        <v>56278</v>
       </c>
       <c r="C282" t="inlineStr">
         <is>
@@ -38458,21 +38458,21 @@
         </is>
       </c>
       <c r="E282" t="n">
-        <v>205995</v>
+        <v>205992</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
@@ -38496,10 +38496,10 @@
         </is>
       </c>
       <c r="Q282" t="n">
-        <v>586446</v>
+        <v>586459</v>
       </c>
       <c r="R282" t="n">
-        <v>6311158</v>
+        <v>6311154</v>
       </c>
       <c r="S282" t="n">
         <v>5</v>
@@ -38531,7 +38531,7 @@
       </c>
       <c r="Z282" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AA282" t="inlineStr">
@@ -38541,7 +38541,7 @@
       </c>
       <c r="AB282" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AC282" t="inlineStr">
@@ -38586,10 +38586,10 @@
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>122254499</v>
+        <v>122254952</v>
       </c>
       <c r="B283" t="n">
-        <v>56266</v>
+        <v>56278</v>
       </c>
       <c r="C283" t="inlineStr">
         <is>
@@ -38598,25 +38598,25 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E283" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
@@ -38640,10 +38640,10 @@
         </is>
       </c>
       <c r="Q283" t="n">
-        <v>586392</v>
+        <v>586455</v>
       </c>
       <c r="R283" t="n">
-        <v>6311147</v>
+        <v>6311156</v>
       </c>
       <c r="S283" t="n">
         <v>5</v>
@@ -38675,7 +38675,7 @@
       </c>
       <c r="Z283" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AA283" t="inlineStr">
@@ -38685,7 +38685,7 @@
       </c>
       <c r="AB283" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AC283" t="inlineStr">
@@ -38730,10 +38730,10 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>122254649</v>
+        <v>122254956</v>
       </c>
       <c r="B284" t="n">
-        <v>56285</v>
+        <v>56278</v>
       </c>
       <c r="C284" t="inlineStr">
         <is>
@@ -38746,21 +38746,21 @@
         </is>
       </c>
       <c r="E284" t="n">
-        <v>205995</v>
+        <v>205992</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
@@ -38784,10 +38784,10 @@
         </is>
       </c>
       <c r="Q284" t="n">
-        <v>586422</v>
+        <v>586441</v>
       </c>
       <c r="R284" t="n">
-        <v>6311100</v>
+        <v>6311152</v>
       </c>
       <c r="S284" t="n">
         <v>5</v>
@@ -38819,7 +38819,7 @@
       </c>
       <c r="Z284" t="inlineStr">
         <is>
-          <t>22:35</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AA284" t="inlineStr">
@@ -38829,7 +38829,7 @@
       </c>
       <c r="AB284" t="inlineStr">
         <is>
-          <t>22:36</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AC284" t="inlineStr">
@@ -38874,10 +38874,10 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>122254637</v>
+        <v>122254588</v>
       </c>
       <c r="B285" t="n">
-        <v>56285</v>
+        <v>56290</v>
       </c>
       <c r="C285" t="inlineStr">
         <is>
@@ -38928,10 +38928,10 @@
         </is>
       </c>
       <c r="Q285" t="n">
-        <v>586408</v>
+        <v>586415</v>
       </c>
       <c r="R285" t="n">
-        <v>6311124</v>
+        <v>6311196</v>
       </c>
       <c r="S285" t="n">
         <v>5</v>
@@ -38963,7 +38963,7 @@
       </c>
       <c r="Z285" t="inlineStr">
         <is>
-          <t>22:43</t>
+          <t>23:22</t>
         </is>
       </c>
       <c r="AA285" t="inlineStr">
@@ -38973,7 +38973,7 @@
       </c>
       <c r="AB285" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>23:23</t>
         </is>
       </c>
       <c r="AC285" t="inlineStr">
@@ -39018,10 +39018,10 @@
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>122254957</v>
+        <v>122254608</v>
       </c>
       <c r="B286" t="n">
-        <v>56273</v>
+        <v>56290</v>
       </c>
       <c r="C286" t="inlineStr">
         <is>
@@ -39034,21 +39034,21 @@
         </is>
       </c>
       <c r="E286" t="n">
-        <v>205992</v>
+        <v>205995</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
@@ -39072,10 +39072,10 @@
         </is>
       </c>
       <c r="Q286" t="n">
-        <v>586444</v>
+        <v>586393</v>
       </c>
       <c r="R286" t="n">
-        <v>6311160</v>
+        <v>6311147</v>
       </c>
       <c r="S286" t="n">
         <v>5</v>
@@ -39107,7 +39107,7 @@
       </c>
       <c r="Z286" t="inlineStr">
         <is>
-          <t>23:24</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AA286" t="inlineStr">
@@ -39117,7 +39117,7 @@
       </c>
       <c r="AB286" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AC286" t="inlineStr">
@@ -39162,10 +39162,10 @@
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>122254954</v>
+        <v>122254654</v>
       </c>
       <c r="B287" t="n">
-        <v>56273</v>
+        <v>56290</v>
       </c>
       <c r="C287" t="inlineStr">
         <is>
@@ -39178,21 +39178,21 @@
         </is>
       </c>
       <c r="E287" t="n">
-        <v>205992</v>
+        <v>205995</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
@@ -39216,10 +39216,10 @@
         </is>
       </c>
       <c r="Q287" t="n">
-        <v>586442</v>
+        <v>586467</v>
       </c>
       <c r="R287" t="n">
-        <v>6311152</v>
+        <v>6311178</v>
       </c>
       <c r="S287" t="n">
         <v>5</v>
@@ -39251,7 +39251,7 @@
       </c>
       <c r="Z287" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AA287" t="inlineStr">
@@ -39261,7 +39261,7 @@
       </c>
       <c r="AB287" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="AC287" t="inlineStr">
@@ -39306,10 +39306,10 @@
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>122254616</v>
+        <v>122254610</v>
       </c>
       <c r="B288" t="n">
-        <v>56285</v>
+        <v>56290</v>
       </c>
       <c r="C288" t="inlineStr">
         <is>
@@ -39360,10 +39360,10 @@
         </is>
       </c>
       <c r="Q288" t="n">
-        <v>586327</v>
+        <v>586389</v>
       </c>
       <c r="R288" t="n">
-        <v>6311118</v>
+        <v>6311141</v>
       </c>
       <c r="S288" t="n">
         <v>5</v>
@@ -39395,7 +39395,7 @@
       </c>
       <c r="Z288" t="inlineStr">
         <is>
-          <t>22:57</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA288" t="inlineStr">
@@ -39405,7 +39405,7 @@
       </c>
       <c r="AB288" t="inlineStr">
         <is>
-          <t>22:58</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AC288" t="inlineStr">
@@ -39450,10 +39450,10 @@
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>122254634</v>
+        <v>122254616</v>
       </c>
       <c r="B289" t="n">
-        <v>56285</v>
+        <v>56290</v>
       </c>
       <c r="C289" t="inlineStr">
         <is>
@@ -39504,10 +39504,10 @@
         </is>
       </c>
       <c r="Q289" t="n">
-        <v>586415</v>
+        <v>586327</v>
       </c>
       <c r="R289" t="n">
-        <v>6311148</v>
+        <v>6311118</v>
       </c>
       <c r="S289" t="n">
         <v>5</v>
@@ -39539,7 +39539,7 @@
       </c>
       <c r="Z289" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>22:57</t>
         </is>
       </c>
       <c r="AA289" t="inlineStr">
@@ -39549,7 +39549,7 @@
       </c>
       <c r="AB289" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>22:58</t>
         </is>
       </c>
       <c r="AC289" t="inlineStr">
@@ -39594,10 +39594,10 @@
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>122254418</v>
+        <v>122254372</v>
       </c>
       <c r="B290" t="n">
-        <v>56280</v>
+        <v>56285</v>
       </c>
       <c r="C290" t="inlineStr">
         <is>
@@ -39648,10 +39648,10 @@
         </is>
       </c>
       <c r="Q290" t="n">
-        <v>586467</v>
+        <v>586306</v>
       </c>
       <c r="R290" t="n">
-        <v>6311178</v>
+        <v>6311131</v>
       </c>
       <c r="S290" t="n">
         <v>5</v>
@@ -39683,7 +39683,7 @@
       </c>
       <c r="Z290" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AA290" t="inlineStr">
@@ -39693,7 +39693,7 @@
       </c>
       <c r="AB290" t="inlineStr">
         <is>
-          <t>22:33</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AC290" t="inlineStr">
@@ -39738,10 +39738,10 @@
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>122254310</v>
+        <v>122254421</v>
       </c>
       <c r="B291" t="n">
-        <v>56280</v>
+        <v>56285</v>
       </c>
       <c r="C291" t="inlineStr">
         <is>
@@ -39792,10 +39792,10 @@
         </is>
       </c>
       <c r="Q291" t="n">
-        <v>586452</v>
+        <v>586468</v>
       </c>
       <c r="R291" t="n">
-        <v>6311156</v>
+        <v>6311181</v>
       </c>
       <c r="S291" t="n">
         <v>5</v>
@@ -39827,7 +39827,7 @@
       </c>
       <c r="Z291" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AA291" t="inlineStr">
@@ -39837,7 +39837,7 @@
       </c>
       <c r="AB291" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="AC291" t="inlineStr">
@@ -39882,10 +39882,10 @@
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>122254412</v>
+        <v>122254394</v>
       </c>
       <c r="B292" t="n">
-        <v>56280</v>
+        <v>56285</v>
       </c>
       <c r="C292" t="inlineStr">
         <is>
@@ -39936,10 +39936,10 @@
         </is>
       </c>
       <c r="Q292" t="n">
-        <v>586424</v>
+        <v>586419</v>
       </c>
       <c r="R292" t="n">
-        <v>6311135</v>
+        <v>6311142</v>
       </c>
       <c r="S292" t="n">
         <v>5</v>
@@ -39971,7 +39971,7 @@
       </c>
       <c r="Z292" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>22:43</t>
         </is>
       </c>
       <c r="AA292" t="inlineStr">
@@ -39981,7 +39981,7 @@
       </c>
       <c r="AB292" t="inlineStr">
         <is>
-          <t>22:38</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AC292" t="inlineStr">
@@ -40026,10 +40026,10 @@
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>122254392</v>
+        <v>122254313</v>
       </c>
       <c r="B293" t="n">
-        <v>56280</v>
+        <v>56285</v>
       </c>
       <c r="C293" t="inlineStr">
         <is>
@@ -40080,10 +40080,10 @@
         </is>
       </c>
       <c r="Q293" t="n">
-        <v>586384</v>
+        <v>586449</v>
       </c>
       <c r="R293" t="n">
-        <v>6311139</v>
+        <v>6311155</v>
       </c>
       <c r="S293" t="n">
         <v>5</v>
@@ -40115,7 +40115,7 @@
       </c>
       <c r="Z293" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA293" t="inlineStr">
@@ -40125,7 +40125,7 @@
       </c>
       <c r="AB293" t="inlineStr">
         <is>
-          <t>22:46</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC293" t="inlineStr">
@@ -40170,10 +40170,10 @@
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>122254608</v>
+        <v>122254648</v>
       </c>
       <c r="B294" t="n">
-        <v>56285</v>
+        <v>56290</v>
       </c>
       <c r="C294" t="inlineStr">
         <is>
@@ -40224,10 +40224,10 @@
         </is>
       </c>
       <c r="Q294" t="n">
-        <v>586393</v>
+        <v>586418</v>
       </c>
       <c r="R294" t="n">
-        <v>6311147</v>
+        <v>6311107</v>
       </c>
       <c r="S294" t="n">
         <v>5</v>
@@ -40259,7 +40259,7 @@
       </c>
       <c r="Z294" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>22:36</t>
         </is>
       </c>
       <c r="AA294" t="inlineStr">
@@ -40269,7 +40269,7 @@
       </c>
       <c r="AB294" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AC294" t="inlineStr">
@@ -40314,10 +40314,10 @@
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>122254617</v>
+        <v>122254584</v>
       </c>
       <c r="B295" t="n">
-        <v>56285</v>
+        <v>56290</v>
       </c>
       <c r="C295" t="inlineStr">
         <is>
@@ -40368,10 +40368,10 @@
         </is>
       </c>
       <c r="Q295" t="n">
-        <v>586317</v>
+        <v>586473</v>
       </c>
       <c r="R295" t="n">
-        <v>6311115</v>
+        <v>6311192</v>
       </c>
       <c r="S295" t="n">
         <v>5</v>
@@ -40403,7 +40403,7 @@
       </c>
       <c r="Z295" t="inlineStr">
         <is>
-          <t>22:57</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AA295" t="inlineStr">
@@ -40413,7 +40413,7 @@
       </c>
       <c r="AB295" t="inlineStr">
         <is>
-          <t>22:58</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AC295" t="inlineStr">
@@ -40458,10 +40458,10 @@
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>122254475</v>
+        <v>122254627</v>
       </c>
       <c r="B296" t="n">
-        <v>56266</v>
+        <v>56290</v>
       </c>
       <c r="C296" t="inlineStr">
         <is>
@@ -40470,25 +40470,25 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E296" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
@@ -40512,10 +40512,10 @@
         </is>
       </c>
       <c r="Q296" t="n">
-        <v>586420</v>
+        <v>586306</v>
       </c>
       <c r="R296" t="n">
-        <v>6311166</v>
+        <v>6311131</v>
       </c>
       <c r="S296" t="n">
         <v>5</v>
@@ -40547,7 +40547,7 @@
       </c>
       <c r="Z296" t="inlineStr">
         <is>
-          <t>23:23</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AA296" t="inlineStr">
@@ -40557,7 +40557,7 @@
       </c>
       <c r="AB296" t="inlineStr">
         <is>
-          <t>23:24</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AC296" t="inlineStr">
@@ -40602,10 +40602,10 @@
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>122254500</v>
+        <v>122254587</v>
       </c>
       <c r="B297" t="n">
-        <v>56266</v>
+        <v>56290</v>
       </c>
       <c r="C297" t="inlineStr">
         <is>
@@ -40614,25 +40614,25 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E297" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
@@ -40656,10 +40656,10 @@
         </is>
       </c>
       <c r="Q297" t="n">
-        <v>586388</v>
+        <v>586443</v>
       </c>
       <c r="R297" t="n">
-        <v>6311142</v>
+        <v>6311163</v>
       </c>
       <c r="S297" t="n">
         <v>5</v>
@@ -40691,7 +40691,7 @@
       </c>
       <c r="Z297" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AA297" t="inlineStr">
@@ -40701,7 +40701,7 @@
       </c>
       <c r="AB297" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AC297" t="inlineStr">
@@ -40746,10 +40746,10 @@
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>122254318</v>
+        <v>122254611</v>
       </c>
       <c r="B298" t="n">
-        <v>56280</v>
+        <v>56290</v>
       </c>
       <c r="C298" t="inlineStr">
         <is>
@@ -40762,21 +40762,21 @@
         </is>
       </c>
       <c r="E298" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
@@ -40800,10 +40800,10 @@
         </is>
       </c>
       <c r="Q298" t="n">
-        <v>586455</v>
+        <v>586370</v>
       </c>
       <c r="R298" t="n">
-        <v>6311228</v>
+        <v>6311139</v>
       </c>
       <c r="S298" t="n">
         <v>5</v>
@@ -40835,7 +40835,7 @@
       </c>
       <c r="Z298" t="inlineStr">
         <is>
-          <t>23:22</t>
+          <t>22:59</t>
         </is>
       </c>
       <c r="AA298" t="inlineStr">
@@ -40845,7 +40845,7 @@
       </c>
       <c r="AB298" t="inlineStr">
         <is>
-          <t>23:23</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AC298" t="inlineStr">
@@ -40890,10 +40890,10 @@
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>122254646</v>
+        <v>122254513</v>
       </c>
       <c r="B299" t="n">
-        <v>56285</v>
+        <v>56271</v>
       </c>
       <c r="C299" t="inlineStr">
         <is>
@@ -40902,25 +40902,25 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E299" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
@@ -40944,10 +40944,10 @@
         </is>
       </c>
       <c r="Q299" t="n">
-        <v>586422</v>
+        <v>586396</v>
       </c>
       <c r="R299" t="n">
-        <v>6311111</v>
+        <v>6311146</v>
       </c>
       <c r="S299" t="n">
         <v>5</v>
@@ -40979,7 +40979,7 @@
       </c>
       <c r="Z299" t="inlineStr">
         <is>
-          <t>22:36</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AA299" t="inlineStr">
@@ -40989,7 +40989,7 @@
       </c>
       <c r="AB299" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AC299" t="inlineStr">
@@ -41034,10 +41034,10 @@
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>122254607</v>
+        <v>122254963</v>
       </c>
       <c r="B300" t="n">
-        <v>56285</v>
+        <v>56278</v>
       </c>
       <c r="C300" t="inlineStr">
         <is>
@@ -41050,21 +41050,21 @@
         </is>
       </c>
       <c r="E300" t="n">
-        <v>205995</v>
+        <v>205992</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
@@ -41088,10 +41088,10 @@
         </is>
       </c>
       <c r="Q300" t="n">
-        <v>586415</v>
+        <v>586374</v>
       </c>
       <c r="R300" t="n">
-        <v>6311149</v>
+        <v>6311140</v>
       </c>
       <c r="S300" t="n">
         <v>5</v>
@@ -41123,7 +41123,7 @@
       </c>
       <c r="Z300" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>22:46</t>
         </is>
       </c>
       <c r="AA300" t="inlineStr">
@@ -41133,7 +41133,7 @@
       </c>
       <c r="AB300" t="inlineStr">
         <is>
-          <t>23:03</t>
+          <t>22:47</t>
         </is>
       </c>
       <c r="AC300" t="inlineStr">
@@ -41178,7 +41178,7 @@
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>122254656</v>
+        <v>122254306</v>
       </c>
       <c r="B301" t="n">
         <v>56285</v>
@@ -41194,21 +41194,21 @@
         </is>
       </c>
       <c r="E301" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
@@ -41232,10 +41232,10 @@
         </is>
       </c>
       <c r="Q301" t="n">
-        <v>586483</v>
+        <v>586473</v>
       </c>
       <c r="R301" t="n">
-        <v>6311186</v>
+        <v>6311192</v>
       </c>
       <c r="S301" t="n">
         <v>5</v>
@@ -41267,7 +41267,7 @@
       </c>
       <c r="Z301" t="inlineStr">
         <is>
-          <t>22:31</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AA301" t="inlineStr">
@@ -41277,7 +41277,7 @@
       </c>
       <c r="AB301" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AC301" t="inlineStr">
@@ -41322,10 +41322,10 @@
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>122254343</v>
+        <v>122254846</v>
       </c>
       <c r="B302" t="n">
-        <v>56280</v>
+        <v>56288</v>
       </c>
       <c r="C302" t="inlineStr">
         <is>
@@ -41338,21 +41338,21 @@
         </is>
       </c>
       <c r="E302" t="n">
-        <v>100092</v>
+        <v>100111</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
@@ -41376,10 +41376,10 @@
         </is>
       </c>
       <c r="Q302" t="n">
-        <v>586388</v>
+        <v>586370</v>
       </c>
       <c r="R302" t="n">
-        <v>6311142</v>
+        <v>6311139</v>
       </c>
       <c r="S302" t="n">
         <v>5</v>
@@ -41411,17 +41411,17 @@
       </c>
       <c r="Z302" t="inlineStr">
         <is>
+          <t>22:59</t>
+        </is>
+      </c>
+      <c r="AA302" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AB302" t="inlineStr">
+        <is>
           <t>23:00</t>
-        </is>
-      </c>
-      <c r="AA302" t="inlineStr">
-        <is>
-          <t>2024-06-26</t>
-        </is>
-      </c>
-      <c r="AB302" t="inlineStr">
-        <is>
-          <t>23:01</t>
         </is>
       </c>
       <c r="AC302" t="inlineStr">
@@ -41466,10 +41466,10 @@
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>122254313</v>
+        <v>122254957</v>
       </c>
       <c r="B303" t="n">
-        <v>56280</v>
+        <v>56278</v>
       </c>
       <c r="C303" t="inlineStr">
         <is>
@@ -41482,21 +41482,21 @@
         </is>
       </c>
       <c r="E303" t="n">
-        <v>100092</v>
+        <v>205992</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
@@ -41520,10 +41520,10 @@
         </is>
       </c>
       <c r="Q303" t="n">
-        <v>586449</v>
+        <v>586444</v>
       </c>
       <c r="R303" t="n">
-        <v>6311155</v>
+        <v>6311160</v>
       </c>
       <c r="S303" t="n">
         <v>5</v>
@@ -41555,7 +41555,7 @@
       </c>
       <c r="Z303" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="AA303" t="inlineStr">
@@ -41565,7 +41565,7 @@
       </c>
       <c r="AB303" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AC303" t="inlineStr">
@@ -41610,10 +41610,10 @@
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>122254341</v>
+        <v>122254500</v>
       </c>
       <c r="B304" t="n">
-        <v>56280</v>
+        <v>56271</v>
       </c>
       <c r="C304" t="inlineStr">
         <is>
@@ -41622,25 +41622,25 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E304" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
@@ -41664,10 +41664,10 @@
         </is>
       </c>
       <c r="Q304" t="n">
-        <v>586415</v>
+        <v>586388</v>
       </c>
       <c r="R304" t="n">
-        <v>6311146</v>
+        <v>6311142</v>
       </c>
       <c r="S304" t="n">
         <v>5</v>
@@ -41699,7 +41699,7 @@
       </c>
       <c r="Z304" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA304" t="inlineStr">
@@ -41709,7 +41709,7 @@
       </c>
       <c r="AB304" t="inlineStr">
         <is>
-          <t>23:03</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AC304" t="inlineStr">
@@ -41754,10 +41754,10 @@
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>122254658</v>
+        <v>122254473</v>
       </c>
       <c r="B305" t="n">
-        <v>56285</v>
+        <v>56271</v>
       </c>
       <c r="C305" t="inlineStr">
         <is>
@@ -41766,25 +41766,25 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E305" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
@@ -41808,10 +41808,10 @@
         </is>
       </c>
       <c r="Q305" t="n">
-        <v>586491</v>
+        <v>586450</v>
       </c>
       <c r="R305" t="n">
-        <v>6311181</v>
+        <v>6311152</v>
       </c>
       <c r="S305" t="n">
         <v>5</v>
@@ -41843,7 +41843,7 @@
       </c>
       <c r="Z305" t="inlineStr">
         <is>
-          <t>22:31</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA305" t="inlineStr">
@@ -41853,7 +41853,7 @@
       </c>
       <c r="AB305" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC305" t="inlineStr">
@@ -41898,10 +41898,10 @@
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>122254513</v>
+        <v>122254417</v>
       </c>
       <c r="B306" t="n">
-        <v>56266</v>
+        <v>56285</v>
       </c>
       <c r="C306" t="inlineStr">
         <is>
@@ -41910,25 +41910,25 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E306" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
@@ -41952,10 +41952,10 @@
         </is>
       </c>
       <c r="Q306" t="n">
-        <v>586396</v>
+        <v>586426</v>
       </c>
       <c r="R306" t="n">
-        <v>6311146</v>
+        <v>6311145</v>
       </c>
       <c r="S306" t="n">
         <v>5</v>
@@ -41987,7 +41987,7 @@
       </c>
       <c r="Z306" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="AA306" t="inlineStr">
@@ -41997,7 +41997,7 @@
       </c>
       <c r="AB306" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>22:34</t>
         </is>
       </c>
       <c r="AC306" t="inlineStr">
@@ -42042,10 +42042,10 @@
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>122254472</v>
+        <v>122254315</v>
       </c>
       <c r="B307" t="n">
-        <v>56266</v>
+        <v>56285</v>
       </c>
       <c r="C307" t="inlineStr">
         <is>
@@ -42054,25 +42054,25 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E307" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
@@ -42096,10 +42096,10 @@
         </is>
       </c>
       <c r="Q307" t="n">
-        <v>586455</v>
+        <v>586441</v>
       </c>
       <c r="R307" t="n">
-        <v>6311159</v>
+        <v>6311155</v>
       </c>
       <c r="S307" t="n">
         <v>5</v>
@@ -42131,7 +42131,7 @@
       </c>
       <c r="Z307" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AA307" t="inlineStr">
@@ -42141,7 +42141,7 @@
       </c>
       <c r="AB307" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AC307" t="inlineStr">
@@ -42186,10 +42186,10 @@
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>122254496</v>
+        <v>122254660</v>
       </c>
       <c r="B308" t="n">
-        <v>56266</v>
+        <v>56290</v>
       </c>
       <c r="C308" t="inlineStr">
         <is>
@@ -42198,25 +42198,25 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E308" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
@@ -42240,10 +42240,10 @@
         </is>
       </c>
       <c r="Q308" t="n">
-        <v>586415</v>
+        <v>586488</v>
       </c>
       <c r="R308" t="n">
-        <v>6311146</v>
+        <v>6311183</v>
       </c>
       <c r="S308" t="n">
         <v>5</v>
@@ -42275,7 +42275,7 @@
       </c>
       <c r="Z308" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>22:31</t>
         </is>
       </c>
       <c r="AA308" t="inlineStr">
@@ -42285,7 +42285,7 @@
       </c>
       <c r="AB308" t="inlineStr">
         <is>
-          <t>23:03</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AC308" t="inlineStr">
@@ -42330,10 +42330,10 @@
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>122254966</v>
+        <v>122254857</v>
       </c>
       <c r="B309" t="n">
-        <v>56273</v>
+        <v>56288</v>
       </c>
       <c r="C309" t="inlineStr">
         <is>
@@ -42346,21 +42346,21 @@
         </is>
       </c>
       <c r="E309" t="n">
-        <v>205992</v>
+        <v>100111</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
@@ -42384,10 +42384,10 @@
         </is>
       </c>
       <c r="Q309" t="n">
-        <v>586467</v>
+        <v>586317</v>
       </c>
       <c r="R309" t="n">
-        <v>6311178</v>
+        <v>6311115</v>
       </c>
       <c r="S309" t="n">
         <v>5</v>
@@ -42419,7 +42419,7 @@
       </c>
       <c r="Z309" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>22:57</t>
         </is>
       </c>
       <c r="AA309" t="inlineStr">
@@ -42429,7 +42429,7 @@
       </c>
       <c r="AB309" t="inlineStr">
         <is>
-          <t>22:33</t>
+          <t>22:58</t>
         </is>
       </c>
       <c r="AC309" t="inlineStr">
@@ -42474,10 +42474,10 @@
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>122254632</v>
+        <v>122254862</v>
       </c>
       <c r="B310" t="n">
-        <v>56285</v>
+        <v>56288</v>
       </c>
       <c r="C310" t="inlineStr">
         <is>
@@ -42490,21 +42490,21 @@
         </is>
       </c>
       <c r="E310" t="n">
-        <v>205995</v>
+        <v>100111</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
@@ -42528,10 +42528,10 @@
         </is>
       </c>
       <c r="Q310" t="n">
-        <v>586374</v>
+        <v>586288</v>
       </c>
       <c r="R310" t="n">
-        <v>6311140</v>
+        <v>6311100</v>
       </c>
       <c r="S310" t="n">
         <v>5</v>
@@ -42563,7 +42563,7 @@
       </c>
       <c r="Z310" t="inlineStr">
         <is>
-          <t>22:46</t>
+          <t>22:55</t>
         </is>
       </c>
       <c r="AA310" t="inlineStr">
@@ -42573,7 +42573,7 @@
       </c>
       <c r="AB310" t="inlineStr">
         <is>
-          <t>22:47</t>
+          <t>22:56</t>
         </is>
       </c>
       <c r="AC310" t="inlineStr">
@@ -42618,10 +42618,10 @@
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>122254651</v>
+        <v>122254514</v>
       </c>
       <c r="B311" t="n">
-        <v>56285</v>
+        <v>56271</v>
       </c>
       <c r="C311" t="inlineStr">
         <is>
@@ -42630,25 +42630,25 @@
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E311" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
@@ -42672,10 +42672,10 @@
         </is>
       </c>
       <c r="Q311" t="n">
-        <v>586425</v>
+        <v>586408</v>
       </c>
       <c r="R311" t="n">
-        <v>6311113</v>
+        <v>6311124</v>
       </c>
       <c r="S311" t="n">
         <v>5</v>
@@ -42707,7 +42707,7 @@
       </c>
       <c r="Z311" t="inlineStr">
         <is>
-          <t>22:35</t>
+          <t>22:43</t>
         </is>
       </c>
       <c r="AA311" t="inlineStr">
@@ -42717,7 +42717,7 @@
       </c>
       <c r="AB311" t="inlineStr">
         <is>
-          <t>22:36</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AC311" t="inlineStr">
@@ -42762,10 +42762,10 @@
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>122254317</v>
+        <v>122254959</v>
       </c>
       <c r="B312" t="n">
-        <v>56280</v>
+        <v>56278</v>
       </c>
       <c r="C312" t="inlineStr">
         <is>
@@ -42778,21 +42778,21 @@
         </is>
       </c>
       <c r="E312" t="n">
-        <v>100092</v>
+        <v>205992</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
@@ -42816,10 +42816,10 @@
         </is>
       </c>
       <c r="Q312" t="n">
-        <v>586438</v>
+        <v>586370</v>
       </c>
       <c r="R312" t="n">
-        <v>6311222</v>
+        <v>6311139</v>
       </c>
       <c r="S312" t="n">
         <v>5</v>
@@ -42851,7 +42851,7 @@
       </c>
       <c r="Z312" t="inlineStr">
         <is>
-          <t>23:22</t>
+          <t>22:59</t>
         </is>
       </c>
       <c r="AA312" t="inlineStr">
@@ -42861,7 +42861,7 @@
       </c>
       <c r="AB312" t="inlineStr">
         <is>
-          <t>23:23</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AC312" t="inlineStr">
@@ -42906,10 +42906,10 @@
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>122254878</v>
+        <v>122254964</v>
       </c>
       <c r="B313" t="n">
-        <v>56283</v>
+        <v>56278</v>
       </c>
       <c r="C313" t="inlineStr">
         <is>
@@ -42922,21 +42922,21 @@
         </is>
       </c>
       <c r="E313" t="n">
-        <v>100111</v>
+        <v>205992</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
@@ -42960,10 +42960,10 @@
         </is>
       </c>
       <c r="Q313" t="n">
-        <v>586280</v>
+        <v>586430</v>
       </c>
       <c r="R313" t="n">
-        <v>6311103</v>
+        <v>6311142</v>
       </c>
       <c r="S313" t="n">
         <v>5</v>
@@ -42995,7 +42995,7 @@
       </c>
       <c r="Z313" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="AA313" t="inlineStr">
@@ -43005,7 +43005,7 @@
       </c>
       <c r="AB313" t="inlineStr">
         <is>
-          <t>22:52</t>
+          <t>22:34</t>
         </is>
       </c>
       <c r="AC313" t="inlineStr">
@@ -43050,10 +43050,10 @@
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>122254950</v>
+        <v>122254659</v>
       </c>
       <c r="B314" t="n">
-        <v>56273</v>
+        <v>56290</v>
       </c>
       <c r="C314" t="inlineStr">
         <is>
@@ -43066,21 +43066,21 @@
         </is>
       </c>
       <c r="E314" t="n">
-        <v>205992</v>
+        <v>205995</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
@@ -43104,10 +43104,10 @@
         </is>
       </c>
       <c r="Q314" t="n">
-        <v>586482</v>
+        <v>586489</v>
       </c>
       <c r="R314" t="n">
-        <v>6311185</v>
+        <v>6311181</v>
       </c>
       <c r="S314" t="n">
         <v>5</v>
@@ -43139,7 +43139,7 @@
       </c>
       <c r="Z314" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>22:31</t>
         </is>
       </c>
       <c r="AA314" t="inlineStr">
@@ -43149,7 +43149,7 @@
       </c>
       <c r="AB314" t="inlineStr">
         <is>
-          <t>23:31</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AC314" t="inlineStr">
@@ -43194,7 +43194,7 @@
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>122254606</v>
+        <v>122254308</v>
       </c>
       <c r="B315" t="n">
         <v>56285</v>
@@ -43210,21 +43210,21 @@
         </is>
       </c>
       <c r="E315" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
@@ -43248,10 +43248,10 @@
         </is>
       </c>
       <c r="Q315" t="n">
-        <v>586415</v>
+        <v>586455</v>
       </c>
       <c r="R315" t="n">
-        <v>6311146</v>
+        <v>6311159</v>
       </c>
       <c r="S315" t="n">
         <v>5</v>
@@ -43283,7 +43283,7 @@
       </c>
       <c r="Z315" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AA315" t="inlineStr">
@@ -43293,7 +43293,7 @@
       </c>
       <c r="AB315" t="inlineStr">
         <is>
-          <t>23:03</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AC315" t="inlineStr">
@@ -43338,10 +43338,10 @@
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>122254843</v>
+        <v>122254390</v>
       </c>
       <c r="B316" t="n">
-        <v>56283</v>
+        <v>56285</v>
       </c>
       <c r="C316" t="inlineStr">
         <is>
@@ -43354,21 +43354,21 @@
         </is>
       </c>
       <c r="E316" t="n">
-        <v>100111</v>
+        <v>100092</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
@@ -43392,10 +43392,10 @@
         </is>
       </c>
       <c r="Q316" t="n">
-        <v>586389</v>
+        <v>586374</v>
       </c>
       <c r="R316" t="n">
-        <v>6311142</v>
+        <v>6311139</v>
       </c>
       <c r="S316" t="n">
         <v>5</v>
@@ -43427,7 +43427,7 @@
       </c>
       <c r="Z316" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:46</t>
         </is>
       </c>
       <c r="AA316" t="inlineStr">
@@ -43437,7 +43437,7 @@
       </c>
       <c r="AB316" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>22:47</t>
         </is>
       </c>
       <c r="AC316" t="inlineStr">
@@ -43482,10 +43482,10 @@
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>122254836</v>
+        <v>122254370</v>
       </c>
       <c r="B317" t="n">
-        <v>56283</v>
+        <v>56285</v>
       </c>
       <c r="C317" t="inlineStr">
         <is>
@@ -43498,21 +43498,21 @@
         </is>
       </c>
       <c r="E317" t="n">
-        <v>100111</v>
+        <v>100092</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
@@ -43536,10 +43536,10 @@
         </is>
       </c>
       <c r="Q317" t="n">
-        <v>586474</v>
+        <v>586309</v>
       </c>
       <c r="R317" t="n">
-        <v>6311176</v>
+        <v>6311119</v>
       </c>
       <c r="S317" t="n">
         <v>5</v>
@@ -43571,7 +43571,7 @@
       </c>
       <c r="Z317" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AA317" t="inlineStr">
@@ -43581,7 +43581,7 @@
       </c>
       <c r="AB317" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AC317" t="inlineStr">
@@ -43626,10 +43626,10 @@
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>122254390</v>
+        <v>122254878</v>
       </c>
       <c r="B318" t="n">
-        <v>56280</v>
+        <v>56288</v>
       </c>
       <c r="C318" t="inlineStr">
         <is>
@@ -43642,21 +43642,21 @@
         </is>
       </c>
       <c r="E318" t="n">
-        <v>100092</v>
+        <v>100111</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
@@ -43680,10 +43680,10 @@
         </is>
       </c>
       <c r="Q318" t="n">
-        <v>586374</v>
+        <v>586280</v>
       </c>
       <c r="R318" t="n">
-        <v>6311139</v>
+        <v>6311103</v>
       </c>
       <c r="S318" t="n">
         <v>5</v>
@@ -43715,7 +43715,7 @@
       </c>
       <c r="Z318" t="inlineStr">
         <is>
-          <t>22:46</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AA318" t="inlineStr">
@@ -43725,7 +43725,7 @@
       </c>
       <c r="AB318" t="inlineStr">
         <is>
-          <t>22:47</t>
+          <t>22:52</t>
         </is>
       </c>
       <c r="AC318" t="inlineStr">
@@ -43770,10 +43770,10 @@
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>122254956</v>
+        <v>122254496</v>
       </c>
       <c r="B319" t="n">
-        <v>56273</v>
+        <v>56271</v>
       </c>
       <c r="C319" t="inlineStr">
         <is>
@@ -43782,25 +43782,25 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E319" t="n">
-        <v>205992</v>
+        <v>205998</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
@@ -43824,10 +43824,10 @@
         </is>
       </c>
       <c r="Q319" t="n">
-        <v>586441</v>
+        <v>586415</v>
       </c>
       <c r="R319" t="n">
-        <v>6311152</v>
+        <v>6311146</v>
       </c>
       <c r="S319" t="n">
         <v>5</v>
@@ -43859,7 +43859,7 @@
       </c>
       <c r="Z319" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AA319" t="inlineStr">
@@ -43869,7 +43869,7 @@
       </c>
       <c r="AB319" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>23:03</t>
         </is>
       </c>
       <c r="AC319" t="inlineStr">
@@ -43914,10 +43914,10 @@
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>122254615</v>
+        <v>122254658</v>
       </c>
       <c r="B320" t="n">
-        <v>56285</v>
+        <v>56290</v>
       </c>
       <c r="C320" t="inlineStr">
         <is>
@@ -43968,10 +43968,10 @@
         </is>
       </c>
       <c r="Q320" t="n">
-        <v>586329</v>
+        <v>586491</v>
       </c>
       <c r="R320" t="n">
-        <v>6311120</v>
+        <v>6311181</v>
       </c>
       <c r="S320" t="n">
         <v>5</v>
@@ -44003,7 +44003,7 @@
       </c>
       <c r="Z320" t="inlineStr">
         <is>
-          <t>22:57</t>
+          <t>22:31</t>
         </is>
       </c>
       <c r="AA320" t="inlineStr">
@@ -44013,7 +44013,7 @@
       </c>
       <c r="AB320" t="inlineStr">
         <is>
-          <t>22:58</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AC320" t="inlineStr">
@@ -44058,7 +44058,7 @@
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>122254660</v>
+        <v>122254343</v>
       </c>
       <c r="B321" t="n">
         <v>56285</v>
@@ -44074,21 +44074,21 @@
         </is>
       </c>
       <c r="E321" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
@@ -44112,10 +44112,10 @@
         </is>
       </c>
       <c r="Q321" t="n">
-        <v>586488</v>
+        <v>586388</v>
       </c>
       <c r="R321" t="n">
-        <v>6311183</v>
+        <v>6311142</v>
       </c>
       <c r="S321" t="n">
         <v>5</v>
@@ -44147,7 +44147,7 @@
       </c>
       <c r="Z321" t="inlineStr">
         <is>
-          <t>22:31</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA321" t="inlineStr">
@@ -44157,7 +44157,7 @@
       </c>
       <c r="AB321" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AC321" t="inlineStr">
@@ -44202,10 +44202,10 @@
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>122254512</v>
+        <v>122254367</v>
       </c>
       <c r="B322" t="n">
-        <v>56266</v>
+        <v>56285</v>
       </c>
       <c r="C322" t="inlineStr">
         <is>
@@ -44214,25 +44214,25 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E322" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
@@ -44256,10 +44256,10 @@
         </is>
       </c>
       <c r="Q322" t="n">
-        <v>586379</v>
+        <v>586280</v>
       </c>
       <c r="R322" t="n">
-        <v>6311136</v>
+        <v>6311103</v>
       </c>
       <c r="S322" t="n">
         <v>5</v>
@@ -44291,7 +44291,7 @@
       </c>
       <c r="Z322" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AA322" t="inlineStr">
@@ -44301,7 +44301,7 @@
       </c>
       <c r="AB322" t="inlineStr">
         <is>
-          <t>22:46</t>
+          <t>22:52</t>
         </is>
       </c>
       <c r="AC322" t="inlineStr">
@@ -44346,7 +44346,7 @@
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>122254611</v>
+        <v>122254314</v>
       </c>
       <c r="B323" t="n">
         <v>56285</v>
@@ -44362,21 +44362,21 @@
         </is>
       </c>
       <c r="E323" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
@@ -44400,10 +44400,10 @@
         </is>
       </c>
       <c r="Q323" t="n">
-        <v>586370</v>
+        <v>586443</v>
       </c>
       <c r="R323" t="n">
-        <v>6311139</v>
+        <v>6311164</v>
       </c>
       <c r="S323" t="n">
         <v>5</v>
@@ -44435,7 +44435,7 @@
       </c>
       <c r="Z323" t="inlineStr">
         <is>
-          <t>22:59</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AA323" t="inlineStr">
@@ -44445,7 +44445,7 @@
       </c>
       <c r="AB323" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AC323" t="inlineStr">
@@ -44490,10 +44490,10 @@
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>122254415</v>
+        <v>122254365</v>
       </c>
       <c r="B324" t="n">
-        <v>56280</v>
+        <v>56285</v>
       </c>
       <c r="C324" t="inlineStr">
         <is>
@@ -44544,10 +44544,10 @@
         </is>
       </c>
       <c r="Q324" t="n">
-        <v>586425</v>
+        <v>586276</v>
       </c>
       <c r="R324" t="n">
-        <v>6311135</v>
+        <v>6311100</v>
       </c>
       <c r="S324" t="n">
         <v>5</v>
@@ -44579,7 +44579,7 @@
       </c>
       <c r="Z324" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AA324" t="inlineStr">
@@ -44589,7 +44589,7 @@
       </c>
       <c r="AB324" t="inlineStr">
         <is>
-          <t>22:38</t>
+          <t>22:52</t>
         </is>
       </c>
       <c r="AC324" t="inlineStr">
@@ -44634,10 +44634,10 @@
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>122254413</v>
+        <v>122254393</v>
       </c>
       <c r="B325" t="n">
-        <v>56280</v>
+        <v>56285</v>
       </c>
       <c r="C325" t="inlineStr">
         <is>
@@ -44688,10 +44688,10 @@
         </is>
       </c>
       <c r="Q325" t="n">
-        <v>586423</v>
+        <v>586396</v>
       </c>
       <c r="R325" t="n">
-        <v>6311137</v>
+        <v>6311146</v>
       </c>
       <c r="S325" t="n">
         <v>5</v>
@@ -44723,7 +44723,7 @@
       </c>
       <c r="Z325" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AA325" t="inlineStr">
@@ -44733,7 +44733,7 @@
       </c>
       <c r="AB325" t="inlineStr">
         <is>
-          <t>22:38</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AC325" t="inlineStr">
@@ -44778,10 +44778,10 @@
     </row>
     <row r="326">
       <c r="A326" t="n">
-        <v>122254416</v>
+        <v>122254318</v>
       </c>
       <c r="B326" t="n">
-        <v>56280</v>
+        <v>56285</v>
       </c>
       <c r="C326" t="inlineStr">
         <is>
@@ -44832,10 +44832,10 @@
         </is>
       </c>
       <c r="Q326" t="n">
-        <v>586410</v>
+        <v>586455</v>
       </c>
       <c r="R326" t="n">
-        <v>6311140</v>
+        <v>6311228</v>
       </c>
       <c r="S326" t="n">
         <v>5</v>
@@ -44867,7 +44867,7 @@
       </c>
       <c r="Z326" t="inlineStr">
         <is>
-          <t>22:33</t>
+          <t>23:22</t>
         </is>
       </c>
       <c r="AA326" t="inlineStr">
@@ -44877,7 +44877,7 @@
       </c>
       <c r="AB326" t="inlineStr">
         <is>
-          <t>22:34</t>
+          <t>23:23</t>
         </is>
       </c>
       <c r="AC326" t="inlineStr">
@@ -44922,10 +44922,10 @@
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>122254367</v>
+        <v>122254391</v>
       </c>
       <c r="B327" t="n">
-        <v>56280</v>
+        <v>56285</v>
       </c>
       <c r="C327" t="inlineStr">
         <is>
@@ -44976,10 +44976,10 @@
         </is>
       </c>
       <c r="Q327" t="n">
-        <v>586280</v>
+        <v>586379</v>
       </c>
       <c r="R327" t="n">
-        <v>6311103</v>
+        <v>6311136</v>
       </c>
       <c r="S327" t="n">
         <v>5</v>
@@ -45011,7 +45011,7 @@
       </c>
       <c r="Z327" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AA327" t="inlineStr">
@@ -45021,7 +45021,7 @@
       </c>
       <c r="AB327" t="inlineStr">
         <is>
-          <t>22:52</t>
+          <t>22:46</t>
         </is>
       </c>
       <c r="AC327" t="inlineStr">
@@ -45066,10 +45066,10 @@
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>122254417</v>
+        <v>122254312</v>
       </c>
       <c r="B328" t="n">
-        <v>56280</v>
+        <v>56285</v>
       </c>
       <c r="C328" t="inlineStr">
         <is>
@@ -45120,10 +45120,10 @@
         </is>
       </c>
       <c r="Q328" t="n">
-        <v>586426</v>
+        <v>586452</v>
       </c>
       <c r="R328" t="n">
-        <v>6311145</v>
+        <v>6311152</v>
       </c>
       <c r="S328" t="n">
         <v>5</v>
@@ -45155,7 +45155,7 @@
       </c>
       <c r="Z328" t="inlineStr">
         <is>
-          <t>22:33</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA328" t="inlineStr">
@@ -45165,7 +45165,7 @@
       </c>
       <c r="AB328" t="inlineStr">
         <is>
-          <t>22:34</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC328" t="inlineStr">
@@ -45210,10 +45210,10 @@
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>122254312</v>
+        <v>122254474</v>
       </c>
       <c r="B329" t="n">
-        <v>56280</v>
+        <v>56271</v>
       </c>
       <c r="C329" t="inlineStr">
         <is>
@@ -45222,25 +45222,25 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E329" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
@@ -45264,10 +45264,10 @@
         </is>
       </c>
       <c r="Q329" t="n">
-        <v>586452</v>
+        <v>586443</v>
       </c>
       <c r="R329" t="n">
-        <v>6311152</v>
+        <v>6311164</v>
       </c>
       <c r="S329" t="n">
         <v>5</v>
@@ -45299,17 +45299,17 @@
       </c>
       <c r="Z329" t="inlineStr">
         <is>
+          <t>23:26</t>
+        </is>
+      </c>
+      <c r="AA329" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AB329" t="inlineStr">
+        <is>
           <t>23:27</t>
-        </is>
-      </c>
-      <c r="AA329" t="inlineStr">
-        <is>
-          <t>2024-06-26</t>
-        </is>
-      </c>
-      <c r="AB329" t="inlineStr">
-        <is>
-          <t>23:28</t>
         </is>
       </c>
       <c r="AC329" t="inlineStr">
@@ -45354,10 +45354,10 @@
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>122254633</v>
+        <v>122254646</v>
       </c>
       <c r="B330" t="n">
-        <v>56285</v>
+        <v>56290</v>
       </c>
       <c r="C330" t="inlineStr">
         <is>
@@ -45408,10 +45408,10 @@
         </is>
       </c>
       <c r="Q330" t="n">
-        <v>586396</v>
+        <v>586422</v>
       </c>
       <c r="R330" t="n">
-        <v>6311146</v>
+        <v>6311111</v>
       </c>
       <c r="S330" t="n">
         <v>5</v>
@@ -45443,7 +45443,7 @@
       </c>
       <c r="Z330" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>22:36</t>
         </is>
       </c>
       <c r="AA330" t="inlineStr">
@@ -45453,7 +45453,7 @@
       </c>
       <c r="AB330" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AC330" t="inlineStr">
@@ -45498,10 +45498,10 @@
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>122254587</v>
+        <v>122254953</v>
       </c>
       <c r="B331" t="n">
-        <v>56285</v>
+        <v>56278</v>
       </c>
       <c r="C331" t="inlineStr">
         <is>
@@ -45514,21 +45514,21 @@
         </is>
       </c>
       <c r="E331" t="n">
-        <v>205995</v>
+        <v>205992</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I331" t="inlineStr">
@@ -45552,10 +45552,10 @@
         </is>
       </c>
       <c r="Q331" t="n">
-        <v>586443</v>
+        <v>586449</v>
       </c>
       <c r="R331" t="n">
-        <v>6311163</v>
+        <v>6311155</v>
       </c>
       <c r="S331" t="n">
         <v>5</v>
@@ -45587,7 +45587,7 @@
       </c>
       <c r="Z331" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA331" t="inlineStr">
@@ -45597,7 +45597,7 @@
       </c>
       <c r="AB331" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC331" t="inlineStr">
@@ -45642,10 +45642,10 @@
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>122254519</v>
+        <v>122254652</v>
       </c>
       <c r="B332" t="n">
-        <v>56266</v>
+        <v>56290</v>
       </c>
       <c r="C332" t="inlineStr">
         <is>
@@ -45654,25 +45654,25 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E332" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
@@ -45696,10 +45696,10 @@
         </is>
       </c>
       <c r="Q332" t="n">
-        <v>586424</v>
+        <v>586432</v>
       </c>
       <c r="R332" t="n">
-        <v>6311135</v>
+        <v>6311118</v>
       </c>
       <c r="S332" t="n">
         <v>5</v>
@@ -45731,7 +45731,7 @@
       </c>
       <c r="Z332" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>22:34</t>
         </is>
       </c>
       <c r="AA332" t="inlineStr">
@@ -45741,7 +45741,7 @@
       </c>
       <c r="AB332" t="inlineStr">
         <is>
-          <t>22:38</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="AC332" t="inlineStr">
@@ -45786,7 +45786,7 @@
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>122254644</v>
+        <v>122254317</v>
       </c>
       <c r="B333" t="n">
         <v>56285</v>
@@ -45802,21 +45802,21 @@
         </is>
       </c>
       <c r="E333" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
@@ -45840,10 +45840,10 @@
         </is>
       </c>
       <c r="Q333" t="n">
-        <v>586429</v>
+        <v>586438</v>
       </c>
       <c r="R333" t="n">
-        <v>6311115</v>
+        <v>6311222</v>
       </c>
       <c r="S333" t="n">
         <v>5</v>
@@ -45875,7 +45875,7 @@
       </c>
       <c r="Z333" t="inlineStr">
         <is>
-          <t>22:36</t>
+          <t>23:22</t>
         </is>
       </c>
       <c r="AA333" t="inlineStr">
@@ -45885,7 +45885,7 @@
       </c>
       <c r="AB333" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>23:23</t>
         </is>
       </c>
       <c r="AC333" t="inlineStr">
@@ -45930,7 +45930,7 @@
     </row>
     <row r="334">
       <c r="A334" t="n">
-        <v>122254652</v>
+        <v>122254307</v>
       </c>
       <c r="B334" t="n">
         <v>56285</v>
@@ -45946,21 +45946,21 @@
         </is>
       </c>
       <c r="E334" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
@@ -45984,10 +45984,10 @@
         </is>
       </c>
       <c r="Q334" t="n">
-        <v>586432</v>
+        <v>586477</v>
       </c>
       <c r="R334" t="n">
-        <v>6311118</v>
+        <v>6311186</v>
       </c>
       <c r="S334" t="n">
         <v>5</v>
@@ -46019,7 +46019,7 @@
       </c>
       <c r="Z334" t="inlineStr">
         <is>
-          <t>22:34</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AA334" t="inlineStr">
@@ -46029,7 +46029,7 @@
       </c>
       <c r="AB334" t="inlineStr">
         <is>
-          <t>22:35</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AC334" t="inlineStr">
@@ -46074,37 +46074,37 @@
     </row>
     <row r="335">
       <c r="A335" t="n">
-        <v>122254854</v>
+        <v>122254173</v>
       </c>
       <c r="B335" t="n">
-        <v>56283</v>
+        <v>56269</v>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Dokumentation efterfrågas</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E335" t="n">
-        <v>100111</v>
+        <v>100015</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Barbastell</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Barbastella barbastellus</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I335" t="inlineStr">
@@ -46128,10 +46128,10 @@
         </is>
       </c>
       <c r="Q335" t="n">
-        <v>586329</v>
+        <v>586415</v>
       </c>
       <c r="R335" t="n">
-        <v>6311120</v>
+        <v>6311149</v>
       </c>
       <c r="S335" t="n">
         <v>5</v>
@@ -46163,7 +46163,7 @@
       </c>
       <c r="Z335" t="inlineStr">
         <is>
-          <t>22:57</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AA335" t="inlineStr">
@@ -46173,7 +46173,7 @@
       </c>
       <c r="AB335" t="inlineStr">
         <is>
-          <t>22:58</t>
+          <t>23:03</t>
         </is>
       </c>
       <c r="AC335" t="inlineStr">
@@ -46218,10 +46218,10 @@
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>122254365</v>
+        <v>122254844</v>
       </c>
       <c r="B336" t="n">
-        <v>56280</v>
+        <v>56288</v>
       </c>
       <c r="C336" t="inlineStr">
         <is>
@@ -46234,21 +46234,21 @@
         </is>
       </c>
       <c r="E336" t="n">
-        <v>100092</v>
+        <v>100111</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
@@ -46272,10 +46272,10 @@
         </is>
       </c>
       <c r="Q336" t="n">
-        <v>586276</v>
+        <v>586387</v>
       </c>
       <c r="R336" t="n">
-        <v>6311100</v>
+        <v>6311141</v>
       </c>
       <c r="S336" t="n">
         <v>5</v>
@@ -46307,7 +46307,7 @@
       </c>
       <c r="Z336" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA336" t="inlineStr">
@@ -46317,7 +46317,7 @@
       </c>
       <c r="AB336" t="inlineStr">
         <is>
-          <t>22:52</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AC336" t="inlineStr">
@@ -46362,10 +46362,10 @@
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>122254953</v>
+        <v>122254954</v>
       </c>
       <c r="B337" t="n">
-        <v>56273</v>
+        <v>56278</v>
       </c>
       <c r="C337" t="inlineStr">
         <is>
@@ -46416,10 +46416,10 @@
         </is>
       </c>
       <c r="Q337" t="n">
-        <v>586449</v>
+        <v>586442</v>
       </c>
       <c r="R337" t="n">
-        <v>6311155</v>
+        <v>6311152</v>
       </c>
       <c r="S337" t="n">
         <v>5</v>
@@ -46451,7 +46451,7 @@
       </c>
       <c r="Z337" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AA337" t="inlineStr">
@@ -46461,7 +46461,7 @@
       </c>
       <c r="AB337" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AC337" t="inlineStr">
@@ -46506,10 +46506,10 @@
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>122254588</v>
+        <v>122254606</v>
       </c>
       <c r="B338" t="n">
-        <v>56285</v>
+        <v>56290</v>
       </c>
       <c r="C338" t="inlineStr">
         <is>
@@ -46563,7 +46563,7 @@
         <v>586415</v>
       </c>
       <c r="R338" t="n">
-        <v>6311196</v>
+        <v>6311146</v>
       </c>
       <c r="S338" t="n">
         <v>5</v>
@@ -46595,7 +46595,7 @@
       </c>
       <c r="Z338" t="inlineStr">
         <is>
-          <t>23:22</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AA338" t="inlineStr">
@@ -46605,7 +46605,7 @@
       </c>
       <c r="AB338" t="inlineStr">
         <is>
-          <t>23:23</t>
+          <t>23:03</t>
         </is>
       </c>
       <c r="AC338" t="inlineStr">
@@ -46650,10 +46650,10 @@
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>122254511</v>
+        <v>122254835</v>
       </c>
       <c r="B339" t="n">
-        <v>56266</v>
+        <v>56288</v>
       </c>
       <c r="C339" t="inlineStr">
         <is>
@@ -46662,25 +46662,25 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E339" t="n">
-        <v>205998</v>
+        <v>100111</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I339" t="inlineStr">
@@ -46704,10 +46704,10 @@
         </is>
       </c>
       <c r="Q339" t="n">
-        <v>586374</v>
+        <v>586473</v>
       </c>
       <c r="R339" t="n">
-        <v>6311139</v>
+        <v>6311192</v>
       </c>
       <c r="S339" t="n">
         <v>5</v>
@@ -46739,7 +46739,7 @@
       </c>
       <c r="Z339" t="inlineStr">
         <is>
-          <t>22:46</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AA339" t="inlineStr">
@@ -46749,7 +46749,7 @@
       </c>
       <c r="AB339" t="inlineStr">
         <is>
-          <t>22:47</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AC339" t="inlineStr">
@@ -46794,10 +46794,10 @@
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>122254342</v>
+        <v>122254854</v>
       </c>
       <c r="B340" t="n">
-        <v>56280</v>
+        <v>56288</v>
       </c>
       <c r="C340" t="inlineStr">
         <is>
@@ -46810,21 +46810,21 @@
         </is>
       </c>
       <c r="E340" t="n">
-        <v>100092</v>
+        <v>100111</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
@@ -46848,10 +46848,10 @@
         </is>
       </c>
       <c r="Q340" t="n">
-        <v>586389</v>
+        <v>586329</v>
       </c>
       <c r="R340" t="n">
-        <v>6311142</v>
+        <v>6311120</v>
       </c>
       <c r="S340" t="n">
         <v>5</v>
@@ -46883,7 +46883,7 @@
       </c>
       <c r="Z340" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:57</t>
         </is>
       </c>
       <c r="AA340" t="inlineStr">
@@ -46893,7 +46893,7 @@
       </c>
       <c r="AB340" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>22:58</t>
         </is>
       </c>
       <c r="AC340" t="inlineStr">
@@ -46938,10 +46938,10 @@
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>122254421</v>
+        <v>122254416</v>
       </c>
       <c r="B341" t="n">
-        <v>56280</v>
+        <v>56285</v>
       </c>
       <c r="C341" t="inlineStr">
         <is>
@@ -46992,10 +46992,10 @@
         </is>
       </c>
       <c r="Q341" t="n">
-        <v>586468</v>
+        <v>586410</v>
       </c>
       <c r="R341" t="n">
-        <v>6311181</v>
+        <v>6311140</v>
       </c>
       <c r="S341" t="n">
         <v>5</v>
@@ -47027,7 +47027,7 @@
       </c>
       <c r="Z341" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="AA341" t="inlineStr">
@@ -47037,7 +47037,7 @@
       </c>
       <c r="AB341" t="inlineStr">
         <is>
-          <t>22:33</t>
+          <t>22:34</t>
         </is>
       </c>
       <c r="AC341" t="inlineStr">
@@ -47082,10 +47082,10 @@
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>122254514</v>
+        <v>122254634</v>
       </c>
       <c r="B342" t="n">
-        <v>56266</v>
+        <v>56290</v>
       </c>
       <c r="C342" t="inlineStr">
         <is>
@@ -47094,25 +47094,25 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E342" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
@@ -47136,10 +47136,10 @@
         </is>
       </c>
       <c r="Q342" t="n">
-        <v>586408</v>
+        <v>586415</v>
       </c>
       <c r="R342" t="n">
-        <v>6311124</v>
+        <v>6311148</v>
       </c>
       <c r="S342" t="n">
         <v>5</v>
@@ -47171,7 +47171,7 @@
       </c>
       <c r="Z342" t="inlineStr">
         <is>
-          <t>22:43</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AA342" t="inlineStr">
@@ -47181,7 +47181,7 @@
       </c>
       <c r="AB342" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AC342" t="inlineStr">
@@ -47226,10 +47226,10 @@
     </row>
     <row r="343">
       <c r="A343" t="n">
-        <v>122254393</v>
+        <v>122254585</v>
       </c>
       <c r="B343" t="n">
-        <v>56280</v>
+        <v>56290</v>
       </c>
       <c r="C343" t="inlineStr">
         <is>
@@ -47242,21 +47242,21 @@
         </is>
       </c>
       <c r="E343" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
@@ -47280,10 +47280,10 @@
         </is>
       </c>
       <c r="Q343" t="n">
-        <v>586396</v>
+        <v>586455</v>
       </c>
       <c r="R343" t="n">
-        <v>6311146</v>
+        <v>6311156</v>
       </c>
       <c r="S343" t="n">
         <v>5</v>
@@ -47315,7 +47315,7 @@
       </c>
       <c r="Z343" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AA343" t="inlineStr">
@@ -47325,7 +47325,7 @@
       </c>
       <c r="AB343" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AC343" t="inlineStr">
@@ -47370,10 +47370,10 @@
     </row>
     <row r="344">
       <c r="A344" t="n">
-        <v>122254959</v>
+        <v>122254373</v>
       </c>
       <c r="B344" t="n">
-        <v>56273</v>
+        <v>56285</v>
       </c>
       <c r="C344" t="inlineStr">
         <is>
@@ -47386,21 +47386,21 @@
         </is>
       </c>
       <c r="E344" t="n">
-        <v>205992</v>
+        <v>100092</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
@@ -47424,10 +47424,10 @@
         </is>
       </c>
       <c r="Q344" t="n">
-        <v>586370</v>
+        <v>586307</v>
       </c>
       <c r="R344" t="n">
-        <v>6311139</v>
+        <v>6311133</v>
       </c>
       <c r="S344" t="n">
         <v>5</v>
@@ -47459,7 +47459,7 @@
       </c>
       <c r="Z344" t="inlineStr">
         <is>
-          <t>22:59</t>
+          <t>22:49</t>
         </is>
       </c>
       <c r="AA344" t="inlineStr">
@@ -47469,7 +47469,7 @@
       </c>
       <c r="AB344" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AC344" t="inlineStr">
@@ -47514,7 +47514,7 @@
     </row>
     <row r="345">
       <c r="A345" t="n">
-        <v>122254655</v>
+        <v>122254310</v>
       </c>
       <c r="B345" t="n">
         <v>56285</v>
@@ -47530,21 +47530,21 @@
         </is>
       </c>
       <c r="E345" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
@@ -47568,10 +47568,10 @@
         </is>
       </c>
       <c r="Q345" t="n">
-        <v>586475</v>
+        <v>586452</v>
       </c>
       <c r="R345" t="n">
-        <v>6311187</v>
+        <v>6311156</v>
       </c>
       <c r="S345" t="n">
         <v>5</v>
@@ -47603,7 +47603,7 @@
       </c>
       <c r="Z345" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA345" t="inlineStr">
@@ -47613,7 +47613,7 @@
       </c>
       <c r="AB345" t="inlineStr">
         <is>
-          <t>22:33</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC345" t="inlineStr">
@@ -47658,10 +47658,10 @@
     </row>
     <row r="346">
       <c r="A346" t="n">
-        <v>122254314</v>
+        <v>122254392</v>
       </c>
       <c r="B346" t="n">
-        <v>56280</v>
+        <v>56285</v>
       </c>
       <c r="C346" t="inlineStr">
         <is>
@@ -47712,10 +47712,10 @@
         </is>
       </c>
       <c r="Q346" t="n">
-        <v>586443</v>
+        <v>586384</v>
       </c>
       <c r="R346" t="n">
-        <v>6311164</v>
+        <v>6311139</v>
       </c>
       <c r="S346" t="n">
         <v>5</v>
@@ -47747,7 +47747,7 @@
       </c>
       <c r="Z346" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AA346" t="inlineStr">
@@ -47757,7 +47757,7 @@
       </c>
       <c r="AB346" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>22:46</t>
         </is>
       </c>
       <c r="AC346" t="inlineStr">
@@ -47802,10 +47802,10 @@
     </row>
     <row r="347">
       <c r="A347" t="n">
-        <v>122254862</v>
+        <v>122254856</v>
       </c>
       <c r="B347" t="n">
-        <v>56283</v>
+        <v>56288</v>
       </c>
       <c r="C347" t="inlineStr">
         <is>
@@ -47856,10 +47856,10 @@
         </is>
       </c>
       <c r="Q347" t="n">
-        <v>586288</v>
+        <v>586327</v>
       </c>
       <c r="R347" t="n">
-        <v>6311100</v>
+        <v>6311118</v>
       </c>
       <c r="S347" t="n">
         <v>5</v>
@@ -47891,7 +47891,7 @@
       </c>
       <c r="Z347" t="inlineStr">
         <is>
-          <t>22:55</t>
+          <t>22:57</t>
         </is>
       </c>
       <c r="AA347" t="inlineStr">
@@ -47901,7 +47901,7 @@
       </c>
       <c r="AB347" t="inlineStr">
         <is>
-          <t>22:56</t>
+          <t>22:58</t>
         </is>
       </c>
       <c r="AC347" t="inlineStr">
@@ -47946,10 +47946,10 @@
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>122254391</v>
+        <v>122254950</v>
       </c>
       <c r="B348" t="n">
-        <v>56280</v>
+        <v>56278</v>
       </c>
       <c r="C348" t="inlineStr">
         <is>
@@ -47962,21 +47962,21 @@
         </is>
       </c>
       <c r="E348" t="n">
-        <v>100092</v>
+        <v>205992</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I348" t="inlineStr">
@@ -48000,10 +48000,10 @@
         </is>
       </c>
       <c r="Q348" t="n">
-        <v>586379</v>
+        <v>586482</v>
       </c>
       <c r="R348" t="n">
-        <v>6311136</v>
+        <v>6311185</v>
       </c>
       <c r="S348" t="n">
         <v>5</v>
@@ -48035,7 +48035,7 @@
       </c>
       <c r="Z348" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AA348" t="inlineStr">
@@ -48045,7 +48045,7 @@
       </c>
       <c r="AB348" t="inlineStr">
         <is>
-          <t>22:46</t>
+          <t>23:31</t>
         </is>
       </c>
       <c r="AC348" t="inlineStr">
@@ -48090,10 +48090,10 @@
     </row>
     <row r="349">
       <c r="A349" t="n">
-        <v>122254350</v>
+        <v>122254649</v>
       </c>
       <c r="B349" t="n">
-        <v>56280</v>
+        <v>56290</v>
       </c>
       <c r="C349" t="inlineStr">
         <is>
@@ -48106,21 +48106,21 @@
         </is>
       </c>
       <c r="E349" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I349" t="inlineStr">
@@ -48144,10 +48144,10 @@
         </is>
       </c>
       <c r="Q349" t="n">
-        <v>586330</v>
+        <v>586422</v>
       </c>
       <c r="R349" t="n">
-        <v>6311120</v>
+        <v>6311100</v>
       </c>
       <c r="S349" t="n">
         <v>5</v>
@@ -48179,7 +48179,7 @@
       </c>
       <c r="Z349" t="inlineStr">
         <is>
-          <t>22:57</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="AA349" t="inlineStr">
@@ -48189,7 +48189,7 @@
       </c>
       <c r="AB349" t="inlineStr">
         <is>
-          <t>22:58</t>
+          <t>22:36</t>
         </is>
       </c>
       <c r="AC349" t="inlineStr">
@@ -48234,10 +48234,10 @@
     </row>
     <row r="350">
       <c r="A350" t="n">
-        <v>122254411</v>
+        <v>122254309</v>
       </c>
       <c r="B350" t="n">
-        <v>56280</v>
+        <v>56285</v>
       </c>
       <c r="C350" t="inlineStr">
         <is>
@@ -48288,10 +48288,10 @@
         </is>
       </c>
       <c r="Q350" t="n">
-        <v>586414</v>
+        <v>586456</v>
       </c>
       <c r="R350" t="n">
-        <v>6311126</v>
+        <v>6311158</v>
       </c>
       <c r="S350" t="n">
         <v>5</v>
@@ -48323,7 +48323,7 @@
       </c>
       <c r="Z350" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AA350" t="inlineStr">
@@ -48333,7 +48333,7 @@
       </c>
       <c r="AB350" t="inlineStr">
         <is>
-          <t>22:38</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AC350" t="inlineStr">
@@ -48378,10 +48378,10 @@
     </row>
     <row r="351">
       <c r="A351" t="n">
-        <v>122254584</v>
+        <v>122254476</v>
       </c>
       <c r="B351" t="n">
-        <v>56285</v>
+        <v>56271</v>
       </c>
       <c r="C351" t="inlineStr">
         <is>
@@ -48390,25 +48390,25 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E351" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I351" t="inlineStr">
@@ -48432,10 +48432,10 @@
         </is>
       </c>
       <c r="Q351" t="n">
-        <v>586473</v>
+        <v>586418</v>
       </c>
       <c r="R351" t="n">
-        <v>6311192</v>
+        <v>6311167</v>
       </c>
       <c r="S351" t="n">
         <v>5</v>
@@ -48467,7 +48467,7 @@
       </c>
       <c r="Z351" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>23:23</t>
         </is>
       </c>
       <c r="AA351" t="inlineStr">
@@ -48477,7 +48477,7 @@
       </c>
       <c r="AB351" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="AC351" t="inlineStr">
@@ -48522,32 +48522,32 @@
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>122254173</v>
+        <v>122254350</v>
       </c>
       <c r="B352" t="n">
-        <v>56264</v>
+        <v>56285</v>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Dokumentation efterfrågas</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E352" t="n">
-        <v>100015</v>
+        <v>100092</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>Barbastell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>Barbastella barbastellus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
@@ -48576,10 +48576,10 @@
         </is>
       </c>
       <c r="Q352" t="n">
-        <v>586415</v>
+        <v>586330</v>
       </c>
       <c r="R352" t="n">
-        <v>6311149</v>
+        <v>6311120</v>
       </c>
       <c r="S352" t="n">
         <v>5</v>
@@ -48611,7 +48611,7 @@
       </c>
       <c r="Z352" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>22:57</t>
         </is>
       </c>
       <c r="AA352" t="inlineStr">
@@ -48621,7 +48621,7 @@
       </c>
       <c r="AB352" t="inlineStr">
         <is>
-          <t>23:03</t>
+          <t>22:58</t>
         </is>
       </c>
       <c r="AC352" t="inlineStr">
@@ -48666,10 +48666,10 @@
     </row>
     <row r="353">
       <c r="A353" t="n">
-        <v>122254395</v>
+        <v>122254633</v>
       </c>
       <c r="B353" t="n">
-        <v>56280</v>
+        <v>56290</v>
       </c>
       <c r="C353" t="inlineStr">
         <is>
@@ -48682,21 +48682,21 @@
         </is>
       </c>
       <c r="E353" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I353" t="inlineStr">
@@ -48720,10 +48720,10 @@
         </is>
       </c>
       <c r="Q353" t="n">
-        <v>586408</v>
+        <v>586396</v>
       </c>
       <c r="R353" t="n">
-        <v>6311124</v>
+        <v>6311146</v>
       </c>
       <c r="S353" t="n">
         <v>5</v>
@@ -48755,7 +48755,7 @@
       </c>
       <c r="Z353" t="inlineStr">
         <is>
-          <t>22:43</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AA353" t="inlineStr">
@@ -48765,7 +48765,7 @@
       </c>
       <c r="AB353" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AC353" t="inlineStr">
@@ -48810,10 +48810,10 @@
     </row>
     <row r="354">
       <c r="A354" t="n">
-        <v>122254476</v>
+        <v>122254656</v>
       </c>
       <c r="B354" t="n">
-        <v>56266</v>
+        <v>56290</v>
       </c>
       <c r="C354" t="inlineStr">
         <is>
@@ -48822,25 +48822,25 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E354" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I354" t="inlineStr">
@@ -48864,10 +48864,10 @@
         </is>
       </c>
       <c r="Q354" t="n">
-        <v>586418</v>
+        <v>586483</v>
       </c>
       <c r="R354" t="n">
-        <v>6311167</v>
+        <v>6311186</v>
       </c>
       <c r="S354" t="n">
         <v>5</v>
@@ -48899,7 +48899,7 @@
       </c>
       <c r="Z354" t="inlineStr">
         <is>
-          <t>23:23</t>
+          <t>22:31</t>
         </is>
       </c>
       <c r="AA354" t="inlineStr">
@@ -48909,7 +48909,7 @@
       </c>
       <c r="AB354" t="inlineStr">
         <is>
-          <t>23:24</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AC354" t="inlineStr">
@@ -48954,10 +48954,10 @@
     </row>
     <row r="355">
       <c r="A355" t="n">
-        <v>122254503</v>
+        <v>122254880</v>
       </c>
       <c r="B355" t="n">
-        <v>56266</v>
+        <v>56288</v>
       </c>
       <c r="C355" t="inlineStr">
         <is>
@@ -48966,25 +48966,25 @@
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E355" t="n">
-        <v>205998</v>
+        <v>100111</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I355" t="inlineStr">
@@ -49008,10 +49008,10 @@
         </is>
       </c>
       <c r="Q355" t="n">
-        <v>586313</v>
+        <v>586303</v>
       </c>
       <c r="R355" t="n">
-        <v>6311124</v>
+        <v>6311115</v>
       </c>
       <c r="S355" t="n">
         <v>5</v>
@@ -49098,10 +49098,10 @@
     </row>
     <row r="356">
       <c r="A356" t="n">
-        <v>122254474</v>
+        <v>122254475</v>
       </c>
       <c r="B356" t="n">
-        <v>56266</v>
+        <v>56271</v>
       </c>
       <c r="C356" t="inlineStr">
         <is>
@@ -49152,10 +49152,10 @@
         </is>
       </c>
       <c r="Q356" t="n">
-        <v>586443</v>
+        <v>586420</v>
       </c>
       <c r="R356" t="n">
-        <v>6311164</v>
+        <v>6311166</v>
       </c>
       <c r="S356" t="n">
         <v>5</v>
@@ -49187,7 +49187,7 @@
       </c>
       <c r="Z356" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>23:23</t>
         </is>
       </c>
       <c r="AA356" t="inlineStr">
@@ -49197,7 +49197,7 @@
       </c>
       <c r="AB356" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="AC356" t="inlineStr">
@@ -49242,10 +49242,10 @@
     </row>
     <row r="357">
       <c r="A357" t="n">
-        <v>122254635</v>
+        <v>122254615</v>
       </c>
       <c r="B357" t="n">
-        <v>56285</v>
+        <v>56290</v>
       </c>
       <c r="C357" t="inlineStr">
         <is>
@@ -49296,10 +49296,10 @@
         </is>
       </c>
       <c r="Q357" t="n">
-        <v>586417</v>
+        <v>586329</v>
       </c>
       <c r="R357" t="n">
-        <v>6311145</v>
+        <v>6311120</v>
       </c>
       <c r="S357" t="n">
         <v>5</v>
@@ -49331,7 +49331,7 @@
       </c>
       <c r="Z357" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>22:57</t>
         </is>
       </c>
       <c r="AA357" t="inlineStr">
@@ -49341,7 +49341,7 @@
       </c>
       <c r="AB357" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>22:58</t>
         </is>
       </c>
       <c r="AC357" t="inlineStr">
@@ -49386,10 +49386,10 @@
     </row>
     <row r="358">
       <c r="A358" t="n">
-        <v>122254636</v>
+        <v>122254635</v>
       </c>
       <c r="B358" t="n">
-        <v>56285</v>
+        <v>56290</v>
       </c>
       <c r="C358" t="inlineStr">
         <is>
@@ -49440,7 +49440,7 @@
         </is>
       </c>
       <c r="Q358" t="n">
-        <v>586418</v>
+        <v>586417</v>
       </c>
       <c r="R358" t="n">
         <v>6311145</v>
@@ -49530,10 +49530,10 @@
     </row>
     <row r="359">
       <c r="A359" t="n">
-        <v>122254316</v>
+        <v>122254655</v>
       </c>
       <c r="B359" t="n">
-        <v>56280</v>
+        <v>56290</v>
       </c>
       <c r="C359" t="inlineStr">
         <is>
@@ -49546,21 +49546,21 @@
         </is>
       </c>
       <c r="E359" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I359" t="inlineStr">
@@ -49584,10 +49584,10 @@
         </is>
       </c>
       <c r="Q359" t="n">
-        <v>586423</v>
+        <v>586475</v>
       </c>
       <c r="R359" t="n">
-        <v>6311166</v>
+        <v>6311187</v>
       </c>
       <c r="S359" t="n">
         <v>5</v>
@@ -49619,7 +49619,7 @@
       </c>
       <c r="Z359" t="inlineStr">
         <is>
-          <t>23:23</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AA359" t="inlineStr">
@@ -49629,7 +49629,7 @@
       </c>
       <c r="AB359" t="inlineStr">
         <is>
-          <t>23:24</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="AC359" t="inlineStr">
@@ -49674,10 +49674,10 @@
     </row>
     <row r="360">
       <c r="A360" t="n">
-        <v>122254963</v>
+        <v>122254644</v>
       </c>
       <c r="B360" t="n">
-        <v>56273</v>
+        <v>56290</v>
       </c>
       <c r="C360" t="inlineStr">
         <is>
@@ -49690,21 +49690,21 @@
         </is>
       </c>
       <c r="E360" t="n">
-        <v>205992</v>
+        <v>205995</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I360" t="inlineStr">
@@ -49728,10 +49728,10 @@
         </is>
       </c>
       <c r="Q360" t="n">
-        <v>586374</v>
+        <v>586429</v>
       </c>
       <c r="R360" t="n">
-        <v>6311140</v>
+        <v>6311115</v>
       </c>
       <c r="S360" t="n">
         <v>5</v>
@@ -49763,7 +49763,7 @@
       </c>
       <c r="Z360" t="inlineStr">
         <is>
-          <t>22:46</t>
+          <t>22:36</t>
         </is>
       </c>
       <c r="AA360" t="inlineStr">
@@ -49773,7 +49773,7 @@
       </c>
       <c r="AB360" t="inlineStr">
         <is>
-          <t>22:47</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AC360" t="inlineStr">
@@ -49818,10 +49818,10 @@
     </row>
     <row r="361">
       <c r="A361" t="n">
-        <v>122254951</v>
+        <v>122254412</v>
       </c>
       <c r="B361" t="n">
-        <v>56273</v>
+        <v>56285</v>
       </c>
       <c r="C361" t="inlineStr">
         <is>
@@ -49834,21 +49834,21 @@
         </is>
       </c>
       <c r="E361" t="n">
-        <v>205992</v>
+        <v>100092</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I361" t="inlineStr">
@@ -49872,10 +49872,10 @@
         </is>
       </c>
       <c r="Q361" t="n">
-        <v>586459</v>
+        <v>586424</v>
       </c>
       <c r="R361" t="n">
-        <v>6311154</v>
+        <v>6311135</v>
       </c>
       <c r="S361" t="n">
         <v>5</v>
@@ -49907,7 +49907,7 @@
       </c>
       <c r="Z361" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AA361" t="inlineStr">
@@ -49917,7 +49917,7 @@
       </c>
       <c r="AB361" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>22:38</t>
         </is>
       </c>
       <c r="AC361" t="inlineStr">
@@ -49962,10 +49962,10 @@
     </row>
     <row r="362">
       <c r="A362" t="n">
-        <v>122254845</v>
+        <v>122254316</v>
       </c>
       <c r="B362" t="n">
-        <v>56283</v>
+        <v>56285</v>
       </c>
       <c r="C362" t="inlineStr">
         <is>
@@ -49978,21 +49978,21 @@
         </is>
       </c>
       <c r="E362" t="n">
-        <v>100111</v>
+        <v>100092</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I362" t="inlineStr">
@@ -50016,10 +50016,10 @@
         </is>
       </c>
       <c r="Q362" t="n">
-        <v>586370</v>
+        <v>586423</v>
       </c>
       <c r="R362" t="n">
-        <v>6311139</v>
+        <v>6311166</v>
       </c>
       <c r="S362" t="n">
         <v>5</v>
@@ -50051,7 +50051,7 @@
       </c>
       <c r="Z362" t="inlineStr">
         <is>
-          <t>22:59</t>
+          <t>23:23</t>
         </is>
       </c>
       <c r="AA362" t="inlineStr">
@@ -50061,7 +50061,7 @@
       </c>
       <c r="AB362" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="AC362" t="inlineStr">
@@ -50106,10 +50106,10 @@
     </row>
     <row r="363">
       <c r="A363" t="n">
-        <v>122254308</v>
+        <v>122254855</v>
       </c>
       <c r="B363" t="n">
-        <v>56280</v>
+        <v>56288</v>
       </c>
       <c r="C363" t="inlineStr">
         <is>
@@ -50122,21 +50122,21 @@
         </is>
       </c>
       <c r="E363" t="n">
-        <v>100092</v>
+        <v>100111</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I363" t="inlineStr">
@@ -50160,10 +50160,10 @@
         </is>
       </c>
       <c r="Q363" t="n">
-        <v>586455</v>
+        <v>586330</v>
       </c>
       <c r="R363" t="n">
-        <v>6311159</v>
+        <v>6311120</v>
       </c>
       <c r="S363" t="n">
         <v>5</v>
@@ -50195,7 +50195,7 @@
       </c>
       <c r="Z363" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>22:57</t>
         </is>
       </c>
       <c r="AA363" t="inlineStr">
@@ -50205,7 +50205,7 @@
       </c>
       <c r="AB363" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>22:58</t>
         </is>
       </c>
       <c r="AC363" t="inlineStr">
@@ -50250,10 +50250,10 @@
     </row>
     <row r="364">
       <c r="A364" t="n">
-        <v>122254309</v>
+        <v>122254877</v>
       </c>
       <c r="B364" t="n">
-        <v>56280</v>
+        <v>56288</v>
       </c>
       <c r="C364" t="inlineStr">
         <is>
@@ -50266,21 +50266,21 @@
         </is>
       </c>
       <c r="E364" t="n">
-        <v>100092</v>
+        <v>100111</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I364" t="inlineStr">
@@ -50304,10 +50304,10 @@
         </is>
       </c>
       <c r="Q364" t="n">
-        <v>586456</v>
+        <v>586276</v>
       </c>
       <c r="R364" t="n">
-        <v>6311158</v>
+        <v>6311100</v>
       </c>
       <c r="S364" t="n">
         <v>5</v>
@@ -50339,7 +50339,7 @@
       </c>
       <c r="Z364" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AA364" t="inlineStr">
@@ -50349,7 +50349,7 @@
       </c>
       <c r="AB364" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>22:52</t>
         </is>
       </c>
       <c r="AC364" t="inlineStr">
@@ -50394,10 +50394,10 @@
     </row>
     <row r="365">
       <c r="A365" t="n">
-        <v>122254306</v>
+        <v>122254503</v>
       </c>
       <c r="B365" t="n">
-        <v>56280</v>
+        <v>56271</v>
       </c>
       <c r="C365" t="inlineStr">
         <is>
@@ -50406,25 +50406,25 @@
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E365" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I365" t="inlineStr">
@@ -50448,10 +50448,10 @@
         </is>
       </c>
       <c r="Q365" t="n">
-        <v>586473</v>
+        <v>586313</v>
       </c>
       <c r="R365" t="n">
-        <v>6311192</v>
+        <v>6311124</v>
       </c>
       <c r="S365" t="n">
         <v>5</v>
@@ -50483,7 +50483,7 @@
       </c>
       <c r="Z365" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AA365" t="inlineStr">
@@ -50493,7 +50493,7 @@
       </c>
       <c r="AB365" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AC365" t="inlineStr">
@@ -50538,10 +50538,10 @@
     </row>
     <row r="366">
       <c r="A366" t="n">
-        <v>122254835</v>
+        <v>122254617</v>
       </c>
       <c r="B366" t="n">
-        <v>56283</v>
+        <v>56290</v>
       </c>
       <c r="C366" t="inlineStr">
         <is>
@@ -50554,21 +50554,21 @@
         </is>
       </c>
       <c r="E366" t="n">
-        <v>100111</v>
+        <v>205995</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I366" t="inlineStr">
@@ -50592,10 +50592,10 @@
         </is>
       </c>
       <c r="Q366" t="n">
-        <v>586473</v>
+        <v>586317</v>
       </c>
       <c r="R366" t="n">
-        <v>6311192</v>
+        <v>6311115</v>
       </c>
       <c r="S366" t="n">
         <v>5</v>
@@ -50627,7 +50627,7 @@
       </c>
       <c r="Z366" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>22:57</t>
         </is>
       </c>
       <c r="AA366" t="inlineStr">
@@ -50637,7 +50637,7 @@
       </c>
       <c r="AB366" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>22:58</t>
         </is>
       </c>
       <c r="AC366" t="inlineStr">
@@ -50682,10 +50682,10 @@
     </row>
     <row r="367">
       <c r="A367" t="n">
-        <v>122254626</v>
+        <v>122254637</v>
       </c>
       <c r="B367" t="n">
-        <v>56285</v>
+        <v>56290</v>
       </c>
       <c r="C367" t="inlineStr">
         <is>
@@ -50736,7 +50736,7 @@
         </is>
       </c>
       <c r="Q367" t="n">
-        <v>586313</v>
+        <v>586408</v>
       </c>
       <c r="R367" t="n">
         <v>6311124</v>
@@ -50771,7 +50771,7 @@
       </c>
       <c r="Z367" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>22:43</t>
         </is>
       </c>
       <c r="AA367" t="inlineStr">
@@ -50781,7 +50781,7 @@
       </c>
       <c r="AB367" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AC367" t="inlineStr">
@@ -50826,10 +50826,10 @@
     </row>
     <row r="368">
       <c r="A368" t="n">
-        <v>122254609</v>
+        <v>122254607</v>
       </c>
       <c r="B368" t="n">
-        <v>56285</v>
+        <v>56290</v>
       </c>
       <c r="C368" t="inlineStr">
         <is>
@@ -50880,10 +50880,10 @@
         </is>
       </c>
       <c r="Q368" t="n">
-        <v>586392</v>
+        <v>586415</v>
       </c>
       <c r="R368" t="n">
-        <v>6311147</v>
+        <v>6311149</v>
       </c>
       <c r="S368" t="n">
         <v>5</v>
@@ -50915,7 +50915,7 @@
       </c>
       <c r="Z368" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AA368" t="inlineStr">
@@ -50925,7 +50925,7 @@
       </c>
       <c r="AB368" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>23:03</t>
         </is>
       </c>
       <c r="AC368" t="inlineStr">
@@ -50970,10 +50970,10 @@
     </row>
     <row r="369">
       <c r="A369" t="n">
-        <v>122254352</v>
+        <v>122254657</v>
       </c>
       <c r="B369" t="n">
-        <v>56280</v>
+        <v>56290</v>
       </c>
       <c r="C369" t="inlineStr">
         <is>
@@ -50986,21 +50986,21 @@
         </is>
       </c>
       <c r="E369" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I369" t="inlineStr">
@@ -51024,10 +51024,10 @@
         </is>
       </c>
       <c r="Q369" t="n">
-        <v>586288</v>
+        <v>586488</v>
       </c>
       <c r="R369" t="n">
-        <v>6311100</v>
+        <v>6311184</v>
       </c>
       <c r="S369" t="n">
         <v>5</v>
@@ -51059,7 +51059,7 @@
       </c>
       <c r="Z369" t="inlineStr">
         <is>
-          <t>22:55</t>
+          <t>22:31</t>
         </is>
       </c>
       <c r="AA369" t="inlineStr">
@@ -51069,7 +51069,7 @@
       </c>
       <c r="AB369" t="inlineStr">
         <is>
-          <t>22:56</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AC369" t="inlineStr">
@@ -51114,10 +51114,10 @@
     </row>
     <row r="370">
       <c r="A370" t="n">
-        <v>122254370</v>
+        <v>122254352</v>
       </c>
       <c r="B370" t="n">
-        <v>56280</v>
+        <v>56285</v>
       </c>
       <c r="C370" t="inlineStr">
         <is>
@@ -51168,10 +51168,10 @@
         </is>
       </c>
       <c r="Q370" t="n">
-        <v>586309</v>
+        <v>586288</v>
       </c>
       <c r="R370" t="n">
-        <v>6311119</v>
+        <v>6311100</v>
       </c>
       <c r="S370" t="n">
         <v>5</v>
@@ -51203,7 +51203,7 @@
       </c>
       <c r="Z370" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>22:55</t>
         </is>
       </c>
       <c r="AA370" t="inlineStr">
@@ -51213,7 +51213,7 @@
       </c>
       <c r="AB370" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>22:56</t>
         </is>
       </c>
       <c r="AC370" t="inlineStr">
@@ -51258,10 +51258,10 @@
     </row>
     <row r="371">
       <c r="A371" t="n">
-        <v>122254473</v>
+        <v>122254519</v>
       </c>
       <c r="B371" t="n">
-        <v>56266</v>
+        <v>56271</v>
       </c>
       <c r="C371" t="inlineStr">
         <is>
@@ -51312,10 +51312,10 @@
         </is>
       </c>
       <c r="Q371" t="n">
-        <v>586450</v>
+        <v>586424</v>
       </c>
       <c r="R371" t="n">
-        <v>6311152</v>
+        <v>6311135</v>
       </c>
       <c r="S371" t="n">
         <v>5</v>
@@ -51347,7 +51347,7 @@
       </c>
       <c r="Z371" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AA371" t="inlineStr">
@@ -51357,7 +51357,7 @@
       </c>
       <c r="AB371" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>22:38</t>
         </is>
       </c>
       <c r="AC371" t="inlineStr">
@@ -51402,10 +51402,10 @@
     </row>
     <row r="372">
       <c r="A372" t="n">
-        <v>122254498</v>
+        <v>122254609</v>
       </c>
       <c r="B372" t="n">
-        <v>56266</v>
+        <v>56290</v>
       </c>
       <c r="C372" t="inlineStr">
         <is>
@@ -51414,25 +51414,25 @@
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E372" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I372" t="inlineStr">
@@ -51456,7 +51456,7 @@
         </is>
       </c>
       <c r="Q372" t="n">
-        <v>586393</v>
+        <v>586392</v>
       </c>
       <c r="R372" t="n">
         <v>6311147</v>
@@ -51546,10 +51546,10 @@
     </row>
     <row r="373">
       <c r="A373" t="n">
-        <v>122254654</v>
+        <v>122254632</v>
       </c>
       <c r="B373" t="n">
-        <v>56285</v>
+        <v>56290</v>
       </c>
       <c r="C373" t="inlineStr">
         <is>
@@ -51600,10 +51600,10 @@
         </is>
       </c>
       <c r="Q373" t="n">
-        <v>586467</v>
+        <v>586374</v>
       </c>
       <c r="R373" t="n">
-        <v>6311178</v>
+        <v>6311140</v>
       </c>
       <c r="S373" t="n">
         <v>5</v>
@@ -51635,7 +51635,7 @@
       </c>
       <c r="Z373" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>22:46</t>
         </is>
       </c>
       <c r="AA373" t="inlineStr">
@@ -51645,7 +51645,7 @@
       </c>
       <c r="AB373" t="inlineStr">
         <is>
-          <t>22:33</t>
+          <t>22:47</t>
         </is>
       </c>
       <c r="AC373" t="inlineStr">
@@ -51690,10 +51690,10 @@
     </row>
     <row r="374">
       <c r="A374" t="n">
-        <v>122254653</v>
+        <v>122254636</v>
       </c>
       <c r="B374" t="n">
-        <v>56285</v>
+        <v>56290</v>
       </c>
       <c r="C374" t="inlineStr">
         <is>
@@ -51744,10 +51744,10 @@
         </is>
       </c>
       <c r="Q374" t="n">
-        <v>586430</v>
+        <v>586418</v>
       </c>
       <c r="R374" t="n">
-        <v>6311142</v>
+        <v>6311145</v>
       </c>
       <c r="S374" t="n">
         <v>5</v>
@@ -51779,7 +51779,7 @@
       </c>
       <c r="Z374" t="inlineStr">
         <is>
-          <t>22:33</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AA374" t="inlineStr">
@@ -51789,7 +51789,7 @@
       </c>
       <c r="AB374" t="inlineStr">
         <is>
-          <t>22:34</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AC374" t="inlineStr">
@@ -51834,10 +51834,10 @@
     </row>
     <row r="375">
       <c r="A375" t="n">
-        <v>122254307</v>
+        <v>122254626</v>
       </c>
       <c r="B375" t="n">
-        <v>56280</v>
+        <v>56290</v>
       </c>
       <c r="C375" t="inlineStr">
         <is>
@@ -51850,21 +51850,21 @@
         </is>
       </c>
       <c r="E375" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I375" t="inlineStr">
@@ -51888,10 +51888,10 @@
         </is>
       </c>
       <c r="Q375" t="n">
-        <v>586477</v>
+        <v>586313</v>
       </c>
       <c r="R375" t="n">
-        <v>6311186</v>
+        <v>6311124</v>
       </c>
       <c r="S375" t="n">
         <v>5</v>
@@ -51923,7 +51923,7 @@
       </c>
       <c r="Z375" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AA375" t="inlineStr">
@@ -51933,7 +51933,7 @@
       </c>
       <c r="AB375" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AC375" t="inlineStr">
@@ -51978,10 +51978,10 @@
     </row>
     <row r="376">
       <c r="A376" t="n">
-        <v>122254369</v>
+        <v>122254472</v>
       </c>
       <c r="B376" t="n">
-        <v>56280</v>
+        <v>56271</v>
       </c>
       <c r="C376" t="inlineStr">
         <is>
@@ -51990,25 +51990,25 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E376" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H376" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I376" t="inlineStr">
@@ -52032,10 +52032,10 @@
         </is>
       </c>
       <c r="Q376" t="n">
-        <v>586300</v>
+        <v>586455</v>
       </c>
       <c r="R376" t="n">
-        <v>6311112</v>
+        <v>6311159</v>
       </c>
       <c r="S376" t="n">
         <v>5</v>
@@ -52067,7 +52067,7 @@
       </c>
       <c r="Z376" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AA376" t="inlineStr">
@@ -52077,7 +52077,7 @@
       </c>
       <c r="AB376" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AC376" t="inlineStr">
@@ -52122,10 +52122,10 @@
     </row>
     <row r="377">
       <c r="A377" t="n">
-        <v>122254877</v>
+        <v>122254411</v>
       </c>
       <c r="B377" t="n">
-        <v>56283</v>
+        <v>56285</v>
       </c>
       <c r="C377" t="inlineStr">
         <is>
@@ -52138,21 +52138,21 @@
         </is>
       </c>
       <c r="E377" t="n">
-        <v>100111</v>
+        <v>100092</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H377" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I377" t="inlineStr">
@@ -52176,10 +52176,10 @@
         </is>
       </c>
       <c r="Q377" t="n">
-        <v>586276</v>
+        <v>586414</v>
       </c>
       <c r="R377" t="n">
-        <v>6311100</v>
+        <v>6311126</v>
       </c>
       <c r="S377" t="n">
         <v>5</v>
@@ -52211,7 +52211,7 @@
       </c>
       <c r="Z377" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AA377" t="inlineStr">
@@ -52221,7 +52221,7 @@
       </c>
       <c r="AB377" t="inlineStr">
         <is>
-          <t>22:52</t>
+          <t>22:38</t>
         </is>
       </c>
       <c r="AC377" t="inlineStr">
@@ -52266,10 +52266,10 @@
     </row>
     <row r="378">
       <c r="A378" t="n">
-        <v>122254855</v>
+        <v>122254511</v>
       </c>
       <c r="B378" t="n">
-        <v>56283</v>
+        <v>56271</v>
       </c>
       <c r="C378" t="inlineStr">
         <is>
@@ -52278,25 +52278,25 @@
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E378" t="n">
-        <v>100111</v>
+        <v>205998</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I378" t="inlineStr">
@@ -52320,10 +52320,10 @@
         </is>
       </c>
       <c r="Q378" t="n">
-        <v>586330</v>
+        <v>586374</v>
       </c>
       <c r="R378" t="n">
-        <v>6311120</v>
+        <v>6311139</v>
       </c>
       <c r="S378" t="n">
         <v>5</v>
@@ -52355,7 +52355,7 @@
       </c>
       <c r="Z378" t="inlineStr">
         <is>
-          <t>22:57</t>
+          <t>22:46</t>
         </is>
       </c>
       <c r="AA378" t="inlineStr">
@@ -52365,7 +52365,7 @@
       </c>
       <c r="AB378" t="inlineStr">
         <is>
-          <t>22:58</t>
+          <t>22:47</t>
         </is>
       </c>
       <c r="AC378" t="inlineStr">
@@ -52410,10 +52410,10 @@
     </row>
     <row r="379">
       <c r="A379" t="n">
-        <v>122254857</v>
+        <v>122254499</v>
       </c>
       <c r="B379" t="n">
-        <v>56283</v>
+        <v>56271</v>
       </c>
       <c r="C379" t="inlineStr">
         <is>
@@ -52422,25 +52422,25 @@
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E379" t="n">
-        <v>100111</v>
+        <v>205998</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H379" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I379" t="inlineStr">
@@ -52464,10 +52464,10 @@
         </is>
       </c>
       <c r="Q379" t="n">
-        <v>586317</v>
+        <v>586392</v>
       </c>
       <c r="R379" t="n">
-        <v>6311115</v>
+        <v>6311147</v>
       </c>
       <c r="S379" t="n">
         <v>5</v>
@@ -52499,7 +52499,7 @@
       </c>
       <c r="Z379" t="inlineStr">
         <is>
-          <t>22:57</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AA379" t="inlineStr">
@@ -52509,7 +52509,7 @@
       </c>
       <c r="AB379" t="inlineStr">
         <is>
-          <t>22:58</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AC379" t="inlineStr">
@@ -52554,10 +52554,10 @@
     </row>
     <row r="380">
       <c r="A380" t="n">
-        <v>122254856</v>
+        <v>122254512</v>
       </c>
       <c r="B380" t="n">
-        <v>56283</v>
+        <v>56271</v>
       </c>
       <c r="C380" t="inlineStr">
         <is>
@@ -52566,25 +52566,25 @@
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E380" t="n">
-        <v>100111</v>
+        <v>205998</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H380" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I380" t="inlineStr">
@@ -52608,10 +52608,10 @@
         </is>
       </c>
       <c r="Q380" t="n">
-        <v>586327</v>
+        <v>586379</v>
       </c>
       <c r="R380" t="n">
-        <v>6311118</v>
+        <v>6311136</v>
       </c>
       <c r="S380" t="n">
         <v>5</v>
@@ -52643,7 +52643,7 @@
       </c>
       <c r="Z380" t="inlineStr">
         <is>
-          <t>22:57</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AA380" t="inlineStr">
@@ -52653,7 +52653,7 @@
       </c>
       <c r="AB380" t="inlineStr">
         <is>
-          <t>22:58</t>
+          <t>22:46</t>
         </is>
       </c>
       <c r="AC380" t="inlineStr">
@@ -52698,10 +52698,10 @@
     </row>
     <row r="381">
       <c r="A381" t="n">
-        <v>122254371</v>
+        <v>122254651</v>
       </c>
       <c r="B381" t="n">
-        <v>56280</v>
+        <v>56290</v>
       </c>
       <c r="C381" t="inlineStr">
         <is>
@@ -52714,21 +52714,21 @@
         </is>
       </c>
       <c r="E381" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I381" t="inlineStr">
@@ -52752,10 +52752,10 @@
         </is>
       </c>
       <c r="Q381" t="n">
-        <v>586308</v>
+        <v>586425</v>
       </c>
       <c r="R381" t="n">
-        <v>6311132</v>
+        <v>6311113</v>
       </c>
       <c r="S381" t="n">
         <v>5</v>
@@ -52787,7 +52787,7 @@
       </c>
       <c r="Z381" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="AA381" t="inlineStr">
@@ -52797,7 +52797,7 @@
       </c>
       <c r="AB381" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>22:36</t>
         </is>
       </c>
       <c r="AC381" t="inlineStr">
@@ -52842,10 +52842,10 @@
     </row>
     <row r="382">
       <c r="A382" t="n">
-        <v>122254627</v>
+        <v>122254586</v>
       </c>
       <c r="B382" t="n">
-        <v>56285</v>
+        <v>56290</v>
       </c>
       <c r="C382" t="inlineStr">
         <is>
@@ -52896,10 +52896,10 @@
         </is>
       </c>
       <c r="Q382" t="n">
-        <v>586306</v>
+        <v>586446</v>
       </c>
       <c r="R382" t="n">
-        <v>6311131</v>
+        <v>6311158</v>
       </c>
       <c r="S382" t="n">
         <v>5</v>
@@ -52931,7 +52931,7 @@
       </c>
       <c r="Z382" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AA382" t="inlineStr">
@@ -52941,7 +52941,7 @@
       </c>
       <c r="AB382" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AC382" t="inlineStr">
@@ -52986,10 +52986,10 @@
     </row>
     <row r="383">
       <c r="A383" t="n">
-        <v>122254372</v>
+        <v>122254650</v>
       </c>
       <c r="B383" t="n">
-        <v>56280</v>
+        <v>56290</v>
       </c>
       <c r="C383" t="inlineStr">
         <is>
@@ -53002,21 +53002,21 @@
         </is>
       </c>
       <c r="E383" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I383" t="inlineStr">
@@ -53040,10 +53040,10 @@
         </is>
       </c>
       <c r="Q383" t="n">
-        <v>586306</v>
+        <v>586422</v>
       </c>
       <c r="R383" t="n">
-        <v>6311131</v>
+        <v>6311105</v>
       </c>
       <c r="S383" t="n">
         <v>5</v>
@@ -53075,7 +53075,7 @@
       </c>
       <c r="Z383" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="AA383" t="inlineStr">
@@ -53085,7 +53085,7 @@
       </c>
       <c r="AB383" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>22:36</t>
         </is>
       </c>
       <c r="AC383" t="inlineStr">
@@ -53130,10 +53130,10 @@
     </row>
     <row r="384">
       <c r="A384" t="n">
-        <v>122254657</v>
+        <v>122254653</v>
       </c>
       <c r="B384" t="n">
-        <v>56285</v>
+        <v>56290</v>
       </c>
       <c r="C384" t="inlineStr">
         <is>
@@ -53184,10 +53184,10 @@
         </is>
       </c>
       <c r="Q384" t="n">
-        <v>586488</v>
+        <v>586430</v>
       </c>
       <c r="R384" t="n">
-        <v>6311184</v>
+        <v>6311142</v>
       </c>
       <c r="S384" t="n">
         <v>5</v>
@@ -53219,7 +53219,7 @@
       </c>
       <c r="Z384" t="inlineStr">
         <is>
-          <t>22:31</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="AA384" t="inlineStr">
@@ -53229,7 +53229,7 @@
       </c>
       <c r="AB384" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>22:34</t>
         </is>
       </c>
       <c r="AC384" t="inlineStr">
@@ -53274,10 +53274,10 @@
     </row>
     <row r="385">
       <c r="A385" t="n">
-        <v>122254880</v>
+        <v>122254498</v>
       </c>
       <c r="B385" t="n">
-        <v>56283</v>
+        <v>56271</v>
       </c>
       <c r="C385" t="inlineStr">
         <is>
@@ -53286,25 +53286,25 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E385" t="n">
-        <v>100111</v>
+        <v>205998</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H385" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I385" t="inlineStr">
@@ -53328,10 +53328,10 @@
         </is>
       </c>
       <c r="Q385" t="n">
-        <v>586303</v>
+        <v>586393</v>
       </c>
       <c r="R385" t="n">
-        <v>6311115</v>
+        <v>6311147</v>
       </c>
       <c r="S385" t="n">
         <v>5</v>
@@ -53363,7 +53363,7 @@
       </c>
       <c r="Z385" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AA385" t="inlineStr">
@@ -53373,7 +53373,7 @@
       </c>
       <c r="AB385" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AC385" t="inlineStr">
@@ -53418,7 +53418,7 @@
     </row>
     <row r="386">
       <c r="A386" t="n">
-        <v>122254648</v>
+        <v>122254341</v>
       </c>
       <c r="B386" t="n">
         <v>56285</v>
@@ -53434,21 +53434,21 @@
         </is>
       </c>
       <c r="E386" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H386" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I386" t="inlineStr">
@@ -53472,10 +53472,10 @@
         </is>
       </c>
       <c r="Q386" t="n">
-        <v>586418</v>
+        <v>586415</v>
       </c>
       <c r="R386" t="n">
-        <v>6311107</v>
+        <v>6311146</v>
       </c>
       <c r="S386" t="n">
         <v>5</v>
@@ -53507,7 +53507,7 @@
       </c>
       <c r="Z386" t="inlineStr">
         <is>
-          <t>22:36</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AA386" t="inlineStr">
@@ -53517,7 +53517,7 @@
       </c>
       <c r="AB386" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>23:03</t>
         </is>
       </c>
       <c r="AC386" t="inlineStr">
@@ -53562,7 +53562,7 @@
     </row>
     <row r="387">
       <c r="A387" t="n">
-        <v>122254650</v>
+        <v>122254415</v>
       </c>
       <c r="B387" t="n">
         <v>56285</v>
@@ -53578,21 +53578,21 @@
         </is>
       </c>
       <c r="E387" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I387" t="inlineStr">
@@ -53616,10 +53616,10 @@
         </is>
       </c>
       <c r="Q387" t="n">
-        <v>586422</v>
+        <v>586425</v>
       </c>
       <c r="R387" t="n">
-        <v>6311105</v>
+        <v>6311135</v>
       </c>
       <c r="S387" t="n">
         <v>5</v>
@@ -53651,7 +53651,7 @@
       </c>
       <c r="Z387" t="inlineStr">
         <is>
-          <t>22:35</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AA387" t="inlineStr">
@@ -53661,7 +53661,7 @@
       </c>
       <c r="AB387" t="inlineStr">
         <is>
-          <t>22:36</t>
+          <t>22:38</t>
         </is>
       </c>
       <c r="AC387" t="inlineStr">
@@ -53706,10 +53706,10 @@
     </row>
     <row r="388">
       <c r="A388" t="n">
-        <v>122254610</v>
+        <v>122254843</v>
       </c>
       <c r="B388" t="n">
-        <v>56285</v>
+        <v>56288</v>
       </c>
       <c r="C388" t="inlineStr">
         <is>
@@ -53722,21 +53722,21 @@
         </is>
       </c>
       <c r="E388" t="n">
-        <v>205995</v>
+        <v>100111</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H388" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I388" t="inlineStr">
@@ -53763,7 +53763,7 @@
         <v>586389</v>
       </c>
       <c r="R388" t="n">
-        <v>6311141</v>
+        <v>6311142</v>
       </c>
       <c r="S388" t="n">
         <v>5</v>
@@ -53850,10 +53850,10 @@
     </row>
     <row r="389">
       <c r="A389" t="n">
-        <v>122254612</v>
+        <v>122254966</v>
       </c>
       <c r="B389" t="n">
-        <v>56285</v>
+        <v>56278</v>
       </c>
       <c r="C389" t="inlineStr">
         <is>
@@ -53866,21 +53866,21 @@
         </is>
       </c>
       <c r="E389" t="n">
-        <v>205995</v>
+        <v>205992</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I389" t="inlineStr">
@@ -53904,10 +53904,10 @@
         </is>
       </c>
       <c r="Q389" t="n">
-        <v>586371</v>
+        <v>586467</v>
       </c>
       <c r="R389" t="n">
-        <v>6311135</v>
+        <v>6311178</v>
       </c>
       <c r="S389" t="n">
         <v>5</v>
@@ -53939,7 +53939,7 @@
       </c>
       <c r="Z389" t="inlineStr">
         <is>
-          <t>22:59</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AA389" t="inlineStr">
@@ -53949,7 +53949,7 @@
       </c>
       <c r="AB389" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="AC389" t="inlineStr">
@@ -53994,10 +53994,10 @@
     </row>
     <row r="390">
       <c r="A390" t="n">
-        <v>122254952</v>
+        <v>122254625</v>
       </c>
       <c r="B390" t="n">
-        <v>56273</v>
+        <v>56290</v>
       </c>
       <c r="C390" t="inlineStr">
         <is>
@@ -54010,21 +54010,21 @@
         </is>
       </c>
       <c r="E390" t="n">
-        <v>205992</v>
+        <v>205995</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I390" t="inlineStr">
@@ -54048,10 +54048,10 @@
         </is>
       </c>
       <c r="Q390" t="n">
-        <v>586455</v>
+        <v>586309</v>
       </c>
       <c r="R390" t="n">
-        <v>6311156</v>
+        <v>6311119</v>
       </c>
       <c r="S390" t="n">
         <v>5</v>
@@ -54083,7 +54083,7 @@
       </c>
       <c r="Z390" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AA390" t="inlineStr">
@@ -54093,7 +54093,7 @@
       </c>
       <c r="AB390" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AC390" t="inlineStr">

--- a/artfynd/A 36363-2024 artfynd.xlsx
+++ b/artfynd/A 36363-2024 artfynd.xlsx
@@ -37002,10 +37002,10 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>122254837</v>
+        <v>122254648</v>
       </c>
       <c r="B272" t="n">
-        <v>56288</v>
+        <v>56290</v>
       </c>
       <c r="C272" t="inlineStr">
         <is>
@@ -37018,21 +37018,21 @@
         </is>
       </c>
       <c r="E272" t="n">
-        <v>100111</v>
+        <v>205995</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
@@ -37056,10 +37056,10 @@
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>586448</v>
+        <v>586418</v>
       </c>
       <c r="R272" t="n">
-        <v>6311154</v>
+        <v>6311107</v>
       </c>
       <c r="S272" t="n">
         <v>5</v>
@@ -37091,7 +37091,7 @@
       </c>
       <c r="Z272" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>22:36</t>
         </is>
       </c>
       <c r="AA272" t="inlineStr">
@@ -37101,7 +37101,7 @@
       </c>
       <c r="AB272" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AC272" t="inlineStr">
@@ -37146,10 +37146,10 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>122254420</v>
+        <v>122254963</v>
       </c>
       <c r="B273" t="n">
-        <v>56285</v>
+        <v>56278</v>
       </c>
       <c r="C273" t="inlineStr">
         <is>
@@ -37162,21 +37162,21 @@
         </is>
       </c>
       <c r="E273" t="n">
-        <v>100092</v>
+        <v>205992</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
@@ -37200,10 +37200,10 @@
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>586467</v>
+        <v>586374</v>
       </c>
       <c r="R273" t="n">
-        <v>6311178</v>
+        <v>6311140</v>
       </c>
       <c r="S273" t="n">
         <v>5</v>
@@ -37235,7 +37235,7 @@
       </c>
       <c r="Z273" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>22:46</t>
         </is>
       </c>
       <c r="AA273" t="inlineStr">
@@ -37245,7 +37245,7 @@
       </c>
       <c r="AB273" t="inlineStr">
         <is>
-          <t>22:33</t>
+          <t>22:47</t>
         </is>
       </c>
       <c r="AC273" t="inlineStr">
@@ -37290,7 +37290,7 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>122254413</v>
+        <v>122254396</v>
       </c>
       <c r="B274" t="n">
         <v>56285</v>
@@ -37344,10 +37344,10 @@
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>586423</v>
+        <v>586408</v>
       </c>
       <c r="R274" t="n">
-        <v>6311137</v>
+        <v>6311124</v>
       </c>
       <c r="S274" t="n">
         <v>5</v>
@@ -37379,7 +37379,7 @@
       </c>
       <c r="Z274" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>22:43</t>
         </is>
       </c>
       <c r="AA274" t="inlineStr">
@@ -37389,7 +37389,7 @@
       </c>
       <c r="AB274" t="inlineStr">
         <is>
-          <t>22:38</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AC274" t="inlineStr">
@@ -37434,10 +37434,10 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>122254395</v>
+        <v>122254835</v>
       </c>
       <c r="B275" t="n">
-        <v>56285</v>
+        <v>56288</v>
       </c>
       <c r="C275" t="inlineStr">
         <is>
@@ -37450,21 +37450,21 @@
         </is>
       </c>
       <c r="E275" t="n">
-        <v>100092</v>
+        <v>100111</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
@@ -37488,10 +37488,10 @@
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>586408</v>
+        <v>586473</v>
       </c>
       <c r="R275" t="n">
-        <v>6311124</v>
+        <v>6311192</v>
       </c>
       <c r="S275" t="n">
         <v>5</v>
@@ -37523,7 +37523,7 @@
       </c>
       <c r="Z275" t="inlineStr">
         <is>
-          <t>22:43</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AA275" t="inlineStr">
@@ -37533,7 +37533,7 @@
       </c>
       <c r="AB275" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AC275" t="inlineStr">
@@ -37578,7 +37578,7 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>122254369</v>
+        <v>122254390</v>
       </c>
       <c r="B276" t="n">
         <v>56285</v>
@@ -37632,10 +37632,10 @@
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>586300</v>
+        <v>586374</v>
       </c>
       <c r="R276" t="n">
-        <v>6311112</v>
+        <v>6311139</v>
       </c>
       <c r="S276" t="n">
         <v>5</v>
@@ -37667,7 +37667,7 @@
       </c>
       <c r="Z276" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>22:46</t>
         </is>
       </c>
       <c r="AA276" t="inlineStr">
@@ -37677,7 +37677,7 @@
       </c>
       <c r="AB276" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>22:47</t>
         </is>
       </c>
       <c r="AC276" t="inlineStr">
@@ -37722,7 +37722,7 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>122254371</v>
+        <v>122254308</v>
       </c>
       <c r="B277" t="n">
         <v>56285</v>
@@ -37776,10 +37776,10 @@
         </is>
       </c>
       <c r="Q277" t="n">
-        <v>586308</v>
+        <v>586455</v>
       </c>
       <c r="R277" t="n">
-        <v>6311132</v>
+        <v>6311159</v>
       </c>
       <c r="S277" t="n">
         <v>5</v>
@@ -37811,7 +37811,7 @@
       </c>
       <c r="Z277" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AA277" t="inlineStr">
@@ -37821,7 +37821,7 @@
       </c>
       <c r="AB277" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AC277" t="inlineStr">
@@ -37866,10 +37866,10 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>122254612</v>
+        <v>122254312</v>
       </c>
       <c r="B278" t="n">
-        <v>56290</v>
+        <v>56285</v>
       </c>
       <c r="C278" t="inlineStr">
         <is>
@@ -37882,21 +37882,21 @@
         </is>
       </c>
       <c r="E278" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
@@ -37920,10 +37920,10 @@
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>586371</v>
+        <v>586452</v>
       </c>
       <c r="R278" t="n">
-        <v>6311135</v>
+        <v>6311152</v>
       </c>
       <c r="S278" t="n">
         <v>5</v>
@@ -37955,7 +37955,7 @@
       </c>
       <c r="Z278" t="inlineStr">
         <is>
-          <t>22:59</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA278" t="inlineStr">
@@ -37965,7 +37965,7 @@
       </c>
       <c r="AB278" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC278" t="inlineStr">
@@ -38010,10 +38010,10 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>122254643</v>
+        <v>122254500</v>
       </c>
       <c r="B279" t="n">
-        <v>56290</v>
+        <v>56271</v>
       </c>
       <c r="C279" t="inlineStr">
         <is>
@@ -38022,25 +38022,25 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E279" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
@@ -38064,10 +38064,10 @@
         </is>
       </c>
       <c r="Q279" t="n">
-        <v>586424</v>
+        <v>586388</v>
       </c>
       <c r="R279" t="n">
-        <v>6311135</v>
+        <v>6311142</v>
       </c>
       <c r="S279" t="n">
         <v>5</v>
@@ -38099,7 +38099,7 @@
       </c>
       <c r="Z279" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA279" t="inlineStr">
@@ -38109,7 +38109,7 @@
       </c>
       <c r="AB279" t="inlineStr">
         <is>
-          <t>22:38</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AC279" t="inlineStr">
@@ -38154,10 +38154,10 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>122254342</v>
+        <v>122254652</v>
       </c>
       <c r="B280" t="n">
-        <v>56285</v>
+        <v>56290</v>
       </c>
       <c r="C280" t="inlineStr">
         <is>
@@ -38170,21 +38170,21 @@
         </is>
       </c>
       <c r="E280" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
@@ -38208,10 +38208,10 @@
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>586389</v>
+        <v>586432</v>
       </c>
       <c r="R280" t="n">
-        <v>6311142</v>
+        <v>6311118</v>
       </c>
       <c r="S280" t="n">
         <v>5</v>
@@ -38243,7 +38243,7 @@
       </c>
       <c r="Z280" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:34</t>
         </is>
       </c>
       <c r="AA280" t="inlineStr">
@@ -38253,7 +38253,7 @@
       </c>
       <c r="AB280" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="AC280" t="inlineStr">
@@ -38298,10 +38298,10 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>122254836</v>
+        <v>122254616</v>
       </c>
       <c r="B281" t="n">
-        <v>56288</v>
+        <v>56290</v>
       </c>
       <c r="C281" t="inlineStr">
         <is>
@@ -38314,21 +38314,21 @@
         </is>
       </c>
       <c r="E281" t="n">
-        <v>100111</v>
+        <v>205995</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
@@ -38352,10 +38352,10 @@
         </is>
       </c>
       <c r="Q281" t="n">
-        <v>586474</v>
+        <v>586327</v>
       </c>
       <c r="R281" t="n">
-        <v>6311176</v>
+        <v>6311118</v>
       </c>
       <c r="S281" t="n">
         <v>5</v>
@@ -38387,7 +38387,7 @@
       </c>
       <c r="Z281" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>22:57</t>
         </is>
       </c>
       <c r="AA281" t="inlineStr">
@@ -38397,7 +38397,7 @@
       </c>
       <c r="AB281" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>22:58</t>
         </is>
       </c>
       <c r="AC281" t="inlineStr">
@@ -38442,10 +38442,10 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>122254951</v>
+        <v>122254372</v>
       </c>
       <c r="B282" t="n">
-        <v>56278</v>
+        <v>56285</v>
       </c>
       <c r="C282" t="inlineStr">
         <is>
@@ -38458,21 +38458,21 @@
         </is>
       </c>
       <c r="E282" t="n">
-        <v>205992</v>
+        <v>100092</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
@@ -38496,10 +38496,10 @@
         </is>
       </c>
       <c r="Q282" t="n">
-        <v>586459</v>
+        <v>586306</v>
       </c>
       <c r="R282" t="n">
-        <v>6311154</v>
+        <v>6311131</v>
       </c>
       <c r="S282" t="n">
         <v>5</v>
@@ -38531,7 +38531,7 @@
       </c>
       <c r="Z282" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AA282" t="inlineStr">
@@ -38541,7 +38541,7 @@
       </c>
       <c r="AB282" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AC282" t="inlineStr">
@@ -38586,10 +38586,10 @@
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>122254952</v>
+        <v>122254342</v>
       </c>
       <c r="B283" t="n">
-        <v>56278</v>
+        <v>56285</v>
       </c>
       <c r="C283" t="inlineStr">
         <is>
@@ -38602,21 +38602,21 @@
         </is>
       </c>
       <c r="E283" t="n">
-        <v>205992</v>
+        <v>100092</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
@@ -38640,10 +38640,10 @@
         </is>
       </c>
       <c r="Q283" t="n">
-        <v>586455</v>
+        <v>586389</v>
       </c>
       <c r="R283" t="n">
-        <v>6311156</v>
+        <v>6311142</v>
       </c>
       <c r="S283" t="n">
         <v>5</v>
@@ -38675,7 +38675,7 @@
       </c>
       <c r="Z283" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA283" t="inlineStr">
@@ -38685,7 +38685,7 @@
       </c>
       <c r="AB283" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AC283" t="inlineStr">
@@ -38730,10 +38730,10 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>122254956</v>
+        <v>122254365</v>
       </c>
       <c r="B284" t="n">
-        <v>56278</v>
+        <v>56285</v>
       </c>
       <c r="C284" t="inlineStr">
         <is>
@@ -38746,21 +38746,21 @@
         </is>
       </c>
       <c r="E284" t="n">
-        <v>205992</v>
+        <v>100092</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
@@ -38784,10 +38784,10 @@
         </is>
       </c>
       <c r="Q284" t="n">
-        <v>586441</v>
+        <v>586276</v>
       </c>
       <c r="R284" t="n">
-        <v>6311152</v>
+        <v>6311100</v>
       </c>
       <c r="S284" t="n">
         <v>5</v>
@@ -38819,7 +38819,7 @@
       </c>
       <c r="Z284" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AA284" t="inlineStr">
@@ -38829,7 +38829,7 @@
       </c>
       <c r="AB284" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>22:52</t>
         </is>
       </c>
       <c r="AC284" t="inlineStr">
@@ -38874,10 +38874,10 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>122254588</v>
+        <v>122254843</v>
       </c>
       <c r="B285" t="n">
-        <v>56290</v>
+        <v>56288</v>
       </c>
       <c r="C285" t="inlineStr">
         <is>
@@ -38890,21 +38890,21 @@
         </is>
       </c>
       <c r="E285" t="n">
-        <v>205995</v>
+        <v>100111</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
@@ -38928,10 +38928,10 @@
         </is>
       </c>
       <c r="Q285" t="n">
-        <v>586415</v>
+        <v>586389</v>
       </c>
       <c r="R285" t="n">
-        <v>6311196</v>
+        <v>6311142</v>
       </c>
       <c r="S285" t="n">
         <v>5</v>
@@ -38963,7 +38963,7 @@
       </c>
       <c r="Z285" t="inlineStr">
         <is>
-          <t>23:22</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA285" t="inlineStr">
@@ -38973,7 +38973,7 @@
       </c>
       <c r="AB285" t="inlineStr">
         <is>
-          <t>23:23</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AC285" t="inlineStr">
@@ -39018,7 +39018,7 @@
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>122254608</v>
+        <v>122254637</v>
       </c>
       <c r="B286" t="n">
         <v>56290</v>
@@ -39072,10 +39072,10 @@
         </is>
       </c>
       <c r="Q286" t="n">
-        <v>586393</v>
+        <v>586408</v>
       </c>
       <c r="R286" t="n">
-        <v>6311147</v>
+        <v>6311124</v>
       </c>
       <c r="S286" t="n">
         <v>5</v>
@@ -39107,7 +39107,7 @@
       </c>
       <c r="Z286" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>22:43</t>
         </is>
       </c>
       <c r="AA286" t="inlineStr">
@@ -39117,7 +39117,7 @@
       </c>
       <c r="AB286" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AC286" t="inlineStr">
@@ -39162,7 +39162,7 @@
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>122254654</v>
+        <v>122254659</v>
       </c>
       <c r="B287" t="n">
         <v>56290</v>
@@ -39216,10 +39216,10 @@
         </is>
       </c>
       <c r="Q287" t="n">
-        <v>586467</v>
+        <v>586489</v>
       </c>
       <c r="R287" t="n">
-        <v>6311178</v>
+        <v>6311181</v>
       </c>
       <c r="S287" t="n">
         <v>5</v>
@@ -39251,17 +39251,17 @@
       </c>
       <c r="Z287" t="inlineStr">
         <is>
+          <t>22:31</t>
+        </is>
+      </c>
+      <c r="AA287" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AB287" t="inlineStr">
+        <is>
           <t>22:32</t>
-        </is>
-      </c>
-      <c r="AA287" t="inlineStr">
-        <is>
-          <t>2024-06-26</t>
-        </is>
-      </c>
-      <c r="AB287" t="inlineStr">
-        <is>
-          <t>22:33</t>
         </is>
       </c>
       <c r="AC287" t="inlineStr">
@@ -39306,7 +39306,7 @@
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>122254610</v>
+        <v>122254627</v>
       </c>
       <c r="B288" t="n">
         <v>56290</v>
@@ -39360,10 +39360,10 @@
         </is>
       </c>
       <c r="Q288" t="n">
-        <v>586389</v>
+        <v>586306</v>
       </c>
       <c r="R288" t="n">
-        <v>6311141</v>
+        <v>6311131</v>
       </c>
       <c r="S288" t="n">
         <v>5</v>
@@ -39395,7 +39395,7 @@
       </c>
       <c r="Z288" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AA288" t="inlineStr">
@@ -39405,7 +39405,7 @@
       </c>
       <c r="AB288" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AC288" t="inlineStr">
@@ -39450,10 +39450,10 @@
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>122254616</v>
+        <v>122254412</v>
       </c>
       <c r="B289" t="n">
-        <v>56290</v>
+        <v>56285</v>
       </c>
       <c r="C289" t="inlineStr">
         <is>
@@ -39466,21 +39466,21 @@
         </is>
       </c>
       <c r="E289" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
@@ -39504,10 +39504,10 @@
         </is>
       </c>
       <c r="Q289" t="n">
-        <v>586327</v>
+        <v>586424</v>
       </c>
       <c r="R289" t="n">
-        <v>6311118</v>
+        <v>6311135</v>
       </c>
       <c r="S289" t="n">
         <v>5</v>
@@ -39539,7 +39539,7 @@
       </c>
       <c r="Z289" t="inlineStr">
         <is>
-          <t>22:57</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AA289" t="inlineStr">
@@ -39549,7 +39549,7 @@
       </c>
       <c r="AB289" t="inlineStr">
         <is>
-          <t>22:58</t>
+          <t>22:38</t>
         </is>
       </c>
       <c r="AC289" t="inlineStr">
@@ -39594,10 +39594,10 @@
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>122254372</v>
+        <v>122254880</v>
       </c>
       <c r="B290" t="n">
-        <v>56285</v>
+        <v>56288</v>
       </c>
       <c r="C290" t="inlineStr">
         <is>
@@ -39610,21 +39610,21 @@
         </is>
       </c>
       <c r="E290" t="n">
-        <v>100092</v>
+        <v>100111</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
@@ -39648,10 +39648,10 @@
         </is>
       </c>
       <c r="Q290" t="n">
-        <v>586306</v>
+        <v>586303</v>
       </c>
       <c r="R290" t="n">
-        <v>6311131</v>
+        <v>6311115</v>
       </c>
       <c r="S290" t="n">
         <v>5</v>
@@ -39738,7 +39738,7 @@
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>122254421</v>
+        <v>122254313</v>
       </c>
       <c r="B291" t="n">
         <v>56285</v>
@@ -39792,10 +39792,10 @@
         </is>
       </c>
       <c r="Q291" t="n">
-        <v>586468</v>
+        <v>586449</v>
       </c>
       <c r="R291" t="n">
-        <v>6311181</v>
+        <v>6311155</v>
       </c>
       <c r="S291" t="n">
         <v>5</v>
@@ -39827,7 +39827,7 @@
       </c>
       <c r="Z291" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA291" t="inlineStr">
@@ -39837,7 +39837,7 @@
       </c>
       <c r="AB291" t="inlineStr">
         <is>
-          <t>22:33</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC291" t="inlineStr">
@@ -39882,10 +39882,10 @@
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>122254394</v>
+        <v>122254656</v>
       </c>
       <c r="B292" t="n">
-        <v>56285</v>
+        <v>56290</v>
       </c>
       <c r="C292" t="inlineStr">
         <is>
@@ -39898,21 +39898,21 @@
         </is>
       </c>
       <c r="E292" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
@@ -39936,10 +39936,10 @@
         </is>
       </c>
       <c r="Q292" t="n">
-        <v>586419</v>
+        <v>586483</v>
       </c>
       <c r="R292" t="n">
-        <v>6311142</v>
+        <v>6311186</v>
       </c>
       <c r="S292" t="n">
         <v>5</v>
@@ -39971,7 +39971,7 @@
       </c>
       <c r="Z292" t="inlineStr">
         <is>
-          <t>22:43</t>
+          <t>22:31</t>
         </is>
       </c>
       <c r="AA292" t="inlineStr">
@@ -39981,7 +39981,7 @@
       </c>
       <c r="AB292" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AC292" t="inlineStr">
@@ -40026,10 +40026,10 @@
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>122254313</v>
+        <v>122254660</v>
       </c>
       <c r="B293" t="n">
-        <v>56285</v>
+        <v>56290</v>
       </c>
       <c r="C293" t="inlineStr">
         <is>
@@ -40042,21 +40042,21 @@
         </is>
       </c>
       <c r="E293" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
@@ -40080,10 +40080,10 @@
         </is>
       </c>
       <c r="Q293" t="n">
-        <v>586449</v>
+        <v>586488</v>
       </c>
       <c r="R293" t="n">
-        <v>6311155</v>
+        <v>6311183</v>
       </c>
       <c r="S293" t="n">
         <v>5</v>
@@ -40115,7 +40115,7 @@
       </c>
       <c r="Z293" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>22:31</t>
         </is>
       </c>
       <c r="AA293" t="inlineStr">
@@ -40125,7 +40125,7 @@
       </c>
       <c r="AB293" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AC293" t="inlineStr">
@@ -40170,7 +40170,7 @@
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>122254648</v>
+        <v>122254588</v>
       </c>
       <c r="B294" t="n">
         <v>56290</v>
@@ -40224,10 +40224,10 @@
         </is>
       </c>
       <c r="Q294" t="n">
-        <v>586418</v>
+        <v>586415</v>
       </c>
       <c r="R294" t="n">
-        <v>6311107</v>
+        <v>6311196</v>
       </c>
       <c r="S294" t="n">
         <v>5</v>
@@ -40259,7 +40259,7 @@
       </c>
       <c r="Z294" t="inlineStr">
         <is>
-          <t>22:36</t>
+          <t>23:22</t>
         </is>
       </c>
       <c r="AA294" t="inlineStr">
@@ -40269,7 +40269,7 @@
       </c>
       <c r="AB294" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>23:23</t>
         </is>
       </c>
       <c r="AC294" t="inlineStr">
@@ -40314,10 +40314,10 @@
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>122254584</v>
+        <v>122254959</v>
       </c>
       <c r="B295" t="n">
-        <v>56290</v>
+        <v>56278</v>
       </c>
       <c r="C295" t="inlineStr">
         <is>
@@ -40330,21 +40330,21 @@
         </is>
       </c>
       <c r="E295" t="n">
-        <v>205995</v>
+        <v>205992</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
@@ -40368,10 +40368,10 @@
         </is>
       </c>
       <c r="Q295" t="n">
-        <v>586473</v>
+        <v>586370</v>
       </c>
       <c r="R295" t="n">
-        <v>6311192</v>
+        <v>6311139</v>
       </c>
       <c r="S295" t="n">
         <v>5</v>
@@ -40403,7 +40403,7 @@
       </c>
       <c r="Z295" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>22:59</t>
         </is>
       </c>
       <c r="AA295" t="inlineStr">
@@ -40413,7 +40413,7 @@
       </c>
       <c r="AB295" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AC295" t="inlineStr">
@@ -40458,7 +40458,7 @@
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>122254627</v>
+        <v>122254611</v>
       </c>
       <c r="B296" t="n">
         <v>56290</v>
@@ -40512,10 +40512,10 @@
         </is>
       </c>
       <c r="Q296" t="n">
-        <v>586306</v>
+        <v>586370</v>
       </c>
       <c r="R296" t="n">
-        <v>6311131</v>
+        <v>6311139</v>
       </c>
       <c r="S296" t="n">
         <v>5</v>
@@ -40547,7 +40547,7 @@
       </c>
       <c r="Z296" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>22:59</t>
         </is>
       </c>
       <c r="AA296" t="inlineStr">
@@ -40557,7 +40557,7 @@
       </c>
       <c r="AB296" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AC296" t="inlineStr">
@@ -40602,7 +40602,7 @@
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>122254587</v>
+        <v>122254653</v>
       </c>
       <c r="B297" t="n">
         <v>56290</v>
@@ -40656,10 +40656,10 @@
         </is>
       </c>
       <c r="Q297" t="n">
-        <v>586443</v>
+        <v>586430</v>
       </c>
       <c r="R297" t="n">
-        <v>6311163</v>
+        <v>6311142</v>
       </c>
       <c r="S297" t="n">
         <v>5</v>
@@ -40691,7 +40691,7 @@
       </c>
       <c r="Z297" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="AA297" t="inlineStr">
@@ -40701,7 +40701,7 @@
       </c>
       <c r="AB297" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>22:34</t>
         </is>
       </c>
       <c r="AC297" t="inlineStr">
@@ -40746,10 +40746,10 @@
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>122254611</v>
+        <v>122254964</v>
       </c>
       <c r="B298" t="n">
-        <v>56290</v>
+        <v>56278</v>
       </c>
       <c r="C298" t="inlineStr">
         <is>
@@ -40762,21 +40762,21 @@
         </is>
       </c>
       <c r="E298" t="n">
-        <v>205995</v>
+        <v>205992</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
@@ -40800,10 +40800,10 @@
         </is>
       </c>
       <c r="Q298" t="n">
-        <v>586370</v>
+        <v>586430</v>
       </c>
       <c r="R298" t="n">
-        <v>6311139</v>
+        <v>6311142</v>
       </c>
       <c r="S298" t="n">
         <v>5</v>
@@ -40835,7 +40835,7 @@
       </c>
       <c r="Z298" t="inlineStr">
         <is>
-          <t>22:59</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="AA298" t="inlineStr">
@@ -40845,7 +40845,7 @@
       </c>
       <c r="AB298" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:34</t>
         </is>
       </c>
       <c r="AC298" t="inlineStr">
@@ -40890,10 +40890,10 @@
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>122254513</v>
+        <v>122254418</v>
       </c>
       <c r="B299" t="n">
-        <v>56271</v>
+        <v>56285</v>
       </c>
       <c r="C299" t="inlineStr">
         <is>
@@ -40902,25 +40902,25 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E299" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
@@ -40944,10 +40944,10 @@
         </is>
       </c>
       <c r="Q299" t="n">
-        <v>586396</v>
+        <v>586467</v>
       </c>
       <c r="R299" t="n">
-        <v>6311146</v>
+        <v>6311178</v>
       </c>
       <c r="S299" t="n">
         <v>5</v>
@@ -40979,7 +40979,7 @@
       </c>
       <c r="Z299" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AA299" t="inlineStr">
@@ -40989,7 +40989,7 @@
       </c>
       <c r="AB299" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="AC299" t="inlineStr">
@@ -41034,10 +41034,10 @@
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>122254963</v>
+        <v>122254367</v>
       </c>
       <c r="B300" t="n">
-        <v>56278</v>
+        <v>56285</v>
       </c>
       <c r="C300" t="inlineStr">
         <is>
@@ -41050,21 +41050,21 @@
         </is>
       </c>
       <c r="E300" t="n">
-        <v>205992</v>
+        <v>100092</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
@@ -41088,10 +41088,10 @@
         </is>
       </c>
       <c r="Q300" t="n">
-        <v>586374</v>
+        <v>586280</v>
       </c>
       <c r="R300" t="n">
-        <v>6311140</v>
+        <v>6311103</v>
       </c>
       <c r="S300" t="n">
         <v>5</v>
@@ -41123,7 +41123,7 @@
       </c>
       <c r="Z300" t="inlineStr">
         <is>
-          <t>22:46</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AA300" t="inlineStr">
@@ -41133,7 +41133,7 @@
       </c>
       <c r="AB300" t="inlineStr">
         <is>
-          <t>22:47</t>
+          <t>22:52</t>
         </is>
       </c>
       <c r="AC300" t="inlineStr">
@@ -41178,7 +41178,7 @@
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>122254306</v>
+        <v>122254370</v>
       </c>
       <c r="B301" t="n">
         <v>56285</v>
@@ -41232,10 +41232,10 @@
         </is>
       </c>
       <c r="Q301" t="n">
-        <v>586473</v>
+        <v>586309</v>
       </c>
       <c r="R301" t="n">
-        <v>6311192</v>
+        <v>6311119</v>
       </c>
       <c r="S301" t="n">
         <v>5</v>
@@ -41267,7 +41267,7 @@
       </c>
       <c r="Z301" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AA301" t="inlineStr">
@@ -41277,7 +41277,7 @@
       </c>
       <c r="AB301" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AC301" t="inlineStr">
@@ -41322,10 +41322,10 @@
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>122254846</v>
+        <v>122254417</v>
       </c>
       <c r="B302" t="n">
-        <v>56288</v>
+        <v>56285</v>
       </c>
       <c r="C302" t="inlineStr">
         <is>
@@ -41338,21 +41338,21 @@
         </is>
       </c>
       <c r="E302" t="n">
-        <v>100111</v>
+        <v>100092</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
@@ -41376,10 +41376,10 @@
         </is>
       </c>
       <c r="Q302" t="n">
-        <v>586370</v>
+        <v>586426</v>
       </c>
       <c r="R302" t="n">
-        <v>6311139</v>
+        <v>6311145</v>
       </c>
       <c r="S302" t="n">
         <v>5</v>
@@ -41411,7 +41411,7 @@
       </c>
       <c r="Z302" t="inlineStr">
         <is>
-          <t>22:59</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="AA302" t="inlineStr">
@@ -41421,7 +41421,7 @@
       </c>
       <c r="AB302" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:34</t>
         </is>
       </c>
       <c r="AC302" t="inlineStr">
@@ -41466,10 +41466,10 @@
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>122254957</v>
+        <v>122254309</v>
       </c>
       <c r="B303" t="n">
-        <v>56278</v>
+        <v>56285</v>
       </c>
       <c r="C303" t="inlineStr">
         <is>
@@ -41482,21 +41482,21 @@
         </is>
       </c>
       <c r="E303" t="n">
-        <v>205992</v>
+        <v>100092</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
@@ -41520,10 +41520,10 @@
         </is>
       </c>
       <c r="Q303" t="n">
-        <v>586444</v>
+        <v>586456</v>
       </c>
       <c r="R303" t="n">
-        <v>6311160</v>
+        <v>6311158</v>
       </c>
       <c r="S303" t="n">
         <v>5</v>
@@ -41555,7 +41555,7 @@
       </c>
       <c r="Z303" t="inlineStr">
         <is>
-          <t>23:24</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AA303" t="inlineStr">
@@ -41565,7 +41565,7 @@
       </c>
       <c r="AB303" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AC303" t="inlineStr">
@@ -41610,10 +41610,10 @@
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>122254500</v>
+        <v>122254854</v>
       </c>
       <c r="B304" t="n">
-        <v>56271</v>
+        <v>56288</v>
       </c>
       <c r="C304" t="inlineStr">
         <is>
@@ -41622,25 +41622,25 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E304" t="n">
-        <v>205998</v>
+        <v>100111</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
@@ -41664,10 +41664,10 @@
         </is>
       </c>
       <c r="Q304" t="n">
-        <v>586388</v>
+        <v>586329</v>
       </c>
       <c r="R304" t="n">
-        <v>6311142</v>
+        <v>6311120</v>
       </c>
       <c r="S304" t="n">
         <v>5</v>
@@ -41699,7 +41699,7 @@
       </c>
       <c r="Z304" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:57</t>
         </is>
       </c>
       <c r="AA304" t="inlineStr">
@@ -41709,7 +41709,7 @@
       </c>
       <c r="AB304" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>22:58</t>
         </is>
       </c>
       <c r="AC304" t="inlineStr">
@@ -41754,10 +41754,10 @@
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>122254473</v>
+        <v>122254857</v>
       </c>
       <c r="B305" t="n">
-        <v>56271</v>
+        <v>56288</v>
       </c>
       <c r="C305" t="inlineStr">
         <is>
@@ -41766,25 +41766,25 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E305" t="n">
-        <v>205998</v>
+        <v>100111</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
@@ -41808,10 +41808,10 @@
         </is>
       </c>
       <c r="Q305" t="n">
-        <v>586450</v>
+        <v>586317</v>
       </c>
       <c r="R305" t="n">
-        <v>6311152</v>
+        <v>6311115</v>
       </c>
       <c r="S305" t="n">
         <v>5</v>
@@ -41843,7 +41843,7 @@
       </c>
       <c r="Z305" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>22:57</t>
         </is>
       </c>
       <c r="AA305" t="inlineStr">
@@ -41853,7 +41853,7 @@
       </c>
       <c r="AB305" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>22:58</t>
         </is>
       </c>
       <c r="AC305" t="inlineStr">
@@ -41898,10 +41898,10 @@
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>122254417</v>
+        <v>122254856</v>
       </c>
       <c r="B306" t="n">
-        <v>56285</v>
+        <v>56288</v>
       </c>
       <c r="C306" t="inlineStr">
         <is>
@@ -41914,21 +41914,21 @@
         </is>
       </c>
       <c r="E306" t="n">
-        <v>100092</v>
+        <v>100111</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
@@ -41952,10 +41952,10 @@
         </is>
       </c>
       <c r="Q306" t="n">
-        <v>586426</v>
+        <v>586327</v>
       </c>
       <c r="R306" t="n">
-        <v>6311145</v>
+        <v>6311118</v>
       </c>
       <c r="S306" t="n">
         <v>5</v>
@@ -41987,7 +41987,7 @@
       </c>
       <c r="Z306" t="inlineStr">
         <is>
-          <t>22:33</t>
+          <t>22:57</t>
         </is>
       </c>
       <c r="AA306" t="inlineStr">
@@ -41997,7 +41997,7 @@
       </c>
       <c r="AB306" t="inlineStr">
         <is>
-          <t>22:34</t>
+          <t>22:58</t>
         </is>
       </c>
       <c r="AC306" t="inlineStr">
@@ -42042,10 +42042,10 @@
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>122254315</v>
+        <v>122254511</v>
       </c>
       <c r="B307" t="n">
-        <v>56285</v>
+        <v>56271</v>
       </c>
       <c r="C307" t="inlineStr">
         <is>
@@ -42054,25 +42054,25 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E307" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
@@ -42096,10 +42096,10 @@
         </is>
       </c>
       <c r="Q307" t="n">
-        <v>586441</v>
+        <v>586374</v>
       </c>
       <c r="R307" t="n">
-        <v>6311155</v>
+        <v>6311139</v>
       </c>
       <c r="S307" t="n">
         <v>5</v>
@@ -42131,7 +42131,7 @@
       </c>
       <c r="Z307" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>22:46</t>
         </is>
       </c>
       <c r="AA307" t="inlineStr">
@@ -42141,7 +42141,7 @@
       </c>
       <c r="AB307" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>22:47</t>
         </is>
       </c>
       <c r="AC307" t="inlineStr">
@@ -42186,7 +42186,7 @@
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>122254660</v>
+        <v>122254610</v>
       </c>
       <c r="B308" t="n">
         <v>56290</v>
@@ -42240,10 +42240,10 @@
         </is>
       </c>
       <c r="Q308" t="n">
-        <v>586488</v>
+        <v>586389</v>
       </c>
       <c r="R308" t="n">
-        <v>6311183</v>
+        <v>6311141</v>
       </c>
       <c r="S308" t="n">
         <v>5</v>
@@ -42275,7 +42275,7 @@
       </c>
       <c r="Z308" t="inlineStr">
         <is>
-          <t>22:31</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA308" t="inlineStr">
@@ -42285,7 +42285,7 @@
       </c>
       <c r="AB308" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AC308" t="inlineStr">
@@ -42330,10 +42330,10 @@
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>122254857</v>
+        <v>122254498</v>
       </c>
       <c r="B309" t="n">
-        <v>56288</v>
+        <v>56271</v>
       </c>
       <c r="C309" t="inlineStr">
         <is>
@@ -42342,25 +42342,25 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E309" t="n">
-        <v>100111</v>
+        <v>205998</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
@@ -42384,10 +42384,10 @@
         </is>
       </c>
       <c r="Q309" t="n">
-        <v>586317</v>
+        <v>586393</v>
       </c>
       <c r="R309" t="n">
-        <v>6311115</v>
+        <v>6311147</v>
       </c>
       <c r="S309" t="n">
         <v>5</v>
@@ -42419,7 +42419,7 @@
       </c>
       <c r="Z309" t="inlineStr">
         <is>
-          <t>22:57</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AA309" t="inlineStr">
@@ -42429,7 +42429,7 @@
       </c>
       <c r="AB309" t="inlineStr">
         <is>
-          <t>22:58</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AC309" t="inlineStr">
@@ -42474,7 +42474,7 @@
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>122254862</v>
+        <v>122254837</v>
       </c>
       <c r="B310" t="n">
         <v>56288</v>
@@ -42528,10 +42528,10 @@
         </is>
       </c>
       <c r="Q310" t="n">
-        <v>586288</v>
+        <v>586448</v>
       </c>
       <c r="R310" t="n">
-        <v>6311100</v>
+        <v>6311154</v>
       </c>
       <c r="S310" t="n">
         <v>5</v>
@@ -42563,7 +42563,7 @@
       </c>
       <c r="Z310" t="inlineStr">
         <is>
-          <t>22:55</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA310" t="inlineStr">
@@ -42573,7 +42573,7 @@
       </c>
       <c r="AB310" t="inlineStr">
         <is>
-          <t>22:56</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC310" t="inlineStr">
@@ -42618,14 +42618,14 @@
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>122254514</v>
+        <v>122254173</v>
       </c>
       <c r="B311" t="n">
-        <v>56271</v>
+        <v>56269</v>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Dokumentation efterfrågas</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -42634,21 +42634,21 @@
         </is>
       </c>
       <c r="E311" t="n">
-        <v>205998</v>
+        <v>100015</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Barbastell</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Barbastella barbastellus</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
@@ -42672,10 +42672,10 @@
         </is>
       </c>
       <c r="Q311" t="n">
-        <v>586408</v>
+        <v>586415</v>
       </c>
       <c r="R311" t="n">
-        <v>6311124</v>
+        <v>6311149</v>
       </c>
       <c r="S311" t="n">
         <v>5</v>
@@ -42707,7 +42707,7 @@
       </c>
       <c r="Z311" t="inlineStr">
         <is>
-          <t>22:43</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AA311" t="inlineStr">
@@ -42717,7 +42717,7 @@
       </c>
       <c r="AB311" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>23:03</t>
         </is>
       </c>
       <c r="AC311" t="inlineStr">
@@ -42762,10 +42762,10 @@
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>122254959</v>
+        <v>122254421</v>
       </c>
       <c r="B312" t="n">
-        <v>56278</v>
+        <v>56285</v>
       </c>
       <c r="C312" t="inlineStr">
         <is>
@@ -42778,21 +42778,21 @@
         </is>
       </c>
       <c r="E312" t="n">
-        <v>205992</v>
+        <v>100092</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
@@ -42816,10 +42816,10 @@
         </is>
       </c>
       <c r="Q312" t="n">
-        <v>586370</v>
+        <v>586468</v>
       </c>
       <c r="R312" t="n">
-        <v>6311139</v>
+        <v>6311181</v>
       </c>
       <c r="S312" t="n">
         <v>5</v>
@@ -42851,7 +42851,7 @@
       </c>
       <c r="Z312" t="inlineStr">
         <is>
-          <t>22:59</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AA312" t="inlineStr">
@@ -42861,7 +42861,7 @@
       </c>
       <c r="AB312" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="AC312" t="inlineStr">
@@ -42906,10 +42906,10 @@
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>122254964</v>
+        <v>122254369</v>
       </c>
       <c r="B313" t="n">
-        <v>56278</v>
+        <v>56285</v>
       </c>
       <c r="C313" t="inlineStr">
         <is>
@@ -42922,21 +42922,21 @@
         </is>
       </c>
       <c r="E313" t="n">
-        <v>205992</v>
+        <v>100092</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
@@ -42960,10 +42960,10 @@
         </is>
       </c>
       <c r="Q313" t="n">
-        <v>586430</v>
+        <v>586300</v>
       </c>
       <c r="R313" t="n">
-        <v>6311142</v>
+        <v>6311112</v>
       </c>
       <c r="S313" t="n">
         <v>5</v>
@@ -42995,7 +42995,7 @@
       </c>
       <c r="Z313" t="inlineStr">
         <is>
-          <t>22:33</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AA313" t="inlineStr">
@@ -43005,7 +43005,7 @@
       </c>
       <c r="AB313" t="inlineStr">
         <is>
-          <t>22:34</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AC313" t="inlineStr">
@@ -43050,10 +43050,10 @@
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>122254659</v>
+        <v>122254845</v>
       </c>
       <c r="B314" t="n">
-        <v>56290</v>
+        <v>56288</v>
       </c>
       <c r="C314" t="inlineStr">
         <is>
@@ -43066,21 +43066,21 @@
         </is>
       </c>
       <c r="E314" t="n">
-        <v>205995</v>
+        <v>100111</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
@@ -43104,10 +43104,10 @@
         </is>
       </c>
       <c r="Q314" t="n">
-        <v>586489</v>
+        <v>586370</v>
       </c>
       <c r="R314" t="n">
-        <v>6311181</v>
+        <v>6311139</v>
       </c>
       <c r="S314" t="n">
         <v>5</v>
@@ -43139,7 +43139,7 @@
       </c>
       <c r="Z314" t="inlineStr">
         <is>
-          <t>22:31</t>
+          <t>22:59</t>
         </is>
       </c>
       <c r="AA314" t="inlineStr">
@@ -43149,7 +43149,7 @@
       </c>
       <c r="AB314" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AC314" t="inlineStr">
@@ -43194,7 +43194,7 @@
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>122254308</v>
+        <v>122254317</v>
       </c>
       <c r="B315" t="n">
         <v>56285</v>
@@ -43248,10 +43248,10 @@
         </is>
       </c>
       <c r="Q315" t="n">
-        <v>586455</v>
+        <v>586438</v>
       </c>
       <c r="R315" t="n">
-        <v>6311159</v>
+        <v>6311222</v>
       </c>
       <c r="S315" t="n">
         <v>5</v>
@@ -43283,7 +43283,7 @@
       </c>
       <c r="Z315" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>23:22</t>
         </is>
       </c>
       <c r="AA315" t="inlineStr">
@@ -43293,7 +43293,7 @@
       </c>
       <c r="AB315" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>23:23</t>
         </is>
       </c>
       <c r="AC315" t="inlineStr">
@@ -43338,10 +43338,10 @@
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>122254390</v>
+        <v>122254855</v>
       </c>
       <c r="B316" t="n">
-        <v>56285</v>
+        <v>56288</v>
       </c>
       <c r="C316" t="inlineStr">
         <is>
@@ -43354,21 +43354,21 @@
         </is>
       </c>
       <c r="E316" t="n">
-        <v>100092</v>
+        <v>100111</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
@@ -43392,10 +43392,10 @@
         </is>
       </c>
       <c r="Q316" t="n">
-        <v>586374</v>
+        <v>586330</v>
       </c>
       <c r="R316" t="n">
-        <v>6311139</v>
+        <v>6311120</v>
       </c>
       <c r="S316" t="n">
         <v>5</v>
@@ -43427,7 +43427,7 @@
       </c>
       <c r="Z316" t="inlineStr">
         <is>
-          <t>22:46</t>
+          <t>22:57</t>
         </is>
       </c>
       <c r="AA316" t="inlineStr">
@@ -43437,7 +43437,7 @@
       </c>
       <c r="AB316" t="inlineStr">
         <is>
-          <t>22:47</t>
+          <t>22:58</t>
         </is>
       </c>
       <c r="AC316" t="inlineStr">
@@ -43482,10 +43482,10 @@
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>122254370</v>
+        <v>122254836</v>
       </c>
       <c r="B317" t="n">
-        <v>56285</v>
+        <v>56288</v>
       </c>
       <c r="C317" t="inlineStr">
         <is>
@@ -43498,21 +43498,21 @@
         </is>
       </c>
       <c r="E317" t="n">
-        <v>100092</v>
+        <v>100111</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
@@ -43536,10 +43536,10 @@
         </is>
       </c>
       <c r="Q317" t="n">
-        <v>586309</v>
+        <v>586474</v>
       </c>
       <c r="R317" t="n">
-        <v>6311119</v>
+        <v>6311176</v>
       </c>
       <c r="S317" t="n">
         <v>5</v>
@@ -43571,7 +43571,7 @@
       </c>
       <c r="Z317" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AA317" t="inlineStr">
@@ -43581,7 +43581,7 @@
       </c>
       <c r="AB317" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AC317" t="inlineStr">
@@ -43626,10 +43626,10 @@
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>122254878</v>
+        <v>122254615</v>
       </c>
       <c r="B318" t="n">
-        <v>56288</v>
+        <v>56290</v>
       </c>
       <c r="C318" t="inlineStr">
         <is>
@@ -43642,21 +43642,21 @@
         </is>
       </c>
       <c r="E318" t="n">
-        <v>100111</v>
+        <v>205995</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
@@ -43680,10 +43680,10 @@
         </is>
       </c>
       <c r="Q318" t="n">
-        <v>586280</v>
+        <v>586329</v>
       </c>
       <c r="R318" t="n">
-        <v>6311103</v>
+        <v>6311120</v>
       </c>
       <c r="S318" t="n">
         <v>5</v>
@@ -43715,7 +43715,7 @@
       </c>
       <c r="Z318" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>22:57</t>
         </is>
       </c>
       <c r="AA318" t="inlineStr">
@@ -43725,7 +43725,7 @@
       </c>
       <c r="AB318" t="inlineStr">
         <is>
-          <t>22:52</t>
+          <t>22:58</t>
         </is>
       </c>
       <c r="AC318" t="inlineStr">
@@ -43770,10 +43770,10 @@
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>122254496</v>
+        <v>122254414</v>
       </c>
       <c r="B319" t="n">
-        <v>56271</v>
+        <v>56285</v>
       </c>
       <c r="C319" t="inlineStr">
         <is>
@@ -43782,25 +43782,25 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E319" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
@@ -43824,10 +43824,10 @@
         </is>
       </c>
       <c r="Q319" t="n">
-        <v>586415</v>
+        <v>586423</v>
       </c>
       <c r="R319" t="n">
-        <v>6311146</v>
+        <v>6311137</v>
       </c>
       <c r="S319" t="n">
         <v>5</v>
@@ -43859,7 +43859,7 @@
       </c>
       <c r="Z319" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AA319" t="inlineStr">
@@ -43869,7 +43869,7 @@
       </c>
       <c r="AB319" t="inlineStr">
         <is>
-          <t>23:03</t>
+          <t>22:38</t>
         </is>
       </c>
       <c r="AC319" t="inlineStr">
@@ -43914,10 +43914,10 @@
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>122254658</v>
+        <v>122254393</v>
       </c>
       <c r="B320" t="n">
-        <v>56290</v>
+        <v>56285</v>
       </c>
       <c r="C320" t="inlineStr">
         <is>
@@ -43930,21 +43930,21 @@
         </is>
       </c>
       <c r="E320" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
@@ -43968,10 +43968,10 @@
         </is>
       </c>
       <c r="Q320" t="n">
-        <v>586491</v>
+        <v>586396</v>
       </c>
       <c r="R320" t="n">
-        <v>6311181</v>
+        <v>6311146</v>
       </c>
       <c r="S320" t="n">
         <v>5</v>
@@ -44003,7 +44003,7 @@
       </c>
       <c r="Z320" t="inlineStr">
         <is>
-          <t>22:31</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AA320" t="inlineStr">
@@ -44013,7 +44013,7 @@
       </c>
       <c r="AB320" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AC320" t="inlineStr">
@@ -44058,7 +44058,7 @@
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>122254343</v>
+        <v>122254394</v>
       </c>
       <c r="B321" t="n">
         <v>56285</v>
@@ -44112,7 +44112,7 @@
         </is>
       </c>
       <c r="Q321" t="n">
-        <v>586388</v>
+        <v>586419</v>
       </c>
       <c r="R321" t="n">
         <v>6311142</v>
@@ -44147,7 +44147,7 @@
       </c>
       <c r="Z321" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:43</t>
         </is>
       </c>
       <c r="AA321" t="inlineStr">
@@ -44157,7 +44157,7 @@
       </c>
       <c r="AB321" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AC321" t="inlineStr">
@@ -44202,10 +44202,10 @@
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>122254367</v>
+        <v>122254499</v>
       </c>
       <c r="B322" t="n">
-        <v>56285</v>
+        <v>56271</v>
       </c>
       <c r="C322" t="inlineStr">
         <is>
@@ -44214,25 +44214,25 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E322" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
@@ -44256,10 +44256,10 @@
         </is>
       </c>
       <c r="Q322" t="n">
-        <v>586280</v>
+        <v>586392</v>
       </c>
       <c r="R322" t="n">
-        <v>6311103</v>
+        <v>6311147</v>
       </c>
       <c r="S322" t="n">
         <v>5</v>
@@ -44291,7 +44291,7 @@
       </c>
       <c r="Z322" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AA322" t="inlineStr">
@@ -44301,7 +44301,7 @@
       </c>
       <c r="AB322" t="inlineStr">
         <is>
-          <t>22:52</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AC322" t="inlineStr">
@@ -44346,10 +44346,10 @@
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>122254314</v>
+        <v>122254626</v>
       </c>
       <c r="B323" t="n">
-        <v>56285</v>
+        <v>56290</v>
       </c>
       <c r="C323" t="inlineStr">
         <is>
@@ -44362,21 +44362,21 @@
         </is>
       </c>
       <c r="E323" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
@@ -44400,10 +44400,10 @@
         </is>
       </c>
       <c r="Q323" t="n">
-        <v>586443</v>
+        <v>586313</v>
       </c>
       <c r="R323" t="n">
-        <v>6311164</v>
+        <v>6311124</v>
       </c>
       <c r="S323" t="n">
         <v>5</v>
@@ -44435,7 +44435,7 @@
       </c>
       <c r="Z323" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AA323" t="inlineStr">
@@ -44445,7 +44445,7 @@
       </c>
       <c r="AB323" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AC323" t="inlineStr">
@@ -44490,10 +44490,10 @@
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>122254365</v>
+        <v>122254612</v>
       </c>
       <c r="B324" t="n">
-        <v>56285</v>
+        <v>56290</v>
       </c>
       <c r="C324" t="inlineStr">
         <is>
@@ -44506,21 +44506,21 @@
         </is>
       </c>
       <c r="E324" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
@@ -44544,10 +44544,10 @@
         </is>
       </c>
       <c r="Q324" t="n">
-        <v>586276</v>
+        <v>586371</v>
       </c>
       <c r="R324" t="n">
-        <v>6311100</v>
+        <v>6311135</v>
       </c>
       <c r="S324" t="n">
         <v>5</v>
@@ -44579,7 +44579,7 @@
       </c>
       <c r="Z324" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>22:59</t>
         </is>
       </c>
       <c r="AA324" t="inlineStr">
@@ -44589,7 +44589,7 @@
       </c>
       <c r="AB324" t="inlineStr">
         <is>
-          <t>22:52</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AC324" t="inlineStr">
@@ -44634,10 +44634,10 @@
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>122254393</v>
+        <v>122254644</v>
       </c>
       <c r="B325" t="n">
-        <v>56285</v>
+        <v>56290</v>
       </c>
       <c r="C325" t="inlineStr">
         <is>
@@ -44650,21 +44650,21 @@
         </is>
       </c>
       <c r="E325" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
@@ -44688,10 +44688,10 @@
         </is>
       </c>
       <c r="Q325" t="n">
-        <v>586396</v>
+        <v>586429</v>
       </c>
       <c r="R325" t="n">
-        <v>6311146</v>
+        <v>6311115</v>
       </c>
       <c r="S325" t="n">
         <v>5</v>
@@ -44723,7 +44723,7 @@
       </c>
       <c r="Z325" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>22:36</t>
         </is>
       </c>
       <c r="AA325" t="inlineStr">
@@ -44733,7 +44733,7 @@
       </c>
       <c r="AB325" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AC325" t="inlineStr">
@@ -44778,10 +44778,10 @@
     </row>
     <row r="326">
       <c r="A326" t="n">
-        <v>122254318</v>
+        <v>122254587</v>
       </c>
       <c r="B326" t="n">
-        <v>56285</v>
+        <v>56290</v>
       </c>
       <c r="C326" t="inlineStr">
         <is>
@@ -44794,21 +44794,21 @@
         </is>
       </c>
       <c r="E326" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
@@ -44832,10 +44832,10 @@
         </is>
       </c>
       <c r="Q326" t="n">
-        <v>586455</v>
+        <v>586443</v>
       </c>
       <c r="R326" t="n">
-        <v>6311228</v>
+        <v>6311163</v>
       </c>
       <c r="S326" t="n">
         <v>5</v>
@@ -44867,7 +44867,7 @@
       </c>
       <c r="Z326" t="inlineStr">
         <is>
-          <t>23:22</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AA326" t="inlineStr">
@@ -44877,7 +44877,7 @@
       </c>
       <c r="AB326" t="inlineStr">
         <is>
-          <t>23:23</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AC326" t="inlineStr">
@@ -44922,7 +44922,7 @@
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>122254391</v>
+        <v>122254314</v>
       </c>
       <c r="B327" t="n">
         <v>56285</v>
@@ -44976,10 +44976,10 @@
         </is>
       </c>
       <c r="Q327" t="n">
-        <v>586379</v>
+        <v>586443</v>
       </c>
       <c r="R327" t="n">
-        <v>6311136</v>
+        <v>6311164</v>
       </c>
       <c r="S327" t="n">
         <v>5</v>
@@ -45011,7 +45011,7 @@
       </c>
       <c r="Z327" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AA327" t="inlineStr">
@@ -45021,7 +45021,7 @@
       </c>
       <c r="AB327" t="inlineStr">
         <is>
-          <t>22:46</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AC327" t="inlineStr">
@@ -45066,7 +45066,7 @@
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>122254312</v>
+        <v>122254315</v>
       </c>
       <c r="B328" t="n">
         <v>56285</v>
@@ -45120,10 +45120,10 @@
         </is>
       </c>
       <c r="Q328" t="n">
-        <v>586452</v>
+        <v>586441</v>
       </c>
       <c r="R328" t="n">
-        <v>6311152</v>
+        <v>6311155</v>
       </c>
       <c r="S328" t="n">
         <v>5</v>
@@ -45155,7 +45155,7 @@
       </c>
       <c r="Z328" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AA328" t="inlineStr">
@@ -45165,7 +45165,7 @@
       </c>
       <c r="AB328" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AC328" t="inlineStr">
@@ -45210,10 +45210,10 @@
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>122254474</v>
+        <v>122254343</v>
       </c>
       <c r="B329" t="n">
-        <v>56271</v>
+        <v>56285</v>
       </c>
       <c r="C329" t="inlineStr">
         <is>
@@ -45222,25 +45222,25 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E329" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
@@ -45264,10 +45264,10 @@
         </is>
       </c>
       <c r="Q329" t="n">
-        <v>586443</v>
+        <v>586388</v>
       </c>
       <c r="R329" t="n">
-        <v>6311164</v>
+        <v>6311142</v>
       </c>
       <c r="S329" t="n">
         <v>5</v>
@@ -45299,7 +45299,7 @@
       </c>
       <c r="Z329" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA329" t="inlineStr">
@@ -45309,7 +45309,7 @@
       </c>
       <c r="AB329" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AC329" t="inlineStr">
@@ -45354,10 +45354,10 @@
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>122254646</v>
+        <v>122254862</v>
       </c>
       <c r="B330" t="n">
-        <v>56290</v>
+        <v>56288</v>
       </c>
       <c r="C330" t="inlineStr">
         <is>
@@ -45370,21 +45370,21 @@
         </is>
       </c>
       <c r="E330" t="n">
-        <v>205995</v>
+        <v>100111</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
@@ -45408,10 +45408,10 @@
         </is>
       </c>
       <c r="Q330" t="n">
-        <v>586422</v>
+        <v>586288</v>
       </c>
       <c r="R330" t="n">
-        <v>6311111</v>
+        <v>6311100</v>
       </c>
       <c r="S330" t="n">
         <v>5</v>
@@ -45443,7 +45443,7 @@
       </c>
       <c r="Z330" t="inlineStr">
         <is>
-          <t>22:36</t>
+          <t>22:55</t>
         </is>
       </c>
       <c r="AA330" t="inlineStr">
@@ -45453,7 +45453,7 @@
       </c>
       <c r="AB330" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>22:56</t>
         </is>
       </c>
       <c r="AC330" t="inlineStr">
@@ -45498,10 +45498,10 @@
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>122254953</v>
+        <v>122254632</v>
       </c>
       <c r="B331" t="n">
-        <v>56278</v>
+        <v>56290</v>
       </c>
       <c r="C331" t="inlineStr">
         <is>
@@ -45514,21 +45514,21 @@
         </is>
       </c>
       <c r="E331" t="n">
-        <v>205992</v>
+        <v>205995</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I331" t="inlineStr">
@@ -45552,10 +45552,10 @@
         </is>
       </c>
       <c r="Q331" t="n">
-        <v>586449</v>
+        <v>586374</v>
       </c>
       <c r="R331" t="n">
-        <v>6311155</v>
+        <v>6311140</v>
       </c>
       <c r="S331" t="n">
         <v>5</v>
@@ -45587,7 +45587,7 @@
       </c>
       <c r="Z331" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>22:46</t>
         </is>
       </c>
       <c r="AA331" t="inlineStr">
@@ -45597,7 +45597,7 @@
       </c>
       <c r="AB331" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>22:47</t>
         </is>
       </c>
       <c r="AC331" t="inlineStr">
@@ -45642,10 +45642,10 @@
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>122254652</v>
+        <v>122254476</v>
       </c>
       <c r="B332" t="n">
-        <v>56290</v>
+        <v>56271</v>
       </c>
       <c r="C332" t="inlineStr">
         <is>
@@ -45654,25 +45654,25 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E332" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
@@ -45696,10 +45696,10 @@
         </is>
       </c>
       <c r="Q332" t="n">
-        <v>586432</v>
+        <v>586418</v>
       </c>
       <c r="R332" t="n">
-        <v>6311118</v>
+        <v>6311167</v>
       </c>
       <c r="S332" t="n">
         <v>5</v>
@@ -45731,7 +45731,7 @@
       </c>
       <c r="Z332" t="inlineStr">
         <is>
-          <t>22:34</t>
+          <t>23:23</t>
         </is>
       </c>
       <c r="AA332" t="inlineStr">
@@ -45741,7 +45741,7 @@
       </c>
       <c r="AB332" t="inlineStr">
         <is>
-          <t>22:35</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="AC332" t="inlineStr">
@@ -45786,10 +45786,10 @@
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>122254317</v>
+        <v>122254950</v>
       </c>
       <c r="B333" t="n">
-        <v>56285</v>
+        <v>56278</v>
       </c>
       <c r="C333" t="inlineStr">
         <is>
@@ -45802,21 +45802,21 @@
         </is>
       </c>
       <c r="E333" t="n">
-        <v>100092</v>
+        <v>205992</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
@@ -45840,10 +45840,10 @@
         </is>
       </c>
       <c r="Q333" t="n">
-        <v>586438</v>
+        <v>586482</v>
       </c>
       <c r="R333" t="n">
-        <v>6311222</v>
+        <v>6311185</v>
       </c>
       <c r="S333" t="n">
         <v>5</v>
@@ -45875,7 +45875,7 @@
       </c>
       <c r="Z333" t="inlineStr">
         <is>
-          <t>23:22</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AA333" t="inlineStr">
@@ -45885,7 +45885,7 @@
       </c>
       <c r="AB333" t="inlineStr">
         <is>
-          <t>23:23</t>
+          <t>23:31</t>
         </is>
       </c>
       <c r="AC333" t="inlineStr">
@@ -45930,10 +45930,10 @@
     </row>
     <row r="334">
       <c r="A334" t="n">
-        <v>122254307</v>
+        <v>122254956</v>
       </c>
       <c r="B334" t="n">
-        <v>56285</v>
+        <v>56278</v>
       </c>
       <c r="C334" t="inlineStr">
         <is>
@@ -45946,21 +45946,21 @@
         </is>
       </c>
       <c r="E334" t="n">
-        <v>100092</v>
+        <v>205992</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
@@ -45984,10 +45984,10 @@
         </is>
       </c>
       <c r="Q334" t="n">
-        <v>586477</v>
+        <v>586441</v>
       </c>
       <c r="R334" t="n">
-        <v>6311186</v>
+        <v>6311152</v>
       </c>
       <c r="S334" t="n">
         <v>5</v>
@@ -46019,7 +46019,7 @@
       </c>
       <c r="Z334" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AA334" t="inlineStr">
@@ -46029,7 +46029,7 @@
       </c>
       <c r="AB334" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AC334" t="inlineStr">
@@ -46074,32 +46074,32 @@
     </row>
     <row r="335">
       <c r="A335" t="n">
-        <v>122254173</v>
+        <v>122254416</v>
       </c>
       <c r="B335" t="n">
-        <v>56269</v>
+        <v>56285</v>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Dokumentation efterfrågas</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E335" t="n">
-        <v>100015</v>
+        <v>100092</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>Barbastell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>Barbastella barbastellus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
@@ -46128,10 +46128,10 @@
         </is>
       </c>
       <c r="Q335" t="n">
-        <v>586415</v>
+        <v>586410</v>
       </c>
       <c r="R335" t="n">
-        <v>6311149</v>
+        <v>6311140</v>
       </c>
       <c r="S335" t="n">
         <v>5</v>
@@ -46163,7 +46163,7 @@
       </c>
       <c r="Z335" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="AA335" t="inlineStr">
@@ -46173,7 +46173,7 @@
       </c>
       <c r="AB335" t="inlineStr">
         <is>
-          <t>23:03</t>
+          <t>22:34</t>
         </is>
       </c>
       <c r="AC335" t="inlineStr">
@@ -46218,10 +46218,10 @@
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>122254844</v>
+        <v>122254514</v>
       </c>
       <c r="B336" t="n">
-        <v>56288</v>
+        <v>56271</v>
       </c>
       <c r="C336" t="inlineStr">
         <is>
@@ -46230,25 +46230,25 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E336" t="n">
-        <v>100111</v>
+        <v>205998</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
@@ -46272,10 +46272,10 @@
         </is>
       </c>
       <c r="Q336" t="n">
-        <v>586387</v>
+        <v>586408</v>
       </c>
       <c r="R336" t="n">
-        <v>6311141</v>
+        <v>6311124</v>
       </c>
       <c r="S336" t="n">
         <v>5</v>
@@ -46307,7 +46307,7 @@
       </c>
       <c r="Z336" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:43</t>
         </is>
       </c>
       <c r="AA336" t="inlineStr">
@@ -46317,7 +46317,7 @@
       </c>
       <c r="AB336" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AC336" t="inlineStr">
@@ -46362,10 +46362,10 @@
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>122254954</v>
+        <v>122254617</v>
       </c>
       <c r="B337" t="n">
-        <v>56278</v>
+        <v>56290</v>
       </c>
       <c r="C337" t="inlineStr">
         <is>
@@ -46378,21 +46378,21 @@
         </is>
       </c>
       <c r="E337" t="n">
-        <v>205992</v>
+        <v>205995</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
@@ -46416,10 +46416,10 @@
         </is>
       </c>
       <c r="Q337" t="n">
-        <v>586442</v>
+        <v>586317</v>
       </c>
       <c r="R337" t="n">
-        <v>6311152</v>
+        <v>6311115</v>
       </c>
       <c r="S337" t="n">
         <v>5</v>
@@ -46451,7 +46451,7 @@
       </c>
       <c r="Z337" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>22:57</t>
         </is>
       </c>
       <c r="AA337" t="inlineStr">
@@ -46461,7 +46461,7 @@
       </c>
       <c r="AB337" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>22:58</t>
         </is>
       </c>
       <c r="AC337" t="inlineStr">
@@ -46506,7 +46506,7 @@
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>122254606</v>
+        <v>122254655</v>
       </c>
       <c r="B338" t="n">
         <v>56290</v>
@@ -46560,10 +46560,10 @@
         </is>
       </c>
       <c r="Q338" t="n">
-        <v>586415</v>
+        <v>586475</v>
       </c>
       <c r="R338" t="n">
-        <v>6311146</v>
+        <v>6311187</v>
       </c>
       <c r="S338" t="n">
         <v>5</v>
@@ -46595,7 +46595,7 @@
       </c>
       <c r="Z338" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AA338" t="inlineStr">
@@ -46605,7 +46605,7 @@
       </c>
       <c r="AB338" t="inlineStr">
         <is>
-          <t>23:03</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="AC338" t="inlineStr">
@@ -46650,10 +46650,10 @@
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>122254835</v>
+        <v>122254651</v>
       </c>
       <c r="B339" t="n">
-        <v>56288</v>
+        <v>56290</v>
       </c>
       <c r="C339" t="inlineStr">
         <is>
@@ -46666,21 +46666,21 @@
         </is>
       </c>
       <c r="E339" t="n">
-        <v>100111</v>
+        <v>205995</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I339" t="inlineStr">
@@ -46704,10 +46704,10 @@
         </is>
       </c>
       <c r="Q339" t="n">
-        <v>586473</v>
+        <v>586425</v>
       </c>
       <c r="R339" t="n">
-        <v>6311192</v>
+        <v>6311113</v>
       </c>
       <c r="S339" t="n">
         <v>5</v>
@@ -46739,7 +46739,7 @@
       </c>
       <c r="Z339" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="AA339" t="inlineStr">
@@ -46749,7 +46749,7 @@
       </c>
       <c r="AB339" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>22:36</t>
         </is>
       </c>
       <c r="AC339" t="inlineStr">
@@ -46794,10 +46794,10 @@
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>122254854</v>
+        <v>122254952</v>
       </c>
       <c r="B340" t="n">
-        <v>56288</v>
+        <v>56278</v>
       </c>
       <c r="C340" t="inlineStr">
         <is>
@@ -46810,21 +46810,21 @@
         </is>
       </c>
       <c r="E340" t="n">
-        <v>100111</v>
+        <v>205992</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
@@ -46848,10 +46848,10 @@
         </is>
       </c>
       <c r="Q340" t="n">
-        <v>586329</v>
+        <v>586455</v>
       </c>
       <c r="R340" t="n">
-        <v>6311120</v>
+        <v>6311156</v>
       </c>
       <c r="S340" t="n">
         <v>5</v>
@@ -46883,7 +46883,7 @@
       </c>
       <c r="Z340" t="inlineStr">
         <is>
-          <t>22:57</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AA340" t="inlineStr">
@@ -46893,7 +46893,7 @@
       </c>
       <c r="AB340" t="inlineStr">
         <is>
-          <t>22:58</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AC340" t="inlineStr">
@@ -46938,10 +46938,10 @@
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>122254416</v>
+        <v>122254953</v>
       </c>
       <c r="B341" t="n">
-        <v>56285</v>
+        <v>56278</v>
       </c>
       <c r="C341" t="inlineStr">
         <is>
@@ -46954,21 +46954,21 @@
         </is>
       </c>
       <c r="E341" t="n">
-        <v>100092</v>
+        <v>205992</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I341" t="inlineStr">
@@ -46992,10 +46992,10 @@
         </is>
       </c>
       <c r="Q341" t="n">
-        <v>586410</v>
+        <v>586449</v>
       </c>
       <c r="R341" t="n">
-        <v>6311140</v>
+        <v>6311155</v>
       </c>
       <c r="S341" t="n">
         <v>5</v>
@@ -47027,7 +47027,7 @@
       </c>
       <c r="Z341" t="inlineStr">
         <is>
-          <t>22:33</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA341" t="inlineStr">
@@ -47037,7 +47037,7 @@
       </c>
       <c r="AB341" t="inlineStr">
         <is>
-          <t>22:34</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC341" t="inlineStr">
@@ -47082,10 +47082,10 @@
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>122254634</v>
+        <v>122254512</v>
       </c>
       <c r="B342" t="n">
-        <v>56290</v>
+        <v>56271</v>
       </c>
       <c r="C342" t="inlineStr">
         <is>
@@ -47094,25 +47094,25 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E342" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
@@ -47136,10 +47136,10 @@
         </is>
       </c>
       <c r="Q342" t="n">
-        <v>586415</v>
+        <v>586379</v>
       </c>
       <c r="R342" t="n">
-        <v>6311148</v>
+        <v>6311136</v>
       </c>
       <c r="S342" t="n">
         <v>5</v>
@@ -47171,7 +47171,7 @@
       </c>
       <c r="Z342" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AA342" t="inlineStr">
@@ -47181,7 +47181,7 @@
       </c>
       <c r="AB342" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>22:46</t>
         </is>
       </c>
       <c r="AC342" t="inlineStr">
@@ -47226,7 +47226,7 @@
     </row>
     <row r="343">
       <c r="A343" t="n">
-        <v>122254585</v>
+        <v>122254608</v>
       </c>
       <c r="B343" t="n">
         <v>56290</v>
@@ -47280,10 +47280,10 @@
         </is>
       </c>
       <c r="Q343" t="n">
-        <v>586455</v>
+        <v>586393</v>
       </c>
       <c r="R343" t="n">
-        <v>6311156</v>
+        <v>6311147</v>
       </c>
       <c r="S343" t="n">
         <v>5</v>
@@ -47315,7 +47315,7 @@
       </c>
       <c r="Z343" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AA343" t="inlineStr">
@@ -47325,7 +47325,7 @@
       </c>
       <c r="AB343" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AC343" t="inlineStr">
@@ -47370,10 +47370,10 @@
     </row>
     <row r="344">
       <c r="A344" t="n">
-        <v>122254373</v>
+        <v>122254503</v>
       </c>
       <c r="B344" t="n">
-        <v>56285</v>
+        <v>56271</v>
       </c>
       <c r="C344" t="inlineStr">
         <is>
@@ -47382,25 +47382,25 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E344" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
@@ -47424,10 +47424,10 @@
         </is>
       </c>
       <c r="Q344" t="n">
-        <v>586307</v>
+        <v>586313</v>
       </c>
       <c r="R344" t="n">
-        <v>6311133</v>
+        <v>6311124</v>
       </c>
       <c r="S344" t="n">
         <v>5</v>
@@ -47459,7 +47459,7 @@
       </c>
       <c r="Z344" t="inlineStr">
         <is>
-          <t>22:49</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AA344" t="inlineStr">
@@ -47469,7 +47469,7 @@
       </c>
       <c r="AB344" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AC344" t="inlineStr">
@@ -47514,10 +47514,10 @@
     </row>
     <row r="345">
       <c r="A345" t="n">
-        <v>122254310</v>
+        <v>122254513</v>
       </c>
       <c r="B345" t="n">
-        <v>56285</v>
+        <v>56271</v>
       </c>
       <c r="C345" t="inlineStr">
         <is>
@@ -47526,25 +47526,25 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E345" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
@@ -47568,10 +47568,10 @@
         </is>
       </c>
       <c r="Q345" t="n">
-        <v>586452</v>
+        <v>586396</v>
       </c>
       <c r="R345" t="n">
-        <v>6311156</v>
+        <v>6311146</v>
       </c>
       <c r="S345" t="n">
         <v>5</v>
@@ -47603,7 +47603,7 @@
       </c>
       <c r="Z345" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AA345" t="inlineStr">
@@ -47613,7 +47613,7 @@
       </c>
       <c r="AB345" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AC345" t="inlineStr">
@@ -47658,7 +47658,7 @@
     </row>
     <row r="346">
       <c r="A346" t="n">
-        <v>122254392</v>
+        <v>122254307</v>
       </c>
       <c r="B346" t="n">
         <v>56285</v>
@@ -47712,10 +47712,10 @@
         </is>
       </c>
       <c r="Q346" t="n">
-        <v>586384</v>
+        <v>586477</v>
       </c>
       <c r="R346" t="n">
-        <v>6311139</v>
+        <v>6311186</v>
       </c>
       <c r="S346" t="n">
         <v>5</v>
@@ -47747,7 +47747,7 @@
       </c>
       <c r="Z346" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AA346" t="inlineStr">
@@ -47757,7 +47757,7 @@
       </c>
       <c r="AB346" t="inlineStr">
         <is>
-          <t>22:46</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AC346" t="inlineStr">
@@ -47802,10 +47802,10 @@
     </row>
     <row r="347">
       <c r="A347" t="n">
-        <v>122254856</v>
+        <v>122254310</v>
       </c>
       <c r="B347" t="n">
-        <v>56288</v>
+        <v>56285</v>
       </c>
       <c r="C347" t="inlineStr">
         <is>
@@ -47818,21 +47818,21 @@
         </is>
       </c>
       <c r="E347" t="n">
-        <v>100111</v>
+        <v>100092</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I347" t="inlineStr">
@@ -47856,10 +47856,10 @@
         </is>
       </c>
       <c r="Q347" t="n">
-        <v>586327</v>
+        <v>586452</v>
       </c>
       <c r="R347" t="n">
-        <v>6311118</v>
+        <v>6311156</v>
       </c>
       <c r="S347" t="n">
         <v>5</v>
@@ -47891,7 +47891,7 @@
       </c>
       <c r="Z347" t="inlineStr">
         <is>
-          <t>22:57</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA347" t="inlineStr">
@@ -47901,7 +47901,7 @@
       </c>
       <c r="AB347" t="inlineStr">
         <is>
-          <t>22:58</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC347" t="inlineStr">
@@ -47946,10 +47946,10 @@
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>122254950</v>
+        <v>122254636</v>
       </c>
       <c r="B348" t="n">
-        <v>56278</v>
+        <v>56290</v>
       </c>
       <c r="C348" t="inlineStr">
         <is>
@@ -47962,21 +47962,21 @@
         </is>
       </c>
       <c r="E348" t="n">
-        <v>205992</v>
+        <v>205995</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I348" t="inlineStr">
@@ -48000,10 +48000,10 @@
         </is>
       </c>
       <c r="Q348" t="n">
-        <v>586482</v>
+        <v>586418</v>
       </c>
       <c r="R348" t="n">
-        <v>6311185</v>
+        <v>6311145</v>
       </c>
       <c r="S348" t="n">
         <v>5</v>
@@ -48035,7 +48035,7 @@
       </c>
       <c r="Z348" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AA348" t="inlineStr">
@@ -48045,7 +48045,7 @@
       </c>
       <c r="AB348" t="inlineStr">
         <is>
-          <t>23:31</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AC348" t="inlineStr">
@@ -48090,7 +48090,7 @@
     </row>
     <row r="349">
       <c r="A349" t="n">
-        <v>122254649</v>
+        <v>122254657</v>
       </c>
       <c r="B349" t="n">
         <v>56290</v>
@@ -48144,10 +48144,10 @@
         </is>
       </c>
       <c r="Q349" t="n">
-        <v>586422</v>
+        <v>586488</v>
       </c>
       <c r="R349" t="n">
-        <v>6311100</v>
+        <v>6311184</v>
       </c>
       <c r="S349" t="n">
         <v>5</v>
@@ -48179,7 +48179,7 @@
       </c>
       <c r="Z349" t="inlineStr">
         <is>
-          <t>22:35</t>
+          <t>22:31</t>
         </is>
       </c>
       <c r="AA349" t="inlineStr">
@@ -48189,7 +48189,7 @@
       </c>
       <c r="AB349" t="inlineStr">
         <is>
-          <t>22:36</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AC349" t="inlineStr">
@@ -48234,10 +48234,10 @@
     </row>
     <row r="350">
       <c r="A350" t="n">
-        <v>122254309</v>
+        <v>122254474</v>
       </c>
       <c r="B350" t="n">
-        <v>56285</v>
+        <v>56271</v>
       </c>
       <c r="C350" t="inlineStr">
         <is>
@@ -48246,25 +48246,25 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E350" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I350" t="inlineStr">
@@ -48288,10 +48288,10 @@
         </is>
       </c>
       <c r="Q350" t="n">
-        <v>586456</v>
+        <v>586443</v>
       </c>
       <c r="R350" t="n">
-        <v>6311158</v>
+        <v>6311164</v>
       </c>
       <c r="S350" t="n">
         <v>5</v>
@@ -48323,7 +48323,7 @@
       </c>
       <c r="Z350" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AA350" t="inlineStr">
@@ -48333,7 +48333,7 @@
       </c>
       <c r="AB350" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AC350" t="inlineStr">
@@ -48378,10 +48378,10 @@
     </row>
     <row r="351">
       <c r="A351" t="n">
-        <v>122254476</v>
+        <v>122254586</v>
       </c>
       <c r="B351" t="n">
-        <v>56271</v>
+        <v>56290</v>
       </c>
       <c r="C351" t="inlineStr">
         <is>
@@ -48390,25 +48390,25 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E351" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I351" t="inlineStr">
@@ -48432,10 +48432,10 @@
         </is>
       </c>
       <c r="Q351" t="n">
-        <v>586418</v>
+        <v>586446</v>
       </c>
       <c r="R351" t="n">
-        <v>6311167</v>
+        <v>6311158</v>
       </c>
       <c r="S351" t="n">
         <v>5</v>
@@ -48467,7 +48467,7 @@
       </c>
       <c r="Z351" t="inlineStr">
         <is>
-          <t>23:23</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AA351" t="inlineStr">
@@ -48477,7 +48477,7 @@
       </c>
       <c r="AB351" t="inlineStr">
         <is>
-          <t>23:24</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AC351" t="inlineStr">
@@ -48522,7 +48522,7 @@
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>122254350</v>
+        <v>122254411</v>
       </c>
       <c r="B352" t="n">
         <v>56285</v>
@@ -48576,10 +48576,10 @@
         </is>
       </c>
       <c r="Q352" t="n">
-        <v>586330</v>
+        <v>586414</v>
       </c>
       <c r="R352" t="n">
-        <v>6311120</v>
+        <v>6311126</v>
       </c>
       <c r="S352" t="n">
         <v>5</v>
@@ -48611,7 +48611,7 @@
       </c>
       <c r="Z352" t="inlineStr">
         <is>
-          <t>22:57</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AA352" t="inlineStr">
@@ -48621,7 +48621,7 @@
       </c>
       <c r="AB352" t="inlineStr">
         <is>
-          <t>22:58</t>
+          <t>22:38</t>
         </is>
       </c>
       <c r="AC352" t="inlineStr">
@@ -48666,10 +48666,10 @@
     </row>
     <row r="353">
       <c r="A353" t="n">
-        <v>122254633</v>
+        <v>122254373</v>
       </c>
       <c r="B353" t="n">
-        <v>56290</v>
+        <v>56285</v>
       </c>
       <c r="C353" t="inlineStr">
         <is>
@@ -48682,21 +48682,21 @@
         </is>
       </c>
       <c r="E353" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I353" t="inlineStr">
@@ -48720,10 +48720,10 @@
         </is>
       </c>
       <c r="Q353" t="n">
-        <v>586396</v>
+        <v>586307</v>
       </c>
       <c r="R353" t="n">
-        <v>6311146</v>
+        <v>6311133</v>
       </c>
       <c r="S353" t="n">
         <v>5</v>
@@ -48755,7 +48755,7 @@
       </c>
       <c r="Z353" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>22:49</t>
         </is>
       </c>
       <c r="AA353" t="inlineStr">
@@ -48765,7 +48765,7 @@
       </c>
       <c r="AB353" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AC353" t="inlineStr">
@@ -48810,10 +48810,10 @@
     </row>
     <row r="354">
       <c r="A354" t="n">
-        <v>122254656</v>
+        <v>122254391</v>
       </c>
       <c r="B354" t="n">
-        <v>56290</v>
+        <v>56285</v>
       </c>
       <c r="C354" t="inlineStr">
         <is>
@@ -48826,21 +48826,21 @@
         </is>
       </c>
       <c r="E354" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I354" t="inlineStr">
@@ -48864,10 +48864,10 @@
         </is>
       </c>
       <c r="Q354" t="n">
-        <v>586483</v>
+        <v>586379</v>
       </c>
       <c r="R354" t="n">
-        <v>6311186</v>
+        <v>6311136</v>
       </c>
       <c r="S354" t="n">
         <v>5</v>
@@ -48899,7 +48899,7 @@
       </c>
       <c r="Z354" t="inlineStr">
         <is>
-          <t>22:31</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AA354" t="inlineStr">
@@ -48909,7 +48909,7 @@
       </c>
       <c r="AB354" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>22:46</t>
         </is>
       </c>
       <c r="AC354" t="inlineStr">
@@ -48954,7 +48954,7 @@
     </row>
     <row r="355">
       <c r="A355" t="n">
-        <v>122254880</v>
+        <v>122254844</v>
       </c>
       <c r="B355" t="n">
         <v>56288</v>
@@ -49008,10 +49008,10 @@
         </is>
       </c>
       <c r="Q355" t="n">
-        <v>586303</v>
+        <v>586387</v>
       </c>
       <c r="R355" t="n">
-        <v>6311115</v>
+        <v>6311141</v>
       </c>
       <c r="S355" t="n">
         <v>5</v>
@@ -49043,7 +49043,7 @@
       </c>
       <c r="Z355" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA355" t="inlineStr">
@@ -49053,7 +49053,7 @@
       </c>
       <c r="AB355" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AC355" t="inlineStr">
@@ -49098,10 +49098,10 @@
     </row>
     <row r="356">
       <c r="A356" t="n">
-        <v>122254475</v>
+        <v>122254318</v>
       </c>
       <c r="B356" t="n">
-        <v>56271</v>
+        <v>56285</v>
       </c>
       <c r="C356" t="inlineStr">
         <is>
@@ -49110,25 +49110,25 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E356" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I356" t="inlineStr">
@@ -49152,10 +49152,10 @@
         </is>
       </c>
       <c r="Q356" t="n">
-        <v>586420</v>
+        <v>586455</v>
       </c>
       <c r="R356" t="n">
-        <v>6311166</v>
+        <v>6311228</v>
       </c>
       <c r="S356" t="n">
         <v>5</v>
@@ -49187,17 +49187,17 @@
       </c>
       <c r="Z356" t="inlineStr">
         <is>
+          <t>23:22</t>
+        </is>
+      </c>
+      <c r="AA356" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AB356" t="inlineStr">
+        <is>
           <t>23:23</t>
-        </is>
-      </c>
-      <c r="AA356" t="inlineStr">
-        <is>
-          <t>2024-06-26</t>
-        </is>
-      </c>
-      <c r="AB356" t="inlineStr">
-        <is>
-          <t>23:24</t>
         </is>
       </c>
       <c r="AC356" t="inlineStr">
@@ -49242,10 +49242,10 @@
     </row>
     <row r="357">
       <c r="A357" t="n">
-        <v>122254615</v>
+        <v>122254350</v>
       </c>
       <c r="B357" t="n">
-        <v>56290</v>
+        <v>56285</v>
       </c>
       <c r="C357" t="inlineStr">
         <is>
@@ -49258,21 +49258,21 @@
         </is>
       </c>
       <c r="E357" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I357" t="inlineStr">
@@ -49296,7 +49296,7 @@
         </is>
       </c>
       <c r="Q357" t="n">
-        <v>586329</v>
+        <v>586330</v>
       </c>
       <c r="R357" t="n">
         <v>6311120</v>
@@ -49386,10 +49386,10 @@
     </row>
     <row r="358">
       <c r="A358" t="n">
-        <v>122254635</v>
+        <v>122254496</v>
       </c>
       <c r="B358" t="n">
-        <v>56290</v>
+        <v>56271</v>
       </c>
       <c r="C358" t="inlineStr">
         <is>
@@ -49398,25 +49398,25 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E358" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H358" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I358" t="inlineStr">
@@ -49440,10 +49440,10 @@
         </is>
       </c>
       <c r="Q358" t="n">
-        <v>586417</v>
+        <v>586415</v>
       </c>
       <c r="R358" t="n">
-        <v>6311145</v>
+        <v>6311146</v>
       </c>
       <c r="S358" t="n">
         <v>5</v>
@@ -49475,7 +49475,7 @@
       </c>
       <c r="Z358" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AA358" t="inlineStr">
@@ -49485,7 +49485,7 @@
       </c>
       <c r="AB358" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>23:03</t>
         </is>
       </c>
       <c r="AC358" t="inlineStr">
@@ -49530,7 +49530,7 @@
     </row>
     <row r="359">
       <c r="A359" t="n">
-        <v>122254655</v>
+        <v>122254649</v>
       </c>
       <c r="B359" t="n">
         <v>56290</v>
@@ -49584,10 +49584,10 @@
         </is>
       </c>
       <c r="Q359" t="n">
-        <v>586475</v>
+        <v>586422</v>
       </c>
       <c r="R359" t="n">
-        <v>6311187</v>
+        <v>6311100</v>
       </c>
       <c r="S359" t="n">
         <v>5</v>
@@ -49619,7 +49619,7 @@
       </c>
       <c r="Z359" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="AA359" t="inlineStr">
@@ -49629,7 +49629,7 @@
       </c>
       <c r="AB359" t="inlineStr">
         <is>
-          <t>22:33</t>
+          <t>22:36</t>
         </is>
       </c>
       <c r="AC359" t="inlineStr">
@@ -49674,10 +49674,10 @@
     </row>
     <row r="360">
       <c r="A360" t="n">
-        <v>122254644</v>
+        <v>122254473</v>
       </c>
       <c r="B360" t="n">
-        <v>56290</v>
+        <v>56271</v>
       </c>
       <c r="C360" t="inlineStr">
         <is>
@@ -49686,25 +49686,25 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E360" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I360" t="inlineStr">
@@ -49728,10 +49728,10 @@
         </is>
       </c>
       <c r="Q360" t="n">
-        <v>586429</v>
+        <v>586450</v>
       </c>
       <c r="R360" t="n">
-        <v>6311115</v>
+        <v>6311152</v>
       </c>
       <c r="S360" t="n">
         <v>5</v>
@@ -49763,7 +49763,7 @@
       </c>
       <c r="Z360" t="inlineStr">
         <is>
-          <t>22:36</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA360" t="inlineStr">
@@ -49773,7 +49773,7 @@
       </c>
       <c r="AB360" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC360" t="inlineStr">
@@ -49818,10 +49818,10 @@
     </row>
     <row r="361">
       <c r="A361" t="n">
-        <v>122254412</v>
+        <v>122254654</v>
       </c>
       <c r="B361" t="n">
-        <v>56285</v>
+        <v>56290</v>
       </c>
       <c r="C361" t="inlineStr">
         <is>
@@ -49834,21 +49834,21 @@
         </is>
       </c>
       <c r="E361" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I361" t="inlineStr">
@@ -49872,10 +49872,10 @@
         </is>
       </c>
       <c r="Q361" t="n">
-        <v>586424</v>
+        <v>586467</v>
       </c>
       <c r="R361" t="n">
-        <v>6311135</v>
+        <v>6311178</v>
       </c>
       <c r="S361" t="n">
         <v>5</v>
@@ -49907,7 +49907,7 @@
       </c>
       <c r="Z361" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AA361" t="inlineStr">
@@ -49917,7 +49917,7 @@
       </c>
       <c r="AB361" t="inlineStr">
         <is>
-          <t>22:38</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="AC361" t="inlineStr">
@@ -49962,10 +49962,10 @@
     </row>
     <row r="362">
       <c r="A362" t="n">
-        <v>122254316</v>
+        <v>122254957</v>
       </c>
       <c r="B362" t="n">
-        <v>56285</v>
+        <v>56278</v>
       </c>
       <c r="C362" t="inlineStr">
         <is>
@@ -49978,21 +49978,21 @@
         </is>
       </c>
       <c r="E362" t="n">
-        <v>100092</v>
+        <v>205992</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I362" t="inlineStr">
@@ -50016,10 +50016,10 @@
         </is>
       </c>
       <c r="Q362" t="n">
-        <v>586423</v>
+        <v>586444</v>
       </c>
       <c r="R362" t="n">
-        <v>6311166</v>
+        <v>6311160</v>
       </c>
       <c r="S362" t="n">
         <v>5</v>
@@ -50051,7 +50051,7 @@
       </c>
       <c r="Z362" t="inlineStr">
         <is>
-          <t>23:23</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="AA362" t="inlineStr">
@@ -50061,7 +50061,7 @@
       </c>
       <c r="AB362" t="inlineStr">
         <is>
-          <t>23:24</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AC362" t="inlineStr">
@@ -50106,10 +50106,10 @@
     </row>
     <row r="363">
       <c r="A363" t="n">
-        <v>122254855</v>
+        <v>122254519</v>
       </c>
       <c r="B363" t="n">
-        <v>56288</v>
+        <v>56271</v>
       </c>
       <c r="C363" t="inlineStr">
         <is>
@@ -50118,25 +50118,25 @@
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E363" t="n">
-        <v>100111</v>
+        <v>205998</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I363" t="inlineStr">
@@ -50160,10 +50160,10 @@
         </is>
       </c>
       <c r="Q363" t="n">
-        <v>586330</v>
+        <v>586424</v>
       </c>
       <c r="R363" t="n">
-        <v>6311120</v>
+        <v>6311135</v>
       </c>
       <c r="S363" t="n">
         <v>5</v>
@@ -50195,7 +50195,7 @@
       </c>
       <c r="Z363" t="inlineStr">
         <is>
-          <t>22:57</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AA363" t="inlineStr">
@@ -50205,7 +50205,7 @@
       </c>
       <c r="AB363" t="inlineStr">
         <is>
-          <t>22:58</t>
+          <t>22:38</t>
         </is>
       </c>
       <c r="AC363" t="inlineStr">
@@ -50250,10 +50250,10 @@
     </row>
     <row r="364">
       <c r="A364" t="n">
-        <v>122254877</v>
+        <v>122254625</v>
       </c>
       <c r="B364" t="n">
-        <v>56288</v>
+        <v>56290</v>
       </c>
       <c r="C364" t="inlineStr">
         <is>
@@ -50266,21 +50266,21 @@
         </is>
       </c>
       <c r="E364" t="n">
-        <v>100111</v>
+        <v>205995</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I364" t="inlineStr">
@@ -50304,10 +50304,10 @@
         </is>
       </c>
       <c r="Q364" t="n">
-        <v>586276</v>
+        <v>586309</v>
       </c>
       <c r="R364" t="n">
-        <v>6311100</v>
+        <v>6311119</v>
       </c>
       <c r="S364" t="n">
         <v>5</v>
@@ -50339,17 +50339,17 @@
       </c>
       <c r="Z364" t="inlineStr">
         <is>
+          <t>22:50</t>
+        </is>
+      </c>
+      <c r="AA364" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AB364" t="inlineStr">
+        <is>
           <t>22:51</t>
-        </is>
-      </c>
-      <c r="AA364" t="inlineStr">
-        <is>
-          <t>2024-06-26</t>
-        </is>
-      </c>
-      <c r="AB364" t="inlineStr">
-        <is>
-          <t>22:52</t>
         </is>
       </c>
       <c r="AC364" t="inlineStr">
@@ -50394,10 +50394,10 @@
     </row>
     <row r="365">
       <c r="A365" t="n">
-        <v>122254503</v>
+        <v>122254392</v>
       </c>
       <c r="B365" t="n">
-        <v>56271</v>
+        <v>56285</v>
       </c>
       <c r="C365" t="inlineStr">
         <is>
@@ -50406,25 +50406,25 @@
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E365" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I365" t="inlineStr">
@@ -50448,10 +50448,10 @@
         </is>
       </c>
       <c r="Q365" t="n">
-        <v>586313</v>
+        <v>586384</v>
       </c>
       <c r="R365" t="n">
-        <v>6311124</v>
+        <v>6311139</v>
       </c>
       <c r="S365" t="n">
         <v>5</v>
@@ -50483,7 +50483,7 @@
       </c>
       <c r="Z365" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AA365" t="inlineStr">
@@ -50493,7 +50493,7 @@
       </c>
       <c r="AB365" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>22:46</t>
         </is>
       </c>
       <c r="AC365" t="inlineStr">
@@ -50538,10 +50538,10 @@
     </row>
     <row r="366">
       <c r="A366" t="n">
-        <v>122254617</v>
+        <v>122254341</v>
       </c>
       <c r="B366" t="n">
-        <v>56290</v>
+        <v>56285</v>
       </c>
       <c r="C366" t="inlineStr">
         <is>
@@ -50554,21 +50554,21 @@
         </is>
       </c>
       <c r="E366" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I366" t="inlineStr">
@@ -50592,10 +50592,10 @@
         </is>
       </c>
       <c r="Q366" t="n">
-        <v>586317</v>
+        <v>586415</v>
       </c>
       <c r="R366" t="n">
-        <v>6311115</v>
+        <v>6311146</v>
       </c>
       <c r="S366" t="n">
         <v>5</v>
@@ -50627,7 +50627,7 @@
       </c>
       <c r="Z366" t="inlineStr">
         <is>
-          <t>22:57</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AA366" t="inlineStr">
@@ -50637,7 +50637,7 @@
       </c>
       <c r="AB366" t="inlineStr">
         <is>
-          <t>22:58</t>
+          <t>23:03</t>
         </is>
       </c>
       <c r="AC366" t="inlineStr">
@@ -50682,10 +50682,10 @@
     </row>
     <row r="367">
       <c r="A367" t="n">
-        <v>122254637</v>
+        <v>122254878</v>
       </c>
       <c r="B367" t="n">
-        <v>56290</v>
+        <v>56288</v>
       </c>
       <c r="C367" t="inlineStr">
         <is>
@@ -50698,21 +50698,21 @@
         </is>
       </c>
       <c r="E367" t="n">
-        <v>205995</v>
+        <v>100111</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I367" t="inlineStr">
@@ -50736,10 +50736,10 @@
         </is>
       </c>
       <c r="Q367" t="n">
-        <v>586408</v>
+        <v>586280</v>
       </c>
       <c r="R367" t="n">
-        <v>6311124</v>
+        <v>6311103</v>
       </c>
       <c r="S367" t="n">
         <v>5</v>
@@ -50771,7 +50771,7 @@
       </c>
       <c r="Z367" t="inlineStr">
         <is>
-          <t>22:43</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AA367" t="inlineStr">
@@ -50781,7 +50781,7 @@
       </c>
       <c r="AB367" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>22:52</t>
         </is>
       </c>
       <c r="AC367" t="inlineStr">
@@ -50826,10 +50826,10 @@
     </row>
     <row r="368">
       <c r="A368" t="n">
-        <v>122254607</v>
+        <v>122254472</v>
       </c>
       <c r="B368" t="n">
-        <v>56290</v>
+        <v>56271</v>
       </c>
       <c r="C368" t="inlineStr">
         <is>
@@ -50838,25 +50838,25 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E368" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H368" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I368" t="inlineStr">
@@ -50880,10 +50880,10 @@
         </is>
       </c>
       <c r="Q368" t="n">
-        <v>586415</v>
+        <v>586455</v>
       </c>
       <c r="R368" t="n">
-        <v>6311149</v>
+        <v>6311159</v>
       </c>
       <c r="S368" t="n">
         <v>5</v>
@@ -50915,7 +50915,7 @@
       </c>
       <c r="Z368" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AA368" t="inlineStr">
@@ -50925,7 +50925,7 @@
       </c>
       <c r="AB368" t="inlineStr">
         <is>
-          <t>23:03</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AC368" t="inlineStr">
@@ -50970,7 +50970,7 @@
     </row>
     <row r="369">
       <c r="A369" t="n">
-        <v>122254657</v>
+        <v>122254650</v>
       </c>
       <c r="B369" t="n">
         <v>56290</v>
@@ -51024,10 +51024,10 @@
         </is>
       </c>
       <c r="Q369" t="n">
-        <v>586488</v>
+        <v>586422</v>
       </c>
       <c r="R369" t="n">
-        <v>6311184</v>
+        <v>6311105</v>
       </c>
       <c r="S369" t="n">
         <v>5</v>
@@ -51059,7 +51059,7 @@
       </c>
       <c r="Z369" t="inlineStr">
         <is>
-          <t>22:31</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="AA369" t="inlineStr">
@@ -51069,7 +51069,7 @@
       </c>
       <c r="AB369" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>22:36</t>
         </is>
       </c>
       <c r="AC369" t="inlineStr">
@@ -51114,10 +51114,10 @@
     </row>
     <row r="370">
       <c r="A370" t="n">
-        <v>122254352</v>
+        <v>122254954</v>
       </c>
       <c r="B370" t="n">
-        <v>56285</v>
+        <v>56278</v>
       </c>
       <c r="C370" t="inlineStr">
         <is>
@@ -51130,21 +51130,21 @@
         </is>
       </c>
       <c r="E370" t="n">
-        <v>100092</v>
+        <v>205992</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I370" t="inlineStr">
@@ -51168,10 +51168,10 @@
         </is>
       </c>
       <c r="Q370" t="n">
-        <v>586288</v>
+        <v>586442</v>
       </c>
       <c r="R370" t="n">
-        <v>6311100</v>
+        <v>6311152</v>
       </c>
       <c r="S370" t="n">
         <v>5</v>
@@ -51203,7 +51203,7 @@
       </c>
       <c r="Z370" t="inlineStr">
         <is>
-          <t>22:55</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AA370" t="inlineStr">
@@ -51213,7 +51213,7 @@
       </c>
       <c r="AB370" t="inlineStr">
         <is>
-          <t>22:56</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AC370" t="inlineStr">
@@ -51258,10 +51258,10 @@
     </row>
     <row r="371">
       <c r="A371" t="n">
-        <v>122254519</v>
+        <v>122254951</v>
       </c>
       <c r="B371" t="n">
-        <v>56271</v>
+        <v>56278</v>
       </c>
       <c r="C371" t="inlineStr">
         <is>
@@ -51270,25 +51270,25 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E371" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I371" t="inlineStr">
@@ -51312,10 +51312,10 @@
         </is>
       </c>
       <c r="Q371" t="n">
-        <v>586424</v>
+        <v>586459</v>
       </c>
       <c r="R371" t="n">
-        <v>6311135</v>
+        <v>6311154</v>
       </c>
       <c r="S371" t="n">
         <v>5</v>
@@ -51347,7 +51347,7 @@
       </c>
       <c r="Z371" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AA371" t="inlineStr">
@@ -51357,7 +51357,7 @@
       </c>
       <c r="AB371" t="inlineStr">
         <is>
-          <t>22:38</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AC371" t="inlineStr">
@@ -51402,7 +51402,7 @@
     </row>
     <row r="372">
       <c r="A372" t="n">
-        <v>122254609</v>
+        <v>122254606</v>
       </c>
       <c r="B372" t="n">
         <v>56290</v>
@@ -51456,10 +51456,10 @@
         </is>
       </c>
       <c r="Q372" t="n">
-        <v>586392</v>
+        <v>586415</v>
       </c>
       <c r="R372" t="n">
-        <v>6311147</v>
+        <v>6311146</v>
       </c>
       <c r="S372" t="n">
         <v>5</v>
@@ -51491,7 +51491,7 @@
       </c>
       <c r="Z372" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AA372" t="inlineStr">
@@ -51501,7 +51501,7 @@
       </c>
       <c r="AB372" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>23:03</t>
         </is>
       </c>
       <c r="AC372" t="inlineStr">
@@ -51546,7 +51546,7 @@
     </row>
     <row r="373">
       <c r="A373" t="n">
-        <v>122254632</v>
+        <v>122254607</v>
       </c>
       <c r="B373" t="n">
         <v>56290</v>
@@ -51600,10 +51600,10 @@
         </is>
       </c>
       <c r="Q373" t="n">
-        <v>586374</v>
+        <v>586415</v>
       </c>
       <c r="R373" t="n">
-        <v>6311140</v>
+        <v>6311149</v>
       </c>
       <c r="S373" t="n">
         <v>5</v>
@@ -51635,7 +51635,7 @@
       </c>
       <c r="Z373" t="inlineStr">
         <is>
-          <t>22:46</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AA373" t="inlineStr">
@@ -51645,7 +51645,7 @@
       </c>
       <c r="AB373" t="inlineStr">
         <is>
-          <t>22:47</t>
+          <t>23:03</t>
         </is>
       </c>
       <c r="AC373" t="inlineStr">
@@ -51690,10 +51690,10 @@
     </row>
     <row r="374">
       <c r="A374" t="n">
-        <v>122254636</v>
+        <v>122254306</v>
       </c>
       <c r="B374" t="n">
-        <v>56290</v>
+        <v>56285</v>
       </c>
       <c r="C374" t="inlineStr">
         <is>
@@ -51706,21 +51706,21 @@
         </is>
       </c>
       <c r="E374" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I374" t="inlineStr">
@@ -51744,10 +51744,10 @@
         </is>
       </c>
       <c r="Q374" t="n">
-        <v>586418</v>
+        <v>586473</v>
       </c>
       <c r="R374" t="n">
-        <v>6311145</v>
+        <v>6311192</v>
       </c>
       <c r="S374" t="n">
         <v>5</v>
@@ -51779,7 +51779,7 @@
       </c>
       <c r="Z374" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AA374" t="inlineStr">
@@ -51789,7 +51789,7 @@
       </c>
       <c r="AB374" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AC374" t="inlineStr">
@@ -51834,7 +51834,7 @@
     </row>
     <row r="375">
       <c r="A375" t="n">
-        <v>122254626</v>
+        <v>122254634</v>
       </c>
       <c r="B375" t="n">
         <v>56290</v>
@@ -51888,10 +51888,10 @@
         </is>
       </c>
       <c r="Q375" t="n">
-        <v>586313</v>
+        <v>586415</v>
       </c>
       <c r="R375" t="n">
-        <v>6311124</v>
+        <v>6311148</v>
       </c>
       <c r="S375" t="n">
         <v>5</v>
@@ -51923,7 +51923,7 @@
       </c>
       <c r="Z375" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AA375" t="inlineStr">
@@ -51933,7 +51933,7 @@
       </c>
       <c r="AB375" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AC375" t="inlineStr">
@@ -51978,10 +51978,10 @@
     </row>
     <row r="376">
       <c r="A376" t="n">
-        <v>122254472</v>
+        <v>122254635</v>
       </c>
       <c r="B376" t="n">
-        <v>56271</v>
+        <v>56290</v>
       </c>
       <c r="C376" t="inlineStr">
         <is>
@@ -51990,25 +51990,25 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E376" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H376" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I376" t="inlineStr">
@@ -52032,10 +52032,10 @@
         </is>
       </c>
       <c r="Q376" t="n">
-        <v>586455</v>
+        <v>586417</v>
       </c>
       <c r="R376" t="n">
-        <v>6311159</v>
+        <v>6311145</v>
       </c>
       <c r="S376" t="n">
         <v>5</v>
@@ -52067,7 +52067,7 @@
       </c>
       <c r="Z376" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AA376" t="inlineStr">
@@ -52077,7 +52077,7 @@
       </c>
       <c r="AB376" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AC376" t="inlineStr">
@@ -52122,10 +52122,10 @@
     </row>
     <row r="377">
       <c r="A377" t="n">
-        <v>122254411</v>
+        <v>122254658</v>
       </c>
       <c r="B377" t="n">
-        <v>56285</v>
+        <v>56290</v>
       </c>
       <c r="C377" t="inlineStr">
         <is>
@@ -52138,21 +52138,21 @@
         </is>
       </c>
       <c r="E377" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H377" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I377" t="inlineStr">
@@ -52176,10 +52176,10 @@
         </is>
       </c>
       <c r="Q377" t="n">
-        <v>586414</v>
+        <v>586491</v>
       </c>
       <c r="R377" t="n">
-        <v>6311126</v>
+        <v>6311181</v>
       </c>
       <c r="S377" t="n">
         <v>5</v>
@@ -52211,7 +52211,7 @@
       </c>
       <c r="Z377" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>22:31</t>
         </is>
       </c>
       <c r="AA377" t="inlineStr">
@@ -52221,7 +52221,7 @@
       </c>
       <c r="AB377" t="inlineStr">
         <is>
-          <t>22:38</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AC377" t="inlineStr">
@@ -52266,10 +52266,10 @@
     </row>
     <row r="378">
       <c r="A378" t="n">
-        <v>122254511</v>
+        <v>122254316</v>
       </c>
       <c r="B378" t="n">
-        <v>56271</v>
+        <v>56285</v>
       </c>
       <c r="C378" t="inlineStr">
         <is>
@@ -52278,25 +52278,25 @@
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E378" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I378" t="inlineStr">
@@ -52320,10 +52320,10 @@
         </is>
       </c>
       <c r="Q378" t="n">
-        <v>586374</v>
+        <v>586423</v>
       </c>
       <c r="R378" t="n">
-        <v>6311139</v>
+        <v>6311166</v>
       </c>
       <c r="S378" t="n">
         <v>5</v>
@@ -52355,7 +52355,7 @@
       </c>
       <c r="Z378" t="inlineStr">
         <is>
-          <t>22:46</t>
+          <t>23:23</t>
         </is>
       </c>
       <c r="AA378" t="inlineStr">
@@ -52365,7 +52365,7 @@
       </c>
       <c r="AB378" t="inlineStr">
         <is>
-          <t>22:47</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="AC378" t="inlineStr">
@@ -52410,10 +52410,10 @@
     </row>
     <row r="379">
       <c r="A379" t="n">
-        <v>122254499</v>
+        <v>122254646</v>
       </c>
       <c r="B379" t="n">
-        <v>56271</v>
+        <v>56290</v>
       </c>
       <c r="C379" t="inlineStr">
         <is>
@@ -52422,25 +52422,25 @@
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E379" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H379" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I379" t="inlineStr">
@@ -52464,10 +52464,10 @@
         </is>
       </c>
       <c r="Q379" t="n">
-        <v>586392</v>
+        <v>586422</v>
       </c>
       <c r="R379" t="n">
-        <v>6311147</v>
+        <v>6311111</v>
       </c>
       <c r="S379" t="n">
         <v>5</v>
@@ -52499,7 +52499,7 @@
       </c>
       <c r="Z379" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>22:36</t>
         </is>
       </c>
       <c r="AA379" t="inlineStr">
@@ -52509,7 +52509,7 @@
       </c>
       <c r="AB379" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AC379" t="inlineStr">
@@ -52554,10 +52554,10 @@
     </row>
     <row r="380">
       <c r="A380" t="n">
-        <v>122254512</v>
+        <v>122254585</v>
       </c>
       <c r="B380" t="n">
-        <v>56271</v>
+        <v>56290</v>
       </c>
       <c r="C380" t="inlineStr">
         <is>
@@ -52566,25 +52566,25 @@
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E380" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H380" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I380" t="inlineStr">
@@ -52608,10 +52608,10 @@
         </is>
       </c>
       <c r="Q380" t="n">
-        <v>586379</v>
+        <v>586455</v>
       </c>
       <c r="R380" t="n">
-        <v>6311136</v>
+        <v>6311156</v>
       </c>
       <c r="S380" t="n">
         <v>5</v>
@@ -52643,7 +52643,7 @@
       </c>
       <c r="Z380" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AA380" t="inlineStr">
@@ -52653,7 +52653,7 @@
       </c>
       <c r="AB380" t="inlineStr">
         <is>
-          <t>22:46</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AC380" t="inlineStr">
@@ -52698,7 +52698,7 @@
     </row>
     <row r="381">
       <c r="A381" t="n">
-        <v>122254651</v>
+        <v>122254609</v>
       </c>
       <c r="B381" t="n">
         <v>56290</v>
@@ -52752,10 +52752,10 @@
         </is>
       </c>
       <c r="Q381" t="n">
-        <v>586425</v>
+        <v>586392</v>
       </c>
       <c r="R381" t="n">
-        <v>6311113</v>
+        <v>6311147</v>
       </c>
       <c r="S381" t="n">
         <v>5</v>
@@ -52787,7 +52787,7 @@
       </c>
       <c r="Z381" t="inlineStr">
         <is>
-          <t>22:35</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AA381" t="inlineStr">
@@ -52797,7 +52797,7 @@
       </c>
       <c r="AB381" t="inlineStr">
         <is>
-          <t>22:36</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AC381" t="inlineStr">
@@ -52842,10 +52842,10 @@
     </row>
     <row r="382">
       <c r="A382" t="n">
-        <v>122254586</v>
+        <v>122254475</v>
       </c>
       <c r="B382" t="n">
-        <v>56290</v>
+        <v>56271</v>
       </c>
       <c r="C382" t="inlineStr">
         <is>
@@ -52854,25 +52854,25 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E382" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H382" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I382" t="inlineStr">
@@ -52896,10 +52896,10 @@
         </is>
       </c>
       <c r="Q382" t="n">
-        <v>586446</v>
+        <v>586420</v>
       </c>
       <c r="R382" t="n">
-        <v>6311158</v>
+        <v>6311166</v>
       </c>
       <c r="S382" t="n">
         <v>5</v>
@@ -52931,7 +52931,7 @@
       </c>
       <c r="Z382" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>23:23</t>
         </is>
       </c>
       <c r="AA382" t="inlineStr">
@@ -52941,7 +52941,7 @@
       </c>
       <c r="AB382" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="AC382" t="inlineStr">
@@ -52986,7 +52986,7 @@
     </row>
     <row r="383">
       <c r="A383" t="n">
-        <v>122254650</v>
+        <v>122254633</v>
       </c>
       <c r="B383" t="n">
         <v>56290</v>
@@ -53040,10 +53040,10 @@
         </is>
       </c>
       <c r="Q383" t="n">
-        <v>586422</v>
+        <v>586396</v>
       </c>
       <c r="R383" t="n">
-        <v>6311105</v>
+        <v>6311146</v>
       </c>
       <c r="S383" t="n">
         <v>5</v>
@@ -53075,7 +53075,7 @@
       </c>
       <c r="Z383" t="inlineStr">
         <is>
-          <t>22:35</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AA383" t="inlineStr">
@@ -53085,7 +53085,7 @@
       </c>
       <c r="AB383" t="inlineStr">
         <is>
-          <t>22:36</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AC383" t="inlineStr">
@@ -53130,7 +53130,7 @@
     </row>
     <row r="384">
       <c r="A384" t="n">
-        <v>122254653</v>
+        <v>122254643</v>
       </c>
       <c r="B384" t="n">
         <v>56290</v>
@@ -53184,10 +53184,10 @@
         </is>
       </c>
       <c r="Q384" t="n">
-        <v>586430</v>
+        <v>586424</v>
       </c>
       <c r="R384" t="n">
-        <v>6311142</v>
+        <v>6311135</v>
       </c>
       <c r="S384" t="n">
         <v>5</v>
@@ -53219,7 +53219,7 @@
       </c>
       <c r="Z384" t="inlineStr">
         <is>
-          <t>22:33</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AA384" t="inlineStr">
@@ -53229,7 +53229,7 @@
       </c>
       <c r="AB384" t="inlineStr">
         <is>
-          <t>22:34</t>
+          <t>22:38</t>
         </is>
       </c>
       <c r="AC384" t="inlineStr">
@@ -53274,10 +53274,10 @@
     </row>
     <row r="385">
       <c r="A385" t="n">
-        <v>122254498</v>
+        <v>122254415</v>
       </c>
       <c r="B385" t="n">
-        <v>56271</v>
+        <v>56285</v>
       </c>
       <c r="C385" t="inlineStr">
         <is>
@@ -53286,25 +53286,25 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E385" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H385" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I385" t="inlineStr">
@@ -53328,10 +53328,10 @@
         </is>
       </c>
       <c r="Q385" t="n">
-        <v>586393</v>
+        <v>586425</v>
       </c>
       <c r="R385" t="n">
-        <v>6311147</v>
+        <v>6311135</v>
       </c>
       <c r="S385" t="n">
         <v>5</v>
@@ -53363,7 +53363,7 @@
       </c>
       <c r="Z385" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AA385" t="inlineStr">
@@ -53373,7 +53373,7 @@
       </c>
       <c r="AB385" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>22:38</t>
         </is>
       </c>
       <c r="AC385" t="inlineStr">
@@ -53418,7 +53418,7 @@
     </row>
     <row r="386">
       <c r="A386" t="n">
-        <v>122254341</v>
+        <v>122254371</v>
       </c>
       <c r="B386" t="n">
         <v>56285</v>
@@ -53472,10 +53472,10 @@
         </is>
       </c>
       <c r="Q386" t="n">
-        <v>586415</v>
+        <v>586308</v>
       </c>
       <c r="R386" t="n">
-        <v>6311146</v>
+        <v>6311132</v>
       </c>
       <c r="S386" t="n">
         <v>5</v>
@@ -53507,7 +53507,7 @@
       </c>
       <c r="Z386" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AA386" t="inlineStr">
@@ -53517,7 +53517,7 @@
       </c>
       <c r="AB386" t="inlineStr">
         <is>
-          <t>23:03</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AC386" t="inlineStr">
@@ -53562,10 +53562,10 @@
     </row>
     <row r="387">
       <c r="A387" t="n">
-        <v>122254415</v>
+        <v>122254877</v>
       </c>
       <c r="B387" t="n">
-        <v>56285</v>
+        <v>56288</v>
       </c>
       <c r="C387" t="inlineStr">
         <is>
@@ -53578,21 +53578,21 @@
         </is>
       </c>
       <c r="E387" t="n">
-        <v>100092</v>
+        <v>100111</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I387" t="inlineStr">
@@ -53616,10 +53616,10 @@
         </is>
       </c>
       <c r="Q387" t="n">
-        <v>586425</v>
+        <v>586276</v>
       </c>
       <c r="R387" t="n">
-        <v>6311135</v>
+        <v>6311100</v>
       </c>
       <c r="S387" t="n">
         <v>5</v>
@@ -53651,7 +53651,7 @@
       </c>
       <c r="Z387" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AA387" t="inlineStr">
@@ -53661,7 +53661,7 @@
       </c>
       <c r="AB387" t="inlineStr">
         <is>
-          <t>22:38</t>
+          <t>22:52</t>
         </is>
       </c>
       <c r="AC387" t="inlineStr">
@@ -53706,10 +53706,10 @@
     </row>
     <row r="388">
       <c r="A388" t="n">
-        <v>122254843</v>
+        <v>122254352</v>
       </c>
       <c r="B388" t="n">
-        <v>56288</v>
+        <v>56285</v>
       </c>
       <c r="C388" t="inlineStr">
         <is>
@@ -53722,21 +53722,21 @@
         </is>
       </c>
       <c r="E388" t="n">
-        <v>100111</v>
+        <v>100092</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H388" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I388" t="inlineStr">
@@ -53760,10 +53760,10 @@
         </is>
       </c>
       <c r="Q388" t="n">
-        <v>586389</v>
+        <v>586288</v>
       </c>
       <c r="R388" t="n">
-        <v>6311142</v>
+        <v>6311100</v>
       </c>
       <c r="S388" t="n">
         <v>5</v>
@@ -53795,7 +53795,7 @@
       </c>
       <c r="Z388" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:55</t>
         </is>
       </c>
       <c r="AA388" t="inlineStr">
@@ -53805,7 +53805,7 @@
       </c>
       <c r="AB388" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>22:56</t>
         </is>
       </c>
       <c r="AC388" t="inlineStr">
@@ -53850,10 +53850,10 @@
     </row>
     <row r="389">
       <c r="A389" t="n">
-        <v>122254966</v>
+        <v>122254584</v>
       </c>
       <c r="B389" t="n">
-        <v>56278</v>
+        <v>56290</v>
       </c>
       <c r="C389" t="inlineStr">
         <is>
@@ -53866,21 +53866,21 @@
         </is>
       </c>
       <c r="E389" t="n">
-        <v>205992</v>
+        <v>205995</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I389" t="inlineStr">
@@ -53904,10 +53904,10 @@
         </is>
       </c>
       <c r="Q389" t="n">
-        <v>586467</v>
+        <v>586473</v>
       </c>
       <c r="R389" t="n">
-        <v>6311178</v>
+        <v>6311192</v>
       </c>
       <c r="S389" t="n">
         <v>5</v>
@@ -53939,7 +53939,7 @@
       </c>
       <c r="Z389" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AA389" t="inlineStr">
@@ -53949,7 +53949,7 @@
       </c>
       <c r="AB389" t="inlineStr">
         <is>
-          <t>22:33</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AC389" t="inlineStr">
@@ -53994,10 +53994,10 @@
     </row>
     <row r="390">
       <c r="A390" t="n">
-        <v>122254625</v>
+        <v>122254966</v>
       </c>
       <c r="B390" t="n">
-        <v>56290</v>
+        <v>56278</v>
       </c>
       <c r="C390" t="inlineStr">
         <is>
@@ -54010,21 +54010,21 @@
         </is>
       </c>
       <c r="E390" t="n">
-        <v>205995</v>
+        <v>205992</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I390" t="inlineStr">
@@ -54048,10 +54048,10 @@
         </is>
       </c>
       <c r="Q390" t="n">
-        <v>586309</v>
+        <v>586467</v>
       </c>
       <c r="R390" t="n">
-        <v>6311119</v>
+        <v>6311178</v>
       </c>
       <c r="S390" t="n">
         <v>5</v>
@@ -54083,7 +54083,7 @@
       </c>
       <c r="Z390" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AA390" t="inlineStr">
@@ -54093,7 +54093,7 @@
       </c>
       <c r="AB390" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="AC390" t="inlineStr">

--- a/artfynd/A 36363-2024 artfynd.xlsx
+++ b/artfynd/A 36363-2024 artfynd.xlsx
@@ -37002,10 +37002,10 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>122254648</v>
+        <v>122254396</v>
       </c>
       <c r="B272" t="n">
-        <v>56290</v>
+        <v>56285</v>
       </c>
       <c r="C272" t="inlineStr">
         <is>
@@ -37018,21 +37018,21 @@
         </is>
       </c>
       <c r="E272" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
@@ -37056,10 +37056,10 @@
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>586418</v>
+        <v>586408</v>
       </c>
       <c r="R272" t="n">
-        <v>6311107</v>
+        <v>6311124</v>
       </c>
       <c r="S272" t="n">
         <v>5</v>
@@ -37091,7 +37091,7 @@
       </c>
       <c r="Z272" t="inlineStr">
         <is>
-          <t>22:36</t>
+          <t>22:43</t>
         </is>
       </c>
       <c r="AA272" t="inlineStr">
@@ -37101,7 +37101,7 @@
       </c>
       <c r="AB272" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AC272" t="inlineStr">
@@ -37146,10 +37146,10 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>122254963</v>
+        <v>122254835</v>
       </c>
       <c r="B273" t="n">
-        <v>56278</v>
+        <v>56288</v>
       </c>
       <c r="C273" t="inlineStr">
         <is>
@@ -37162,21 +37162,21 @@
         </is>
       </c>
       <c r="E273" t="n">
-        <v>205992</v>
+        <v>100111</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
@@ -37200,10 +37200,10 @@
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>586374</v>
+        <v>586473</v>
       </c>
       <c r="R273" t="n">
-        <v>6311140</v>
+        <v>6311192</v>
       </c>
       <c r="S273" t="n">
         <v>5</v>
@@ -37235,7 +37235,7 @@
       </c>
       <c r="Z273" t="inlineStr">
         <is>
-          <t>22:46</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AA273" t="inlineStr">
@@ -37245,7 +37245,7 @@
       </c>
       <c r="AB273" t="inlineStr">
         <is>
-          <t>22:47</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AC273" t="inlineStr">
@@ -37290,10 +37290,10 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>122254396</v>
+        <v>122254648</v>
       </c>
       <c r="B274" t="n">
-        <v>56285</v>
+        <v>56290</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>
@@ -37306,21 +37306,21 @@
         </is>
       </c>
       <c r="E274" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
@@ -37344,10 +37344,10 @@
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>586408</v>
+        <v>586418</v>
       </c>
       <c r="R274" t="n">
-        <v>6311124</v>
+        <v>6311107</v>
       </c>
       <c r="S274" t="n">
         <v>5</v>
@@ -37379,7 +37379,7 @@
       </c>
       <c r="Z274" t="inlineStr">
         <is>
-          <t>22:43</t>
+          <t>22:36</t>
         </is>
       </c>
       <c r="AA274" t="inlineStr">
@@ -37389,7 +37389,7 @@
       </c>
       <c r="AB274" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AC274" t="inlineStr">
@@ -37434,10 +37434,10 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>122254835</v>
+        <v>122254963</v>
       </c>
       <c r="B275" t="n">
-        <v>56288</v>
+        <v>56278</v>
       </c>
       <c r="C275" t="inlineStr">
         <is>
@@ -37450,21 +37450,21 @@
         </is>
       </c>
       <c r="E275" t="n">
-        <v>100111</v>
+        <v>205992</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
@@ -37488,10 +37488,10 @@
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>586473</v>
+        <v>586374</v>
       </c>
       <c r="R275" t="n">
-        <v>6311192</v>
+        <v>6311140</v>
       </c>
       <c r="S275" t="n">
         <v>5</v>
@@ -37523,7 +37523,7 @@
       </c>
       <c r="Z275" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>22:46</t>
         </is>
       </c>
       <c r="AA275" t="inlineStr">
@@ -37533,7 +37533,7 @@
       </c>
       <c r="AB275" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>22:47</t>
         </is>
       </c>
       <c r="AC275" t="inlineStr">
@@ -42186,10 +42186,10 @@
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>122254610</v>
+        <v>122254421</v>
       </c>
       <c r="B308" t="n">
-        <v>56290</v>
+        <v>56285</v>
       </c>
       <c r="C308" t="inlineStr">
         <is>
@@ -42202,21 +42202,21 @@
         </is>
       </c>
       <c r="E308" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
@@ -42240,10 +42240,10 @@
         </is>
       </c>
       <c r="Q308" t="n">
-        <v>586389</v>
+        <v>586468</v>
       </c>
       <c r="R308" t="n">
-        <v>6311141</v>
+        <v>6311181</v>
       </c>
       <c r="S308" t="n">
         <v>5</v>
@@ -42275,7 +42275,7 @@
       </c>
       <c r="Z308" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AA308" t="inlineStr">
@@ -42285,7 +42285,7 @@
       </c>
       <c r="AB308" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="AC308" t="inlineStr">
@@ -42330,10 +42330,10 @@
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>122254498</v>
+        <v>122254369</v>
       </c>
       <c r="B309" t="n">
-        <v>56271</v>
+        <v>56285</v>
       </c>
       <c r="C309" t="inlineStr">
         <is>
@@ -42342,25 +42342,25 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E309" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
@@ -42384,10 +42384,10 @@
         </is>
       </c>
       <c r="Q309" t="n">
-        <v>586393</v>
+        <v>586300</v>
       </c>
       <c r="R309" t="n">
-        <v>6311147</v>
+        <v>6311112</v>
       </c>
       <c r="S309" t="n">
         <v>5</v>
@@ -42419,7 +42419,7 @@
       </c>
       <c r="Z309" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AA309" t="inlineStr">
@@ -42429,7 +42429,7 @@
       </c>
       <c r="AB309" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AC309" t="inlineStr">
@@ -42474,10 +42474,10 @@
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>122254837</v>
+        <v>122254317</v>
       </c>
       <c r="B310" t="n">
-        <v>56288</v>
+        <v>56285</v>
       </c>
       <c r="C310" t="inlineStr">
         <is>
@@ -42490,21 +42490,21 @@
         </is>
       </c>
       <c r="E310" t="n">
-        <v>100111</v>
+        <v>100092</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
@@ -42528,10 +42528,10 @@
         </is>
       </c>
       <c r="Q310" t="n">
-        <v>586448</v>
+        <v>586438</v>
       </c>
       <c r="R310" t="n">
-        <v>6311154</v>
+        <v>6311222</v>
       </c>
       <c r="S310" t="n">
         <v>5</v>
@@ -42563,7 +42563,7 @@
       </c>
       <c r="Z310" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>23:22</t>
         </is>
       </c>
       <c r="AA310" t="inlineStr">
@@ -42573,7 +42573,7 @@
       </c>
       <c r="AB310" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>23:23</t>
         </is>
       </c>
       <c r="AC310" t="inlineStr">
@@ -42618,37 +42618,37 @@
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>122254173</v>
+        <v>122254845</v>
       </c>
       <c r="B311" t="n">
-        <v>56269</v>
+        <v>56288</v>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Dokumentation efterfrågas</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E311" t="n">
-        <v>100015</v>
+        <v>100111</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Barbastell</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>Barbastella barbastellus</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
@@ -42672,10 +42672,10 @@
         </is>
       </c>
       <c r="Q311" t="n">
-        <v>586415</v>
+        <v>586370</v>
       </c>
       <c r="R311" t="n">
-        <v>6311149</v>
+        <v>6311139</v>
       </c>
       <c r="S311" t="n">
         <v>5</v>
@@ -42707,7 +42707,7 @@
       </c>
       <c r="Z311" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>22:59</t>
         </is>
       </c>
       <c r="AA311" t="inlineStr">
@@ -42717,7 +42717,7 @@
       </c>
       <c r="AB311" t="inlineStr">
         <is>
-          <t>23:03</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AC311" t="inlineStr">
@@ -42762,10 +42762,10 @@
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>122254421</v>
+        <v>122254837</v>
       </c>
       <c r="B312" t="n">
-        <v>56285</v>
+        <v>56288</v>
       </c>
       <c r="C312" t="inlineStr">
         <is>
@@ -42778,21 +42778,21 @@
         </is>
       </c>
       <c r="E312" t="n">
-        <v>100092</v>
+        <v>100111</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
@@ -42816,10 +42816,10 @@
         </is>
       </c>
       <c r="Q312" t="n">
-        <v>586468</v>
+        <v>586448</v>
       </c>
       <c r="R312" t="n">
-        <v>6311181</v>
+        <v>6311154</v>
       </c>
       <c r="S312" t="n">
         <v>5</v>
@@ -42851,7 +42851,7 @@
       </c>
       <c r="Z312" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA312" t="inlineStr">
@@ -42861,7 +42861,7 @@
       </c>
       <c r="AB312" t="inlineStr">
         <is>
-          <t>22:33</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC312" t="inlineStr">
@@ -42906,10 +42906,10 @@
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>122254369</v>
+        <v>122254498</v>
       </c>
       <c r="B313" t="n">
-        <v>56285</v>
+        <v>56271</v>
       </c>
       <c r="C313" t="inlineStr">
         <is>
@@ -42918,25 +42918,25 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E313" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
@@ -42960,10 +42960,10 @@
         </is>
       </c>
       <c r="Q313" t="n">
-        <v>586300</v>
+        <v>586393</v>
       </c>
       <c r="R313" t="n">
-        <v>6311112</v>
+        <v>6311147</v>
       </c>
       <c r="S313" t="n">
         <v>5</v>
@@ -42995,7 +42995,7 @@
       </c>
       <c r="Z313" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AA313" t="inlineStr">
@@ -43005,7 +43005,7 @@
       </c>
       <c r="AB313" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AC313" t="inlineStr">
@@ -43050,10 +43050,10 @@
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>122254845</v>
+        <v>122254610</v>
       </c>
       <c r="B314" t="n">
-        <v>56288</v>
+        <v>56290</v>
       </c>
       <c r="C314" t="inlineStr">
         <is>
@@ -43066,21 +43066,21 @@
         </is>
       </c>
       <c r="E314" t="n">
-        <v>100111</v>
+        <v>205995</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
@@ -43104,10 +43104,10 @@
         </is>
       </c>
       <c r="Q314" t="n">
-        <v>586370</v>
+        <v>586389</v>
       </c>
       <c r="R314" t="n">
-        <v>6311139</v>
+        <v>6311141</v>
       </c>
       <c r="S314" t="n">
         <v>5</v>
@@ -43139,7 +43139,7 @@
       </c>
       <c r="Z314" t="inlineStr">
         <is>
-          <t>22:59</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA314" t="inlineStr">
@@ -43149,7 +43149,7 @@
       </c>
       <c r="AB314" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AC314" t="inlineStr">
@@ -43194,10 +43194,10 @@
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>122254317</v>
+        <v>122254855</v>
       </c>
       <c r="B315" t="n">
-        <v>56285</v>
+        <v>56288</v>
       </c>
       <c r="C315" t="inlineStr">
         <is>
@@ -43210,21 +43210,21 @@
         </is>
       </c>
       <c r="E315" t="n">
-        <v>100092</v>
+        <v>100111</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
@@ -43248,10 +43248,10 @@
         </is>
       </c>
       <c r="Q315" t="n">
-        <v>586438</v>
+        <v>586330</v>
       </c>
       <c r="R315" t="n">
-        <v>6311222</v>
+        <v>6311120</v>
       </c>
       <c r="S315" t="n">
         <v>5</v>
@@ -43283,7 +43283,7 @@
       </c>
       <c r="Z315" t="inlineStr">
         <is>
-          <t>23:22</t>
+          <t>22:57</t>
         </is>
       </c>
       <c r="AA315" t="inlineStr">
@@ -43293,7 +43293,7 @@
       </c>
       <c r="AB315" t="inlineStr">
         <is>
-          <t>23:23</t>
+          <t>22:58</t>
         </is>
       </c>
       <c r="AC315" t="inlineStr">
@@ -43338,7 +43338,7 @@
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>122254855</v>
+        <v>122254836</v>
       </c>
       <c r="B316" t="n">
         <v>56288</v>
@@ -43392,10 +43392,10 @@
         </is>
       </c>
       <c r="Q316" t="n">
-        <v>586330</v>
+        <v>586474</v>
       </c>
       <c r="R316" t="n">
-        <v>6311120</v>
+        <v>6311176</v>
       </c>
       <c r="S316" t="n">
         <v>5</v>
@@ -43427,7 +43427,7 @@
       </c>
       <c r="Z316" t="inlineStr">
         <is>
-          <t>22:57</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AA316" t="inlineStr">
@@ -43437,7 +43437,7 @@
       </c>
       <c r="AB316" t="inlineStr">
         <is>
-          <t>22:58</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AC316" t="inlineStr">
@@ -43482,10 +43482,10 @@
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>122254836</v>
+        <v>122254615</v>
       </c>
       <c r="B317" t="n">
-        <v>56288</v>
+        <v>56290</v>
       </c>
       <c r="C317" t="inlineStr">
         <is>
@@ -43498,21 +43498,21 @@
         </is>
       </c>
       <c r="E317" t="n">
-        <v>100111</v>
+        <v>205995</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
@@ -43536,10 +43536,10 @@
         </is>
       </c>
       <c r="Q317" t="n">
-        <v>586474</v>
+        <v>586329</v>
       </c>
       <c r="R317" t="n">
-        <v>6311176</v>
+        <v>6311120</v>
       </c>
       <c r="S317" t="n">
         <v>5</v>
@@ -43571,7 +43571,7 @@
       </c>
       <c r="Z317" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>22:57</t>
         </is>
       </c>
       <c r="AA317" t="inlineStr">
@@ -43581,7 +43581,7 @@
       </c>
       <c r="AB317" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>22:58</t>
         </is>
       </c>
       <c r="AC317" t="inlineStr">
@@ -43626,10 +43626,10 @@
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>122254615</v>
+        <v>122254414</v>
       </c>
       <c r="B318" t="n">
-        <v>56290</v>
+        <v>56285</v>
       </c>
       <c r="C318" t="inlineStr">
         <is>
@@ -43642,21 +43642,21 @@
         </is>
       </c>
       <c r="E318" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
@@ -43680,10 +43680,10 @@
         </is>
       </c>
       <c r="Q318" t="n">
-        <v>586329</v>
+        <v>586423</v>
       </c>
       <c r="R318" t="n">
-        <v>6311120</v>
+        <v>6311137</v>
       </c>
       <c r="S318" t="n">
         <v>5</v>
@@ -43715,7 +43715,7 @@
       </c>
       <c r="Z318" t="inlineStr">
         <is>
-          <t>22:57</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AA318" t="inlineStr">
@@ -43725,7 +43725,7 @@
       </c>
       <c r="AB318" t="inlineStr">
         <is>
-          <t>22:58</t>
+          <t>22:38</t>
         </is>
       </c>
       <c r="AC318" t="inlineStr">
@@ -43770,7 +43770,7 @@
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>122254414</v>
+        <v>122254393</v>
       </c>
       <c r="B319" t="n">
         <v>56285</v>
@@ -43824,10 +43824,10 @@
         </is>
       </c>
       <c r="Q319" t="n">
-        <v>586423</v>
+        <v>586396</v>
       </c>
       <c r="R319" t="n">
-        <v>6311137</v>
+        <v>6311146</v>
       </c>
       <c r="S319" t="n">
         <v>5</v>
@@ -43859,7 +43859,7 @@
       </c>
       <c r="Z319" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AA319" t="inlineStr">
@@ -43869,7 +43869,7 @@
       </c>
       <c r="AB319" t="inlineStr">
         <is>
-          <t>22:38</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AC319" t="inlineStr">
@@ -43914,7 +43914,7 @@
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>122254393</v>
+        <v>122254394</v>
       </c>
       <c r="B320" t="n">
         <v>56285</v>
@@ -43968,10 +43968,10 @@
         </is>
       </c>
       <c r="Q320" t="n">
-        <v>586396</v>
+        <v>586419</v>
       </c>
       <c r="R320" t="n">
-        <v>6311146</v>
+        <v>6311142</v>
       </c>
       <c r="S320" t="n">
         <v>5</v>
@@ -44003,17 +44003,17 @@
       </c>
       <c r="Z320" t="inlineStr">
         <is>
+          <t>22:43</t>
+        </is>
+      </c>
+      <c r="AA320" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AB320" t="inlineStr">
+        <is>
           <t>22:44</t>
-        </is>
-      </c>
-      <c r="AA320" t="inlineStr">
-        <is>
-          <t>2024-06-26</t>
-        </is>
-      </c>
-      <c r="AB320" t="inlineStr">
-        <is>
-          <t>22:45</t>
         </is>
       </c>
       <c r="AC320" t="inlineStr">
@@ -44058,10 +44058,10 @@
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>122254394</v>
+        <v>122254499</v>
       </c>
       <c r="B321" t="n">
-        <v>56285</v>
+        <v>56271</v>
       </c>
       <c r="C321" t="inlineStr">
         <is>
@@ -44070,25 +44070,25 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E321" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
@@ -44112,10 +44112,10 @@
         </is>
       </c>
       <c r="Q321" t="n">
-        <v>586419</v>
+        <v>586392</v>
       </c>
       <c r="R321" t="n">
-        <v>6311142</v>
+        <v>6311147</v>
       </c>
       <c r="S321" t="n">
         <v>5</v>
@@ -44147,7 +44147,7 @@
       </c>
       <c r="Z321" t="inlineStr">
         <is>
-          <t>22:43</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AA321" t="inlineStr">
@@ -44157,7 +44157,7 @@
       </c>
       <c r="AB321" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AC321" t="inlineStr">
@@ -44202,10 +44202,10 @@
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>122254499</v>
+        <v>122254626</v>
       </c>
       <c r="B322" t="n">
-        <v>56271</v>
+        <v>56290</v>
       </c>
       <c r="C322" t="inlineStr">
         <is>
@@ -44214,25 +44214,25 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E322" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
@@ -44256,10 +44256,10 @@
         </is>
       </c>
       <c r="Q322" t="n">
-        <v>586392</v>
+        <v>586313</v>
       </c>
       <c r="R322" t="n">
-        <v>6311147</v>
+        <v>6311124</v>
       </c>
       <c r="S322" t="n">
         <v>5</v>
@@ -44291,7 +44291,7 @@
       </c>
       <c r="Z322" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AA322" t="inlineStr">
@@ -44301,7 +44301,7 @@
       </c>
       <c r="AB322" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AC322" t="inlineStr">
@@ -44346,7 +44346,7 @@
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>122254626</v>
+        <v>122254612</v>
       </c>
       <c r="B323" t="n">
         <v>56290</v>
@@ -44400,10 +44400,10 @@
         </is>
       </c>
       <c r="Q323" t="n">
-        <v>586313</v>
+        <v>586371</v>
       </c>
       <c r="R323" t="n">
-        <v>6311124</v>
+        <v>6311135</v>
       </c>
       <c r="S323" t="n">
         <v>5</v>
@@ -44435,7 +44435,7 @@
       </c>
       <c r="Z323" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>22:59</t>
         </is>
       </c>
       <c r="AA323" t="inlineStr">
@@ -44445,7 +44445,7 @@
       </c>
       <c r="AB323" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AC323" t="inlineStr">
@@ -44490,7 +44490,7 @@
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>122254612</v>
+        <v>122254644</v>
       </c>
       <c r="B324" t="n">
         <v>56290</v>
@@ -44544,10 +44544,10 @@
         </is>
       </c>
       <c r="Q324" t="n">
-        <v>586371</v>
+        <v>586429</v>
       </c>
       <c r="R324" t="n">
-        <v>6311135</v>
+        <v>6311115</v>
       </c>
       <c r="S324" t="n">
         <v>5</v>
@@ -44579,7 +44579,7 @@
       </c>
       <c r="Z324" t="inlineStr">
         <is>
-          <t>22:59</t>
+          <t>22:36</t>
         </is>
       </c>
       <c r="AA324" t="inlineStr">
@@ -44589,7 +44589,7 @@
       </c>
       <c r="AB324" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AC324" t="inlineStr">
@@ -44634,7 +44634,7 @@
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>122254644</v>
+        <v>122254587</v>
       </c>
       <c r="B325" t="n">
         <v>56290</v>
@@ -44688,10 +44688,10 @@
         </is>
       </c>
       <c r="Q325" t="n">
-        <v>586429</v>
+        <v>586443</v>
       </c>
       <c r="R325" t="n">
-        <v>6311115</v>
+        <v>6311163</v>
       </c>
       <c r="S325" t="n">
         <v>5</v>
@@ -44723,7 +44723,7 @@
       </c>
       <c r="Z325" t="inlineStr">
         <is>
-          <t>22:36</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AA325" t="inlineStr">
@@ -44733,7 +44733,7 @@
       </c>
       <c r="AB325" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AC325" t="inlineStr">
@@ -44778,10 +44778,10 @@
     </row>
     <row r="326">
       <c r="A326" t="n">
-        <v>122254587</v>
+        <v>122254314</v>
       </c>
       <c r="B326" t="n">
-        <v>56290</v>
+        <v>56285</v>
       </c>
       <c r="C326" t="inlineStr">
         <is>
@@ -44794,21 +44794,21 @@
         </is>
       </c>
       <c r="E326" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
@@ -44835,7 +44835,7 @@
         <v>586443</v>
       </c>
       <c r="R326" t="n">
-        <v>6311163</v>
+        <v>6311164</v>
       </c>
       <c r="S326" t="n">
         <v>5</v>
@@ -44922,7 +44922,7 @@
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>122254314</v>
+        <v>122254315</v>
       </c>
       <c r="B327" t="n">
         <v>56285</v>
@@ -44976,10 +44976,10 @@
         </is>
       </c>
       <c r="Q327" t="n">
-        <v>586443</v>
+        <v>586441</v>
       </c>
       <c r="R327" t="n">
-        <v>6311164</v>
+        <v>6311155</v>
       </c>
       <c r="S327" t="n">
         <v>5</v>
@@ -45011,17 +45011,17 @@
       </c>
       <c r="Z327" t="inlineStr">
         <is>
+          <t>23:25</t>
+        </is>
+      </c>
+      <c r="AA327" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AB327" t="inlineStr">
+        <is>
           <t>23:26</t>
-        </is>
-      </c>
-      <c r="AA327" t="inlineStr">
-        <is>
-          <t>2024-06-26</t>
-        </is>
-      </c>
-      <c r="AB327" t="inlineStr">
-        <is>
-          <t>23:27</t>
         </is>
       </c>
       <c r="AC327" t="inlineStr">
@@ -45066,7 +45066,7 @@
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>122254315</v>
+        <v>122254343</v>
       </c>
       <c r="B328" t="n">
         <v>56285</v>
@@ -45120,10 +45120,10 @@
         </is>
       </c>
       <c r="Q328" t="n">
-        <v>586441</v>
+        <v>586388</v>
       </c>
       <c r="R328" t="n">
-        <v>6311155</v>
+        <v>6311142</v>
       </c>
       <c r="S328" t="n">
         <v>5</v>
@@ -45155,7 +45155,7 @@
       </c>
       <c r="Z328" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA328" t="inlineStr">
@@ -45165,7 +45165,7 @@
       </c>
       <c r="AB328" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AC328" t="inlineStr">
@@ -45210,10 +45210,10 @@
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>122254343</v>
+        <v>122254862</v>
       </c>
       <c r="B329" t="n">
-        <v>56285</v>
+        <v>56288</v>
       </c>
       <c r="C329" t="inlineStr">
         <is>
@@ -45226,21 +45226,21 @@
         </is>
       </c>
       <c r="E329" t="n">
-        <v>100092</v>
+        <v>100111</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
@@ -45264,10 +45264,10 @@
         </is>
       </c>
       <c r="Q329" t="n">
-        <v>586388</v>
+        <v>586288</v>
       </c>
       <c r="R329" t="n">
-        <v>6311142</v>
+        <v>6311100</v>
       </c>
       <c r="S329" t="n">
         <v>5</v>
@@ -45299,7 +45299,7 @@
       </c>
       <c r="Z329" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:55</t>
         </is>
       </c>
       <c r="AA329" t="inlineStr">
@@ -45309,7 +45309,7 @@
       </c>
       <c r="AB329" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>22:56</t>
         </is>
       </c>
       <c r="AC329" t="inlineStr">
@@ -45354,10 +45354,10 @@
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>122254862</v>
+        <v>122254632</v>
       </c>
       <c r="B330" t="n">
-        <v>56288</v>
+        <v>56290</v>
       </c>
       <c r="C330" t="inlineStr">
         <is>
@@ -45370,21 +45370,21 @@
         </is>
       </c>
       <c r="E330" t="n">
-        <v>100111</v>
+        <v>205995</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
@@ -45408,10 +45408,10 @@
         </is>
       </c>
       <c r="Q330" t="n">
-        <v>586288</v>
+        <v>586374</v>
       </c>
       <c r="R330" t="n">
-        <v>6311100</v>
+        <v>6311140</v>
       </c>
       <c r="S330" t="n">
         <v>5</v>
@@ -45443,7 +45443,7 @@
       </c>
       <c r="Z330" t="inlineStr">
         <is>
-          <t>22:55</t>
+          <t>22:46</t>
         </is>
       </c>
       <c r="AA330" t="inlineStr">
@@ -45453,7 +45453,7 @@
       </c>
       <c r="AB330" t="inlineStr">
         <is>
-          <t>22:56</t>
+          <t>22:47</t>
         </is>
       </c>
       <c r="AC330" t="inlineStr">
@@ -45498,10 +45498,10 @@
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>122254632</v>
+        <v>122254476</v>
       </c>
       <c r="B331" t="n">
-        <v>56290</v>
+        <v>56271</v>
       </c>
       <c r="C331" t="inlineStr">
         <is>
@@ -45510,25 +45510,25 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E331" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I331" t="inlineStr">
@@ -45552,10 +45552,10 @@
         </is>
       </c>
       <c r="Q331" t="n">
-        <v>586374</v>
+        <v>586418</v>
       </c>
       <c r="R331" t="n">
-        <v>6311140</v>
+        <v>6311167</v>
       </c>
       <c r="S331" t="n">
         <v>5</v>
@@ -45587,7 +45587,7 @@
       </c>
       <c r="Z331" t="inlineStr">
         <is>
-          <t>22:46</t>
+          <t>23:23</t>
         </is>
       </c>
       <c r="AA331" t="inlineStr">
@@ -45597,7 +45597,7 @@
       </c>
       <c r="AB331" t="inlineStr">
         <is>
-          <t>22:47</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="AC331" t="inlineStr">
@@ -45642,10 +45642,10 @@
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>122254476</v>
+        <v>122254950</v>
       </c>
       <c r="B332" t="n">
-        <v>56271</v>
+        <v>56278</v>
       </c>
       <c r="C332" t="inlineStr">
         <is>
@@ -45654,25 +45654,25 @@
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E332" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
@@ -45696,10 +45696,10 @@
         </is>
       </c>
       <c r="Q332" t="n">
-        <v>586418</v>
+        <v>586482</v>
       </c>
       <c r="R332" t="n">
-        <v>6311167</v>
+        <v>6311185</v>
       </c>
       <c r="S332" t="n">
         <v>5</v>
@@ -45731,7 +45731,7 @@
       </c>
       <c r="Z332" t="inlineStr">
         <is>
-          <t>23:23</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AA332" t="inlineStr">
@@ -45741,7 +45741,7 @@
       </c>
       <c r="AB332" t="inlineStr">
         <is>
-          <t>23:24</t>
+          <t>23:31</t>
         </is>
       </c>
       <c r="AC332" t="inlineStr">
@@ -45786,7 +45786,7 @@
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>122254950</v>
+        <v>122254956</v>
       </c>
       <c r="B333" t="n">
         <v>56278</v>
@@ -45840,10 +45840,10 @@
         </is>
       </c>
       <c r="Q333" t="n">
-        <v>586482</v>
+        <v>586441</v>
       </c>
       <c r="R333" t="n">
-        <v>6311185</v>
+        <v>6311152</v>
       </c>
       <c r="S333" t="n">
         <v>5</v>
@@ -45875,7 +45875,7 @@
       </c>
       <c r="Z333" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AA333" t="inlineStr">
@@ -45885,7 +45885,7 @@
       </c>
       <c r="AB333" t="inlineStr">
         <is>
-          <t>23:31</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AC333" t="inlineStr">
@@ -45930,10 +45930,10 @@
     </row>
     <row r="334">
       <c r="A334" t="n">
-        <v>122254956</v>
+        <v>122254416</v>
       </c>
       <c r="B334" t="n">
-        <v>56278</v>
+        <v>56285</v>
       </c>
       <c r="C334" t="inlineStr">
         <is>
@@ -45946,21 +45946,21 @@
         </is>
       </c>
       <c r="E334" t="n">
-        <v>205992</v>
+        <v>100092</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
@@ -45984,10 +45984,10 @@
         </is>
       </c>
       <c r="Q334" t="n">
-        <v>586441</v>
+        <v>586410</v>
       </c>
       <c r="R334" t="n">
-        <v>6311152</v>
+        <v>6311140</v>
       </c>
       <c r="S334" t="n">
         <v>5</v>
@@ -46019,7 +46019,7 @@
       </c>
       <c r="Z334" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="AA334" t="inlineStr">
@@ -46029,7 +46029,7 @@
       </c>
       <c r="AB334" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>22:34</t>
         </is>
       </c>
       <c r="AC334" t="inlineStr">
@@ -46074,10 +46074,10 @@
     </row>
     <row r="335">
       <c r="A335" t="n">
-        <v>122254416</v>
+        <v>122254514</v>
       </c>
       <c r="B335" t="n">
-        <v>56285</v>
+        <v>56271</v>
       </c>
       <c r="C335" t="inlineStr">
         <is>
@@ -46086,25 +46086,25 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E335" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I335" t="inlineStr">
@@ -46128,10 +46128,10 @@
         </is>
       </c>
       <c r="Q335" t="n">
-        <v>586410</v>
+        <v>586408</v>
       </c>
       <c r="R335" t="n">
-        <v>6311140</v>
+        <v>6311124</v>
       </c>
       <c r="S335" t="n">
         <v>5</v>
@@ -46163,7 +46163,7 @@
       </c>
       <c r="Z335" t="inlineStr">
         <is>
-          <t>22:33</t>
+          <t>22:43</t>
         </is>
       </c>
       <c r="AA335" t="inlineStr">
@@ -46173,7 +46173,7 @@
       </c>
       <c r="AB335" t="inlineStr">
         <is>
-          <t>22:34</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AC335" t="inlineStr">
@@ -46218,10 +46218,10 @@
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>122254514</v>
+        <v>122254617</v>
       </c>
       <c r="B336" t="n">
-        <v>56271</v>
+        <v>56290</v>
       </c>
       <c r="C336" t="inlineStr">
         <is>
@@ -46230,25 +46230,25 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E336" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
@@ -46272,10 +46272,10 @@
         </is>
       </c>
       <c r="Q336" t="n">
-        <v>586408</v>
+        <v>586317</v>
       </c>
       <c r="R336" t="n">
-        <v>6311124</v>
+        <v>6311115</v>
       </c>
       <c r="S336" t="n">
         <v>5</v>
@@ -46307,7 +46307,7 @@
       </c>
       <c r="Z336" t="inlineStr">
         <is>
-          <t>22:43</t>
+          <t>22:57</t>
         </is>
       </c>
       <c r="AA336" t="inlineStr">
@@ -46317,7 +46317,7 @@
       </c>
       <c r="AB336" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>22:58</t>
         </is>
       </c>
       <c r="AC336" t="inlineStr">
@@ -46362,7 +46362,7 @@
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>122254617</v>
+        <v>122254655</v>
       </c>
       <c r="B337" t="n">
         <v>56290</v>
@@ -46416,10 +46416,10 @@
         </is>
       </c>
       <c r="Q337" t="n">
-        <v>586317</v>
+        <v>586475</v>
       </c>
       <c r="R337" t="n">
-        <v>6311115</v>
+        <v>6311187</v>
       </c>
       <c r="S337" t="n">
         <v>5</v>
@@ -46451,7 +46451,7 @@
       </c>
       <c r="Z337" t="inlineStr">
         <is>
-          <t>22:57</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AA337" t="inlineStr">
@@ -46461,7 +46461,7 @@
       </c>
       <c r="AB337" t="inlineStr">
         <is>
-          <t>22:58</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="AC337" t="inlineStr">
@@ -46506,7 +46506,7 @@
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>122254655</v>
+        <v>122254651</v>
       </c>
       <c r="B338" t="n">
         <v>56290</v>
@@ -46560,10 +46560,10 @@
         </is>
       </c>
       <c r="Q338" t="n">
-        <v>586475</v>
+        <v>586425</v>
       </c>
       <c r="R338" t="n">
-        <v>6311187</v>
+        <v>6311113</v>
       </c>
       <c r="S338" t="n">
         <v>5</v>
@@ -46595,7 +46595,7 @@
       </c>
       <c r="Z338" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="AA338" t="inlineStr">
@@ -46605,7 +46605,7 @@
       </c>
       <c r="AB338" t="inlineStr">
         <is>
-          <t>22:33</t>
+          <t>22:36</t>
         </is>
       </c>
       <c r="AC338" t="inlineStr">
@@ -46650,10 +46650,10 @@
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>122254651</v>
+        <v>122254952</v>
       </c>
       <c r="B339" t="n">
-        <v>56290</v>
+        <v>56278</v>
       </c>
       <c r="C339" t="inlineStr">
         <is>
@@ -46666,21 +46666,21 @@
         </is>
       </c>
       <c r="E339" t="n">
-        <v>205995</v>
+        <v>205992</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I339" t="inlineStr">
@@ -46704,10 +46704,10 @@
         </is>
       </c>
       <c r="Q339" t="n">
-        <v>586425</v>
+        <v>586455</v>
       </c>
       <c r="R339" t="n">
-        <v>6311113</v>
+        <v>6311156</v>
       </c>
       <c r="S339" t="n">
         <v>5</v>
@@ -46739,7 +46739,7 @@
       </c>
       <c r="Z339" t="inlineStr">
         <is>
-          <t>22:35</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AA339" t="inlineStr">
@@ -46749,7 +46749,7 @@
       </c>
       <c r="AB339" t="inlineStr">
         <is>
-          <t>22:36</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AC339" t="inlineStr">
@@ -46794,7 +46794,7 @@
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>122254952</v>
+        <v>122254953</v>
       </c>
       <c r="B340" t="n">
         <v>56278</v>
@@ -46848,10 +46848,10 @@
         </is>
       </c>
       <c r="Q340" t="n">
-        <v>586455</v>
+        <v>586449</v>
       </c>
       <c r="R340" t="n">
-        <v>6311156</v>
+        <v>6311155</v>
       </c>
       <c r="S340" t="n">
         <v>5</v>
@@ -46883,17 +46883,17 @@
       </c>
       <c r="Z340" t="inlineStr">
         <is>
+          <t>23:27</t>
+        </is>
+      </c>
+      <c r="AA340" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AB340" t="inlineStr">
+        <is>
           <t>23:28</t>
-        </is>
-      </c>
-      <c r="AA340" t="inlineStr">
-        <is>
-          <t>2024-06-26</t>
-        </is>
-      </c>
-      <c r="AB340" t="inlineStr">
-        <is>
-          <t>23:29</t>
         </is>
       </c>
       <c r="AC340" t="inlineStr">
@@ -46938,10 +46938,10 @@
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>122254953</v>
+        <v>122254512</v>
       </c>
       <c r="B341" t="n">
-        <v>56278</v>
+        <v>56271</v>
       </c>
       <c r="C341" t="inlineStr">
         <is>
@@ -46950,25 +46950,25 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E341" t="n">
-        <v>205992</v>
+        <v>205998</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I341" t="inlineStr">
@@ -46992,10 +46992,10 @@
         </is>
       </c>
       <c r="Q341" t="n">
-        <v>586449</v>
+        <v>586379</v>
       </c>
       <c r="R341" t="n">
-        <v>6311155</v>
+        <v>6311136</v>
       </c>
       <c r="S341" t="n">
         <v>5</v>
@@ -47027,7 +47027,7 @@
       </c>
       <c r="Z341" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AA341" t="inlineStr">
@@ -47037,7 +47037,7 @@
       </c>
       <c r="AB341" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>22:46</t>
         </is>
       </c>
       <c r="AC341" t="inlineStr">
@@ -47082,10 +47082,10 @@
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>122254512</v>
+        <v>122254608</v>
       </c>
       <c r="B342" t="n">
-        <v>56271</v>
+        <v>56290</v>
       </c>
       <c r="C342" t="inlineStr">
         <is>
@@ -47094,25 +47094,25 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E342" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
@@ -47136,10 +47136,10 @@
         </is>
       </c>
       <c r="Q342" t="n">
-        <v>586379</v>
+        <v>586393</v>
       </c>
       <c r="R342" t="n">
-        <v>6311136</v>
+        <v>6311147</v>
       </c>
       <c r="S342" t="n">
         <v>5</v>
@@ -47171,7 +47171,7 @@
       </c>
       <c r="Z342" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AA342" t="inlineStr">
@@ -47181,7 +47181,7 @@
       </c>
       <c r="AB342" t="inlineStr">
         <is>
-          <t>22:46</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AC342" t="inlineStr">
@@ -47226,10 +47226,10 @@
     </row>
     <row r="343">
       <c r="A343" t="n">
-        <v>122254608</v>
+        <v>122254503</v>
       </c>
       <c r="B343" t="n">
-        <v>56290</v>
+        <v>56271</v>
       </c>
       <c r="C343" t="inlineStr">
         <is>
@@ -47238,25 +47238,25 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E343" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
@@ -47280,10 +47280,10 @@
         </is>
       </c>
       <c r="Q343" t="n">
-        <v>586393</v>
+        <v>586313</v>
       </c>
       <c r="R343" t="n">
-        <v>6311147</v>
+        <v>6311124</v>
       </c>
       <c r="S343" t="n">
         <v>5</v>
@@ -47315,7 +47315,7 @@
       </c>
       <c r="Z343" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AA343" t="inlineStr">
@@ -47325,7 +47325,7 @@
       </c>
       <c r="AB343" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AC343" t="inlineStr">
@@ -47370,7 +47370,7 @@
     </row>
     <row r="344">
       <c r="A344" t="n">
-        <v>122254503</v>
+        <v>122254513</v>
       </c>
       <c r="B344" t="n">
         <v>56271</v>
@@ -47424,10 +47424,10 @@
         </is>
       </c>
       <c r="Q344" t="n">
-        <v>586313</v>
+        <v>586396</v>
       </c>
       <c r="R344" t="n">
-        <v>6311124</v>
+        <v>6311146</v>
       </c>
       <c r="S344" t="n">
         <v>5</v>
@@ -47459,7 +47459,7 @@
       </c>
       <c r="Z344" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AA344" t="inlineStr">
@@ -47469,7 +47469,7 @@
       </c>
       <c r="AB344" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AC344" t="inlineStr">
@@ -47514,10 +47514,10 @@
     </row>
     <row r="345">
       <c r="A345" t="n">
-        <v>122254513</v>
+        <v>122254307</v>
       </c>
       <c r="B345" t="n">
-        <v>56271</v>
+        <v>56285</v>
       </c>
       <c r="C345" t="inlineStr">
         <is>
@@ -47526,25 +47526,25 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E345" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
@@ -47568,10 +47568,10 @@
         </is>
       </c>
       <c r="Q345" t="n">
-        <v>586396</v>
+        <v>586477</v>
       </c>
       <c r="R345" t="n">
-        <v>6311146</v>
+        <v>6311186</v>
       </c>
       <c r="S345" t="n">
         <v>5</v>
@@ -47603,7 +47603,7 @@
       </c>
       <c r="Z345" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AA345" t="inlineStr">
@@ -47613,7 +47613,7 @@
       </c>
       <c r="AB345" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AC345" t="inlineStr">
@@ -47658,7 +47658,7 @@
     </row>
     <row r="346">
       <c r="A346" t="n">
-        <v>122254307</v>
+        <v>122254310</v>
       </c>
       <c r="B346" t="n">
         <v>56285</v>
@@ -47712,10 +47712,10 @@
         </is>
       </c>
       <c r="Q346" t="n">
-        <v>586477</v>
+        <v>586452</v>
       </c>
       <c r="R346" t="n">
-        <v>6311186</v>
+        <v>6311156</v>
       </c>
       <c r="S346" t="n">
         <v>5</v>
@@ -47747,7 +47747,7 @@
       </c>
       <c r="Z346" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA346" t="inlineStr">
@@ -47757,7 +47757,7 @@
       </c>
       <c r="AB346" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC346" t="inlineStr">
@@ -47802,10 +47802,10 @@
     </row>
     <row r="347">
       <c r="A347" t="n">
-        <v>122254310</v>
+        <v>122254636</v>
       </c>
       <c r="B347" t="n">
-        <v>56285</v>
+        <v>56290</v>
       </c>
       <c r="C347" t="inlineStr">
         <is>
@@ -47818,21 +47818,21 @@
         </is>
       </c>
       <c r="E347" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I347" t="inlineStr">
@@ -47856,10 +47856,10 @@
         </is>
       </c>
       <c r="Q347" t="n">
-        <v>586452</v>
+        <v>586418</v>
       </c>
       <c r="R347" t="n">
-        <v>6311156</v>
+        <v>6311145</v>
       </c>
       <c r="S347" t="n">
         <v>5</v>
@@ -47891,7 +47891,7 @@
       </c>
       <c r="Z347" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AA347" t="inlineStr">
@@ -47901,7 +47901,7 @@
       </c>
       <c r="AB347" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AC347" t="inlineStr">
@@ -47946,7 +47946,7 @@
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>122254636</v>
+        <v>122254657</v>
       </c>
       <c r="B348" t="n">
         <v>56290</v>
@@ -48000,10 +48000,10 @@
         </is>
       </c>
       <c r="Q348" t="n">
-        <v>586418</v>
+        <v>586488</v>
       </c>
       <c r="R348" t="n">
-        <v>6311145</v>
+        <v>6311184</v>
       </c>
       <c r="S348" t="n">
         <v>5</v>
@@ -48035,7 +48035,7 @@
       </c>
       <c r="Z348" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>22:31</t>
         </is>
       </c>
       <c r="AA348" t="inlineStr">
@@ -48045,7 +48045,7 @@
       </c>
       <c r="AB348" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AC348" t="inlineStr">
@@ -48090,10 +48090,10 @@
     </row>
     <row r="349">
       <c r="A349" t="n">
-        <v>122254657</v>
+        <v>122254474</v>
       </c>
       <c r="B349" t="n">
-        <v>56290</v>
+        <v>56271</v>
       </c>
       <c r="C349" t="inlineStr">
         <is>
@@ -48102,25 +48102,25 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E349" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I349" t="inlineStr">
@@ -48144,10 +48144,10 @@
         </is>
       </c>
       <c r="Q349" t="n">
-        <v>586488</v>
+        <v>586443</v>
       </c>
       <c r="R349" t="n">
-        <v>6311184</v>
+        <v>6311164</v>
       </c>
       <c r="S349" t="n">
         <v>5</v>
@@ -48179,7 +48179,7 @@
       </c>
       <c r="Z349" t="inlineStr">
         <is>
-          <t>22:31</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AA349" t="inlineStr">
@@ -48189,7 +48189,7 @@
       </c>
       <c r="AB349" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AC349" t="inlineStr">
@@ -48234,10 +48234,10 @@
     </row>
     <row r="350">
       <c r="A350" t="n">
-        <v>122254474</v>
+        <v>122254586</v>
       </c>
       <c r="B350" t="n">
-        <v>56271</v>
+        <v>56290</v>
       </c>
       <c r="C350" t="inlineStr">
         <is>
@@ -48246,25 +48246,25 @@
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E350" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I350" t="inlineStr">
@@ -48288,10 +48288,10 @@
         </is>
       </c>
       <c r="Q350" t="n">
-        <v>586443</v>
+        <v>586446</v>
       </c>
       <c r="R350" t="n">
-        <v>6311164</v>
+        <v>6311158</v>
       </c>
       <c r="S350" t="n">
         <v>5</v>
@@ -48378,10 +48378,10 @@
     </row>
     <row r="351">
       <c r="A351" t="n">
-        <v>122254586</v>
+        <v>122254411</v>
       </c>
       <c r="B351" t="n">
-        <v>56290</v>
+        <v>56285</v>
       </c>
       <c r="C351" t="inlineStr">
         <is>
@@ -48394,21 +48394,21 @@
         </is>
       </c>
       <c r="E351" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I351" t="inlineStr">
@@ -48432,10 +48432,10 @@
         </is>
       </c>
       <c r="Q351" t="n">
-        <v>586446</v>
+        <v>586414</v>
       </c>
       <c r="R351" t="n">
-        <v>6311158</v>
+        <v>6311126</v>
       </c>
       <c r="S351" t="n">
         <v>5</v>
@@ -48467,7 +48467,7 @@
       </c>
       <c r="Z351" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AA351" t="inlineStr">
@@ -48477,7 +48477,7 @@
       </c>
       <c r="AB351" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>22:38</t>
         </is>
       </c>
       <c r="AC351" t="inlineStr">
@@ -48522,7 +48522,7 @@
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>122254411</v>
+        <v>122254373</v>
       </c>
       <c r="B352" t="n">
         <v>56285</v>
@@ -48576,10 +48576,10 @@
         </is>
       </c>
       <c r="Q352" t="n">
-        <v>586414</v>
+        <v>586307</v>
       </c>
       <c r="R352" t="n">
-        <v>6311126</v>
+        <v>6311133</v>
       </c>
       <c r="S352" t="n">
         <v>5</v>
@@ -48611,7 +48611,7 @@
       </c>
       <c r="Z352" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>22:49</t>
         </is>
       </c>
       <c r="AA352" t="inlineStr">
@@ -48621,7 +48621,7 @@
       </c>
       <c r="AB352" t="inlineStr">
         <is>
-          <t>22:38</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AC352" t="inlineStr">
@@ -48666,7 +48666,7 @@
     </row>
     <row r="353">
       <c r="A353" t="n">
-        <v>122254373</v>
+        <v>122254391</v>
       </c>
       <c r="B353" t="n">
         <v>56285</v>
@@ -48720,10 +48720,10 @@
         </is>
       </c>
       <c r="Q353" t="n">
-        <v>586307</v>
+        <v>586379</v>
       </c>
       <c r="R353" t="n">
-        <v>6311133</v>
+        <v>6311136</v>
       </c>
       <c r="S353" t="n">
         <v>5</v>
@@ -48755,7 +48755,7 @@
       </c>
       <c r="Z353" t="inlineStr">
         <is>
-          <t>22:49</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AA353" t="inlineStr">
@@ -48765,7 +48765,7 @@
       </c>
       <c r="AB353" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>22:46</t>
         </is>
       </c>
       <c r="AC353" t="inlineStr">
@@ -48810,10 +48810,10 @@
     </row>
     <row r="354">
       <c r="A354" t="n">
-        <v>122254391</v>
+        <v>122254844</v>
       </c>
       <c r="B354" t="n">
-        <v>56285</v>
+        <v>56288</v>
       </c>
       <c r="C354" t="inlineStr">
         <is>
@@ -48826,21 +48826,21 @@
         </is>
       </c>
       <c r="E354" t="n">
-        <v>100092</v>
+        <v>100111</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I354" t="inlineStr">
@@ -48864,10 +48864,10 @@
         </is>
       </c>
       <c r="Q354" t="n">
-        <v>586379</v>
+        <v>586387</v>
       </c>
       <c r="R354" t="n">
-        <v>6311136</v>
+        <v>6311141</v>
       </c>
       <c r="S354" t="n">
         <v>5</v>
@@ -48899,7 +48899,7 @@
       </c>
       <c r="Z354" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA354" t="inlineStr">
@@ -48909,7 +48909,7 @@
       </c>
       <c r="AB354" t="inlineStr">
         <is>
-          <t>22:46</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AC354" t="inlineStr">
@@ -48954,10 +48954,10 @@
     </row>
     <row r="355">
       <c r="A355" t="n">
-        <v>122254844</v>
+        <v>122254318</v>
       </c>
       <c r="B355" t="n">
-        <v>56288</v>
+        <v>56285</v>
       </c>
       <c r="C355" t="inlineStr">
         <is>
@@ -48970,21 +48970,21 @@
         </is>
       </c>
       <c r="E355" t="n">
-        <v>100111</v>
+        <v>100092</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I355" t="inlineStr">
@@ -49008,10 +49008,10 @@
         </is>
       </c>
       <c r="Q355" t="n">
-        <v>586387</v>
+        <v>586455</v>
       </c>
       <c r="R355" t="n">
-        <v>6311141</v>
+        <v>6311228</v>
       </c>
       <c r="S355" t="n">
         <v>5</v>
@@ -49043,7 +49043,7 @@
       </c>
       <c r="Z355" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>23:22</t>
         </is>
       </c>
       <c r="AA355" t="inlineStr">
@@ -49053,7 +49053,7 @@
       </c>
       <c r="AB355" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>23:23</t>
         </is>
       </c>
       <c r="AC355" t="inlineStr">
@@ -49098,7 +49098,7 @@
     </row>
     <row r="356">
       <c r="A356" t="n">
-        <v>122254318</v>
+        <v>122254350</v>
       </c>
       <c r="B356" t="n">
         <v>56285</v>
@@ -49152,10 +49152,10 @@
         </is>
       </c>
       <c r="Q356" t="n">
-        <v>586455</v>
+        <v>586330</v>
       </c>
       <c r="R356" t="n">
-        <v>6311228</v>
+        <v>6311120</v>
       </c>
       <c r="S356" t="n">
         <v>5</v>
@@ -49187,7 +49187,7 @@
       </c>
       <c r="Z356" t="inlineStr">
         <is>
-          <t>23:22</t>
+          <t>22:57</t>
         </is>
       </c>
       <c r="AA356" t="inlineStr">
@@ -49197,7 +49197,7 @@
       </c>
       <c r="AB356" t="inlineStr">
         <is>
-          <t>23:23</t>
+          <t>22:58</t>
         </is>
       </c>
       <c r="AC356" t="inlineStr">
@@ -49242,10 +49242,10 @@
     </row>
     <row r="357">
       <c r="A357" t="n">
-        <v>122254350</v>
+        <v>122254496</v>
       </c>
       <c r="B357" t="n">
-        <v>56285</v>
+        <v>56271</v>
       </c>
       <c r="C357" t="inlineStr">
         <is>
@@ -49254,25 +49254,25 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E357" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I357" t="inlineStr">
@@ -49296,10 +49296,10 @@
         </is>
       </c>
       <c r="Q357" t="n">
-        <v>586330</v>
+        <v>586415</v>
       </c>
       <c r="R357" t="n">
-        <v>6311120</v>
+        <v>6311146</v>
       </c>
       <c r="S357" t="n">
         <v>5</v>
@@ -49331,7 +49331,7 @@
       </c>
       <c r="Z357" t="inlineStr">
         <is>
-          <t>22:57</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AA357" t="inlineStr">
@@ -49341,7 +49341,7 @@
       </c>
       <c r="AB357" t="inlineStr">
         <is>
-          <t>22:58</t>
+          <t>23:03</t>
         </is>
       </c>
       <c r="AC357" t="inlineStr">
@@ -49386,10 +49386,10 @@
     </row>
     <row r="358">
       <c r="A358" t="n">
-        <v>122254496</v>
+        <v>122254649</v>
       </c>
       <c r="B358" t="n">
-        <v>56271</v>
+        <v>56290</v>
       </c>
       <c r="C358" t="inlineStr">
         <is>
@@ -49398,25 +49398,25 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E358" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H358" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I358" t="inlineStr">
@@ -49440,10 +49440,10 @@
         </is>
       </c>
       <c r="Q358" t="n">
-        <v>586415</v>
+        <v>586422</v>
       </c>
       <c r="R358" t="n">
-        <v>6311146</v>
+        <v>6311100</v>
       </c>
       <c r="S358" t="n">
         <v>5</v>
@@ -49475,7 +49475,7 @@
       </c>
       <c r="Z358" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="AA358" t="inlineStr">
@@ -49485,7 +49485,7 @@
       </c>
       <c r="AB358" t="inlineStr">
         <is>
-          <t>23:03</t>
+          <t>22:36</t>
         </is>
       </c>
       <c r="AC358" t="inlineStr">
@@ -49530,10 +49530,10 @@
     </row>
     <row r="359">
       <c r="A359" t="n">
-        <v>122254649</v>
+        <v>122254473</v>
       </c>
       <c r="B359" t="n">
-        <v>56290</v>
+        <v>56271</v>
       </c>
       <c r="C359" t="inlineStr">
         <is>
@@ -49542,25 +49542,25 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E359" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I359" t="inlineStr">
@@ -49584,10 +49584,10 @@
         </is>
       </c>
       <c r="Q359" t="n">
-        <v>586422</v>
+        <v>586450</v>
       </c>
       <c r="R359" t="n">
-        <v>6311100</v>
+        <v>6311152</v>
       </c>
       <c r="S359" t="n">
         <v>5</v>
@@ -49619,7 +49619,7 @@
       </c>
       <c r="Z359" t="inlineStr">
         <is>
-          <t>22:35</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA359" t="inlineStr">
@@ -49629,7 +49629,7 @@
       </c>
       <c r="AB359" t="inlineStr">
         <is>
-          <t>22:36</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC359" t="inlineStr">
@@ -49674,10 +49674,10 @@
     </row>
     <row r="360">
       <c r="A360" t="n">
-        <v>122254473</v>
+        <v>122254654</v>
       </c>
       <c r="B360" t="n">
-        <v>56271</v>
+        <v>56290</v>
       </c>
       <c r="C360" t="inlineStr">
         <is>
@@ -49686,25 +49686,25 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E360" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I360" t="inlineStr">
@@ -49728,10 +49728,10 @@
         </is>
       </c>
       <c r="Q360" t="n">
-        <v>586450</v>
+        <v>586467</v>
       </c>
       <c r="R360" t="n">
-        <v>6311152</v>
+        <v>6311178</v>
       </c>
       <c r="S360" t="n">
         <v>5</v>
@@ -49763,7 +49763,7 @@
       </c>
       <c r="Z360" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AA360" t="inlineStr">
@@ -49773,7 +49773,7 @@
       </c>
       <c r="AB360" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="AC360" t="inlineStr">
@@ -49818,10 +49818,10 @@
     </row>
     <row r="361">
       <c r="A361" t="n">
-        <v>122254654</v>
+        <v>122254957</v>
       </c>
       <c r="B361" t="n">
-        <v>56290</v>
+        <v>56278</v>
       </c>
       <c r="C361" t="inlineStr">
         <is>
@@ -49834,21 +49834,21 @@
         </is>
       </c>
       <c r="E361" t="n">
-        <v>205995</v>
+        <v>205992</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I361" t="inlineStr">
@@ -49872,10 +49872,10 @@
         </is>
       </c>
       <c r="Q361" t="n">
-        <v>586467</v>
+        <v>586444</v>
       </c>
       <c r="R361" t="n">
-        <v>6311178</v>
+        <v>6311160</v>
       </c>
       <c r="S361" t="n">
         <v>5</v>
@@ -49907,7 +49907,7 @@
       </c>
       <c r="Z361" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="AA361" t="inlineStr">
@@ -49917,7 +49917,7 @@
       </c>
       <c r="AB361" t="inlineStr">
         <is>
-          <t>22:33</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AC361" t="inlineStr">
@@ -49962,10 +49962,10 @@
     </row>
     <row r="362">
       <c r="A362" t="n">
-        <v>122254957</v>
+        <v>122254519</v>
       </c>
       <c r="B362" t="n">
-        <v>56278</v>
+        <v>56271</v>
       </c>
       <c r="C362" t="inlineStr">
         <is>
@@ -49974,25 +49974,25 @@
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E362" t="n">
-        <v>205992</v>
+        <v>205998</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I362" t="inlineStr">
@@ -50016,10 +50016,10 @@
         </is>
       </c>
       <c r="Q362" t="n">
-        <v>586444</v>
+        <v>586424</v>
       </c>
       <c r="R362" t="n">
-        <v>6311160</v>
+        <v>6311135</v>
       </c>
       <c r="S362" t="n">
         <v>5</v>
@@ -50051,7 +50051,7 @@
       </c>
       <c r="Z362" t="inlineStr">
         <is>
-          <t>23:24</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AA362" t="inlineStr">
@@ -50061,7 +50061,7 @@
       </c>
       <c r="AB362" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>22:38</t>
         </is>
       </c>
       <c r="AC362" t="inlineStr">
@@ -50106,10 +50106,10 @@
     </row>
     <row r="363">
       <c r="A363" t="n">
-        <v>122254519</v>
+        <v>122254392</v>
       </c>
       <c r="B363" t="n">
-        <v>56271</v>
+        <v>56285</v>
       </c>
       <c r="C363" t="inlineStr">
         <is>
@@ -50118,25 +50118,25 @@
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E363" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I363" t="inlineStr">
@@ -50160,10 +50160,10 @@
         </is>
       </c>
       <c r="Q363" t="n">
-        <v>586424</v>
+        <v>586384</v>
       </c>
       <c r="R363" t="n">
-        <v>6311135</v>
+        <v>6311139</v>
       </c>
       <c r="S363" t="n">
         <v>5</v>
@@ -50195,7 +50195,7 @@
       </c>
       <c r="Z363" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AA363" t="inlineStr">
@@ -50205,7 +50205,7 @@
       </c>
       <c r="AB363" t="inlineStr">
         <is>
-          <t>22:38</t>
+          <t>22:46</t>
         </is>
       </c>
       <c r="AC363" t="inlineStr">
@@ -50394,10 +50394,10 @@
     </row>
     <row r="365">
       <c r="A365" t="n">
-        <v>122254392</v>
+        <v>122254472</v>
       </c>
       <c r="B365" t="n">
-        <v>56285</v>
+        <v>56271</v>
       </c>
       <c r="C365" t="inlineStr">
         <is>
@@ -50406,25 +50406,25 @@
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E365" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I365" t="inlineStr">
@@ -50448,10 +50448,10 @@
         </is>
       </c>
       <c r="Q365" t="n">
-        <v>586384</v>
+        <v>586455</v>
       </c>
       <c r="R365" t="n">
-        <v>6311139</v>
+        <v>6311159</v>
       </c>
       <c r="S365" t="n">
         <v>5</v>
@@ -50483,7 +50483,7 @@
       </c>
       <c r="Z365" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AA365" t="inlineStr">
@@ -50493,7 +50493,7 @@
       </c>
       <c r="AB365" t="inlineStr">
         <is>
-          <t>22:46</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AC365" t="inlineStr">
@@ -50538,10 +50538,10 @@
     </row>
     <row r="366">
       <c r="A366" t="n">
-        <v>122254341</v>
+        <v>122254650</v>
       </c>
       <c r="B366" t="n">
-        <v>56285</v>
+        <v>56290</v>
       </c>
       <c r="C366" t="inlineStr">
         <is>
@@ -50554,21 +50554,21 @@
         </is>
       </c>
       <c r="E366" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I366" t="inlineStr">
@@ -50592,10 +50592,10 @@
         </is>
       </c>
       <c r="Q366" t="n">
-        <v>586415</v>
+        <v>586422</v>
       </c>
       <c r="R366" t="n">
-        <v>6311146</v>
+        <v>6311105</v>
       </c>
       <c r="S366" t="n">
         <v>5</v>
@@ -50627,7 +50627,7 @@
       </c>
       <c r="Z366" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="AA366" t="inlineStr">
@@ -50637,7 +50637,7 @@
       </c>
       <c r="AB366" t="inlineStr">
         <is>
-          <t>23:03</t>
+          <t>22:36</t>
         </is>
       </c>
       <c r="AC366" t="inlineStr">
@@ -50682,10 +50682,10 @@
     </row>
     <row r="367">
       <c r="A367" t="n">
-        <v>122254878</v>
+        <v>122254954</v>
       </c>
       <c r="B367" t="n">
-        <v>56288</v>
+        <v>56278</v>
       </c>
       <c r="C367" t="inlineStr">
         <is>
@@ -50698,21 +50698,21 @@
         </is>
       </c>
       <c r="E367" t="n">
-        <v>100111</v>
+        <v>205992</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I367" t="inlineStr">
@@ -50736,10 +50736,10 @@
         </is>
       </c>
       <c r="Q367" t="n">
-        <v>586280</v>
+        <v>586442</v>
       </c>
       <c r="R367" t="n">
-        <v>6311103</v>
+        <v>6311152</v>
       </c>
       <c r="S367" t="n">
         <v>5</v>
@@ -50771,7 +50771,7 @@
       </c>
       <c r="Z367" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AA367" t="inlineStr">
@@ -50781,7 +50781,7 @@
       </c>
       <c r="AB367" t="inlineStr">
         <is>
-          <t>22:52</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AC367" t="inlineStr">
@@ -50826,10 +50826,10 @@
     </row>
     <row r="368">
       <c r="A368" t="n">
-        <v>122254472</v>
+        <v>122254951</v>
       </c>
       <c r="B368" t="n">
-        <v>56271</v>
+        <v>56278</v>
       </c>
       <c r="C368" t="inlineStr">
         <is>
@@ -50838,25 +50838,25 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E368" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H368" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I368" t="inlineStr">
@@ -50880,10 +50880,10 @@
         </is>
       </c>
       <c r="Q368" t="n">
-        <v>586455</v>
+        <v>586459</v>
       </c>
       <c r="R368" t="n">
-        <v>6311159</v>
+        <v>6311154</v>
       </c>
       <c r="S368" t="n">
         <v>5</v>
@@ -50970,7 +50970,7 @@
     </row>
     <row r="369">
       <c r="A369" t="n">
-        <v>122254650</v>
+        <v>122254606</v>
       </c>
       <c r="B369" t="n">
         <v>56290</v>
@@ -51024,10 +51024,10 @@
         </is>
       </c>
       <c r="Q369" t="n">
-        <v>586422</v>
+        <v>586415</v>
       </c>
       <c r="R369" t="n">
-        <v>6311105</v>
+        <v>6311146</v>
       </c>
       <c r="S369" t="n">
         <v>5</v>
@@ -51059,7 +51059,7 @@
       </c>
       <c r="Z369" t="inlineStr">
         <is>
-          <t>22:35</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AA369" t="inlineStr">
@@ -51069,7 +51069,7 @@
       </c>
       <c r="AB369" t="inlineStr">
         <is>
-          <t>22:36</t>
+          <t>23:03</t>
         </is>
       </c>
       <c r="AC369" t="inlineStr">
@@ -51114,10 +51114,10 @@
     </row>
     <row r="370">
       <c r="A370" t="n">
-        <v>122254954</v>
+        <v>122254341</v>
       </c>
       <c r="B370" t="n">
-        <v>56278</v>
+        <v>56285</v>
       </c>
       <c r="C370" t="inlineStr">
         <is>
@@ -51130,21 +51130,21 @@
         </is>
       </c>
       <c r="E370" t="n">
-        <v>205992</v>
+        <v>100092</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I370" t="inlineStr">
@@ -51168,10 +51168,10 @@
         </is>
       </c>
       <c r="Q370" t="n">
-        <v>586442</v>
+        <v>586415</v>
       </c>
       <c r="R370" t="n">
-        <v>6311152</v>
+        <v>6311146</v>
       </c>
       <c r="S370" t="n">
         <v>5</v>
@@ -51203,7 +51203,7 @@
       </c>
       <c r="Z370" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AA370" t="inlineStr">
@@ -51213,7 +51213,7 @@
       </c>
       <c r="AB370" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>23:03</t>
         </is>
       </c>
       <c r="AC370" t="inlineStr">
@@ -51258,10 +51258,10 @@
     </row>
     <row r="371">
       <c r="A371" t="n">
-        <v>122254951</v>
+        <v>122254878</v>
       </c>
       <c r="B371" t="n">
-        <v>56278</v>
+        <v>56288</v>
       </c>
       <c r="C371" t="inlineStr">
         <is>
@@ -51274,21 +51274,21 @@
         </is>
       </c>
       <c r="E371" t="n">
-        <v>205992</v>
+        <v>100111</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I371" t="inlineStr">
@@ -51312,10 +51312,10 @@
         </is>
       </c>
       <c r="Q371" t="n">
-        <v>586459</v>
+        <v>586280</v>
       </c>
       <c r="R371" t="n">
-        <v>6311154</v>
+        <v>6311103</v>
       </c>
       <c r="S371" t="n">
         <v>5</v>
@@ -51347,7 +51347,7 @@
       </c>
       <c r="Z371" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AA371" t="inlineStr">
@@ -51357,7 +51357,7 @@
       </c>
       <c r="AB371" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>22:52</t>
         </is>
       </c>
       <c r="AC371" t="inlineStr">
@@ -51402,7 +51402,7 @@
     </row>
     <row r="372">
       <c r="A372" t="n">
-        <v>122254606</v>
+        <v>122254607</v>
       </c>
       <c r="B372" t="n">
         <v>56290</v>
@@ -51459,7 +51459,7 @@
         <v>586415</v>
       </c>
       <c r="R372" t="n">
-        <v>6311146</v>
+        <v>6311149</v>
       </c>
       <c r="S372" t="n">
         <v>5</v>
@@ -51546,10 +51546,10 @@
     </row>
     <row r="373">
       <c r="A373" t="n">
-        <v>122254607</v>
+        <v>122254306</v>
       </c>
       <c r="B373" t="n">
-        <v>56290</v>
+        <v>56285</v>
       </c>
       <c r="C373" t="inlineStr">
         <is>
@@ -51562,21 +51562,21 @@
         </is>
       </c>
       <c r="E373" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H373" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I373" t="inlineStr">
@@ -51600,10 +51600,10 @@
         </is>
       </c>
       <c r="Q373" t="n">
-        <v>586415</v>
+        <v>586473</v>
       </c>
       <c r="R373" t="n">
-        <v>6311149</v>
+        <v>6311192</v>
       </c>
       <c r="S373" t="n">
         <v>5</v>
@@ -51635,7 +51635,7 @@
       </c>
       <c r="Z373" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AA373" t="inlineStr">
@@ -51645,7 +51645,7 @@
       </c>
       <c r="AB373" t="inlineStr">
         <is>
-          <t>23:03</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AC373" t="inlineStr">
@@ -51690,10 +51690,10 @@
     </row>
     <row r="374">
       <c r="A374" t="n">
-        <v>122254306</v>
+        <v>122254634</v>
       </c>
       <c r="B374" t="n">
-        <v>56285</v>
+        <v>56290</v>
       </c>
       <c r="C374" t="inlineStr">
         <is>
@@ -51706,21 +51706,21 @@
         </is>
       </c>
       <c r="E374" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I374" t="inlineStr">
@@ -51744,10 +51744,10 @@
         </is>
       </c>
       <c r="Q374" t="n">
-        <v>586473</v>
+        <v>586415</v>
       </c>
       <c r="R374" t="n">
-        <v>6311192</v>
+        <v>6311148</v>
       </c>
       <c r="S374" t="n">
         <v>5</v>
@@ -51779,7 +51779,7 @@
       </c>
       <c r="Z374" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AA374" t="inlineStr">
@@ -51789,7 +51789,7 @@
       </c>
       <c r="AB374" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AC374" t="inlineStr">
@@ -51834,7 +51834,7 @@
     </row>
     <row r="375">
       <c r="A375" t="n">
-        <v>122254634</v>
+        <v>122254635</v>
       </c>
       <c r="B375" t="n">
         <v>56290</v>
@@ -51888,10 +51888,10 @@
         </is>
       </c>
       <c r="Q375" t="n">
-        <v>586415</v>
+        <v>586417</v>
       </c>
       <c r="R375" t="n">
-        <v>6311148</v>
+        <v>6311145</v>
       </c>
       <c r="S375" t="n">
         <v>5</v>
@@ -51978,7 +51978,7 @@
     </row>
     <row r="376">
       <c r="A376" t="n">
-        <v>122254635</v>
+        <v>122254658</v>
       </c>
       <c r="B376" t="n">
         <v>56290</v>
@@ -52032,10 +52032,10 @@
         </is>
       </c>
       <c r="Q376" t="n">
-        <v>586417</v>
+        <v>586491</v>
       </c>
       <c r="R376" t="n">
-        <v>6311145</v>
+        <v>6311181</v>
       </c>
       <c r="S376" t="n">
         <v>5</v>
@@ -52067,7 +52067,7 @@
       </c>
       <c r="Z376" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>22:31</t>
         </is>
       </c>
       <c r="AA376" t="inlineStr">
@@ -52077,7 +52077,7 @@
       </c>
       <c r="AB376" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AC376" t="inlineStr">
@@ -52122,10 +52122,10 @@
     </row>
     <row r="377">
       <c r="A377" t="n">
-        <v>122254658</v>
+        <v>122254316</v>
       </c>
       <c r="B377" t="n">
-        <v>56290</v>
+        <v>56285</v>
       </c>
       <c r="C377" t="inlineStr">
         <is>
@@ -52138,21 +52138,21 @@
         </is>
       </c>
       <c r="E377" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H377" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I377" t="inlineStr">
@@ -52176,10 +52176,10 @@
         </is>
       </c>
       <c r="Q377" t="n">
-        <v>586491</v>
+        <v>586423</v>
       </c>
       <c r="R377" t="n">
-        <v>6311181</v>
+        <v>6311166</v>
       </c>
       <c r="S377" t="n">
         <v>5</v>
@@ -52211,7 +52211,7 @@
       </c>
       <c r="Z377" t="inlineStr">
         <is>
-          <t>22:31</t>
+          <t>23:23</t>
         </is>
       </c>
       <c r="AA377" t="inlineStr">
@@ -52221,7 +52221,7 @@
       </c>
       <c r="AB377" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="AC377" t="inlineStr">
@@ -52266,10 +52266,10 @@
     </row>
     <row r="378">
       <c r="A378" t="n">
-        <v>122254316</v>
+        <v>122254646</v>
       </c>
       <c r="B378" t="n">
-        <v>56285</v>
+        <v>56290</v>
       </c>
       <c r="C378" t="inlineStr">
         <is>
@@ -52282,21 +52282,21 @@
         </is>
       </c>
       <c r="E378" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I378" t="inlineStr">
@@ -52320,10 +52320,10 @@
         </is>
       </c>
       <c r="Q378" t="n">
-        <v>586423</v>
+        <v>586422</v>
       </c>
       <c r="R378" t="n">
-        <v>6311166</v>
+        <v>6311111</v>
       </c>
       <c r="S378" t="n">
         <v>5</v>
@@ -52355,7 +52355,7 @@
       </c>
       <c r="Z378" t="inlineStr">
         <is>
-          <t>23:23</t>
+          <t>22:36</t>
         </is>
       </c>
       <c r="AA378" t="inlineStr">
@@ -52365,7 +52365,7 @@
       </c>
       <c r="AB378" t="inlineStr">
         <is>
-          <t>23:24</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AC378" t="inlineStr">
@@ -52410,7 +52410,7 @@
     </row>
     <row r="379">
       <c r="A379" t="n">
-        <v>122254646</v>
+        <v>122254585</v>
       </c>
       <c r="B379" t="n">
         <v>56290</v>
@@ -52464,10 +52464,10 @@
         </is>
       </c>
       <c r="Q379" t="n">
-        <v>586422</v>
+        <v>586455</v>
       </c>
       <c r="R379" t="n">
-        <v>6311111</v>
+        <v>6311156</v>
       </c>
       <c r="S379" t="n">
         <v>5</v>
@@ -52499,7 +52499,7 @@
       </c>
       <c r="Z379" t="inlineStr">
         <is>
-          <t>22:36</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AA379" t="inlineStr">
@@ -52509,7 +52509,7 @@
       </c>
       <c r="AB379" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AC379" t="inlineStr">
@@ -52554,7 +52554,7 @@
     </row>
     <row r="380">
       <c r="A380" t="n">
-        <v>122254585</v>
+        <v>122254609</v>
       </c>
       <c r="B380" t="n">
         <v>56290</v>
@@ -52608,10 +52608,10 @@
         </is>
       </c>
       <c r="Q380" t="n">
-        <v>586455</v>
+        <v>586392</v>
       </c>
       <c r="R380" t="n">
-        <v>6311156</v>
+        <v>6311147</v>
       </c>
       <c r="S380" t="n">
         <v>5</v>
@@ -52643,7 +52643,7 @@
       </c>
       <c r="Z380" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AA380" t="inlineStr">
@@ -52653,7 +52653,7 @@
       </c>
       <c r="AB380" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AC380" t="inlineStr">
@@ -52698,10 +52698,10 @@
     </row>
     <row r="381">
       <c r="A381" t="n">
-        <v>122254609</v>
+        <v>122254475</v>
       </c>
       <c r="B381" t="n">
-        <v>56290</v>
+        <v>56271</v>
       </c>
       <c r="C381" t="inlineStr">
         <is>
@@ -52710,25 +52710,25 @@
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E381" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I381" t="inlineStr">
@@ -52752,10 +52752,10 @@
         </is>
       </c>
       <c r="Q381" t="n">
-        <v>586392</v>
+        <v>586420</v>
       </c>
       <c r="R381" t="n">
-        <v>6311147</v>
+        <v>6311166</v>
       </c>
       <c r="S381" t="n">
         <v>5</v>
@@ -52787,7 +52787,7 @@
       </c>
       <c r="Z381" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>23:23</t>
         </is>
       </c>
       <c r="AA381" t="inlineStr">
@@ -52797,7 +52797,7 @@
       </c>
       <c r="AB381" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="AC381" t="inlineStr">
@@ -52842,10 +52842,10 @@
     </row>
     <row r="382">
       <c r="A382" t="n">
-        <v>122254475</v>
+        <v>122254633</v>
       </c>
       <c r="B382" t="n">
-        <v>56271</v>
+        <v>56290</v>
       </c>
       <c r="C382" t="inlineStr">
         <is>
@@ -52854,25 +52854,25 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E382" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H382" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I382" t="inlineStr">
@@ -52896,10 +52896,10 @@
         </is>
       </c>
       <c r="Q382" t="n">
-        <v>586420</v>
+        <v>586396</v>
       </c>
       <c r="R382" t="n">
-        <v>6311166</v>
+        <v>6311146</v>
       </c>
       <c r="S382" t="n">
         <v>5</v>
@@ -52931,7 +52931,7 @@
       </c>
       <c r="Z382" t="inlineStr">
         <is>
-          <t>23:23</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AA382" t="inlineStr">
@@ -52941,7 +52941,7 @@
       </c>
       <c r="AB382" t="inlineStr">
         <is>
-          <t>23:24</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AC382" t="inlineStr">
@@ -52986,7 +52986,7 @@
     </row>
     <row r="383">
       <c r="A383" t="n">
-        <v>122254633</v>
+        <v>122254643</v>
       </c>
       <c r="B383" t="n">
         <v>56290</v>
@@ -53040,10 +53040,10 @@
         </is>
       </c>
       <c r="Q383" t="n">
-        <v>586396</v>
+        <v>586424</v>
       </c>
       <c r="R383" t="n">
-        <v>6311146</v>
+        <v>6311135</v>
       </c>
       <c r="S383" t="n">
         <v>5</v>
@@ -53075,7 +53075,7 @@
       </c>
       <c r="Z383" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AA383" t="inlineStr">
@@ -53085,7 +53085,7 @@
       </c>
       <c r="AB383" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>22:38</t>
         </is>
       </c>
       <c r="AC383" t="inlineStr">
@@ -53130,10 +53130,10 @@
     </row>
     <row r="384">
       <c r="A384" t="n">
-        <v>122254643</v>
+        <v>122254415</v>
       </c>
       <c r="B384" t="n">
-        <v>56290</v>
+        <v>56285</v>
       </c>
       <c r="C384" t="inlineStr">
         <is>
@@ -53146,21 +53146,21 @@
         </is>
       </c>
       <c r="E384" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I384" t="inlineStr">
@@ -53184,7 +53184,7 @@
         </is>
       </c>
       <c r="Q384" t="n">
-        <v>586424</v>
+        <v>586425</v>
       </c>
       <c r="R384" t="n">
         <v>6311135</v>
@@ -53274,7 +53274,7 @@
     </row>
     <row r="385">
       <c r="A385" t="n">
-        <v>122254415</v>
+        <v>122254371</v>
       </c>
       <c r="B385" t="n">
         <v>56285</v>
@@ -53328,10 +53328,10 @@
         </is>
       </c>
       <c r="Q385" t="n">
-        <v>586425</v>
+        <v>586308</v>
       </c>
       <c r="R385" t="n">
-        <v>6311135</v>
+        <v>6311132</v>
       </c>
       <c r="S385" t="n">
         <v>5</v>
@@ -53363,7 +53363,7 @@
       </c>
       <c r="Z385" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AA385" t="inlineStr">
@@ -53373,7 +53373,7 @@
       </c>
       <c r="AB385" t="inlineStr">
         <is>
-          <t>22:38</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AC385" t="inlineStr">
@@ -53418,10 +53418,10 @@
     </row>
     <row r="386">
       <c r="A386" t="n">
-        <v>122254371</v>
+        <v>122254877</v>
       </c>
       <c r="B386" t="n">
-        <v>56285</v>
+        <v>56288</v>
       </c>
       <c r="C386" t="inlineStr">
         <is>
@@ -53434,21 +53434,21 @@
         </is>
       </c>
       <c r="E386" t="n">
-        <v>100092</v>
+        <v>100111</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H386" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I386" t="inlineStr">
@@ -53472,10 +53472,10 @@
         </is>
       </c>
       <c r="Q386" t="n">
-        <v>586308</v>
+        <v>586276</v>
       </c>
       <c r="R386" t="n">
-        <v>6311132</v>
+        <v>6311100</v>
       </c>
       <c r="S386" t="n">
         <v>5</v>
@@ -53507,7 +53507,7 @@
       </c>
       <c r="Z386" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AA386" t="inlineStr">
@@ -53517,7 +53517,7 @@
       </c>
       <c r="AB386" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>22:52</t>
         </is>
       </c>
       <c r="AC386" t="inlineStr">
@@ -53562,10 +53562,10 @@
     </row>
     <row r="387">
       <c r="A387" t="n">
-        <v>122254877</v>
+        <v>122254584</v>
       </c>
       <c r="B387" t="n">
-        <v>56288</v>
+        <v>56290</v>
       </c>
       <c r="C387" t="inlineStr">
         <is>
@@ -53578,21 +53578,21 @@
         </is>
       </c>
       <c r="E387" t="n">
-        <v>100111</v>
+        <v>205995</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I387" t="inlineStr">
@@ -53616,10 +53616,10 @@
         </is>
       </c>
       <c r="Q387" t="n">
-        <v>586276</v>
+        <v>586473</v>
       </c>
       <c r="R387" t="n">
-        <v>6311100</v>
+        <v>6311192</v>
       </c>
       <c r="S387" t="n">
         <v>5</v>
@@ -53651,7 +53651,7 @@
       </c>
       <c r="Z387" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AA387" t="inlineStr">
@@ -53661,7 +53661,7 @@
       </c>
       <c r="AB387" t="inlineStr">
         <is>
-          <t>22:52</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AC387" t="inlineStr">
@@ -53706,10 +53706,10 @@
     </row>
     <row r="388">
       <c r="A388" t="n">
-        <v>122254352</v>
+        <v>122254966</v>
       </c>
       <c r="B388" t="n">
-        <v>56285</v>
+        <v>56278</v>
       </c>
       <c r="C388" t="inlineStr">
         <is>
@@ -53722,21 +53722,21 @@
         </is>
       </c>
       <c r="E388" t="n">
-        <v>100092</v>
+        <v>205992</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H388" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I388" t="inlineStr">
@@ -53760,10 +53760,10 @@
         </is>
       </c>
       <c r="Q388" t="n">
-        <v>586288</v>
+        <v>586467</v>
       </c>
       <c r="R388" t="n">
-        <v>6311100</v>
+        <v>6311178</v>
       </c>
       <c r="S388" t="n">
         <v>5</v>
@@ -53795,7 +53795,7 @@
       </c>
       <c r="Z388" t="inlineStr">
         <is>
-          <t>22:55</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AA388" t="inlineStr">
@@ -53805,7 +53805,7 @@
       </c>
       <c r="AB388" t="inlineStr">
         <is>
-          <t>22:56</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="AC388" t="inlineStr">
@@ -53850,10 +53850,10 @@
     </row>
     <row r="389">
       <c r="A389" t="n">
-        <v>122254584</v>
+        <v>122254352</v>
       </c>
       <c r="B389" t="n">
-        <v>56290</v>
+        <v>56285</v>
       </c>
       <c r="C389" t="inlineStr">
         <is>
@@ -53866,21 +53866,21 @@
         </is>
       </c>
       <c r="E389" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I389" t="inlineStr">
@@ -53904,10 +53904,10 @@
         </is>
       </c>
       <c r="Q389" t="n">
-        <v>586473</v>
+        <v>586288</v>
       </c>
       <c r="R389" t="n">
-        <v>6311192</v>
+        <v>6311100</v>
       </c>
       <c r="S389" t="n">
         <v>5</v>
@@ -53939,7 +53939,7 @@
       </c>
       <c r="Z389" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>22:55</t>
         </is>
       </c>
       <c r="AA389" t="inlineStr">
@@ -53949,7 +53949,7 @@
       </c>
       <c r="AB389" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>22:56</t>
         </is>
       </c>
       <c r="AC389" t="inlineStr">
@@ -53994,37 +53994,37 @@
     </row>
     <row r="390">
       <c r="A390" t="n">
-        <v>122254966</v>
+        <v>122254173</v>
       </c>
       <c r="B390" t="n">
-        <v>56278</v>
+        <v>56269</v>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E390" t="n">
-        <v>205992</v>
+        <v>100015</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Barbastell</t>
         </is>
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Barbastella barbastellus</t>
         </is>
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I390" t="inlineStr">
@@ -54048,10 +54048,10 @@
         </is>
       </c>
       <c r="Q390" t="n">
-        <v>586467</v>
+        <v>586415</v>
       </c>
       <c r="R390" t="n">
-        <v>6311178</v>
+        <v>6311149</v>
       </c>
       <c r="S390" t="n">
         <v>5</v>
@@ -54083,7 +54083,7 @@
       </c>
       <c r="Z390" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AA390" t="inlineStr">
@@ -54093,7 +54093,7 @@
       </c>
       <c r="AB390" t="inlineStr">
         <is>
-          <t>22:33</t>
+          <t>23:03</t>
         </is>
       </c>
       <c r="AC390" t="inlineStr">

--- a/artfynd/A 36363-2024 artfynd.xlsx
+++ b/artfynd/A 36363-2024 artfynd.xlsx
@@ -37002,10 +37002,10 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>122254396</v>
+        <v>122254648</v>
       </c>
       <c r="B272" t="n">
-        <v>56285</v>
+        <v>56290</v>
       </c>
       <c r="C272" t="inlineStr">
         <is>
@@ -37018,21 +37018,21 @@
         </is>
       </c>
       <c r="E272" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
@@ -37056,10 +37056,10 @@
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>586408</v>
+        <v>586418</v>
       </c>
       <c r="R272" t="n">
-        <v>6311124</v>
+        <v>6311107</v>
       </c>
       <c r="S272" t="n">
         <v>5</v>
@@ -37091,7 +37091,7 @@
       </c>
       <c r="Z272" t="inlineStr">
         <is>
-          <t>22:43</t>
+          <t>22:36</t>
         </is>
       </c>
       <c r="AA272" t="inlineStr">
@@ -37101,7 +37101,7 @@
       </c>
       <c r="AB272" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AC272" t="inlineStr">
@@ -37146,10 +37146,10 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>122254835</v>
+        <v>122254963</v>
       </c>
       <c r="B273" t="n">
-        <v>56288</v>
+        <v>56278</v>
       </c>
       <c r="C273" t="inlineStr">
         <is>
@@ -37162,21 +37162,21 @@
         </is>
       </c>
       <c r="E273" t="n">
-        <v>100111</v>
+        <v>205992</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
@@ -37200,10 +37200,10 @@
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>586473</v>
+        <v>586374</v>
       </c>
       <c r="R273" t="n">
-        <v>6311192</v>
+        <v>6311140</v>
       </c>
       <c r="S273" t="n">
         <v>5</v>
@@ -37235,7 +37235,7 @@
       </c>
       <c r="Z273" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>22:46</t>
         </is>
       </c>
       <c r="AA273" t="inlineStr">
@@ -37245,7 +37245,7 @@
       </c>
       <c r="AB273" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>22:47</t>
         </is>
       </c>
       <c r="AC273" t="inlineStr">
@@ -37290,10 +37290,10 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>122254648</v>
+        <v>122254396</v>
       </c>
       <c r="B274" t="n">
-        <v>56290</v>
+        <v>56285</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>
@@ -37306,21 +37306,21 @@
         </is>
       </c>
       <c r="E274" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
@@ -37344,10 +37344,10 @@
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>586418</v>
+        <v>586408</v>
       </c>
       <c r="R274" t="n">
-        <v>6311107</v>
+        <v>6311124</v>
       </c>
       <c r="S274" t="n">
         <v>5</v>
@@ -37379,7 +37379,7 @@
       </c>
       <c r="Z274" t="inlineStr">
         <is>
-          <t>22:36</t>
+          <t>22:43</t>
         </is>
       </c>
       <c r="AA274" t="inlineStr">
@@ -37389,7 +37389,7 @@
       </c>
       <c r="AB274" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AC274" t="inlineStr">
@@ -37434,10 +37434,10 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>122254963</v>
+        <v>122254835</v>
       </c>
       <c r="B275" t="n">
-        <v>56278</v>
+        <v>56288</v>
       </c>
       <c r="C275" t="inlineStr">
         <is>
@@ -37450,21 +37450,21 @@
         </is>
       </c>
       <c r="E275" t="n">
-        <v>205992</v>
+        <v>100111</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
@@ -37488,10 +37488,10 @@
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>586374</v>
+        <v>586473</v>
       </c>
       <c r="R275" t="n">
-        <v>6311140</v>
+        <v>6311192</v>
       </c>
       <c r="S275" t="n">
         <v>5</v>
@@ -37523,7 +37523,7 @@
       </c>
       <c r="Z275" t="inlineStr">
         <is>
-          <t>22:46</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AA275" t="inlineStr">
@@ -37533,7 +37533,7 @@
       </c>
       <c r="AB275" t="inlineStr">
         <is>
-          <t>22:47</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AC275" t="inlineStr">
@@ -42186,10 +42186,10 @@
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>122254421</v>
+        <v>122254610</v>
       </c>
       <c r="B308" t="n">
-        <v>56285</v>
+        <v>56290</v>
       </c>
       <c r="C308" t="inlineStr">
         <is>
@@ -42202,21 +42202,21 @@
         </is>
       </c>
       <c r="E308" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
@@ -42240,10 +42240,10 @@
         </is>
       </c>
       <c r="Q308" t="n">
-        <v>586468</v>
+        <v>586389</v>
       </c>
       <c r="R308" t="n">
-        <v>6311181</v>
+        <v>6311141</v>
       </c>
       <c r="S308" t="n">
         <v>5</v>
@@ -42275,7 +42275,7 @@
       </c>
       <c r="Z308" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA308" t="inlineStr">
@@ -42285,7 +42285,7 @@
       </c>
       <c r="AB308" t="inlineStr">
         <is>
-          <t>22:33</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AC308" t="inlineStr">
@@ -42330,10 +42330,10 @@
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>122254369</v>
+        <v>122254498</v>
       </c>
       <c r="B309" t="n">
-        <v>56285</v>
+        <v>56271</v>
       </c>
       <c r="C309" t="inlineStr">
         <is>
@@ -42342,25 +42342,25 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E309" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
@@ -42384,10 +42384,10 @@
         </is>
       </c>
       <c r="Q309" t="n">
-        <v>586300</v>
+        <v>586393</v>
       </c>
       <c r="R309" t="n">
-        <v>6311112</v>
+        <v>6311147</v>
       </c>
       <c r="S309" t="n">
         <v>5</v>
@@ -42419,7 +42419,7 @@
       </c>
       <c r="Z309" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AA309" t="inlineStr">
@@ -42429,7 +42429,7 @@
       </c>
       <c r="AB309" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AC309" t="inlineStr">
@@ -42474,10 +42474,10 @@
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>122254317</v>
+        <v>122254837</v>
       </c>
       <c r="B310" t="n">
-        <v>56285</v>
+        <v>56288</v>
       </c>
       <c r="C310" t="inlineStr">
         <is>
@@ -42490,21 +42490,21 @@
         </is>
       </c>
       <c r="E310" t="n">
-        <v>100092</v>
+        <v>100111</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
@@ -42528,10 +42528,10 @@
         </is>
       </c>
       <c r="Q310" t="n">
-        <v>586438</v>
+        <v>586448</v>
       </c>
       <c r="R310" t="n">
-        <v>6311222</v>
+        <v>6311154</v>
       </c>
       <c r="S310" t="n">
         <v>5</v>
@@ -42563,7 +42563,7 @@
       </c>
       <c r="Z310" t="inlineStr">
         <is>
-          <t>23:22</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA310" t="inlineStr">
@@ -42573,7 +42573,7 @@
       </c>
       <c r="AB310" t="inlineStr">
         <is>
-          <t>23:23</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC310" t="inlineStr">
@@ -42618,10 +42618,10 @@
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>122254845</v>
+        <v>122254421</v>
       </c>
       <c r="B311" t="n">
-        <v>56288</v>
+        <v>56285</v>
       </c>
       <c r="C311" t="inlineStr">
         <is>
@@ -42634,21 +42634,21 @@
         </is>
       </c>
       <c r="E311" t="n">
-        <v>100111</v>
+        <v>100092</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
@@ -42672,10 +42672,10 @@
         </is>
       </c>
       <c r="Q311" t="n">
-        <v>586370</v>
+        <v>586468</v>
       </c>
       <c r="R311" t="n">
-        <v>6311139</v>
+        <v>6311181</v>
       </c>
       <c r="S311" t="n">
         <v>5</v>
@@ -42707,7 +42707,7 @@
       </c>
       <c r="Z311" t="inlineStr">
         <is>
-          <t>22:59</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AA311" t="inlineStr">
@@ -42717,7 +42717,7 @@
       </c>
       <c r="AB311" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="AC311" t="inlineStr">
@@ -42762,10 +42762,10 @@
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>122254837</v>
+        <v>122254369</v>
       </c>
       <c r="B312" t="n">
-        <v>56288</v>
+        <v>56285</v>
       </c>
       <c r="C312" t="inlineStr">
         <is>
@@ -42778,21 +42778,21 @@
         </is>
       </c>
       <c r="E312" t="n">
-        <v>100111</v>
+        <v>100092</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
@@ -42816,10 +42816,10 @@
         </is>
       </c>
       <c r="Q312" t="n">
-        <v>586448</v>
+        <v>586300</v>
       </c>
       <c r="R312" t="n">
-        <v>6311154</v>
+        <v>6311112</v>
       </c>
       <c r="S312" t="n">
         <v>5</v>
@@ -42851,7 +42851,7 @@
       </c>
       <c r="Z312" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AA312" t="inlineStr">
@@ -42861,7 +42861,7 @@
       </c>
       <c r="AB312" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AC312" t="inlineStr">
@@ -42906,10 +42906,10 @@
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>122254498</v>
+        <v>122254845</v>
       </c>
       <c r="B313" t="n">
-        <v>56271</v>
+        <v>56288</v>
       </c>
       <c r="C313" t="inlineStr">
         <is>
@@ -42918,25 +42918,25 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E313" t="n">
-        <v>205998</v>
+        <v>100111</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
@@ -42960,10 +42960,10 @@
         </is>
       </c>
       <c r="Q313" t="n">
-        <v>586393</v>
+        <v>586370</v>
       </c>
       <c r="R313" t="n">
-        <v>6311147</v>
+        <v>6311139</v>
       </c>
       <c r="S313" t="n">
         <v>5</v>
@@ -42995,7 +42995,7 @@
       </c>
       <c r="Z313" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>22:59</t>
         </is>
       </c>
       <c r="AA313" t="inlineStr">
@@ -43005,7 +43005,7 @@
       </c>
       <c r="AB313" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AC313" t="inlineStr">
@@ -43050,10 +43050,10 @@
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>122254610</v>
+        <v>122254317</v>
       </c>
       <c r="B314" t="n">
-        <v>56290</v>
+        <v>56285</v>
       </c>
       <c r="C314" t="inlineStr">
         <is>
@@ -43066,21 +43066,21 @@
         </is>
       </c>
       <c r="E314" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
@@ -43104,10 +43104,10 @@
         </is>
       </c>
       <c r="Q314" t="n">
-        <v>586389</v>
+        <v>586438</v>
       </c>
       <c r="R314" t="n">
-        <v>6311141</v>
+        <v>6311222</v>
       </c>
       <c r="S314" t="n">
         <v>5</v>
@@ -43139,7 +43139,7 @@
       </c>
       <c r="Z314" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>23:22</t>
         </is>
       </c>
       <c r="AA314" t="inlineStr">
@@ -43149,7 +43149,7 @@
       </c>
       <c r="AB314" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>23:23</t>
         </is>
       </c>
       <c r="AC314" t="inlineStr">
@@ -52698,10 +52698,10 @@
     </row>
     <row r="381">
       <c r="A381" t="n">
-        <v>122254475</v>
+        <v>122254415</v>
       </c>
       <c r="B381" t="n">
-        <v>56271</v>
+        <v>56285</v>
       </c>
       <c r="C381" t="inlineStr">
         <is>
@@ -52710,25 +52710,25 @@
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E381" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I381" t="inlineStr">
@@ -52752,10 +52752,10 @@
         </is>
       </c>
       <c r="Q381" t="n">
-        <v>586420</v>
+        <v>586425</v>
       </c>
       <c r="R381" t="n">
-        <v>6311166</v>
+        <v>6311135</v>
       </c>
       <c r="S381" t="n">
         <v>5</v>
@@ -52787,7 +52787,7 @@
       </c>
       <c r="Z381" t="inlineStr">
         <is>
-          <t>23:23</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AA381" t="inlineStr">
@@ -52797,7 +52797,7 @@
       </c>
       <c r="AB381" t="inlineStr">
         <is>
-          <t>23:24</t>
+          <t>22:38</t>
         </is>
       </c>
       <c r="AC381" t="inlineStr">
@@ -52842,10 +52842,10 @@
     </row>
     <row r="382">
       <c r="A382" t="n">
-        <v>122254633</v>
+        <v>122254371</v>
       </c>
       <c r="B382" t="n">
-        <v>56290</v>
+        <v>56285</v>
       </c>
       <c r="C382" t="inlineStr">
         <is>
@@ -52858,21 +52858,21 @@
         </is>
       </c>
       <c r="E382" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H382" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I382" t="inlineStr">
@@ -52896,10 +52896,10 @@
         </is>
       </c>
       <c r="Q382" t="n">
-        <v>586396</v>
+        <v>586308</v>
       </c>
       <c r="R382" t="n">
-        <v>6311146</v>
+        <v>6311132</v>
       </c>
       <c r="S382" t="n">
         <v>5</v>
@@ -52931,7 +52931,7 @@
       </c>
       <c r="Z382" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AA382" t="inlineStr">
@@ -52941,7 +52941,7 @@
       </c>
       <c r="AB382" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AC382" t="inlineStr">
@@ -52986,10 +52986,10 @@
     </row>
     <row r="383">
       <c r="A383" t="n">
-        <v>122254643</v>
+        <v>122254877</v>
       </c>
       <c r="B383" t="n">
-        <v>56290</v>
+        <v>56288</v>
       </c>
       <c r="C383" t="inlineStr">
         <is>
@@ -53002,21 +53002,21 @@
         </is>
       </c>
       <c r="E383" t="n">
-        <v>205995</v>
+        <v>100111</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I383" t="inlineStr">
@@ -53040,10 +53040,10 @@
         </is>
       </c>
       <c r="Q383" t="n">
-        <v>586424</v>
+        <v>586276</v>
       </c>
       <c r="R383" t="n">
-        <v>6311135</v>
+        <v>6311100</v>
       </c>
       <c r="S383" t="n">
         <v>5</v>
@@ -53075,7 +53075,7 @@
       </c>
       <c r="Z383" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AA383" t="inlineStr">
@@ -53085,7 +53085,7 @@
       </c>
       <c r="AB383" t="inlineStr">
         <is>
-          <t>22:38</t>
+          <t>22:52</t>
         </is>
       </c>
       <c r="AC383" t="inlineStr">
@@ -53130,10 +53130,10 @@
     </row>
     <row r="384">
       <c r="A384" t="n">
-        <v>122254415</v>
+        <v>122254475</v>
       </c>
       <c r="B384" t="n">
-        <v>56285</v>
+        <v>56271</v>
       </c>
       <c r="C384" t="inlineStr">
         <is>
@@ -53142,25 +53142,25 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E384" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I384" t="inlineStr">
@@ -53184,10 +53184,10 @@
         </is>
       </c>
       <c r="Q384" t="n">
-        <v>586425</v>
+        <v>586420</v>
       </c>
       <c r="R384" t="n">
-        <v>6311135</v>
+        <v>6311166</v>
       </c>
       <c r="S384" t="n">
         <v>5</v>
@@ -53219,7 +53219,7 @@
       </c>
       <c r="Z384" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>23:23</t>
         </is>
       </c>
       <c r="AA384" t="inlineStr">
@@ -53229,7 +53229,7 @@
       </c>
       <c r="AB384" t="inlineStr">
         <is>
-          <t>22:38</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="AC384" t="inlineStr">
@@ -53274,10 +53274,10 @@
     </row>
     <row r="385">
       <c r="A385" t="n">
-        <v>122254371</v>
+        <v>122254633</v>
       </c>
       <c r="B385" t="n">
-        <v>56285</v>
+        <v>56290</v>
       </c>
       <c r="C385" t="inlineStr">
         <is>
@@ -53290,21 +53290,21 @@
         </is>
       </c>
       <c r="E385" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H385" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I385" t="inlineStr">
@@ -53328,10 +53328,10 @@
         </is>
       </c>
       <c r="Q385" t="n">
-        <v>586308</v>
+        <v>586396</v>
       </c>
       <c r="R385" t="n">
-        <v>6311132</v>
+        <v>6311146</v>
       </c>
       <c r="S385" t="n">
         <v>5</v>
@@ -53363,7 +53363,7 @@
       </c>
       <c r="Z385" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AA385" t="inlineStr">
@@ -53373,7 +53373,7 @@
       </c>
       <c r="AB385" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AC385" t="inlineStr">
@@ -53418,10 +53418,10 @@
     </row>
     <row r="386">
       <c r="A386" t="n">
-        <v>122254877</v>
+        <v>122254643</v>
       </c>
       <c r="B386" t="n">
-        <v>56288</v>
+        <v>56290</v>
       </c>
       <c r="C386" t="inlineStr">
         <is>
@@ -53434,21 +53434,21 @@
         </is>
       </c>
       <c r="E386" t="n">
-        <v>100111</v>
+        <v>205995</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H386" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I386" t="inlineStr">
@@ -53472,10 +53472,10 @@
         </is>
       </c>
       <c r="Q386" t="n">
-        <v>586276</v>
+        <v>586424</v>
       </c>
       <c r="R386" t="n">
-        <v>6311100</v>
+        <v>6311135</v>
       </c>
       <c r="S386" t="n">
         <v>5</v>
@@ -53507,7 +53507,7 @@
       </c>
       <c r="Z386" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AA386" t="inlineStr">
@@ -53517,7 +53517,7 @@
       </c>
       <c r="AB386" t="inlineStr">
         <is>
-          <t>22:52</t>
+          <t>22:38</t>
         </is>
       </c>
       <c r="AC386" t="inlineStr">

--- a/artfynd/A 36363-2024 artfynd.xlsx
+++ b/artfynd/A 36363-2024 artfynd.xlsx
@@ -37002,10 +37002,10 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>122254648</v>
+        <v>122254416</v>
       </c>
       <c r="B272" t="n">
-        <v>56290</v>
+        <v>56285</v>
       </c>
       <c r="C272" t="inlineStr">
         <is>
@@ -37018,21 +37018,16 @@
         </is>
       </c>
       <c r="E272" t="n">
-        <v>205995</v>
-      </c>
-      <c r="F272" t="inlineStr">
-        <is>
-          <t>Dvärgpipistrell</t>
-        </is>
+        <v>100092</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
@@ -37056,10 +37051,10 @@
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>586418</v>
+        <v>586410</v>
       </c>
       <c r="R272" t="n">
-        <v>6311107</v>
+        <v>6311140</v>
       </c>
       <c r="S272" t="n">
         <v>5</v>
@@ -37091,7 +37086,7 @@
       </c>
       <c r="Z272" t="inlineStr">
         <is>
-          <t>22:36</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="AA272" t="inlineStr">
@@ -37101,7 +37096,7 @@
       </c>
       <c r="AB272" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>22:34</t>
         </is>
       </c>
       <c r="AC272" t="inlineStr">
@@ -37146,10 +37141,10 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>122254963</v>
+        <v>122254636</v>
       </c>
       <c r="B273" t="n">
-        <v>56278</v>
+        <v>56290</v>
       </c>
       <c r="C273" t="inlineStr">
         <is>
@@ -37162,21 +37157,16 @@
         </is>
       </c>
       <c r="E273" t="n">
-        <v>205992</v>
-      </c>
-      <c r="F273" t="inlineStr">
-        <is>
-          <t>Vattenfladdermus</t>
-        </is>
+        <v>205995</v>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
@@ -37200,10 +37190,10 @@
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>586374</v>
+        <v>586418</v>
       </c>
       <c r="R273" t="n">
-        <v>6311140</v>
+        <v>6311145</v>
       </c>
       <c r="S273" t="n">
         <v>5</v>
@@ -37235,7 +37225,7 @@
       </c>
       <c r="Z273" t="inlineStr">
         <is>
-          <t>22:46</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AA273" t="inlineStr">
@@ -37245,7 +37235,7 @@
       </c>
       <c r="AB273" t="inlineStr">
         <is>
-          <t>22:47</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AC273" t="inlineStr">
@@ -37290,10 +37280,10 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>122254396</v>
+        <v>122254609</v>
       </c>
       <c r="B274" t="n">
-        <v>56285</v>
+        <v>56290</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>
@@ -37306,21 +37296,16 @@
         </is>
       </c>
       <c r="E274" t="n">
-        <v>100092</v>
-      </c>
-      <c r="F274" t="inlineStr">
-        <is>
-          <t>Större brunfladdermus</t>
-        </is>
+        <v>205995</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
@@ -37344,10 +37329,10 @@
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>586408</v>
+        <v>586392</v>
       </c>
       <c r="R274" t="n">
-        <v>6311124</v>
+        <v>6311147</v>
       </c>
       <c r="S274" t="n">
         <v>5</v>
@@ -37379,7 +37364,7 @@
       </c>
       <c r="Z274" t="inlineStr">
         <is>
-          <t>22:43</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AA274" t="inlineStr">
@@ -37389,7 +37374,7 @@
       </c>
       <c r="AB274" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AC274" t="inlineStr">
@@ -37434,10 +37419,10 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>122254835</v>
+        <v>122254659</v>
       </c>
       <c r="B275" t="n">
-        <v>56288</v>
+        <v>56290</v>
       </c>
       <c r="C275" t="inlineStr">
         <is>
@@ -37450,21 +37435,16 @@
         </is>
       </c>
       <c r="E275" t="n">
-        <v>100111</v>
-      </c>
-      <c r="F275" t="inlineStr">
-        <is>
-          <t>Trollpipistrell</t>
-        </is>
+        <v>205995</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
@@ -37488,10 +37468,10 @@
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>586473</v>
+        <v>586489</v>
       </c>
       <c r="R275" t="n">
-        <v>6311192</v>
+        <v>6311181</v>
       </c>
       <c r="S275" t="n">
         <v>5</v>
@@ -37523,7 +37503,7 @@
       </c>
       <c r="Z275" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>22:31</t>
         </is>
       </c>
       <c r="AA275" t="inlineStr">
@@ -37533,7 +37513,7 @@
       </c>
       <c r="AB275" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AC275" t="inlineStr">
@@ -37578,7 +37558,7 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>122254390</v>
+        <v>122254415</v>
       </c>
       <c r="B276" t="n">
         <v>56285</v>
@@ -37596,11 +37576,6 @@
       <c r="E276" t="n">
         <v>100092</v>
       </c>
-      <c r="F276" t="inlineStr">
-        <is>
-          <t>Större brunfladdermus</t>
-        </is>
-      </c>
       <c r="G276" t="inlineStr">
         <is>
           <t>Nyctalus noctula</t>
@@ -37632,10 +37607,10 @@
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>586374</v>
+        <v>586425</v>
       </c>
       <c r="R276" t="n">
-        <v>6311139</v>
+        <v>6311135</v>
       </c>
       <c r="S276" t="n">
         <v>5</v>
@@ -37667,7 +37642,7 @@
       </c>
       <c r="Z276" t="inlineStr">
         <is>
-          <t>22:46</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AA276" t="inlineStr">
@@ -37677,7 +37652,7 @@
       </c>
       <c r="AB276" t="inlineStr">
         <is>
-          <t>22:47</t>
+          <t>22:38</t>
         </is>
       </c>
       <c r="AC276" t="inlineStr">
@@ -37722,10 +37697,10 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>122254308</v>
+        <v>122254588</v>
       </c>
       <c r="B277" t="n">
-        <v>56285</v>
+        <v>56290</v>
       </c>
       <c r="C277" t="inlineStr">
         <is>
@@ -37738,21 +37713,16 @@
         </is>
       </c>
       <c r="E277" t="n">
-        <v>100092</v>
-      </c>
-      <c r="F277" t="inlineStr">
-        <is>
-          <t>Större brunfladdermus</t>
-        </is>
+        <v>205995</v>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
@@ -37776,10 +37746,10 @@
         </is>
       </c>
       <c r="Q277" t="n">
-        <v>586455</v>
+        <v>586415</v>
       </c>
       <c r="R277" t="n">
-        <v>6311159</v>
+        <v>6311196</v>
       </c>
       <c r="S277" t="n">
         <v>5</v>
@@ -37811,7 +37781,7 @@
       </c>
       <c r="Z277" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>23:22</t>
         </is>
       </c>
       <c r="AA277" t="inlineStr">
@@ -37821,7 +37791,7 @@
       </c>
       <c r="AB277" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>23:23</t>
         </is>
       </c>
       <c r="AC277" t="inlineStr">
@@ -37866,10 +37836,10 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>122254312</v>
+        <v>122254855</v>
       </c>
       <c r="B278" t="n">
-        <v>56285</v>
+        <v>56288</v>
       </c>
       <c r="C278" t="inlineStr">
         <is>
@@ -37882,21 +37852,16 @@
         </is>
       </c>
       <c r="E278" t="n">
-        <v>100092</v>
-      </c>
-      <c r="F278" t="inlineStr">
-        <is>
-          <t>Större brunfladdermus</t>
-        </is>
+        <v>100111</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
@@ -37920,10 +37885,10 @@
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>586452</v>
+        <v>586330</v>
       </c>
       <c r="R278" t="n">
-        <v>6311152</v>
+        <v>6311120</v>
       </c>
       <c r="S278" t="n">
         <v>5</v>
@@ -37955,7 +37920,7 @@
       </c>
       <c r="Z278" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>22:57</t>
         </is>
       </c>
       <c r="AA278" t="inlineStr">
@@ -37965,7 +37930,7 @@
       </c>
       <c r="AB278" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>22:58</t>
         </is>
       </c>
       <c r="AC278" t="inlineStr">
@@ -38010,10 +37975,10 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>122254500</v>
+        <v>122254371</v>
       </c>
       <c r="B279" t="n">
-        <v>56271</v>
+        <v>56285</v>
       </c>
       <c r="C279" t="inlineStr">
         <is>
@@ -38022,25 +37987,20 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E279" t="n">
-        <v>205998</v>
-      </c>
-      <c r="F279" t="inlineStr">
-        <is>
-          <t>Nordfladdermus</t>
-        </is>
+        <v>100092</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
@@ -38064,10 +38024,10 @@
         </is>
       </c>
       <c r="Q279" t="n">
-        <v>586388</v>
+        <v>586308</v>
       </c>
       <c r="R279" t="n">
-        <v>6311142</v>
+        <v>6311132</v>
       </c>
       <c r="S279" t="n">
         <v>5</v>
@@ -38099,7 +38059,7 @@
       </c>
       <c r="Z279" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AA279" t="inlineStr">
@@ -38109,7 +38069,7 @@
       </c>
       <c r="AB279" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AC279" t="inlineStr">
@@ -38154,10 +38114,10 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>122254652</v>
+        <v>122254476</v>
       </c>
       <c r="B280" t="n">
-        <v>56290</v>
+        <v>56271</v>
       </c>
       <c r="C280" t="inlineStr">
         <is>
@@ -38166,25 +38126,20 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E280" t="n">
-        <v>205995</v>
-      </c>
-      <c r="F280" t="inlineStr">
-        <is>
-          <t>Dvärgpipistrell</t>
-        </is>
+        <v>205998</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
@@ -38208,10 +38163,10 @@
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>586432</v>
+        <v>586418</v>
       </c>
       <c r="R280" t="n">
-        <v>6311118</v>
+        <v>6311167</v>
       </c>
       <c r="S280" t="n">
         <v>5</v>
@@ -38243,7 +38198,7 @@
       </c>
       <c r="Z280" t="inlineStr">
         <is>
-          <t>22:34</t>
+          <t>23:23</t>
         </is>
       </c>
       <c r="AA280" t="inlineStr">
@@ -38253,7 +38208,7 @@
       </c>
       <c r="AB280" t="inlineStr">
         <is>
-          <t>22:35</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="AC280" t="inlineStr">
@@ -38298,7 +38253,7 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>122254616</v>
+        <v>122254635</v>
       </c>
       <c r="B281" t="n">
         <v>56290</v>
@@ -38316,11 +38271,6 @@
       <c r="E281" t="n">
         <v>205995</v>
       </c>
-      <c r="F281" t="inlineStr">
-        <is>
-          <t>Dvärgpipistrell</t>
-        </is>
-      </c>
       <c r="G281" t="inlineStr">
         <is>
           <t>Pipistrellus pygmaeus</t>
@@ -38352,10 +38302,10 @@
         </is>
       </c>
       <c r="Q281" t="n">
-        <v>586327</v>
+        <v>586417</v>
       </c>
       <c r="R281" t="n">
-        <v>6311118</v>
+        <v>6311145</v>
       </c>
       <c r="S281" t="n">
         <v>5</v>
@@ -38387,7 +38337,7 @@
       </c>
       <c r="Z281" t="inlineStr">
         <is>
-          <t>22:57</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AA281" t="inlineStr">
@@ -38397,7 +38347,7 @@
       </c>
       <c r="AB281" t="inlineStr">
         <is>
-          <t>22:58</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AC281" t="inlineStr">
@@ -38442,10 +38392,10 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>122254372</v>
+        <v>122254644</v>
       </c>
       <c r="B282" t="n">
-        <v>56285</v>
+        <v>56290</v>
       </c>
       <c r="C282" t="inlineStr">
         <is>
@@ -38458,21 +38408,16 @@
         </is>
       </c>
       <c r="E282" t="n">
-        <v>100092</v>
-      </c>
-      <c r="F282" t="inlineStr">
-        <is>
-          <t>Större brunfladdermus</t>
-        </is>
+        <v>205995</v>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
@@ -38496,10 +38441,10 @@
         </is>
       </c>
       <c r="Q282" t="n">
-        <v>586306</v>
+        <v>586429</v>
       </c>
       <c r="R282" t="n">
-        <v>6311131</v>
+        <v>6311115</v>
       </c>
       <c r="S282" t="n">
         <v>5</v>
@@ -38531,7 +38476,7 @@
       </c>
       <c r="Z282" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>22:36</t>
         </is>
       </c>
       <c r="AA282" t="inlineStr">
@@ -38541,7 +38486,7 @@
       </c>
       <c r="AB282" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AC282" t="inlineStr">
@@ -38586,10 +38531,10 @@
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>122254342</v>
+        <v>122254652</v>
       </c>
       <c r="B283" t="n">
-        <v>56285</v>
+        <v>56290</v>
       </c>
       <c r="C283" t="inlineStr">
         <is>
@@ -38602,21 +38547,16 @@
         </is>
       </c>
       <c r="E283" t="n">
-        <v>100092</v>
-      </c>
-      <c r="F283" t="inlineStr">
-        <is>
-          <t>Större brunfladdermus</t>
-        </is>
+        <v>205995</v>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
@@ -38640,10 +38580,10 @@
         </is>
       </c>
       <c r="Q283" t="n">
-        <v>586389</v>
+        <v>586432</v>
       </c>
       <c r="R283" t="n">
-        <v>6311142</v>
+        <v>6311118</v>
       </c>
       <c r="S283" t="n">
         <v>5</v>
@@ -38675,7 +38615,7 @@
       </c>
       <c r="Z283" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:34</t>
         </is>
       </c>
       <c r="AA283" t="inlineStr">
@@ -38685,7 +38625,7 @@
       </c>
       <c r="AB283" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="AC283" t="inlineStr">
@@ -38730,10 +38670,10 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>122254365</v>
+        <v>122254587</v>
       </c>
       <c r="B284" t="n">
-        <v>56285</v>
+        <v>56290</v>
       </c>
       <c r="C284" t="inlineStr">
         <is>
@@ -38746,21 +38686,16 @@
         </is>
       </c>
       <c r="E284" t="n">
-        <v>100092</v>
-      </c>
-      <c r="F284" t="inlineStr">
-        <is>
-          <t>Större brunfladdermus</t>
-        </is>
+        <v>205995</v>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
@@ -38784,10 +38719,10 @@
         </is>
       </c>
       <c r="Q284" t="n">
-        <v>586276</v>
+        <v>586443</v>
       </c>
       <c r="R284" t="n">
-        <v>6311100</v>
+        <v>6311163</v>
       </c>
       <c r="S284" t="n">
         <v>5</v>
@@ -38819,7 +38754,7 @@
       </c>
       <c r="Z284" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AA284" t="inlineStr">
@@ -38829,7 +38764,7 @@
       </c>
       <c r="AB284" t="inlineStr">
         <is>
-          <t>22:52</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AC284" t="inlineStr">
@@ -38874,10 +38809,10 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>122254843</v>
+        <v>122254367</v>
       </c>
       <c r="B285" t="n">
-        <v>56288</v>
+        <v>56285</v>
       </c>
       <c r="C285" t="inlineStr">
         <is>
@@ -38890,21 +38825,16 @@
         </is>
       </c>
       <c r="E285" t="n">
-        <v>100111</v>
-      </c>
-      <c r="F285" t="inlineStr">
-        <is>
-          <t>Trollpipistrell</t>
-        </is>
+        <v>100092</v>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
@@ -38928,10 +38858,10 @@
         </is>
       </c>
       <c r="Q285" t="n">
-        <v>586389</v>
+        <v>586280</v>
       </c>
       <c r="R285" t="n">
-        <v>6311142</v>
+        <v>6311103</v>
       </c>
       <c r="S285" t="n">
         <v>5</v>
@@ -38963,7 +38893,7 @@
       </c>
       <c r="Z285" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AA285" t="inlineStr">
@@ -38973,7 +38903,7 @@
       </c>
       <c r="AB285" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>22:52</t>
         </is>
       </c>
       <c r="AC285" t="inlineStr">
@@ -39018,10 +38948,10 @@
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>122254637</v>
+        <v>122254417</v>
       </c>
       <c r="B286" t="n">
-        <v>56290</v>
+        <v>56285</v>
       </c>
       <c r="C286" t="inlineStr">
         <is>
@@ -39034,21 +38964,16 @@
         </is>
       </c>
       <c r="E286" t="n">
-        <v>205995</v>
-      </c>
-      <c r="F286" t="inlineStr">
-        <is>
-          <t>Dvärgpipistrell</t>
-        </is>
+        <v>100092</v>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
@@ -39072,10 +38997,10 @@
         </is>
       </c>
       <c r="Q286" t="n">
-        <v>586408</v>
+        <v>586426</v>
       </c>
       <c r="R286" t="n">
-        <v>6311124</v>
+        <v>6311145</v>
       </c>
       <c r="S286" t="n">
         <v>5</v>
@@ -39107,7 +39032,7 @@
       </c>
       <c r="Z286" t="inlineStr">
         <is>
-          <t>22:43</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="AA286" t="inlineStr">
@@ -39117,7 +39042,7 @@
       </c>
       <c r="AB286" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>22:34</t>
         </is>
       </c>
       <c r="AC286" t="inlineStr">
@@ -39162,10 +39087,10 @@
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>122254659</v>
+        <v>122254964</v>
       </c>
       <c r="B287" t="n">
-        <v>56290</v>
+        <v>56278</v>
       </c>
       <c r="C287" t="inlineStr">
         <is>
@@ -39178,21 +39103,16 @@
         </is>
       </c>
       <c r="E287" t="n">
-        <v>205995</v>
-      </c>
-      <c r="F287" t="inlineStr">
-        <is>
-          <t>Dvärgpipistrell</t>
-        </is>
+        <v>205992</v>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
@@ -39216,10 +39136,10 @@
         </is>
       </c>
       <c r="Q287" t="n">
-        <v>586489</v>
+        <v>586430</v>
       </c>
       <c r="R287" t="n">
-        <v>6311181</v>
+        <v>6311142</v>
       </c>
       <c r="S287" t="n">
         <v>5</v>
@@ -39251,7 +39171,7 @@
       </c>
       <c r="Z287" t="inlineStr">
         <is>
-          <t>22:31</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="AA287" t="inlineStr">
@@ -39261,7 +39181,7 @@
       </c>
       <c r="AB287" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>22:34</t>
         </is>
       </c>
       <c r="AC287" t="inlineStr">
@@ -39306,10 +39226,10 @@
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>122254627</v>
+        <v>122254836</v>
       </c>
       <c r="B288" t="n">
-        <v>56290</v>
+        <v>56288</v>
       </c>
       <c r="C288" t="inlineStr">
         <is>
@@ -39322,21 +39242,16 @@
         </is>
       </c>
       <c r="E288" t="n">
-        <v>205995</v>
-      </c>
-      <c r="F288" t="inlineStr">
-        <is>
-          <t>Dvärgpipistrell</t>
-        </is>
+        <v>100111</v>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
@@ -39360,10 +39275,10 @@
         </is>
       </c>
       <c r="Q288" t="n">
-        <v>586306</v>
+        <v>586474</v>
       </c>
       <c r="R288" t="n">
-        <v>6311131</v>
+        <v>6311176</v>
       </c>
       <c r="S288" t="n">
         <v>5</v>
@@ -39395,7 +39310,7 @@
       </c>
       <c r="Z288" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AA288" t="inlineStr">
@@ -39405,7 +39320,7 @@
       </c>
       <c r="AB288" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AC288" t="inlineStr">
@@ -39450,10 +39365,10 @@
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>122254412</v>
+        <v>122254878</v>
       </c>
       <c r="B289" t="n">
-        <v>56285</v>
+        <v>56288</v>
       </c>
       <c r="C289" t="inlineStr">
         <is>
@@ -39466,21 +39381,16 @@
         </is>
       </c>
       <c r="E289" t="n">
-        <v>100092</v>
-      </c>
-      <c r="F289" t="inlineStr">
-        <is>
-          <t>Större brunfladdermus</t>
-        </is>
+        <v>100111</v>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
@@ -39504,10 +39414,10 @@
         </is>
       </c>
       <c r="Q289" t="n">
-        <v>586424</v>
+        <v>586280</v>
       </c>
       <c r="R289" t="n">
-        <v>6311135</v>
+        <v>6311103</v>
       </c>
       <c r="S289" t="n">
         <v>5</v>
@@ -39539,7 +39449,7 @@
       </c>
       <c r="Z289" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AA289" t="inlineStr">
@@ -39549,7 +39459,7 @@
       </c>
       <c r="AB289" t="inlineStr">
         <is>
-          <t>22:38</t>
+          <t>22:52</t>
         </is>
       </c>
       <c r="AC289" t="inlineStr">
@@ -39594,7 +39504,7 @@
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>122254880</v>
+        <v>122254846</v>
       </c>
       <c r="B290" t="n">
         <v>56288</v>
@@ -39612,11 +39522,6 @@
       <c r="E290" t="n">
         <v>100111</v>
       </c>
-      <c r="F290" t="inlineStr">
-        <is>
-          <t>Trollpipistrell</t>
-        </is>
-      </c>
       <c r="G290" t="inlineStr">
         <is>
           <t>Pipistrellus nathusii</t>
@@ -39648,10 +39553,10 @@
         </is>
       </c>
       <c r="Q290" t="n">
-        <v>586303</v>
+        <v>586370</v>
       </c>
       <c r="R290" t="n">
-        <v>6311115</v>
+        <v>6311139</v>
       </c>
       <c r="S290" t="n">
         <v>5</v>
@@ -39683,7 +39588,7 @@
       </c>
       <c r="Z290" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>22:59</t>
         </is>
       </c>
       <c r="AA290" t="inlineStr">
@@ -39693,7 +39598,7 @@
       </c>
       <c r="AB290" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AC290" t="inlineStr">
@@ -39738,7 +39643,7 @@
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>122254313</v>
+        <v>122254394</v>
       </c>
       <c r="B291" t="n">
         <v>56285</v>
@@ -39756,11 +39661,6 @@
       <c r="E291" t="n">
         <v>100092</v>
       </c>
-      <c r="F291" t="inlineStr">
-        <is>
-          <t>Större brunfladdermus</t>
-        </is>
-      </c>
       <c r="G291" t="inlineStr">
         <is>
           <t>Nyctalus noctula</t>
@@ -39792,10 +39692,10 @@
         </is>
       </c>
       <c r="Q291" t="n">
-        <v>586449</v>
+        <v>586419</v>
       </c>
       <c r="R291" t="n">
-        <v>6311155</v>
+        <v>6311142</v>
       </c>
       <c r="S291" t="n">
         <v>5</v>
@@ -39827,7 +39727,7 @@
       </c>
       <c r="Z291" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>22:43</t>
         </is>
       </c>
       <c r="AA291" t="inlineStr">
@@ -39837,7 +39737,7 @@
       </c>
       <c r="AB291" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AC291" t="inlineStr">
@@ -39882,10 +39782,10 @@
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>122254656</v>
+        <v>122254390</v>
       </c>
       <c r="B292" t="n">
-        <v>56290</v>
+        <v>56285</v>
       </c>
       <c r="C292" t="inlineStr">
         <is>
@@ -39898,21 +39798,16 @@
         </is>
       </c>
       <c r="E292" t="n">
-        <v>205995</v>
-      </c>
-      <c r="F292" t="inlineStr">
-        <is>
-          <t>Dvärgpipistrell</t>
-        </is>
+        <v>100092</v>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
@@ -39936,10 +39831,10 @@
         </is>
       </c>
       <c r="Q292" t="n">
-        <v>586483</v>
+        <v>586374</v>
       </c>
       <c r="R292" t="n">
-        <v>6311186</v>
+        <v>6311139</v>
       </c>
       <c r="S292" t="n">
         <v>5</v>
@@ -39971,7 +39866,7 @@
       </c>
       <c r="Z292" t="inlineStr">
         <is>
-          <t>22:31</t>
+          <t>22:46</t>
         </is>
       </c>
       <c r="AA292" t="inlineStr">
@@ -39981,7 +39876,7 @@
       </c>
       <c r="AB292" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>22:47</t>
         </is>
       </c>
       <c r="AC292" t="inlineStr">
@@ -40026,7 +39921,7 @@
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>122254660</v>
+        <v>122254634</v>
       </c>
       <c r="B293" t="n">
         <v>56290</v>
@@ -40044,11 +39939,6 @@
       <c r="E293" t="n">
         <v>205995</v>
       </c>
-      <c r="F293" t="inlineStr">
-        <is>
-          <t>Dvärgpipistrell</t>
-        </is>
-      </c>
       <c r="G293" t="inlineStr">
         <is>
           <t>Pipistrellus pygmaeus</t>
@@ -40080,10 +39970,10 @@
         </is>
       </c>
       <c r="Q293" t="n">
-        <v>586488</v>
+        <v>586415</v>
       </c>
       <c r="R293" t="n">
-        <v>6311183</v>
+        <v>6311148</v>
       </c>
       <c r="S293" t="n">
         <v>5</v>
@@ -40115,7 +40005,7 @@
       </c>
       <c r="Z293" t="inlineStr">
         <is>
-          <t>22:31</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AA293" t="inlineStr">
@@ -40125,7 +40015,7 @@
       </c>
       <c r="AB293" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AC293" t="inlineStr">
@@ -40170,7 +40060,7 @@
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>122254588</v>
+        <v>122254653</v>
       </c>
       <c r="B294" t="n">
         <v>56290</v>
@@ -40188,11 +40078,6 @@
       <c r="E294" t="n">
         <v>205995</v>
       </c>
-      <c r="F294" t="inlineStr">
-        <is>
-          <t>Dvärgpipistrell</t>
-        </is>
-      </c>
       <c r="G294" t="inlineStr">
         <is>
           <t>Pipistrellus pygmaeus</t>
@@ -40224,10 +40109,10 @@
         </is>
       </c>
       <c r="Q294" t="n">
-        <v>586415</v>
+        <v>586430</v>
       </c>
       <c r="R294" t="n">
-        <v>6311196</v>
+        <v>6311142</v>
       </c>
       <c r="S294" t="n">
         <v>5</v>
@@ -40259,7 +40144,7 @@
       </c>
       <c r="Z294" t="inlineStr">
         <is>
-          <t>23:22</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="AA294" t="inlineStr">
@@ -40269,7 +40154,7 @@
       </c>
       <c r="AB294" t="inlineStr">
         <is>
-          <t>23:23</t>
+          <t>22:34</t>
         </is>
       </c>
       <c r="AC294" t="inlineStr">
@@ -40314,10 +40199,10 @@
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>122254959</v>
+        <v>122254584</v>
       </c>
       <c r="B295" t="n">
-        <v>56278</v>
+        <v>56290</v>
       </c>
       <c r="C295" t="inlineStr">
         <is>
@@ -40330,21 +40215,16 @@
         </is>
       </c>
       <c r="E295" t="n">
-        <v>205992</v>
-      </c>
-      <c r="F295" t="inlineStr">
-        <is>
-          <t>Vattenfladdermus</t>
-        </is>
+        <v>205995</v>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
@@ -40368,10 +40248,10 @@
         </is>
       </c>
       <c r="Q295" t="n">
-        <v>586370</v>
+        <v>586473</v>
       </c>
       <c r="R295" t="n">
-        <v>6311139</v>
+        <v>6311192</v>
       </c>
       <c r="S295" t="n">
         <v>5</v>
@@ -40403,7 +40283,7 @@
       </c>
       <c r="Z295" t="inlineStr">
         <is>
-          <t>22:59</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AA295" t="inlineStr">
@@ -40413,7 +40293,7 @@
       </c>
       <c r="AB295" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AC295" t="inlineStr">
@@ -40458,7 +40338,7 @@
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>122254611</v>
+        <v>122254627</v>
       </c>
       <c r="B296" t="n">
         <v>56290</v>
@@ -40476,11 +40356,6 @@
       <c r="E296" t="n">
         <v>205995</v>
       </c>
-      <c r="F296" t="inlineStr">
-        <is>
-          <t>Dvärgpipistrell</t>
-        </is>
-      </c>
       <c r="G296" t="inlineStr">
         <is>
           <t>Pipistrellus pygmaeus</t>
@@ -40512,10 +40387,10 @@
         </is>
       </c>
       <c r="Q296" t="n">
-        <v>586370</v>
+        <v>586306</v>
       </c>
       <c r="R296" t="n">
-        <v>6311139</v>
+        <v>6311131</v>
       </c>
       <c r="S296" t="n">
         <v>5</v>
@@ -40547,7 +40422,7 @@
       </c>
       <c r="Z296" t="inlineStr">
         <is>
-          <t>22:59</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AA296" t="inlineStr">
@@ -40557,7 +40432,7 @@
       </c>
       <c r="AB296" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AC296" t="inlineStr">
@@ -40602,7 +40477,7 @@
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>122254653</v>
+        <v>122254633</v>
       </c>
       <c r="B297" t="n">
         <v>56290</v>
@@ -40620,11 +40495,6 @@
       <c r="E297" t="n">
         <v>205995</v>
       </c>
-      <c r="F297" t="inlineStr">
-        <is>
-          <t>Dvärgpipistrell</t>
-        </is>
-      </c>
       <c r="G297" t="inlineStr">
         <is>
           <t>Pipistrellus pygmaeus</t>
@@ -40656,10 +40526,10 @@
         </is>
       </c>
       <c r="Q297" t="n">
-        <v>586430</v>
+        <v>586396</v>
       </c>
       <c r="R297" t="n">
-        <v>6311142</v>
+        <v>6311146</v>
       </c>
       <c r="S297" t="n">
         <v>5</v>
@@ -40691,7 +40561,7 @@
       </c>
       <c r="Z297" t="inlineStr">
         <is>
-          <t>22:33</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AA297" t="inlineStr">
@@ -40701,7 +40571,7 @@
       </c>
       <c r="AB297" t="inlineStr">
         <is>
-          <t>22:34</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AC297" t="inlineStr">
@@ -40746,10 +40616,10 @@
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>122254964</v>
+        <v>122254626</v>
       </c>
       <c r="B298" t="n">
-        <v>56278</v>
+        <v>56290</v>
       </c>
       <c r="C298" t="inlineStr">
         <is>
@@ -40762,21 +40632,16 @@
         </is>
       </c>
       <c r="E298" t="n">
-        <v>205992</v>
-      </c>
-      <c r="F298" t="inlineStr">
-        <is>
-          <t>Vattenfladdermus</t>
-        </is>
+        <v>205995</v>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
@@ -40800,10 +40665,10 @@
         </is>
       </c>
       <c r="Q298" t="n">
-        <v>586430</v>
+        <v>586313</v>
       </c>
       <c r="R298" t="n">
-        <v>6311142</v>
+        <v>6311124</v>
       </c>
       <c r="S298" t="n">
         <v>5</v>
@@ -40835,7 +40700,7 @@
       </c>
       <c r="Z298" t="inlineStr">
         <is>
-          <t>22:33</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AA298" t="inlineStr">
@@ -40845,7 +40710,7 @@
       </c>
       <c r="AB298" t="inlineStr">
         <is>
-          <t>22:34</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AC298" t="inlineStr">
@@ -40890,7 +40755,7 @@
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>122254418</v>
+        <v>122254395</v>
       </c>
       <c r="B299" t="n">
         <v>56285</v>
@@ -40908,11 +40773,6 @@
       <c r="E299" t="n">
         <v>100092</v>
       </c>
-      <c r="F299" t="inlineStr">
-        <is>
-          <t>Större brunfladdermus</t>
-        </is>
-      </c>
       <c r="G299" t="inlineStr">
         <is>
           <t>Nyctalus noctula</t>
@@ -40944,10 +40804,10 @@
         </is>
       </c>
       <c r="Q299" t="n">
-        <v>586467</v>
+        <v>586408</v>
       </c>
       <c r="R299" t="n">
-        <v>6311178</v>
+        <v>6311124</v>
       </c>
       <c r="S299" t="n">
         <v>5</v>
@@ -40979,7 +40839,7 @@
       </c>
       <c r="Z299" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>22:43</t>
         </is>
       </c>
       <c r="AA299" t="inlineStr">
@@ -40989,7 +40849,7 @@
       </c>
       <c r="AB299" t="inlineStr">
         <is>
-          <t>22:33</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AC299" t="inlineStr">
@@ -41034,10 +40894,10 @@
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>122254367</v>
+        <v>122254837</v>
       </c>
       <c r="B300" t="n">
-        <v>56285</v>
+        <v>56288</v>
       </c>
       <c r="C300" t="inlineStr">
         <is>
@@ -41050,21 +40910,16 @@
         </is>
       </c>
       <c r="E300" t="n">
-        <v>100092</v>
-      </c>
-      <c r="F300" t="inlineStr">
-        <is>
-          <t>Större brunfladdermus</t>
-        </is>
+        <v>100111</v>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
@@ -41088,10 +40943,10 @@
         </is>
       </c>
       <c r="Q300" t="n">
-        <v>586280</v>
+        <v>586448</v>
       </c>
       <c r="R300" t="n">
-        <v>6311103</v>
+        <v>6311154</v>
       </c>
       <c r="S300" t="n">
         <v>5</v>
@@ -41123,7 +40978,7 @@
       </c>
       <c r="Z300" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA300" t="inlineStr">
@@ -41133,7 +40988,7 @@
       </c>
       <c r="AB300" t="inlineStr">
         <is>
-          <t>22:52</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC300" t="inlineStr">
@@ -41178,10 +41033,10 @@
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>122254370</v>
+        <v>122254880</v>
       </c>
       <c r="B301" t="n">
-        <v>56285</v>
+        <v>56288</v>
       </c>
       <c r="C301" t="inlineStr">
         <is>
@@ -41194,21 +41049,16 @@
         </is>
       </c>
       <c r="E301" t="n">
-        <v>100092</v>
-      </c>
-      <c r="F301" t="inlineStr">
-        <is>
-          <t>Större brunfladdermus</t>
-        </is>
+        <v>100111</v>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
@@ -41232,10 +41082,10 @@
         </is>
       </c>
       <c r="Q301" t="n">
-        <v>586309</v>
+        <v>586303</v>
       </c>
       <c r="R301" t="n">
-        <v>6311119</v>
+        <v>6311115</v>
       </c>
       <c r="S301" t="n">
         <v>5</v>
@@ -41322,10 +41172,10 @@
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>122254417</v>
+        <v>122254474</v>
       </c>
       <c r="B302" t="n">
-        <v>56285</v>
+        <v>56271</v>
       </c>
       <c r="C302" t="inlineStr">
         <is>
@@ -41334,25 +41184,20 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E302" t="n">
-        <v>100092</v>
-      </c>
-      <c r="F302" t="inlineStr">
-        <is>
-          <t>Större brunfladdermus</t>
-        </is>
+        <v>205998</v>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
@@ -41376,10 +41221,10 @@
         </is>
       </c>
       <c r="Q302" t="n">
-        <v>586426</v>
+        <v>586443</v>
       </c>
       <c r="R302" t="n">
-        <v>6311145</v>
+        <v>6311164</v>
       </c>
       <c r="S302" t="n">
         <v>5</v>
@@ -41411,7 +41256,7 @@
       </c>
       <c r="Z302" t="inlineStr">
         <is>
-          <t>22:33</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AA302" t="inlineStr">
@@ -41421,7 +41266,7 @@
       </c>
       <c r="AB302" t="inlineStr">
         <is>
-          <t>22:34</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AC302" t="inlineStr">
@@ -41466,10 +41311,10 @@
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>122254309</v>
+        <v>122254856</v>
       </c>
       <c r="B303" t="n">
-        <v>56285</v>
+        <v>56288</v>
       </c>
       <c r="C303" t="inlineStr">
         <is>
@@ -41482,21 +41327,16 @@
         </is>
       </c>
       <c r="E303" t="n">
-        <v>100092</v>
-      </c>
-      <c r="F303" t="inlineStr">
-        <is>
-          <t>Större brunfladdermus</t>
-        </is>
+        <v>100111</v>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
@@ -41520,10 +41360,10 @@
         </is>
       </c>
       <c r="Q303" t="n">
-        <v>586456</v>
+        <v>586327</v>
       </c>
       <c r="R303" t="n">
-        <v>6311158</v>
+        <v>6311118</v>
       </c>
       <c r="S303" t="n">
         <v>5</v>
@@ -41555,7 +41395,7 @@
       </c>
       <c r="Z303" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>22:57</t>
         </is>
       </c>
       <c r="AA303" t="inlineStr">
@@ -41565,7 +41405,7 @@
       </c>
       <c r="AB303" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>22:58</t>
         </is>
       </c>
       <c r="AC303" t="inlineStr">
@@ -41610,10 +41450,10 @@
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>122254854</v>
+        <v>122254514</v>
       </c>
       <c r="B304" t="n">
-        <v>56288</v>
+        <v>56271</v>
       </c>
       <c r="C304" t="inlineStr">
         <is>
@@ -41622,25 +41462,20 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E304" t="n">
-        <v>100111</v>
-      </c>
-      <c r="F304" t="inlineStr">
-        <is>
-          <t>Trollpipistrell</t>
-        </is>
+        <v>205998</v>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
@@ -41664,10 +41499,10 @@
         </is>
       </c>
       <c r="Q304" t="n">
-        <v>586329</v>
+        <v>586408</v>
       </c>
       <c r="R304" t="n">
-        <v>6311120</v>
+        <v>6311124</v>
       </c>
       <c r="S304" t="n">
         <v>5</v>
@@ -41699,7 +41534,7 @@
       </c>
       <c r="Z304" t="inlineStr">
         <is>
-          <t>22:57</t>
+          <t>22:43</t>
         </is>
       </c>
       <c r="AA304" t="inlineStr">
@@ -41709,7 +41544,7 @@
       </c>
       <c r="AB304" t="inlineStr">
         <is>
-          <t>22:58</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AC304" t="inlineStr">
@@ -41754,10 +41589,10 @@
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>122254857</v>
+        <v>122254950</v>
       </c>
       <c r="B305" t="n">
-        <v>56288</v>
+        <v>56278</v>
       </c>
       <c r="C305" t="inlineStr">
         <is>
@@ -41770,21 +41605,16 @@
         </is>
       </c>
       <c r="E305" t="n">
-        <v>100111</v>
-      </c>
-      <c r="F305" t="inlineStr">
-        <is>
-          <t>Trollpipistrell</t>
-        </is>
+        <v>205992</v>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
@@ -41808,10 +41638,10 @@
         </is>
       </c>
       <c r="Q305" t="n">
-        <v>586317</v>
+        <v>586482</v>
       </c>
       <c r="R305" t="n">
-        <v>6311115</v>
+        <v>6311185</v>
       </c>
       <c r="S305" t="n">
         <v>5</v>
@@ -41843,7 +41673,7 @@
       </c>
       <c r="Z305" t="inlineStr">
         <is>
-          <t>22:57</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AA305" t="inlineStr">
@@ -41853,7 +41683,7 @@
       </c>
       <c r="AB305" t="inlineStr">
         <is>
-          <t>22:58</t>
+          <t>23:31</t>
         </is>
       </c>
       <c r="AC305" t="inlineStr">
@@ -41898,10 +41728,10 @@
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>122254856</v>
+        <v>122254500</v>
       </c>
       <c r="B306" t="n">
-        <v>56288</v>
+        <v>56271</v>
       </c>
       <c r="C306" t="inlineStr">
         <is>
@@ -41910,25 +41740,20 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E306" t="n">
-        <v>100111</v>
-      </c>
-      <c r="F306" t="inlineStr">
-        <is>
-          <t>Trollpipistrell</t>
-        </is>
+        <v>205998</v>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
@@ -41952,10 +41777,10 @@
         </is>
       </c>
       <c r="Q306" t="n">
-        <v>586327</v>
+        <v>586388</v>
       </c>
       <c r="R306" t="n">
-        <v>6311118</v>
+        <v>6311142</v>
       </c>
       <c r="S306" t="n">
         <v>5</v>
@@ -41987,7 +41812,7 @@
       </c>
       <c r="Z306" t="inlineStr">
         <is>
-          <t>22:57</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA306" t="inlineStr">
@@ -41997,7 +41822,7 @@
       </c>
       <c r="AB306" t="inlineStr">
         <is>
-          <t>22:58</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AC306" t="inlineStr">
@@ -42042,10 +41867,10 @@
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>122254511</v>
+        <v>122254657</v>
       </c>
       <c r="B307" t="n">
-        <v>56271</v>
+        <v>56290</v>
       </c>
       <c r="C307" t="inlineStr">
         <is>
@@ -42054,25 +41879,20 @@
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E307" t="n">
-        <v>205998</v>
-      </c>
-      <c r="F307" t="inlineStr">
-        <is>
-          <t>Nordfladdermus</t>
-        </is>
+        <v>205995</v>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
@@ -42096,10 +41916,10 @@
         </is>
       </c>
       <c r="Q307" t="n">
-        <v>586374</v>
+        <v>586488</v>
       </c>
       <c r="R307" t="n">
-        <v>6311139</v>
+        <v>6311184</v>
       </c>
       <c r="S307" t="n">
         <v>5</v>
@@ -42131,7 +41951,7 @@
       </c>
       <c r="Z307" t="inlineStr">
         <is>
-          <t>22:46</t>
+          <t>22:31</t>
         </is>
       </c>
       <c r="AA307" t="inlineStr">
@@ -42141,7 +41961,7 @@
       </c>
       <c r="AB307" t="inlineStr">
         <is>
-          <t>22:47</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AC307" t="inlineStr">
@@ -42186,7 +42006,7 @@
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>122254610</v>
+        <v>122254615</v>
       </c>
       <c r="B308" t="n">
         <v>56290</v>
@@ -42204,11 +42024,6 @@
       <c r="E308" t="n">
         <v>205995</v>
       </c>
-      <c r="F308" t="inlineStr">
-        <is>
-          <t>Dvärgpipistrell</t>
-        </is>
-      </c>
       <c r="G308" t="inlineStr">
         <is>
           <t>Pipistrellus pygmaeus</t>
@@ -42240,10 +42055,10 @@
         </is>
       </c>
       <c r="Q308" t="n">
-        <v>586389</v>
+        <v>586329</v>
       </c>
       <c r="R308" t="n">
-        <v>6311141</v>
+        <v>6311120</v>
       </c>
       <c r="S308" t="n">
         <v>5</v>
@@ -42275,7 +42090,7 @@
       </c>
       <c r="Z308" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:57</t>
         </is>
       </c>
       <c r="AA308" t="inlineStr">
@@ -42285,7 +42100,7 @@
       </c>
       <c r="AB308" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>22:58</t>
         </is>
       </c>
       <c r="AC308" t="inlineStr">
@@ -42330,10 +42145,10 @@
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>122254498</v>
+        <v>122254660</v>
       </c>
       <c r="B309" t="n">
-        <v>56271</v>
+        <v>56290</v>
       </c>
       <c r="C309" t="inlineStr">
         <is>
@@ -42342,25 +42157,20 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E309" t="n">
-        <v>205998</v>
-      </c>
-      <c r="F309" t="inlineStr">
-        <is>
-          <t>Nordfladdermus</t>
-        </is>
+        <v>205995</v>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
@@ -42384,10 +42194,10 @@
         </is>
       </c>
       <c r="Q309" t="n">
-        <v>586393</v>
+        <v>586488</v>
       </c>
       <c r="R309" t="n">
-        <v>6311147</v>
+        <v>6311183</v>
       </c>
       <c r="S309" t="n">
         <v>5</v>
@@ -42419,7 +42229,7 @@
       </c>
       <c r="Z309" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>22:31</t>
         </is>
       </c>
       <c r="AA309" t="inlineStr">
@@ -42429,7 +42239,7 @@
       </c>
       <c r="AB309" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AC309" t="inlineStr">
@@ -42474,10 +42284,10 @@
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>122254837</v>
+        <v>122254610</v>
       </c>
       <c r="B310" t="n">
-        <v>56288</v>
+        <v>56290</v>
       </c>
       <c r="C310" t="inlineStr">
         <is>
@@ -42490,21 +42300,16 @@
         </is>
       </c>
       <c r="E310" t="n">
-        <v>100111</v>
-      </c>
-      <c r="F310" t="inlineStr">
-        <is>
-          <t>Trollpipistrell</t>
-        </is>
+        <v>205995</v>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
@@ -42528,10 +42333,10 @@
         </is>
       </c>
       <c r="Q310" t="n">
-        <v>586448</v>
+        <v>586389</v>
       </c>
       <c r="R310" t="n">
-        <v>6311154</v>
+        <v>6311141</v>
       </c>
       <c r="S310" t="n">
         <v>5</v>
@@ -42563,7 +42368,7 @@
       </c>
       <c r="Z310" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA310" t="inlineStr">
@@ -42573,7 +42378,7 @@
       </c>
       <c r="AB310" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AC310" t="inlineStr">
@@ -42618,10 +42423,10 @@
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>122254421</v>
+        <v>122254612</v>
       </c>
       <c r="B311" t="n">
-        <v>56285</v>
+        <v>56290</v>
       </c>
       <c r="C311" t="inlineStr">
         <is>
@@ -42634,21 +42439,16 @@
         </is>
       </c>
       <c r="E311" t="n">
-        <v>100092</v>
-      </c>
-      <c r="F311" t="inlineStr">
-        <is>
-          <t>Större brunfladdermus</t>
-        </is>
+        <v>205995</v>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
@@ -42672,10 +42472,10 @@
         </is>
       </c>
       <c r="Q311" t="n">
-        <v>586468</v>
+        <v>586371</v>
       </c>
       <c r="R311" t="n">
-        <v>6311181</v>
+        <v>6311135</v>
       </c>
       <c r="S311" t="n">
         <v>5</v>
@@ -42707,7 +42507,7 @@
       </c>
       <c r="Z311" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>22:59</t>
         </is>
       </c>
       <c r="AA311" t="inlineStr">
@@ -42717,7 +42517,7 @@
       </c>
       <c r="AB311" t="inlineStr">
         <is>
-          <t>22:33</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AC311" t="inlineStr">
@@ -42762,7 +42562,7 @@
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>122254369</v>
+        <v>122254308</v>
       </c>
       <c r="B312" t="n">
         <v>56285</v>
@@ -42780,11 +42580,6 @@
       <c r="E312" t="n">
         <v>100092</v>
       </c>
-      <c r="F312" t="inlineStr">
-        <is>
-          <t>Större brunfladdermus</t>
-        </is>
-      </c>
       <c r="G312" t="inlineStr">
         <is>
           <t>Nyctalus noctula</t>
@@ -42816,10 +42611,10 @@
         </is>
       </c>
       <c r="Q312" t="n">
-        <v>586300</v>
+        <v>586455</v>
       </c>
       <c r="R312" t="n">
-        <v>6311112</v>
+        <v>6311159</v>
       </c>
       <c r="S312" t="n">
         <v>5</v>
@@ -42851,7 +42646,7 @@
       </c>
       <c r="Z312" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AA312" t="inlineStr">
@@ -42861,7 +42656,7 @@
       </c>
       <c r="AB312" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AC312" t="inlineStr">
@@ -42906,10 +42701,10 @@
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>122254845</v>
+        <v>122254350</v>
       </c>
       <c r="B313" t="n">
-        <v>56288</v>
+        <v>56285</v>
       </c>
       <c r="C313" t="inlineStr">
         <is>
@@ -42922,21 +42717,16 @@
         </is>
       </c>
       <c r="E313" t="n">
-        <v>100111</v>
-      </c>
-      <c r="F313" t="inlineStr">
-        <is>
-          <t>Trollpipistrell</t>
-        </is>
+        <v>100092</v>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
@@ -42960,10 +42750,10 @@
         </is>
       </c>
       <c r="Q313" t="n">
-        <v>586370</v>
+        <v>586330</v>
       </c>
       <c r="R313" t="n">
-        <v>6311139</v>
+        <v>6311120</v>
       </c>
       <c r="S313" t="n">
         <v>5</v>
@@ -42995,7 +42785,7 @@
       </c>
       <c r="Z313" t="inlineStr">
         <is>
-          <t>22:59</t>
+          <t>22:57</t>
         </is>
       </c>
       <c r="AA313" t="inlineStr">
@@ -43005,7 +42795,7 @@
       </c>
       <c r="AB313" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:58</t>
         </is>
       </c>
       <c r="AC313" t="inlineStr">
@@ -43050,7 +42840,7 @@
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>122254317</v>
+        <v>122254316</v>
       </c>
       <c r="B314" t="n">
         <v>56285</v>
@@ -43068,11 +42858,6 @@
       <c r="E314" t="n">
         <v>100092</v>
       </c>
-      <c r="F314" t="inlineStr">
-        <is>
-          <t>Större brunfladdermus</t>
-        </is>
-      </c>
       <c r="G314" t="inlineStr">
         <is>
           <t>Nyctalus noctula</t>
@@ -43104,10 +42889,10 @@
         </is>
       </c>
       <c r="Q314" t="n">
-        <v>586438</v>
+        <v>586423</v>
       </c>
       <c r="R314" t="n">
-        <v>6311222</v>
+        <v>6311166</v>
       </c>
       <c r="S314" t="n">
         <v>5</v>
@@ -43139,7 +42924,7 @@
       </c>
       <c r="Z314" t="inlineStr">
         <is>
-          <t>23:22</t>
+          <t>23:23</t>
         </is>
       </c>
       <c r="AA314" t="inlineStr">
@@ -43149,7 +42934,7 @@
       </c>
       <c r="AB314" t="inlineStr">
         <is>
-          <t>23:23</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="AC314" t="inlineStr">
@@ -43194,10 +42979,10 @@
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>122254855</v>
+        <v>122254312</v>
       </c>
       <c r="B315" t="n">
-        <v>56288</v>
+        <v>56285</v>
       </c>
       <c r="C315" t="inlineStr">
         <is>
@@ -43210,21 +42995,16 @@
         </is>
       </c>
       <c r="E315" t="n">
-        <v>100111</v>
-      </c>
-      <c r="F315" t="inlineStr">
-        <is>
-          <t>Trollpipistrell</t>
-        </is>
+        <v>100092</v>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
@@ -43248,10 +43028,10 @@
         </is>
       </c>
       <c r="Q315" t="n">
-        <v>586330</v>
+        <v>586452</v>
       </c>
       <c r="R315" t="n">
-        <v>6311120</v>
+        <v>6311152</v>
       </c>
       <c r="S315" t="n">
         <v>5</v>
@@ -43283,7 +43063,7 @@
       </c>
       <c r="Z315" t="inlineStr">
         <is>
-          <t>22:57</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA315" t="inlineStr">
@@ -43293,7 +43073,7 @@
       </c>
       <c r="AB315" t="inlineStr">
         <is>
-          <t>22:58</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC315" t="inlineStr">
@@ -43338,10 +43118,10 @@
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>122254836</v>
+        <v>122254503</v>
       </c>
       <c r="B316" t="n">
-        <v>56288</v>
+        <v>56271</v>
       </c>
       <c r="C316" t="inlineStr">
         <is>
@@ -43350,25 +43130,20 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E316" t="n">
-        <v>100111</v>
-      </c>
-      <c r="F316" t="inlineStr">
-        <is>
-          <t>Trollpipistrell</t>
-        </is>
+        <v>205998</v>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
@@ -43392,10 +43167,10 @@
         </is>
       </c>
       <c r="Q316" t="n">
-        <v>586474</v>
+        <v>586313</v>
       </c>
       <c r="R316" t="n">
-        <v>6311176</v>
+        <v>6311124</v>
       </c>
       <c r="S316" t="n">
         <v>5</v>
@@ -43427,7 +43202,7 @@
       </c>
       <c r="Z316" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AA316" t="inlineStr">
@@ -43437,7 +43212,7 @@
       </c>
       <c r="AB316" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AC316" t="inlineStr">
@@ -43482,7 +43257,7 @@
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>122254615</v>
+        <v>122254655</v>
       </c>
       <c r="B317" t="n">
         <v>56290</v>
@@ -43500,11 +43275,6 @@
       <c r="E317" t="n">
         <v>205995</v>
       </c>
-      <c r="F317" t="inlineStr">
-        <is>
-          <t>Dvärgpipistrell</t>
-        </is>
-      </c>
       <c r="G317" t="inlineStr">
         <is>
           <t>Pipistrellus pygmaeus</t>
@@ -43536,10 +43306,10 @@
         </is>
       </c>
       <c r="Q317" t="n">
-        <v>586329</v>
+        <v>586475</v>
       </c>
       <c r="R317" t="n">
-        <v>6311120</v>
+        <v>6311187</v>
       </c>
       <c r="S317" t="n">
         <v>5</v>
@@ -43571,7 +43341,7 @@
       </c>
       <c r="Z317" t="inlineStr">
         <is>
-          <t>22:57</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AA317" t="inlineStr">
@@ -43581,7 +43351,7 @@
       </c>
       <c r="AB317" t="inlineStr">
         <is>
-          <t>22:58</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="AC317" t="inlineStr">
@@ -43626,10 +43396,10 @@
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>122254414</v>
+        <v>122254959</v>
       </c>
       <c r="B318" t="n">
-        <v>56285</v>
+        <v>56278</v>
       </c>
       <c r="C318" t="inlineStr">
         <is>
@@ -43642,21 +43412,16 @@
         </is>
       </c>
       <c r="E318" t="n">
-        <v>100092</v>
-      </c>
-      <c r="F318" t="inlineStr">
-        <is>
-          <t>Större brunfladdermus</t>
-        </is>
+        <v>205992</v>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
@@ -43680,10 +43445,10 @@
         </is>
       </c>
       <c r="Q318" t="n">
-        <v>586423</v>
+        <v>586370</v>
       </c>
       <c r="R318" t="n">
-        <v>6311137</v>
+        <v>6311139</v>
       </c>
       <c r="S318" t="n">
         <v>5</v>
@@ -43715,7 +43480,7 @@
       </c>
       <c r="Z318" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>22:59</t>
         </is>
       </c>
       <c r="AA318" t="inlineStr">
@@ -43725,7 +43490,7 @@
       </c>
       <c r="AB318" t="inlineStr">
         <is>
-          <t>22:38</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AC318" t="inlineStr">
@@ -43770,10 +43535,10 @@
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>122254393</v>
+        <v>122254585</v>
       </c>
       <c r="B319" t="n">
-        <v>56285</v>
+        <v>56290</v>
       </c>
       <c r="C319" t="inlineStr">
         <is>
@@ -43786,21 +43551,16 @@
         </is>
       </c>
       <c r="E319" t="n">
-        <v>100092</v>
-      </c>
-      <c r="F319" t="inlineStr">
-        <is>
-          <t>Större brunfladdermus</t>
-        </is>
+        <v>205995</v>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
@@ -43824,10 +43584,10 @@
         </is>
       </c>
       <c r="Q319" t="n">
-        <v>586396</v>
+        <v>586455</v>
       </c>
       <c r="R319" t="n">
-        <v>6311146</v>
+        <v>6311156</v>
       </c>
       <c r="S319" t="n">
         <v>5</v>
@@ -43859,7 +43619,7 @@
       </c>
       <c r="Z319" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AA319" t="inlineStr">
@@ -43869,7 +43629,7 @@
       </c>
       <c r="AB319" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AC319" t="inlineStr">
@@ -43914,10 +43674,10 @@
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>122254394</v>
+        <v>122254473</v>
       </c>
       <c r="B320" t="n">
-        <v>56285</v>
+        <v>56271</v>
       </c>
       <c r="C320" t="inlineStr">
         <is>
@@ -43926,25 +43686,20 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E320" t="n">
-        <v>100092</v>
-      </c>
-      <c r="F320" t="inlineStr">
-        <is>
-          <t>Större brunfladdermus</t>
-        </is>
+        <v>205998</v>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
@@ -43968,10 +43723,10 @@
         </is>
       </c>
       <c r="Q320" t="n">
-        <v>586419</v>
+        <v>586450</v>
       </c>
       <c r="R320" t="n">
-        <v>6311142</v>
+        <v>6311152</v>
       </c>
       <c r="S320" t="n">
         <v>5</v>
@@ -44003,7 +43758,7 @@
       </c>
       <c r="Z320" t="inlineStr">
         <is>
-          <t>22:43</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA320" t="inlineStr">
@@ -44013,7 +43768,7 @@
       </c>
       <c r="AB320" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC320" t="inlineStr">
@@ -44058,10 +43813,10 @@
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>122254499</v>
+        <v>122254607</v>
       </c>
       <c r="B321" t="n">
-        <v>56271</v>
+        <v>56290</v>
       </c>
       <c r="C321" t="inlineStr">
         <is>
@@ -44070,25 +43825,20 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E321" t="n">
-        <v>205998</v>
-      </c>
-      <c r="F321" t="inlineStr">
-        <is>
-          <t>Nordfladdermus</t>
-        </is>
+        <v>205995</v>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
@@ -44112,10 +43862,10 @@
         </is>
       </c>
       <c r="Q321" t="n">
-        <v>586392</v>
+        <v>586415</v>
       </c>
       <c r="R321" t="n">
-        <v>6311147</v>
+        <v>6311149</v>
       </c>
       <c r="S321" t="n">
         <v>5</v>
@@ -44147,7 +43897,7 @@
       </c>
       <c r="Z321" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AA321" t="inlineStr">
@@ -44157,7 +43907,7 @@
       </c>
       <c r="AB321" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>23:03</t>
         </is>
       </c>
       <c r="AC321" t="inlineStr">
@@ -44202,10 +43952,10 @@
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>122254626</v>
+        <v>122254953</v>
       </c>
       <c r="B322" t="n">
-        <v>56290</v>
+        <v>56278</v>
       </c>
       <c r="C322" t="inlineStr">
         <is>
@@ -44218,21 +43968,16 @@
         </is>
       </c>
       <c r="E322" t="n">
-        <v>205995</v>
-      </c>
-      <c r="F322" t="inlineStr">
-        <is>
-          <t>Dvärgpipistrell</t>
-        </is>
+        <v>205992</v>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
@@ -44256,10 +44001,10 @@
         </is>
       </c>
       <c r="Q322" t="n">
-        <v>586313</v>
+        <v>586449</v>
       </c>
       <c r="R322" t="n">
-        <v>6311124</v>
+        <v>6311155</v>
       </c>
       <c r="S322" t="n">
         <v>5</v>
@@ -44291,7 +44036,7 @@
       </c>
       <c r="Z322" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA322" t="inlineStr">
@@ -44301,7 +44046,7 @@
       </c>
       <c r="AB322" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC322" t="inlineStr">
@@ -44346,10 +44091,10 @@
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>122254612</v>
+        <v>122254343</v>
       </c>
       <c r="B323" t="n">
-        <v>56290</v>
+        <v>56285</v>
       </c>
       <c r="C323" t="inlineStr">
         <is>
@@ -44362,21 +44107,16 @@
         </is>
       </c>
       <c r="E323" t="n">
-        <v>205995</v>
-      </c>
-      <c r="F323" t="inlineStr">
-        <is>
-          <t>Dvärgpipistrell</t>
-        </is>
+        <v>100092</v>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
@@ -44400,10 +44140,10 @@
         </is>
       </c>
       <c r="Q323" t="n">
-        <v>586371</v>
+        <v>586388</v>
       </c>
       <c r="R323" t="n">
-        <v>6311135</v>
+        <v>6311142</v>
       </c>
       <c r="S323" t="n">
         <v>5</v>
@@ -44435,7 +44175,7 @@
       </c>
       <c r="Z323" t="inlineStr">
         <is>
-          <t>22:59</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA323" t="inlineStr">
@@ -44445,7 +44185,7 @@
       </c>
       <c r="AB323" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AC323" t="inlineStr">
@@ -44490,10 +44230,10 @@
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>122254644</v>
+        <v>122254373</v>
       </c>
       <c r="B324" t="n">
-        <v>56290</v>
+        <v>56285</v>
       </c>
       <c r="C324" t="inlineStr">
         <is>
@@ -44506,21 +44246,16 @@
         </is>
       </c>
       <c r="E324" t="n">
-        <v>205995</v>
-      </c>
-      <c r="F324" t="inlineStr">
-        <is>
-          <t>Dvärgpipistrell</t>
-        </is>
+        <v>100092</v>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
@@ -44544,10 +44279,10 @@
         </is>
       </c>
       <c r="Q324" t="n">
-        <v>586429</v>
+        <v>586307</v>
       </c>
       <c r="R324" t="n">
-        <v>6311115</v>
+        <v>6311133</v>
       </c>
       <c r="S324" t="n">
         <v>5</v>
@@ -44579,7 +44314,7 @@
       </c>
       <c r="Z324" t="inlineStr">
         <is>
-          <t>22:36</t>
+          <t>22:49</t>
         </is>
       </c>
       <c r="AA324" t="inlineStr">
@@ -44589,7 +44324,7 @@
       </c>
       <c r="AB324" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AC324" t="inlineStr">
@@ -44634,10 +44369,10 @@
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>122254587</v>
+        <v>122254843</v>
       </c>
       <c r="B325" t="n">
-        <v>56290</v>
+        <v>56288</v>
       </c>
       <c r="C325" t="inlineStr">
         <is>
@@ -44650,21 +44385,16 @@
         </is>
       </c>
       <c r="E325" t="n">
-        <v>205995</v>
-      </c>
-      <c r="F325" t="inlineStr">
-        <is>
-          <t>Dvärgpipistrell</t>
-        </is>
+        <v>100111</v>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
@@ -44688,10 +44418,10 @@
         </is>
       </c>
       <c r="Q325" t="n">
-        <v>586443</v>
+        <v>586389</v>
       </c>
       <c r="R325" t="n">
-        <v>6311163</v>
+        <v>6311142</v>
       </c>
       <c r="S325" t="n">
         <v>5</v>
@@ -44723,7 +44453,7 @@
       </c>
       <c r="Z325" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA325" t="inlineStr">
@@ -44733,7 +44463,7 @@
       </c>
       <c r="AB325" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AC325" t="inlineStr">
@@ -44778,10 +44508,10 @@
     </row>
     <row r="326">
       <c r="A326" t="n">
-        <v>122254314</v>
+        <v>122254472</v>
       </c>
       <c r="B326" t="n">
-        <v>56285</v>
+        <v>56271</v>
       </c>
       <c r="C326" t="inlineStr">
         <is>
@@ -44790,25 +44520,20 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E326" t="n">
-        <v>100092</v>
-      </c>
-      <c r="F326" t="inlineStr">
-        <is>
-          <t>Större brunfladdermus</t>
-        </is>
+        <v>205998</v>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
@@ -44832,10 +44557,10 @@
         </is>
       </c>
       <c r="Q326" t="n">
-        <v>586443</v>
+        <v>586455</v>
       </c>
       <c r="R326" t="n">
-        <v>6311164</v>
+        <v>6311159</v>
       </c>
       <c r="S326" t="n">
         <v>5</v>
@@ -44867,7 +44592,7 @@
       </c>
       <c r="Z326" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AA326" t="inlineStr">
@@ -44877,7 +44602,7 @@
       </c>
       <c r="AB326" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AC326" t="inlineStr">
@@ -44922,10 +44647,10 @@
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>122254315</v>
+        <v>122254643</v>
       </c>
       <c r="B327" t="n">
-        <v>56285</v>
+        <v>56290</v>
       </c>
       <c r="C327" t="inlineStr">
         <is>
@@ -44938,21 +44663,16 @@
         </is>
       </c>
       <c r="E327" t="n">
-        <v>100092</v>
-      </c>
-      <c r="F327" t="inlineStr">
-        <is>
-          <t>Större brunfladdermus</t>
-        </is>
+        <v>205995</v>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
@@ -44976,10 +44696,10 @@
         </is>
       </c>
       <c r="Q327" t="n">
-        <v>586441</v>
+        <v>586424</v>
       </c>
       <c r="R327" t="n">
-        <v>6311155</v>
+        <v>6311135</v>
       </c>
       <c r="S327" t="n">
         <v>5</v>
@@ -45011,7 +44731,7 @@
       </c>
       <c r="Z327" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AA327" t="inlineStr">
@@ -45021,7 +44741,7 @@
       </c>
       <c r="AB327" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>22:38</t>
         </is>
       </c>
       <c r="AC327" t="inlineStr">
@@ -45066,7 +44786,7 @@
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>122254343</v>
+        <v>122254310</v>
       </c>
       <c r="B328" t="n">
         <v>56285</v>
@@ -45084,11 +44804,6 @@
       <c r="E328" t="n">
         <v>100092</v>
       </c>
-      <c r="F328" t="inlineStr">
-        <is>
-          <t>Större brunfladdermus</t>
-        </is>
-      </c>
       <c r="G328" t="inlineStr">
         <is>
           <t>Nyctalus noctula</t>
@@ -45120,10 +44835,10 @@
         </is>
       </c>
       <c r="Q328" t="n">
-        <v>586388</v>
+        <v>586452</v>
       </c>
       <c r="R328" t="n">
-        <v>6311142</v>
+        <v>6311156</v>
       </c>
       <c r="S328" t="n">
         <v>5</v>
@@ -45155,7 +44870,7 @@
       </c>
       <c r="Z328" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA328" t="inlineStr">
@@ -45165,7 +44880,7 @@
       </c>
       <c r="AB328" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC328" t="inlineStr">
@@ -45210,10 +44925,10 @@
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>122254862</v>
+        <v>122254391</v>
       </c>
       <c r="B329" t="n">
-        <v>56288</v>
+        <v>56285</v>
       </c>
       <c r="C329" t="inlineStr">
         <is>
@@ -45226,21 +44941,16 @@
         </is>
       </c>
       <c r="E329" t="n">
-        <v>100111</v>
-      </c>
-      <c r="F329" t="inlineStr">
-        <is>
-          <t>Trollpipistrell</t>
-        </is>
+        <v>100092</v>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
@@ -45264,10 +44974,10 @@
         </is>
       </c>
       <c r="Q329" t="n">
-        <v>586288</v>
+        <v>586379</v>
       </c>
       <c r="R329" t="n">
-        <v>6311100</v>
+        <v>6311136</v>
       </c>
       <c r="S329" t="n">
         <v>5</v>
@@ -45299,7 +45009,7 @@
       </c>
       <c r="Z329" t="inlineStr">
         <is>
-          <t>22:55</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AA329" t="inlineStr">
@@ -45309,7 +45019,7 @@
       </c>
       <c r="AB329" t="inlineStr">
         <is>
-          <t>22:56</t>
+          <t>22:46</t>
         </is>
       </c>
       <c r="AC329" t="inlineStr">
@@ -45354,10 +45064,10 @@
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>122254632</v>
+        <v>122254369</v>
       </c>
       <c r="B330" t="n">
-        <v>56290</v>
+        <v>56285</v>
       </c>
       <c r="C330" t="inlineStr">
         <is>
@@ -45370,21 +45080,16 @@
         </is>
       </c>
       <c r="E330" t="n">
-        <v>205995</v>
-      </c>
-      <c r="F330" t="inlineStr">
-        <is>
-          <t>Dvärgpipistrell</t>
-        </is>
+        <v>100092</v>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
@@ -45408,10 +45113,10 @@
         </is>
       </c>
       <c r="Q330" t="n">
-        <v>586374</v>
+        <v>586300</v>
       </c>
       <c r="R330" t="n">
-        <v>6311140</v>
+        <v>6311112</v>
       </c>
       <c r="S330" t="n">
         <v>5</v>
@@ -45443,7 +45148,7 @@
       </c>
       <c r="Z330" t="inlineStr">
         <is>
-          <t>22:46</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AA330" t="inlineStr">
@@ -45453,7 +45158,7 @@
       </c>
       <c r="AB330" t="inlineStr">
         <is>
-          <t>22:47</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AC330" t="inlineStr">
@@ -45498,10 +45203,10 @@
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>122254476</v>
+        <v>122254857</v>
       </c>
       <c r="B331" t="n">
-        <v>56271</v>
+        <v>56288</v>
       </c>
       <c r="C331" t="inlineStr">
         <is>
@@ -45510,25 +45215,20 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E331" t="n">
-        <v>205998</v>
-      </c>
-      <c r="F331" t="inlineStr">
-        <is>
-          <t>Nordfladdermus</t>
-        </is>
+        <v>100111</v>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I331" t="inlineStr">
@@ -45552,10 +45252,10 @@
         </is>
       </c>
       <c r="Q331" t="n">
-        <v>586418</v>
+        <v>586317</v>
       </c>
       <c r="R331" t="n">
-        <v>6311167</v>
+        <v>6311115</v>
       </c>
       <c r="S331" t="n">
         <v>5</v>
@@ -45587,7 +45287,7 @@
       </c>
       <c r="Z331" t="inlineStr">
         <is>
-          <t>23:23</t>
+          <t>22:57</t>
         </is>
       </c>
       <c r="AA331" t="inlineStr">
@@ -45597,7 +45297,7 @@
       </c>
       <c r="AB331" t="inlineStr">
         <is>
-          <t>23:24</t>
+          <t>22:58</t>
         </is>
       </c>
       <c r="AC331" t="inlineStr">
@@ -45642,10 +45342,10 @@
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>122254950</v>
+        <v>122254877</v>
       </c>
       <c r="B332" t="n">
-        <v>56278</v>
+        <v>56288</v>
       </c>
       <c r="C332" t="inlineStr">
         <is>
@@ -45658,21 +45358,16 @@
         </is>
       </c>
       <c r="E332" t="n">
-        <v>205992</v>
-      </c>
-      <c r="F332" t="inlineStr">
-        <is>
-          <t>Vattenfladdermus</t>
-        </is>
+        <v>100111</v>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
@@ -45696,10 +45391,10 @@
         </is>
       </c>
       <c r="Q332" t="n">
-        <v>586482</v>
+        <v>586276</v>
       </c>
       <c r="R332" t="n">
-        <v>6311185</v>
+        <v>6311100</v>
       </c>
       <c r="S332" t="n">
         <v>5</v>
@@ -45731,7 +45426,7 @@
       </c>
       <c r="Z332" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AA332" t="inlineStr">
@@ -45741,7 +45436,7 @@
       </c>
       <c r="AB332" t="inlineStr">
         <is>
-          <t>23:31</t>
+          <t>22:52</t>
         </is>
       </c>
       <c r="AC332" t="inlineStr">
@@ -45786,7 +45481,7 @@
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>122254956</v>
+        <v>122254954</v>
       </c>
       <c r="B333" t="n">
         <v>56278</v>
@@ -45804,11 +45499,6 @@
       <c r="E333" t="n">
         <v>205992</v>
       </c>
-      <c r="F333" t="inlineStr">
-        <is>
-          <t>Vattenfladdermus</t>
-        </is>
-      </c>
       <c r="G333" t="inlineStr">
         <is>
           <t>Myotis daubentonii</t>
@@ -45840,7 +45530,7 @@
         </is>
       </c>
       <c r="Q333" t="n">
-        <v>586441</v>
+        <v>586442</v>
       </c>
       <c r="R333" t="n">
         <v>6311152</v>
@@ -45930,10 +45620,10 @@
     </row>
     <row r="334">
       <c r="A334" t="n">
-        <v>122254416</v>
+        <v>122254498</v>
       </c>
       <c r="B334" t="n">
-        <v>56285</v>
+        <v>56271</v>
       </c>
       <c r="C334" t="inlineStr">
         <is>
@@ -45942,25 +45632,20 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E334" t="n">
-        <v>100092</v>
-      </c>
-      <c r="F334" t="inlineStr">
-        <is>
-          <t>Större brunfladdermus</t>
-        </is>
+        <v>205998</v>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
@@ -45984,10 +45669,10 @@
         </is>
       </c>
       <c r="Q334" t="n">
-        <v>586410</v>
+        <v>586393</v>
       </c>
       <c r="R334" t="n">
-        <v>6311140</v>
+        <v>6311147</v>
       </c>
       <c r="S334" t="n">
         <v>5</v>
@@ -46019,7 +45704,7 @@
       </c>
       <c r="Z334" t="inlineStr">
         <is>
-          <t>22:33</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AA334" t="inlineStr">
@@ -46029,7 +45714,7 @@
       </c>
       <c r="AB334" t="inlineStr">
         <is>
-          <t>22:34</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AC334" t="inlineStr">
@@ -46074,10 +45759,10 @@
     </row>
     <row r="335">
       <c r="A335" t="n">
-        <v>122254514</v>
+        <v>122254835</v>
       </c>
       <c r="B335" t="n">
-        <v>56271</v>
+        <v>56288</v>
       </c>
       <c r="C335" t="inlineStr">
         <is>
@@ -46086,25 +45771,20 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E335" t="n">
-        <v>205998</v>
-      </c>
-      <c r="F335" t="inlineStr">
-        <is>
-          <t>Nordfladdermus</t>
-        </is>
+        <v>100111</v>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I335" t="inlineStr">
@@ -46128,10 +45808,10 @@
         </is>
       </c>
       <c r="Q335" t="n">
-        <v>586408</v>
+        <v>586473</v>
       </c>
       <c r="R335" t="n">
-        <v>6311124</v>
+        <v>6311192</v>
       </c>
       <c r="S335" t="n">
         <v>5</v>
@@ -46163,7 +45843,7 @@
       </c>
       <c r="Z335" t="inlineStr">
         <is>
-          <t>22:43</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AA335" t="inlineStr">
@@ -46173,7 +45853,7 @@
       </c>
       <c r="AB335" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AC335" t="inlineStr">
@@ -46218,7 +45898,7 @@
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>122254617</v>
+        <v>122254649</v>
       </c>
       <c r="B336" t="n">
         <v>56290</v>
@@ -46236,11 +45916,6 @@
       <c r="E336" t="n">
         <v>205995</v>
       </c>
-      <c r="F336" t="inlineStr">
-        <is>
-          <t>Dvärgpipistrell</t>
-        </is>
-      </c>
       <c r="G336" t="inlineStr">
         <is>
           <t>Pipistrellus pygmaeus</t>
@@ -46272,10 +45947,10 @@
         </is>
       </c>
       <c r="Q336" t="n">
-        <v>586317</v>
+        <v>586422</v>
       </c>
       <c r="R336" t="n">
-        <v>6311115</v>
+        <v>6311100</v>
       </c>
       <c r="S336" t="n">
         <v>5</v>
@@ -46307,7 +45982,7 @@
       </c>
       <c r="Z336" t="inlineStr">
         <is>
-          <t>22:57</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="AA336" t="inlineStr">
@@ -46317,7 +45992,7 @@
       </c>
       <c r="AB336" t="inlineStr">
         <is>
-          <t>22:58</t>
+          <t>22:36</t>
         </is>
       </c>
       <c r="AC336" t="inlineStr">
@@ -46362,7 +46037,7 @@
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>122254655</v>
+        <v>122254608</v>
       </c>
       <c r="B337" t="n">
         <v>56290</v>
@@ -46380,11 +46055,6 @@
       <c r="E337" t="n">
         <v>205995</v>
       </c>
-      <c r="F337" t="inlineStr">
-        <is>
-          <t>Dvärgpipistrell</t>
-        </is>
-      </c>
       <c r="G337" t="inlineStr">
         <is>
           <t>Pipistrellus pygmaeus</t>
@@ -46416,10 +46086,10 @@
         </is>
       </c>
       <c r="Q337" t="n">
-        <v>586475</v>
+        <v>586393</v>
       </c>
       <c r="R337" t="n">
-        <v>6311187</v>
+        <v>6311147</v>
       </c>
       <c r="S337" t="n">
         <v>5</v>
@@ -46451,7 +46121,7 @@
       </c>
       <c r="Z337" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AA337" t="inlineStr">
@@ -46461,7 +46131,7 @@
       </c>
       <c r="AB337" t="inlineStr">
         <is>
-          <t>22:33</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AC337" t="inlineStr">
@@ -46506,10 +46176,10 @@
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>122254651</v>
+        <v>122254513</v>
       </c>
       <c r="B338" t="n">
-        <v>56290</v>
+        <v>56271</v>
       </c>
       <c r="C338" t="inlineStr">
         <is>
@@ -46518,25 +46188,20 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E338" t="n">
-        <v>205995</v>
-      </c>
-      <c r="F338" t="inlineStr">
-        <is>
-          <t>Dvärgpipistrell</t>
-        </is>
+        <v>205998</v>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
@@ -46560,10 +46225,10 @@
         </is>
       </c>
       <c r="Q338" t="n">
-        <v>586425</v>
+        <v>586396</v>
       </c>
       <c r="R338" t="n">
-        <v>6311113</v>
+        <v>6311146</v>
       </c>
       <c r="S338" t="n">
         <v>5</v>
@@ -46595,7 +46260,7 @@
       </c>
       <c r="Z338" t="inlineStr">
         <is>
-          <t>22:35</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AA338" t="inlineStr">
@@ -46605,7 +46270,7 @@
       </c>
       <c r="AB338" t="inlineStr">
         <is>
-          <t>22:36</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AC338" t="inlineStr">
@@ -46650,10 +46315,10 @@
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>122254952</v>
+        <v>122254499</v>
       </c>
       <c r="B339" t="n">
-        <v>56278</v>
+        <v>56271</v>
       </c>
       <c r="C339" t="inlineStr">
         <is>
@@ -46662,25 +46327,20 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E339" t="n">
-        <v>205992</v>
-      </c>
-      <c r="F339" t="inlineStr">
-        <is>
-          <t>Vattenfladdermus</t>
-        </is>
+        <v>205998</v>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I339" t="inlineStr">
@@ -46704,10 +46364,10 @@
         </is>
       </c>
       <c r="Q339" t="n">
-        <v>586455</v>
+        <v>586392</v>
       </c>
       <c r="R339" t="n">
-        <v>6311156</v>
+        <v>6311147</v>
       </c>
       <c r="S339" t="n">
         <v>5</v>
@@ -46739,7 +46399,7 @@
       </c>
       <c r="Z339" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AA339" t="inlineStr">
@@ -46749,7 +46409,7 @@
       </c>
       <c r="AB339" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AC339" t="inlineStr">
@@ -46794,10 +46454,10 @@
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>122254953</v>
+        <v>122254372</v>
       </c>
       <c r="B340" t="n">
-        <v>56278</v>
+        <v>56285</v>
       </c>
       <c r="C340" t="inlineStr">
         <is>
@@ -46810,21 +46470,16 @@
         </is>
       </c>
       <c r="E340" t="n">
-        <v>205992</v>
-      </c>
-      <c r="F340" t="inlineStr">
-        <is>
-          <t>Vattenfladdermus</t>
-        </is>
+        <v>100092</v>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
@@ -46848,10 +46503,10 @@
         </is>
       </c>
       <c r="Q340" t="n">
-        <v>586449</v>
+        <v>586306</v>
       </c>
       <c r="R340" t="n">
-        <v>6311155</v>
+        <v>6311131</v>
       </c>
       <c r="S340" t="n">
         <v>5</v>
@@ -46883,7 +46538,7 @@
       </c>
       <c r="Z340" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AA340" t="inlineStr">
@@ -46893,7 +46548,7 @@
       </c>
       <c r="AB340" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AC340" t="inlineStr">
@@ -46938,10 +46593,10 @@
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>122254512</v>
+        <v>122254307</v>
       </c>
       <c r="B341" t="n">
-        <v>56271</v>
+        <v>56285</v>
       </c>
       <c r="C341" t="inlineStr">
         <is>
@@ -46950,25 +46605,20 @@
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E341" t="n">
-        <v>205998</v>
-      </c>
-      <c r="F341" t="inlineStr">
-        <is>
-          <t>Nordfladdermus</t>
-        </is>
+        <v>100092</v>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I341" t="inlineStr">
@@ -46992,10 +46642,10 @@
         </is>
       </c>
       <c r="Q341" t="n">
-        <v>586379</v>
+        <v>586477</v>
       </c>
       <c r="R341" t="n">
-        <v>6311136</v>
+        <v>6311186</v>
       </c>
       <c r="S341" t="n">
         <v>5</v>
@@ -47027,7 +46677,7 @@
       </c>
       <c r="Z341" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AA341" t="inlineStr">
@@ -47037,7 +46687,7 @@
       </c>
       <c r="AB341" t="inlineStr">
         <is>
-          <t>22:46</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AC341" t="inlineStr">
@@ -47082,10 +46732,10 @@
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>122254608</v>
+        <v>122254314</v>
       </c>
       <c r="B342" t="n">
-        <v>56290</v>
+        <v>56285</v>
       </c>
       <c r="C342" t="inlineStr">
         <is>
@@ -47098,21 +46748,16 @@
         </is>
       </c>
       <c r="E342" t="n">
-        <v>205995</v>
-      </c>
-      <c r="F342" t="inlineStr">
-        <is>
-          <t>Dvärgpipistrell</t>
-        </is>
+        <v>100092</v>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
@@ -47136,10 +46781,10 @@
         </is>
       </c>
       <c r="Q342" t="n">
-        <v>586393</v>
+        <v>586443</v>
       </c>
       <c r="R342" t="n">
-        <v>6311147</v>
+        <v>6311164</v>
       </c>
       <c r="S342" t="n">
         <v>5</v>
@@ -47171,7 +46816,7 @@
       </c>
       <c r="Z342" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AA342" t="inlineStr">
@@ -47181,7 +46826,7 @@
       </c>
       <c r="AB342" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AC342" t="inlineStr">
@@ -47226,10 +46871,10 @@
     </row>
     <row r="343">
       <c r="A343" t="n">
-        <v>122254503</v>
+        <v>122254309</v>
       </c>
       <c r="B343" t="n">
-        <v>56271</v>
+        <v>56285</v>
       </c>
       <c r="C343" t="inlineStr">
         <is>
@@ -47238,25 +46883,20 @@
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E343" t="n">
-        <v>205998</v>
-      </c>
-      <c r="F343" t="inlineStr">
-        <is>
-          <t>Nordfladdermus</t>
-        </is>
+        <v>100092</v>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
@@ -47280,10 +46920,10 @@
         </is>
       </c>
       <c r="Q343" t="n">
-        <v>586313</v>
+        <v>586456</v>
       </c>
       <c r="R343" t="n">
-        <v>6311124</v>
+        <v>6311158</v>
       </c>
       <c r="S343" t="n">
         <v>5</v>
@@ -47315,7 +46955,7 @@
       </c>
       <c r="Z343" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AA343" t="inlineStr">
@@ -47325,7 +46965,7 @@
       </c>
       <c r="AB343" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AC343" t="inlineStr">
@@ -47370,10 +47010,10 @@
     </row>
     <row r="344">
       <c r="A344" t="n">
-        <v>122254513</v>
+        <v>122254862</v>
       </c>
       <c r="B344" t="n">
-        <v>56271</v>
+        <v>56288</v>
       </c>
       <c r="C344" t="inlineStr">
         <is>
@@ -47382,25 +47022,20 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E344" t="n">
-        <v>205998</v>
-      </c>
-      <c r="F344" t="inlineStr">
-        <is>
-          <t>Nordfladdermus</t>
-        </is>
+        <v>100111</v>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
@@ -47424,10 +47059,10 @@
         </is>
       </c>
       <c r="Q344" t="n">
-        <v>586396</v>
+        <v>586288</v>
       </c>
       <c r="R344" t="n">
-        <v>6311146</v>
+        <v>6311100</v>
       </c>
       <c r="S344" t="n">
         <v>5</v>
@@ -47459,7 +47094,7 @@
       </c>
       <c r="Z344" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>22:55</t>
         </is>
       </c>
       <c r="AA344" t="inlineStr">
@@ -47469,7 +47104,7 @@
       </c>
       <c r="AB344" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>22:56</t>
         </is>
       </c>
       <c r="AC344" t="inlineStr">
@@ -47514,10 +47149,10 @@
     </row>
     <row r="345">
       <c r="A345" t="n">
-        <v>122254307</v>
+        <v>122254625</v>
       </c>
       <c r="B345" t="n">
-        <v>56285</v>
+        <v>56290</v>
       </c>
       <c r="C345" t="inlineStr">
         <is>
@@ -47530,21 +47165,16 @@
         </is>
       </c>
       <c r="E345" t="n">
-        <v>100092</v>
-      </c>
-      <c r="F345" t="inlineStr">
-        <is>
-          <t>Större brunfladdermus</t>
-        </is>
+        <v>205995</v>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
@@ -47568,10 +47198,10 @@
         </is>
       </c>
       <c r="Q345" t="n">
-        <v>586477</v>
+        <v>586309</v>
       </c>
       <c r="R345" t="n">
-        <v>6311186</v>
+        <v>6311119</v>
       </c>
       <c r="S345" t="n">
         <v>5</v>
@@ -47603,7 +47233,7 @@
       </c>
       <c r="Z345" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AA345" t="inlineStr">
@@ -47613,7 +47243,7 @@
       </c>
       <c r="AB345" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AC345" t="inlineStr">
@@ -47658,10 +47288,10 @@
     </row>
     <row r="346">
       <c r="A346" t="n">
-        <v>122254310</v>
+        <v>122254651</v>
       </c>
       <c r="B346" t="n">
-        <v>56285</v>
+        <v>56290</v>
       </c>
       <c r="C346" t="inlineStr">
         <is>
@@ -47674,21 +47304,16 @@
         </is>
       </c>
       <c r="E346" t="n">
-        <v>100092</v>
-      </c>
-      <c r="F346" t="inlineStr">
-        <is>
-          <t>Större brunfladdermus</t>
-        </is>
+        <v>205995</v>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
@@ -47712,10 +47337,10 @@
         </is>
       </c>
       <c r="Q346" t="n">
-        <v>586452</v>
+        <v>586425</v>
       </c>
       <c r="R346" t="n">
-        <v>6311156</v>
+        <v>6311113</v>
       </c>
       <c r="S346" t="n">
         <v>5</v>
@@ -47747,7 +47372,7 @@
       </c>
       <c r="Z346" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="AA346" t="inlineStr">
@@ -47757,7 +47382,7 @@
       </c>
       <c r="AB346" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>22:36</t>
         </is>
       </c>
       <c r="AC346" t="inlineStr">
@@ -47802,7 +47427,7 @@
     </row>
     <row r="347">
       <c r="A347" t="n">
-        <v>122254636</v>
+        <v>122254654</v>
       </c>
       <c r="B347" t="n">
         <v>56290</v>
@@ -47820,11 +47445,6 @@
       <c r="E347" t="n">
         <v>205995</v>
       </c>
-      <c r="F347" t="inlineStr">
-        <is>
-          <t>Dvärgpipistrell</t>
-        </is>
-      </c>
       <c r="G347" t="inlineStr">
         <is>
           <t>Pipistrellus pygmaeus</t>
@@ -47856,10 +47476,10 @@
         </is>
       </c>
       <c r="Q347" t="n">
-        <v>586418</v>
+        <v>586467</v>
       </c>
       <c r="R347" t="n">
-        <v>6311145</v>
+        <v>6311178</v>
       </c>
       <c r="S347" t="n">
         <v>5</v>
@@ -47891,7 +47511,7 @@
       </c>
       <c r="Z347" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AA347" t="inlineStr">
@@ -47901,7 +47521,7 @@
       </c>
       <c r="AB347" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="AC347" t="inlineStr">
@@ -47946,7 +47566,7 @@
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>122254657</v>
+        <v>122254632</v>
       </c>
       <c r="B348" t="n">
         <v>56290</v>
@@ -47964,11 +47584,6 @@
       <c r="E348" t="n">
         <v>205995</v>
       </c>
-      <c r="F348" t="inlineStr">
-        <is>
-          <t>Dvärgpipistrell</t>
-        </is>
-      </c>
       <c r="G348" t="inlineStr">
         <is>
           <t>Pipistrellus pygmaeus</t>
@@ -48000,10 +47615,10 @@
         </is>
       </c>
       <c r="Q348" t="n">
-        <v>586488</v>
+        <v>586374</v>
       </c>
       <c r="R348" t="n">
-        <v>6311184</v>
+        <v>6311140</v>
       </c>
       <c r="S348" t="n">
         <v>5</v>
@@ -48035,7 +47650,7 @@
       </c>
       <c r="Z348" t="inlineStr">
         <is>
-          <t>22:31</t>
+          <t>22:46</t>
         </is>
       </c>
       <c r="AA348" t="inlineStr">
@@ -48045,7 +47660,7 @@
       </c>
       <c r="AB348" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>22:47</t>
         </is>
       </c>
       <c r="AC348" t="inlineStr">
@@ -48090,10 +47705,10 @@
     </row>
     <row r="349">
       <c r="A349" t="n">
-        <v>122254474</v>
+        <v>122254646</v>
       </c>
       <c r="B349" t="n">
-        <v>56271</v>
+        <v>56290</v>
       </c>
       <c r="C349" t="inlineStr">
         <is>
@@ -48102,25 +47717,20 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E349" t="n">
-        <v>205998</v>
-      </c>
-      <c r="F349" t="inlineStr">
-        <is>
-          <t>Nordfladdermus</t>
-        </is>
+        <v>205995</v>
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I349" t="inlineStr">
@@ -48144,10 +47754,10 @@
         </is>
       </c>
       <c r="Q349" t="n">
-        <v>586443</v>
+        <v>586422</v>
       </c>
       <c r="R349" t="n">
-        <v>6311164</v>
+        <v>6311111</v>
       </c>
       <c r="S349" t="n">
         <v>5</v>
@@ -48179,7 +47789,7 @@
       </c>
       <c r="Z349" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>22:36</t>
         </is>
       </c>
       <c r="AA349" t="inlineStr">
@@ -48189,7 +47799,7 @@
       </c>
       <c r="AB349" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AC349" t="inlineStr">
@@ -48234,10 +47844,10 @@
     </row>
     <row r="350">
       <c r="A350" t="n">
-        <v>122254586</v>
+        <v>122254317</v>
       </c>
       <c r="B350" t="n">
-        <v>56290</v>
+        <v>56285</v>
       </c>
       <c r="C350" t="inlineStr">
         <is>
@@ -48250,21 +47860,16 @@
         </is>
       </c>
       <c r="E350" t="n">
-        <v>205995</v>
-      </c>
-      <c r="F350" t="inlineStr">
-        <is>
-          <t>Dvärgpipistrell</t>
-        </is>
+        <v>100092</v>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I350" t="inlineStr">
@@ -48288,10 +47893,10 @@
         </is>
       </c>
       <c r="Q350" t="n">
-        <v>586446</v>
+        <v>586438</v>
       </c>
       <c r="R350" t="n">
-        <v>6311158</v>
+        <v>6311222</v>
       </c>
       <c r="S350" t="n">
         <v>5</v>
@@ -48323,7 +47928,7 @@
       </c>
       <c r="Z350" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>23:22</t>
         </is>
       </c>
       <c r="AA350" t="inlineStr">
@@ -48333,7 +47938,7 @@
       </c>
       <c r="AB350" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>23:23</t>
         </is>
       </c>
       <c r="AC350" t="inlineStr">
@@ -48378,7 +47983,7 @@
     </row>
     <row r="351">
       <c r="A351" t="n">
-        <v>122254411</v>
+        <v>122254341</v>
       </c>
       <c r="B351" t="n">
         <v>56285</v>
@@ -48396,11 +48001,6 @@
       <c r="E351" t="n">
         <v>100092</v>
       </c>
-      <c r="F351" t="inlineStr">
-        <is>
-          <t>Större brunfladdermus</t>
-        </is>
-      </c>
       <c r="G351" t="inlineStr">
         <is>
           <t>Nyctalus noctula</t>
@@ -48432,10 +48032,10 @@
         </is>
       </c>
       <c r="Q351" t="n">
-        <v>586414</v>
+        <v>586415</v>
       </c>
       <c r="R351" t="n">
-        <v>6311126</v>
+        <v>6311146</v>
       </c>
       <c r="S351" t="n">
         <v>5</v>
@@ -48467,7 +48067,7 @@
       </c>
       <c r="Z351" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AA351" t="inlineStr">
@@ -48477,7 +48077,7 @@
       </c>
       <c r="AB351" t="inlineStr">
         <is>
-          <t>22:38</t>
+          <t>23:03</t>
         </is>
       </c>
       <c r="AC351" t="inlineStr">
@@ -48522,7 +48122,7 @@
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>122254373</v>
+        <v>122254411</v>
       </c>
       <c r="B352" t="n">
         <v>56285</v>
@@ -48540,11 +48140,6 @@
       <c r="E352" t="n">
         <v>100092</v>
       </c>
-      <c r="F352" t="inlineStr">
-        <is>
-          <t>Större brunfladdermus</t>
-        </is>
-      </c>
       <c r="G352" t="inlineStr">
         <is>
           <t>Nyctalus noctula</t>
@@ -48576,10 +48171,10 @@
         </is>
       </c>
       <c r="Q352" t="n">
-        <v>586307</v>
+        <v>586414</v>
       </c>
       <c r="R352" t="n">
-        <v>6311133</v>
+        <v>6311126</v>
       </c>
       <c r="S352" t="n">
         <v>5</v>
@@ -48611,7 +48206,7 @@
       </c>
       <c r="Z352" t="inlineStr">
         <is>
-          <t>22:49</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AA352" t="inlineStr">
@@ -48621,7 +48216,7 @@
       </c>
       <c r="AB352" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>22:38</t>
         </is>
       </c>
       <c r="AC352" t="inlineStr">
@@ -48666,7 +48261,7 @@
     </row>
     <row r="353">
       <c r="A353" t="n">
-        <v>122254391</v>
+        <v>122254421</v>
       </c>
       <c r="B353" t="n">
         <v>56285</v>
@@ -48684,11 +48279,6 @@
       <c r="E353" t="n">
         <v>100092</v>
       </c>
-      <c r="F353" t="inlineStr">
-        <is>
-          <t>Större brunfladdermus</t>
-        </is>
-      </c>
       <c r="G353" t="inlineStr">
         <is>
           <t>Nyctalus noctula</t>
@@ -48720,10 +48310,10 @@
         </is>
       </c>
       <c r="Q353" t="n">
-        <v>586379</v>
+        <v>586468</v>
       </c>
       <c r="R353" t="n">
-        <v>6311136</v>
+        <v>6311181</v>
       </c>
       <c r="S353" t="n">
         <v>5</v>
@@ -48755,7 +48345,7 @@
       </c>
       <c r="Z353" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AA353" t="inlineStr">
@@ -48765,7 +48355,7 @@
       </c>
       <c r="AB353" t="inlineStr">
         <is>
-          <t>22:46</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="AC353" t="inlineStr">
@@ -48810,10 +48400,10 @@
     </row>
     <row r="354">
       <c r="A354" t="n">
-        <v>122254844</v>
+        <v>122254414</v>
       </c>
       <c r="B354" t="n">
-        <v>56288</v>
+        <v>56285</v>
       </c>
       <c r="C354" t="inlineStr">
         <is>
@@ -48826,21 +48416,16 @@
         </is>
       </c>
       <c r="E354" t="n">
-        <v>100111</v>
-      </c>
-      <c r="F354" t="inlineStr">
-        <is>
-          <t>Trollpipistrell</t>
-        </is>
+        <v>100092</v>
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I354" t="inlineStr">
@@ -48864,10 +48449,10 @@
         </is>
       </c>
       <c r="Q354" t="n">
-        <v>586387</v>
+        <v>586423</v>
       </c>
       <c r="R354" t="n">
-        <v>6311141</v>
+        <v>6311137</v>
       </c>
       <c r="S354" t="n">
         <v>5</v>
@@ -48899,7 +48484,7 @@
       </c>
       <c r="Z354" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AA354" t="inlineStr">
@@ -48909,7 +48494,7 @@
       </c>
       <c r="AB354" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>22:38</t>
         </is>
       </c>
       <c r="AC354" t="inlineStr">
@@ -48954,7 +48539,7 @@
     </row>
     <row r="355">
       <c r="A355" t="n">
-        <v>122254318</v>
+        <v>122254420</v>
       </c>
       <c r="B355" t="n">
         <v>56285</v>
@@ -48972,11 +48557,6 @@
       <c r="E355" t="n">
         <v>100092</v>
       </c>
-      <c r="F355" t="inlineStr">
-        <is>
-          <t>Större brunfladdermus</t>
-        </is>
-      </c>
       <c r="G355" t="inlineStr">
         <is>
           <t>Nyctalus noctula</t>
@@ -49008,10 +48588,10 @@
         </is>
       </c>
       <c r="Q355" t="n">
-        <v>586455</v>
+        <v>586467</v>
       </c>
       <c r="R355" t="n">
-        <v>6311228</v>
+        <v>6311178</v>
       </c>
       <c r="S355" t="n">
         <v>5</v>
@@ -49043,7 +48623,7 @@
       </c>
       <c r="Z355" t="inlineStr">
         <is>
-          <t>23:22</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AA355" t="inlineStr">
@@ -49053,7 +48633,7 @@
       </c>
       <c r="AB355" t="inlineStr">
         <is>
-          <t>23:23</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="AC355" t="inlineStr">
@@ -49098,10 +48678,10 @@
     </row>
     <row r="356">
       <c r="A356" t="n">
-        <v>122254350</v>
+        <v>122254854</v>
       </c>
       <c r="B356" t="n">
-        <v>56285</v>
+        <v>56288</v>
       </c>
       <c r="C356" t="inlineStr">
         <is>
@@ -49114,21 +48694,16 @@
         </is>
       </c>
       <c r="E356" t="n">
-        <v>100092</v>
-      </c>
-      <c r="F356" t="inlineStr">
-        <is>
-          <t>Större brunfladdermus</t>
-        </is>
+        <v>100111</v>
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I356" t="inlineStr">
@@ -49152,7 +48727,7 @@
         </is>
       </c>
       <c r="Q356" t="n">
-        <v>586330</v>
+        <v>586329</v>
       </c>
       <c r="R356" t="n">
         <v>6311120</v>
@@ -49242,7 +48817,7 @@
     </row>
     <row r="357">
       <c r="A357" t="n">
-        <v>122254496</v>
+        <v>122254475</v>
       </c>
       <c r="B357" t="n">
         <v>56271</v>
@@ -49260,11 +48835,6 @@
       <c r="E357" t="n">
         <v>205998</v>
       </c>
-      <c r="F357" t="inlineStr">
-        <is>
-          <t>Nordfladdermus</t>
-        </is>
-      </c>
       <c r="G357" t="inlineStr">
         <is>
           <t>Eptesicus nilssonii</t>
@@ -49296,10 +48866,10 @@
         </is>
       </c>
       <c r="Q357" t="n">
-        <v>586415</v>
+        <v>586420</v>
       </c>
       <c r="R357" t="n">
-        <v>6311146</v>
+        <v>6311166</v>
       </c>
       <c r="S357" t="n">
         <v>5</v>
@@ -49331,7 +48901,7 @@
       </c>
       <c r="Z357" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>23:23</t>
         </is>
       </c>
       <c r="AA357" t="inlineStr">
@@ -49341,7 +48911,7 @@
       </c>
       <c r="AB357" t="inlineStr">
         <is>
-          <t>23:03</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="AC357" t="inlineStr">
@@ -49386,10 +48956,10 @@
     </row>
     <row r="358">
       <c r="A358" t="n">
-        <v>122254649</v>
+        <v>122254957</v>
       </c>
       <c r="B358" t="n">
-        <v>56290</v>
+        <v>56278</v>
       </c>
       <c r="C358" t="inlineStr">
         <is>
@@ -49402,21 +48972,16 @@
         </is>
       </c>
       <c r="E358" t="n">
-        <v>205995</v>
-      </c>
-      <c r="F358" t="inlineStr">
-        <is>
-          <t>Dvärgpipistrell</t>
-        </is>
+        <v>205992</v>
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H358" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I358" t="inlineStr">
@@ -49440,10 +49005,10 @@
         </is>
       </c>
       <c r="Q358" t="n">
-        <v>586422</v>
+        <v>586444</v>
       </c>
       <c r="R358" t="n">
-        <v>6311100</v>
+        <v>6311160</v>
       </c>
       <c r="S358" t="n">
         <v>5</v>
@@ -49475,7 +49040,7 @@
       </c>
       <c r="Z358" t="inlineStr">
         <is>
-          <t>22:35</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="AA358" t="inlineStr">
@@ -49485,7 +49050,7 @@
       </c>
       <c r="AB358" t="inlineStr">
         <is>
-          <t>22:36</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AC358" t="inlineStr">
@@ -49530,7 +49095,7 @@
     </row>
     <row r="359">
       <c r="A359" t="n">
-        <v>122254473</v>
+        <v>122254511</v>
       </c>
       <c r="B359" t="n">
         <v>56271</v>
@@ -49548,11 +49113,6 @@
       <c r="E359" t="n">
         <v>205998</v>
       </c>
-      <c r="F359" t="inlineStr">
-        <is>
-          <t>Nordfladdermus</t>
-        </is>
-      </c>
       <c r="G359" t="inlineStr">
         <is>
           <t>Eptesicus nilssonii</t>
@@ -49584,10 +49144,10 @@
         </is>
       </c>
       <c r="Q359" t="n">
-        <v>586450</v>
+        <v>586374</v>
       </c>
       <c r="R359" t="n">
-        <v>6311152</v>
+        <v>6311139</v>
       </c>
       <c r="S359" t="n">
         <v>5</v>
@@ -49619,7 +49179,7 @@
       </c>
       <c r="Z359" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>22:46</t>
         </is>
       </c>
       <c r="AA359" t="inlineStr">
@@ -49629,7 +49189,7 @@
       </c>
       <c r="AB359" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>22:47</t>
         </is>
       </c>
       <c r="AC359" t="inlineStr">
@@ -49674,10 +49234,10 @@
     </row>
     <row r="360">
       <c r="A360" t="n">
-        <v>122254654</v>
+        <v>122254956</v>
       </c>
       <c r="B360" t="n">
-        <v>56290</v>
+        <v>56278</v>
       </c>
       <c r="C360" t="inlineStr">
         <is>
@@ -49690,21 +49250,16 @@
         </is>
       </c>
       <c r="E360" t="n">
-        <v>205995</v>
-      </c>
-      <c r="F360" t="inlineStr">
-        <is>
-          <t>Dvärgpipistrell</t>
-        </is>
+        <v>205992</v>
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I360" t="inlineStr">
@@ -49728,10 +49283,10 @@
         </is>
       </c>
       <c r="Q360" t="n">
-        <v>586467</v>
+        <v>586441</v>
       </c>
       <c r="R360" t="n">
-        <v>6311178</v>
+        <v>6311152</v>
       </c>
       <c r="S360" t="n">
         <v>5</v>
@@ -49763,7 +49318,7 @@
       </c>
       <c r="Z360" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AA360" t="inlineStr">
@@ -49773,7 +49328,7 @@
       </c>
       <c r="AB360" t="inlineStr">
         <is>
-          <t>22:33</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AC360" t="inlineStr">
@@ -49818,10 +49373,10 @@
     </row>
     <row r="361">
       <c r="A361" t="n">
-        <v>122254957</v>
+        <v>122254393</v>
       </c>
       <c r="B361" t="n">
-        <v>56278</v>
+        <v>56285</v>
       </c>
       <c r="C361" t="inlineStr">
         <is>
@@ -49834,21 +49389,16 @@
         </is>
       </c>
       <c r="E361" t="n">
-        <v>205992</v>
-      </c>
-      <c r="F361" t="inlineStr">
-        <is>
-          <t>Vattenfladdermus</t>
-        </is>
+        <v>100092</v>
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I361" t="inlineStr">
@@ -49872,10 +49422,10 @@
         </is>
       </c>
       <c r="Q361" t="n">
-        <v>586444</v>
+        <v>586396</v>
       </c>
       <c r="R361" t="n">
-        <v>6311160</v>
+        <v>6311146</v>
       </c>
       <c r="S361" t="n">
         <v>5</v>
@@ -49907,7 +49457,7 @@
       </c>
       <c r="Z361" t="inlineStr">
         <is>
-          <t>23:24</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AA361" t="inlineStr">
@@ -49917,7 +49467,7 @@
       </c>
       <c r="AB361" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AC361" t="inlineStr">
@@ -49962,10 +49512,10 @@
     </row>
     <row r="362">
       <c r="A362" t="n">
-        <v>122254519</v>
+        <v>122254392</v>
       </c>
       <c r="B362" t="n">
-        <v>56271</v>
+        <v>56285</v>
       </c>
       <c r="C362" t="inlineStr">
         <is>
@@ -49974,25 +49524,20 @@
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E362" t="n">
-        <v>205998</v>
-      </c>
-      <c r="F362" t="inlineStr">
-        <is>
-          <t>Nordfladdermus</t>
-        </is>
+        <v>100092</v>
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I362" t="inlineStr">
@@ -50016,10 +49561,10 @@
         </is>
       </c>
       <c r="Q362" t="n">
-        <v>586424</v>
+        <v>586384</v>
       </c>
       <c r="R362" t="n">
-        <v>6311135</v>
+        <v>6311139</v>
       </c>
       <c r="S362" t="n">
         <v>5</v>
@@ -50051,7 +49596,7 @@
       </c>
       <c r="Z362" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AA362" t="inlineStr">
@@ -50061,7 +49606,7 @@
       </c>
       <c r="AB362" t="inlineStr">
         <is>
-          <t>22:38</t>
+          <t>22:46</t>
         </is>
       </c>
       <c r="AC362" t="inlineStr">
@@ -50106,7 +49651,7 @@
     </row>
     <row r="363">
       <c r="A363" t="n">
-        <v>122254392</v>
+        <v>122254306</v>
       </c>
       <c r="B363" t="n">
         <v>56285</v>
@@ -50124,11 +49669,6 @@
       <c r="E363" t="n">
         <v>100092</v>
       </c>
-      <c r="F363" t="inlineStr">
-        <is>
-          <t>Större brunfladdermus</t>
-        </is>
-      </c>
       <c r="G363" t="inlineStr">
         <is>
           <t>Nyctalus noctula</t>
@@ -50160,10 +49700,10 @@
         </is>
       </c>
       <c r="Q363" t="n">
-        <v>586384</v>
+        <v>586473</v>
       </c>
       <c r="R363" t="n">
-        <v>6311139</v>
+        <v>6311192</v>
       </c>
       <c r="S363" t="n">
         <v>5</v>
@@ -50195,7 +49735,7 @@
       </c>
       <c r="Z363" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AA363" t="inlineStr">
@@ -50205,7 +49745,7 @@
       </c>
       <c r="AB363" t="inlineStr">
         <is>
-          <t>22:46</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AC363" t="inlineStr">
@@ -50250,10 +49790,10 @@
     </row>
     <row r="364">
       <c r="A364" t="n">
-        <v>122254625</v>
+        <v>122254844</v>
       </c>
       <c r="B364" t="n">
-        <v>56290</v>
+        <v>56288</v>
       </c>
       <c r="C364" t="inlineStr">
         <is>
@@ -50266,21 +49806,16 @@
         </is>
       </c>
       <c r="E364" t="n">
-        <v>205995</v>
-      </c>
-      <c r="F364" t="inlineStr">
-        <is>
-          <t>Dvärgpipistrell</t>
-        </is>
+        <v>100111</v>
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I364" t="inlineStr">
@@ -50304,10 +49839,10 @@
         </is>
       </c>
       <c r="Q364" t="n">
-        <v>586309</v>
+        <v>586387</v>
       </c>
       <c r="R364" t="n">
-        <v>6311119</v>
+        <v>6311141</v>
       </c>
       <c r="S364" t="n">
         <v>5</v>
@@ -50339,7 +49874,7 @@
       </c>
       <c r="Z364" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA364" t="inlineStr">
@@ -50349,7 +49884,7 @@
       </c>
       <c r="AB364" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AC364" t="inlineStr">
@@ -50394,10 +49929,10 @@
     </row>
     <row r="365">
       <c r="A365" t="n">
-        <v>122254472</v>
+        <v>122254963</v>
       </c>
       <c r="B365" t="n">
-        <v>56271</v>
+        <v>56278</v>
       </c>
       <c r="C365" t="inlineStr">
         <is>
@@ -50406,25 +49941,20 @@
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E365" t="n">
-        <v>205998</v>
-      </c>
-      <c r="F365" t="inlineStr">
-        <is>
-          <t>Nordfladdermus</t>
-        </is>
+        <v>205992</v>
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I365" t="inlineStr">
@@ -50448,10 +49978,10 @@
         </is>
       </c>
       <c r="Q365" t="n">
-        <v>586455</v>
+        <v>586374</v>
       </c>
       <c r="R365" t="n">
-        <v>6311159</v>
+        <v>6311140</v>
       </c>
       <c r="S365" t="n">
         <v>5</v>
@@ -50483,7 +50013,7 @@
       </c>
       <c r="Z365" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>22:46</t>
         </is>
       </c>
       <c r="AA365" t="inlineStr">
@@ -50493,7 +50023,7 @@
       </c>
       <c r="AB365" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>22:47</t>
         </is>
       </c>
       <c r="AC365" t="inlineStr">
@@ -50538,10 +50068,10 @@
     </row>
     <row r="366">
       <c r="A366" t="n">
-        <v>122254650</v>
+        <v>122254519</v>
       </c>
       <c r="B366" t="n">
-        <v>56290</v>
+        <v>56271</v>
       </c>
       <c r="C366" t="inlineStr">
         <is>
@@ -50550,25 +50080,20 @@
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E366" t="n">
-        <v>205995</v>
-      </c>
-      <c r="F366" t="inlineStr">
-        <is>
-          <t>Dvärgpipistrell</t>
-        </is>
+        <v>205998</v>
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I366" t="inlineStr">
@@ -50592,10 +50117,10 @@
         </is>
       </c>
       <c r="Q366" t="n">
-        <v>586422</v>
+        <v>586424</v>
       </c>
       <c r="R366" t="n">
-        <v>6311105</v>
+        <v>6311135</v>
       </c>
       <c r="S366" t="n">
         <v>5</v>
@@ -50627,7 +50152,7 @@
       </c>
       <c r="Z366" t="inlineStr">
         <is>
-          <t>22:35</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AA366" t="inlineStr">
@@ -50637,7 +50162,7 @@
       </c>
       <c r="AB366" t="inlineStr">
         <is>
-          <t>22:36</t>
+          <t>22:38</t>
         </is>
       </c>
       <c r="AC366" t="inlineStr">
@@ -50682,10 +50207,10 @@
     </row>
     <row r="367">
       <c r="A367" t="n">
-        <v>122254954</v>
+        <v>122254496</v>
       </c>
       <c r="B367" t="n">
-        <v>56278</v>
+        <v>56271</v>
       </c>
       <c r="C367" t="inlineStr">
         <is>
@@ -50694,25 +50219,20 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E367" t="n">
-        <v>205992</v>
-      </c>
-      <c r="F367" t="inlineStr">
-        <is>
-          <t>Vattenfladdermus</t>
-        </is>
+        <v>205998</v>
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I367" t="inlineStr">
@@ -50736,10 +50256,10 @@
         </is>
       </c>
       <c r="Q367" t="n">
-        <v>586442</v>
+        <v>586415</v>
       </c>
       <c r="R367" t="n">
-        <v>6311152</v>
+        <v>6311146</v>
       </c>
       <c r="S367" t="n">
         <v>5</v>
@@ -50771,7 +50291,7 @@
       </c>
       <c r="Z367" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AA367" t="inlineStr">
@@ -50781,7 +50301,7 @@
       </c>
       <c r="AB367" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>23:03</t>
         </is>
       </c>
       <c r="AC367" t="inlineStr">
@@ -50826,7 +50346,7 @@
     </row>
     <row r="368">
       <c r="A368" t="n">
-        <v>122254951</v>
+        <v>122254952</v>
       </c>
       <c r="B368" t="n">
         <v>56278</v>
@@ -50844,11 +50364,6 @@
       <c r="E368" t="n">
         <v>205992</v>
       </c>
-      <c r="F368" t="inlineStr">
-        <is>
-          <t>Vattenfladdermus</t>
-        </is>
-      </c>
       <c r="G368" t="inlineStr">
         <is>
           <t>Myotis daubentonii</t>
@@ -50880,10 +50395,10 @@
         </is>
       </c>
       <c r="Q368" t="n">
-        <v>586459</v>
+        <v>586455</v>
       </c>
       <c r="R368" t="n">
-        <v>6311154</v>
+        <v>6311156</v>
       </c>
       <c r="S368" t="n">
         <v>5</v>
@@ -50970,7 +50485,7 @@
     </row>
     <row r="369">
       <c r="A369" t="n">
-        <v>122254606</v>
+        <v>122254616</v>
       </c>
       <c r="B369" t="n">
         <v>56290</v>
@@ -50988,11 +50503,6 @@
       <c r="E369" t="n">
         <v>205995</v>
       </c>
-      <c r="F369" t="inlineStr">
-        <is>
-          <t>Dvärgpipistrell</t>
-        </is>
-      </c>
       <c r="G369" t="inlineStr">
         <is>
           <t>Pipistrellus pygmaeus</t>
@@ -51024,10 +50534,10 @@
         </is>
       </c>
       <c r="Q369" t="n">
-        <v>586415</v>
+        <v>586327</v>
       </c>
       <c r="R369" t="n">
-        <v>6311146</v>
+        <v>6311118</v>
       </c>
       <c r="S369" t="n">
         <v>5</v>
@@ -51059,7 +50569,7 @@
       </c>
       <c r="Z369" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>22:57</t>
         </is>
       </c>
       <c r="AA369" t="inlineStr">
@@ -51069,7 +50579,7 @@
       </c>
       <c r="AB369" t="inlineStr">
         <is>
-          <t>23:03</t>
+          <t>22:58</t>
         </is>
       </c>
       <c r="AC369" t="inlineStr">
@@ -51114,7 +50624,7 @@
     </row>
     <row r="370">
       <c r="A370" t="n">
-        <v>122254341</v>
+        <v>122254365</v>
       </c>
       <c r="B370" t="n">
         <v>56285</v>
@@ -51132,11 +50642,6 @@
       <c r="E370" t="n">
         <v>100092</v>
       </c>
-      <c r="F370" t="inlineStr">
-        <is>
-          <t>Större brunfladdermus</t>
-        </is>
-      </c>
       <c r="G370" t="inlineStr">
         <is>
           <t>Nyctalus noctula</t>
@@ -51168,10 +50673,10 @@
         </is>
       </c>
       <c r="Q370" t="n">
-        <v>586415</v>
+        <v>586276</v>
       </c>
       <c r="R370" t="n">
-        <v>6311146</v>
+        <v>6311100</v>
       </c>
       <c r="S370" t="n">
         <v>5</v>
@@ -51203,7 +50708,7 @@
       </c>
       <c r="Z370" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AA370" t="inlineStr">
@@ -51213,7 +50718,7 @@
       </c>
       <c r="AB370" t="inlineStr">
         <is>
-          <t>23:03</t>
+          <t>22:52</t>
         </is>
       </c>
       <c r="AC370" t="inlineStr">
@@ -51258,10 +50763,10 @@
     </row>
     <row r="371">
       <c r="A371" t="n">
-        <v>122254878</v>
+        <v>122254315</v>
       </c>
       <c r="B371" t="n">
-        <v>56288</v>
+        <v>56285</v>
       </c>
       <c r="C371" t="inlineStr">
         <is>
@@ -51274,21 +50779,16 @@
         </is>
       </c>
       <c r="E371" t="n">
-        <v>100111</v>
-      </c>
-      <c r="F371" t="inlineStr">
-        <is>
-          <t>Trollpipistrell</t>
-        </is>
+        <v>100092</v>
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I371" t="inlineStr">
@@ -51312,10 +50812,10 @@
         </is>
       </c>
       <c r="Q371" t="n">
-        <v>586280</v>
+        <v>586441</v>
       </c>
       <c r="R371" t="n">
-        <v>6311103</v>
+        <v>6311155</v>
       </c>
       <c r="S371" t="n">
         <v>5</v>
@@ -51347,7 +50847,7 @@
       </c>
       <c r="Z371" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AA371" t="inlineStr">
@@ -51357,7 +50857,7 @@
       </c>
       <c r="AB371" t="inlineStr">
         <is>
-          <t>22:52</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AC371" t="inlineStr">
@@ -51402,10 +50902,10 @@
     </row>
     <row r="372">
       <c r="A372" t="n">
-        <v>122254607</v>
+        <v>122254951</v>
       </c>
       <c r="B372" t="n">
-        <v>56290</v>
+        <v>56278</v>
       </c>
       <c r="C372" t="inlineStr">
         <is>
@@ -51418,21 +50918,16 @@
         </is>
       </c>
       <c r="E372" t="n">
-        <v>205995</v>
-      </c>
-      <c r="F372" t="inlineStr">
-        <is>
-          <t>Dvärgpipistrell</t>
-        </is>
+        <v>205992</v>
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I372" t="inlineStr">
@@ -51456,10 +50951,10 @@
         </is>
       </c>
       <c r="Q372" t="n">
-        <v>586415</v>
+        <v>586459</v>
       </c>
       <c r="R372" t="n">
-        <v>6311149</v>
+        <v>6311154</v>
       </c>
       <c r="S372" t="n">
         <v>5</v>
@@ -51491,7 +50986,7 @@
       </c>
       <c r="Z372" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AA372" t="inlineStr">
@@ -51501,7 +50996,7 @@
       </c>
       <c r="AB372" t="inlineStr">
         <is>
-          <t>23:03</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AC372" t="inlineStr">
@@ -51546,10 +51041,10 @@
     </row>
     <row r="373">
       <c r="A373" t="n">
-        <v>122254306</v>
+        <v>122254637</v>
       </c>
       <c r="B373" t="n">
-        <v>56285</v>
+        <v>56290</v>
       </c>
       <c r="C373" t="inlineStr">
         <is>
@@ -51562,21 +51057,16 @@
         </is>
       </c>
       <c r="E373" t="n">
-        <v>100092</v>
-      </c>
-      <c r="F373" t="inlineStr">
-        <is>
-          <t>Större brunfladdermus</t>
-        </is>
+        <v>205995</v>
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H373" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I373" t="inlineStr">
@@ -51600,10 +51090,10 @@
         </is>
       </c>
       <c r="Q373" t="n">
-        <v>586473</v>
+        <v>586408</v>
       </c>
       <c r="R373" t="n">
-        <v>6311192</v>
+        <v>6311124</v>
       </c>
       <c r="S373" t="n">
         <v>5</v>
@@ -51635,7 +51125,7 @@
       </c>
       <c r="Z373" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>22:43</t>
         </is>
       </c>
       <c r="AA373" t="inlineStr">
@@ -51645,7 +51135,7 @@
       </c>
       <c r="AB373" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AC373" t="inlineStr">
@@ -51690,10 +51180,10 @@
     </row>
     <row r="374">
       <c r="A374" t="n">
-        <v>122254634</v>
+        <v>122254512</v>
       </c>
       <c r="B374" t="n">
-        <v>56290</v>
+        <v>56271</v>
       </c>
       <c r="C374" t="inlineStr">
         <is>
@@ -51702,25 +51192,20 @@
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E374" t="n">
-        <v>205995</v>
-      </c>
-      <c r="F374" t="inlineStr">
-        <is>
-          <t>Dvärgpipistrell</t>
-        </is>
+        <v>205998</v>
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I374" t="inlineStr">
@@ -51744,10 +51229,10 @@
         </is>
       </c>
       <c r="Q374" t="n">
-        <v>586415</v>
+        <v>586379</v>
       </c>
       <c r="R374" t="n">
-        <v>6311148</v>
+        <v>6311136</v>
       </c>
       <c r="S374" t="n">
         <v>5</v>
@@ -51779,7 +51264,7 @@
       </c>
       <c r="Z374" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AA374" t="inlineStr">
@@ -51789,7 +51274,7 @@
       </c>
       <c r="AB374" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>22:46</t>
         </is>
       </c>
       <c r="AC374" t="inlineStr">
@@ -51834,7 +51319,7 @@
     </row>
     <row r="375">
       <c r="A375" t="n">
-        <v>122254635</v>
+        <v>122254611</v>
       </c>
       <c r="B375" t="n">
         <v>56290</v>
@@ -51852,11 +51337,6 @@
       <c r="E375" t="n">
         <v>205995</v>
       </c>
-      <c r="F375" t="inlineStr">
-        <is>
-          <t>Dvärgpipistrell</t>
-        </is>
-      </c>
       <c r="G375" t="inlineStr">
         <is>
           <t>Pipistrellus pygmaeus</t>
@@ -51888,10 +51368,10 @@
         </is>
       </c>
       <c r="Q375" t="n">
-        <v>586417</v>
+        <v>586370</v>
       </c>
       <c r="R375" t="n">
-        <v>6311145</v>
+        <v>6311139</v>
       </c>
       <c r="S375" t="n">
         <v>5</v>
@@ -51923,7 +51403,7 @@
       </c>
       <c r="Z375" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>22:59</t>
         </is>
       </c>
       <c r="AA375" t="inlineStr">
@@ -51933,7 +51413,7 @@
       </c>
       <c r="AB375" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AC375" t="inlineStr">
@@ -51978,10 +51458,10 @@
     </row>
     <row r="376">
       <c r="A376" t="n">
-        <v>122254658</v>
+        <v>122254412</v>
       </c>
       <c r="B376" t="n">
-        <v>56290</v>
+        <v>56285</v>
       </c>
       <c r="C376" t="inlineStr">
         <is>
@@ -51994,21 +51474,16 @@
         </is>
       </c>
       <c r="E376" t="n">
-        <v>205995</v>
-      </c>
-      <c r="F376" t="inlineStr">
-        <is>
-          <t>Dvärgpipistrell</t>
-        </is>
+        <v>100092</v>
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H376" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I376" t="inlineStr">
@@ -52032,10 +51507,10 @@
         </is>
       </c>
       <c r="Q376" t="n">
-        <v>586491</v>
+        <v>586424</v>
       </c>
       <c r="R376" t="n">
-        <v>6311181</v>
+        <v>6311135</v>
       </c>
       <c r="S376" t="n">
         <v>5</v>
@@ -52067,7 +51542,7 @@
       </c>
       <c r="Z376" t="inlineStr">
         <is>
-          <t>22:31</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AA376" t="inlineStr">
@@ -52077,7 +51552,7 @@
       </c>
       <c r="AB376" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>22:38</t>
         </is>
       </c>
       <c r="AC376" t="inlineStr">
@@ -52122,7 +51597,7 @@
     </row>
     <row r="377">
       <c r="A377" t="n">
-        <v>122254316</v>
+        <v>122254313</v>
       </c>
       <c r="B377" t="n">
         <v>56285</v>
@@ -52140,11 +51615,6 @@
       <c r="E377" t="n">
         <v>100092</v>
       </c>
-      <c r="F377" t="inlineStr">
-        <is>
-          <t>Större brunfladdermus</t>
-        </is>
-      </c>
       <c r="G377" t="inlineStr">
         <is>
           <t>Nyctalus noctula</t>
@@ -52176,10 +51646,10 @@
         </is>
       </c>
       <c r="Q377" t="n">
-        <v>586423</v>
+        <v>586449</v>
       </c>
       <c r="R377" t="n">
-        <v>6311166</v>
+        <v>6311155</v>
       </c>
       <c r="S377" t="n">
         <v>5</v>
@@ -52211,7 +51681,7 @@
       </c>
       <c r="Z377" t="inlineStr">
         <is>
-          <t>23:23</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA377" t="inlineStr">
@@ -52221,7 +51691,7 @@
       </c>
       <c r="AB377" t="inlineStr">
         <is>
-          <t>23:24</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC377" t="inlineStr">
@@ -52266,10 +51736,10 @@
     </row>
     <row r="378">
       <c r="A378" t="n">
-        <v>122254646</v>
+        <v>122254370</v>
       </c>
       <c r="B378" t="n">
-        <v>56290</v>
+        <v>56285</v>
       </c>
       <c r="C378" t="inlineStr">
         <is>
@@ -52282,21 +51752,16 @@
         </is>
       </c>
       <c r="E378" t="n">
-        <v>205995</v>
-      </c>
-      <c r="F378" t="inlineStr">
-        <is>
-          <t>Dvärgpipistrell</t>
-        </is>
+        <v>100092</v>
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I378" t="inlineStr">
@@ -52320,10 +51785,10 @@
         </is>
       </c>
       <c r="Q378" t="n">
-        <v>586422</v>
+        <v>586309</v>
       </c>
       <c r="R378" t="n">
-        <v>6311111</v>
+        <v>6311119</v>
       </c>
       <c r="S378" t="n">
         <v>5</v>
@@ -52355,7 +51820,7 @@
       </c>
       <c r="Z378" t="inlineStr">
         <is>
-          <t>22:36</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AA378" t="inlineStr">
@@ -52365,7 +51830,7 @@
       </c>
       <c r="AB378" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AC378" t="inlineStr">
@@ -52410,7 +51875,7 @@
     </row>
     <row r="379">
       <c r="A379" t="n">
-        <v>122254585</v>
+        <v>122254658</v>
       </c>
       <c r="B379" t="n">
         <v>56290</v>
@@ -52428,11 +51893,6 @@
       <c r="E379" t="n">
         <v>205995</v>
       </c>
-      <c r="F379" t="inlineStr">
-        <is>
-          <t>Dvärgpipistrell</t>
-        </is>
-      </c>
       <c r="G379" t="inlineStr">
         <is>
           <t>Pipistrellus pygmaeus</t>
@@ -52464,10 +51924,10 @@
         </is>
       </c>
       <c r="Q379" t="n">
-        <v>586455</v>
+        <v>586491</v>
       </c>
       <c r="R379" t="n">
-        <v>6311156</v>
+        <v>6311181</v>
       </c>
       <c r="S379" t="n">
         <v>5</v>
@@ -52499,7 +51959,7 @@
       </c>
       <c r="Z379" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>22:31</t>
         </is>
       </c>
       <c r="AA379" t="inlineStr">
@@ -52509,7 +51969,7 @@
       </c>
       <c r="AB379" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AC379" t="inlineStr">
@@ -52554,7 +52014,7 @@
     </row>
     <row r="380">
       <c r="A380" t="n">
-        <v>122254609</v>
+        <v>122254650</v>
       </c>
       <c r="B380" t="n">
         <v>56290</v>
@@ -52572,11 +52032,6 @@
       <c r="E380" t="n">
         <v>205995</v>
       </c>
-      <c r="F380" t="inlineStr">
-        <is>
-          <t>Dvärgpipistrell</t>
-        </is>
-      </c>
       <c r="G380" t="inlineStr">
         <is>
           <t>Pipistrellus pygmaeus</t>
@@ -52608,10 +52063,10 @@
         </is>
       </c>
       <c r="Q380" t="n">
-        <v>586392</v>
+        <v>586422</v>
       </c>
       <c r="R380" t="n">
-        <v>6311147</v>
+        <v>6311105</v>
       </c>
       <c r="S380" t="n">
         <v>5</v>
@@ -52643,7 +52098,7 @@
       </c>
       <c r="Z380" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="AA380" t="inlineStr">
@@ -52653,7 +52108,7 @@
       </c>
       <c r="AB380" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>22:36</t>
         </is>
       </c>
       <c r="AC380" t="inlineStr">
@@ -52698,7 +52153,7 @@
     </row>
     <row r="381">
       <c r="A381" t="n">
-        <v>122254415</v>
+        <v>122254318</v>
       </c>
       <c r="B381" t="n">
         <v>56285</v>
@@ -52716,11 +52171,6 @@
       <c r="E381" t="n">
         <v>100092</v>
       </c>
-      <c r="F381" t="inlineStr">
-        <is>
-          <t>Större brunfladdermus</t>
-        </is>
-      </c>
       <c r="G381" t="inlineStr">
         <is>
           <t>Nyctalus noctula</t>
@@ -52752,10 +52202,10 @@
         </is>
       </c>
       <c r="Q381" t="n">
-        <v>586425</v>
+        <v>586455</v>
       </c>
       <c r="R381" t="n">
-        <v>6311135</v>
+        <v>6311228</v>
       </c>
       <c r="S381" t="n">
         <v>5</v>
@@ -52787,7 +52237,7 @@
       </c>
       <c r="Z381" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>23:22</t>
         </is>
       </c>
       <c r="AA381" t="inlineStr">
@@ -52797,7 +52247,7 @@
       </c>
       <c r="AB381" t="inlineStr">
         <is>
-          <t>22:38</t>
+          <t>23:23</t>
         </is>
       </c>
       <c r="AC381" t="inlineStr">
@@ -52842,10 +52292,10 @@
     </row>
     <row r="382">
       <c r="A382" t="n">
-        <v>122254371</v>
+        <v>122254648</v>
       </c>
       <c r="B382" t="n">
-        <v>56285</v>
+        <v>56290</v>
       </c>
       <c r="C382" t="inlineStr">
         <is>
@@ -52858,21 +52308,16 @@
         </is>
       </c>
       <c r="E382" t="n">
-        <v>100092</v>
-      </c>
-      <c r="F382" t="inlineStr">
-        <is>
-          <t>Större brunfladdermus</t>
-        </is>
+        <v>205995</v>
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H382" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I382" t="inlineStr">
@@ -52896,10 +52341,10 @@
         </is>
       </c>
       <c r="Q382" t="n">
-        <v>586308</v>
+        <v>586418</v>
       </c>
       <c r="R382" t="n">
-        <v>6311132</v>
+        <v>6311107</v>
       </c>
       <c r="S382" t="n">
         <v>5</v>
@@ -52931,7 +52376,7 @@
       </c>
       <c r="Z382" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>22:36</t>
         </is>
       </c>
       <c r="AA382" t="inlineStr">
@@ -52941,7 +52386,7 @@
       </c>
       <c r="AB382" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AC382" t="inlineStr">
@@ -52986,10 +52431,10 @@
     </row>
     <row r="383">
       <c r="A383" t="n">
-        <v>122254877</v>
+        <v>122254606</v>
       </c>
       <c r="B383" t="n">
-        <v>56288</v>
+        <v>56290</v>
       </c>
       <c r="C383" t="inlineStr">
         <is>
@@ -53002,21 +52447,16 @@
         </is>
       </c>
       <c r="E383" t="n">
-        <v>100111</v>
-      </c>
-      <c r="F383" t="inlineStr">
-        <is>
-          <t>Trollpipistrell</t>
-        </is>
+        <v>205995</v>
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I383" t="inlineStr">
@@ -53040,10 +52480,10 @@
         </is>
       </c>
       <c r="Q383" t="n">
-        <v>586276</v>
+        <v>586415</v>
       </c>
       <c r="R383" t="n">
-        <v>6311100</v>
+        <v>6311146</v>
       </c>
       <c r="S383" t="n">
         <v>5</v>
@@ -53075,7 +52515,7 @@
       </c>
       <c r="Z383" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AA383" t="inlineStr">
@@ -53085,7 +52525,7 @@
       </c>
       <c r="AB383" t="inlineStr">
         <is>
-          <t>22:52</t>
+          <t>23:03</t>
         </is>
       </c>
       <c r="AC383" t="inlineStr">
@@ -53130,10 +52570,10 @@
     </row>
     <row r="384">
       <c r="A384" t="n">
-        <v>122254475</v>
+        <v>122254966</v>
       </c>
       <c r="B384" t="n">
-        <v>56271</v>
+        <v>56278</v>
       </c>
       <c r="C384" t="inlineStr">
         <is>
@@ -53142,25 +52582,20 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E384" t="n">
-        <v>205998</v>
-      </c>
-      <c r="F384" t="inlineStr">
-        <is>
-          <t>Nordfladdermus</t>
-        </is>
+        <v>205992</v>
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I384" t="inlineStr">
@@ -53184,10 +52619,10 @@
         </is>
       </c>
       <c r="Q384" t="n">
-        <v>586420</v>
+        <v>586467</v>
       </c>
       <c r="R384" t="n">
-        <v>6311166</v>
+        <v>6311178</v>
       </c>
       <c r="S384" t="n">
         <v>5</v>
@@ -53219,7 +52654,7 @@
       </c>
       <c r="Z384" t="inlineStr">
         <is>
-          <t>23:23</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AA384" t="inlineStr">
@@ -53229,7 +52664,7 @@
       </c>
       <c r="AB384" t="inlineStr">
         <is>
-          <t>23:24</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="AC384" t="inlineStr">
@@ -53274,10 +52709,10 @@
     </row>
     <row r="385">
       <c r="A385" t="n">
-        <v>122254633</v>
+        <v>122254342</v>
       </c>
       <c r="B385" t="n">
-        <v>56290</v>
+        <v>56285</v>
       </c>
       <c r="C385" t="inlineStr">
         <is>
@@ -53290,21 +52725,16 @@
         </is>
       </c>
       <c r="E385" t="n">
-        <v>205995</v>
-      </c>
-      <c r="F385" t="inlineStr">
-        <is>
-          <t>Dvärgpipistrell</t>
-        </is>
+        <v>100092</v>
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H385" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I385" t="inlineStr">
@@ -53328,10 +52758,10 @@
         </is>
       </c>
       <c r="Q385" t="n">
-        <v>586396</v>
+        <v>586389</v>
       </c>
       <c r="R385" t="n">
-        <v>6311146</v>
+        <v>6311142</v>
       </c>
       <c r="S385" t="n">
         <v>5</v>
@@ -53363,7 +52793,7 @@
       </c>
       <c r="Z385" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA385" t="inlineStr">
@@ -53373,7 +52803,7 @@
       </c>
       <c r="AB385" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AC385" t="inlineStr">
@@ -53418,7 +52848,7 @@
     </row>
     <row r="386">
       <c r="A386" t="n">
-        <v>122254643</v>
+        <v>122254656</v>
       </c>
       <c r="B386" t="n">
         <v>56290</v>
@@ -53436,11 +52866,6 @@
       <c r="E386" t="n">
         <v>205995</v>
       </c>
-      <c r="F386" t="inlineStr">
-        <is>
-          <t>Dvärgpipistrell</t>
-        </is>
-      </c>
       <c r="G386" t="inlineStr">
         <is>
           <t>Pipistrellus pygmaeus</t>
@@ -53472,10 +52897,10 @@
         </is>
       </c>
       <c r="Q386" t="n">
-        <v>586424</v>
+        <v>586483</v>
       </c>
       <c r="R386" t="n">
-        <v>6311135</v>
+        <v>6311186</v>
       </c>
       <c r="S386" t="n">
         <v>5</v>
@@ -53507,7 +52932,7 @@
       </c>
       <c r="Z386" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>22:31</t>
         </is>
       </c>
       <c r="AA386" t="inlineStr">
@@ -53517,7 +52942,7 @@
       </c>
       <c r="AB386" t="inlineStr">
         <is>
-          <t>22:38</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AC386" t="inlineStr">
@@ -53562,10 +52987,10 @@
     </row>
     <row r="387">
       <c r="A387" t="n">
-        <v>122254584</v>
+        <v>122254352</v>
       </c>
       <c r="B387" t="n">
-        <v>56290</v>
+        <v>56285</v>
       </c>
       <c r="C387" t="inlineStr">
         <is>
@@ -53578,21 +53003,16 @@
         </is>
       </c>
       <c r="E387" t="n">
-        <v>205995</v>
-      </c>
-      <c r="F387" t="inlineStr">
-        <is>
-          <t>Dvärgpipistrell</t>
-        </is>
+        <v>100092</v>
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I387" t="inlineStr">
@@ -53616,10 +53036,10 @@
         </is>
       </c>
       <c r="Q387" t="n">
-        <v>586473</v>
+        <v>586288</v>
       </c>
       <c r="R387" t="n">
-        <v>6311192</v>
+        <v>6311100</v>
       </c>
       <c r="S387" t="n">
         <v>5</v>
@@ -53651,7 +53071,7 @@
       </c>
       <c r="Z387" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>22:55</t>
         </is>
       </c>
       <c r="AA387" t="inlineStr">
@@ -53661,7 +53081,7 @@
       </c>
       <c r="AB387" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>22:56</t>
         </is>
       </c>
       <c r="AC387" t="inlineStr">
@@ -53706,10 +53126,10 @@
     </row>
     <row r="388">
       <c r="A388" t="n">
-        <v>122254966</v>
+        <v>122254617</v>
       </c>
       <c r="B388" t="n">
-        <v>56278</v>
+        <v>56290</v>
       </c>
       <c r="C388" t="inlineStr">
         <is>
@@ -53722,21 +53142,16 @@
         </is>
       </c>
       <c r="E388" t="n">
-        <v>205992</v>
-      </c>
-      <c r="F388" t="inlineStr">
-        <is>
-          <t>Vattenfladdermus</t>
-        </is>
+        <v>205995</v>
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H388" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I388" t="inlineStr">
@@ -53760,10 +53175,10 @@
         </is>
       </c>
       <c r="Q388" t="n">
-        <v>586467</v>
+        <v>586317</v>
       </c>
       <c r="R388" t="n">
-        <v>6311178</v>
+        <v>6311115</v>
       </c>
       <c r="S388" t="n">
         <v>5</v>
@@ -53795,7 +53210,7 @@
       </c>
       <c r="Z388" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>22:57</t>
         </is>
       </c>
       <c r="AA388" t="inlineStr">
@@ -53805,7 +53220,7 @@
       </c>
       <c r="AB388" t="inlineStr">
         <is>
-          <t>22:33</t>
+          <t>22:58</t>
         </is>
       </c>
       <c r="AC388" t="inlineStr">
@@ -53850,10 +53265,10 @@
     </row>
     <row r="389">
       <c r="A389" t="n">
-        <v>122254352</v>
+        <v>122254586</v>
       </c>
       <c r="B389" t="n">
-        <v>56285</v>
+        <v>56290</v>
       </c>
       <c r="C389" t="inlineStr">
         <is>
@@ -53866,21 +53281,16 @@
         </is>
       </c>
       <c r="E389" t="n">
-        <v>100092</v>
-      </c>
-      <c r="F389" t="inlineStr">
-        <is>
-          <t>Större brunfladdermus</t>
-        </is>
+        <v>205995</v>
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I389" t="inlineStr">
@@ -53904,10 +53314,10 @@
         </is>
       </c>
       <c r="Q389" t="n">
-        <v>586288</v>
+        <v>586446</v>
       </c>
       <c r="R389" t="n">
-        <v>6311100</v>
+        <v>6311158</v>
       </c>
       <c r="S389" t="n">
         <v>5</v>
@@ -53939,7 +53349,7 @@
       </c>
       <c r="Z389" t="inlineStr">
         <is>
-          <t>22:55</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AA389" t="inlineStr">
@@ -53949,7 +53359,7 @@
       </c>
       <c r="AB389" t="inlineStr">
         <is>
-          <t>22:56</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AC389" t="inlineStr">
@@ -54011,11 +53421,6 @@
       </c>
       <c r="E390" t="n">
         <v>100015</v>
-      </c>
-      <c r="F390" t="inlineStr">
-        <is>
-          <t>Barbastell</t>
-        </is>
       </c>
       <c r="G390" t="inlineStr">
         <is>

--- a/artfynd/A 36363-2024 artfynd.xlsx
+++ b/artfynd/A 36363-2024 artfynd.xlsx
@@ -39921,10 +39921,10 @@
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>122254634</v>
+        <v>122254395</v>
       </c>
       <c r="B293" t="n">
-        <v>56290</v>
+        <v>56285</v>
       </c>
       <c r="C293" t="inlineStr">
         <is>
@@ -39937,16 +39937,16 @@
         </is>
       </c>
       <c r="E293" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
@@ -39970,10 +39970,10 @@
         </is>
       </c>
       <c r="Q293" t="n">
-        <v>586415</v>
+        <v>586408</v>
       </c>
       <c r="R293" t="n">
-        <v>6311148</v>
+        <v>6311124</v>
       </c>
       <c r="S293" t="n">
         <v>5</v>
@@ -40005,17 +40005,17 @@
       </c>
       <c r="Z293" t="inlineStr">
         <is>
+          <t>22:43</t>
+        </is>
+      </c>
+      <c r="AA293" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AB293" t="inlineStr">
+        <is>
           <t>22:44</t>
-        </is>
-      </c>
-      <c r="AA293" t="inlineStr">
-        <is>
-          <t>2024-06-26</t>
-        </is>
-      </c>
-      <c r="AB293" t="inlineStr">
-        <is>
-          <t>22:45</t>
         </is>
       </c>
       <c r="AC293" t="inlineStr">
@@ -40060,10 +40060,10 @@
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>122254653</v>
+        <v>122254837</v>
       </c>
       <c r="B294" t="n">
-        <v>56290</v>
+        <v>56288</v>
       </c>
       <c r="C294" t="inlineStr">
         <is>
@@ -40076,16 +40076,16 @@
         </is>
       </c>
       <c r="E294" t="n">
-        <v>205995</v>
+        <v>100111</v>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
@@ -40109,10 +40109,10 @@
         </is>
       </c>
       <c r="Q294" t="n">
-        <v>586430</v>
+        <v>586448</v>
       </c>
       <c r="R294" t="n">
-        <v>6311142</v>
+        <v>6311154</v>
       </c>
       <c r="S294" t="n">
         <v>5</v>
@@ -40144,7 +40144,7 @@
       </c>
       <c r="Z294" t="inlineStr">
         <is>
-          <t>22:33</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA294" t="inlineStr">
@@ -40154,7 +40154,7 @@
       </c>
       <c r="AB294" t="inlineStr">
         <is>
-          <t>22:34</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC294" t="inlineStr">
@@ -40199,10 +40199,10 @@
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>122254584</v>
+        <v>122254880</v>
       </c>
       <c r="B295" t="n">
-        <v>56290</v>
+        <v>56288</v>
       </c>
       <c r="C295" t="inlineStr">
         <is>
@@ -40215,16 +40215,16 @@
         </is>
       </c>
       <c r="E295" t="n">
-        <v>205995</v>
+        <v>100111</v>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
@@ -40248,10 +40248,10 @@
         </is>
       </c>
       <c r="Q295" t="n">
-        <v>586473</v>
+        <v>586303</v>
       </c>
       <c r="R295" t="n">
-        <v>6311192</v>
+        <v>6311115</v>
       </c>
       <c r="S295" t="n">
         <v>5</v>
@@ -40283,7 +40283,7 @@
       </c>
       <c r="Z295" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AA295" t="inlineStr">
@@ -40293,7 +40293,7 @@
       </c>
       <c r="AB295" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AC295" t="inlineStr">
@@ -40338,7 +40338,7 @@
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>122254627</v>
+        <v>122254633</v>
       </c>
       <c r="B296" t="n">
         <v>56290</v>
@@ -40387,10 +40387,10 @@
         </is>
       </c>
       <c r="Q296" t="n">
-        <v>586306</v>
+        <v>586396</v>
       </c>
       <c r="R296" t="n">
-        <v>6311131</v>
+        <v>6311146</v>
       </c>
       <c r="S296" t="n">
         <v>5</v>
@@ -40422,7 +40422,7 @@
       </c>
       <c r="Z296" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AA296" t="inlineStr">
@@ -40432,7 +40432,7 @@
       </c>
       <c r="AB296" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AC296" t="inlineStr">
@@ -40477,7 +40477,7 @@
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>122254633</v>
+        <v>122254634</v>
       </c>
       <c r="B297" t="n">
         <v>56290</v>
@@ -40526,10 +40526,10 @@
         </is>
       </c>
       <c r="Q297" t="n">
-        <v>586396</v>
+        <v>586415</v>
       </c>
       <c r="R297" t="n">
-        <v>6311146</v>
+        <v>6311148</v>
       </c>
       <c r="S297" t="n">
         <v>5</v>
@@ -40616,7 +40616,7 @@
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>122254626</v>
+        <v>122254653</v>
       </c>
       <c r="B298" t="n">
         <v>56290</v>
@@ -40665,10 +40665,10 @@
         </is>
       </c>
       <c r="Q298" t="n">
-        <v>586313</v>
+        <v>586430</v>
       </c>
       <c r="R298" t="n">
-        <v>6311124</v>
+        <v>6311142</v>
       </c>
       <c r="S298" t="n">
         <v>5</v>
@@ -40700,7 +40700,7 @@
       </c>
       <c r="Z298" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="AA298" t="inlineStr">
@@ -40710,7 +40710,7 @@
       </c>
       <c r="AB298" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>22:34</t>
         </is>
       </c>
       <c r="AC298" t="inlineStr">
@@ -40755,10 +40755,10 @@
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>122254395</v>
+        <v>122254584</v>
       </c>
       <c r="B299" t="n">
-        <v>56285</v>
+        <v>56290</v>
       </c>
       <c r="C299" t="inlineStr">
         <is>
@@ -40771,16 +40771,16 @@
         </is>
       </c>
       <c r="E299" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
@@ -40804,10 +40804,10 @@
         </is>
       </c>
       <c r="Q299" t="n">
-        <v>586408</v>
+        <v>586473</v>
       </c>
       <c r="R299" t="n">
-        <v>6311124</v>
+        <v>6311192</v>
       </c>
       <c r="S299" t="n">
         <v>5</v>
@@ -40839,7 +40839,7 @@
       </c>
       <c r="Z299" t="inlineStr">
         <is>
-          <t>22:43</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AA299" t="inlineStr">
@@ -40849,7 +40849,7 @@
       </c>
       <c r="AB299" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AC299" t="inlineStr">
@@ -40894,10 +40894,10 @@
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>122254837</v>
+        <v>122254627</v>
       </c>
       <c r="B300" t="n">
-        <v>56288</v>
+        <v>56290</v>
       </c>
       <c r="C300" t="inlineStr">
         <is>
@@ -40910,16 +40910,16 @@
         </is>
       </c>
       <c r="E300" t="n">
-        <v>100111</v>
+        <v>205995</v>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
@@ -40943,10 +40943,10 @@
         </is>
       </c>
       <c r="Q300" t="n">
-        <v>586448</v>
+        <v>586306</v>
       </c>
       <c r="R300" t="n">
-        <v>6311154</v>
+        <v>6311131</v>
       </c>
       <c r="S300" t="n">
         <v>5</v>
@@ -40978,7 +40978,7 @@
       </c>
       <c r="Z300" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AA300" t="inlineStr">
@@ -40988,7 +40988,7 @@
       </c>
       <c r="AB300" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AC300" t="inlineStr">
@@ -41033,10 +41033,10 @@
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>122254880</v>
+        <v>122254626</v>
       </c>
       <c r="B301" t="n">
-        <v>56288</v>
+        <v>56290</v>
       </c>
       <c r="C301" t="inlineStr">
         <is>
@@ -41049,16 +41049,16 @@
         </is>
       </c>
       <c r="E301" t="n">
-        <v>100111</v>
+        <v>205995</v>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
@@ -41082,10 +41082,10 @@
         </is>
       </c>
       <c r="Q301" t="n">
-        <v>586303</v>
+        <v>586313</v>
       </c>
       <c r="R301" t="n">
-        <v>6311115</v>
+        <v>6311124</v>
       </c>
       <c r="S301" t="n">
         <v>5</v>
@@ -42006,10 +42006,10 @@
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>122254615</v>
+        <v>122254308</v>
       </c>
       <c r="B308" t="n">
-        <v>56290</v>
+        <v>56285</v>
       </c>
       <c r="C308" t="inlineStr">
         <is>
@@ -42022,16 +42022,16 @@
         </is>
       </c>
       <c r="E308" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
@@ -42055,10 +42055,10 @@
         </is>
       </c>
       <c r="Q308" t="n">
-        <v>586329</v>
+        <v>586455</v>
       </c>
       <c r="R308" t="n">
-        <v>6311120</v>
+        <v>6311159</v>
       </c>
       <c r="S308" t="n">
         <v>5</v>
@@ -42090,7 +42090,7 @@
       </c>
       <c r="Z308" t="inlineStr">
         <is>
-          <t>22:57</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AA308" t="inlineStr">
@@ -42100,7 +42100,7 @@
       </c>
       <c r="AB308" t="inlineStr">
         <is>
-          <t>22:58</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AC308" t="inlineStr">
@@ -42145,10 +42145,10 @@
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>122254660</v>
+        <v>122254350</v>
       </c>
       <c r="B309" t="n">
-        <v>56290</v>
+        <v>56285</v>
       </c>
       <c r="C309" t="inlineStr">
         <is>
@@ -42161,16 +42161,16 @@
         </is>
       </c>
       <c r="E309" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
@@ -42194,10 +42194,10 @@
         </is>
       </c>
       <c r="Q309" t="n">
-        <v>586488</v>
+        <v>586330</v>
       </c>
       <c r="R309" t="n">
-        <v>6311183</v>
+        <v>6311120</v>
       </c>
       <c r="S309" t="n">
         <v>5</v>
@@ -42229,7 +42229,7 @@
       </c>
       <c r="Z309" t="inlineStr">
         <is>
-          <t>22:31</t>
+          <t>22:57</t>
         </is>
       </c>
       <c r="AA309" t="inlineStr">
@@ -42239,7 +42239,7 @@
       </c>
       <c r="AB309" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>22:58</t>
         </is>
       </c>
       <c r="AC309" t="inlineStr">
@@ -42284,10 +42284,10 @@
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>122254610</v>
+        <v>122254316</v>
       </c>
       <c r="B310" t="n">
-        <v>56290</v>
+        <v>56285</v>
       </c>
       <c r="C310" t="inlineStr">
         <is>
@@ -42300,16 +42300,16 @@
         </is>
       </c>
       <c r="E310" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
@@ -42333,10 +42333,10 @@
         </is>
       </c>
       <c r="Q310" t="n">
-        <v>586389</v>
+        <v>586423</v>
       </c>
       <c r="R310" t="n">
-        <v>6311141</v>
+        <v>6311166</v>
       </c>
       <c r="S310" t="n">
         <v>5</v>
@@ -42368,7 +42368,7 @@
       </c>
       <c r="Z310" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>23:23</t>
         </is>
       </c>
       <c r="AA310" t="inlineStr">
@@ -42378,7 +42378,7 @@
       </c>
       <c r="AB310" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="AC310" t="inlineStr">
@@ -42423,10 +42423,10 @@
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>122254612</v>
+        <v>122254312</v>
       </c>
       <c r="B311" t="n">
-        <v>56290</v>
+        <v>56285</v>
       </c>
       <c r="C311" t="inlineStr">
         <is>
@@ -42439,16 +42439,16 @@
         </is>
       </c>
       <c r="E311" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
@@ -42472,10 +42472,10 @@
         </is>
       </c>
       <c r="Q311" t="n">
-        <v>586371</v>
+        <v>586452</v>
       </c>
       <c r="R311" t="n">
-        <v>6311135</v>
+        <v>6311152</v>
       </c>
       <c r="S311" t="n">
         <v>5</v>
@@ -42507,7 +42507,7 @@
       </c>
       <c r="Z311" t="inlineStr">
         <is>
-          <t>22:59</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA311" t="inlineStr">
@@ -42517,7 +42517,7 @@
       </c>
       <c r="AB311" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC311" t="inlineStr">
@@ -42562,10 +42562,10 @@
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>122254308</v>
+        <v>122254615</v>
       </c>
       <c r="B312" t="n">
-        <v>56285</v>
+        <v>56290</v>
       </c>
       <c r="C312" t="inlineStr">
         <is>
@@ -42578,16 +42578,16 @@
         </is>
       </c>
       <c r="E312" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
@@ -42611,10 +42611,10 @@
         </is>
       </c>
       <c r="Q312" t="n">
-        <v>586455</v>
+        <v>586329</v>
       </c>
       <c r="R312" t="n">
-        <v>6311159</v>
+        <v>6311120</v>
       </c>
       <c r="S312" t="n">
         <v>5</v>
@@ -42646,7 +42646,7 @@
       </c>
       <c r="Z312" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>22:57</t>
         </is>
       </c>
       <c r="AA312" t="inlineStr">
@@ -42656,7 +42656,7 @@
       </c>
       <c r="AB312" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>22:58</t>
         </is>
       </c>
       <c r="AC312" t="inlineStr">
@@ -42701,10 +42701,10 @@
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>122254350</v>
+        <v>122254660</v>
       </c>
       <c r="B313" t="n">
-        <v>56285</v>
+        <v>56290</v>
       </c>
       <c r="C313" t="inlineStr">
         <is>
@@ -42717,16 +42717,16 @@
         </is>
       </c>
       <c r="E313" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
@@ -42750,10 +42750,10 @@
         </is>
       </c>
       <c r="Q313" t="n">
-        <v>586330</v>
+        <v>586488</v>
       </c>
       <c r="R313" t="n">
-        <v>6311120</v>
+        <v>6311183</v>
       </c>
       <c r="S313" t="n">
         <v>5</v>
@@ -42785,7 +42785,7 @@
       </c>
       <c r="Z313" t="inlineStr">
         <is>
-          <t>22:57</t>
+          <t>22:31</t>
         </is>
       </c>
       <c r="AA313" t="inlineStr">
@@ -42795,7 +42795,7 @@
       </c>
       <c r="AB313" t="inlineStr">
         <is>
-          <t>22:58</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AC313" t="inlineStr">
@@ -42840,10 +42840,10 @@
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>122254316</v>
+        <v>122254610</v>
       </c>
       <c r="B314" t="n">
-        <v>56285</v>
+        <v>56290</v>
       </c>
       <c r="C314" t="inlineStr">
         <is>
@@ -42856,16 +42856,16 @@
         </is>
       </c>
       <c r="E314" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
@@ -42889,10 +42889,10 @@
         </is>
       </c>
       <c r="Q314" t="n">
-        <v>586423</v>
+        <v>586389</v>
       </c>
       <c r="R314" t="n">
-        <v>6311166</v>
+        <v>6311141</v>
       </c>
       <c r="S314" t="n">
         <v>5</v>
@@ -42924,7 +42924,7 @@
       </c>
       <c r="Z314" t="inlineStr">
         <is>
-          <t>23:23</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA314" t="inlineStr">
@@ -42934,7 +42934,7 @@
       </c>
       <c r="AB314" t="inlineStr">
         <is>
-          <t>23:24</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AC314" t="inlineStr">
@@ -42979,10 +42979,10 @@
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>122254312</v>
+        <v>122254612</v>
       </c>
       <c r="B315" t="n">
-        <v>56285</v>
+        <v>56290</v>
       </c>
       <c r="C315" t="inlineStr">
         <is>
@@ -42995,16 +42995,16 @@
         </is>
       </c>
       <c r="E315" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
@@ -43028,10 +43028,10 @@
         </is>
       </c>
       <c r="Q315" t="n">
-        <v>586452</v>
+        <v>586371</v>
       </c>
       <c r="R315" t="n">
-        <v>6311152</v>
+        <v>6311135</v>
       </c>
       <c r="S315" t="n">
         <v>5</v>
@@ -43063,7 +43063,7 @@
       </c>
       <c r="Z315" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>22:59</t>
         </is>
       </c>
       <c r="AA315" t="inlineStr">
@@ -43073,7 +43073,7 @@
       </c>
       <c r="AB315" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AC315" t="inlineStr">
@@ -45898,10 +45898,10 @@
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>122254649</v>
+        <v>122254499</v>
       </c>
       <c r="B336" t="n">
-        <v>56290</v>
+        <v>56271</v>
       </c>
       <c r="C336" t="inlineStr">
         <is>
@@ -45910,20 +45910,20 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E336" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
@@ -45947,10 +45947,10 @@
         </is>
       </c>
       <c r="Q336" t="n">
-        <v>586422</v>
+        <v>586392</v>
       </c>
       <c r="R336" t="n">
-        <v>6311100</v>
+        <v>6311147</v>
       </c>
       <c r="S336" t="n">
         <v>5</v>
@@ -45982,7 +45982,7 @@
       </c>
       <c r="Z336" t="inlineStr">
         <is>
-          <t>22:35</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AA336" t="inlineStr">
@@ -45992,7 +45992,7 @@
       </c>
       <c r="AB336" t="inlineStr">
         <is>
-          <t>22:36</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AC336" t="inlineStr">
@@ -46037,7 +46037,7 @@
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>122254608</v>
+        <v>122254649</v>
       </c>
       <c r="B337" t="n">
         <v>56290</v>
@@ -46086,10 +46086,10 @@
         </is>
       </c>
       <c r="Q337" t="n">
-        <v>586393</v>
+        <v>586422</v>
       </c>
       <c r="R337" t="n">
-        <v>6311147</v>
+        <v>6311100</v>
       </c>
       <c r="S337" t="n">
         <v>5</v>
@@ -46121,7 +46121,7 @@
       </c>
       <c r="Z337" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="AA337" t="inlineStr">
@@ -46131,7 +46131,7 @@
       </c>
       <c r="AB337" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>22:36</t>
         </is>
       </c>
       <c r="AC337" t="inlineStr">
@@ -46176,10 +46176,10 @@
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>122254513</v>
+        <v>122254608</v>
       </c>
       <c r="B338" t="n">
-        <v>56271</v>
+        <v>56290</v>
       </c>
       <c r="C338" t="inlineStr">
         <is>
@@ -46188,20 +46188,20 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E338" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
@@ -46225,10 +46225,10 @@
         </is>
       </c>
       <c r="Q338" t="n">
-        <v>586396</v>
+        <v>586393</v>
       </c>
       <c r="R338" t="n">
-        <v>6311146</v>
+        <v>6311147</v>
       </c>
       <c r="S338" t="n">
         <v>5</v>
@@ -46260,7 +46260,7 @@
       </c>
       <c r="Z338" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AA338" t="inlineStr">
@@ -46270,7 +46270,7 @@
       </c>
       <c r="AB338" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AC338" t="inlineStr">
@@ -46315,7 +46315,7 @@
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>122254499</v>
+        <v>122254513</v>
       </c>
       <c r="B339" t="n">
         <v>56271</v>
@@ -46364,10 +46364,10 @@
         </is>
       </c>
       <c r="Q339" t="n">
-        <v>586392</v>
+        <v>586396</v>
       </c>
       <c r="R339" t="n">
-        <v>6311147</v>
+        <v>6311146</v>
       </c>
       <c r="S339" t="n">
         <v>5</v>
@@ -46399,7 +46399,7 @@
       </c>
       <c r="Z339" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AA339" t="inlineStr">
@@ -46409,7 +46409,7 @@
       </c>
       <c r="AB339" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AC339" t="inlineStr">
@@ -46454,10 +46454,10 @@
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>122254372</v>
+        <v>122254625</v>
       </c>
       <c r="B340" t="n">
-        <v>56285</v>
+        <v>56290</v>
       </c>
       <c r="C340" t="inlineStr">
         <is>
@@ -46470,16 +46470,16 @@
         </is>
       </c>
       <c r="E340" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
@@ -46503,10 +46503,10 @@
         </is>
       </c>
       <c r="Q340" t="n">
-        <v>586306</v>
+        <v>586309</v>
       </c>
       <c r="R340" t="n">
-        <v>6311131</v>
+        <v>6311119</v>
       </c>
       <c r="S340" t="n">
         <v>5</v>
@@ -46593,10 +46593,10 @@
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>122254307</v>
+        <v>122254651</v>
       </c>
       <c r="B341" t="n">
-        <v>56285</v>
+        <v>56290</v>
       </c>
       <c r="C341" t="inlineStr">
         <is>
@@ -46609,16 +46609,16 @@
         </is>
       </c>
       <c r="E341" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I341" t="inlineStr">
@@ -46642,10 +46642,10 @@
         </is>
       </c>
       <c r="Q341" t="n">
-        <v>586477</v>
+        <v>586425</v>
       </c>
       <c r="R341" t="n">
-        <v>6311186</v>
+        <v>6311113</v>
       </c>
       <c r="S341" t="n">
         <v>5</v>
@@ -46677,7 +46677,7 @@
       </c>
       <c r="Z341" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="AA341" t="inlineStr">
@@ -46687,7 +46687,7 @@
       </c>
       <c r="AB341" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>22:36</t>
         </is>
       </c>
       <c r="AC341" t="inlineStr">
@@ -46732,10 +46732,10 @@
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>122254314</v>
+        <v>122254654</v>
       </c>
       <c r="B342" t="n">
-        <v>56285</v>
+        <v>56290</v>
       </c>
       <c r="C342" t="inlineStr">
         <is>
@@ -46748,16 +46748,16 @@
         </is>
       </c>
       <c r="E342" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
@@ -46781,10 +46781,10 @@
         </is>
       </c>
       <c r="Q342" t="n">
-        <v>586443</v>
+        <v>586467</v>
       </c>
       <c r="R342" t="n">
-        <v>6311164</v>
+        <v>6311178</v>
       </c>
       <c r="S342" t="n">
         <v>5</v>
@@ -46816,7 +46816,7 @@
       </c>
       <c r="Z342" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AA342" t="inlineStr">
@@ -46826,7 +46826,7 @@
       </c>
       <c r="AB342" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="AC342" t="inlineStr">
@@ -46871,10 +46871,10 @@
     </row>
     <row r="343">
       <c r="A343" t="n">
-        <v>122254309</v>
+        <v>122254632</v>
       </c>
       <c r="B343" t="n">
-        <v>56285</v>
+        <v>56290</v>
       </c>
       <c r="C343" t="inlineStr">
         <is>
@@ -46887,16 +46887,16 @@
         </is>
       </c>
       <c r="E343" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
@@ -46920,10 +46920,10 @@
         </is>
       </c>
       <c r="Q343" t="n">
-        <v>586456</v>
+        <v>586374</v>
       </c>
       <c r="R343" t="n">
-        <v>6311158</v>
+        <v>6311140</v>
       </c>
       <c r="S343" t="n">
         <v>5</v>
@@ -46955,7 +46955,7 @@
       </c>
       <c r="Z343" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>22:46</t>
         </is>
       </c>
       <c r="AA343" t="inlineStr">
@@ -46965,7 +46965,7 @@
       </c>
       <c r="AB343" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>22:47</t>
         </is>
       </c>
       <c r="AC343" t="inlineStr">
@@ -47010,10 +47010,10 @@
     </row>
     <row r="344">
       <c r="A344" t="n">
-        <v>122254862</v>
+        <v>122254646</v>
       </c>
       <c r="B344" t="n">
-        <v>56288</v>
+        <v>56290</v>
       </c>
       <c r="C344" t="inlineStr">
         <is>
@@ -47026,16 +47026,16 @@
         </is>
       </c>
       <c r="E344" t="n">
-        <v>100111</v>
+        <v>205995</v>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
@@ -47059,10 +47059,10 @@
         </is>
       </c>
       <c r="Q344" t="n">
-        <v>586288</v>
+        <v>586422</v>
       </c>
       <c r="R344" t="n">
-        <v>6311100</v>
+        <v>6311111</v>
       </c>
       <c r="S344" t="n">
         <v>5</v>
@@ -47094,7 +47094,7 @@
       </c>
       <c r="Z344" t="inlineStr">
         <is>
-          <t>22:55</t>
+          <t>22:36</t>
         </is>
       </c>
       <c r="AA344" t="inlineStr">
@@ -47104,7 +47104,7 @@
       </c>
       <c r="AB344" t="inlineStr">
         <is>
-          <t>22:56</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AC344" t="inlineStr">
@@ -47149,10 +47149,10 @@
     </row>
     <row r="345">
       <c r="A345" t="n">
-        <v>122254625</v>
+        <v>122254372</v>
       </c>
       <c r="B345" t="n">
-        <v>56290</v>
+        <v>56285</v>
       </c>
       <c r="C345" t="inlineStr">
         <is>
@@ -47165,16 +47165,16 @@
         </is>
       </c>
       <c r="E345" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
@@ -47198,10 +47198,10 @@
         </is>
       </c>
       <c r="Q345" t="n">
-        <v>586309</v>
+        <v>586306</v>
       </c>
       <c r="R345" t="n">
-        <v>6311119</v>
+        <v>6311131</v>
       </c>
       <c r="S345" t="n">
         <v>5</v>
@@ -47288,10 +47288,10 @@
     </row>
     <row r="346">
       <c r="A346" t="n">
-        <v>122254651</v>
+        <v>122254307</v>
       </c>
       <c r="B346" t="n">
-        <v>56290</v>
+        <v>56285</v>
       </c>
       <c r="C346" t="inlineStr">
         <is>
@@ -47304,16 +47304,16 @@
         </is>
       </c>
       <c r="E346" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
@@ -47337,10 +47337,10 @@
         </is>
       </c>
       <c r="Q346" t="n">
-        <v>586425</v>
+        <v>586477</v>
       </c>
       <c r="R346" t="n">
-        <v>6311113</v>
+        <v>6311186</v>
       </c>
       <c r="S346" t="n">
         <v>5</v>
@@ -47372,7 +47372,7 @@
       </c>
       <c r="Z346" t="inlineStr">
         <is>
-          <t>22:35</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AA346" t="inlineStr">
@@ -47382,7 +47382,7 @@
       </c>
       <c r="AB346" t="inlineStr">
         <is>
-          <t>22:36</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AC346" t="inlineStr">
@@ -47427,10 +47427,10 @@
     </row>
     <row r="347">
       <c r="A347" t="n">
-        <v>122254654</v>
+        <v>122254314</v>
       </c>
       <c r="B347" t="n">
-        <v>56290</v>
+        <v>56285</v>
       </c>
       <c r="C347" t="inlineStr">
         <is>
@@ -47443,16 +47443,16 @@
         </is>
       </c>
       <c r="E347" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I347" t="inlineStr">
@@ -47476,10 +47476,10 @@
         </is>
       </c>
       <c r="Q347" t="n">
-        <v>586467</v>
+        <v>586443</v>
       </c>
       <c r="R347" t="n">
-        <v>6311178</v>
+        <v>6311164</v>
       </c>
       <c r="S347" t="n">
         <v>5</v>
@@ -47511,7 +47511,7 @@
       </c>
       <c r="Z347" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AA347" t="inlineStr">
@@ -47521,7 +47521,7 @@
       </c>
       <c r="AB347" t="inlineStr">
         <is>
-          <t>22:33</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AC347" t="inlineStr">
@@ -47566,10 +47566,10 @@
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>122254632</v>
+        <v>122254309</v>
       </c>
       <c r="B348" t="n">
-        <v>56290</v>
+        <v>56285</v>
       </c>
       <c r="C348" t="inlineStr">
         <is>
@@ -47582,16 +47582,16 @@
         </is>
       </c>
       <c r="E348" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I348" t="inlineStr">
@@ -47615,10 +47615,10 @@
         </is>
       </c>
       <c r="Q348" t="n">
-        <v>586374</v>
+        <v>586456</v>
       </c>
       <c r="R348" t="n">
-        <v>6311140</v>
+        <v>6311158</v>
       </c>
       <c r="S348" t="n">
         <v>5</v>
@@ -47650,7 +47650,7 @@
       </c>
       <c r="Z348" t="inlineStr">
         <is>
-          <t>22:46</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AA348" t="inlineStr">
@@ -47660,7 +47660,7 @@
       </c>
       <c r="AB348" t="inlineStr">
         <is>
-          <t>22:47</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AC348" t="inlineStr">
@@ -47705,10 +47705,10 @@
     </row>
     <row r="349">
       <c r="A349" t="n">
-        <v>122254646</v>
+        <v>122254862</v>
       </c>
       <c r="B349" t="n">
-        <v>56290</v>
+        <v>56288</v>
       </c>
       <c r="C349" t="inlineStr">
         <is>
@@ -47721,16 +47721,16 @@
         </is>
       </c>
       <c r="E349" t="n">
-        <v>205995</v>
+        <v>100111</v>
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I349" t="inlineStr">
@@ -47754,10 +47754,10 @@
         </is>
       </c>
       <c r="Q349" t="n">
-        <v>586422</v>
+        <v>586288</v>
       </c>
       <c r="R349" t="n">
-        <v>6311111</v>
+        <v>6311100</v>
       </c>
       <c r="S349" t="n">
         <v>5</v>
@@ -47789,7 +47789,7 @@
       </c>
       <c r="Z349" t="inlineStr">
         <is>
-          <t>22:36</t>
+          <t>22:55</t>
         </is>
       </c>
       <c r="AA349" t="inlineStr">
@@ -47799,7 +47799,7 @@
       </c>
       <c r="AB349" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>22:56</t>
         </is>
       </c>
       <c r="AC349" t="inlineStr">
@@ -48817,7 +48817,7 @@
     </row>
     <row r="357">
       <c r="A357" t="n">
-        <v>122254475</v>
+        <v>122254511</v>
       </c>
       <c r="B357" t="n">
         <v>56271</v>
@@ -48866,10 +48866,10 @@
         </is>
       </c>
       <c r="Q357" t="n">
-        <v>586420</v>
+        <v>586374</v>
       </c>
       <c r="R357" t="n">
-        <v>6311166</v>
+        <v>6311139</v>
       </c>
       <c r="S357" t="n">
         <v>5</v>
@@ -48901,7 +48901,7 @@
       </c>
       <c r="Z357" t="inlineStr">
         <is>
-          <t>23:23</t>
+          <t>22:46</t>
         </is>
       </c>
       <c r="AA357" t="inlineStr">
@@ -48911,7 +48911,7 @@
       </c>
       <c r="AB357" t="inlineStr">
         <is>
-          <t>23:24</t>
+          <t>22:47</t>
         </is>
       </c>
       <c r="AC357" t="inlineStr">
@@ -48956,7 +48956,7 @@
     </row>
     <row r="358">
       <c r="A358" t="n">
-        <v>122254957</v>
+        <v>122254956</v>
       </c>
       <c r="B358" t="n">
         <v>56278</v>
@@ -49005,10 +49005,10 @@
         </is>
       </c>
       <c r="Q358" t="n">
-        <v>586444</v>
+        <v>586441</v>
       </c>
       <c r="R358" t="n">
-        <v>6311160</v>
+        <v>6311152</v>
       </c>
       <c r="S358" t="n">
         <v>5</v>
@@ -49040,7 +49040,7 @@
       </c>
       <c r="Z358" t="inlineStr">
         <is>
-          <t>23:24</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AA358" t="inlineStr">
@@ -49050,7 +49050,7 @@
       </c>
       <c r="AB358" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AC358" t="inlineStr">
@@ -49095,7 +49095,7 @@
     </row>
     <row r="359">
       <c r="A359" t="n">
-        <v>122254511</v>
+        <v>122254475</v>
       </c>
       <c r="B359" t="n">
         <v>56271</v>
@@ -49144,10 +49144,10 @@
         </is>
       </c>
       <c r="Q359" t="n">
-        <v>586374</v>
+        <v>586420</v>
       </c>
       <c r="R359" t="n">
-        <v>6311139</v>
+        <v>6311166</v>
       </c>
       <c r="S359" t="n">
         <v>5</v>
@@ -49179,7 +49179,7 @@
       </c>
       <c r="Z359" t="inlineStr">
         <is>
-          <t>22:46</t>
+          <t>23:23</t>
         </is>
       </c>
       <c r="AA359" t="inlineStr">
@@ -49189,7 +49189,7 @@
       </c>
       <c r="AB359" t="inlineStr">
         <is>
-          <t>22:47</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="AC359" t="inlineStr">
@@ -49234,7 +49234,7 @@
     </row>
     <row r="360">
       <c r="A360" t="n">
-        <v>122254956</v>
+        <v>122254957</v>
       </c>
       <c r="B360" t="n">
         <v>56278</v>
@@ -49283,10 +49283,10 @@
         </is>
       </c>
       <c r="Q360" t="n">
-        <v>586441</v>
+        <v>586444</v>
       </c>
       <c r="R360" t="n">
-        <v>6311152</v>
+        <v>6311160</v>
       </c>
       <c r="S360" t="n">
         <v>5</v>
@@ -49318,17 +49318,17 @@
       </c>
       <c r="Z360" t="inlineStr">
         <is>
+          <t>23:24</t>
+        </is>
+      </c>
+      <c r="AA360" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AB360" t="inlineStr">
+        <is>
           <t>23:25</t>
-        </is>
-      </c>
-      <c r="AA360" t="inlineStr">
-        <is>
-          <t>2024-06-26</t>
-        </is>
-      </c>
-      <c r="AB360" t="inlineStr">
-        <is>
-          <t>23:26</t>
         </is>
       </c>
       <c r="AC360" t="inlineStr">

--- a/artfynd/A 36363-2024 artfynd.xlsx
+++ b/artfynd/A 36363-2024 artfynd.xlsx
@@ -37836,10 +37836,10 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>122254855</v>
+        <v>122254371</v>
       </c>
       <c r="B278" t="n">
-        <v>56288</v>
+        <v>56285</v>
       </c>
       <c r="C278" t="inlineStr">
         <is>
@@ -37852,16 +37852,16 @@
         </is>
       </c>
       <c r="E278" t="n">
-        <v>100111</v>
+        <v>100092</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
@@ -37885,10 +37885,10 @@
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>586330</v>
+        <v>586308</v>
       </c>
       <c r="R278" t="n">
-        <v>6311120</v>
+        <v>6311132</v>
       </c>
       <c r="S278" t="n">
         <v>5</v>
@@ -37920,7 +37920,7 @@
       </c>
       <c r="Z278" t="inlineStr">
         <is>
-          <t>22:57</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AA278" t="inlineStr">
@@ -37930,7 +37930,7 @@
       </c>
       <c r="AB278" t="inlineStr">
         <is>
-          <t>22:58</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AC278" t="inlineStr">
@@ -37975,10 +37975,10 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>122254371</v>
+        <v>122254476</v>
       </c>
       <c r="B279" t="n">
-        <v>56285</v>
+        <v>56271</v>
       </c>
       <c r="C279" t="inlineStr">
         <is>
@@ -37987,20 +37987,20 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E279" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
@@ -38024,10 +38024,10 @@
         </is>
       </c>
       <c r="Q279" t="n">
-        <v>586308</v>
+        <v>586418</v>
       </c>
       <c r="R279" t="n">
-        <v>6311132</v>
+        <v>6311167</v>
       </c>
       <c r="S279" t="n">
         <v>5</v>
@@ -38059,7 +38059,7 @@
       </c>
       <c r="Z279" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>23:23</t>
         </is>
       </c>
       <c r="AA279" t="inlineStr">
@@ -38069,7 +38069,7 @@
       </c>
       <c r="AB279" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="AC279" t="inlineStr">
@@ -38114,10 +38114,10 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>122254476</v>
+        <v>122254635</v>
       </c>
       <c r="B280" t="n">
-        <v>56271</v>
+        <v>56290</v>
       </c>
       <c r="C280" t="inlineStr">
         <is>
@@ -38126,20 +38126,20 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E280" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
@@ -38163,10 +38163,10 @@
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>586418</v>
+        <v>586417</v>
       </c>
       <c r="R280" t="n">
-        <v>6311167</v>
+        <v>6311145</v>
       </c>
       <c r="S280" t="n">
         <v>5</v>
@@ -38198,7 +38198,7 @@
       </c>
       <c r="Z280" t="inlineStr">
         <is>
-          <t>23:23</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AA280" t="inlineStr">
@@ -38208,7 +38208,7 @@
       </c>
       <c r="AB280" t="inlineStr">
         <is>
-          <t>23:24</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AC280" t="inlineStr">
@@ -38253,7 +38253,7 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>122254635</v>
+        <v>122254644</v>
       </c>
       <c r="B281" t="n">
         <v>56290</v>
@@ -38302,10 +38302,10 @@
         </is>
       </c>
       <c r="Q281" t="n">
-        <v>586417</v>
+        <v>586429</v>
       </c>
       <c r="R281" t="n">
-        <v>6311145</v>
+        <v>6311115</v>
       </c>
       <c r="S281" t="n">
         <v>5</v>
@@ -38337,7 +38337,7 @@
       </c>
       <c r="Z281" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>22:36</t>
         </is>
       </c>
       <c r="AA281" t="inlineStr">
@@ -38347,7 +38347,7 @@
       </c>
       <c r="AB281" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AC281" t="inlineStr">
@@ -38392,7 +38392,7 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>122254644</v>
+        <v>122254652</v>
       </c>
       <c r="B282" t="n">
         <v>56290</v>
@@ -38441,10 +38441,10 @@
         </is>
       </c>
       <c r="Q282" t="n">
-        <v>586429</v>
+        <v>586432</v>
       </c>
       <c r="R282" t="n">
-        <v>6311115</v>
+        <v>6311118</v>
       </c>
       <c r="S282" t="n">
         <v>5</v>
@@ -38476,7 +38476,7 @@
       </c>
       <c r="Z282" t="inlineStr">
         <is>
-          <t>22:36</t>
+          <t>22:34</t>
         </is>
       </c>
       <c r="AA282" t="inlineStr">
@@ -38486,7 +38486,7 @@
       </c>
       <c r="AB282" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="AC282" t="inlineStr">
@@ -38531,7 +38531,7 @@
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>122254652</v>
+        <v>122254587</v>
       </c>
       <c r="B283" t="n">
         <v>56290</v>
@@ -38580,10 +38580,10 @@
         </is>
       </c>
       <c r="Q283" t="n">
-        <v>586432</v>
+        <v>586443</v>
       </c>
       <c r="R283" t="n">
-        <v>6311118</v>
+        <v>6311163</v>
       </c>
       <c r="S283" t="n">
         <v>5</v>
@@ -38615,7 +38615,7 @@
       </c>
       <c r="Z283" t="inlineStr">
         <is>
-          <t>22:34</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AA283" t="inlineStr">
@@ -38625,7 +38625,7 @@
       </c>
       <c r="AB283" t="inlineStr">
         <is>
-          <t>22:35</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AC283" t="inlineStr">
@@ -38670,10 +38670,10 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>122254587</v>
+        <v>122254855</v>
       </c>
       <c r="B284" t="n">
-        <v>56290</v>
+        <v>56288</v>
       </c>
       <c r="C284" t="inlineStr">
         <is>
@@ -38686,16 +38686,16 @@
         </is>
       </c>
       <c r="E284" t="n">
-        <v>205995</v>
+        <v>100111</v>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
@@ -38719,10 +38719,10 @@
         </is>
       </c>
       <c r="Q284" t="n">
-        <v>586443</v>
+        <v>586330</v>
       </c>
       <c r="R284" t="n">
-        <v>6311163</v>
+        <v>6311120</v>
       </c>
       <c r="S284" t="n">
         <v>5</v>
@@ -38754,7 +38754,7 @@
       </c>
       <c r="Z284" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>22:57</t>
         </is>
       </c>
       <c r="AA284" t="inlineStr">
@@ -38764,7 +38764,7 @@
       </c>
       <c r="AB284" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>22:58</t>
         </is>
       </c>
       <c r="AC284" t="inlineStr">
@@ -41172,10 +41172,10 @@
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>122254474</v>
+        <v>122254856</v>
       </c>
       <c r="B302" t="n">
-        <v>56271</v>
+        <v>56288</v>
       </c>
       <c r="C302" t="inlineStr">
         <is>
@@ -41184,20 +41184,20 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E302" t="n">
-        <v>205998</v>
+        <v>100111</v>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
@@ -41221,10 +41221,10 @@
         </is>
       </c>
       <c r="Q302" t="n">
-        <v>586443</v>
+        <v>586327</v>
       </c>
       <c r="R302" t="n">
-        <v>6311164</v>
+        <v>6311118</v>
       </c>
       <c r="S302" t="n">
         <v>5</v>
@@ -41256,7 +41256,7 @@
       </c>
       <c r="Z302" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>22:57</t>
         </is>
       </c>
       <c r="AA302" t="inlineStr">
@@ -41266,7 +41266,7 @@
       </c>
       <c r="AB302" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>22:58</t>
         </is>
       </c>
       <c r="AC302" t="inlineStr">
@@ -41311,10 +41311,10 @@
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>122254856</v>
+        <v>122254474</v>
       </c>
       <c r="B303" t="n">
-        <v>56288</v>
+        <v>56271</v>
       </c>
       <c r="C303" t="inlineStr">
         <is>
@@ -41323,20 +41323,20 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E303" t="n">
-        <v>100111</v>
+        <v>205998</v>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
@@ -41360,10 +41360,10 @@
         </is>
       </c>
       <c r="Q303" t="n">
-        <v>586327</v>
+        <v>586443</v>
       </c>
       <c r="R303" t="n">
-        <v>6311118</v>
+        <v>6311164</v>
       </c>
       <c r="S303" t="n">
         <v>5</v>
@@ -41395,7 +41395,7 @@
       </c>
       <c r="Z303" t="inlineStr">
         <is>
-          <t>22:57</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AA303" t="inlineStr">
@@ -41405,7 +41405,7 @@
       </c>
       <c r="AB303" t="inlineStr">
         <is>
-          <t>22:58</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AC303" t="inlineStr">
@@ -43118,10 +43118,10 @@
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>122254503</v>
+        <v>122254343</v>
       </c>
       <c r="B316" t="n">
-        <v>56271</v>
+        <v>56285</v>
       </c>
       <c r="C316" t="inlineStr">
         <is>
@@ -43130,20 +43130,20 @@
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E316" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
@@ -43167,10 +43167,10 @@
         </is>
       </c>
       <c r="Q316" t="n">
-        <v>586313</v>
+        <v>586388</v>
       </c>
       <c r="R316" t="n">
-        <v>6311124</v>
+        <v>6311142</v>
       </c>
       <c r="S316" t="n">
         <v>5</v>
@@ -43202,7 +43202,7 @@
       </c>
       <c r="Z316" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA316" t="inlineStr">
@@ -43212,7 +43212,7 @@
       </c>
       <c r="AB316" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AC316" t="inlineStr">
@@ -43257,10 +43257,10 @@
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>122254655</v>
+        <v>122254373</v>
       </c>
       <c r="B317" t="n">
-        <v>56290</v>
+        <v>56285</v>
       </c>
       <c r="C317" t="inlineStr">
         <is>
@@ -43273,16 +43273,16 @@
         </is>
       </c>
       <c r="E317" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
@@ -43306,10 +43306,10 @@
         </is>
       </c>
       <c r="Q317" t="n">
-        <v>586475</v>
+        <v>586307</v>
       </c>
       <c r="R317" t="n">
-        <v>6311187</v>
+        <v>6311133</v>
       </c>
       <c r="S317" t="n">
         <v>5</v>
@@ -43341,7 +43341,7 @@
       </c>
       <c r="Z317" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>22:49</t>
         </is>
       </c>
       <c r="AA317" t="inlineStr">
@@ -43351,7 +43351,7 @@
       </c>
       <c r="AB317" t="inlineStr">
         <is>
-          <t>22:33</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AC317" t="inlineStr">
@@ -43396,10 +43396,10 @@
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>122254959</v>
+        <v>122254503</v>
       </c>
       <c r="B318" t="n">
-        <v>56278</v>
+        <v>56271</v>
       </c>
       <c r="C318" t="inlineStr">
         <is>
@@ -43408,20 +43408,20 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E318" t="n">
-        <v>205992</v>
+        <v>205998</v>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
@@ -43445,10 +43445,10 @@
         </is>
       </c>
       <c r="Q318" t="n">
-        <v>586370</v>
+        <v>586313</v>
       </c>
       <c r="R318" t="n">
-        <v>6311139</v>
+        <v>6311124</v>
       </c>
       <c r="S318" t="n">
         <v>5</v>
@@ -43480,7 +43480,7 @@
       </c>
       <c r="Z318" t="inlineStr">
         <is>
-          <t>22:59</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AA318" t="inlineStr">
@@ -43490,7 +43490,7 @@
       </c>
       <c r="AB318" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AC318" t="inlineStr">
@@ -43535,7 +43535,7 @@
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>122254585</v>
+        <v>122254655</v>
       </c>
       <c r="B319" t="n">
         <v>56290</v>
@@ -43584,10 +43584,10 @@
         </is>
       </c>
       <c r="Q319" t="n">
-        <v>586455</v>
+        <v>586475</v>
       </c>
       <c r="R319" t="n">
-        <v>6311156</v>
+        <v>6311187</v>
       </c>
       <c r="S319" t="n">
         <v>5</v>
@@ -43619,7 +43619,7 @@
       </c>
       <c r="Z319" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AA319" t="inlineStr">
@@ -43629,7 +43629,7 @@
       </c>
       <c r="AB319" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="AC319" t="inlineStr">
@@ -43674,10 +43674,10 @@
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>122254473</v>
+        <v>122254959</v>
       </c>
       <c r="B320" t="n">
-        <v>56271</v>
+        <v>56278</v>
       </c>
       <c r="C320" t="inlineStr">
         <is>
@@ -43686,20 +43686,20 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E320" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
@@ -43723,10 +43723,10 @@
         </is>
       </c>
       <c r="Q320" t="n">
-        <v>586450</v>
+        <v>586370</v>
       </c>
       <c r="R320" t="n">
-        <v>6311152</v>
+        <v>6311139</v>
       </c>
       <c r="S320" t="n">
         <v>5</v>
@@ -43758,7 +43758,7 @@
       </c>
       <c r="Z320" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>22:59</t>
         </is>
       </c>
       <c r="AA320" t="inlineStr">
@@ -43768,7 +43768,7 @@
       </c>
       <c r="AB320" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AC320" t="inlineStr">
@@ -43813,7 +43813,7 @@
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>122254607</v>
+        <v>122254585</v>
       </c>
       <c r="B321" t="n">
         <v>56290</v>
@@ -43862,10 +43862,10 @@
         </is>
       </c>
       <c r="Q321" t="n">
-        <v>586415</v>
+        <v>586455</v>
       </c>
       <c r="R321" t="n">
-        <v>6311149</v>
+        <v>6311156</v>
       </c>
       <c r="S321" t="n">
         <v>5</v>
@@ -43897,7 +43897,7 @@
       </c>
       <c r="Z321" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AA321" t="inlineStr">
@@ -43907,7 +43907,7 @@
       </c>
       <c r="AB321" t="inlineStr">
         <is>
-          <t>23:03</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AC321" t="inlineStr">
@@ -43952,10 +43952,10 @@
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>122254953</v>
+        <v>122254473</v>
       </c>
       <c r="B322" t="n">
-        <v>56278</v>
+        <v>56271</v>
       </c>
       <c r="C322" t="inlineStr">
         <is>
@@ -43964,20 +43964,20 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E322" t="n">
-        <v>205992</v>
+        <v>205998</v>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
@@ -44001,10 +44001,10 @@
         </is>
       </c>
       <c r="Q322" t="n">
-        <v>586449</v>
+        <v>586450</v>
       </c>
       <c r="R322" t="n">
-        <v>6311155</v>
+        <v>6311152</v>
       </c>
       <c r="S322" t="n">
         <v>5</v>
@@ -44091,10 +44091,10 @@
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>122254343</v>
+        <v>122254607</v>
       </c>
       <c r="B323" t="n">
-        <v>56285</v>
+        <v>56290</v>
       </c>
       <c r="C323" t="inlineStr">
         <is>
@@ -44107,16 +44107,16 @@
         </is>
       </c>
       <c r="E323" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
@@ -44140,10 +44140,10 @@
         </is>
       </c>
       <c r="Q323" t="n">
-        <v>586388</v>
+        <v>586415</v>
       </c>
       <c r="R323" t="n">
-        <v>6311142</v>
+        <v>6311149</v>
       </c>
       <c r="S323" t="n">
         <v>5</v>
@@ -44175,7 +44175,7 @@
       </c>
       <c r="Z323" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AA323" t="inlineStr">
@@ -44185,7 +44185,7 @@
       </c>
       <c r="AB323" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>23:03</t>
         </is>
       </c>
       <c r="AC323" t="inlineStr">
@@ -44230,10 +44230,10 @@
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>122254373</v>
+        <v>122254953</v>
       </c>
       <c r="B324" t="n">
-        <v>56285</v>
+        <v>56278</v>
       </c>
       <c r="C324" t="inlineStr">
         <is>
@@ -44246,16 +44246,16 @@
         </is>
       </c>
       <c r="E324" t="n">
-        <v>100092</v>
+        <v>205992</v>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
@@ -44279,10 +44279,10 @@
         </is>
       </c>
       <c r="Q324" t="n">
-        <v>586307</v>
+        <v>586449</v>
       </c>
       <c r="R324" t="n">
-        <v>6311133</v>
+        <v>6311155</v>
       </c>
       <c r="S324" t="n">
         <v>5</v>
@@ -44314,7 +44314,7 @@
       </c>
       <c r="Z324" t="inlineStr">
         <is>
-          <t>22:49</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA324" t="inlineStr">
@@ -44324,7 +44324,7 @@
       </c>
       <c r="AB324" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC324" t="inlineStr">
@@ -45203,10 +45203,10 @@
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>122254857</v>
+        <v>122254954</v>
       </c>
       <c r="B331" t="n">
-        <v>56288</v>
+        <v>56278</v>
       </c>
       <c r="C331" t="inlineStr">
         <is>
@@ -45219,16 +45219,16 @@
         </is>
       </c>
       <c r="E331" t="n">
-        <v>100111</v>
+        <v>205992</v>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I331" t="inlineStr">
@@ -45252,10 +45252,10 @@
         </is>
       </c>
       <c r="Q331" t="n">
-        <v>586317</v>
+        <v>586442</v>
       </c>
       <c r="R331" t="n">
-        <v>6311115</v>
+        <v>6311152</v>
       </c>
       <c r="S331" t="n">
         <v>5</v>
@@ -45287,7 +45287,7 @@
       </c>
       <c r="Z331" t="inlineStr">
         <is>
-          <t>22:57</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AA331" t="inlineStr">
@@ -45297,7 +45297,7 @@
       </c>
       <c r="AB331" t="inlineStr">
         <is>
-          <t>22:58</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AC331" t="inlineStr">
@@ -45342,7 +45342,7 @@
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>122254877</v>
+        <v>122254857</v>
       </c>
       <c r="B332" t="n">
         <v>56288</v>
@@ -45391,10 +45391,10 @@
         </is>
       </c>
       <c r="Q332" t="n">
-        <v>586276</v>
+        <v>586317</v>
       </c>
       <c r="R332" t="n">
-        <v>6311100</v>
+        <v>6311115</v>
       </c>
       <c r="S332" t="n">
         <v>5</v>
@@ -45426,7 +45426,7 @@
       </c>
       <c r="Z332" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>22:57</t>
         </is>
       </c>
       <c r="AA332" t="inlineStr">
@@ -45436,7 +45436,7 @@
       </c>
       <c r="AB332" t="inlineStr">
         <is>
-          <t>22:52</t>
+          <t>22:58</t>
         </is>
       </c>
       <c r="AC332" t="inlineStr">
@@ -45481,10 +45481,10 @@
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>122254954</v>
+        <v>122254877</v>
       </c>
       <c r="B333" t="n">
-        <v>56278</v>
+        <v>56288</v>
       </c>
       <c r="C333" t="inlineStr">
         <is>
@@ -45497,16 +45497,16 @@
         </is>
       </c>
       <c r="E333" t="n">
-        <v>205992</v>
+        <v>100111</v>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
@@ -45530,10 +45530,10 @@
         </is>
       </c>
       <c r="Q333" t="n">
-        <v>586442</v>
+        <v>586276</v>
       </c>
       <c r="R333" t="n">
-        <v>6311152</v>
+        <v>6311100</v>
       </c>
       <c r="S333" t="n">
         <v>5</v>
@@ -45565,7 +45565,7 @@
       </c>
       <c r="Z333" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AA333" t="inlineStr">
@@ -45575,7 +45575,7 @@
       </c>
       <c r="AB333" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>22:52</t>
         </is>
       </c>
       <c r="AC333" t="inlineStr">
@@ -45898,10 +45898,10 @@
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>122254499</v>
+        <v>122254649</v>
       </c>
       <c r="B336" t="n">
-        <v>56271</v>
+        <v>56290</v>
       </c>
       <c r="C336" t="inlineStr">
         <is>
@@ -45910,20 +45910,20 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E336" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
@@ -45947,10 +45947,10 @@
         </is>
       </c>
       <c r="Q336" t="n">
-        <v>586392</v>
+        <v>586422</v>
       </c>
       <c r="R336" t="n">
-        <v>6311147</v>
+        <v>6311100</v>
       </c>
       <c r="S336" t="n">
         <v>5</v>
@@ -45982,7 +45982,7 @@
       </c>
       <c r="Z336" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="AA336" t="inlineStr">
@@ -45992,7 +45992,7 @@
       </c>
       <c r="AB336" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>22:36</t>
         </is>
       </c>
       <c r="AC336" t="inlineStr">
@@ -46037,7 +46037,7 @@
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>122254649</v>
+        <v>122254608</v>
       </c>
       <c r="B337" t="n">
         <v>56290</v>
@@ -46086,10 +46086,10 @@
         </is>
       </c>
       <c r="Q337" t="n">
-        <v>586422</v>
+        <v>586393</v>
       </c>
       <c r="R337" t="n">
-        <v>6311100</v>
+        <v>6311147</v>
       </c>
       <c r="S337" t="n">
         <v>5</v>
@@ -46121,7 +46121,7 @@
       </c>
       <c r="Z337" t="inlineStr">
         <is>
-          <t>22:35</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AA337" t="inlineStr">
@@ -46131,7 +46131,7 @@
       </c>
       <c r="AB337" t="inlineStr">
         <is>
-          <t>22:36</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AC337" t="inlineStr">
@@ -46176,10 +46176,10 @@
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>122254608</v>
+        <v>122254513</v>
       </c>
       <c r="B338" t="n">
-        <v>56290</v>
+        <v>56271</v>
       </c>
       <c r="C338" t="inlineStr">
         <is>
@@ -46188,20 +46188,20 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E338" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
@@ -46225,10 +46225,10 @@
         </is>
       </c>
       <c r="Q338" t="n">
-        <v>586393</v>
+        <v>586396</v>
       </c>
       <c r="R338" t="n">
-        <v>6311147</v>
+        <v>6311146</v>
       </c>
       <c r="S338" t="n">
         <v>5</v>
@@ -46260,7 +46260,7 @@
       </c>
       <c r="Z338" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AA338" t="inlineStr">
@@ -46270,7 +46270,7 @@
       </c>
       <c r="AB338" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AC338" t="inlineStr">
@@ -46315,7 +46315,7 @@
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>122254513</v>
+        <v>122254499</v>
       </c>
       <c r="B339" t="n">
         <v>56271</v>
@@ -46364,10 +46364,10 @@
         </is>
       </c>
       <c r="Q339" t="n">
-        <v>586396</v>
+        <v>586392</v>
       </c>
       <c r="R339" t="n">
-        <v>6311146</v>
+        <v>6311147</v>
       </c>
       <c r="S339" t="n">
         <v>5</v>
@@ -46399,7 +46399,7 @@
       </c>
       <c r="Z339" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AA339" t="inlineStr">
@@ -46409,7 +46409,7 @@
       </c>
       <c r="AB339" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AC339" t="inlineStr">
@@ -48817,7 +48817,7 @@
     </row>
     <row r="357">
       <c r="A357" t="n">
-        <v>122254511</v>
+        <v>122254475</v>
       </c>
       <c r="B357" t="n">
         <v>56271</v>
@@ -48866,10 +48866,10 @@
         </is>
       </c>
       <c r="Q357" t="n">
-        <v>586374</v>
+        <v>586420</v>
       </c>
       <c r="R357" t="n">
-        <v>6311139</v>
+        <v>6311166</v>
       </c>
       <c r="S357" t="n">
         <v>5</v>
@@ -48901,7 +48901,7 @@
       </c>
       <c r="Z357" t="inlineStr">
         <is>
-          <t>22:46</t>
+          <t>23:23</t>
         </is>
       </c>
       <c r="AA357" t="inlineStr">
@@ -48911,7 +48911,7 @@
       </c>
       <c r="AB357" t="inlineStr">
         <is>
-          <t>22:47</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="AC357" t="inlineStr">
@@ -48956,7 +48956,7 @@
     </row>
     <row r="358">
       <c r="A358" t="n">
-        <v>122254956</v>
+        <v>122254957</v>
       </c>
       <c r="B358" t="n">
         <v>56278</v>
@@ -49005,10 +49005,10 @@
         </is>
       </c>
       <c r="Q358" t="n">
-        <v>586441</v>
+        <v>586444</v>
       </c>
       <c r="R358" t="n">
-        <v>6311152</v>
+        <v>6311160</v>
       </c>
       <c r="S358" t="n">
         <v>5</v>
@@ -49040,17 +49040,17 @@
       </c>
       <c r="Z358" t="inlineStr">
         <is>
+          <t>23:24</t>
+        </is>
+      </c>
+      <c r="AA358" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AB358" t="inlineStr">
+        <is>
           <t>23:25</t>
-        </is>
-      </c>
-      <c r="AA358" t="inlineStr">
-        <is>
-          <t>2024-06-26</t>
-        </is>
-      </c>
-      <c r="AB358" t="inlineStr">
-        <is>
-          <t>23:26</t>
         </is>
       </c>
       <c r="AC358" t="inlineStr">
@@ -49095,7 +49095,7 @@
     </row>
     <row r="359">
       <c r="A359" t="n">
-        <v>122254475</v>
+        <v>122254511</v>
       </c>
       <c r="B359" t="n">
         <v>56271</v>
@@ -49144,10 +49144,10 @@
         </is>
       </c>
       <c r="Q359" t="n">
-        <v>586420</v>
+        <v>586374</v>
       </c>
       <c r="R359" t="n">
-        <v>6311166</v>
+        <v>6311139</v>
       </c>
       <c r="S359" t="n">
         <v>5</v>
@@ -49179,7 +49179,7 @@
       </c>
       <c r="Z359" t="inlineStr">
         <is>
-          <t>23:23</t>
+          <t>22:46</t>
         </is>
       </c>
       <c r="AA359" t="inlineStr">
@@ -49189,7 +49189,7 @@
       </c>
       <c r="AB359" t="inlineStr">
         <is>
-          <t>23:24</t>
+          <t>22:47</t>
         </is>
       </c>
       <c r="AC359" t="inlineStr">
@@ -49234,7 +49234,7 @@
     </row>
     <row r="360">
       <c r="A360" t="n">
-        <v>122254957</v>
+        <v>122254956</v>
       </c>
       <c r="B360" t="n">
         <v>56278</v>
@@ -49283,10 +49283,10 @@
         </is>
       </c>
       <c r="Q360" t="n">
-        <v>586444</v>
+        <v>586441</v>
       </c>
       <c r="R360" t="n">
-        <v>6311160</v>
+        <v>6311152</v>
       </c>
       <c r="S360" t="n">
         <v>5</v>
@@ -49318,7 +49318,7 @@
       </c>
       <c r="Z360" t="inlineStr">
         <is>
-          <t>23:24</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AA360" t="inlineStr">
@@ -49328,7 +49328,7 @@
       </c>
       <c r="AB360" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AC360" t="inlineStr">
@@ -50624,10 +50624,10 @@
     </row>
     <row r="370">
       <c r="A370" t="n">
-        <v>122254365</v>
+        <v>122254951</v>
       </c>
       <c r="B370" t="n">
-        <v>56285</v>
+        <v>56278</v>
       </c>
       <c r="C370" t="inlineStr">
         <is>
@@ -50640,16 +50640,16 @@
         </is>
       </c>
       <c r="E370" t="n">
-        <v>100092</v>
+        <v>205992</v>
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I370" t="inlineStr">
@@ -50673,10 +50673,10 @@
         </is>
       </c>
       <c r="Q370" t="n">
-        <v>586276</v>
+        <v>586459</v>
       </c>
       <c r="R370" t="n">
-        <v>6311100</v>
+        <v>6311154</v>
       </c>
       <c r="S370" t="n">
         <v>5</v>
@@ -50708,7 +50708,7 @@
       </c>
       <c r="Z370" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AA370" t="inlineStr">
@@ -50718,7 +50718,7 @@
       </c>
       <c r="AB370" t="inlineStr">
         <is>
-          <t>22:52</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AC370" t="inlineStr">
@@ -50763,10 +50763,10 @@
     </row>
     <row r="371">
       <c r="A371" t="n">
-        <v>122254315</v>
+        <v>122254637</v>
       </c>
       <c r="B371" t="n">
-        <v>56285</v>
+        <v>56290</v>
       </c>
       <c r="C371" t="inlineStr">
         <is>
@@ -50779,16 +50779,16 @@
         </is>
       </c>
       <c r="E371" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I371" t="inlineStr">
@@ -50812,10 +50812,10 @@
         </is>
       </c>
       <c r="Q371" t="n">
-        <v>586441</v>
+        <v>586408</v>
       </c>
       <c r="R371" t="n">
-        <v>6311155</v>
+        <v>6311124</v>
       </c>
       <c r="S371" t="n">
         <v>5</v>
@@ -50847,7 +50847,7 @@
       </c>
       <c r="Z371" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>22:43</t>
         </is>
       </c>
       <c r="AA371" t="inlineStr">
@@ -50857,7 +50857,7 @@
       </c>
       <c r="AB371" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AC371" t="inlineStr">
@@ -50902,10 +50902,10 @@
     </row>
     <row r="372">
       <c r="A372" t="n">
-        <v>122254951</v>
+        <v>122254512</v>
       </c>
       <c r="B372" t="n">
-        <v>56278</v>
+        <v>56271</v>
       </c>
       <c r="C372" t="inlineStr">
         <is>
@@ -50914,20 +50914,20 @@
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E372" t="n">
-        <v>205992</v>
+        <v>205998</v>
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I372" t="inlineStr">
@@ -50951,10 +50951,10 @@
         </is>
       </c>
       <c r="Q372" t="n">
-        <v>586459</v>
+        <v>586379</v>
       </c>
       <c r="R372" t="n">
-        <v>6311154</v>
+        <v>6311136</v>
       </c>
       <c r="S372" t="n">
         <v>5</v>
@@ -50986,7 +50986,7 @@
       </c>
       <c r="Z372" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AA372" t="inlineStr">
@@ -50996,7 +50996,7 @@
       </c>
       <c r="AB372" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>22:46</t>
         </is>
       </c>
       <c r="AC372" t="inlineStr">
@@ -51041,7 +51041,7 @@
     </row>
     <row r="373">
       <c r="A373" t="n">
-        <v>122254637</v>
+        <v>122254611</v>
       </c>
       <c r="B373" t="n">
         <v>56290</v>
@@ -51090,10 +51090,10 @@
         </is>
       </c>
       <c r="Q373" t="n">
-        <v>586408</v>
+        <v>586370</v>
       </c>
       <c r="R373" t="n">
-        <v>6311124</v>
+        <v>6311139</v>
       </c>
       <c r="S373" t="n">
         <v>5</v>
@@ -51125,7 +51125,7 @@
       </c>
       <c r="Z373" t="inlineStr">
         <is>
-          <t>22:43</t>
+          <t>22:59</t>
         </is>
       </c>
       <c r="AA373" t="inlineStr">
@@ -51135,7 +51135,7 @@
       </c>
       <c r="AB373" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AC373" t="inlineStr">
@@ -51180,10 +51180,10 @@
     </row>
     <row r="374">
       <c r="A374" t="n">
-        <v>122254512</v>
+        <v>122254365</v>
       </c>
       <c r="B374" t="n">
-        <v>56271</v>
+        <v>56285</v>
       </c>
       <c r="C374" t="inlineStr">
         <is>
@@ -51192,20 +51192,20 @@
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E374" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I374" t="inlineStr">
@@ -51229,10 +51229,10 @@
         </is>
       </c>
       <c r="Q374" t="n">
-        <v>586379</v>
+        <v>586276</v>
       </c>
       <c r="R374" t="n">
-        <v>6311136</v>
+        <v>6311100</v>
       </c>
       <c r="S374" t="n">
         <v>5</v>
@@ -51264,7 +51264,7 @@
       </c>
       <c r="Z374" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AA374" t="inlineStr">
@@ -51274,7 +51274,7 @@
       </c>
       <c r="AB374" t="inlineStr">
         <is>
-          <t>22:46</t>
+          <t>22:52</t>
         </is>
       </c>
       <c r="AC374" t="inlineStr">
@@ -51319,10 +51319,10 @@
     </row>
     <row r="375">
       <c r="A375" t="n">
-        <v>122254611</v>
+        <v>122254315</v>
       </c>
       <c r="B375" t="n">
-        <v>56290</v>
+        <v>56285</v>
       </c>
       <c r="C375" t="inlineStr">
         <is>
@@ -51335,16 +51335,16 @@
         </is>
       </c>
       <c r="E375" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I375" t="inlineStr">
@@ -51368,10 +51368,10 @@
         </is>
       </c>
       <c r="Q375" t="n">
-        <v>586370</v>
+        <v>586441</v>
       </c>
       <c r="R375" t="n">
-        <v>6311139</v>
+        <v>6311155</v>
       </c>
       <c r="S375" t="n">
         <v>5</v>
@@ -51403,7 +51403,7 @@
       </c>
       <c r="Z375" t="inlineStr">
         <is>
-          <t>22:59</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AA375" t="inlineStr">
@@ -51413,7 +51413,7 @@
       </c>
       <c r="AB375" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AC375" t="inlineStr">
@@ -52153,10 +52153,10 @@
     </row>
     <row r="381">
       <c r="A381" t="n">
-        <v>122254318</v>
+        <v>122254648</v>
       </c>
       <c r="B381" t="n">
-        <v>56285</v>
+        <v>56290</v>
       </c>
       <c r="C381" t="inlineStr">
         <is>
@@ -52169,16 +52169,16 @@
         </is>
       </c>
       <c r="E381" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I381" t="inlineStr">
@@ -52202,10 +52202,10 @@
         </is>
       </c>
       <c r="Q381" t="n">
-        <v>586455</v>
+        <v>586418</v>
       </c>
       <c r="R381" t="n">
-        <v>6311228</v>
+        <v>6311107</v>
       </c>
       <c r="S381" t="n">
         <v>5</v>
@@ -52237,7 +52237,7 @@
       </c>
       <c r="Z381" t="inlineStr">
         <is>
-          <t>23:22</t>
+          <t>22:36</t>
         </is>
       </c>
       <c r="AA381" t="inlineStr">
@@ -52247,7 +52247,7 @@
       </c>
       <c r="AB381" t="inlineStr">
         <is>
-          <t>23:23</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AC381" t="inlineStr">
@@ -52292,7 +52292,7 @@
     </row>
     <row r="382">
       <c r="A382" t="n">
-        <v>122254648</v>
+        <v>122254606</v>
       </c>
       <c r="B382" t="n">
         <v>56290</v>
@@ -52341,10 +52341,10 @@
         </is>
       </c>
       <c r="Q382" t="n">
-        <v>586418</v>
+        <v>586415</v>
       </c>
       <c r="R382" t="n">
-        <v>6311107</v>
+        <v>6311146</v>
       </c>
       <c r="S382" t="n">
         <v>5</v>
@@ -52376,7 +52376,7 @@
       </c>
       <c r="Z382" t="inlineStr">
         <is>
-          <t>22:36</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AA382" t="inlineStr">
@@ -52386,7 +52386,7 @@
       </c>
       <c r="AB382" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>23:03</t>
         </is>
       </c>
       <c r="AC382" t="inlineStr">
@@ -52431,10 +52431,10 @@
     </row>
     <row r="383">
       <c r="A383" t="n">
-        <v>122254606</v>
+        <v>122254966</v>
       </c>
       <c r="B383" t="n">
-        <v>56290</v>
+        <v>56278</v>
       </c>
       <c r="C383" t="inlineStr">
         <is>
@@ -52447,16 +52447,16 @@
         </is>
       </c>
       <c r="E383" t="n">
-        <v>205995</v>
+        <v>205992</v>
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I383" t="inlineStr">
@@ -52480,10 +52480,10 @@
         </is>
       </c>
       <c r="Q383" t="n">
-        <v>586415</v>
+        <v>586467</v>
       </c>
       <c r="R383" t="n">
-        <v>6311146</v>
+        <v>6311178</v>
       </c>
       <c r="S383" t="n">
         <v>5</v>
@@ -52515,7 +52515,7 @@
       </c>
       <c r="Z383" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AA383" t="inlineStr">
@@ -52525,7 +52525,7 @@
       </c>
       <c r="AB383" t="inlineStr">
         <is>
-          <t>23:03</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="AC383" t="inlineStr">
@@ -52570,10 +52570,10 @@
     </row>
     <row r="384">
       <c r="A384" t="n">
-        <v>122254966</v>
+        <v>122254318</v>
       </c>
       <c r="B384" t="n">
-        <v>56278</v>
+        <v>56285</v>
       </c>
       <c r="C384" t="inlineStr">
         <is>
@@ -52586,16 +52586,16 @@
         </is>
       </c>
       <c r="E384" t="n">
-        <v>205992</v>
+        <v>100092</v>
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I384" t="inlineStr">
@@ -52619,10 +52619,10 @@
         </is>
       </c>
       <c r="Q384" t="n">
-        <v>586467</v>
+        <v>586455</v>
       </c>
       <c r="R384" t="n">
-        <v>6311178</v>
+        <v>6311228</v>
       </c>
       <c r="S384" t="n">
         <v>5</v>
@@ -52654,7 +52654,7 @@
       </c>
       <c r="Z384" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>23:22</t>
         </is>
       </c>
       <c r="AA384" t="inlineStr">
@@ -52664,7 +52664,7 @@
       </c>
       <c r="AB384" t="inlineStr">
         <is>
-          <t>22:33</t>
+          <t>23:23</t>
         </is>
       </c>
       <c r="AC384" t="inlineStr">
@@ -52987,10 +52987,10 @@
     </row>
     <row r="387">
       <c r="A387" t="n">
-        <v>122254352</v>
+        <v>122254617</v>
       </c>
       <c r="B387" t="n">
-        <v>56285</v>
+        <v>56290</v>
       </c>
       <c r="C387" t="inlineStr">
         <is>
@@ -53003,16 +53003,16 @@
         </is>
       </c>
       <c r="E387" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I387" t="inlineStr">
@@ -53036,10 +53036,10 @@
         </is>
       </c>
       <c r="Q387" t="n">
-        <v>586288</v>
+        <v>586317</v>
       </c>
       <c r="R387" t="n">
-        <v>6311100</v>
+        <v>6311115</v>
       </c>
       <c r="S387" t="n">
         <v>5</v>
@@ -53071,7 +53071,7 @@
       </c>
       <c r="Z387" t="inlineStr">
         <is>
-          <t>22:55</t>
+          <t>22:57</t>
         </is>
       </c>
       <c r="AA387" t="inlineStr">
@@ -53081,7 +53081,7 @@
       </c>
       <c r="AB387" t="inlineStr">
         <is>
-          <t>22:56</t>
+          <t>22:58</t>
         </is>
       </c>
       <c r="AC387" t="inlineStr">
@@ -53126,7 +53126,7 @@
     </row>
     <row r="388">
       <c r="A388" t="n">
-        <v>122254617</v>
+        <v>122254586</v>
       </c>
       <c r="B388" t="n">
         <v>56290</v>
@@ -53175,10 +53175,10 @@
         </is>
       </c>
       <c r="Q388" t="n">
-        <v>586317</v>
+        <v>586446</v>
       </c>
       <c r="R388" t="n">
-        <v>6311115</v>
+        <v>6311158</v>
       </c>
       <c r="S388" t="n">
         <v>5</v>
@@ -53210,7 +53210,7 @@
       </c>
       <c r="Z388" t="inlineStr">
         <is>
-          <t>22:57</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AA388" t="inlineStr">
@@ -53220,7 +53220,7 @@
       </c>
       <c r="AB388" t="inlineStr">
         <is>
-          <t>22:58</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AC388" t="inlineStr">
@@ -53265,10 +53265,10 @@
     </row>
     <row r="389">
       <c r="A389" t="n">
-        <v>122254586</v>
+        <v>122254352</v>
       </c>
       <c r="B389" t="n">
-        <v>56290</v>
+        <v>56285</v>
       </c>
       <c r="C389" t="inlineStr">
         <is>
@@ -53281,16 +53281,16 @@
         </is>
       </c>
       <c r="E389" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I389" t="inlineStr">
@@ -53314,10 +53314,10 @@
         </is>
       </c>
       <c r="Q389" t="n">
-        <v>586446</v>
+        <v>586288</v>
       </c>
       <c r="R389" t="n">
-        <v>6311158</v>
+        <v>6311100</v>
       </c>
       <c r="S389" t="n">
         <v>5</v>
@@ -53349,7 +53349,7 @@
       </c>
       <c r="Z389" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>22:55</t>
         </is>
       </c>
       <c r="AA389" t="inlineStr">
@@ -53359,7 +53359,7 @@
       </c>
       <c r="AB389" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>22:56</t>
         </is>
       </c>
       <c r="AC389" t="inlineStr">

--- a/artfynd/A 36363-2024 artfynd.xlsx
+++ b/artfynd/A 36363-2024 artfynd.xlsx
@@ -37002,10 +37002,10 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>122254416</v>
+        <v>122254352</v>
       </c>
       <c r="B272" t="n">
-        <v>56285</v>
+        <v>56289</v>
       </c>
       <c r="C272" t="inlineStr">
         <is>
@@ -37020,6 +37020,11 @@
       <c r="E272" t="n">
         <v>100092</v>
       </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>Större brunfladdermus</t>
+        </is>
+      </c>
       <c r="G272" t="inlineStr">
         <is>
           <t>Nyctalus noctula</t>
@@ -37051,10 +37056,10 @@
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>586410</v>
+        <v>586288</v>
       </c>
       <c r="R272" t="n">
-        <v>6311140</v>
+        <v>6311100</v>
       </c>
       <c r="S272" t="n">
         <v>5</v>
@@ -37086,7 +37091,7 @@
       </c>
       <c r="Z272" t="inlineStr">
         <is>
-          <t>22:33</t>
+          <t>22:55</t>
         </is>
       </c>
       <c r="AA272" t="inlineStr">
@@ -37096,7 +37101,7 @@
       </c>
       <c r="AB272" t="inlineStr">
         <is>
-          <t>22:34</t>
+          <t>22:56</t>
         </is>
       </c>
       <c r="AC272" t="inlineStr">
@@ -37141,10 +37146,10 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>122254636</v>
+        <v>122254365</v>
       </c>
       <c r="B273" t="n">
-        <v>56290</v>
+        <v>56289</v>
       </c>
       <c r="C273" t="inlineStr">
         <is>
@@ -37157,16 +37162,21 @@
         </is>
       </c>
       <c r="E273" t="n">
-        <v>205995</v>
+        <v>100092</v>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>Större brunfladdermus</t>
+        </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
@@ -37190,10 +37200,10 @@
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>586418</v>
+        <v>586276</v>
       </c>
       <c r="R273" t="n">
-        <v>6311145</v>
+        <v>6311100</v>
       </c>
       <c r="S273" t="n">
         <v>5</v>
@@ -37225,7 +37235,7 @@
       </c>
       <c r="Z273" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AA273" t="inlineStr">
@@ -37235,7 +37245,7 @@
       </c>
       <c r="AB273" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>22:52</t>
         </is>
       </c>
       <c r="AC273" t="inlineStr">
@@ -37280,10 +37290,10 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>122254609</v>
+        <v>122254617</v>
       </c>
       <c r="B274" t="n">
-        <v>56290</v>
+        <v>56294</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>
@@ -37298,6 +37308,11 @@
       <c r="E274" t="n">
         <v>205995</v>
       </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
       <c r="G274" t="inlineStr">
         <is>
           <t>Pipistrellus pygmaeus</t>
@@ -37329,10 +37344,10 @@
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>586392</v>
+        <v>586317</v>
       </c>
       <c r="R274" t="n">
-        <v>6311147</v>
+        <v>6311115</v>
       </c>
       <c r="S274" t="n">
         <v>5</v>
@@ -37364,7 +37379,7 @@
       </c>
       <c r="Z274" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>22:57</t>
         </is>
       </c>
       <c r="AA274" t="inlineStr">
@@ -37374,7 +37389,7 @@
       </c>
       <c r="AB274" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>22:58</t>
         </is>
       </c>
       <c r="AC274" t="inlineStr">
@@ -37419,10 +37434,10 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>122254659</v>
+        <v>122254953</v>
       </c>
       <c r="B275" t="n">
-        <v>56290</v>
+        <v>56282</v>
       </c>
       <c r="C275" t="inlineStr">
         <is>
@@ -37435,16 +37450,21 @@
         </is>
       </c>
       <c r="E275" t="n">
-        <v>205995</v>
+        <v>205992</v>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>Vattenfladdermus</t>
+        </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
@@ -37468,10 +37488,10 @@
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>586489</v>
+        <v>586449</v>
       </c>
       <c r="R275" t="n">
-        <v>6311181</v>
+        <v>6311155</v>
       </c>
       <c r="S275" t="n">
         <v>5</v>
@@ -37503,7 +37523,7 @@
       </c>
       <c r="Z275" t="inlineStr">
         <is>
-          <t>22:31</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA275" t="inlineStr">
@@ -37513,7 +37533,7 @@
       </c>
       <c r="AB275" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC275" t="inlineStr">
@@ -37558,10 +37578,10 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>122254415</v>
+        <v>122254475</v>
       </c>
       <c r="B276" t="n">
-        <v>56285</v>
+        <v>56275</v>
       </c>
       <c r="C276" t="inlineStr">
         <is>
@@ -37570,20 +37590,25 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E276" t="n">
-        <v>100092</v>
+        <v>205998</v>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
@@ -37607,10 +37632,10 @@
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>586425</v>
+        <v>586420</v>
       </c>
       <c r="R276" t="n">
-        <v>6311135</v>
+        <v>6311166</v>
       </c>
       <c r="S276" t="n">
         <v>5</v>
@@ -37642,7 +37667,7 @@
       </c>
       <c r="Z276" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>23:23</t>
         </is>
       </c>
       <c r="AA276" t="inlineStr">
@@ -37652,7 +37677,7 @@
       </c>
       <c r="AB276" t="inlineStr">
         <is>
-          <t>22:38</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="AC276" t="inlineStr">
@@ -37697,10 +37722,10 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>122254588</v>
+        <v>122254954</v>
       </c>
       <c r="B277" t="n">
-        <v>56290</v>
+        <v>56282</v>
       </c>
       <c r="C277" t="inlineStr">
         <is>
@@ -37713,16 +37738,21 @@
         </is>
       </c>
       <c r="E277" t="n">
-        <v>205995</v>
+        <v>205992</v>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>Vattenfladdermus</t>
+        </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
@@ -37746,10 +37776,10 @@
         </is>
       </c>
       <c r="Q277" t="n">
-        <v>586415</v>
+        <v>586442</v>
       </c>
       <c r="R277" t="n">
-        <v>6311196</v>
+        <v>6311152</v>
       </c>
       <c r="S277" t="n">
         <v>5</v>
@@ -37781,7 +37811,7 @@
       </c>
       <c r="Z277" t="inlineStr">
         <is>
-          <t>23:22</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AA277" t="inlineStr">
@@ -37791,7 +37821,7 @@
       </c>
       <c r="AB277" t="inlineStr">
         <is>
-          <t>23:23</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AC277" t="inlineStr">
@@ -37836,10 +37866,10 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>122254371</v>
+        <v>122254394</v>
       </c>
       <c r="B278" t="n">
-        <v>56285</v>
+        <v>56289</v>
       </c>
       <c r="C278" t="inlineStr">
         <is>
@@ -37854,6 +37884,11 @@
       <c r="E278" t="n">
         <v>100092</v>
       </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>Större brunfladdermus</t>
+        </is>
+      </c>
       <c r="G278" t="inlineStr">
         <is>
           <t>Nyctalus noctula</t>
@@ -37885,10 +37920,10 @@
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>586308</v>
+        <v>586419</v>
       </c>
       <c r="R278" t="n">
-        <v>6311132</v>
+        <v>6311142</v>
       </c>
       <c r="S278" t="n">
         <v>5</v>
@@ -37920,7 +37955,7 @@
       </c>
       <c r="Z278" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>22:43</t>
         </is>
       </c>
       <c r="AA278" t="inlineStr">
@@ -37930,7 +37965,7 @@
       </c>
       <c r="AB278" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AC278" t="inlineStr">
@@ -37975,10 +38010,10 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>122254476</v>
+        <v>122254498</v>
       </c>
       <c r="B279" t="n">
-        <v>56271</v>
+        <v>56275</v>
       </c>
       <c r="C279" t="inlineStr">
         <is>
@@ -37993,6 +38028,11 @@
       <c r="E279" t="n">
         <v>205998</v>
       </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
       <c r="G279" t="inlineStr">
         <is>
           <t>Eptesicus nilssonii</t>
@@ -38024,10 +38064,10 @@
         </is>
       </c>
       <c r="Q279" t="n">
-        <v>586418</v>
+        <v>586393</v>
       </c>
       <c r="R279" t="n">
-        <v>6311167</v>
+        <v>6311147</v>
       </c>
       <c r="S279" t="n">
         <v>5</v>
@@ -38059,7 +38099,7 @@
       </c>
       <c r="Z279" t="inlineStr">
         <is>
-          <t>23:23</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AA279" t="inlineStr">
@@ -38069,7 +38109,7 @@
       </c>
       <c r="AB279" t="inlineStr">
         <is>
-          <t>23:24</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AC279" t="inlineStr">
@@ -38114,10 +38154,10 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>122254635</v>
+        <v>122254837</v>
       </c>
       <c r="B280" t="n">
-        <v>56290</v>
+        <v>56292</v>
       </c>
       <c r="C280" t="inlineStr">
         <is>
@@ -38130,16 +38170,21 @@
         </is>
       </c>
       <c r="E280" t="n">
-        <v>205995</v>
+        <v>100111</v>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>Trollpipistrell</t>
+        </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
@@ -38163,10 +38208,10 @@
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>586417</v>
+        <v>586448</v>
       </c>
       <c r="R280" t="n">
-        <v>6311145</v>
+        <v>6311154</v>
       </c>
       <c r="S280" t="n">
         <v>5</v>
@@ -38198,7 +38243,7 @@
       </c>
       <c r="Z280" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA280" t="inlineStr">
@@ -38208,7 +38253,7 @@
       </c>
       <c r="AB280" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC280" t="inlineStr">
@@ -38253,10 +38298,10 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>122254644</v>
+        <v>122254306</v>
       </c>
       <c r="B281" t="n">
-        <v>56290</v>
+        <v>56289</v>
       </c>
       <c r="C281" t="inlineStr">
         <is>
@@ -38269,16 +38314,21 @@
         </is>
       </c>
       <c r="E281" t="n">
-        <v>205995</v>
+        <v>100092</v>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>Större brunfladdermus</t>
+        </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
@@ -38302,10 +38352,10 @@
         </is>
       </c>
       <c r="Q281" t="n">
-        <v>586429</v>
+        <v>586473</v>
       </c>
       <c r="R281" t="n">
-        <v>6311115</v>
+        <v>6311192</v>
       </c>
       <c r="S281" t="n">
         <v>5</v>
@@ -38337,7 +38387,7 @@
       </c>
       <c r="Z281" t="inlineStr">
         <is>
-          <t>22:36</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AA281" t="inlineStr">
@@ -38347,7 +38397,7 @@
       </c>
       <c r="AB281" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AC281" t="inlineStr">
@@ -38392,10 +38442,10 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>122254652</v>
+        <v>122254312</v>
       </c>
       <c r="B282" t="n">
-        <v>56290</v>
+        <v>56289</v>
       </c>
       <c r="C282" t="inlineStr">
         <is>
@@ -38408,16 +38458,21 @@
         </is>
       </c>
       <c r="E282" t="n">
-        <v>205995</v>
+        <v>100092</v>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>Större brunfladdermus</t>
+        </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
@@ -38441,10 +38496,10 @@
         </is>
       </c>
       <c r="Q282" t="n">
-        <v>586432</v>
+        <v>586452</v>
       </c>
       <c r="R282" t="n">
-        <v>6311118</v>
+        <v>6311152</v>
       </c>
       <c r="S282" t="n">
         <v>5</v>
@@ -38476,7 +38531,7 @@
       </c>
       <c r="Z282" t="inlineStr">
         <is>
-          <t>22:34</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA282" t="inlineStr">
@@ -38486,7 +38541,7 @@
       </c>
       <c r="AB282" t="inlineStr">
         <is>
-          <t>22:35</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC282" t="inlineStr">
@@ -38531,10 +38586,10 @@
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>122254587</v>
+        <v>122254857</v>
       </c>
       <c r="B283" t="n">
-        <v>56290</v>
+        <v>56292</v>
       </c>
       <c r="C283" t="inlineStr">
         <is>
@@ -38547,16 +38602,21 @@
         </is>
       </c>
       <c r="E283" t="n">
-        <v>205995</v>
+        <v>100111</v>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>Trollpipistrell</t>
+        </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
@@ -38580,10 +38640,10 @@
         </is>
       </c>
       <c r="Q283" t="n">
-        <v>586443</v>
+        <v>586317</v>
       </c>
       <c r="R283" t="n">
-        <v>6311163</v>
+        <v>6311115</v>
       </c>
       <c r="S283" t="n">
         <v>5</v>
@@ -38615,7 +38675,7 @@
       </c>
       <c r="Z283" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>22:57</t>
         </is>
       </c>
       <c r="AA283" t="inlineStr">
@@ -38625,7 +38685,7 @@
       </c>
       <c r="AB283" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>22:58</t>
         </is>
       </c>
       <c r="AC283" t="inlineStr">
@@ -38670,10 +38730,10 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>122254855</v>
+        <v>122254878</v>
       </c>
       <c r="B284" t="n">
-        <v>56288</v>
+        <v>56292</v>
       </c>
       <c r="C284" t="inlineStr">
         <is>
@@ -38688,6 +38748,11 @@
       <c r="E284" t="n">
         <v>100111</v>
       </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>Trollpipistrell</t>
+        </is>
+      </c>
       <c r="G284" t="inlineStr">
         <is>
           <t>Pipistrellus nathusii</t>
@@ -38719,10 +38784,10 @@
         </is>
       </c>
       <c r="Q284" t="n">
-        <v>586330</v>
+        <v>586280</v>
       </c>
       <c r="R284" t="n">
-        <v>6311120</v>
+        <v>6311103</v>
       </c>
       <c r="S284" t="n">
         <v>5</v>
@@ -38754,7 +38819,7 @@
       </c>
       <c r="Z284" t="inlineStr">
         <is>
-          <t>22:57</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AA284" t="inlineStr">
@@ -38764,7 +38829,7 @@
       </c>
       <c r="AB284" t="inlineStr">
         <is>
-          <t>22:58</t>
+          <t>22:52</t>
         </is>
       </c>
       <c r="AC284" t="inlineStr">
@@ -38809,10 +38874,10 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>122254367</v>
+        <v>122254418</v>
       </c>
       <c r="B285" t="n">
-        <v>56285</v>
+        <v>56289</v>
       </c>
       <c r="C285" t="inlineStr">
         <is>
@@ -38827,6 +38892,11 @@
       <c r="E285" t="n">
         <v>100092</v>
       </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>Större brunfladdermus</t>
+        </is>
+      </c>
       <c r="G285" t="inlineStr">
         <is>
           <t>Nyctalus noctula</t>
@@ -38858,10 +38928,10 @@
         </is>
       </c>
       <c r="Q285" t="n">
-        <v>586280</v>
+        <v>586467</v>
       </c>
       <c r="R285" t="n">
-        <v>6311103</v>
+        <v>6311178</v>
       </c>
       <c r="S285" t="n">
         <v>5</v>
@@ -38893,7 +38963,7 @@
       </c>
       <c r="Z285" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AA285" t="inlineStr">
@@ -38903,7 +38973,7 @@
       </c>
       <c r="AB285" t="inlineStr">
         <is>
-          <t>22:52</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="AC285" t="inlineStr">
@@ -38948,10 +39018,10 @@
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>122254417</v>
+        <v>122254421</v>
       </c>
       <c r="B286" t="n">
-        <v>56285</v>
+        <v>56289</v>
       </c>
       <c r="C286" t="inlineStr">
         <is>
@@ -38966,6 +39036,11 @@
       <c r="E286" t="n">
         <v>100092</v>
       </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>Större brunfladdermus</t>
+        </is>
+      </c>
       <c r="G286" t="inlineStr">
         <is>
           <t>Nyctalus noctula</t>
@@ -38997,10 +39072,10 @@
         </is>
       </c>
       <c r="Q286" t="n">
-        <v>586426</v>
+        <v>586468</v>
       </c>
       <c r="R286" t="n">
-        <v>6311145</v>
+        <v>6311181</v>
       </c>
       <c r="S286" t="n">
         <v>5</v>
@@ -39032,17 +39107,17 @@
       </c>
       <c r="Z286" t="inlineStr">
         <is>
+          <t>22:32</t>
+        </is>
+      </c>
+      <c r="AA286" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AB286" t="inlineStr">
+        <is>
           <t>22:33</t>
-        </is>
-      </c>
-      <c r="AA286" t="inlineStr">
-        <is>
-          <t>2024-06-26</t>
-        </is>
-      </c>
-      <c r="AB286" t="inlineStr">
-        <is>
-          <t>22:34</t>
         </is>
       </c>
       <c r="AC286" t="inlineStr">
@@ -39087,10 +39162,10 @@
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>122254964</v>
+        <v>122254396</v>
       </c>
       <c r="B287" t="n">
-        <v>56278</v>
+        <v>56289</v>
       </c>
       <c r="C287" t="inlineStr">
         <is>
@@ -39103,16 +39178,21 @@
         </is>
       </c>
       <c r="E287" t="n">
-        <v>205992</v>
+        <v>100092</v>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>Större brunfladdermus</t>
+        </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
@@ -39136,10 +39216,10 @@
         </is>
       </c>
       <c r="Q287" t="n">
-        <v>586430</v>
+        <v>586408</v>
       </c>
       <c r="R287" t="n">
-        <v>6311142</v>
+        <v>6311124</v>
       </c>
       <c r="S287" t="n">
         <v>5</v>
@@ -39171,7 +39251,7 @@
       </c>
       <c r="Z287" t="inlineStr">
         <is>
-          <t>22:33</t>
+          <t>22:43</t>
         </is>
       </c>
       <c r="AA287" t="inlineStr">
@@ -39181,7 +39261,7 @@
       </c>
       <c r="AB287" t="inlineStr">
         <is>
-          <t>22:34</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AC287" t="inlineStr">
@@ -39226,10 +39306,10 @@
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>122254836</v>
+        <v>122254632</v>
       </c>
       <c r="B288" t="n">
-        <v>56288</v>
+        <v>56294</v>
       </c>
       <c r="C288" t="inlineStr">
         <is>
@@ -39242,16 +39322,21 @@
         </is>
       </c>
       <c r="E288" t="n">
-        <v>100111</v>
+        <v>205995</v>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
@@ -39275,10 +39360,10 @@
         </is>
       </c>
       <c r="Q288" t="n">
-        <v>586474</v>
+        <v>586374</v>
       </c>
       <c r="R288" t="n">
-        <v>6311176</v>
+        <v>6311140</v>
       </c>
       <c r="S288" t="n">
         <v>5</v>
@@ -39310,7 +39395,7 @@
       </c>
       <c r="Z288" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>22:46</t>
         </is>
       </c>
       <c r="AA288" t="inlineStr">
@@ -39320,7 +39405,7 @@
       </c>
       <c r="AB288" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>22:47</t>
         </is>
       </c>
       <c r="AC288" t="inlineStr">
@@ -39365,10 +39450,10 @@
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>122254878</v>
+        <v>122254317</v>
       </c>
       <c r="B289" t="n">
-        <v>56288</v>
+        <v>56289</v>
       </c>
       <c r="C289" t="inlineStr">
         <is>
@@ -39381,16 +39466,21 @@
         </is>
       </c>
       <c r="E289" t="n">
-        <v>100111</v>
+        <v>100092</v>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>Större brunfladdermus</t>
+        </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
@@ -39414,10 +39504,10 @@
         </is>
       </c>
       <c r="Q289" t="n">
-        <v>586280</v>
+        <v>586438</v>
       </c>
       <c r="R289" t="n">
-        <v>6311103</v>
+        <v>6311222</v>
       </c>
       <c r="S289" t="n">
         <v>5</v>
@@ -39449,7 +39539,7 @@
       </c>
       <c r="Z289" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>23:22</t>
         </is>
       </c>
       <c r="AA289" t="inlineStr">
@@ -39459,7 +39549,7 @@
       </c>
       <c r="AB289" t="inlineStr">
         <is>
-          <t>22:52</t>
+          <t>23:23</t>
         </is>
       </c>
       <c r="AC289" t="inlineStr">
@@ -39504,10 +39594,10 @@
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>122254846</v>
+        <v>122254372</v>
       </c>
       <c r="B290" t="n">
-        <v>56288</v>
+        <v>56289</v>
       </c>
       <c r="C290" t="inlineStr">
         <is>
@@ -39520,16 +39610,21 @@
         </is>
       </c>
       <c r="E290" t="n">
-        <v>100111</v>
+        <v>100092</v>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>Större brunfladdermus</t>
+        </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
@@ -39553,10 +39648,10 @@
         </is>
       </c>
       <c r="Q290" t="n">
-        <v>586370</v>
+        <v>586306</v>
       </c>
       <c r="R290" t="n">
-        <v>6311139</v>
+        <v>6311131</v>
       </c>
       <c r="S290" t="n">
         <v>5</v>
@@ -39588,7 +39683,7 @@
       </c>
       <c r="Z290" t="inlineStr">
         <is>
-          <t>22:59</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AA290" t="inlineStr">
@@ -39598,7 +39693,7 @@
       </c>
       <c r="AB290" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AC290" t="inlineStr">
@@ -39643,10 +39738,10 @@
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>122254394</v>
+        <v>122254310</v>
       </c>
       <c r="B291" t="n">
-        <v>56285</v>
+        <v>56289</v>
       </c>
       <c r="C291" t="inlineStr">
         <is>
@@ -39661,6 +39756,11 @@
       <c r="E291" t="n">
         <v>100092</v>
       </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>Större brunfladdermus</t>
+        </is>
+      </c>
       <c r="G291" t="inlineStr">
         <is>
           <t>Nyctalus noctula</t>
@@ -39692,10 +39792,10 @@
         </is>
       </c>
       <c r="Q291" t="n">
-        <v>586419</v>
+        <v>586452</v>
       </c>
       <c r="R291" t="n">
-        <v>6311142</v>
+        <v>6311156</v>
       </c>
       <c r="S291" t="n">
         <v>5</v>
@@ -39727,7 +39827,7 @@
       </c>
       <c r="Z291" t="inlineStr">
         <is>
-          <t>22:43</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA291" t="inlineStr">
@@ -39737,7 +39837,7 @@
       </c>
       <c r="AB291" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC291" t="inlineStr">
@@ -39782,10 +39882,10 @@
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>122254390</v>
+        <v>122254315</v>
       </c>
       <c r="B292" t="n">
-        <v>56285</v>
+        <v>56289</v>
       </c>
       <c r="C292" t="inlineStr">
         <is>
@@ -39800,6 +39900,11 @@
       <c r="E292" t="n">
         <v>100092</v>
       </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>Större brunfladdermus</t>
+        </is>
+      </c>
       <c r="G292" t="inlineStr">
         <is>
           <t>Nyctalus noctula</t>
@@ -39831,10 +39936,10 @@
         </is>
       </c>
       <c r="Q292" t="n">
-        <v>586374</v>
+        <v>586441</v>
       </c>
       <c r="R292" t="n">
-        <v>6311139</v>
+        <v>6311155</v>
       </c>
       <c r="S292" t="n">
         <v>5</v>
@@ -39866,7 +39971,7 @@
       </c>
       <c r="Z292" t="inlineStr">
         <is>
-          <t>22:46</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AA292" t="inlineStr">
@@ -39876,7 +39981,7 @@
       </c>
       <c r="AB292" t="inlineStr">
         <is>
-          <t>22:47</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AC292" t="inlineStr">
@@ -39921,10 +40026,10 @@
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>122254395</v>
+        <v>122254496</v>
       </c>
       <c r="B293" t="n">
-        <v>56285</v>
+        <v>56275</v>
       </c>
       <c r="C293" t="inlineStr">
         <is>
@@ -39933,20 +40038,25 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E293" t="n">
-        <v>100092</v>
+        <v>205998</v>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
@@ -39970,10 +40080,10 @@
         </is>
       </c>
       <c r="Q293" t="n">
-        <v>586408</v>
+        <v>586415</v>
       </c>
       <c r="R293" t="n">
-        <v>6311124</v>
+        <v>6311146</v>
       </c>
       <c r="S293" t="n">
         <v>5</v>
@@ -40005,7 +40115,7 @@
       </c>
       <c r="Z293" t="inlineStr">
         <is>
-          <t>22:43</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AA293" t="inlineStr">
@@ -40015,7 +40125,7 @@
       </c>
       <c r="AB293" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>23:03</t>
         </is>
       </c>
       <c r="AC293" t="inlineStr">
@@ -40060,10 +40170,10 @@
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>122254837</v>
+        <v>122254473</v>
       </c>
       <c r="B294" t="n">
-        <v>56288</v>
+        <v>56275</v>
       </c>
       <c r="C294" t="inlineStr">
         <is>
@@ -40072,20 +40182,25 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E294" t="n">
-        <v>100111</v>
+        <v>205998</v>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
@@ -40109,10 +40224,10 @@
         </is>
       </c>
       <c r="Q294" t="n">
-        <v>586448</v>
+        <v>586450</v>
       </c>
       <c r="R294" t="n">
-        <v>6311154</v>
+        <v>6311152</v>
       </c>
       <c r="S294" t="n">
         <v>5</v>
@@ -40199,10 +40314,10 @@
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>122254880</v>
+        <v>122254415</v>
       </c>
       <c r="B295" t="n">
-        <v>56288</v>
+        <v>56289</v>
       </c>
       <c r="C295" t="inlineStr">
         <is>
@@ -40215,16 +40330,21 @@
         </is>
       </c>
       <c r="E295" t="n">
-        <v>100111</v>
+        <v>100092</v>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>Större brunfladdermus</t>
+        </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
@@ -40248,10 +40368,10 @@
         </is>
       </c>
       <c r="Q295" t="n">
-        <v>586303</v>
+        <v>586425</v>
       </c>
       <c r="R295" t="n">
-        <v>6311115</v>
+        <v>6311135</v>
       </c>
       <c r="S295" t="n">
         <v>5</v>
@@ -40283,7 +40403,7 @@
       </c>
       <c r="Z295" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AA295" t="inlineStr">
@@ -40293,7 +40413,7 @@
       </c>
       <c r="AB295" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>22:38</t>
         </is>
       </c>
       <c r="AC295" t="inlineStr">
@@ -40338,10 +40458,10 @@
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>122254633</v>
+        <v>122254393</v>
       </c>
       <c r="B296" t="n">
-        <v>56290</v>
+        <v>56289</v>
       </c>
       <c r="C296" t="inlineStr">
         <is>
@@ -40354,16 +40474,21 @@
         </is>
       </c>
       <c r="E296" t="n">
-        <v>205995</v>
+        <v>100092</v>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>Större brunfladdermus</t>
+        </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
@@ -40477,10 +40602,10 @@
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>122254634</v>
+        <v>122254308</v>
       </c>
       <c r="B297" t="n">
-        <v>56290</v>
+        <v>56289</v>
       </c>
       <c r="C297" t="inlineStr">
         <is>
@@ -40493,16 +40618,21 @@
         </is>
       </c>
       <c r="E297" t="n">
-        <v>205995</v>
+        <v>100092</v>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>Större brunfladdermus</t>
+        </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
@@ -40526,10 +40656,10 @@
         </is>
       </c>
       <c r="Q297" t="n">
-        <v>586415</v>
+        <v>586455</v>
       </c>
       <c r="R297" t="n">
-        <v>6311148</v>
+        <v>6311159</v>
       </c>
       <c r="S297" t="n">
         <v>5</v>
@@ -40561,7 +40691,7 @@
       </c>
       <c r="Z297" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AA297" t="inlineStr">
@@ -40571,7 +40701,7 @@
       </c>
       <c r="AB297" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AC297" t="inlineStr">
@@ -40616,10 +40746,10 @@
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>122254653</v>
+        <v>122254649</v>
       </c>
       <c r="B298" t="n">
-        <v>56290</v>
+        <v>56294</v>
       </c>
       <c r="C298" t="inlineStr">
         <is>
@@ -40634,6 +40764,11 @@
       <c r="E298" t="n">
         <v>205995</v>
       </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
       <c r="G298" t="inlineStr">
         <is>
           <t>Pipistrellus pygmaeus</t>
@@ -40665,10 +40800,10 @@
         </is>
       </c>
       <c r="Q298" t="n">
-        <v>586430</v>
+        <v>586422</v>
       </c>
       <c r="R298" t="n">
-        <v>6311142</v>
+        <v>6311100</v>
       </c>
       <c r="S298" t="n">
         <v>5</v>
@@ -40700,7 +40835,7 @@
       </c>
       <c r="Z298" t="inlineStr">
         <is>
-          <t>22:33</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="AA298" t="inlineStr">
@@ -40710,7 +40845,7 @@
       </c>
       <c r="AB298" t="inlineStr">
         <is>
-          <t>22:34</t>
+          <t>22:36</t>
         </is>
       </c>
       <c r="AC298" t="inlineStr">
@@ -40755,10 +40890,10 @@
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>122254584</v>
+        <v>122254843</v>
       </c>
       <c r="B299" t="n">
-        <v>56290</v>
+        <v>56292</v>
       </c>
       <c r="C299" t="inlineStr">
         <is>
@@ -40771,16 +40906,21 @@
         </is>
       </c>
       <c r="E299" t="n">
-        <v>205995</v>
+        <v>100111</v>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>Trollpipistrell</t>
+        </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
@@ -40804,10 +40944,10 @@
         </is>
       </c>
       <c r="Q299" t="n">
-        <v>586473</v>
+        <v>586389</v>
       </c>
       <c r="R299" t="n">
-        <v>6311192</v>
+        <v>6311142</v>
       </c>
       <c r="S299" t="n">
         <v>5</v>
@@ -40839,7 +40979,7 @@
       </c>
       <c r="Z299" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA299" t="inlineStr">
@@ -40849,7 +40989,7 @@
       </c>
       <c r="AB299" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AC299" t="inlineStr">
@@ -40894,10 +41034,10 @@
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>122254627</v>
+        <v>122254856</v>
       </c>
       <c r="B300" t="n">
-        <v>56290</v>
+        <v>56292</v>
       </c>
       <c r="C300" t="inlineStr">
         <is>
@@ -40910,16 +41050,21 @@
         </is>
       </c>
       <c r="E300" t="n">
-        <v>205995</v>
+        <v>100111</v>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>Trollpipistrell</t>
+        </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
@@ -40943,10 +41088,10 @@
         </is>
       </c>
       <c r="Q300" t="n">
-        <v>586306</v>
+        <v>586327</v>
       </c>
       <c r="R300" t="n">
-        <v>6311131</v>
+        <v>6311118</v>
       </c>
       <c r="S300" t="n">
         <v>5</v>
@@ -40978,7 +41123,7 @@
       </c>
       <c r="Z300" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>22:57</t>
         </is>
       </c>
       <c r="AA300" t="inlineStr">
@@ -40988,7 +41133,7 @@
       </c>
       <c r="AB300" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>22:58</t>
         </is>
       </c>
       <c r="AC300" t="inlineStr">
@@ -41033,10 +41178,10 @@
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>122254626</v>
+        <v>122254616</v>
       </c>
       <c r="B301" t="n">
-        <v>56290</v>
+        <v>56294</v>
       </c>
       <c r="C301" t="inlineStr">
         <is>
@@ -41051,6 +41196,11 @@
       <c r="E301" t="n">
         <v>205995</v>
       </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
       <c r="G301" t="inlineStr">
         <is>
           <t>Pipistrellus pygmaeus</t>
@@ -41082,10 +41232,10 @@
         </is>
       </c>
       <c r="Q301" t="n">
-        <v>586313</v>
+        <v>586327</v>
       </c>
       <c r="R301" t="n">
-        <v>6311124</v>
+        <v>6311118</v>
       </c>
       <c r="S301" t="n">
         <v>5</v>
@@ -41117,7 +41267,7 @@
       </c>
       <c r="Z301" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>22:57</t>
         </is>
       </c>
       <c r="AA301" t="inlineStr">
@@ -41127,7 +41277,7 @@
       </c>
       <c r="AB301" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>22:58</t>
         </is>
       </c>
       <c r="AC301" t="inlineStr">
@@ -41172,10 +41322,10 @@
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>122254856</v>
+        <v>122254342</v>
       </c>
       <c r="B302" t="n">
-        <v>56288</v>
+        <v>56289</v>
       </c>
       <c r="C302" t="inlineStr">
         <is>
@@ -41188,16 +41338,21 @@
         </is>
       </c>
       <c r="E302" t="n">
-        <v>100111</v>
+        <v>100092</v>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>Större brunfladdermus</t>
+        </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
@@ -41221,10 +41376,10 @@
         </is>
       </c>
       <c r="Q302" t="n">
-        <v>586327</v>
+        <v>586389</v>
       </c>
       <c r="R302" t="n">
-        <v>6311118</v>
+        <v>6311142</v>
       </c>
       <c r="S302" t="n">
         <v>5</v>
@@ -41256,7 +41411,7 @@
       </c>
       <c r="Z302" t="inlineStr">
         <is>
-          <t>22:57</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA302" t="inlineStr">
@@ -41266,7 +41421,7 @@
       </c>
       <c r="AB302" t="inlineStr">
         <is>
-          <t>22:58</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AC302" t="inlineStr">
@@ -41311,10 +41466,10 @@
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>122254474</v>
+        <v>122254411</v>
       </c>
       <c r="B303" t="n">
-        <v>56271</v>
+        <v>56289</v>
       </c>
       <c r="C303" t="inlineStr">
         <is>
@@ -41323,20 +41478,25 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E303" t="n">
-        <v>205998</v>
+        <v>100092</v>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>Större brunfladdermus</t>
+        </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
@@ -41360,10 +41520,10 @@
         </is>
       </c>
       <c r="Q303" t="n">
-        <v>586443</v>
+        <v>586414</v>
       </c>
       <c r="R303" t="n">
-        <v>6311164</v>
+        <v>6311126</v>
       </c>
       <c r="S303" t="n">
         <v>5</v>
@@ -41395,7 +41555,7 @@
       </c>
       <c r="Z303" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AA303" t="inlineStr">
@@ -41405,7 +41565,7 @@
       </c>
       <c r="AB303" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>22:38</t>
         </is>
       </c>
       <c r="AC303" t="inlineStr">
@@ -41450,10 +41610,10 @@
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>122254514</v>
+        <v>122254314</v>
       </c>
       <c r="B304" t="n">
-        <v>56271</v>
+        <v>56289</v>
       </c>
       <c r="C304" t="inlineStr">
         <is>
@@ -41462,20 +41622,25 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E304" t="n">
-        <v>205998</v>
+        <v>100092</v>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>Större brunfladdermus</t>
+        </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
@@ -41499,10 +41664,10 @@
         </is>
       </c>
       <c r="Q304" t="n">
-        <v>586408</v>
+        <v>586443</v>
       </c>
       <c r="R304" t="n">
-        <v>6311124</v>
+        <v>6311164</v>
       </c>
       <c r="S304" t="n">
         <v>5</v>
@@ -41534,7 +41699,7 @@
       </c>
       <c r="Z304" t="inlineStr">
         <is>
-          <t>22:43</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AA304" t="inlineStr">
@@ -41544,7 +41709,7 @@
       </c>
       <c r="AB304" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AC304" t="inlineStr">
@@ -41589,10 +41754,10 @@
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>122254950</v>
+        <v>122254846</v>
       </c>
       <c r="B305" t="n">
-        <v>56278</v>
+        <v>56292</v>
       </c>
       <c r="C305" t="inlineStr">
         <is>
@@ -41605,16 +41770,21 @@
         </is>
       </c>
       <c r="E305" t="n">
-        <v>205992</v>
+        <v>100111</v>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>Trollpipistrell</t>
+        </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
@@ -41638,10 +41808,10 @@
         </is>
       </c>
       <c r="Q305" t="n">
-        <v>586482</v>
+        <v>586370</v>
       </c>
       <c r="R305" t="n">
-        <v>6311185</v>
+        <v>6311139</v>
       </c>
       <c r="S305" t="n">
         <v>5</v>
@@ -41673,7 +41843,7 @@
       </c>
       <c r="Z305" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>22:59</t>
         </is>
       </c>
       <c r="AA305" t="inlineStr">
@@ -41683,7 +41853,7 @@
       </c>
       <c r="AB305" t="inlineStr">
         <is>
-          <t>23:31</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AC305" t="inlineStr">
@@ -41728,10 +41898,10 @@
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>122254500</v>
+        <v>122254413</v>
       </c>
       <c r="B306" t="n">
-        <v>56271</v>
+        <v>56289</v>
       </c>
       <c r="C306" t="inlineStr">
         <is>
@@ -41740,20 +41910,25 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E306" t="n">
-        <v>205998</v>
+        <v>100092</v>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>Större brunfladdermus</t>
+        </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
@@ -41777,10 +41952,10 @@
         </is>
       </c>
       <c r="Q306" t="n">
-        <v>586388</v>
+        <v>586423</v>
       </c>
       <c r="R306" t="n">
-        <v>6311142</v>
+        <v>6311137</v>
       </c>
       <c r="S306" t="n">
         <v>5</v>
@@ -41812,7 +41987,7 @@
       </c>
       <c r="Z306" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AA306" t="inlineStr">
@@ -41822,7 +41997,7 @@
       </c>
       <c r="AB306" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>22:38</t>
         </is>
       </c>
       <c r="AC306" t="inlineStr">
@@ -41867,10 +42042,10 @@
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>122254657</v>
+        <v>122254350</v>
       </c>
       <c r="B307" t="n">
-        <v>56290</v>
+        <v>56289</v>
       </c>
       <c r="C307" t="inlineStr">
         <is>
@@ -41883,16 +42058,21 @@
         </is>
       </c>
       <c r="E307" t="n">
-        <v>205995</v>
+        <v>100092</v>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>Större brunfladdermus</t>
+        </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
@@ -41916,10 +42096,10 @@
         </is>
       </c>
       <c r="Q307" t="n">
-        <v>586488</v>
+        <v>586330</v>
       </c>
       <c r="R307" t="n">
-        <v>6311184</v>
+        <v>6311120</v>
       </c>
       <c r="S307" t="n">
         <v>5</v>
@@ -41951,7 +42131,7 @@
       </c>
       <c r="Z307" t="inlineStr">
         <is>
-          <t>22:31</t>
+          <t>22:57</t>
         </is>
       </c>
       <c r="AA307" t="inlineStr">
@@ -41961,7 +42141,7 @@
       </c>
       <c r="AB307" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>22:58</t>
         </is>
       </c>
       <c r="AC307" t="inlineStr">
@@ -42006,10 +42186,10 @@
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>122254308</v>
+        <v>122254635</v>
       </c>
       <c r="B308" t="n">
-        <v>56285</v>
+        <v>56294</v>
       </c>
       <c r="C308" t="inlineStr">
         <is>
@@ -42022,16 +42202,21 @@
         </is>
       </c>
       <c r="E308" t="n">
-        <v>100092</v>
+        <v>205995</v>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
@@ -42055,10 +42240,10 @@
         </is>
       </c>
       <c r="Q308" t="n">
-        <v>586455</v>
+        <v>586417</v>
       </c>
       <c r="R308" t="n">
-        <v>6311159</v>
+        <v>6311145</v>
       </c>
       <c r="S308" t="n">
         <v>5</v>
@@ -42090,7 +42275,7 @@
       </c>
       <c r="Z308" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AA308" t="inlineStr">
@@ -42100,7 +42285,7 @@
       </c>
       <c r="AB308" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AC308" t="inlineStr">
@@ -42145,10 +42330,10 @@
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>122254350</v>
+        <v>122254637</v>
       </c>
       <c r="B309" t="n">
-        <v>56285</v>
+        <v>56294</v>
       </c>
       <c r="C309" t="inlineStr">
         <is>
@@ -42161,16 +42346,21 @@
         </is>
       </c>
       <c r="E309" t="n">
-        <v>100092</v>
+        <v>205995</v>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
@@ -42194,10 +42384,10 @@
         </is>
       </c>
       <c r="Q309" t="n">
-        <v>586330</v>
+        <v>586408</v>
       </c>
       <c r="R309" t="n">
-        <v>6311120</v>
+        <v>6311124</v>
       </c>
       <c r="S309" t="n">
         <v>5</v>
@@ -42229,7 +42419,7 @@
       </c>
       <c r="Z309" t="inlineStr">
         <is>
-          <t>22:57</t>
+          <t>22:43</t>
         </is>
       </c>
       <c r="AA309" t="inlineStr">
@@ -42239,7 +42429,7 @@
       </c>
       <c r="AB309" t="inlineStr">
         <is>
-          <t>22:58</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AC309" t="inlineStr">
@@ -42284,10 +42474,10 @@
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>122254316</v>
+        <v>122254636</v>
       </c>
       <c r="B310" t="n">
-        <v>56285</v>
+        <v>56294</v>
       </c>
       <c r="C310" t="inlineStr">
         <is>
@@ -42300,16 +42490,21 @@
         </is>
       </c>
       <c r="E310" t="n">
-        <v>100092</v>
+        <v>205995</v>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
@@ -42333,10 +42528,10 @@
         </is>
       </c>
       <c r="Q310" t="n">
-        <v>586423</v>
+        <v>586418</v>
       </c>
       <c r="R310" t="n">
-        <v>6311166</v>
+        <v>6311145</v>
       </c>
       <c r="S310" t="n">
         <v>5</v>
@@ -42368,7 +42563,7 @@
       </c>
       <c r="Z310" t="inlineStr">
         <is>
-          <t>23:23</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AA310" t="inlineStr">
@@ -42378,7 +42573,7 @@
       </c>
       <c r="AB310" t="inlineStr">
         <is>
-          <t>23:24</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AC310" t="inlineStr">
@@ -42423,10 +42618,10 @@
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>122254312</v>
+        <v>122254950</v>
       </c>
       <c r="B311" t="n">
-        <v>56285</v>
+        <v>56282</v>
       </c>
       <c r="C311" t="inlineStr">
         <is>
@@ -42439,16 +42634,21 @@
         </is>
       </c>
       <c r="E311" t="n">
-        <v>100092</v>
+        <v>205992</v>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>Vattenfladdermus</t>
+        </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
@@ -42472,10 +42672,10 @@
         </is>
       </c>
       <c r="Q311" t="n">
-        <v>586452</v>
+        <v>586482</v>
       </c>
       <c r="R311" t="n">
-        <v>6311152</v>
+        <v>6311185</v>
       </c>
       <c r="S311" t="n">
         <v>5</v>
@@ -42507,7 +42707,7 @@
       </c>
       <c r="Z311" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AA311" t="inlineStr">
@@ -42517,7 +42717,7 @@
       </c>
       <c r="AB311" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>23:31</t>
         </is>
       </c>
       <c r="AC311" t="inlineStr">
@@ -42562,10 +42762,10 @@
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>122254615</v>
+        <v>122254844</v>
       </c>
       <c r="B312" t="n">
-        <v>56290</v>
+        <v>56292</v>
       </c>
       <c r="C312" t="inlineStr">
         <is>
@@ -42578,16 +42778,21 @@
         </is>
       </c>
       <c r="E312" t="n">
-        <v>205995</v>
+        <v>100111</v>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>Trollpipistrell</t>
+        </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
@@ -42611,10 +42816,10 @@
         </is>
       </c>
       <c r="Q312" t="n">
-        <v>586329</v>
+        <v>586387</v>
       </c>
       <c r="R312" t="n">
-        <v>6311120</v>
+        <v>6311141</v>
       </c>
       <c r="S312" t="n">
         <v>5</v>
@@ -42646,7 +42851,7 @@
       </c>
       <c r="Z312" t="inlineStr">
         <is>
-          <t>22:57</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA312" t="inlineStr">
@@ -42656,7 +42861,7 @@
       </c>
       <c r="AB312" t="inlineStr">
         <is>
-          <t>22:58</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AC312" t="inlineStr">
@@ -42701,10 +42906,10 @@
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>122254660</v>
+        <v>122254367</v>
       </c>
       <c r="B313" t="n">
-        <v>56290</v>
+        <v>56289</v>
       </c>
       <c r="C313" t="inlineStr">
         <is>
@@ -42717,16 +42922,21 @@
         </is>
       </c>
       <c r="E313" t="n">
-        <v>205995</v>
+        <v>100092</v>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>Större brunfladdermus</t>
+        </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
@@ -42750,10 +42960,10 @@
         </is>
       </c>
       <c r="Q313" t="n">
-        <v>586488</v>
+        <v>586280</v>
       </c>
       <c r="R313" t="n">
-        <v>6311183</v>
+        <v>6311103</v>
       </c>
       <c r="S313" t="n">
         <v>5</v>
@@ -42785,7 +42995,7 @@
       </c>
       <c r="Z313" t="inlineStr">
         <is>
-          <t>22:31</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AA313" t="inlineStr">
@@ -42795,7 +43005,7 @@
       </c>
       <c r="AB313" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>22:52</t>
         </is>
       </c>
       <c r="AC313" t="inlineStr">
@@ -42840,10 +43050,10 @@
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>122254610</v>
+        <v>122254660</v>
       </c>
       <c r="B314" t="n">
-        <v>56290</v>
+        <v>56294</v>
       </c>
       <c r="C314" t="inlineStr">
         <is>
@@ -42858,6 +43068,11 @@
       <c r="E314" t="n">
         <v>205995</v>
       </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
       <c r="G314" t="inlineStr">
         <is>
           <t>Pipistrellus pygmaeus</t>
@@ -42889,10 +43104,10 @@
         </is>
       </c>
       <c r="Q314" t="n">
-        <v>586389</v>
+        <v>586488</v>
       </c>
       <c r="R314" t="n">
-        <v>6311141</v>
+        <v>6311183</v>
       </c>
       <c r="S314" t="n">
         <v>5</v>
@@ -42924,7 +43139,7 @@
       </c>
       <c r="Z314" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:31</t>
         </is>
       </c>
       <c r="AA314" t="inlineStr">
@@ -42934,7 +43149,7 @@
       </c>
       <c r="AB314" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AC314" t="inlineStr">
@@ -42979,10 +43194,10 @@
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>122254612</v>
+        <v>122254652</v>
       </c>
       <c r="B315" t="n">
-        <v>56290</v>
+        <v>56294</v>
       </c>
       <c r="C315" t="inlineStr">
         <is>
@@ -42997,6 +43212,11 @@
       <c r="E315" t="n">
         <v>205995</v>
       </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
       <c r="G315" t="inlineStr">
         <is>
           <t>Pipistrellus pygmaeus</t>
@@ -43028,10 +43248,10 @@
         </is>
       </c>
       <c r="Q315" t="n">
-        <v>586371</v>
+        <v>586432</v>
       </c>
       <c r="R315" t="n">
-        <v>6311135</v>
+        <v>6311118</v>
       </c>
       <c r="S315" t="n">
         <v>5</v>
@@ -43063,7 +43283,7 @@
       </c>
       <c r="Z315" t="inlineStr">
         <is>
-          <t>22:59</t>
+          <t>22:34</t>
         </is>
       </c>
       <c r="AA315" t="inlineStr">
@@ -43073,7 +43293,7 @@
       </c>
       <c r="AB315" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="AC315" t="inlineStr">
@@ -43118,10 +43338,10 @@
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>122254343</v>
+        <v>122254957</v>
       </c>
       <c r="B316" t="n">
-        <v>56285</v>
+        <v>56282</v>
       </c>
       <c r="C316" t="inlineStr">
         <is>
@@ -43134,16 +43354,21 @@
         </is>
       </c>
       <c r="E316" t="n">
-        <v>100092</v>
+        <v>205992</v>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>Vattenfladdermus</t>
+        </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
@@ -43167,10 +43392,10 @@
         </is>
       </c>
       <c r="Q316" t="n">
-        <v>586388</v>
+        <v>586444</v>
       </c>
       <c r="R316" t="n">
-        <v>6311142</v>
+        <v>6311160</v>
       </c>
       <c r="S316" t="n">
         <v>5</v>
@@ -43202,7 +43427,7 @@
       </c>
       <c r="Z316" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="AA316" t="inlineStr">
@@ -43212,7 +43437,7 @@
       </c>
       <c r="AB316" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AC316" t="inlineStr">
@@ -43257,10 +43482,10 @@
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>122254373</v>
+        <v>122254959</v>
       </c>
       <c r="B317" t="n">
-        <v>56285</v>
+        <v>56282</v>
       </c>
       <c r="C317" t="inlineStr">
         <is>
@@ -43273,16 +43498,21 @@
         </is>
       </c>
       <c r="E317" t="n">
-        <v>100092</v>
+        <v>205992</v>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>Vattenfladdermus</t>
+        </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
@@ -43306,10 +43536,10 @@
         </is>
       </c>
       <c r="Q317" t="n">
-        <v>586307</v>
+        <v>586370</v>
       </c>
       <c r="R317" t="n">
-        <v>6311133</v>
+        <v>6311139</v>
       </c>
       <c r="S317" t="n">
         <v>5</v>
@@ -43341,7 +43571,7 @@
       </c>
       <c r="Z317" t="inlineStr">
         <is>
-          <t>22:49</t>
+          <t>22:59</t>
         </is>
       </c>
       <c r="AA317" t="inlineStr">
@@ -43351,7 +43581,7 @@
       </c>
       <c r="AB317" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AC317" t="inlineStr">
@@ -43396,10 +43626,10 @@
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>122254503</v>
+        <v>122254519</v>
       </c>
       <c r="B318" t="n">
-        <v>56271</v>
+        <v>56275</v>
       </c>
       <c r="C318" t="inlineStr">
         <is>
@@ -43414,6 +43644,11 @@
       <c r="E318" t="n">
         <v>205998</v>
       </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
       <c r="G318" t="inlineStr">
         <is>
           <t>Eptesicus nilssonii</t>
@@ -43445,10 +43680,10 @@
         </is>
       </c>
       <c r="Q318" t="n">
-        <v>586313</v>
+        <v>586424</v>
       </c>
       <c r="R318" t="n">
-        <v>6311124</v>
+        <v>6311135</v>
       </c>
       <c r="S318" t="n">
         <v>5</v>
@@ -43480,7 +43715,7 @@
       </c>
       <c r="Z318" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AA318" t="inlineStr">
@@ -43490,7 +43725,7 @@
       </c>
       <c r="AB318" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>22:38</t>
         </is>
       </c>
       <c r="AC318" t="inlineStr">
@@ -43535,10 +43770,10 @@
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>122254655</v>
+        <v>122254648</v>
       </c>
       <c r="B319" t="n">
-        <v>56290</v>
+        <v>56294</v>
       </c>
       <c r="C319" t="inlineStr">
         <is>
@@ -43553,6 +43788,11 @@
       <c r="E319" t="n">
         <v>205995</v>
       </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
       <c r="G319" t="inlineStr">
         <is>
           <t>Pipistrellus pygmaeus</t>
@@ -43584,10 +43824,10 @@
         </is>
       </c>
       <c r="Q319" t="n">
-        <v>586475</v>
+        <v>586418</v>
       </c>
       <c r="R319" t="n">
-        <v>6311187</v>
+        <v>6311107</v>
       </c>
       <c r="S319" t="n">
         <v>5</v>
@@ -43619,7 +43859,7 @@
       </c>
       <c r="Z319" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>22:36</t>
         </is>
       </c>
       <c r="AA319" t="inlineStr">
@@ -43629,7 +43869,7 @@
       </c>
       <c r="AB319" t="inlineStr">
         <is>
-          <t>22:33</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AC319" t="inlineStr">
@@ -43674,10 +43914,10 @@
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>122254959</v>
+        <v>122254650</v>
       </c>
       <c r="B320" t="n">
-        <v>56278</v>
+        <v>56294</v>
       </c>
       <c r="C320" t="inlineStr">
         <is>
@@ -43690,16 +43930,21 @@
         </is>
       </c>
       <c r="E320" t="n">
-        <v>205992</v>
+        <v>205995</v>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
@@ -43723,10 +43968,10 @@
         </is>
       </c>
       <c r="Q320" t="n">
-        <v>586370</v>
+        <v>586422</v>
       </c>
       <c r="R320" t="n">
-        <v>6311139</v>
+        <v>6311105</v>
       </c>
       <c r="S320" t="n">
         <v>5</v>
@@ -43758,7 +44003,7 @@
       </c>
       <c r="Z320" t="inlineStr">
         <is>
-          <t>22:59</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="AA320" t="inlineStr">
@@ -43768,7 +44013,7 @@
       </c>
       <c r="AB320" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:36</t>
         </is>
       </c>
       <c r="AC320" t="inlineStr">
@@ -43813,10 +44058,10 @@
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>122254585</v>
+        <v>122254654</v>
       </c>
       <c r="B321" t="n">
-        <v>56290</v>
+        <v>56294</v>
       </c>
       <c r="C321" t="inlineStr">
         <is>
@@ -43831,6 +44076,11 @@
       <c r="E321" t="n">
         <v>205995</v>
       </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
       <c r="G321" t="inlineStr">
         <is>
           <t>Pipistrellus pygmaeus</t>
@@ -43862,10 +44112,10 @@
         </is>
       </c>
       <c r="Q321" t="n">
-        <v>586455</v>
+        <v>586467</v>
       </c>
       <c r="R321" t="n">
-        <v>6311156</v>
+        <v>6311178</v>
       </c>
       <c r="S321" t="n">
         <v>5</v>
@@ -43897,7 +44147,7 @@
       </c>
       <c r="Z321" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AA321" t="inlineStr">
@@ -43907,7 +44157,7 @@
       </c>
       <c r="AB321" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="AC321" t="inlineStr">
@@ -43952,10 +44202,10 @@
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>122254473</v>
+        <v>122254609</v>
       </c>
       <c r="B322" t="n">
-        <v>56271</v>
+        <v>56294</v>
       </c>
       <c r="C322" t="inlineStr">
         <is>
@@ -43964,20 +44214,25 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E322" t="n">
-        <v>205998</v>
+        <v>205995</v>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
@@ -44001,10 +44256,10 @@
         </is>
       </c>
       <c r="Q322" t="n">
-        <v>586450</v>
+        <v>586392</v>
       </c>
       <c r="R322" t="n">
-        <v>6311152</v>
+        <v>6311147</v>
       </c>
       <c r="S322" t="n">
         <v>5</v>
@@ -44036,7 +44291,7 @@
       </c>
       <c r="Z322" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AA322" t="inlineStr">
@@ -44046,7 +44301,7 @@
       </c>
       <c r="AB322" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AC322" t="inlineStr">
@@ -44091,10 +44346,10 @@
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>122254607</v>
+        <v>122254956</v>
       </c>
       <c r="B323" t="n">
-        <v>56290</v>
+        <v>56282</v>
       </c>
       <c r="C323" t="inlineStr">
         <is>
@@ -44107,16 +44362,21 @@
         </is>
       </c>
       <c r="E323" t="n">
-        <v>205995</v>
+        <v>205992</v>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>Vattenfladdermus</t>
+        </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
@@ -44140,10 +44400,10 @@
         </is>
       </c>
       <c r="Q323" t="n">
-        <v>586415</v>
+        <v>586441</v>
       </c>
       <c r="R323" t="n">
-        <v>6311149</v>
+        <v>6311152</v>
       </c>
       <c r="S323" t="n">
         <v>5</v>
@@ -44175,7 +44435,7 @@
       </c>
       <c r="Z323" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AA323" t="inlineStr">
@@ -44185,7 +44445,7 @@
       </c>
       <c r="AB323" t="inlineStr">
         <is>
-          <t>23:03</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AC323" t="inlineStr">
@@ -44230,10 +44490,10 @@
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>122254953</v>
+        <v>122254835</v>
       </c>
       <c r="B324" t="n">
-        <v>56278</v>
+        <v>56292</v>
       </c>
       <c r="C324" t="inlineStr">
         <is>
@@ -44246,16 +44506,21 @@
         </is>
       </c>
       <c r="E324" t="n">
-        <v>205992</v>
+        <v>100111</v>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>Trollpipistrell</t>
+        </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
@@ -44279,10 +44544,10 @@
         </is>
       </c>
       <c r="Q324" t="n">
-        <v>586449</v>
+        <v>586473</v>
       </c>
       <c r="R324" t="n">
-        <v>6311155</v>
+        <v>6311192</v>
       </c>
       <c r="S324" t="n">
         <v>5</v>
@@ -44314,7 +44579,7 @@
       </c>
       <c r="Z324" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AA324" t="inlineStr">
@@ -44324,7 +44589,7 @@
       </c>
       <c r="AB324" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AC324" t="inlineStr">
@@ -44369,10 +44634,10 @@
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>122254843</v>
+        <v>122254877</v>
       </c>
       <c r="B325" t="n">
-        <v>56288</v>
+        <v>56292</v>
       </c>
       <c r="C325" t="inlineStr">
         <is>
@@ -44387,6 +44652,11 @@
       <c r="E325" t="n">
         <v>100111</v>
       </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>Trollpipistrell</t>
+        </is>
+      </c>
       <c r="G325" t="inlineStr">
         <is>
           <t>Pipistrellus nathusii</t>
@@ -44418,10 +44688,10 @@
         </is>
       </c>
       <c r="Q325" t="n">
-        <v>586389</v>
+        <v>586276</v>
       </c>
       <c r="R325" t="n">
-        <v>6311142</v>
+        <v>6311100</v>
       </c>
       <c r="S325" t="n">
         <v>5</v>
@@ -44453,7 +44723,7 @@
       </c>
       <c r="Z325" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AA325" t="inlineStr">
@@ -44463,7 +44733,7 @@
       </c>
       <c r="AB325" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>22:52</t>
         </is>
       </c>
       <c r="AC325" t="inlineStr">
@@ -44508,10 +44778,10 @@
     </row>
     <row r="326">
       <c r="A326" t="n">
-        <v>122254472</v>
+        <v>122254412</v>
       </c>
       <c r="B326" t="n">
-        <v>56271</v>
+        <v>56289</v>
       </c>
       <c r="C326" t="inlineStr">
         <is>
@@ -44520,20 +44790,25 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E326" t="n">
-        <v>205998</v>
+        <v>100092</v>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>Större brunfladdermus</t>
+        </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
@@ -44557,10 +44832,10 @@
         </is>
       </c>
       <c r="Q326" t="n">
-        <v>586455</v>
+        <v>586424</v>
       </c>
       <c r="R326" t="n">
-        <v>6311159</v>
+        <v>6311135</v>
       </c>
       <c r="S326" t="n">
         <v>5</v>
@@ -44592,7 +44867,7 @@
       </c>
       <c r="Z326" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AA326" t="inlineStr">
@@ -44602,7 +44877,7 @@
       </c>
       <c r="AB326" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>22:38</t>
         </is>
       </c>
       <c r="AC326" t="inlineStr">
@@ -44647,10 +44922,10 @@
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>122254643</v>
+        <v>122254634</v>
       </c>
       <c r="B327" t="n">
-        <v>56290</v>
+        <v>56294</v>
       </c>
       <c r="C327" t="inlineStr">
         <is>
@@ -44665,6 +44940,11 @@
       <c r="E327" t="n">
         <v>205995</v>
       </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
       <c r="G327" t="inlineStr">
         <is>
           <t>Pipistrellus pygmaeus</t>
@@ -44696,10 +44976,10 @@
         </is>
       </c>
       <c r="Q327" t="n">
-        <v>586424</v>
+        <v>586415</v>
       </c>
       <c r="R327" t="n">
-        <v>6311135</v>
+        <v>6311148</v>
       </c>
       <c r="S327" t="n">
         <v>5</v>
@@ -44731,7 +45011,7 @@
       </c>
       <c r="Z327" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AA327" t="inlineStr">
@@ -44741,7 +45021,7 @@
       </c>
       <c r="AB327" t="inlineStr">
         <is>
-          <t>22:38</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AC327" t="inlineStr">
@@ -44786,10 +45066,10 @@
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>122254310</v>
+        <v>122254964</v>
       </c>
       <c r="B328" t="n">
-        <v>56285</v>
+        <v>56282</v>
       </c>
       <c r="C328" t="inlineStr">
         <is>
@@ -44802,16 +45082,21 @@
         </is>
       </c>
       <c r="E328" t="n">
-        <v>100092</v>
+        <v>205992</v>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>Vattenfladdermus</t>
+        </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
@@ -44835,10 +45120,10 @@
         </is>
       </c>
       <c r="Q328" t="n">
-        <v>586452</v>
+        <v>586430</v>
       </c>
       <c r="R328" t="n">
-        <v>6311156</v>
+        <v>6311142</v>
       </c>
       <c r="S328" t="n">
         <v>5</v>
@@ -44870,7 +45155,7 @@
       </c>
       <c r="Z328" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="AA328" t="inlineStr">
@@ -44880,7 +45165,7 @@
       </c>
       <c r="AB328" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>22:34</t>
         </is>
       </c>
       <c r="AC328" t="inlineStr">
@@ -44925,10 +45210,10 @@
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>122254391</v>
+        <v>122254627</v>
       </c>
       <c r="B329" t="n">
-        <v>56285</v>
+        <v>56294</v>
       </c>
       <c r="C329" t="inlineStr">
         <is>
@@ -44941,16 +45226,21 @@
         </is>
       </c>
       <c r="E329" t="n">
-        <v>100092</v>
+        <v>205995</v>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
@@ -44974,10 +45264,10 @@
         </is>
       </c>
       <c r="Q329" t="n">
-        <v>586379</v>
+        <v>586306</v>
       </c>
       <c r="R329" t="n">
-        <v>6311136</v>
+        <v>6311131</v>
       </c>
       <c r="S329" t="n">
         <v>5</v>
@@ -45009,7 +45299,7 @@
       </c>
       <c r="Z329" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AA329" t="inlineStr">
@@ -45019,7 +45309,7 @@
       </c>
       <c r="AB329" t="inlineStr">
         <is>
-          <t>22:46</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AC329" t="inlineStr">
@@ -45064,10 +45354,10 @@
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>122254369</v>
+        <v>122254607</v>
       </c>
       <c r="B330" t="n">
-        <v>56285</v>
+        <v>56294</v>
       </c>
       <c r="C330" t="inlineStr">
         <is>
@@ -45080,16 +45370,21 @@
         </is>
       </c>
       <c r="E330" t="n">
-        <v>100092</v>
+        <v>205995</v>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
@@ -45113,10 +45408,10 @@
         </is>
       </c>
       <c r="Q330" t="n">
-        <v>586300</v>
+        <v>586415</v>
       </c>
       <c r="R330" t="n">
-        <v>6311112</v>
+        <v>6311149</v>
       </c>
       <c r="S330" t="n">
         <v>5</v>
@@ -45148,7 +45443,7 @@
       </c>
       <c r="Z330" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AA330" t="inlineStr">
@@ -45158,7 +45453,7 @@
       </c>
       <c r="AB330" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>23:03</t>
         </is>
       </c>
       <c r="AC330" t="inlineStr">
@@ -45203,10 +45498,10 @@
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>122254954</v>
+        <v>122254514</v>
       </c>
       <c r="B331" t="n">
-        <v>56278</v>
+        <v>56275</v>
       </c>
       <c r="C331" t="inlineStr">
         <is>
@@ -45215,20 +45510,25 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E331" t="n">
-        <v>205992</v>
+        <v>205998</v>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I331" t="inlineStr">
@@ -45252,10 +45552,10 @@
         </is>
       </c>
       <c r="Q331" t="n">
-        <v>586442</v>
+        <v>586408</v>
       </c>
       <c r="R331" t="n">
-        <v>6311152</v>
+        <v>6311124</v>
       </c>
       <c r="S331" t="n">
         <v>5</v>
@@ -45287,7 +45587,7 @@
       </c>
       <c r="Z331" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>22:43</t>
         </is>
       </c>
       <c r="AA331" t="inlineStr">
@@ -45297,7 +45597,7 @@
       </c>
       <c r="AB331" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AC331" t="inlineStr">
@@ -45342,10 +45642,10 @@
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>122254857</v>
+        <v>122254390</v>
       </c>
       <c r="B332" t="n">
-        <v>56288</v>
+        <v>56289</v>
       </c>
       <c r="C332" t="inlineStr">
         <is>
@@ -45358,16 +45658,21 @@
         </is>
       </c>
       <c r="E332" t="n">
-        <v>100111</v>
+        <v>100092</v>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>Större brunfladdermus</t>
+        </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
@@ -45391,10 +45696,10 @@
         </is>
       </c>
       <c r="Q332" t="n">
-        <v>586317</v>
+        <v>586374</v>
       </c>
       <c r="R332" t="n">
-        <v>6311115</v>
+        <v>6311139</v>
       </c>
       <c r="S332" t="n">
         <v>5</v>
@@ -45426,7 +45731,7 @@
       </c>
       <c r="Z332" t="inlineStr">
         <is>
-          <t>22:57</t>
+          <t>22:46</t>
         </is>
       </c>
       <c r="AA332" t="inlineStr">
@@ -45436,7 +45741,7 @@
       </c>
       <c r="AB332" t="inlineStr">
         <is>
-          <t>22:58</t>
+          <t>22:47</t>
         </is>
       </c>
       <c r="AC332" t="inlineStr">
@@ -45481,10 +45786,10 @@
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>122254877</v>
+        <v>122254966</v>
       </c>
       <c r="B333" t="n">
-        <v>56288</v>
+        <v>56282</v>
       </c>
       <c r="C333" t="inlineStr">
         <is>
@@ -45497,16 +45802,21 @@
         </is>
       </c>
       <c r="E333" t="n">
-        <v>100111</v>
+        <v>205992</v>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>Vattenfladdermus</t>
+        </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
@@ -45530,10 +45840,10 @@
         </is>
       </c>
       <c r="Q333" t="n">
-        <v>586276</v>
+        <v>586467</v>
       </c>
       <c r="R333" t="n">
-        <v>6311100</v>
+        <v>6311178</v>
       </c>
       <c r="S333" t="n">
         <v>5</v>
@@ -45565,7 +45875,7 @@
       </c>
       <c r="Z333" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AA333" t="inlineStr">
@@ -45575,7 +45885,7 @@
       </c>
       <c r="AB333" t="inlineStr">
         <is>
-          <t>22:52</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="AC333" t="inlineStr">
@@ -45620,10 +45930,10 @@
     </row>
     <row r="334">
       <c r="A334" t="n">
-        <v>122254498</v>
+        <v>122254651</v>
       </c>
       <c r="B334" t="n">
-        <v>56271</v>
+        <v>56294</v>
       </c>
       <c r="C334" t="inlineStr">
         <is>
@@ -45632,20 +45942,25 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E334" t="n">
-        <v>205998</v>
+        <v>205995</v>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
@@ -45669,10 +45984,10 @@
         </is>
       </c>
       <c r="Q334" t="n">
-        <v>586393</v>
+        <v>586425</v>
       </c>
       <c r="R334" t="n">
-        <v>6311147</v>
+        <v>6311113</v>
       </c>
       <c r="S334" t="n">
         <v>5</v>
@@ -45704,7 +46019,7 @@
       </c>
       <c r="Z334" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="AA334" t="inlineStr">
@@ -45714,7 +46029,7 @@
       </c>
       <c r="AB334" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>22:36</t>
         </is>
       </c>
       <c r="AC334" t="inlineStr">
@@ -45759,10 +46074,10 @@
     </row>
     <row r="335">
       <c r="A335" t="n">
-        <v>122254835</v>
+        <v>122254612</v>
       </c>
       <c r="B335" t="n">
-        <v>56288</v>
+        <v>56294</v>
       </c>
       <c r="C335" t="inlineStr">
         <is>
@@ -45775,16 +46090,21 @@
         </is>
       </c>
       <c r="E335" t="n">
-        <v>100111</v>
+        <v>205995</v>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I335" t="inlineStr">
@@ -45808,10 +46128,10 @@
         </is>
       </c>
       <c r="Q335" t="n">
-        <v>586473</v>
+        <v>586371</v>
       </c>
       <c r="R335" t="n">
-        <v>6311192</v>
+        <v>6311135</v>
       </c>
       <c r="S335" t="n">
         <v>5</v>
@@ -45843,7 +46163,7 @@
       </c>
       <c r="Z335" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>22:59</t>
         </is>
       </c>
       <c r="AA335" t="inlineStr">
@@ -45853,7 +46173,7 @@
       </c>
       <c r="AB335" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AC335" t="inlineStr">
@@ -45898,10 +46218,10 @@
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>122254649</v>
+        <v>122254644</v>
       </c>
       <c r="B336" t="n">
-        <v>56290</v>
+        <v>56294</v>
       </c>
       <c r="C336" t="inlineStr">
         <is>
@@ -45916,6 +46236,11 @@
       <c r="E336" t="n">
         <v>205995</v>
       </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
       <c r="G336" t="inlineStr">
         <is>
           <t>Pipistrellus pygmaeus</t>
@@ -45947,10 +46272,10 @@
         </is>
       </c>
       <c r="Q336" t="n">
-        <v>586422</v>
+        <v>586429</v>
       </c>
       <c r="R336" t="n">
-        <v>6311100</v>
+        <v>6311115</v>
       </c>
       <c r="S336" t="n">
         <v>5</v>
@@ -45982,7 +46307,7 @@
       </c>
       <c r="Z336" t="inlineStr">
         <is>
-          <t>22:35</t>
+          <t>22:36</t>
         </is>
       </c>
       <c r="AA336" t="inlineStr">
@@ -45992,7 +46317,7 @@
       </c>
       <c r="AB336" t="inlineStr">
         <is>
-          <t>22:36</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AC336" t="inlineStr">
@@ -46037,10 +46362,10 @@
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>122254608</v>
+        <v>122254633</v>
       </c>
       <c r="B337" t="n">
-        <v>56290</v>
+        <v>56294</v>
       </c>
       <c r="C337" t="inlineStr">
         <is>
@@ -46055,6 +46380,11 @@
       <c r="E337" t="n">
         <v>205995</v>
       </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
       <c r="G337" t="inlineStr">
         <is>
           <t>Pipistrellus pygmaeus</t>
@@ -46086,10 +46416,10 @@
         </is>
       </c>
       <c r="Q337" t="n">
-        <v>586393</v>
+        <v>586396</v>
       </c>
       <c r="R337" t="n">
-        <v>6311147</v>
+        <v>6311146</v>
       </c>
       <c r="S337" t="n">
         <v>5</v>
@@ -46121,7 +46451,7 @@
       </c>
       <c r="Z337" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AA337" t="inlineStr">
@@ -46131,7 +46461,7 @@
       </c>
       <c r="AB337" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AC337" t="inlineStr">
@@ -46176,10 +46506,10 @@
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>122254513</v>
+        <v>122254341</v>
       </c>
       <c r="B338" t="n">
-        <v>56271</v>
+        <v>56289</v>
       </c>
       <c r="C338" t="inlineStr">
         <is>
@@ -46188,20 +46518,25 @@
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E338" t="n">
-        <v>205998</v>
+        <v>100092</v>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>Större brunfladdermus</t>
+        </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
@@ -46225,7 +46560,7 @@
         </is>
       </c>
       <c r="Q338" t="n">
-        <v>586396</v>
+        <v>586415</v>
       </c>
       <c r="R338" t="n">
         <v>6311146</v>
@@ -46260,7 +46595,7 @@
       </c>
       <c r="Z338" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AA338" t="inlineStr">
@@ -46270,7 +46605,7 @@
       </c>
       <c r="AB338" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>23:03</t>
         </is>
       </c>
       <c r="AC338" t="inlineStr">
@@ -46315,10 +46650,10 @@
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>122254499</v>
+        <v>122254343</v>
       </c>
       <c r="B339" t="n">
-        <v>56271</v>
+        <v>56289</v>
       </c>
       <c r="C339" t="inlineStr">
         <is>
@@ -46327,20 +46662,25 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E339" t="n">
-        <v>205998</v>
+        <v>100092</v>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>Större brunfladdermus</t>
+        </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I339" t="inlineStr">
@@ -46364,10 +46704,10 @@
         </is>
       </c>
       <c r="Q339" t="n">
-        <v>586392</v>
+        <v>586388</v>
       </c>
       <c r="R339" t="n">
-        <v>6311147</v>
+        <v>6311142</v>
       </c>
       <c r="S339" t="n">
         <v>5</v>
@@ -46399,17 +46739,17 @@
       </c>
       <c r="Z339" t="inlineStr">
         <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="AA339" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AB339" t="inlineStr">
+        <is>
           <t>23:01</t>
-        </is>
-      </c>
-      <c r="AA339" t="inlineStr">
-        <is>
-          <t>2024-06-26</t>
-        </is>
-      </c>
-      <c r="AB339" t="inlineStr">
-        <is>
-          <t>23:02</t>
         </is>
       </c>
       <c r="AC339" t="inlineStr">
@@ -46454,10 +46794,10 @@
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>122254625</v>
+        <v>122254370</v>
       </c>
       <c r="B340" t="n">
-        <v>56290</v>
+        <v>56289</v>
       </c>
       <c r="C340" t="inlineStr">
         <is>
@@ -46470,16 +46810,21 @@
         </is>
       </c>
       <c r="E340" t="n">
-        <v>205995</v>
+        <v>100092</v>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>Större brunfladdermus</t>
+        </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
@@ -46593,10 +46938,10 @@
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>122254651</v>
+        <v>122254963</v>
       </c>
       <c r="B341" t="n">
-        <v>56290</v>
+        <v>56282</v>
       </c>
       <c r="C341" t="inlineStr">
         <is>
@@ -46609,16 +46954,21 @@
         </is>
       </c>
       <c r="E341" t="n">
-        <v>205995</v>
+        <v>205992</v>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>Vattenfladdermus</t>
+        </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I341" t="inlineStr">
@@ -46642,10 +46992,10 @@
         </is>
       </c>
       <c r="Q341" t="n">
-        <v>586425</v>
+        <v>586374</v>
       </c>
       <c r="R341" t="n">
-        <v>6311113</v>
+        <v>6311140</v>
       </c>
       <c r="S341" t="n">
         <v>5</v>
@@ -46677,7 +47027,7 @@
       </c>
       <c r="Z341" t="inlineStr">
         <is>
-          <t>22:35</t>
+          <t>22:46</t>
         </is>
       </c>
       <c r="AA341" t="inlineStr">
@@ -46687,7 +47037,7 @@
       </c>
       <c r="AB341" t="inlineStr">
         <is>
-          <t>22:36</t>
+          <t>22:47</t>
         </is>
       </c>
       <c r="AC341" t="inlineStr">
@@ -46732,10 +47082,10 @@
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>122254654</v>
+        <v>122254606</v>
       </c>
       <c r="B342" t="n">
-        <v>56290</v>
+        <v>56294</v>
       </c>
       <c r="C342" t="inlineStr">
         <is>
@@ -46750,6 +47100,11 @@
       <c r="E342" t="n">
         <v>205995</v>
       </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
       <c r="G342" t="inlineStr">
         <is>
           <t>Pipistrellus pygmaeus</t>
@@ -46781,10 +47136,10 @@
         </is>
       </c>
       <c r="Q342" t="n">
-        <v>586467</v>
+        <v>586415</v>
       </c>
       <c r="R342" t="n">
-        <v>6311178</v>
+        <v>6311146</v>
       </c>
       <c r="S342" t="n">
         <v>5</v>
@@ -46816,7 +47171,7 @@
       </c>
       <c r="Z342" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AA342" t="inlineStr">
@@ -46826,7 +47181,7 @@
       </c>
       <c r="AB342" t="inlineStr">
         <is>
-          <t>22:33</t>
+          <t>23:03</t>
         </is>
       </c>
       <c r="AC342" t="inlineStr">
@@ -46871,10 +47226,10 @@
     </row>
     <row r="343">
       <c r="A343" t="n">
-        <v>122254632</v>
+        <v>122254656</v>
       </c>
       <c r="B343" t="n">
-        <v>56290</v>
+        <v>56294</v>
       </c>
       <c r="C343" t="inlineStr">
         <is>
@@ -46889,6 +47244,11 @@
       <c r="E343" t="n">
         <v>205995</v>
       </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
       <c r="G343" t="inlineStr">
         <is>
           <t>Pipistrellus pygmaeus</t>
@@ -46920,10 +47280,10 @@
         </is>
       </c>
       <c r="Q343" t="n">
-        <v>586374</v>
+        <v>586483</v>
       </c>
       <c r="R343" t="n">
-        <v>6311140</v>
+        <v>6311186</v>
       </c>
       <c r="S343" t="n">
         <v>5</v>
@@ -46955,7 +47315,7 @@
       </c>
       <c r="Z343" t="inlineStr">
         <is>
-          <t>22:46</t>
+          <t>22:31</t>
         </is>
       </c>
       <c r="AA343" t="inlineStr">
@@ -46965,7 +47325,7 @@
       </c>
       <c r="AB343" t="inlineStr">
         <is>
-          <t>22:47</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AC343" t="inlineStr">
@@ -47010,10 +47370,10 @@
     </row>
     <row r="344">
       <c r="A344" t="n">
-        <v>122254646</v>
+        <v>122254513</v>
       </c>
       <c r="B344" t="n">
-        <v>56290</v>
+        <v>56275</v>
       </c>
       <c r="C344" t="inlineStr">
         <is>
@@ -47022,20 +47382,25 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E344" t="n">
-        <v>205995</v>
+        <v>205998</v>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
@@ -47059,10 +47424,10 @@
         </is>
       </c>
       <c r="Q344" t="n">
-        <v>586422</v>
+        <v>586396</v>
       </c>
       <c r="R344" t="n">
-        <v>6311111</v>
+        <v>6311146</v>
       </c>
       <c r="S344" t="n">
         <v>5</v>
@@ -47094,7 +47459,7 @@
       </c>
       <c r="Z344" t="inlineStr">
         <is>
-          <t>22:36</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AA344" t="inlineStr">
@@ -47104,7 +47469,7 @@
       </c>
       <c r="AB344" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AC344" t="inlineStr">
@@ -47149,10 +47514,10 @@
     </row>
     <row r="345">
       <c r="A345" t="n">
-        <v>122254372</v>
+        <v>122254512</v>
       </c>
       <c r="B345" t="n">
-        <v>56285</v>
+        <v>56275</v>
       </c>
       <c r="C345" t="inlineStr">
         <is>
@@ -47161,20 +47526,25 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E345" t="n">
-        <v>100092</v>
+        <v>205998</v>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
@@ -47198,10 +47568,10 @@
         </is>
       </c>
       <c r="Q345" t="n">
-        <v>586306</v>
+        <v>586379</v>
       </c>
       <c r="R345" t="n">
-        <v>6311131</v>
+        <v>6311136</v>
       </c>
       <c r="S345" t="n">
         <v>5</v>
@@ -47233,7 +47603,7 @@
       </c>
       <c r="Z345" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AA345" t="inlineStr">
@@ -47243,7 +47613,7 @@
       </c>
       <c r="AB345" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>22:46</t>
         </is>
       </c>
       <c r="AC345" t="inlineStr">
@@ -47288,10 +47658,10 @@
     </row>
     <row r="346">
       <c r="A346" t="n">
-        <v>122254307</v>
+        <v>122254392</v>
       </c>
       <c r="B346" t="n">
-        <v>56285</v>
+        <v>56289</v>
       </c>
       <c r="C346" t="inlineStr">
         <is>
@@ -47306,6 +47676,11 @@
       <c r="E346" t="n">
         <v>100092</v>
       </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>Större brunfladdermus</t>
+        </is>
+      </c>
       <c r="G346" t="inlineStr">
         <is>
           <t>Nyctalus noctula</t>
@@ -47337,10 +47712,10 @@
         </is>
       </c>
       <c r="Q346" t="n">
-        <v>586477</v>
+        <v>586384</v>
       </c>
       <c r="R346" t="n">
-        <v>6311186</v>
+        <v>6311139</v>
       </c>
       <c r="S346" t="n">
         <v>5</v>
@@ -47372,7 +47747,7 @@
       </c>
       <c r="Z346" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AA346" t="inlineStr">
@@ -47382,7 +47757,7 @@
       </c>
       <c r="AB346" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>22:46</t>
         </is>
       </c>
       <c r="AC346" t="inlineStr">
@@ -47427,10 +47802,10 @@
     </row>
     <row r="347">
       <c r="A347" t="n">
-        <v>122254314</v>
+        <v>122254584</v>
       </c>
       <c r="B347" t="n">
-        <v>56285</v>
+        <v>56294</v>
       </c>
       <c r="C347" t="inlineStr">
         <is>
@@ -47443,16 +47818,21 @@
         </is>
       </c>
       <c r="E347" t="n">
-        <v>100092</v>
+        <v>205995</v>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I347" t="inlineStr">
@@ -47476,10 +47856,10 @@
         </is>
       </c>
       <c r="Q347" t="n">
-        <v>586443</v>
+        <v>586473</v>
       </c>
       <c r="R347" t="n">
-        <v>6311164</v>
+        <v>6311192</v>
       </c>
       <c r="S347" t="n">
         <v>5</v>
@@ -47511,7 +47891,7 @@
       </c>
       <c r="Z347" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AA347" t="inlineStr">
@@ -47521,7 +47901,7 @@
       </c>
       <c r="AB347" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AC347" t="inlineStr">
@@ -47566,10 +47946,10 @@
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>122254309</v>
+        <v>122254474</v>
       </c>
       <c r="B348" t="n">
-        <v>56285</v>
+        <v>56275</v>
       </c>
       <c r="C348" t="inlineStr">
         <is>
@@ -47578,20 +47958,25 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E348" t="n">
-        <v>100092</v>
+        <v>205998</v>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I348" t="inlineStr">
@@ -47615,10 +48000,10 @@
         </is>
       </c>
       <c r="Q348" t="n">
-        <v>586456</v>
+        <v>586443</v>
       </c>
       <c r="R348" t="n">
-        <v>6311158</v>
+        <v>6311164</v>
       </c>
       <c r="S348" t="n">
         <v>5</v>
@@ -47650,7 +48035,7 @@
       </c>
       <c r="Z348" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AA348" t="inlineStr">
@@ -47660,7 +48045,7 @@
       </c>
       <c r="AB348" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AC348" t="inlineStr">
@@ -47705,10 +48090,10 @@
     </row>
     <row r="349">
       <c r="A349" t="n">
-        <v>122254862</v>
+        <v>122254588</v>
       </c>
       <c r="B349" t="n">
-        <v>56288</v>
+        <v>56294</v>
       </c>
       <c r="C349" t="inlineStr">
         <is>
@@ -47721,16 +48106,21 @@
         </is>
       </c>
       <c r="E349" t="n">
-        <v>100111</v>
+        <v>205995</v>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I349" t="inlineStr">
@@ -47754,10 +48144,10 @@
         </is>
       </c>
       <c r="Q349" t="n">
-        <v>586288</v>
+        <v>586415</v>
       </c>
       <c r="R349" t="n">
-        <v>6311100</v>
+        <v>6311196</v>
       </c>
       <c r="S349" t="n">
         <v>5</v>
@@ -47789,7 +48179,7 @@
       </c>
       <c r="Z349" t="inlineStr">
         <is>
-          <t>22:55</t>
+          <t>23:22</t>
         </is>
       </c>
       <c r="AA349" t="inlineStr">
@@ -47799,7 +48189,7 @@
       </c>
       <c r="AB349" t="inlineStr">
         <is>
-          <t>22:56</t>
+          <t>23:23</t>
         </is>
       </c>
       <c r="AC349" t="inlineStr">
@@ -47844,10 +48234,10 @@
     </row>
     <row r="350">
       <c r="A350" t="n">
-        <v>122254317</v>
+        <v>122254855</v>
       </c>
       <c r="B350" t="n">
-        <v>56285</v>
+        <v>56292</v>
       </c>
       <c r="C350" t="inlineStr">
         <is>
@@ -47860,16 +48250,21 @@
         </is>
       </c>
       <c r="E350" t="n">
-        <v>100092</v>
+        <v>100111</v>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>Trollpipistrell</t>
+        </is>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I350" t="inlineStr">
@@ -47893,10 +48288,10 @@
         </is>
       </c>
       <c r="Q350" t="n">
-        <v>586438</v>
+        <v>586330</v>
       </c>
       <c r="R350" t="n">
-        <v>6311222</v>
+        <v>6311120</v>
       </c>
       <c r="S350" t="n">
         <v>5</v>
@@ -47928,7 +48323,7 @@
       </c>
       <c r="Z350" t="inlineStr">
         <is>
-          <t>23:22</t>
+          <t>22:57</t>
         </is>
       </c>
       <c r="AA350" t="inlineStr">
@@ -47938,7 +48333,7 @@
       </c>
       <c r="AB350" t="inlineStr">
         <is>
-          <t>23:23</t>
+          <t>22:58</t>
         </is>
       </c>
       <c r="AC350" t="inlineStr">
@@ -47983,10 +48378,10 @@
     </row>
     <row r="351">
       <c r="A351" t="n">
-        <v>122254341</v>
+        <v>122254587</v>
       </c>
       <c r="B351" t="n">
-        <v>56285</v>
+        <v>56294</v>
       </c>
       <c r="C351" t="inlineStr">
         <is>
@@ -47999,16 +48394,21 @@
         </is>
       </c>
       <c r="E351" t="n">
-        <v>100092</v>
+        <v>205995</v>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I351" t="inlineStr">
@@ -48032,10 +48432,10 @@
         </is>
       </c>
       <c r="Q351" t="n">
-        <v>586415</v>
+        <v>586443</v>
       </c>
       <c r="R351" t="n">
-        <v>6311146</v>
+        <v>6311163</v>
       </c>
       <c r="S351" t="n">
         <v>5</v>
@@ -48067,7 +48467,7 @@
       </c>
       <c r="Z351" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AA351" t="inlineStr">
@@ -48077,7 +48477,7 @@
       </c>
       <c r="AB351" t="inlineStr">
         <is>
-          <t>23:03</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AC351" t="inlineStr">
@@ -48122,10 +48522,10 @@
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>122254411</v>
+        <v>122254503</v>
       </c>
       <c r="B352" t="n">
-        <v>56285</v>
+        <v>56275</v>
       </c>
       <c r="C352" t="inlineStr">
         <is>
@@ -48134,20 +48534,25 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E352" t="n">
-        <v>100092</v>
+        <v>205998</v>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I352" t="inlineStr">
@@ -48171,10 +48576,10 @@
         </is>
       </c>
       <c r="Q352" t="n">
-        <v>586414</v>
+        <v>586313</v>
       </c>
       <c r="R352" t="n">
-        <v>6311126</v>
+        <v>6311124</v>
       </c>
       <c r="S352" t="n">
         <v>5</v>
@@ -48206,7 +48611,7 @@
       </c>
       <c r="Z352" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AA352" t="inlineStr">
@@ -48216,7 +48621,7 @@
       </c>
       <c r="AB352" t="inlineStr">
         <is>
-          <t>22:38</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AC352" t="inlineStr">
@@ -48261,10 +48666,10 @@
     </row>
     <row r="353">
       <c r="A353" t="n">
-        <v>122254421</v>
+        <v>122254499</v>
       </c>
       <c r="B353" t="n">
-        <v>56285</v>
+        <v>56275</v>
       </c>
       <c r="C353" t="inlineStr">
         <is>
@@ -48273,20 +48678,25 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E353" t="n">
-        <v>100092</v>
+        <v>205998</v>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I353" t="inlineStr">
@@ -48310,10 +48720,10 @@
         </is>
       </c>
       <c r="Q353" t="n">
-        <v>586468</v>
+        <v>586392</v>
       </c>
       <c r="R353" t="n">
-        <v>6311181</v>
+        <v>6311147</v>
       </c>
       <c r="S353" t="n">
         <v>5</v>
@@ -48345,7 +48755,7 @@
       </c>
       <c r="Z353" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AA353" t="inlineStr">
@@ -48355,7 +48765,7 @@
       </c>
       <c r="AB353" t="inlineStr">
         <is>
-          <t>22:33</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AC353" t="inlineStr">
@@ -48400,10 +48810,10 @@
     </row>
     <row r="354">
       <c r="A354" t="n">
-        <v>122254414</v>
+        <v>122254643</v>
       </c>
       <c r="B354" t="n">
-        <v>56285</v>
+        <v>56294</v>
       </c>
       <c r="C354" t="inlineStr">
         <is>
@@ -48416,16 +48826,21 @@
         </is>
       </c>
       <c r="E354" t="n">
-        <v>100092</v>
+        <v>205995</v>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I354" t="inlineStr">
@@ -48449,10 +48864,10 @@
         </is>
       </c>
       <c r="Q354" t="n">
-        <v>586423</v>
+        <v>586424</v>
       </c>
       <c r="R354" t="n">
-        <v>6311137</v>
+        <v>6311135</v>
       </c>
       <c r="S354" t="n">
         <v>5</v>
@@ -48539,10 +48954,10 @@
     </row>
     <row r="355">
       <c r="A355" t="n">
-        <v>122254420</v>
+        <v>122254626</v>
       </c>
       <c r="B355" t="n">
-        <v>56285</v>
+        <v>56294</v>
       </c>
       <c r="C355" t="inlineStr">
         <is>
@@ -48555,16 +48970,21 @@
         </is>
       </c>
       <c r="E355" t="n">
-        <v>100092</v>
+        <v>205995</v>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I355" t="inlineStr">
@@ -48588,10 +49008,10 @@
         </is>
       </c>
       <c r="Q355" t="n">
-        <v>586467</v>
+        <v>586313</v>
       </c>
       <c r="R355" t="n">
-        <v>6311178</v>
+        <v>6311124</v>
       </c>
       <c r="S355" t="n">
         <v>5</v>
@@ -48623,7 +49043,7 @@
       </c>
       <c r="Z355" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AA355" t="inlineStr">
@@ -48633,7 +49053,7 @@
       </c>
       <c r="AB355" t="inlineStr">
         <is>
-          <t>22:33</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AC355" t="inlineStr">
@@ -48678,10 +49098,10 @@
     </row>
     <row r="356">
       <c r="A356" t="n">
-        <v>122254854</v>
+        <v>122254307</v>
       </c>
       <c r="B356" t="n">
-        <v>56288</v>
+        <v>56289</v>
       </c>
       <c r="C356" t="inlineStr">
         <is>
@@ -48694,16 +49114,21 @@
         </is>
       </c>
       <c r="E356" t="n">
-        <v>100111</v>
+        <v>100092</v>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>Större brunfladdermus</t>
+        </is>
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I356" t="inlineStr">
@@ -48727,10 +49152,10 @@
         </is>
       </c>
       <c r="Q356" t="n">
-        <v>586329</v>
+        <v>586477</v>
       </c>
       <c r="R356" t="n">
-        <v>6311120</v>
+        <v>6311186</v>
       </c>
       <c r="S356" t="n">
         <v>5</v>
@@ -48762,7 +49187,7 @@
       </c>
       <c r="Z356" t="inlineStr">
         <is>
-          <t>22:57</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AA356" t="inlineStr">
@@ -48772,7 +49197,7 @@
       </c>
       <c r="AB356" t="inlineStr">
         <is>
-          <t>22:58</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AC356" t="inlineStr">
@@ -48817,10 +49242,10 @@
     </row>
     <row r="357">
       <c r="A357" t="n">
-        <v>122254475</v>
+        <v>122254318</v>
       </c>
       <c r="B357" t="n">
-        <v>56271</v>
+        <v>56289</v>
       </c>
       <c r="C357" t="inlineStr">
         <is>
@@ -48829,20 +49254,25 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E357" t="n">
-        <v>205998</v>
+        <v>100092</v>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>Större brunfladdermus</t>
+        </is>
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I357" t="inlineStr">
@@ -48866,10 +49296,10 @@
         </is>
       </c>
       <c r="Q357" t="n">
-        <v>586420</v>
+        <v>586455</v>
       </c>
       <c r="R357" t="n">
-        <v>6311166</v>
+        <v>6311228</v>
       </c>
       <c r="S357" t="n">
         <v>5</v>
@@ -48901,17 +49331,17 @@
       </c>
       <c r="Z357" t="inlineStr">
         <is>
+          <t>23:22</t>
+        </is>
+      </c>
+      <c r="AA357" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AB357" t="inlineStr">
+        <is>
           <t>23:23</t>
-        </is>
-      </c>
-      <c r="AA357" t="inlineStr">
-        <is>
-          <t>2024-06-26</t>
-        </is>
-      </c>
-      <c r="AB357" t="inlineStr">
-        <is>
-          <t>23:24</t>
         </is>
       </c>
       <c r="AC357" t="inlineStr">
@@ -48956,10 +49386,10 @@
     </row>
     <row r="358">
       <c r="A358" t="n">
-        <v>122254957</v>
+        <v>122254309</v>
       </c>
       <c r="B358" t="n">
-        <v>56278</v>
+        <v>56289</v>
       </c>
       <c r="C358" t="inlineStr">
         <is>
@@ -48972,16 +49402,21 @@
         </is>
       </c>
       <c r="E358" t="n">
-        <v>205992</v>
+        <v>100092</v>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>Större brunfladdermus</t>
+        </is>
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H358" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I358" t="inlineStr">
@@ -49005,10 +49440,10 @@
         </is>
       </c>
       <c r="Q358" t="n">
-        <v>586444</v>
+        <v>586456</v>
       </c>
       <c r="R358" t="n">
-        <v>6311160</v>
+        <v>6311158</v>
       </c>
       <c r="S358" t="n">
         <v>5</v>
@@ -49040,7 +49475,7 @@
       </c>
       <c r="Z358" t="inlineStr">
         <is>
-          <t>23:24</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AA358" t="inlineStr">
@@ -49050,7 +49485,7 @@
       </c>
       <c r="AB358" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AC358" t="inlineStr">
@@ -49095,10 +49530,10 @@
     </row>
     <row r="359">
       <c r="A359" t="n">
-        <v>122254511</v>
+        <v>122254880</v>
       </c>
       <c r="B359" t="n">
-        <v>56271</v>
+        <v>56292</v>
       </c>
       <c r="C359" t="inlineStr">
         <is>
@@ -49107,20 +49542,25 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E359" t="n">
-        <v>205998</v>
+        <v>100111</v>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>Trollpipistrell</t>
+        </is>
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I359" t="inlineStr">
@@ -49144,10 +49584,10 @@
         </is>
       </c>
       <c r="Q359" t="n">
-        <v>586374</v>
+        <v>586303</v>
       </c>
       <c r="R359" t="n">
-        <v>6311139</v>
+        <v>6311115</v>
       </c>
       <c r="S359" t="n">
         <v>5</v>
@@ -49179,7 +49619,7 @@
       </c>
       <c r="Z359" t="inlineStr">
         <is>
-          <t>22:46</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AA359" t="inlineStr">
@@ -49189,7 +49629,7 @@
       </c>
       <c r="AB359" t="inlineStr">
         <is>
-          <t>22:47</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AC359" t="inlineStr">
@@ -49234,10 +49674,10 @@
     </row>
     <row r="360">
       <c r="A360" t="n">
-        <v>122254956</v>
+        <v>122254313</v>
       </c>
       <c r="B360" t="n">
-        <v>56278</v>
+        <v>56289</v>
       </c>
       <c r="C360" t="inlineStr">
         <is>
@@ -49250,16 +49690,21 @@
         </is>
       </c>
       <c r="E360" t="n">
-        <v>205992</v>
+        <v>100092</v>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>Större brunfladdermus</t>
+        </is>
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I360" t="inlineStr">
@@ -49283,10 +49728,10 @@
         </is>
       </c>
       <c r="Q360" t="n">
-        <v>586441</v>
+        <v>586449</v>
       </c>
       <c r="R360" t="n">
-        <v>6311152</v>
+        <v>6311155</v>
       </c>
       <c r="S360" t="n">
         <v>5</v>
@@ -49318,7 +49763,7 @@
       </c>
       <c r="Z360" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA360" t="inlineStr">
@@ -49328,7 +49773,7 @@
       </c>
       <c r="AB360" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC360" t="inlineStr">
@@ -49373,10 +49818,10 @@
     </row>
     <row r="361">
       <c r="A361" t="n">
-        <v>122254393</v>
+        <v>122254416</v>
       </c>
       <c r="B361" t="n">
-        <v>56285</v>
+        <v>56289</v>
       </c>
       <c r="C361" t="inlineStr">
         <is>
@@ -49391,6 +49836,11 @@
       <c r="E361" t="n">
         <v>100092</v>
       </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>Större brunfladdermus</t>
+        </is>
+      </c>
       <c r="G361" t="inlineStr">
         <is>
           <t>Nyctalus noctula</t>
@@ -49422,10 +49872,10 @@
         </is>
       </c>
       <c r="Q361" t="n">
-        <v>586396</v>
+        <v>586410</v>
       </c>
       <c r="R361" t="n">
-        <v>6311146</v>
+        <v>6311140</v>
       </c>
       <c r="S361" t="n">
         <v>5</v>
@@ -49457,7 +49907,7 @@
       </c>
       <c r="Z361" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="AA361" t="inlineStr">
@@ -49467,7 +49917,7 @@
       </c>
       <c r="AB361" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>22:34</t>
         </is>
       </c>
       <c r="AC361" t="inlineStr">
@@ -49512,10 +49962,10 @@
     </row>
     <row r="362">
       <c r="A362" t="n">
-        <v>122254392</v>
+        <v>122254655</v>
       </c>
       <c r="B362" t="n">
-        <v>56285</v>
+        <v>56294</v>
       </c>
       <c r="C362" t="inlineStr">
         <is>
@@ -49528,16 +49978,21 @@
         </is>
       </c>
       <c r="E362" t="n">
-        <v>100092</v>
+        <v>205995</v>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I362" t="inlineStr">
@@ -49561,10 +50016,10 @@
         </is>
       </c>
       <c r="Q362" t="n">
-        <v>586384</v>
+        <v>586475</v>
       </c>
       <c r="R362" t="n">
-        <v>6311139</v>
+        <v>6311187</v>
       </c>
       <c r="S362" t="n">
         <v>5</v>
@@ -49596,7 +50051,7 @@
       </c>
       <c r="Z362" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AA362" t="inlineStr">
@@ -49606,7 +50061,7 @@
       </c>
       <c r="AB362" t="inlineStr">
         <is>
-          <t>22:46</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="AC362" t="inlineStr">
@@ -49651,10 +50106,10 @@
     </row>
     <row r="363">
       <c r="A363" t="n">
-        <v>122254306</v>
+        <v>122254659</v>
       </c>
       <c r="B363" t="n">
-        <v>56285</v>
+        <v>56294</v>
       </c>
       <c r="C363" t="inlineStr">
         <is>
@@ -49667,16 +50122,21 @@
         </is>
       </c>
       <c r="E363" t="n">
-        <v>100092</v>
+        <v>205995</v>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I363" t="inlineStr">
@@ -49700,10 +50160,10 @@
         </is>
       </c>
       <c r="Q363" t="n">
-        <v>586473</v>
+        <v>586489</v>
       </c>
       <c r="R363" t="n">
-        <v>6311192</v>
+        <v>6311181</v>
       </c>
       <c r="S363" t="n">
         <v>5</v>
@@ -49735,7 +50195,7 @@
       </c>
       <c r="Z363" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>22:31</t>
         </is>
       </c>
       <c r="AA363" t="inlineStr">
@@ -49745,7 +50205,7 @@
       </c>
       <c r="AB363" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AC363" t="inlineStr">
@@ -49790,10 +50250,10 @@
     </row>
     <row r="364">
       <c r="A364" t="n">
-        <v>122254844</v>
+        <v>122254951</v>
       </c>
       <c r="B364" t="n">
-        <v>56288</v>
+        <v>56282</v>
       </c>
       <c r="C364" t="inlineStr">
         <is>
@@ -49806,16 +50266,21 @@
         </is>
       </c>
       <c r="E364" t="n">
-        <v>100111</v>
+        <v>205992</v>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>Vattenfladdermus</t>
+        </is>
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I364" t="inlineStr">
@@ -49839,10 +50304,10 @@
         </is>
       </c>
       <c r="Q364" t="n">
-        <v>586387</v>
+        <v>586459</v>
       </c>
       <c r="R364" t="n">
-        <v>6311141</v>
+        <v>6311154</v>
       </c>
       <c r="S364" t="n">
         <v>5</v>
@@ -49874,7 +50339,7 @@
       </c>
       <c r="Z364" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AA364" t="inlineStr">
@@ -49884,7 +50349,7 @@
       </c>
       <c r="AB364" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AC364" t="inlineStr">
@@ -49929,10 +50394,10 @@
     </row>
     <row r="365">
       <c r="A365" t="n">
-        <v>122254963</v>
+        <v>122254476</v>
       </c>
       <c r="B365" t="n">
-        <v>56278</v>
+        <v>56275</v>
       </c>
       <c r="C365" t="inlineStr">
         <is>
@@ -49941,20 +50406,25 @@
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E365" t="n">
-        <v>205992</v>
+        <v>205998</v>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I365" t="inlineStr">
@@ -49978,10 +50448,10 @@
         </is>
       </c>
       <c r="Q365" t="n">
-        <v>586374</v>
+        <v>586418</v>
       </c>
       <c r="R365" t="n">
-        <v>6311140</v>
+        <v>6311167</v>
       </c>
       <c r="S365" t="n">
         <v>5</v>
@@ -50013,7 +50483,7 @@
       </c>
       <c r="Z365" t="inlineStr">
         <is>
-          <t>22:46</t>
+          <t>23:23</t>
         </is>
       </c>
       <c r="AA365" t="inlineStr">
@@ -50023,7 +50493,7 @@
       </c>
       <c r="AB365" t="inlineStr">
         <is>
-          <t>22:47</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="AC365" t="inlineStr">
@@ -50068,10 +50538,10 @@
     </row>
     <row r="366">
       <c r="A366" t="n">
-        <v>122254519</v>
+        <v>122254316</v>
       </c>
       <c r="B366" t="n">
-        <v>56271</v>
+        <v>56289</v>
       </c>
       <c r="C366" t="inlineStr">
         <is>
@@ -50080,20 +50550,25 @@
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E366" t="n">
-        <v>205998</v>
+        <v>100092</v>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>Större brunfladdermus</t>
+        </is>
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I366" t="inlineStr">
@@ -50117,10 +50592,10 @@
         </is>
       </c>
       <c r="Q366" t="n">
-        <v>586424</v>
+        <v>586423</v>
       </c>
       <c r="R366" t="n">
-        <v>6311135</v>
+        <v>6311166</v>
       </c>
       <c r="S366" t="n">
         <v>5</v>
@@ -50152,7 +50627,7 @@
       </c>
       <c r="Z366" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>23:23</t>
         </is>
       </c>
       <c r="AA366" t="inlineStr">
@@ -50162,7 +50637,7 @@
       </c>
       <c r="AB366" t="inlineStr">
         <is>
-          <t>22:38</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="AC366" t="inlineStr">
@@ -50207,10 +50682,10 @@
     </row>
     <row r="367">
       <c r="A367" t="n">
-        <v>122254496</v>
+        <v>122254611</v>
       </c>
       <c r="B367" t="n">
-        <v>56271</v>
+        <v>56294</v>
       </c>
       <c r="C367" t="inlineStr">
         <is>
@@ -50219,20 +50694,25 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E367" t="n">
-        <v>205998</v>
+        <v>205995</v>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I367" t="inlineStr">
@@ -50256,10 +50736,10 @@
         </is>
       </c>
       <c r="Q367" t="n">
-        <v>586415</v>
+        <v>586370</v>
       </c>
       <c r="R367" t="n">
-        <v>6311146</v>
+        <v>6311139</v>
       </c>
       <c r="S367" t="n">
         <v>5</v>
@@ -50291,7 +50771,7 @@
       </c>
       <c r="Z367" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>22:59</t>
         </is>
       </c>
       <c r="AA367" t="inlineStr">
@@ -50301,7 +50781,7 @@
       </c>
       <c r="AB367" t="inlineStr">
         <is>
-          <t>23:03</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AC367" t="inlineStr">
@@ -50346,10 +50826,10 @@
     </row>
     <row r="368">
       <c r="A368" t="n">
-        <v>122254952</v>
+        <v>122254615</v>
       </c>
       <c r="B368" t="n">
-        <v>56278</v>
+        <v>56294</v>
       </c>
       <c r="C368" t="inlineStr">
         <is>
@@ -50362,16 +50842,21 @@
         </is>
       </c>
       <c r="E368" t="n">
-        <v>205992</v>
+        <v>205995</v>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H368" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I368" t="inlineStr">
@@ -50395,10 +50880,10 @@
         </is>
       </c>
       <c r="Q368" t="n">
-        <v>586455</v>
+        <v>586329</v>
       </c>
       <c r="R368" t="n">
-        <v>6311156</v>
+        <v>6311120</v>
       </c>
       <c r="S368" t="n">
         <v>5</v>
@@ -50430,7 +50915,7 @@
       </c>
       <c r="Z368" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>22:57</t>
         </is>
       </c>
       <c r="AA368" t="inlineStr">
@@ -50440,7 +50925,7 @@
       </c>
       <c r="AB368" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>22:58</t>
         </is>
       </c>
       <c r="AC368" t="inlineStr">
@@ -50485,10 +50970,10 @@
     </row>
     <row r="369">
       <c r="A369" t="n">
-        <v>122254616</v>
+        <v>122254952</v>
       </c>
       <c r="B369" t="n">
-        <v>56290</v>
+        <v>56282</v>
       </c>
       <c r="C369" t="inlineStr">
         <is>
@@ -50501,16 +50986,21 @@
         </is>
       </c>
       <c r="E369" t="n">
-        <v>205995</v>
+        <v>205992</v>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>Vattenfladdermus</t>
+        </is>
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I369" t="inlineStr">
@@ -50534,10 +51024,10 @@
         </is>
       </c>
       <c r="Q369" t="n">
-        <v>586327</v>
+        <v>586455</v>
       </c>
       <c r="R369" t="n">
-        <v>6311118</v>
+        <v>6311156</v>
       </c>
       <c r="S369" t="n">
         <v>5</v>
@@ -50569,7 +51059,7 @@
       </c>
       <c r="Z369" t="inlineStr">
         <is>
-          <t>22:57</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AA369" t="inlineStr">
@@ -50579,7 +51069,7 @@
       </c>
       <c r="AB369" t="inlineStr">
         <is>
-          <t>22:58</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AC369" t="inlineStr">
@@ -50624,10 +51114,10 @@
     </row>
     <row r="370">
       <c r="A370" t="n">
-        <v>122254951</v>
+        <v>122254854</v>
       </c>
       <c r="B370" t="n">
-        <v>56278</v>
+        <v>56292</v>
       </c>
       <c r="C370" t="inlineStr">
         <is>
@@ -50640,16 +51130,21 @@
         </is>
       </c>
       <c r="E370" t="n">
-        <v>205992</v>
+        <v>100111</v>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>Trollpipistrell</t>
+        </is>
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I370" t="inlineStr">
@@ -50673,10 +51168,10 @@
         </is>
       </c>
       <c r="Q370" t="n">
-        <v>586459</v>
+        <v>586329</v>
       </c>
       <c r="R370" t="n">
-        <v>6311154</v>
+        <v>6311120</v>
       </c>
       <c r="S370" t="n">
         <v>5</v>
@@ -50708,7 +51203,7 @@
       </c>
       <c r="Z370" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>22:57</t>
         </is>
       </c>
       <c r="AA370" t="inlineStr">
@@ -50718,7 +51213,7 @@
       </c>
       <c r="AB370" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>22:58</t>
         </is>
       </c>
       <c r="AC370" t="inlineStr">
@@ -50763,10 +51258,10 @@
     </row>
     <row r="371">
       <c r="A371" t="n">
-        <v>122254637</v>
+        <v>122254391</v>
       </c>
       <c r="B371" t="n">
-        <v>56290</v>
+        <v>56289</v>
       </c>
       <c r="C371" t="inlineStr">
         <is>
@@ -50779,16 +51274,21 @@
         </is>
       </c>
       <c r="E371" t="n">
-        <v>205995</v>
+        <v>100092</v>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>Större brunfladdermus</t>
+        </is>
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I371" t="inlineStr">
@@ -50812,10 +51312,10 @@
         </is>
       </c>
       <c r="Q371" t="n">
-        <v>586408</v>
+        <v>586379</v>
       </c>
       <c r="R371" t="n">
-        <v>6311124</v>
+        <v>6311136</v>
       </c>
       <c r="S371" t="n">
         <v>5</v>
@@ -50847,7 +51347,7 @@
       </c>
       <c r="Z371" t="inlineStr">
         <is>
-          <t>22:43</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AA371" t="inlineStr">
@@ -50857,7 +51357,7 @@
       </c>
       <c r="AB371" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>22:46</t>
         </is>
       </c>
       <c r="AC371" t="inlineStr">
@@ -50902,10 +51402,10 @@
     </row>
     <row r="372">
       <c r="A372" t="n">
-        <v>122254512</v>
+        <v>122254369</v>
       </c>
       <c r="B372" t="n">
-        <v>56271</v>
+        <v>56289</v>
       </c>
       <c r="C372" t="inlineStr">
         <is>
@@ -50914,20 +51414,25 @@
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E372" t="n">
-        <v>205998</v>
+        <v>100092</v>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>Större brunfladdermus</t>
+        </is>
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I372" t="inlineStr">
@@ -50951,10 +51456,10 @@
         </is>
       </c>
       <c r="Q372" t="n">
-        <v>586379</v>
+        <v>586300</v>
       </c>
       <c r="R372" t="n">
-        <v>6311136</v>
+        <v>6311112</v>
       </c>
       <c r="S372" t="n">
         <v>5</v>
@@ -50986,7 +51491,7 @@
       </c>
       <c r="Z372" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AA372" t="inlineStr">
@@ -50996,7 +51501,7 @@
       </c>
       <c r="AB372" t="inlineStr">
         <is>
-          <t>22:46</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AC372" t="inlineStr">
@@ -51041,10 +51546,10 @@
     </row>
     <row r="373">
       <c r="A373" t="n">
-        <v>122254611</v>
+        <v>122254371</v>
       </c>
       <c r="B373" t="n">
-        <v>56290</v>
+        <v>56289</v>
       </c>
       <c r="C373" t="inlineStr">
         <is>
@@ -51057,16 +51562,21 @@
         </is>
       </c>
       <c r="E373" t="n">
-        <v>205995</v>
+        <v>100092</v>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>Större brunfladdermus</t>
+        </is>
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H373" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I373" t="inlineStr">
@@ -51090,10 +51600,10 @@
         </is>
       </c>
       <c r="Q373" t="n">
-        <v>586370</v>
+        <v>586308</v>
       </c>
       <c r="R373" t="n">
-        <v>6311139</v>
+        <v>6311132</v>
       </c>
       <c r="S373" t="n">
         <v>5</v>
@@ -51125,7 +51635,7 @@
       </c>
       <c r="Z373" t="inlineStr">
         <is>
-          <t>22:59</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AA373" t="inlineStr">
@@ -51135,7 +51645,7 @@
       </c>
       <c r="AB373" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AC373" t="inlineStr">
@@ -51180,10 +51690,10 @@
     </row>
     <row r="374">
       <c r="A374" t="n">
-        <v>122254365</v>
+        <v>122254625</v>
       </c>
       <c r="B374" t="n">
-        <v>56285</v>
+        <v>56294</v>
       </c>
       <c r="C374" t="inlineStr">
         <is>
@@ -51196,16 +51706,21 @@
         </is>
       </c>
       <c r="E374" t="n">
-        <v>100092</v>
+        <v>205995</v>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I374" t="inlineStr">
@@ -51229,10 +51744,10 @@
         </is>
       </c>
       <c r="Q374" t="n">
-        <v>586276</v>
+        <v>586309</v>
       </c>
       <c r="R374" t="n">
-        <v>6311100</v>
+        <v>6311119</v>
       </c>
       <c r="S374" t="n">
         <v>5</v>
@@ -51264,17 +51779,17 @@
       </c>
       <c r="Z374" t="inlineStr">
         <is>
+          <t>22:50</t>
+        </is>
+      </c>
+      <c r="AA374" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AB374" t="inlineStr">
+        <is>
           <t>22:51</t>
-        </is>
-      </c>
-      <c r="AA374" t="inlineStr">
-        <is>
-          <t>2024-06-26</t>
-        </is>
-      </c>
-      <c r="AB374" t="inlineStr">
-        <is>
-          <t>22:52</t>
         </is>
       </c>
       <c r="AC374" t="inlineStr">
@@ -51319,10 +51834,10 @@
     </row>
     <row r="375">
       <c r="A375" t="n">
-        <v>122254315</v>
+        <v>122254585</v>
       </c>
       <c r="B375" t="n">
-        <v>56285</v>
+        <v>56294</v>
       </c>
       <c r="C375" t="inlineStr">
         <is>
@@ -51335,16 +51850,21 @@
         </is>
       </c>
       <c r="E375" t="n">
-        <v>100092</v>
+        <v>205995</v>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I375" t="inlineStr">
@@ -51368,10 +51888,10 @@
         </is>
       </c>
       <c r="Q375" t="n">
-        <v>586441</v>
+        <v>586455</v>
       </c>
       <c r="R375" t="n">
-        <v>6311155</v>
+        <v>6311156</v>
       </c>
       <c r="S375" t="n">
         <v>5</v>
@@ -51403,7 +51923,7 @@
       </c>
       <c r="Z375" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AA375" t="inlineStr">
@@ -51413,7 +51933,7 @@
       </c>
       <c r="AB375" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AC375" t="inlineStr">
@@ -51458,10 +51978,10 @@
     </row>
     <row r="376">
       <c r="A376" t="n">
-        <v>122254412</v>
+        <v>122254373</v>
       </c>
       <c r="B376" t="n">
-        <v>56285</v>
+        <v>56289</v>
       </c>
       <c r="C376" t="inlineStr">
         <is>
@@ -51476,6 +51996,11 @@
       <c r="E376" t="n">
         <v>100092</v>
       </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>Större brunfladdermus</t>
+        </is>
+      </c>
       <c r="G376" t="inlineStr">
         <is>
           <t>Nyctalus noctula</t>
@@ -51507,10 +52032,10 @@
         </is>
       </c>
       <c r="Q376" t="n">
-        <v>586424</v>
+        <v>586307</v>
       </c>
       <c r="R376" t="n">
-        <v>6311135</v>
+        <v>6311133</v>
       </c>
       <c r="S376" t="n">
         <v>5</v>
@@ -51542,7 +52067,7 @@
       </c>
       <c r="Z376" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>22:49</t>
         </is>
       </c>
       <c r="AA376" t="inlineStr">
@@ -51552,7 +52077,7 @@
       </c>
       <c r="AB376" t="inlineStr">
         <is>
-          <t>22:38</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AC376" t="inlineStr">
@@ -51597,10 +52122,10 @@
     </row>
     <row r="377">
       <c r="A377" t="n">
-        <v>122254313</v>
+        <v>122254417</v>
       </c>
       <c r="B377" t="n">
-        <v>56285</v>
+        <v>56289</v>
       </c>
       <c r="C377" t="inlineStr">
         <is>
@@ -51615,6 +52140,11 @@
       <c r="E377" t="n">
         <v>100092</v>
       </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>Större brunfladdermus</t>
+        </is>
+      </c>
       <c r="G377" t="inlineStr">
         <is>
           <t>Nyctalus noctula</t>
@@ -51646,10 +52176,10 @@
         </is>
       </c>
       <c r="Q377" t="n">
-        <v>586449</v>
+        <v>586426</v>
       </c>
       <c r="R377" t="n">
-        <v>6311155</v>
+        <v>6311145</v>
       </c>
       <c r="S377" t="n">
         <v>5</v>
@@ -51681,7 +52211,7 @@
       </c>
       <c r="Z377" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="AA377" t="inlineStr">
@@ -51691,7 +52221,7 @@
       </c>
       <c r="AB377" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>22:34</t>
         </is>
       </c>
       <c r="AC377" t="inlineStr">
@@ -51736,10 +52266,10 @@
     </row>
     <row r="378">
       <c r="A378" t="n">
-        <v>122254370</v>
+        <v>122254608</v>
       </c>
       <c r="B378" t="n">
-        <v>56285</v>
+        <v>56294</v>
       </c>
       <c r="C378" t="inlineStr">
         <is>
@@ -51752,16 +52282,21 @@
         </is>
       </c>
       <c r="E378" t="n">
-        <v>100092</v>
+        <v>205995</v>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I378" t="inlineStr">
@@ -51785,10 +52320,10 @@
         </is>
       </c>
       <c r="Q378" t="n">
-        <v>586309</v>
+        <v>586393</v>
       </c>
       <c r="R378" t="n">
-        <v>6311119</v>
+        <v>6311147</v>
       </c>
       <c r="S378" t="n">
         <v>5</v>
@@ -51820,7 +52355,7 @@
       </c>
       <c r="Z378" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AA378" t="inlineStr">
@@ -51830,7 +52365,7 @@
       </c>
       <c r="AB378" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AC378" t="inlineStr">
@@ -51878,7 +52413,7 @@
         <v>122254658</v>
       </c>
       <c r="B379" t="n">
-        <v>56290</v>
+        <v>56294</v>
       </c>
       <c r="C379" t="inlineStr">
         <is>
@@ -51892,6 +52427,11 @@
       </c>
       <c r="E379" t="n">
         <v>205995</v>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
       </c>
       <c r="G379" t="inlineStr">
         <is>
@@ -52014,10 +52554,10 @@
     </row>
     <row r="380">
       <c r="A380" t="n">
-        <v>122254650</v>
+        <v>122254586</v>
       </c>
       <c r="B380" t="n">
-        <v>56290</v>
+        <v>56294</v>
       </c>
       <c r="C380" t="inlineStr">
         <is>
@@ -52032,6 +52572,11 @@
       <c r="E380" t="n">
         <v>205995</v>
       </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
       <c r="G380" t="inlineStr">
         <is>
           <t>Pipistrellus pygmaeus</t>
@@ -52063,10 +52608,10 @@
         </is>
       </c>
       <c r="Q380" t="n">
-        <v>586422</v>
+        <v>586446</v>
       </c>
       <c r="R380" t="n">
-        <v>6311105</v>
+        <v>6311158</v>
       </c>
       <c r="S380" t="n">
         <v>5</v>
@@ -52098,7 +52643,7 @@
       </c>
       <c r="Z380" t="inlineStr">
         <is>
-          <t>22:35</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AA380" t="inlineStr">
@@ -52108,7 +52653,7 @@
       </c>
       <c r="AB380" t="inlineStr">
         <is>
-          <t>22:36</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AC380" t="inlineStr">
@@ -52153,10 +52698,10 @@
     </row>
     <row r="381">
       <c r="A381" t="n">
-        <v>122254648</v>
+        <v>122254862</v>
       </c>
       <c r="B381" t="n">
-        <v>56290</v>
+        <v>56292</v>
       </c>
       <c r="C381" t="inlineStr">
         <is>
@@ -52169,16 +52714,21 @@
         </is>
       </c>
       <c r="E381" t="n">
-        <v>205995</v>
+        <v>100111</v>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>Trollpipistrell</t>
+        </is>
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I381" t="inlineStr">
@@ -52202,10 +52752,10 @@
         </is>
       </c>
       <c r="Q381" t="n">
-        <v>586418</v>
+        <v>586288</v>
       </c>
       <c r="R381" t="n">
-        <v>6311107</v>
+        <v>6311100</v>
       </c>
       <c r="S381" t="n">
         <v>5</v>
@@ -52237,7 +52787,7 @@
       </c>
       <c r="Z381" t="inlineStr">
         <is>
-          <t>22:36</t>
+          <t>22:55</t>
         </is>
       </c>
       <c r="AA381" t="inlineStr">
@@ -52247,7 +52797,7 @@
       </c>
       <c r="AB381" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>22:56</t>
         </is>
       </c>
       <c r="AC381" t="inlineStr">
@@ -52292,10 +52842,10 @@
     </row>
     <row r="382">
       <c r="A382" t="n">
-        <v>122254606</v>
+        <v>122254836</v>
       </c>
       <c r="B382" t="n">
-        <v>56290</v>
+        <v>56292</v>
       </c>
       <c r="C382" t="inlineStr">
         <is>
@@ -52308,16 +52858,21 @@
         </is>
       </c>
       <c r="E382" t="n">
-        <v>205995</v>
+        <v>100111</v>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>Trollpipistrell</t>
+        </is>
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H382" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I382" t="inlineStr">
@@ -52341,10 +52896,10 @@
         </is>
       </c>
       <c r="Q382" t="n">
-        <v>586415</v>
+        <v>586474</v>
       </c>
       <c r="R382" t="n">
-        <v>6311146</v>
+        <v>6311176</v>
       </c>
       <c r="S382" t="n">
         <v>5</v>
@@ -52376,7 +52931,7 @@
       </c>
       <c r="Z382" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AA382" t="inlineStr">
@@ -52386,7 +52941,7 @@
       </c>
       <c r="AB382" t="inlineStr">
         <is>
-          <t>23:03</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AC382" t="inlineStr">
@@ -52431,10 +52986,10 @@
     </row>
     <row r="383">
       <c r="A383" t="n">
-        <v>122254966</v>
+        <v>122254657</v>
       </c>
       <c r="B383" t="n">
-        <v>56278</v>
+        <v>56294</v>
       </c>
       <c r="C383" t="inlineStr">
         <is>
@@ -52447,16 +53002,21 @@
         </is>
       </c>
       <c r="E383" t="n">
-        <v>205992</v>
+        <v>205995</v>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I383" t="inlineStr">
@@ -52480,10 +53040,10 @@
         </is>
       </c>
       <c r="Q383" t="n">
-        <v>586467</v>
+        <v>586488</v>
       </c>
       <c r="R383" t="n">
-        <v>6311178</v>
+        <v>6311184</v>
       </c>
       <c r="S383" t="n">
         <v>5</v>
@@ -52515,17 +53075,17 @@
       </c>
       <c r="Z383" t="inlineStr">
         <is>
+          <t>22:31</t>
+        </is>
+      </c>
+      <c r="AA383" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AB383" t="inlineStr">
+        <is>
           <t>22:32</t>
-        </is>
-      </c>
-      <c r="AA383" t="inlineStr">
-        <is>
-          <t>2024-06-26</t>
-        </is>
-      </c>
-      <c r="AB383" t="inlineStr">
-        <is>
-          <t>22:33</t>
         </is>
       </c>
       <c r="AC383" t="inlineStr">
@@ -52570,10 +53130,10 @@
     </row>
     <row r="384">
       <c r="A384" t="n">
-        <v>122254318</v>
+        <v>122254653</v>
       </c>
       <c r="B384" t="n">
-        <v>56285</v>
+        <v>56294</v>
       </c>
       <c r="C384" t="inlineStr">
         <is>
@@ -52586,16 +53146,21 @@
         </is>
       </c>
       <c r="E384" t="n">
-        <v>100092</v>
+        <v>205995</v>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I384" t="inlineStr">
@@ -52619,10 +53184,10 @@
         </is>
       </c>
       <c r="Q384" t="n">
-        <v>586455</v>
+        <v>586430</v>
       </c>
       <c r="R384" t="n">
-        <v>6311228</v>
+        <v>6311142</v>
       </c>
       <c r="S384" t="n">
         <v>5</v>
@@ -52654,7 +53219,7 @@
       </c>
       <c r="Z384" t="inlineStr">
         <is>
-          <t>23:22</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="AA384" t="inlineStr">
@@ -52664,7 +53229,7 @@
       </c>
       <c r="AB384" t="inlineStr">
         <is>
-          <t>23:23</t>
+          <t>22:34</t>
         </is>
       </c>
       <c r="AC384" t="inlineStr">
@@ -52709,10 +53274,10 @@
     </row>
     <row r="385">
       <c r="A385" t="n">
-        <v>122254342</v>
+        <v>122254610</v>
       </c>
       <c r="B385" t="n">
-        <v>56285</v>
+        <v>56294</v>
       </c>
       <c r="C385" t="inlineStr">
         <is>
@@ -52725,16 +53290,21 @@
         </is>
       </c>
       <c r="E385" t="n">
-        <v>100092</v>
+        <v>205995</v>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H385" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I385" t="inlineStr">
@@ -52761,7 +53331,7 @@
         <v>586389</v>
       </c>
       <c r="R385" t="n">
-        <v>6311142</v>
+        <v>6311141</v>
       </c>
       <c r="S385" t="n">
         <v>5</v>
@@ -52848,10 +53418,10 @@
     </row>
     <row r="386">
       <c r="A386" t="n">
-        <v>122254656</v>
+        <v>122254646</v>
       </c>
       <c r="B386" t="n">
-        <v>56290</v>
+        <v>56294</v>
       </c>
       <c r="C386" t="inlineStr">
         <is>
@@ -52866,6 +53436,11 @@
       <c r="E386" t="n">
         <v>205995</v>
       </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
       <c r="G386" t="inlineStr">
         <is>
           <t>Pipistrellus pygmaeus</t>
@@ -52897,10 +53472,10 @@
         </is>
       </c>
       <c r="Q386" t="n">
-        <v>586483</v>
+        <v>586422</v>
       </c>
       <c r="R386" t="n">
-        <v>6311186</v>
+        <v>6311111</v>
       </c>
       <c r="S386" t="n">
         <v>5</v>
@@ -52932,7 +53507,7 @@
       </c>
       <c r="Z386" t="inlineStr">
         <is>
-          <t>22:31</t>
+          <t>22:36</t>
         </is>
       </c>
       <c r="AA386" t="inlineStr">
@@ -52942,7 +53517,7 @@
       </c>
       <c r="AB386" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AC386" t="inlineStr">
@@ -52987,10 +53562,10 @@
     </row>
     <row r="387">
       <c r="A387" t="n">
-        <v>122254617</v>
+        <v>122254500</v>
       </c>
       <c r="B387" t="n">
-        <v>56290</v>
+        <v>56275</v>
       </c>
       <c r="C387" t="inlineStr">
         <is>
@@ -52999,20 +53574,25 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E387" t="n">
-        <v>205995</v>
+        <v>205998</v>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I387" t="inlineStr">
@@ -53036,10 +53616,10 @@
         </is>
       </c>
       <c r="Q387" t="n">
-        <v>586317</v>
+        <v>586388</v>
       </c>
       <c r="R387" t="n">
-        <v>6311115</v>
+        <v>6311142</v>
       </c>
       <c r="S387" t="n">
         <v>5</v>
@@ -53071,7 +53651,7 @@
       </c>
       <c r="Z387" t="inlineStr">
         <is>
-          <t>22:57</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA387" t="inlineStr">
@@ -53081,7 +53661,7 @@
       </c>
       <c r="AB387" t="inlineStr">
         <is>
-          <t>22:58</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AC387" t="inlineStr">
@@ -53126,10 +53706,10 @@
     </row>
     <row r="388">
       <c r="A388" t="n">
-        <v>122254586</v>
+        <v>122254472</v>
       </c>
       <c r="B388" t="n">
-        <v>56290</v>
+        <v>56275</v>
       </c>
       <c r="C388" t="inlineStr">
         <is>
@@ -53138,20 +53718,25 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E388" t="n">
-        <v>205995</v>
+        <v>205998</v>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H388" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I388" t="inlineStr">
@@ -53175,10 +53760,10 @@
         </is>
       </c>
       <c r="Q388" t="n">
-        <v>586446</v>
+        <v>586455</v>
       </c>
       <c r="R388" t="n">
-        <v>6311158</v>
+        <v>6311159</v>
       </c>
       <c r="S388" t="n">
         <v>5</v>
@@ -53210,7 +53795,7 @@
       </c>
       <c r="Z388" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AA388" t="inlineStr">
@@ -53220,7 +53805,7 @@
       </c>
       <c r="AB388" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AC388" t="inlineStr">
@@ -53265,10 +53850,10 @@
     </row>
     <row r="389">
       <c r="A389" t="n">
-        <v>122254352</v>
+        <v>122254511</v>
       </c>
       <c r="B389" t="n">
-        <v>56285</v>
+        <v>56275</v>
       </c>
       <c r="C389" t="inlineStr">
         <is>
@@ -53277,20 +53862,25 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E389" t="n">
-        <v>100092</v>
+        <v>205998</v>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I389" t="inlineStr">
@@ -53314,10 +53904,10 @@
         </is>
       </c>
       <c r="Q389" t="n">
-        <v>586288</v>
+        <v>586374</v>
       </c>
       <c r="R389" t="n">
-        <v>6311100</v>
+        <v>6311139</v>
       </c>
       <c r="S389" t="n">
         <v>5</v>
@@ -53349,7 +53939,7 @@
       </c>
       <c r="Z389" t="inlineStr">
         <is>
-          <t>22:55</t>
+          <t>22:46</t>
         </is>
       </c>
       <c r="AA389" t="inlineStr">
@@ -53359,7 +53949,7 @@
       </c>
       <c r="AB389" t="inlineStr">
         <is>
-          <t>22:56</t>
+          <t>22:47</t>
         </is>
       </c>
       <c r="AC389" t="inlineStr">
@@ -53407,7 +53997,7 @@
         <v>122254173</v>
       </c>
       <c r="B390" t="n">
-        <v>56269</v>
+        <v>56273</v>
       </c>
       <c r="C390" t="inlineStr">
         <is>
@@ -53421,6 +54011,11 @@
       </c>
       <c r="E390" t="n">
         <v>100015</v>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>Barbastell</t>
+        </is>
       </c>
       <c r="G390" t="inlineStr">
         <is>

--- a/artfynd/A 36363-2024 artfynd.xlsx
+++ b/artfynd/A 36363-2024 artfynd.xlsx
@@ -37002,7 +37002,7 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>122254352</v>
+        <v>122254411</v>
       </c>
       <c r="B272" t="n">
         <v>56289</v>
@@ -37056,10 +37056,10 @@
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>586288</v>
+        <v>586414</v>
       </c>
       <c r="R272" t="n">
-        <v>6311100</v>
+        <v>6311126</v>
       </c>
       <c r="S272" t="n">
         <v>5</v>
@@ -37091,7 +37091,7 @@
       </c>
       <c r="Z272" t="inlineStr">
         <is>
-          <t>22:55</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AA272" t="inlineStr">
@@ -37101,7 +37101,7 @@
       </c>
       <c r="AB272" t="inlineStr">
         <is>
-          <t>22:56</t>
+          <t>22:38</t>
         </is>
       </c>
       <c r="AC272" t="inlineStr">
@@ -37146,7 +37146,7 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>122254365</v>
+        <v>122254371</v>
       </c>
       <c r="B273" t="n">
         <v>56289</v>
@@ -37200,10 +37200,10 @@
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>586276</v>
+        <v>586308</v>
       </c>
       <c r="R273" t="n">
-        <v>6311100</v>
+        <v>6311132</v>
       </c>
       <c r="S273" t="n">
         <v>5</v>
@@ -37235,17 +37235,17 @@
       </c>
       <c r="Z273" t="inlineStr">
         <is>
+          <t>22:50</t>
+        </is>
+      </c>
+      <c r="AA273" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AB273" t="inlineStr">
+        <is>
           <t>22:51</t>
-        </is>
-      </c>
-      <c r="AA273" t="inlineStr">
-        <is>
-          <t>2024-06-26</t>
-        </is>
-      </c>
-      <c r="AB273" t="inlineStr">
-        <is>
-          <t>22:52</t>
         </is>
       </c>
       <c r="AC273" t="inlineStr">
@@ -37290,10 +37290,10 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>122254617</v>
+        <v>122254838</v>
       </c>
       <c r="B274" t="n">
-        <v>56294</v>
+        <v>56292</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>
@@ -37306,21 +37306,21 @@
         </is>
       </c>
       <c r="E274" t="n">
-        <v>205995</v>
+        <v>100111</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
@@ -37344,10 +37344,10 @@
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>586317</v>
+        <v>586448</v>
       </c>
       <c r="R274" t="n">
-        <v>6311115</v>
+        <v>6311154</v>
       </c>
       <c r="S274" t="n">
         <v>5</v>
@@ -37379,7 +37379,7 @@
       </c>
       <c r="Z274" t="inlineStr">
         <is>
-          <t>22:57</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA274" t="inlineStr">
@@ -37389,7 +37389,7 @@
       </c>
       <c r="AB274" t="inlineStr">
         <is>
-          <t>22:58</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC274" t="inlineStr">
@@ -37434,7 +37434,7 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>122254953</v>
+        <v>122254950</v>
       </c>
       <c r="B275" t="n">
         <v>56282</v>
@@ -37488,10 +37488,10 @@
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>586449</v>
+        <v>586482</v>
       </c>
       <c r="R275" t="n">
-        <v>6311155</v>
+        <v>6311185</v>
       </c>
       <c r="S275" t="n">
         <v>5</v>
@@ -37523,7 +37523,7 @@
       </c>
       <c r="Z275" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AA275" t="inlineStr">
@@ -37533,7 +37533,7 @@
       </c>
       <c r="AB275" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>23:31</t>
         </is>
       </c>
       <c r="AC275" t="inlineStr">
@@ -37578,10 +37578,10 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>122254475</v>
+        <v>122254617</v>
       </c>
       <c r="B276" t="n">
-        <v>56275</v>
+        <v>56294</v>
       </c>
       <c r="C276" t="inlineStr">
         <is>
@@ -37590,25 +37590,25 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E276" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
@@ -37632,10 +37632,10 @@
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>586420</v>
+        <v>586317</v>
       </c>
       <c r="R276" t="n">
-        <v>6311166</v>
+        <v>6311115</v>
       </c>
       <c r="S276" t="n">
         <v>5</v>
@@ -37667,7 +37667,7 @@
       </c>
       <c r="Z276" t="inlineStr">
         <is>
-          <t>23:23</t>
+          <t>22:57</t>
         </is>
       </c>
       <c r="AA276" t="inlineStr">
@@ -37677,7 +37677,7 @@
       </c>
       <c r="AB276" t="inlineStr">
         <is>
-          <t>23:24</t>
+          <t>22:58</t>
         </is>
       </c>
       <c r="AC276" t="inlineStr">
@@ -37722,7 +37722,7 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>122254954</v>
+        <v>122254952</v>
       </c>
       <c r="B277" t="n">
         <v>56282</v>
@@ -37776,10 +37776,10 @@
         </is>
       </c>
       <c r="Q277" t="n">
-        <v>586442</v>
+        <v>586455</v>
       </c>
       <c r="R277" t="n">
-        <v>6311152</v>
+        <v>6311156</v>
       </c>
       <c r="S277" t="n">
         <v>5</v>
@@ -37811,7 +37811,7 @@
       </c>
       <c r="Z277" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AA277" t="inlineStr">
@@ -37821,7 +37821,7 @@
       </c>
       <c r="AB277" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AC277" t="inlineStr">
@@ -37866,7 +37866,7 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>122254394</v>
+        <v>122254369</v>
       </c>
       <c r="B278" t="n">
         <v>56289</v>
@@ -37920,10 +37920,10 @@
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>586419</v>
+        <v>586300</v>
       </c>
       <c r="R278" t="n">
-        <v>6311142</v>
+        <v>6311112</v>
       </c>
       <c r="S278" t="n">
         <v>5</v>
@@ -37955,7 +37955,7 @@
       </c>
       <c r="Z278" t="inlineStr">
         <is>
-          <t>22:43</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AA278" t="inlineStr">
@@ -37965,7 +37965,7 @@
       </c>
       <c r="AB278" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AC278" t="inlineStr">
@@ -38010,10 +38010,10 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>122254498</v>
+        <v>122254625</v>
       </c>
       <c r="B279" t="n">
-        <v>56275</v>
+        <v>56294</v>
       </c>
       <c r="C279" t="inlineStr">
         <is>
@@ -38022,25 +38022,25 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E279" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
@@ -38064,10 +38064,10 @@
         </is>
       </c>
       <c r="Q279" t="n">
-        <v>586393</v>
+        <v>586309</v>
       </c>
       <c r="R279" t="n">
-        <v>6311147</v>
+        <v>6311119</v>
       </c>
       <c r="S279" t="n">
         <v>5</v>
@@ -38099,7 +38099,7 @@
       </c>
       <c r="Z279" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AA279" t="inlineStr">
@@ -38109,7 +38109,7 @@
       </c>
       <c r="AB279" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AC279" t="inlineStr">
@@ -38154,10 +38154,10 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>122254837</v>
+        <v>122254608</v>
       </c>
       <c r="B280" t="n">
-        <v>56292</v>
+        <v>56294</v>
       </c>
       <c r="C280" t="inlineStr">
         <is>
@@ -38170,21 +38170,21 @@
         </is>
       </c>
       <c r="E280" t="n">
-        <v>100111</v>
+        <v>205995</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
@@ -38208,10 +38208,10 @@
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>586448</v>
+        <v>586393</v>
       </c>
       <c r="R280" t="n">
-        <v>6311154</v>
+        <v>6311147</v>
       </c>
       <c r="S280" t="n">
         <v>5</v>
@@ -38243,7 +38243,7 @@
       </c>
       <c r="Z280" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AA280" t="inlineStr">
@@ -38253,7 +38253,7 @@
       </c>
       <c r="AB280" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AC280" t="inlineStr">
@@ -38298,10 +38298,10 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>122254306</v>
+        <v>122254655</v>
       </c>
       <c r="B281" t="n">
-        <v>56289</v>
+        <v>56294</v>
       </c>
       <c r="C281" t="inlineStr">
         <is>
@@ -38314,21 +38314,21 @@
         </is>
       </c>
       <c r="E281" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
@@ -38352,10 +38352,10 @@
         </is>
       </c>
       <c r="Q281" t="n">
-        <v>586473</v>
+        <v>586475</v>
       </c>
       <c r="R281" t="n">
-        <v>6311192</v>
+        <v>6311187</v>
       </c>
       <c r="S281" t="n">
         <v>5</v>
@@ -38387,7 +38387,7 @@
       </c>
       <c r="Z281" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AA281" t="inlineStr">
@@ -38397,7 +38397,7 @@
       </c>
       <c r="AB281" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="AC281" t="inlineStr">
@@ -38442,10 +38442,10 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>122254312</v>
+        <v>122254637</v>
       </c>
       <c r="B282" t="n">
-        <v>56289</v>
+        <v>56294</v>
       </c>
       <c r="C282" t="inlineStr">
         <is>
@@ -38458,21 +38458,21 @@
         </is>
       </c>
       <c r="E282" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
@@ -38496,10 +38496,10 @@
         </is>
       </c>
       <c r="Q282" t="n">
-        <v>586452</v>
+        <v>586408</v>
       </c>
       <c r="R282" t="n">
-        <v>6311152</v>
+        <v>6311124</v>
       </c>
       <c r="S282" t="n">
         <v>5</v>
@@ -38531,7 +38531,7 @@
       </c>
       <c r="Z282" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>22:43</t>
         </is>
       </c>
       <c r="AA282" t="inlineStr">
@@ -38541,7 +38541,7 @@
       </c>
       <c r="AB282" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AC282" t="inlineStr">
@@ -38586,10 +38586,10 @@
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>122254857</v>
+        <v>122254413</v>
       </c>
       <c r="B283" t="n">
-        <v>56292</v>
+        <v>56289</v>
       </c>
       <c r="C283" t="inlineStr">
         <is>
@@ -38602,21 +38602,21 @@
         </is>
       </c>
       <c r="E283" t="n">
-        <v>100111</v>
+        <v>100092</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
@@ -38640,10 +38640,10 @@
         </is>
       </c>
       <c r="Q283" t="n">
-        <v>586317</v>
+        <v>586423</v>
       </c>
       <c r="R283" t="n">
-        <v>6311115</v>
+        <v>6311137</v>
       </c>
       <c r="S283" t="n">
         <v>5</v>
@@ -38675,7 +38675,7 @@
       </c>
       <c r="Z283" t="inlineStr">
         <is>
-          <t>22:57</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AA283" t="inlineStr">
@@ -38685,7 +38685,7 @@
       </c>
       <c r="AB283" t="inlineStr">
         <is>
-          <t>22:58</t>
+          <t>22:38</t>
         </is>
       </c>
       <c r="AC283" t="inlineStr">
@@ -38730,10 +38730,10 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>122254878</v>
+        <v>122254316</v>
       </c>
       <c r="B284" t="n">
-        <v>56292</v>
+        <v>56289</v>
       </c>
       <c r="C284" t="inlineStr">
         <is>
@@ -38746,21 +38746,21 @@
         </is>
       </c>
       <c r="E284" t="n">
-        <v>100111</v>
+        <v>100092</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
@@ -38784,10 +38784,10 @@
         </is>
       </c>
       <c r="Q284" t="n">
-        <v>586280</v>
+        <v>586423</v>
       </c>
       <c r="R284" t="n">
-        <v>6311103</v>
+        <v>6311166</v>
       </c>
       <c r="S284" t="n">
         <v>5</v>
@@ -38819,7 +38819,7 @@
       </c>
       <c r="Z284" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>23:23</t>
         </is>
       </c>
       <c r="AA284" t="inlineStr">
@@ -38829,7 +38829,7 @@
       </c>
       <c r="AB284" t="inlineStr">
         <is>
-          <t>22:52</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="AC284" t="inlineStr">
@@ -38874,7 +38874,7 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>122254418</v>
+        <v>122254393</v>
       </c>
       <c r="B285" t="n">
         <v>56289</v>
@@ -38928,10 +38928,10 @@
         </is>
       </c>
       <c r="Q285" t="n">
-        <v>586467</v>
+        <v>586396</v>
       </c>
       <c r="R285" t="n">
-        <v>6311178</v>
+        <v>6311146</v>
       </c>
       <c r="S285" t="n">
         <v>5</v>
@@ -38963,7 +38963,7 @@
       </c>
       <c r="Z285" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AA285" t="inlineStr">
@@ -38973,7 +38973,7 @@
       </c>
       <c r="AB285" t="inlineStr">
         <is>
-          <t>22:33</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AC285" t="inlineStr">
@@ -39018,7 +39018,7 @@
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>122254421</v>
+        <v>122254420</v>
       </c>
       <c r="B286" t="n">
         <v>56289</v>
@@ -39072,10 +39072,10 @@
         </is>
       </c>
       <c r="Q286" t="n">
-        <v>586468</v>
+        <v>586467</v>
       </c>
       <c r="R286" t="n">
-        <v>6311181</v>
+        <v>6311178</v>
       </c>
       <c r="S286" t="n">
         <v>5</v>
@@ -39162,10 +39162,10 @@
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>122254396</v>
+        <v>122254855</v>
       </c>
       <c r="B287" t="n">
-        <v>56289</v>
+        <v>56292</v>
       </c>
       <c r="C287" t="inlineStr">
         <is>
@@ -39178,21 +39178,21 @@
         </is>
       </c>
       <c r="E287" t="n">
-        <v>100092</v>
+        <v>100111</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
@@ -39216,10 +39216,10 @@
         </is>
       </c>
       <c r="Q287" t="n">
-        <v>586408</v>
+        <v>586330</v>
       </c>
       <c r="R287" t="n">
-        <v>6311124</v>
+        <v>6311120</v>
       </c>
       <c r="S287" t="n">
         <v>5</v>
@@ -39251,7 +39251,7 @@
       </c>
       <c r="Z287" t="inlineStr">
         <is>
-          <t>22:43</t>
+          <t>22:57</t>
         </is>
       </c>
       <c r="AA287" t="inlineStr">
@@ -39261,7 +39261,7 @@
       </c>
       <c r="AB287" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>22:58</t>
         </is>
       </c>
       <c r="AC287" t="inlineStr">
@@ -39306,7 +39306,7 @@
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>122254632</v>
+        <v>122254658</v>
       </c>
       <c r="B288" t="n">
         <v>56294</v>
@@ -39360,10 +39360,10 @@
         </is>
       </c>
       <c r="Q288" t="n">
-        <v>586374</v>
+        <v>586491</v>
       </c>
       <c r="R288" t="n">
-        <v>6311140</v>
+        <v>6311181</v>
       </c>
       <c r="S288" t="n">
         <v>5</v>
@@ -39395,7 +39395,7 @@
       </c>
       <c r="Z288" t="inlineStr">
         <is>
-          <t>22:46</t>
+          <t>22:31</t>
         </is>
       </c>
       <c r="AA288" t="inlineStr">
@@ -39405,7 +39405,7 @@
       </c>
       <c r="AB288" t="inlineStr">
         <is>
-          <t>22:47</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AC288" t="inlineStr">
@@ -39450,10 +39450,10 @@
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>122254317</v>
+        <v>122254612</v>
       </c>
       <c r="B289" t="n">
-        <v>56289</v>
+        <v>56294</v>
       </c>
       <c r="C289" t="inlineStr">
         <is>
@@ -39466,21 +39466,21 @@
         </is>
       </c>
       <c r="E289" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
@@ -39504,10 +39504,10 @@
         </is>
       </c>
       <c r="Q289" t="n">
-        <v>586438</v>
+        <v>586371</v>
       </c>
       <c r="R289" t="n">
-        <v>6311222</v>
+        <v>6311135</v>
       </c>
       <c r="S289" t="n">
         <v>5</v>
@@ -39539,7 +39539,7 @@
       </c>
       <c r="Z289" t="inlineStr">
         <is>
-          <t>23:22</t>
+          <t>22:59</t>
         </is>
       </c>
       <c r="AA289" t="inlineStr">
@@ -39549,7 +39549,7 @@
       </c>
       <c r="AB289" t="inlineStr">
         <is>
-          <t>23:23</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AC289" t="inlineStr">
@@ -39594,10 +39594,10 @@
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>122254372</v>
+        <v>122254966</v>
       </c>
       <c r="B290" t="n">
-        <v>56289</v>
+        <v>56282</v>
       </c>
       <c r="C290" t="inlineStr">
         <is>
@@ -39610,21 +39610,21 @@
         </is>
       </c>
       <c r="E290" t="n">
-        <v>100092</v>
+        <v>205992</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
@@ -39648,10 +39648,10 @@
         </is>
       </c>
       <c r="Q290" t="n">
-        <v>586306</v>
+        <v>586467</v>
       </c>
       <c r="R290" t="n">
-        <v>6311131</v>
+        <v>6311178</v>
       </c>
       <c r="S290" t="n">
         <v>5</v>
@@ -39683,7 +39683,7 @@
       </c>
       <c r="Z290" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AA290" t="inlineStr">
@@ -39693,7 +39693,7 @@
       </c>
       <c r="AB290" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="AC290" t="inlineStr">
@@ -39738,7 +39738,7 @@
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>122254310</v>
+        <v>122254314</v>
       </c>
       <c r="B291" t="n">
         <v>56289</v>
@@ -39792,10 +39792,10 @@
         </is>
       </c>
       <c r="Q291" t="n">
-        <v>586452</v>
+        <v>586443</v>
       </c>
       <c r="R291" t="n">
-        <v>6311156</v>
+        <v>6311164</v>
       </c>
       <c r="S291" t="n">
         <v>5</v>
@@ -39827,17 +39827,17 @@
       </c>
       <c r="Z291" t="inlineStr">
         <is>
+          <t>23:26</t>
+        </is>
+      </c>
+      <c r="AA291" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AB291" t="inlineStr">
+        <is>
           <t>23:27</t>
-        </is>
-      </c>
-      <c r="AA291" t="inlineStr">
-        <is>
-          <t>2024-06-26</t>
-        </is>
-      </c>
-      <c r="AB291" t="inlineStr">
-        <is>
-          <t>23:28</t>
         </is>
       </c>
       <c r="AC291" t="inlineStr">
@@ -39882,10 +39882,10 @@
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>122254315</v>
+        <v>122254476</v>
       </c>
       <c r="B292" t="n">
-        <v>56289</v>
+        <v>56275</v>
       </c>
       <c r="C292" t="inlineStr">
         <is>
@@ -39894,25 +39894,25 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E292" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
@@ -39936,10 +39936,10 @@
         </is>
       </c>
       <c r="Q292" t="n">
-        <v>586441</v>
+        <v>586418</v>
       </c>
       <c r="R292" t="n">
-        <v>6311155</v>
+        <v>6311167</v>
       </c>
       <c r="S292" t="n">
         <v>5</v>
@@ -39971,7 +39971,7 @@
       </c>
       <c r="Z292" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>23:23</t>
         </is>
       </c>
       <c r="AA292" t="inlineStr">
@@ -39981,7 +39981,7 @@
       </c>
       <c r="AB292" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="AC292" t="inlineStr">
@@ -40026,10 +40026,10 @@
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>122254496</v>
+        <v>122254660</v>
       </c>
       <c r="B293" t="n">
-        <v>56275</v>
+        <v>56294</v>
       </c>
       <c r="C293" t="inlineStr">
         <is>
@@ -40038,25 +40038,25 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E293" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
@@ -40080,10 +40080,10 @@
         </is>
       </c>
       <c r="Q293" t="n">
-        <v>586415</v>
+        <v>586488</v>
       </c>
       <c r="R293" t="n">
-        <v>6311146</v>
+        <v>6311183</v>
       </c>
       <c r="S293" t="n">
         <v>5</v>
@@ -40115,7 +40115,7 @@
       </c>
       <c r="Z293" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>22:31</t>
         </is>
       </c>
       <c r="AA293" t="inlineStr">
@@ -40125,7 +40125,7 @@
       </c>
       <c r="AB293" t="inlineStr">
         <is>
-          <t>23:03</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AC293" t="inlineStr">
@@ -40170,10 +40170,10 @@
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>122254473</v>
+        <v>122254959</v>
       </c>
       <c r="B294" t="n">
-        <v>56275</v>
+        <v>56282</v>
       </c>
       <c r="C294" t="inlineStr">
         <is>
@@ -40182,25 +40182,25 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E294" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
@@ -40224,10 +40224,10 @@
         </is>
       </c>
       <c r="Q294" t="n">
-        <v>586450</v>
+        <v>586370</v>
       </c>
       <c r="R294" t="n">
-        <v>6311152</v>
+        <v>6311139</v>
       </c>
       <c r="S294" t="n">
         <v>5</v>
@@ -40259,7 +40259,7 @@
       </c>
       <c r="Z294" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>22:59</t>
         </is>
       </c>
       <c r="AA294" t="inlineStr">
@@ -40269,7 +40269,7 @@
       </c>
       <c r="AB294" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AC294" t="inlineStr">
@@ -40314,10 +40314,10 @@
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>122254415</v>
+        <v>122254607</v>
       </c>
       <c r="B295" t="n">
-        <v>56289</v>
+        <v>56294</v>
       </c>
       <c r="C295" t="inlineStr">
         <is>
@@ -40330,21 +40330,21 @@
         </is>
       </c>
       <c r="E295" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
@@ -40368,10 +40368,10 @@
         </is>
       </c>
       <c r="Q295" t="n">
-        <v>586425</v>
+        <v>586415</v>
       </c>
       <c r="R295" t="n">
-        <v>6311135</v>
+        <v>6311149</v>
       </c>
       <c r="S295" t="n">
         <v>5</v>
@@ -40403,7 +40403,7 @@
       </c>
       <c r="Z295" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AA295" t="inlineStr">
@@ -40413,7 +40413,7 @@
       </c>
       <c r="AB295" t="inlineStr">
         <is>
-          <t>22:38</t>
+          <t>23:03</t>
         </is>
       </c>
       <c r="AC295" t="inlineStr">
@@ -40458,10 +40458,10 @@
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>122254393</v>
+        <v>122254657</v>
       </c>
       <c r="B296" t="n">
-        <v>56289</v>
+        <v>56294</v>
       </c>
       <c r="C296" t="inlineStr">
         <is>
@@ -40474,21 +40474,21 @@
         </is>
       </c>
       <c r="E296" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
@@ -40512,10 +40512,10 @@
         </is>
       </c>
       <c r="Q296" t="n">
-        <v>586396</v>
+        <v>586488</v>
       </c>
       <c r="R296" t="n">
-        <v>6311146</v>
+        <v>6311184</v>
       </c>
       <c r="S296" t="n">
         <v>5</v>
@@ -40547,7 +40547,7 @@
       </c>
       <c r="Z296" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>22:31</t>
         </is>
       </c>
       <c r="AA296" t="inlineStr">
@@ -40557,7 +40557,7 @@
       </c>
       <c r="AB296" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AC296" t="inlineStr">
@@ -40602,10 +40602,10 @@
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>122254308</v>
+        <v>122254953</v>
       </c>
       <c r="B297" t="n">
-        <v>56289</v>
+        <v>56282</v>
       </c>
       <c r="C297" t="inlineStr">
         <is>
@@ -40618,21 +40618,21 @@
         </is>
       </c>
       <c r="E297" t="n">
-        <v>100092</v>
+        <v>205992</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
@@ -40656,10 +40656,10 @@
         </is>
       </c>
       <c r="Q297" t="n">
-        <v>586455</v>
+        <v>586449</v>
       </c>
       <c r="R297" t="n">
-        <v>6311159</v>
+        <v>6311155</v>
       </c>
       <c r="S297" t="n">
         <v>5</v>
@@ -40691,17 +40691,17 @@
       </c>
       <c r="Z297" t="inlineStr">
         <is>
+          <t>23:27</t>
+        </is>
+      </c>
+      <c r="AA297" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AB297" t="inlineStr">
+        <is>
           <t>23:28</t>
-        </is>
-      </c>
-      <c r="AA297" t="inlineStr">
-        <is>
-          <t>2024-06-26</t>
-        </is>
-      </c>
-      <c r="AB297" t="inlineStr">
-        <is>
-          <t>23:29</t>
         </is>
       </c>
       <c r="AC297" t="inlineStr">
@@ -40746,10 +40746,10 @@
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>122254649</v>
+        <v>122254343</v>
       </c>
       <c r="B298" t="n">
-        <v>56294</v>
+        <v>56289</v>
       </c>
       <c r="C298" t="inlineStr">
         <is>
@@ -40762,21 +40762,21 @@
         </is>
       </c>
       <c r="E298" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
@@ -40800,10 +40800,10 @@
         </is>
       </c>
       <c r="Q298" t="n">
-        <v>586422</v>
+        <v>586388</v>
       </c>
       <c r="R298" t="n">
-        <v>6311100</v>
+        <v>6311142</v>
       </c>
       <c r="S298" t="n">
         <v>5</v>
@@ -40835,7 +40835,7 @@
       </c>
       <c r="Z298" t="inlineStr">
         <is>
-          <t>22:35</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA298" t="inlineStr">
@@ -40845,7 +40845,7 @@
       </c>
       <c r="AB298" t="inlineStr">
         <is>
-          <t>22:36</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AC298" t="inlineStr">
@@ -40890,10 +40890,10 @@
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>122254843</v>
+        <v>122254367</v>
       </c>
       <c r="B299" t="n">
-        <v>56292</v>
+        <v>56289</v>
       </c>
       <c r="C299" t="inlineStr">
         <is>
@@ -40906,21 +40906,21 @@
         </is>
       </c>
       <c r="E299" t="n">
-        <v>100111</v>
+        <v>100092</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
@@ -40944,10 +40944,10 @@
         </is>
       </c>
       <c r="Q299" t="n">
-        <v>586389</v>
+        <v>586280</v>
       </c>
       <c r="R299" t="n">
-        <v>6311142</v>
+        <v>6311103</v>
       </c>
       <c r="S299" t="n">
         <v>5</v>
@@ -40979,7 +40979,7 @@
       </c>
       <c r="Z299" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AA299" t="inlineStr">
@@ -40989,7 +40989,7 @@
       </c>
       <c r="AB299" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>22:52</t>
         </is>
       </c>
       <c r="AC299" t="inlineStr">
@@ -41034,10 +41034,10 @@
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>122254856</v>
+        <v>122254310</v>
       </c>
       <c r="B300" t="n">
-        <v>56292</v>
+        <v>56289</v>
       </c>
       <c r="C300" t="inlineStr">
         <is>
@@ -41050,21 +41050,21 @@
         </is>
       </c>
       <c r="E300" t="n">
-        <v>100111</v>
+        <v>100092</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
@@ -41088,10 +41088,10 @@
         </is>
       </c>
       <c r="Q300" t="n">
-        <v>586327</v>
+        <v>586452</v>
       </c>
       <c r="R300" t="n">
-        <v>6311118</v>
+        <v>6311156</v>
       </c>
       <c r="S300" t="n">
         <v>5</v>
@@ -41123,7 +41123,7 @@
       </c>
       <c r="Z300" t="inlineStr">
         <is>
-          <t>22:57</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA300" t="inlineStr">
@@ -41133,7 +41133,7 @@
       </c>
       <c r="AB300" t="inlineStr">
         <is>
-          <t>22:58</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC300" t="inlineStr">
@@ -41178,10 +41178,10 @@
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>122254616</v>
+        <v>122254843</v>
       </c>
       <c r="B301" t="n">
-        <v>56294</v>
+        <v>56292</v>
       </c>
       <c r="C301" t="inlineStr">
         <is>
@@ -41194,21 +41194,21 @@
         </is>
       </c>
       <c r="E301" t="n">
-        <v>205995</v>
+        <v>100111</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
@@ -41232,10 +41232,10 @@
         </is>
       </c>
       <c r="Q301" t="n">
-        <v>586327</v>
+        <v>586389</v>
       </c>
       <c r="R301" t="n">
-        <v>6311118</v>
+        <v>6311142</v>
       </c>
       <c r="S301" t="n">
         <v>5</v>
@@ -41267,7 +41267,7 @@
       </c>
       <c r="Z301" t="inlineStr">
         <is>
-          <t>22:57</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA301" t="inlineStr">
@@ -41277,7 +41277,7 @@
       </c>
       <c r="AB301" t="inlineStr">
         <is>
-          <t>22:58</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AC301" t="inlineStr">
@@ -41322,10 +41322,10 @@
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>122254342</v>
+        <v>122254632</v>
       </c>
       <c r="B302" t="n">
-        <v>56289</v>
+        <v>56294</v>
       </c>
       <c r="C302" t="inlineStr">
         <is>
@@ -41338,21 +41338,21 @@
         </is>
       </c>
       <c r="E302" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
@@ -41376,10 +41376,10 @@
         </is>
       </c>
       <c r="Q302" t="n">
-        <v>586389</v>
+        <v>586374</v>
       </c>
       <c r="R302" t="n">
-        <v>6311142</v>
+        <v>6311140</v>
       </c>
       <c r="S302" t="n">
         <v>5</v>
@@ -41411,7 +41411,7 @@
       </c>
       <c r="Z302" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:46</t>
         </is>
       </c>
       <c r="AA302" t="inlineStr">
@@ -41421,7 +41421,7 @@
       </c>
       <c r="AB302" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>22:47</t>
         </is>
       </c>
       <c r="AC302" t="inlineStr">
@@ -41466,10 +41466,10 @@
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>122254411</v>
+        <v>122254512</v>
       </c>
       <c r="B303" t="n">
-        <v>56289</v>
+        <v>56275</v>
       </c>
       <c r="C303" t="inlineStr">
         <is>
@@ -41478,25 +41478,25 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E303" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
@@ -41520,10 +41520,10 @@
         </is>
       </c>
       <c r="Q303" t="n">
-        <v>586414</v>
+        <v>586379</v>
       </c>
       <c r="R303" t="n">
-        <v>6311126</v>
+        <v>6311136</v>
       </c>
       <c r="S303" t="n">
         <v>5</v>
@@ -41555,7 +41555,7 @@
       </c>
       <c r="Z303" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AA303" t="inlineStr">
@@ -41565,7 +41565,7 @@
       </c>
       <c r="AB303" t="inlineStr">
         <is>
-          <t>22:38</t>
+          <t>22:46</t>
         </is>
       </c>
       <c r="AC303" t="inlineStr">
@@ -41610,10 +41610,10 @@
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>122254314</v>
+        <v>122254615</v>
       </c>
       <c r="B304" t="n">
-        <v>56289</v>
+        <v>56294</v>
       </c>
       <c r="C304" t="inlineStr">
         <is>
@@ -41626,21 +41626,21 @@
         </is>
       </c>
       <c r="E304" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
@@ -41664,10 +41664,10 @@
         </is>
       </c>
       <c r="Q304" t="n">
-        <v>586443</v>
+        <v>586329</v>
       </c>
       <c r="R304" t="n">
-        <v>6311164</v>
+        <v>6311120</v>
       </c>
       <c r="S304" t="n">
         <v>5</v>
@@ -41699,7 +41699,7 @@
       </c>
       <c r="Z304" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>22:57</t>
         </is>
       </c>
       <c r="AA304" t="inlineStr">
@@ -41709,7 +41709,7 @@
       </c>
       <c r="AB304" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>22:58</t>
         </is>
       </c>
       <c r="AC304" t="inlineStr">
@@ -41754,10 +41754,10 @@
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>122254846</v>
+        <v>122254514</v>
       </c>
       <c r="B305" t="n">
-        <v>56292</v>
+        <v>56275</v>
       </c>
       <c r="C305" t="inlineStr">
         <is>
@@ -41766,25 +41766,25 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E305" t="n">
-        <v>100111</v>
+        <v>205998</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
@@ -41808,10 +41808,10 @@
         </is>
       </c>
       <c r="Q305" t="n">
-        <v>586370</v>
+        <v>586408</v>
       </c>
       <c r="R305" t="n">
-        <v>6311139</v>
+        <v>6311124</v>
       </c>
       <c r="S305" t="n">
         <v>5</v>
@@ -41843,7 +41843,7 @@
       </c>
       <c r="Z305" t="inlineStr">
         <is>
-          <t>22:59</t>
+          <t>22:43</t>
         </is>
       </c>
       <c r="AA305" t="inlineStr">
@@ -41853,7 +41853,7 @@
       </c>
       <c r="AB305" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AC305" t="inlineStr">
@@ -41898,10 +41898,10 @@
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>122254413</v>
+        <v>122254519</v>
       </c>
       <c r="B306" t="n">
-        <v>56289</v>
+        <v>56275</v>
       </c>
       <c r="C306" t="inlineStr">
         <is>
@@ -41910,25 +41910,25 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E306" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
@@ -41952,10 +41952,10 @@
         </is>
       </c>
       <c r="Q306" t="n">
-        <v>586423</v>
+        <v>586424</v>
       </c>
       <c r="R306" t="n">
-        <v>6311137</v>
+        <v>6311135</v>
       </c>
       <c r="S306" t="n">
         <v>5</v>
@@ -42042,10 +42042,10 @@
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>122254350</v>
+        <v>122254954</v>
       </c>
       <c r="B307" t="n">
-        <v>56289</v>
+        <v>56282</v>
       </c>
       <c r="C307" t="inlineStr">
         <is>
@@ -42058,21 +42058,21 @@
         </is>
       </c>
       <c r="E307" t="n">
-        <v>100092</v>
+        <v>205992</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
@@ -42096,10 +42096,10 @@
         </is>
       </c>
       <c r="Q307" t="n">
-        <v>586330</v>
+        <v>586442</v>
       </c>
       <c r="R307" t="n">
-        <v>6311120</v>
+        <v>6311152</v>
       </c>
       <c r="S307" t="n">
         <v>5</v>
@@ -42131,7 +42131,7 @@
       </c>
       <c r="Z307" t="inlineStr">
         <is>
-          <t>22:57</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AA307" t="inlineStr">
@@ -42141,7 +42141,7 @@
       </c>
       <c r="AB307" t="inlineStr">
         <is>
-          <t>22:58</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AC307" t="inlineStr">
@@ -42186,10 +42186,10 @@
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>122254635</v>
+        <v>122254370</v>
       </c>
       <c r="B308" t="n">
-        <v>56294</v>
+        <v>56289</v>
       </c>
       <c r="C308" t="inlineStr">
         <is>
@@ -42202,21 +42202,21 @@
         </is>
       </c>
       <c r="E308" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
@@ -42240,10 +42240,10 @@
         </is>
       </c>
       <c r="Q308" t="n">
-        <v>586417</v>
+        <v>586309</v>
       </c>
       <c r="R308" t="n">
-        <v>6311145</v>
+        <v>6311119</v>
       </c>
       <c r="S308" t="n">
         <v>5</v>
@@ -42275,7 +42275,7 @@
       </c>
       <c r="Z308" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AA308" t="inlineStr">
@@ -42285,7 +42285,7 @@
       </c>
       <c r="AB308" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AC308" t="inlineStr">
@@ -42330,10 +42330,10 @@
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>122254637</v>
+        <v>122254880</v>
       </c>
       <c r="B309" t="n">
-        <v>56294</v>
+        <v>56292</v>
       </c>
       <c r="C309" t="inlineStr">
         <is>
@@ -42346,21 +42346,21 @@
         </is>
       </c>
       <c r="E309" t="n">
-        <v>205995</v>
+        <v>100111</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
@@ -42384,10 +42384,10 @@
         </is>
       </c>
       <c r="Q309" t="n">
-        <v>586408</v>
+        <v>586303</v>
       </c>
       <c r="R309" t="n">
-        <v>6311124</v>
+        <v>6311115</v>
       </c>
       <c r="S309" t="n">
         <v>5</v>
@@ -42419,7 +42419,7 @@
       </c>
       <c r="Z309" t="inlineStr">
         <is>
-          <t>22:43</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AA309" t="inlineStr">
@@ -42429,7 +42429,7 @@
       </c>
       <c r="AB309" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AC309" t="inlineStr">
@@ -42474,10 +42474,10 @@
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>122254636</v>
+        <v>122254854</v>
       </c>
       <c r="B310" t="n">
-        <v>56294</v>
+        <v>56292</v>
       </c>
       <c r="C310" t="inlineStr">
         <is>
@@ -42490,21 +42490,21 @@
         </is>
       </c>
       <c r="E310" t="n">
-        <v>205995</v>
+        <v>100111</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
@@ -42528,10 +42528,10 @@
         </is>
       </c>
       <c r="Q310" t="n">
-        <v>586418</v>
+        <v>586329</v>
       </c>
       <c r="R310" t="n">
-        <v>6311145</v>
+        <v>6311120</v>
       </c>
       <c r="S310" t="n">
         <v>5</v>
@@ -42563,7 +42563,7 @@
       </c>
       <c r="Z310" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>22:57</t>
         </is>
       </c>
       <c r="AA310" t="inlineStr">
@@ -42573,7 +42573,7 @@
       </c>
       <c r="AB310" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>22:58</t>
         </is>
       </c>
       <c r="AC310" t="inlineStr">
@@ -42618,10 +42618,10 @@
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>122254950</v>
+        <v>122254844</v>
       </c>
       <c r="B311" t="n">
-        <v>56282</v>
+        <v>56292</v>
       </c>
       <c r="C311" t="inlineStr">
         <is>
@@ -42634,21 +42634,21 @@
         </is>
       </c>
       <c r="E311" t="n">
-        <v>205992</v>
+        <v>100111</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
@@ -42672,10 +42672,10 @@
         </is>
       </c>
       <c r="Q311" t="n">
-        <v>586482</v>
+        <v>586387</v>
       </c>
       <c r="R311" t="n">
-        <v>6311185</v>
+        <v>6311141</v>
       </c>
       <c r="S311" t="n">
         <v>5</v>
@@ -42707,7 +42707,7 @@
       </c>
       <c r="Z311" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA311" t="inlineStr">
@@ -42717,7 +42717,7 @@
       </c>
       <c r="AB311" t="inlineStr">
         <is>
-          <t>23:31</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AC311" t="inlineStr">
@@ -42762,10 +42762,10 @@
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>122254844</v>
+        <v>122254372</v>
       </c>
       <c r="B312" t="n">
-        <v>56292</v>
+        <v>56289</v>
       </c>
       <c r="C312" t="inlineStr">
         <is>
@@ -42778,21 +42778,21 @@
         </is>
       </c>
       <c r="E312" t="n">
-        <v>100111</v>
+        <v>100092</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
@@ -42816,10 +42816,10 @@
         </is>
       </c>
       <c r="Q312" t="n">
-        <v>586387</v>
+        <v>586306</v>
       </c>
       <c r="R312" t="n">
-        <v>6311141</v>
+        <v>6311131</v>
       </c>
       <c r="S312" t="n">
         <v>5</v>
@@ -42851,7 +42851,7 @@
       </c>
       <c r="Z312" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AA312" t="inlineStr">
@@ -42861,7 +42861,7 @@
       </c>
       <c r="AB312" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AC312" t="inlineStr">
@@ -42906,10 +42906,10 @@
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>122254367</v>
+        <v>122254651</v>
       </c>
       <c r="B313" t="n">
-        <v>56289</v>
+        <v>56294</v>
       </c>
       <c r="C313" t="inlineStr">
         <is>
@@ -42922,21 +42922,21 @@
         </is>
       </c>
       <c r="E313" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
@@ -42960,10 +42960,10 @@
         </is>
       </c>
       <c r="Q313" t="n">
-        <v>586280</v>
+        <v>586425</v>
       </c>
       <c r="R313" t="n">
-        <v>6311103</v>
+        <v>6311113</v>
       </c>
       <c r="S313" t="n">
         <v>5</v>
@@ -42995,7 +42995,7 @@
       </c>
       <c r="Z313" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="AA313" t="inlineStr">
@@ -43005,7 +43005,7 @@
       </c>
       <c r="AB313" t="inlineStr">
         <is>
-          <t>22:52</t>
+          <t>22:36</t>
         </is>
       </c>
       <c r="AC313" t="inlineStr">
@@ -43050,10 +43050,10 @@
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>122254660</v>
+        <v>122254964</v>
       </c>
       <c r="B314" t="n">
-        <v>56294</v>
+        <v>56282</v>
       </c>
       <c r="C314" t="inlineStr">
         <is>
@@ -43066,21 +43066,21 @@
         </is>
       </c>
       <c r="E314" t="n">
-        <v>205995</v>
+        <v>205992</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
@@ -43104,10 +43104,10 @@
         </is>
       </c>
       <c r="Q314" t="n">
-        <v>586488</v>
+        <v>586430</v>
       </c>
       <c r="R314" t="n">
-        <v>6311183</v>
+        <v>6311142</v>
       </c>
       <c r="S314" t="n">
         <v>5</v>
@@ -43139,7 +43139,7 @@
       </c>
       <c r="Z314" t="inlineStr">
         <is>
-          <t>22:31</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="AA314" t="inlineStr">
@@ -43149,7 +43149,7 @@
       </c>
       <c r="AB314" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>22:34</t>
         </is>
       </c>
       <c r="AC314" t="inlineStr">
@@ -43194,10 +43194,10 @@
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>122254652</v>
+        <v>122254473</v>
       </c>
       <c r="B315" t="n">
-        <v>56294</v>
+        <v>56275</v>
       </c>
       <c r="C315" t="inlineStr">
         <is>
@@ -43206,25 +43206,25 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E315" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
@@ -43248,10 +43248,10 @@
         </is>
       </c>
       <c r="Q315" t="n">
-        <v>586432</v>
+        <v>586450</v>
       </c>
       <c r="R315" t="n">
-        <v>6311118</v>
+        <v>6311152</v>
       </c>
       <c r="S315" t="n">
         <v>5</v>
@@ -43283,7 +43283,7 @@
       </c>
       <c r="Z315" t="inlineStr">
         <is>
-          <t>22:34</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA315" t="inlineStr">
@@ -43293,7 +43293,7 @@
       </c>
       <c r="AB315" t="inlineStr">
         <is>
-          <t>22:35</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC315" t="inlineStr">
@@ -43338,10 +43338,10 @@
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>122254957</v>
+        <v>122254342</v>
       </c>
       <c r="B316" t="n">
-        <v>56282</v>
+        <v>56289</v>
       </c>
       <c r="C316" t="inlineStr">
         <is>
@@ -43354,21 +43354,21 @@
         </is>
       </c>
       <c r="E316" t="n">
-        <v>205992</v>
+        <v>100092</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
@@ -43392,10 +43392,10 @@
         </is>
       </c>
       <c r="Q316" t="n">
-        <v>586444</v>
+        <v>586389</v>
       </c>
       <c r="R316" t="n">
-        <v>6311160</v>
+        <v>6311142</v>
       </c>
       <c r="S316" t="n">
         <v>5</v>
@@ -43427,7 +43427,7 @@
       </c>
       <c r="Z316" t="inlineStr">
         <is>
-          <t>23:24</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA316" t="inlineStr">
@@ -43437,7 +43437,7 @@
       </c>
       <c r="AB316" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AC316" t="inlineStr">
@@ -43482,10 +43482,10 @@
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>122254959</v>
+        <v>122254390</v>
       </c>
       <c r="B317" t="n">
-        <v>56282</v>
+        <v>56289</v>
       </c>
       <c r="C317" t="inlineStr">
         <is>
@@ -43498,21 +43498,21 @@
         </is>
       </c>
       <c r="E317" t="n">
-        <v>205992</v>
+        <v>100092</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
@@ -43536,7 +43536,7 @@
         </is>
       </c>
       <c r="Q317" t="n">
-        <v>586370</v>
+        <v>586374</v>
       </c>
       <c r="R317" t="n">
         <v>6311139</v>
@@ -43571,7 +43571,7 @@
       </c>
       <c r="Z317" t="inlineStr">
         <is>
-          <t>22:59</t>
+          <t>22:46</t>
         </is>
       </c>
       <c r="AA317" t="inlineStr">
@@ -43581,7 +43581,7 @@
       </c>
       <c r="AB317" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:47</t>
         </is>
       </c>
       <c r="AC317" t="inlineStr">
@@ -43626,10 +43626,10 @@
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>122254519</v>
+        <v>122254392</v>
       </c>
       <c r="B318" t="n">
-        <v>56275</v>
+        <v>56289</v>
       </c>
       <c r="C318" t="inlineStr">
         <is>
@@ -43638,25 +43638,25 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E318" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
@@ -43680,10 +43680,10 @@
         </is>
       </c>
       <c r="Q318" t="n">
-        <v>586424</v>
+        <v>586384</v>
       </c>
       <c r="R318" t="n">
-        <v>6311135</v>
+        <v>6311139</v>
       </c>
       <c r="S318" t="n">
         <v>5</v>
@@ -43715,7 +43715,7 @@
       </c>
       <c r="Z318" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AA318" t="inlineStr">
@@ -43725,7 +43725,7 @@
       </c>
       <c r="AB318" t="inlineStr">
         <is>
-          <t>22:38</t>
+          <t>22:46</t>
         </is>
       </c>
       <c r="AC318" t="inlineStr">
@@ -43770,7 +43770,7 @@
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>122254648</v>
+        <v>122254588</v>
       </c>
       <c r="B319" t="n">
         <v>56294</v>
@@ -43824,10 +43824,10 @@
         </is>
       </c>
       <c r="Q319" t="n">
-        <v>586418</v>
+        <v>586415</v>
       </c>
       <c r="R319" t="n">
-        <v>6311107</v>
+        <v>6311196</v>
       </c>
       <c r="S319" t="n">
         <v>5</v>
@@ -43859,7 +43859,7 @@
       </c>
       <c r="Z319" t="inlineStr">
         <is>
-          <t>22:36</t>
+          <t>23:22</t>
         </is>
       </c>
       <c r="AA319" t="inlineStr">
@@ -43869,7 +43869,7 @@
       </c>
       <c r="AB319" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>23:23</t>
         </is>
       </c>
       <c r="AC319" t="inlineStr">
@@ -43914,7 +43914,7 @@
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>122254650</v>
+        <v>122254635</v>
       </c>
       <c r="B320" t="n">
         <v>56294</v>
@@ -43968,10 +43968,10 @@
         </is>
       </c>
       <c r="Q320" t="n">
-        <v>586422</v>
+        <v>586417</v>
       </c>
       <c r="R320" t="n">
-        <v>6311105</v>
+        <v>6311145</v>
       </c>
       <c r="S320" t="n">
         <v>5</v>
@@ -44003,7 +44003,7 @@
       </c>
       <c r="Z320" t="inlineStr">
         <is>
-          <t>22:35</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AA320" t="inlineStr">
@@ -44013,7 +44013,7 @@
       </c>
       <c r="AB320" t="inlineStr">
         <is>
-          <t>22:36</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AC320" t="inlineStr">
@@ -44058,7 +44058,7 @@
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>122254654</v>
+        <v>122254627</v>
       </c>
       <c r="B321" t="n">
         <v>56294</v>
@@ -44112,10 +44112,10 @@
         </is>
       </c>
       <c r="Q321" t="n">
-        <v>586467</v>
+        <v>586306</v>
       </c>
       <c r="R321" t="n">
-        <v>6311178</v>
+        <v>6311131</v>
       </c>
       <c r="S321" t="n">
         <v>5</v>
@@ -44147,7 +44147,7 @@
       </c>
       <c r="Z321" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AA321" t="inlineStr">
@@ -44157,7 +44157,7 @@
       </c>
       <c r="AB321" t="inlineStr">
         <is>
-          <t>22:33</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AC321" t="inlineStr">
@@ -44202,10 +44202,10 @@
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>122254609</v>
+        <v>122254472</v>
       </c>
       <c r="B322" t="n">
-        <v>56294</v>
+        <v>56275</v>
       </c>
       <c r="C322" t="inlineStr">
         <is>
@@ -44214,25 +44214,25 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E322" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
@@ -44256,10 +44256,10 @@
         </is>
       </c>
       <c r="Q322" t="n">
-        <v>586392</v>
+        <v>586455</v>
       </c>
       <c r="R322" t="n">
-        <v>6311147</v>
+        <v>6311159</v>
       </c>
       <c r="S322" t="n">
         <v>5</v>
@@ -44291,7 +44291,7 @@
       </c>
       <c r="Z322" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AA322" t="inlineStr">
@@ -44301,7 +44301,7 @@
       </c>
       <c r="AB322" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AC322" t="inlineStr">
@@ -44346,10 +44346,10 @@
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>122254956</v>
+        <v>122254585</v>
       </c>
       <c r="B323" t="n">
-        <v>56282</v>
+        <v>56294</v>
       </c>
       <c r="C323" t="inlineStr">
         <is>
@@ -44362,21 +44362,21 @@
         </is>
       </c>
       <c r="E323" t="n">
-        <v>205992</v>
+        <v>205995</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
@@ -44400,10 +44400,10 @@
         </is>
       </c>
       <c r="Q323" t="n">
-        <v>586441</v>
+        <v>586455</v>
       </c>
       <c r="R323" t="n">
-        <v>6311152</v>
+        <v>6311156</v>
       </c>
       <c r="S323" t="n">
         <v>5</v>
@@ -44435,7 +44435,7 @@
       </c>
       <c r="Z323" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AA323" t="inlineStr">
@@ -44445,7 +44445,7 @@
       </c>
       <c r="AB323" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AC323" t="inlineStr">
@@ -44490,10 +44490,10 @@
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>122254835</v>
+        <v>122254636</v>
       </c>
       <c r="B324" t="n">
-        <v>56292</v>
+        <v>56294</v>
       </c>
       <c r="C324" t="inlineStr">
         <is>
@@ -44506,21 +44506,21 @@
         </is>
       </c>
       <c r="E324" t="n">
-        <v>100111</v>
+        <v>205995</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
@@ -44544,10 +44544,10 @@
         </is>
       </c>
       <c r="Q324" t="n">
-        <v>586473</v>
+        <v>586418</v>
       </c>
       <c r="R324" t="n">
-        <v>6311192</v>
+        <v>6311145</v>
       </c>
       <c r="S324" t="n">
         <v>5</v>
@@ -44579,7 +44579,7 @@
       </c>
       <c r="Z324" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AA324" t="inlineStr">
@@ -44589,7 +44589,7 @@
       </c>
       <c r="AB324" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AC324" t="inlineStr">
@@ -44634,10 +44634,10 @@
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>122254877</v>
+        <v>122254309</v>
       </c>
       <c r="B325" t="n">
-        <v>56292</v>
+        <v>56289</v>
       </c>
       <c r="C325" t="inlineStr">
         <is>
@@ -44650,21 +44650,21 @@
         </is>
       </c>
       <c r="E325" t="n">
-        <v>100111</v>
+        <v>100092</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
@@ -44688,10 +44688,10 @@
         </is>
       </c>
       <c r="Q325" t="n">
-        <v>586276</v>
+        <v>586456</v>
       </c>
       <c r="R325" t="n">
-        <v>6311100</v>
+        <v>6311158</v>
       </c>
       <c r="S325" t="n">
         <v>5</v>
@@ -44723,7 +44723,7 @@
       </c>
       <c r="Z325" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AA325" t="inlineStr">
@@ -44733,7 +44733,7 @@
       </c>
       <c r="AB325" t="inlineStr">
         <is>
-          <t>22:52</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AC325" t="inlineStr">
@@ -44778,10 +44778,10 @@
     </row>
     <row r="326">
       <c r="A326" t="n">
-        <v>122254412</v>
+        <v>122254878</v>
       </c>
       <c r="B326" t="n">
-        <v>56289</v>
+        <v>56292</v>
       </c>
       <c r="C326" t="inlineStr">
         <is>
@@ -44794,21 +44794,21 @@
         </is>
       </c>
       <c r="E326" t="n">
-        <v>100092</v>
+        <v>100111</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
@@ -44832,10 +44832,10 @@
         </is>
       </c>
       <c r="Q326" t="n">
-        <v>586424</v>
+        <v>586280</v>
       </c>
       <c r="R326" t="n">
-        <v>6311135</v>
+        <v>6311103</v>
       </c>
       <c r="S326" t="n">
         <v>5</v>
@@ -44867,7 +44867,7 @@
       </c>
       <c r="Z326" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AA326" t="inlineStr">
@@ -44877,7 +44877,7 @@
       </c>
       <c r="AB326" t="inlineStr">
         <is>
-          <t>22:38</t>
+          <t>22:52</t>
         </is>
       </c>
       <c r="AC326" t="inlineStr">
@@ -44922,10 +44922,10 @@
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>122254634</v>
+        <v>122254391</v>
       </c>
       <c r="B327" t="n">
-        <v>56294</v>
+        <v>56289</v>
       </c>
       <c r="C327" t="inlineStr">
         <is>
@@ -44938,21 +44938,21 @@
         </is>
       </c>
       <c r="E327" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
@@ -44976,10 +44976,10 @@
         </is>
       </c>
       <c r="Q327" t="n">
-        <v>586415</v>
+        <v>586379</v>
       </c>
       <c r="R327" t="n">
-        <v>6311148</v>
+        <v>6311136</v>
       </c>
       <c r="S327" t="n">
         <v>5</v>
@@ -45011,7 +45011,7 @@
       </c>
       <c r="Z327" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AA327" t="inlineStr">
@@ -45021,7 +45021,7 @@
       </c>
       <c r="AB327" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>22:46</t>
         </is>
       </c>
       <c r="AC327" t="inlineStr">
@@ -45066,10 +45066,10 @@
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>122254964</v>
+        <v>122254503</v>
       </c>
       <c r="B328" t="n">
-        <v>56282</v>
+        <v>56275</v>
       </c>
       <c r="C328" t="inlineStr">
         <is>
@@ -45078,25 +45078,25 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E328" t="n">
-        <v>205992</v>
+        <v>205998</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
@@ -45120,10 +45120,10 @@
         </is>
       </c>
       <c r="Q328" t="n">
-        <v>586430</v>
+        <v>586313</v>
       </c>
       <c r="R328" t="n">
-        <v>6311142</v>
+        <v>6311124</v>
       </c>
       <c r="S328" t="n">
         <v>5</v>
@@ -45155,7 +45155,7 @@
       </c>
       <c r="Z328" t="inlineStr">
         <is>
-          <t>22:33</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AA328" t="inlineStr">
@@ -45165,7 +45165,7 @@
       </c>
       <c r="AB328" t="inlineStr">
         <is>
-          <t>22:34</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AC328" t="inlineStr">
@@ -45210,10 +45210,10 @@
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>122254627</v>
+        <v>122254498</v>
       </c>
       <c r="B329" t="n">
-        <v>56294</v>
+        <v>56275</v>
       </c>
       <c r="C329" t="inlineStr">
         <is>
@@ -45222,25 +45222,25 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E329" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
@@ -45264,10 +45264,10 @@
         </is>
       </c>
       <c r="Q329" t="n">
-        <v>586306</v>
+        <v>586393</v>
       </c>
       <c r="R329" t="n">
-        <v>6311131</v>
+        <v>6311147</v>
       </c>
       <c r="S329" t="n">
         <v>5</v>
@@ -45299,7 +45299,7 @@
       </c>
       <c r="Z329" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AA329" t="inlineStr">
@@ -45309,7 +45309,7 @@
       </c>
       <c r="AB329" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AC329" t="inlineStr">
@@ -45354,10 +45354,10 @@
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>122254607</v>
+        <v>122254318</v>
       </c>
       <c r="B330" t="n">
-        <v>56294</v>
+        <v>56289</v>
       </c>
       <c r="C330" t="inlineStr">
         <is>
@@ -45370,21 +45370,21 @@
         </is>
       </c>
       <c r="E330" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
@@ -45408,10 +45408,10 @@
         </is>
       </c>
       <c r="Q330" t="n">
-        <v>586415</v>
+        <v>586455</v>
       </c>
       <c r="R330" t="n">
-        <v>6311149</v>
+        <v>6311228</v>
       </c>
       <c r="S330" t="n">
         <v>5</v>
@@ -45443,7 +45443,7 @@
       </c>
       <c r="Z330" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>23:22</t>
         </is>
       </c>
       <c r="AA330" t="inlineStr">
@@ -45453,7 +45453,7 @@
       </c>
       <c r="AB330" t="inlineStr">
         <is>
-          <t>23:03</t>
+          <t>23:23</t>
         </is>
       </c>
       <c r="AC330" t="inlineStr">
@@ -45498,10 +45498,10 @@
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>122254514</v>
+        <v>122254306</v>
       </c>
       <c r="B331" t="n">
-        <v>56275</v>
+        <v>56289</v>
       </c>
       <c r="C331" t="inlineStr">
         <is>
@@ -45510,25 +45510,25 @@
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E331" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I331" t="inlineStr">
@@ -45552,10 +45552,10 @@
         </is>
       </c>
       <c r="Q331" t="n">
-        <v>586408</v>
+        <v>586473</v>
       </c>
       <c r="R331" t="n">
-        <v>6311124</v>
+        <v>6311192</v>
       </c>
       <c r="S331" t="n">
         <v>5</v>
@@ -45587,7 +45587,7 @@
       </c>
       <c r="Z331" t="inlineStr">
         <is>
-          <t>22:43</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AA331" t="inlineStr">
@@ -45597,7 +45597,7 @@
       </c>
       <c r="AB331" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AC331" t="inlineStr">
@@ -45642,10 +45642,10 @@
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>122254390</v>
+        <v>122254951</v>
       </c>
       <c r="B332" t="n">
-        <v>56289</v>
+        <v>56282</v>
       </c>
       <c r="C332" t="inlineStr">
         <is>
@@ -45658,21 +45658,21 @@
         </is>
       </c>
       <c r="E332" t="n">
-        <v>100092</v>
+        <v>205992</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
@@ -45696,10 +45696,10 @@
         </is>
       </c>
       <c r="Q332" t="n">
-        <v>586374</v>
+        <v>586459</v>
       </c>
       <c r="R332" t="n">
-        <v>6311139</v>
+        <v>6311154</v>
       </c>
       <c r="S332" t="n">
         <v>5</v>
@@ -45731,7 +45731,7 @@
       </c>
       <c r="Z332" t="inlineStr">
         <is>
-          <t>22:46</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AA332" t="inlineStr">
@@ -45741,7 +45741,7 @@
       </c>
       <c r="AB332" t="inlineStr">
         <is>
-          <t>22:47</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AC332" t="inlineStr">
@@ -45786,10 +45786,10 @@
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>122254966</v>
+        <v>122254606</v>
       </c>
       <c r="B333" t="n">
-        <v>56282</v>
+        <v>56294</v>
       </c>
       <c r="C333" t="inlineStr">
         <is>
@@ -45802,21 +45802,21 @@
         </is>
       </c>
       <c r="E333" t="n">
-        <v>205992</v>
+        <v>205995</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
@@ -45840,10 +45840,10 @@
         </is>
       </c>
       <c r="Q333" t="n">
-        <v>586467</v>
+        <v>586415</v>
       </c>
       <c r="R333" t="n">
-        <v>6311178</v>
+        <v>6311146</v>
       </c>
       <c r="S333" t="n">
         <v>5</v>
@@ -45875,7 +45875,7 @@
       </c>
       <c r="Z333" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AA333" t="inlineStr">
@@ -45885,7 +45885,7 @@
       </c>
       <c r="AB333" t="inlineStr">
         <is>
-          <t>22:33</t>
+          <t>23:03</t>
         </is>
       </c>
       <c r="AC333" t="inlineStr">
@@ -45930,7 +45930,7 @@
     </row>
     <row r="334">
       <c r="A334" t="n">
-        <v>122254651</v>
+        <v>122254656</v>
       </c>
       <c r="B334" t="n">
         <v>56294</v>
@@ -45984,10 +45984,10 @@
         </is>
       </c>
       <c r="Q334" t="n">
-        <v>586425</v>
+        <v>586483</v>
       </c>
       <c r="R334" t="n">
-        <v>6311113</v>
+        <v>6311186</v>
       </c>
       <c r="S334" t="n">
         <v>5</v>
@@ -46019,7 +46019,7 @@
       </c>
       <c r="Z334" t="inlineStr">
         <is>
-          <t>22:35</t>
+          <t>22:31</t>
         </is>
       </c>
       <c r="AA334" t="inlineStr">
@@ -46029,7 +46029,7 @@
       </c>
       <c r="AB334" t="inlineStr">
         <is>
-          <t>22:36</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AC334" t="inlineStr">
@@ -46074,7 +46074,7 @@
     </row>
     <row r="335">
       <c r="A335" t="n">
-        <v>122254612</v>
+        <v>122254611</v>
       </c>
       <c r="B335" t="n">
         <v>56294</v>
@@ -46128,10 +46128,10 @@
         </is>
       </c>
       <c r="Q335" t="n">
-        <v>586371</v>
+        <v>586370</v>
       </c>
       <c r="R335" t="n">
-        <v>6311135</v>
+        <v>6311139</v>
       </c>
       <c r="S335" t="n">
         <v>5</v>
@@ -46218,10 +46218,10 @@
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>122254644</v>
+        <v>122254836</v>
       </c>
       <c r="B336" t="n">
-        <v>56294</v>
+        <v>56292</v>
       </c>
       <c r="C336" t="inlineStr">
         <is>
@@ -46234,21 +46234,21 @@
         </is>
       </c>
       <c r="E336" t="n">
-        <v>205995</v>
+        <v>100111</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
@@ -46272,10 +46272,10 @@
         </is>
       </c>
       <c r="Q336" t="n">
-        <v>586429</v>
+        <v>586474</v>
       </c>
       <c r="R336" t="n">
-        <v>6311115</v>
+        <v>6311176</v>
       </c>
       <c r="S336" t="n">
         <v>5</v>
@@ -46307,7 +46307,7 @@
       </c>
       <c r="Z336" t="inlineStr">
         <is>
-          <t>22:36</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AA336" t="inlineStr">
@@ -46317,7 +46317,7 @@
       </c>
       <c r="AB336" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AC336" t="inlineStr">
@@ -46362,10 +46362,10 @@
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>122254633</v>
+        <v>122254341</v>
       </c>
       <c r="B337" t="n">
-        <v>56294</v>
+        <v>56289</v>
       </c>
       <c r="C337" t="inlineStr">
         <is>
@@ -46378,21 +46378,21 @@
         </is>
       </c>
       <c r="E337" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
@@ -46416,7 +46416,7 @@
         </is>
       </c>
       <c r="Q337" t="n">
-        <v>586396</v>
+        <v>586415</v>
       </c>
       <c r="R337" t="n">
         <v>6311146</v>
@@ -46451,7 +46451,7 @@
       </c>
       <c r="Z337" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AA337" t="inlineStr">
@@ -46461,7 +46461,7 @@
       </c>
       <c r="AB337" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>23:03</t>
         </is>
       </c>
       <c r="AC337" t="inlineStr">
@@ -46506,7 +46506,7 @@
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>122254341</v>
+        <v>122254313</v>
       </c>
       <c r="B338" t="n">
         <v>56289</v>
@@ -46560,10 +46560,10 @@
         </is>
       </c>
       <c r="Q338" t="n">
-        <v>586415</v>
+        <v>586449</v>
       </c>
       <c r="R338" t="n">
-        <v>6311146</v>
+        <v>6311155</v>
       </c>
       <c r="S338" t="n">
         <v>5</v>
@@ -46595,7 +46595,7 @@
       </c>
       <c r="Z338" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA338" t="inlineStr">
@@ -46605,7 +46605,7 @@
       </c>
       <c r="AB338" t="inlineStr">
         <is>
-          <t>23:03</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC338" t="inlineStr">
@@ -46650,7 +46650,7 @@
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>122254343</v>
+        <v>122254373</v>
       </c>
       <c r="B339" t="n">
         <v>56289</v>
@@ -46704,10 +46704,10 @@
         </is>
       </c>
       <c r="Q339" t="n">
-        <v>586388</v>
+        <v>586307</v>
       </c>
       <c r="R339" t="n">
-        <v>6311142</v>
+        <v>6311133</v>
       </c>
       <c r="S339" t="n">
         <v>5</v>
@@ -46739,7 +46739,7 @@
       </c>
       <c r="Z339" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:49</t>
         </is>
       </c>
       <c r="AA339" t="inlineStr">
@@ -46749,7 +46749,7 @@
       </c>
       <c r="AB339" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AC339" t="inlineStr">
@@ -46794,10 +46794,10 @@
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>122254370</v>
+        <v>122254845</v>
       </c>
       <c r="B340" t="n">
-        <v>56289</v>
+        <v>56292</v>
       </c>
       <c r="C340" t="inlineStr">
         <is>
@@ -46810,21 +46810,21 @@
         </is>
       </c>
       <c r="E340" t="n">
-        <v>100092</v>
+        <v>100111</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
@@ -46848,10 +46848,10 @@
         </is>
       </c>
       <c r="Q340" t="n">
-        <v>586309</v>
+        <v>586370</v>
       </c>
       <c r="R340" t="n">
-        <v>6311119</v>
+        <v>6311139</v>
       </c>
       <c r="S340" t="n">
         <v>5</v>
@@ -46883,7 +46883,7 @@
       </c>
       <c r="Z340" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>22:59</t>
         </is>
       </c>
       <c r="AA340" t="inlineStr">
@@ -46893,7 +46893,7 @@
       </c>
       <c r="AB340" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AC340" t="inlineStr">
@@ -46938,10 +46938,10 @@
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>122254963</v>
+        <v>122254856</v>
       </c>
       <c r="B341" t="n">
-        <v>56282</v>
+        <v>56292</v>
       </c>
       <c r="C341" t="inlineStr">
         <is>
@@ -46954,21 +46954,21 @@
         </is>
       </c>
       <c r="E341" t="n">
-        <v>205992</v>
+        <v>100111</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I341" t="inlineStr">
@@ -46992,10 +46992,10 @@
         </is>
       </c>
       <c r="Q341" t="n">
-        <v>586374</v>
+        <v>586327</v>
       </c>
       <c r="R341" t="n">
-        <v>6311140</v>
+        <v>6311118</v>
       </c>
       <c r="S341" t="n">
         <v>5</v>
@@ -47027,7 +47027,7 @@
       </c>
       <c r="Z341" t="inlineStr">
         <is>
-          <t>22:46</t>
+          <t>22:57</t>
         </is>
       </c>
       <c r="AA341" t="inlineStr">
@@ -47037,7 +47037,7 @@
       </c>
       <c r="AB341" t="inlineStr">
         <is>
-          <t>22:47</t>
+          <t>22:58</t>
         </is>
       </c>
       <c r="AC341" t="inlineStr">
@@ -47082,10 +47082,10 @@
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>122254606</v>
+        <v>122254513</v>
       </c>
       <c r="B342" t="n">
-        <v>56294</v>
+        <v>56275</v>
       </c>
       <c r="C342" t="inlineStr">
         <is>
@@ -47094,25 +47094,25 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E342" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
@@ -47136,7 +47136,7 @@
         </is>
       </c>
       <c r="Q342" t="n">
-        <v>586415</v>
+        <v>586396</v>
       </c>
       <c r="R342" t="n">
         <v>6311146</v>
@@ -47171,7 +47171,7 @@
       </c>
       <c r="Z342" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AA342" t="inlineStr">
@@ -47181,7 +47181,7 @@
       </c>
       <c r="AB342" t="inlineStr">
         <is>
-          <t>23:03</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AC342" t="inlineStr">
@@ -47226,10 +47226,10 @@
     </row>
     <row r="343">
       <c r="A343" t="n">
-        <v>122254656</v>
+        <v>122254957</v>
       </c>
       <c r="B343" t="n">
-        <v>56294</v>
+        <v>56282</v>
       </c>
       <c r="C343" t="inlineStr">
         <is>
@@ -47242,21 +47242,21 @@
         </is>
       </c>
       <c r="E343" t="n">
-        <v>205995</v>
+        <v>205992</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
@@ -47280,10 +47280,10 @@
         </is>
       </c>
       <c r="Q343" t="n">
-        <v>586483</v>
+        <v>586444</v>
       </c>
       <c r="R343" t="n">
-        <v>6311186</v>
+        <v>6311160</v>
       </c>
       <c r="S343" t="n">
         <v>5</v>
@@ -47315,7 +47315,7 @@
       </c>
       <c r="Z343" t="inlineStr">
         <is>
-          <t>22:31</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="AA343" t="inlineStr">
@@ -47325,7 +47325,7 @@
       </c>
       <c r="AB343" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AC343" t="inlineStr">
@@ -47370,7 +47370,7 @@
     </row>
     <row r="344">
       <c r="A344" t="n">
-        <v>122254513</v>
+        <v>122254499</v>
       </c>
       <c r="B344" t="n">
         <v>56275</v>
@@ -47424,10 +47424,10 @@
         </is>
       </c>
       <c r="Q344" t="n">
-        <v>586396</v>
+        <v>586392</v>
       </c>
       <c r="R344" t="n">
-        <v>6311146</v>
+        <v>6311147</v>
       </c>
       <c r="S344" t="n">
         <v>5</v>
@@ -47459,7 +47459,7 @@
       </c>
       <c r="Z344" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AA344" t="inlineStr">
@@ -47469,7 +47469,7 @@
       </c>
       <c r="AB344" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AC344" t="inlineStr">
@@ -47514,10 +47514,10 @@
     </row>
     <row r="345">
       <c r="A345" t="n">
-        <v>122254512</v>
+        <v>122254648</v>
       </c>
       <c r="B345" t="n">
-        <v>56275</v>
+        <v>56294</v>
       </c>
       <c r="C345" t="inlineStr">
         <is>
@@ -47526,25 +47526,25 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E345" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
@@ -47568,10 +47568,10 @@
         </is>
       </c>
       <c r="Q345" t="n">
-        <v>586379</v>
+        <v>586418</v>
       </c>
       <c r="R345" t="n">
-        <v>6311136</v>
+        <v>6311107</v>
       </c>
       <c r="S345" t="n">
         <v>5</v>
@@ -47603,7 +47603,7 @@
       </c>
       <c r="Z345" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>22:36</t>
         </is>
       </c>
       <c r="AA345" t="inlineStr">
@@ -47613,7 +47613,7 @@
       </c>
       <c r="AB345" t="inlineStr">
         <is>
-          <t>22:46</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AC345" t="inlineStr">
@@ -47658,10 +47658,10 @@
     </row>
     <row r="346">
       <c r="A346" t="n">
-        <v>122254392</v>
+        <v>122254963</v>
       </c>
       <c r="B346" t="n">
-        <v>56289</v>
+        <v>56282</v>
       </c>
       <c r="C346" t="inlineStr">
         <is>
@@ -47674,21 +47674,21 @@
         </is>
       </c>
       <c r="E346" t="n">
-        <v>100092</v>
+        <v>205992</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
@@ -47712,10 +47712,10 @@
         </is>
       </c>
       <c r="Q346" t="n">
-        <v>586384</v>
+        <v>586374</v>
       </c>
       <c r="R346" t="n">
-        <v>6311139</v>
+        <v>6311140</v>
       </c>
       <c r="S346" t="n">
         <v>5</v>
@@ -47747,7 +47747,7 @@
       </c>
       <c r="Z346" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>22:46</t>
         </is>
       </c>
       <c r="AA346" t="inlineStr">
@@ -47757,7 +47757,7 @@
       </c>
       <c r="AB346" t="inlineStr">
         <is>
-          <t>22:46</t>
+          <t>22:47</t>
         </is>
       </c>
       <c r="AC346" t="inlineStr">
@@ -47802,7 +47802,7 @@
     </row>
     <row r="347">
       <c r="A347" t="n">
-        <v>122254584</v>
+        <v>122254653</v>
       </c>
       <c r="B347" t="n">
         <v>56294</v>
@@ -47856,10 +47856,10 @@
         </is>
       </c>
       <c r="Q347" t="n">
-        <v>586473</v>
+        <v>586430</v>
       </c>
       <c r="R347" t="n">
-        <v>6311192</v>
+        <v>6311142</v>
       </c>
       <c r="S347" t="n">
         <v>5</v>
@@ -47891,7 +47891,7 @@
       </c>
       <c r="Z347" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="AA347" t="inlineStr">
@@ -47901,7 +47901,7 @@
       </c>
       <c r="AB347" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>22:34</t>
         </is>
       </c>
       <c r="AC347" t="inlineStr">
@@ -47946,10 +47946,10 @@
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>122254474</v>
+        <v>122254609</v>
       </c>
       <c r="B348" t="n">
-        <v>56275</v>
+        <v>56294</v>
       </c>
       <c r="C348" t="inlineStr">
         <is>
@@ -47958,25 +47958,25 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E348" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I348" t="inlineStr">
@@ -48000,10 +48000,10 @@
         </is>
       </c>
       <c r="Q348" t="n">
-        <v>586443</v>
+        <v>586392</v>
       </c>
       <c r="R348" t="n">
-        <v>6311164</v>
+        <v>6311147</v>
       </c>
       <c r="S348" t="n">
         <v>5</v>
@@ -48035,7 +48035,7 @@
       </c>
       <c r="Z348" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AA348" t="inlineStr">
@@ -48045,7 +48045,7 @@
       </c>
       <c r="AB348" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AC348" t="inlineStr">
@@ -48090,7 +48090,7 @@
     </row>
     <row r="349">
       <c r="A349" t="n">
-        <v>122254588</v>
+        <v>122254659</v>
       </c>
       <c r="B349" t="n">
         <v>56294</v>
@@ -48144,10 +48144,10 @@
         </is>
       </c>
       <c r="Q349" t="n">
-        <v>586415</v>
+        <v>586489</v>
       </c>
       <c r="R349" t="n">
-        <v>6311196</v>
+        <v>6311181</v>
       </c>
       <c r="S349" t="n">
         <v>5</v>
@@ -48179,7 +48179,7 @@
       </c>
       <c r="Z349" t="inlineStr">
         <is>
-          <t>23:22</t>
+          <t>22:31</t>
         </is>
       </c>
       <c r="AA349" t="inlineStr">
@@ -48189,7 +48189,7 @@
       </c>
       <c r="AB349" t="inlineStr">
         <is>
-          <t>23:23</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AC349" t="inlineStr">
@@ -48234,10 +48234,10 @@
     </row>
     <row r="350">
       <c r="A350" t="n">
-        <v>122254855</v>
+        <v>122254416</v>
       </c>
       <c r="B350" t="n">
-        <v>56292</v>
+        <v>56289</v>
       </c>
       <c r="C350" t="inlineStr">
         <is>
@@ -48250,21 +48250,21 @@
         </is>
       </c>
       <c r="E350" t="n">
-        <v>100111</v>
+        <v>100092</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I350" t="inlineStr">
@@ -48288,10 +48288,10 @@
         </is>
       </c>
       <c r="Q350" t="n">
-        <v>586330</v>
+        <v>586410</v>
       </c>
       <c r="R350" t="n">
-        <v>6311120</v>
+        <v>6311140</v>
       </c>
       <c r="S350" t="n">
         <v>5</v>
@@ -48323,7 +48323,7 @@
       </c>
       <c r="Z350" t="inlineStr">
         <is>
-          <t>22:57</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="AA350" t="inlineStr">
@@ -48333,7 +48333,7 @@
       </c>
       <c r="AB350" t="inlineStr">
         <is>
-          <t>22:58</t>
+          <t>22:34</t>
         </is>
       </c>
       <c r="AC350" t="inlineStr">
@@ -48378,10 +48378,10 @@
     </row>
     <row r="351">
       <c r="A351" t="n">
-        <v>122254587</v>
+        <v>122254396</v>
       </c>
       <c r="B351" t="n">
-        <v>56294</v>
+        <v>56289</v>
       </c>
       <c r="C351" t="inlineStr">
         <is>
@@ -48394,21 +48394,21 @@
         </is>
       </c>
       <c r="E351" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I351" t="inlineStr">
@@ -48432,10 +48432,10 @@
         </is>
       </c>
       <c r="Q351" t="n">
-        <v>586443</v>
+        <v>586408</v>
       </c>
       <c r="R351" t="n">
-        <v>6311163</v>
+        <v>6311124</v>
       </c>
       <c r="S351" t="n">
         <v>5</v>
@@ -48467,7 +48467,7 @@
       </c>
       <c r="Z351" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>22:43</t>
         </is>
       </c>
       <c r="AA351" t="inlineStr">
@@ -48477,7 +48477,7 @@
       </c>
       <c r="AB351" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AC351" t="inlineStr">
@@ -48522,10 +48522,10 @@
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>122254503</v>
+        <v>122254365</v>
       </c>
       <c r="B352" t="n">
-        <v>56275</v>
+        <v>56289</v>
       </c>
       <c r="C352" t="inlineStr">
         <is>
@@ -48534,25 +48534,25 @@
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E352" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I352" t="inlineStr">
@@ -48576,10 +48576,10 @@
         </is>
       </c>
       <c r="Q352" t="n">
-        <v>586313</v>
+        <v>586276</v>
       </c>
       <c r="R352" t="n">
-        <v>6311124</v>
+        <v>6311100</v>
       </c>
       <c r="S352" t="n">
         <v>5</v>
@@ -48611,7 +48611,7 @@
       </c>
       <c r="Z352" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AA352" t="inlineStr">
@@ -48621,7 +48621,7 @@
       </c>
       <c r="AB352" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>22:52</t>
         </is>
       </c>
       <c r="AC352" t="inlineStr">
@@ -48666,10 +48666,10 @@
     </row>
     <row r="353">
       <c r="A353" t="n">
-        <v>122254499</v>
+        <v>122254315</v>
       </c>
       <c r="B353" t="n">
-        <v>56275</v>
+        <v>56289</v>
       </c>
       <c r="C353" t="inlineStr">
         <is>
@@ -48678,25 +48678,25 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E353" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I353" t="inlineStr">
@@ -48720,10 +48720,10 @@
         </is>
       </c>
       <c r="Q353" t="n">
-        <v>586392</v>
+        <v>586441</v>
       </c>
       <c r="R353" t="n">
-        <v>6311147</v>
+        <v>6311155</v>
       </c>
       <c r="S353" t="n">
         <v>5</v>
@@ -48755,7 +48755,7 @@
       </c>
       <c r="Z353" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AA353" t="inlineStr">
@@ -48765,7 +48765,7 @@
       </c>
       <c r="AB353" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AC353" t="inlineStr">
@@ -48810,10 +48810,10 @@
     </row>
     <row r="354">
       <c r="A354" t="n">
-        <v>122254643</v>
+        <v>122254312</v>
       </c>
       <c r="B354" t="n">
-        <v>56294</v>
+        <v>56289</v>
       </c>
       <c r="C354" t="inlineStr">
         <is>
@@ -48826,21 +48826,21 @@
         </is>
       </c>
       <c r="E354" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I354" t="inlineStr">
@@ -48864,10 +48864,10 @@
         </is>
       </c>
       <c r="Q354" t="n">
-        <v>586424</v>
+        <v>586452</v>
       </c>
       <c r="R354" t="n">
-        <v>6311135</v>
+        <v>6311152</v>
       </c>
       <c r="S354" t="n">
         <v>5</v>
@@ -48899,7 +48899,7 @@
       </c>
       <c r="Z354" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA354" t="inlineStr">
@@ -48909,7 +48909,7 @@
       </c>
       <c r="AB354" t="inlineStr">
         <is>
-          <t>22:38</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC354" t="inlineStr">
@@ -48954,10 +48954,10 @@
     </row>
     <row r="355">
       <c r="A355" t="n">
-        <v>122254626</v>
+        <v>122254835</v>
       </c>
       <c r="B355" t="n">
-        <v>56294</v>
+        <v>56292</v>
       </c>
       <c r="C355" t="inlineStr">
         <is>
@@ -48970,21 +48970,21 @@
         </is>
       </c>
       <c r="E355" t="n">
-        <v>205995</v>
+        <v>100111</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I355" t="inlineStr">
@@ -49008,10 +49008,10 @@
         </is>
       </c>
       <c r="Q355" t="n">
-        <v>586313</v>
+        <v>586473</v>
       </c>
       <c r="R355" t="n">
-        <v>6311124</v>
+        <v>6311192</v>
       </c>
       <c r="S355" t="n">
         <v>5</v>
@@ -49043,7 +49043,7 @@
       </c>
       <c r="Z355" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AA355" t="inlineStr">
@@ -49053,7 +49053,7 @@
       </c>
       <c r="AB355" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AC355" t="inlineStr">
@@ -49098,10 +49098,10 @@
     </row>
     <row r="356">
       <c r="A356" t="n">
-        <v>122254307</v>
+        <v>122254862</v>
       </c>
       <c r="B356" t="n">
-        <v>56289</v>
+        <v>56292</v>
       </c>
       <c r="C356" t="inlineStr">
         <is>
@@ -49114,21 +49114,21 @@
         </is>
       </c>
       <c r="E356" t="n">
-        <v>100092</v>
+        <v>100111</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I356" t="inlineStr">
@@ -49152,10 +49152,10 @@
         </is>
       </c>
       <c r="Q356" t="n">
-        <v>586477</v>
+        <v>586288</v>
       </c>
       <c r="R356" t="n">
-        <v>6311186</v>
+        <v>6311100</v>
       </c>
       <c r="S356" t="n">
         <v>5</v>
@@ -49187,7 +49187,7 @@
       </c>
       <c r="Z356" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>22:55</t>
         </is>
       </c>
       <c r="AA356" t="inlineStr">
@@ -49197,7 +49197,7 @@
       </c>
       <c r="AB356" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>22:56</t>
         </is>
       </c>
       <c r="AC356" t="inlineStr">
@@ -49242,10 +49242,10 @@
     </row>
     <row r="357">
       <c r="A357" t="n">
-        <v>122254318</v>
+        <v>122254610</v>
       </c>
       <c r="B357" t="n">
-        <v>56289</v>
+        <v>56294</v>
       </c>
       <c r="C357" t="inlineStr">
         <is>
@@ -49258,21 +49258,21 @@
         </is>
       </c>
       <c r="E357" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I357" t="inlineStr">
@@ -49296,10 +49296,10 @@
         </is>
       </c>
       <c r="Q357" t="n">
-        <v>586455</v>
+        <v>586389</v>
       </c>
       <c r="R357" t="n">
-        <v>6311228</v>
+        <v>6311141</v>
       </c>
       <c r="S357" t="n">
         <v>5</v>
@@ -49331,7 +49331,7 @@
       </c>
       <c r="Z357" t="inlineStr">
         <is>
-          <t>23:22</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA357" t="inlineStr">
@@ -49341,7 +49341,7 @@
       </c>
       <c r="AB357" t="inlineStr">
         <is>
-          <t>23:23</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AC357" t="inlineStr">
@@ -49386,10 +49386,10 @@
     </row>
     <row r="358">
       <c r="A358" t="n">
-        <v>122254309</v>
+        <v>122254633</v>
       </c>
       <c r="B358" t="n">
-        <v>56289</v>
+        <v>56294</v>
       </c>
       <c r="C358" t="inlineStr">
         <is>
@@ -49402,21 +49402,21 @@
         </is>
       </c>
       <c r="E358" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H358" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I358" t="inlineStr">
@@ -49440,10 +49440,10 @@
         </is>
       </c>
       <c r="Q358" t="n">
-        <v>586456</v>
+        <v>586396</v>
       </c>
       <c r="R358" t="n">
-        <v>6311158</v>
+        <v>6311146</v>
       </c>
       <c r="S358" t="n">
         <v>5</v>
@@ -49475,7 +49475,7 @@
       </c>
       <c r="Z358" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AA358" t="inlineStr">
@@ -49485,7 +49485,7 @@
       </c>
       <c r="AB358" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AC358" t="inlineStr">
@@ -49530,10 +49530,10 @@
     </row>
     <row r="359">
       <c r="A359" t="n">
-        <v>122254880</v>
+        <v>122254511</v>
       </c>
       <c r="B359" t="n">
-        <v>56292</v>
+        <v>56275</v>
       </c>
       <c r="C359" t="inlineStr">
         <is>
@@ -49542,25 +49542,25 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E359" t="n">
-        <v>100111</v>
+        <v>205998</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I359" t="inlineStr">
@@ -49584,10 +49584,10 @@
         </is>
       </c>
       <c r="Q359" t="n">
-        <v>586303</v>
+        <v>586374</v>
       </c>
       <c r="R359" t="n">
-        <v>6311115</v>
+        <v>6311139</v>
       </c>
       <c r="S359" t="n">
         <v>5</v>
@@ -49619,7 +49619,7 @@
       </c>
       <c r="Z359" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>22:46</t>
         </is>
       </c>
       <c r="AA359" t="inlineStr">
@@ -49629,7 +49629,7 @@
       </c>
       <c r="AB359" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>22:47</t>
         </is>
       </c>
       <c r="AC359" t="inlineStr">
@@ -49674,7 +49674,7 @@
     </row>
     <row r="360">
       <c r="A360" t="n">
-        <v>122254313</v>
+        <v>122254317</v>
       </c>
       <c r="B360" t="n">
         <v>56289</v>
@@ -49728,10 +49728,10 @@
         </is>
       </c>
       <c r="Q360" t="n">
-        <v>586449</v>
+        <v>586438</v>
       </c>
       <c r="R360" t="n">
-        <v>6311155</v>
+        <v>6311222</v>
       </c>
       <c r="S360" t="n">
         <v>5</v>
@@ -49763,7 +49763,7 @@
       </c>
       <c r="Z360" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>23:22</t>
         </is>
       </c>
       <c r="AA360" t="inlineStr">
@@ -49773,7 +49773,7 @@
       </c>
       <c r="AB360" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>23:23</t>
         </is>
       </c>
       <c r="AC360" t="inlineStr">
@@ -49818,7 +49818,7 @@
     </row>
     <row r="361">
       <c r="A361" t="n">
-        <v>122254416</v>
+        <v>122254412</v>
       </c>
       <c r="B361" t="n">
         <v>56289</v>
@@ -49872,10 +49872,10 @@
         </is>
       </c>
       <c r="Q361" t="n">
-        <v>586410</v>
+        <v>586424</v>
       </c>
       <c r="R361" t="n">
-        <v>6311140</v>
+        <v>6311135</v>
       </c>
       <c r="S361" t="n">
         <v>5</v>
@@ -49907,7 +49907,7 @@
       </c>
       <c r="Z361" t="inlineStr">
         <is>
-          <t>22:33</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AA361" t="inlineStr">
@@ -49917,7 +49917,7 @@
       </c>
       <c r="AB361" t="inlineStr">
         <is>
-          <t>22:34</t>
+          <t>22:38</t>
         </is>
       </c>
       <c r="AC361" t="inlineStr">
@@ -49962,10 +49962,10 @@
     </row>
     <row r="362">
       <c r="A362" t="n">
-        <v>122254655</v>
+        <v>122254415</v>
       </c>
       <c r="B362" t="n">
-        <v>56294</v>
+        <v>56289</v>
       </c>
       <c r="C362" t="inlineStr">
         <is>
@@ -49978,21 +49978,21 @@
         </is>
       </c>
       <c r="E362" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I362" t="inlineStr">
@@ -50016,10 +50016,10 @@
         </is>
       </c>
       <c r="Q362" t="n">
-        <v>586475</v>
+        <v>586425</v>
       </c>
       <c r="R362" t="n">
-        <v>6311187</v>
+        <v>6311135</v>
       </c>
       <c r="S362" t="n">
         <v>5</v>
@@ -50051,7 +50051,7 @@
       </c>
       <c r="Z362" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AA362" t="inlineStr">
@@ -50061,7 +50061,7 @@
       </c>
       <c r="AB362" t="inlineStr">
         <is>
-          <t>22:33</t>
+          <t>22:38</t>
         </is>
       </c>
       <c r="AC362" t="inlineStr">
@@ -50106,10 +50106,10 @@
     </row>
     <row r="363">
       <c r="A363" t="n">
-        <v>122254659</v>
+        <v>122254352</v>
       </c>
       <c r="B363" t="n">
-        <v>56294</v>
+        <v>56289</v>
       </c>
       <c r="C363" t="inlineStr">
         <is>
@@ -50122,21 +50122,21 @@
         </is>
       </c>
       <c r="E363" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I363" t="inlineStr">
@@ -50160,10 +50160,10 @@
         </is>
       </c>
       <c r="Q363" t="n">
-        <v>586489</v>
+        <v>586288</v>
       </c>
       <c r="R363" t="n">
-        <v>6311181</v>
+        <v>6311100</v>
       </c>
       <c r="S363" t="n">
         <v>5</v>
@@ -50195,7 +50195,7 @@
       </c>
       <c r="Z363" t="inlineStr">
         <is>
-          <t>22:31</t>
+          <t>22:55</t>
         </is>
       </c>
       <c r="AA363" t="inlineStr">
@@ -50205,7 +50205,7 @@
       </c>
       <c r="AB363" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>22:56</t>
         </is>
       </c>
       <c r="AC363" t="inlineStr">
@@ -50250,10 +50250,10 @@
     </row>
     <row r="364">
       <c r="A364" t="n">
-        <v>122254951</v>
+        <v>122254308</v>
       </c>
       <c r="B364" t="n">
-        <v>56282</v>
+        <v>56289</v>
       </c>
       <c r="C364" t="inlineStr">
         <is>
@@ -50266,21 +50266,21 @@
         </is>
       </c>
       <c r="E364" t="n">
-        <v>205992</v>
+        <v>100092</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I364" t="inlineStr">
@@ -50304,10 +50304,10 @@
         </is>
       </c>
       <c r="Q364" t="n">
-        <v>586459</v>
+        <v>586455</v>
       </c>
       <c r="R364" t="n">
-        <v>6311154</v>
+        <v>6311159</v>
       </c>
       <c r="S364" t="n">
         <v>5</v>
@@ -50394,10 +50394,10 @@
     </row>
     <row r="365">
       <c r="A365" t="n">
-        <v>122254476</v>
+        <v>122254417</v>
       </c>
       <c r="B365" t="n">
-        <v>56275</v>
+        <v>56289</v>
       </c>
       <c r="C365" t="inlineStr">
         <is>
@@ -50406,25 +50406,25 @@
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E365" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I365" t="inlineStr">
@@ -50448,10 +50448,10 @@
         </is>
       </c>
       <c r="Q365" t="n">
-        <v>586418</v>
+        <v>586426</v>
       </c>
       <c r="R365" t="n">
-        <v>6311167</v>
+        <v>6311145</v>
       </c>
       <c r="S365" t="n">
         <v>5</v>
@@ -50483,7 +50483,7 @@
       </c>
       <c r="Z365" t="inlineStr">
         <is>
-          <t>23:23</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="AA365" t="inlineStr">
@@ -50493,7 +50493,7 @@
       </c>
       <c r="AB365" t="inlineStr">
         <is>
-          <t>23:24</t>
+          <t>22:34</t>
         </is>
       </c>
       <c r="AC365" t="inlineStr">
@@ -50538,10 +50538,10 @@
     </row>
     <row r="366">
       <c r="A366" t="n">
-        <v>122254316</v>
+        <v>122254857</v>
       </c>
       <c r="B366" t="n">
-        <v>56289</v>
+        <v>56292</v>
       </c>
       <c r="C366" t="inlineStr">
         <is>
@@ -50554,21 +50554,21 @@
         </is>
       </c>
       <c r="E366" t="n">
-        <v>100092</v>
+        <v>100111</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I366" t="inlineStr">
@@ -50592,10 +50592,10 @@
         </is>
       </c>
       <c r="Q366" t="n">
-        <v>586423</v>
+        <v>586317</v>
       </c>
       <c r="R366" t="n">
-        <v>6311166</v>
+        <v>6311115</v>
       </c>
       <c r="S366" t="n">
         <v>5</v>
@@ -50627,7 +50627,7 @@
       </c>
       <c r="Z366" t="inlineStr">
         <is>
-          <t>23:23</t>
+          <t>22:57</t>
         </is>
       </c>
       <c r="AA366" t="inlineStr">
@@ -50637,7 +50637,7 @@
       </c>
       <c r="AB366" t="inlineStr">
         <is>
-          <t>23:24</t>
+          <t>22:58</t>
         </is>
       </c>
       <c r="AC366" t="inlineStr">
@@ -50682,7 +50682,7 @@
     </row>
     <row r="367">
       <c r="A367" t="n">
-        <v>122254611</v>
+        <v>122254649</v>
       </c>
       <c r="B367" t="n">
         <v>56294</v>
@@ -50736,10 +50736,10 @@
         </is>
       </c>
       <c r="Q367" t="n">
-        <v>586370</v>
+        <v>586422</v>
       </c>
       <c r="R367" t="n">
-        <v>6311139</v>
+        <v>6311100</v>
       </c>
       <c r="S367" t="n">
         <v>5</v>
@@ -50771,7 +50771,7 @@
       </c>
       <c r="Z367" t="inlineStr">
         <is>
-          <t>22:59</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="AA367" t="inlineStr">
@@ -50781,7 +50781,7 @@
       </c>
       <c r="AB367" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:36</t>
         </is>
       </c>
       <c r="AC367" t="inlineStr">
@@ -50826,10 +50826,10 @@
     </row>
     <row r="368">
       <c r="A368" t="n">
-        <v>122254615</v>
+        <v>122254475</v>
       </c>
       <c r="B368" t="n">
-        <v>56294</v>
+        <v>56275</v>
       </c>
       <c r="C368" t="inlineStr">
         <is>
@@ -50838,25 +50838,25 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E368" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H368" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I368" t="inlineStr">
@@ -50880,10 +50880,10 @@
         </is>
       </c>
       <c r="Q368" t="n">
-        <v>586329</v>
+        <v>586420</v>
       </c>
       <c r="R368" t="n">
-        <v>6311120</v>
+        <v>6311166</v>
       </c>
       <c r="S368" t="n">
         <v>5</v>
@@ -50915,7 +50915,7 @@
       </c>
       <c r="Z368" t="inlineStr">
         <is>
-          <t>22:57</t>
+          <t>23:23</t>
         </is>
       </c>
       <c r="AA368" t="inlineStr">
@@ -50925,7 +50925,7 @@
       </c>
       <c r="AB368" t="inlineStr">
         <is>
-          <t>22:58</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="AC368" t="inlineStr">
@@ -50970,10 +50970,10 @@
     </row>
     <row r="369">
       <c r="A369" t="n">
-        <v>122254952</v>
+        <v>122254474</v>
       </c>
       <c r="B369" t="n">
-        <v>56282</v>
+        <v>56275</v>
       </c>
       <c r="C369" t="inlineStr">
         <is>
@@ -50982,25 +50982,25 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E369" t="n">
-        <v>205992</v>
+        <v>205998</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I369" t="inlineStr">
@@ -51024,10 +51024,10 @@
         </is>
       </c>
       <c r="Q369" t="n">
-        <v>586455</v>
+        <v>586443</v>
       </c>
       <c r="R369" t="n">
-        <v>6311156</v>
+        <v>6311164</v>
       </c>
       <c r="S369" t="n">
         <v>5</v>
@@ -51059,7 +51059,7 @@
       </c>
       <c r="Z369" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AA369" t="inlineStr">
@@ -51069,7 +51069,7 @@
       </c>
       <c r="AB369" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AC369" t="inlineStr">
@@ -51114,10 +51114,10 @@
     </row>
     <row r="370">
       <c r="A370" t="n">
-        <v>122254854</v>
+        <v>122254650</v>
       </c>
       <c r="B370" t="n">
-        <v>56292</v>
+        <v>56294</v>
       </c>
       <c r="C370" t="inlineStr">
         <is>
@@ -51130,21 +51130,21 @@
         </is>
       </c>
       <c r="E370" t="n">
-        <v>100111</v>
+        <v>205995</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I370" t="inlineStr">
@@ -51168,10 +51168,10 @@
         </is>
       </c>
       <c r="Q370" t="n">
-        <v>586329</v>
+        <v>586422</v>
       </c>
       <c r="R370" t="n">
-        <v>6311120</v>
+        <v>6311105</v>
       </c>
       <c r="S370" t="n">
         <v>5</v>
@@ -51203,7 +51203,7 @@
       </c>
       <c r="Z370" t="inlineStr">
         <is>
-          <t>22:57</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="AA370" t="inlineStr">
@@ -51213,7 +51213,7 @@
       </c>
       <c r="AB370" t="inlineStr">
         <is>
-          <t>22:58</t>
+          <t>22:36</t>
         </is>
       </c>
       <c r="AC370" t="inlineStr">
@@ -51258,10 +51258,10 @@
     </row>
     <row r="371">
       <c r="A371" t="n">
-        <v>122254391</v>
+        <v>122254644</v>
       </c>
       <c r="B371" t="n">
-        <v>56289</v>
+        <v>56294</v>
       </c>
       <c r="C371" t="inlineStr">
         <is>
@@ -51274,21 +51274,21 @@
         </is>
       </c>
       <c r="E371" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I371" t="inlineStr">
@@ -51312,10 +51312,10 @@
         </is>
       </c>
       <c r="Q371" t="n">
-        <v>586379</v>
+        <v>586429</v>
       </c>
       <c r="R371" t="n">
-        <v>6311136</v>
+        <v>6311115</v>
       </c>
       <c r="S371" t="n">
         <v>5</v>
@@ -51347,7 +51347,7 @@
       </c>
       <c r="Z371" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>22:36</t>
         </is>
       </c>
       <c r="AA371" t="inlineStr">
@@ -51357,7 +51357,7 @@
       </c>
       <c r="AB371" t="inlineStr">
         <is>
-          <t>22:46</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AC371" t="inlineStr">
@@ -51402,10 +51402,10 @@
     </row>
     <row r="372">
       <c r="A372" t="n">
-        <v>122254369</v>
+        <v>122254652</v>
       </c>
       <c r="B372" t="n">
-        <v>56289</v>
+        <v>56294</v>
       </c>
       <c r="C372" t="inlineStr">
         <is>
@@ -51418,21 +51418,21 @@
         </is>
       </c>
       <c r="E372" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I372" t="inlineStr">
@@ -51456,10 +51456,10 @@
         </is>
       </c>
       <c r="Q372" t="n">
-        <v>586300</v>
+        <v>586432</v>
       </c>
       <c r="R372" t="n">
-        <v>6311112</v>
+        <v>6311118</v>
       </c>
       <c r="S372" t="n">
         <v>5</v>
@@ -51491,7 +51491,7 @@
       </c>
       <c r="Z372" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>22:34</t>
         </is>
       </c>
       <c r="AA372" t="inlineStr">
@@ -51501,7 +51501,7 @@
       </c>
       <c r="AB372" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="AC372" t="inlineStr">
@@ -51546,10 +51546,10 @@
     </row>
     <row r="373">
       <c r="A373" t="n">
-        <v>122254371</v>
+        <v>122254586</v>
       </c>
       <c r="B373" t="n">
-        <v>56289</v>
+        <v>56294</v>
       </c>
       <c r="C373" t="inlineStr">
         <is>
@@ -51562,21 +51562,21 @@
         </is>
       </c>
       <c r="E373" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H373" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I373" t="inlineStr">
@@ -51600,10 +51600,10 @@
         </is>
       </c>
       <c r="Q373" t="n">
-        <v>586308</v>
+        <v>586446</v>
       </c>
       <c r="R373" t="n">
-        <v>6311132</v>
+        <v>6311158</v>
       </c>
       <c r="S373" t="n">
         <v>5</v>
@@ -51635,7 +51635,7 @@
       </c>
       <c r="Z373" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AA373" t="inlineStr">
@@ -51645,7 +51645,7 @@
       </c>
       <c r="AB373" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AC373" t="inlineStr">
@@ -51690,10 +51690,10 @@
     </row>
     <row r="374">
       <c r="A374" t="n">
-        <v>122254625</v>
+        <v>122254956</v>
       </c>
       <c r="B374" t="n">
-        <v>56294</v>
+        <v>56282</v>
       </c>
       <c r="C374" t="inlineStr">
         <is>
@@ -51706,21 +51706,21 @@
         </is>
       </c>
       <c r="E374" t="n">
-        <v>205995</v>
+        <v>205992</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I374" t="inlineStr">
@@ -51744,10 +51744,10 @@
         </is>
       </c>
       <c r="Q374" t="n">
-        <v>586309</v>
+        <v>586441</v>
       </c>
       <c r="R374" t="n">
-        <v>6311119</v>
+        <v>6311152</v>
       </c>
       <c r="S374" t="n">
         <v>5</v>
@@ -51779,7 +51779,7 @@
       </c>
       <c r="Z374" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AA374" t="inlineStr">
@@ -51789,7 +51789,7 @@
       </c>
       <c r="AB374" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AC374" t="inlineStr">
@@ -51834,10 +51834,10 @@
     </row>
     <row r="375">
       <c r="A375" t="n">
-        <v>122254585</v>
+        <v>122254877</v>
       </c>
       <c r="B375" t="n">
-        <v>56294</v>
+        <v>56292</v>
       </c>
       <c r="C375" t="inlineStr">
         <is>
@@ -51850,21 +51850,21 @@
         </is>
       </c>
       <c r="E375" t="n">
-        <v>205995</v>
+        <v>100111</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I375" t="inlineStr">
@@ -51888,10 +51888,10 @@
         </is>
       </c>
       <c r="Q375" t="n">
-        <v>586455</v>
+        <v>586276</v>
       </c>
       <c r="R375" t="n">
-        <v>6311156</v>
+        <v>6311100</v>
       </c>
       <c r="S375" t="n">
         <v>5</v>
@@ -51923,7 +51923,7 @@
       </c>
       <c r="Z375" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AA375" t="inlineStr">
@@ -51933,7 +51933,7 @@
       </c>
       <c r="AB375" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>22:52</t>
         </is>
       </c>
       <c r="AC375" t="inlineStr">
@@ -51978,10 +51978,10 @@
     </row>
     <row r="376">
       <c r="A376" t="n">
-        <v>122254373</v>
+        <v>122254584</v>
       </c>
       <c r="B376" t="n">
-        <v>56289</v>
+        <v>56294</v>
       </c>
       <c r="C376" t="inlineStr">
         <is>
@@ -51994,21 +51994,21 @@
         </is>
       </c>
       <c r="E376" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H376" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I376" t="inlineStr">
@@ -52032,10 +52032,10 @@
         </is>
       </c>
       <c r="Q376" t="n">
-        <v>586307</v>
+        <v>586473</v>
       </c>
       <c r="R376" t="n">
-        <v>6311133</v>
+        <v>6311192</v>
       </c>
       <c r="S376" t="n">
         <v>5</v>
@@ -52067,7 +52067,7 @@
       </c>
       <c r="Z376" t="inlineStr">
         <is>
-          <t>22:49</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AA376" t="inlineStr">
@@ -52077,7 +52077,7 @@
       </c>
       <c r="AB376" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AC376" t="inlineStr">
@@ -52122,10 +52122,10 @@
     </row>
     <row r="377">
       <c r="A377" t="n">
-        <v>122254417</v>
+        <v>122254646</v>
       </c>
       <c r="B377" t="n">
-        <v>56289</v>
+        <v>56294</v>
       </c>
       <c r="C377" t="inlineStr">
         <is>
@@ -52138,21 +52138,21 @@
         </is>
       </c>
       <c r="E377" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H377" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I377" t="inlineStr">
@@ -52176,10 +52176,10 @@
         </is>
       </c>
       <c r="Q377" t="n">
-        <v>586426</v>
+        <v>586422</v>
       </c>
       <c r="R377" t="n">
-        <v>6311145</v>
+        <v>6311111</v>
       </c>
       <c r="S377" t="n">
         <v>5</v>
@@ -52211,7 +52211,7 @@
       </c>
       <c r="Z377" t="inlineStr">
         <is>
-          <t>22:33</t>
+          <t>22:36</t>
         </is>
       </c>
       <c r="AA377" t="inlineStr">
@@ -52221,7 +52221,7 @@
       </c>
       <c r="AB377" t="inlineStr">
         <is>
-          <t>22:34</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AC377" t="inlineStr">
@@ -52266,7 +52266,7 @@
     </row>
     <row r="378">
       <c r="A378" t="n">
-        <v>122254608</v>
+        <v>122254616</v>
       </c>
       <c r="B378" t="n">
         <v>56294</v>
@@ -52320,10 +52320,10 @@
         </is>
       </c>
       <c r="Q378" t="n">
-        <v>586393</v>
+        <v>586327</v>
       </c>
       <c r="R378" t="n">
-        <v>6311147</v>
+        <v>6311118</v>
       </c>
       <c r="S378" t="n">
         <v>5</v>
@@ -52355,7 +52355,7 @@
       </c>
       <c r="Z378" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>22:57</t>
         </is>
       </c>
       <c r="AA378" t="inlineStr">
@@ -52365,7 +52365,7 @@
       </c>
       <c r="AB378" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>22:58</t>
         </is>
       </c>
       <c r="AC378" t="inlineStr">
@@ -52410,7 +52410,7 @@
     </row>
     <row r="379">
       <c r="A379" t="n">
-        <v>122254658</v>
+        <v>122254643</v>
       </c>
       <c r="B379" t="n">
         <v>56294</v>
@@ -52464,10 +52464,10 @@
         </is>
       </c>
       <c r="Q379" t="n">
-        <v>586491</v>
+        <v>586424</v>
       </c>
       <c r="R379" t="n">
-        <v>6311181</v>
+        <v>6311135</v>
       </c>
       <c r="S379" t="n">
         <v>5</v>
@@ -52499,7 +52499,7 @@
       </c>
       <c r="Z379" t="inlineStr">
         <is>
-          <t>22:31</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AA379" t="inlineStr">
@@ -52509,7 +52509,7 @@
       </c>
       <c r="AB379" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>22:38</t>
         </is>
       </c>
       <c r="AC379" t="inlineStr">
@@ -52554,7 +52554,7 @@
     </row>
     <row r="380">
       <c r="A380" t="n">
-        <v>122254586</v>
+        <v>122254626</v>
       </c>
       <c r="B380" t="n">
         <v>56294</v>
@@ -52608,10 +52608,10 @@
         </is>
       </c>
       <c r="Q380" t="n">
-        <v>586446</v>
+        <v>586313</v>
       </c>
       <c r="R380" t="n">
-        <v>6311158</v>
+        <v>6311124</v>
       </c>
       <c r="S380" t="n">
         <v>5</v>
@@ -52643,7 +52643,7 @@
       </c>
       <c r="Z380" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AA380" t="inlineStr">
@@ -52653,7 +52653,7 @@
       </c>
       <c r="AB380" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AC380" t="inlineStr">
@@ -52698,10 +52698,10 @@
     </row>
     <row r="381">
       <c r="A381" t="n">
-        <v>122254862</v>
+        <v>122254587</v>
       </c>
       <c r="B381" t="n">
-        <v>56292</v>
+        <v>56294</v>
       </c>
       <c r="C381" t="inlineStr">
         <is>
@@ -52714,21 +52714,21 @@
         </is>
       </c>
       <c r="E381" t="n">
-        <v>100111</v>
+        <v>205995</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I381" t="inlineStr">
@@ -52752,10 +52752,10 @@
         </is>
       </c>
       <c r="Q381" t="n">
-        <v>586288</v>
+        <v>586443</v>
       </c>
       <c r="R381" t="n">
-        <v>6311100</v>
+        <v>6311163</v>
       </c>
       <c r="S381" t="n">
         <v>5</v>
@@ -52787,7 +52787,7 @@
       </c>
       <c r="Z381" t="inlineStr">
         <is>
-          <t>22:55</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AA381" t="inlineStr">
@@ -52797,7 +52797,7 @@
       </c>
       <c r="AB381" t="inlineStr">
         <is>
-          <t>22:56</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AC381" t="inlineStr">
@@ -52842,10 +52842,10 @@
     </row>
     <row r="382">
       <c r="A382" t="n">
-        <v>122254836</v>
+        <v>122254421</v>
       </c>
       <c r="B382" t="n">
-        <v>56292</v>
+        <v>56289</v>
       </c>
       <c r="C382" t="inlineStr">
         <is>
@@ -52858,21 +52858,21 @@
         </is>
       </c>
       <c r="E382" t="n">
-        <v>100111</v>
+        <v>100092</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H382" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I382" t="inlineStr">
@@ -52896,10 +52896,10 @@
         </is>
       </c>
       <c r="Q382" t="n">
-        <v>586474</v>
+        <v>586468</v>
       </c>
       <c r="R382" t="n">
-        <v>6311176</v>
+        <v>6311181</v>
       </c>
       <c r="S382" t="n">
         <v>5</v>
@@ -52931,7 +52931,7 @@
       </c>
       <c r="Z382" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AA382" t="inlineStr">
@@ -52941,7 +52941,7 @@
       </c>
       <c r="AB382" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="AC382" t="inlineStr">
@@ -52986,7 +52986,7 @@
     </row>
     <row r="383">
       <c r="A383" t="n">
-        <v>122254657</v>
+        <v>122254634</v>
       </c>
       <c r="B383" t="n">
         <v>56294</v>
@@ -53040,10 +53040,10 @@
         </is>
       </c>
       <c r="Q383" t="n">
-        <v>586488</v>
+        <v>586415</v>
       </c>
       <c r="R383" t="n">
-        <v>6311184</v>
+        <v>6311148</v>
       </c>
       <c r="S383" t="n">
         <v>5</v>
@@ -53075,7 +53075,7 @@
       </c>
       <c r="Z383" t="inlineStr">
         <is>
-          <t>22:31</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AA383" t="inlineStr">
@@ -53085,7 +53085,7 @@
       </c>
       <c r="AB383" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AC383" t="inlineStr">
@@ -53130,7 +53130,7 @@
     </row>
     <row r="384">
       <c r="A384" t="n">
-        <v>122254653</v>
+        <v>122254654</v>
       </c>
       <c r="B384" t="n">
         <v>56294</v>
@@ -53184,10 +53184,10 @@
         </is>
       </c>
       <c r="Q384" t="n">
-        <v>586430</v>
+        <v>586467</v>
       </c>
       <c r="R384" t="n">
-        <v>6311142</v>
+        <v>6311178</v>
       </c>
       <c r="S384" t="n">
         <v>5</v>
@@ -53219,17 +53219,17 @@
       </c>
       <c r="Z384" t="inlineStr">
         <is>
+          <t>22:32</t>
+        </is>
+      </c>
+      <c r="AA384" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AB384" t="inlineStr">
+        <is>
           <t>22:33</t>
-        </is>
-      </c>
-      <c r="AA384" t="inlineStr">
-        <is>
-          <t>2024-06-26</t>
-        </is>
-      </c>
-      <c r="AB384" t="inlineStr">
-        <is>
-          <t>22:34</t>
         </is>
       </c>
       <c r="AC384" t="inlineStr">
@@ -53274,10 +53274,10 @@
     </row>
     <row r="385">
       <c r="A385" t="n">
-        <v>122254610</v>
+        <v>122254496</v>
       </c>
       <c r="B385" t="n">
-        <v>56294</v>
+        <v>56275</v>
       </c>
       <c r="C385" t="inlineStr">
         <is>
@@ -53286,25 +53286,25 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E385" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H385" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I385" t="inlineStr">
@@ -53328,10 +53328,10 @@
         </is>
       </c>
       <c r="Q385" t="n">
-        <v>586389</v>
+        <v>586415</v>
       </c>
       <c r="R385" t="n">
-        <v>6311141</v>
+        <v>6311146</v>
       </c>
       <c r="S385" t="n">
         <v>5</v>
@@ -53363,7 +53363,7 @@
       </c>
       <c r="Z385" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AA385" t="inlineStr">
@@ -53373,7 +53373,7 @@
       </c>
       <c r="AB385" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>23:03</t>
         </is>
       </c>
       <c r="AC385" t="inlineStr">
@@ -53418,10 +53418,10 @@
     </row>
     <row r="386">
       <c r="A386" t="n">
-        <v>122254646</v>
+        <v>122254500</v>
       </c>
       <c r="B386" t="n">
-        <v>56294</v>
+        <v>56275</v>
       </c>
       <c r="C386" t="inlineStr">
         <is>
@@ -53430,25 +53430,25 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E386" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H386" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I386" t="inlineStr">
@@ -53472,10 +53472,10 @@
         </is>
       </c>
       <c r="Q386" t="n">
-        <v>586422</v>
+        <v>586388</v>
       </c>
       <c r="R386" t="n">
-        <v>6311111</v>
+        <v>6311142</v>
       </c>
       <c r="S386" t="n">
         <v>5</v>
@@ -53507,7 +53507,7 @@
       </c>
       <c r="Z386" t="inlineStr">
         <is>
-          <t>22:36</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA386" t="inlineStr">
@@ -53517,7 +53517,7 @@
       </c>
       <c r="AB386" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AC386" t="inlineStr">
@@ -53562,10 +53562,10 @@
     </row>
     <row r="387">
       <c r="A387" t="n">
-        <v>122254500</v>
+        <v>122254307</v>
       </c>
       <c r="B387" t="n">
-        <v>56275</v>
+        <v>56289</v>
       </c>
       <c r="C387" t="inlineStr">
         <is>
@@ -53574,25 +53574,25 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E387" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I387" t="inlineStr">
@@ -53616,10 +53616,10 @@
         </is>
       </c>
       <c r="Q387" t="n">
-        <v>586388</v>
+        <v>586477</v>
       </c>
       <c r="R387" t="n">
-        <v>6311142</v>
+        <v>6311186</v>
       </c>
       <c r="S387" t="n">
         <v>5</v>
@@ -53651,7 +53651,7 @@
       </c>
       <c r="Z387" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AA387" t="inlineStr">
@@ -53661,7 +53661,7 @@
       </c>
       <c r="AB387" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AC387" t="inlineStr">
@@ -53706,10 +53706,10 @@
     </row>
     <row r="388">
       <c r="A388" t="n">
-        <v>122254472</v>
+        <v>122254394</v>
       </c>
       <c r="B388" t="n">
-        <v>56275</v>
+        <v>56289</v>
       </c>
       <c r="C388" t="inlineStr">
         <is>
@@ -53718,25 +53718,25 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E388" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H388" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I388" t="inlineStr">
@@ -53760,10 +53760,10 @@
         </is>
       </c>
       <c r="Q388" t="n">
-        <v>586455</v>
+        <v>586419</v>
       </c>
       <c r="R388" t="n">
-        <v>6311159</v>
+        <v>6311142</v>
       </c>
       <c r="S388" t="n">
         <v>5</v>
@@ -53795,7 +53795,7 @@
       </c>
       <c r="Z388" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>22:43</t>
         </is>
       </c>
       <c r="AA388" t="inlineStr">
@@ -53805,7 +53805,7 @@
       </c>
       <c r="AB388" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AC388" t="inlineStr">
@@ -53850,10 +53850,10 @@
     </row>
     <row r="389">
       <c r="A389" t="n">
-        <v>122254511</v>
+        <v>122254350</v>
       </c>
       <c r="B389" t="n">
-        <v>56275</v>
+        <v>56289</v>
       </c>
       <c r="C389" t="inlineStr">
         <is>
@@ -53862,25 +53862,25 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E389" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I389" t="inlineStr">
@@ -53904,10 +53904,10 @@
         </is>
       </c>
       <c r="Q389" t="n">
-        <v>586374</v>
+        <v>586330</v>
       </c>
       <c r="R389" t="n">
-        <v>6311139</v>
+        <v>6311120</v>
       </c>
       <c r="S389" t="n">
         <v>5</v>
@@ -53939,7 +53939,7 @@
       </c>
       <c r="Z389" t="inlineStr">
         <is>
-          <t>22:46</t>
+          <t>22:57</t>
         </is>
       </c>
       <c r="AA389" t="inlineStr">
@@ -53949,7 +53949,7 @@
       </c>
       <c r="AB389" t="inlineStr">
         <is>
-          <t>22:47</t>
+          <t>22:58</t>
         </is>
       </c>
       <c r="AC389" t="inlineStr">

--- a/artfynd/A 36363-2024 artfynd.xlsx
+++ b/artfynd/A 36363-2024 artfynd.xlsx
@@ -42474,10 +42474,10 @@
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>122254854</v>
+        <v>122254372</v>
       </c>
       <c r="B310" t="n">
-        <v>56292</v>
+        <v>56289</v>
       </c>
       <c r="C310" t="inlineStr">
         <is>
@@ -42490,21 +42490,21 @@
         </is>
       </c>
       <c r="E310" t="n">
-        <v>100111</v>
+        <v>100092</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
@@ -42528,10 +42528,10 @@
         </is>
       </c>
       <c r="Q310" t="n">
-        <v>586329</v>
+        <v>586306</v>
       </c>
       <c r="R310" t="n">
-        <v>6311120</v>
+        <v>6311131</v>
       </c>
       <c r="S310" t="n">
         <v>5</v>
@@ -42563,7 +42563,7 @@
       </c>
       <c r="Z310" t="inlineStr">
         <is>
-          <t>22:57</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AA310" t="inlineStr">
@@ -42573,7 +42573,7 @@
       </c>
       <c r="AB310" t="inlineStr">
         <is>
-          <t>22:58</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AC310" t="inlineStr">
@@ -42618,7 +42618,7 @@
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>122254844</v>
+        <v>122254854</v>
       </c>
       <c r="B311" t="n">
         <v>56292</v>
@@ -42672,10 +42672,10 @@
         </is>
       </c>
       <c r="Q311" t="n">
-        <v>586387</v>
+        <v>586329</v>
       </c>
       <c r="R311" t="n">
-        <v>6311141</v>
+        <v>6311120</v>
       </c>
       <c r="S311" t="n">
         <v>5</v>
@@ -42707,7 +42707,7 @@
       </c>
       <c r="Z311" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:57</t>
         </is>
       </c>
       <c r="AA311" t="inlineStr">
@@ -42717,7 +42717,7 @@
       </c>
       <c r="AB311" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>22:58</t>
         </is>
       </c>
       <c r="AC311" t="inlineStr">
@@ -42762,10 +42762,10 @@
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>122254372</v>
+        <v>122254844</v>
       </c>
       <c r="B312" t="n">
-        <v>56289</v>
+        <v>56292</v>
       </c>
       <c r="C312" t="inlineStr">
         <is>
@@ -42778,21 +42778,21 @@
         </is>
       </c>
       <c r="E312" t="n">
-        <v>100092</v>
+        <v>100111</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
@@ -42816,10 +42816,10 @@
         </is>
       </c>
       <c r="Q312" t="n">
-        <v>586306</v>
+        <v>586387</v>
       </c>
       <c r="R312" t="n">
-        <v>6311131</v>
+        <v>6311141</v>
       </c>
       <c r="S312" t="n">
         <v>5</v>
@@ -42851,7 +42851,7 @@
       </c>
       <c r="Z312" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA312" t="inlineStr">
@@ -42861,7 +42861,7 @@
       </c>
       <c r="AB312" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AC312" t="inlineStr">
@@ -43770,7 +43770,7 @@
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>122254588</v>
+        <v>122254635</v>
       </c>
       <c r="B319" t="n">
         <v>56294</v>
@@ -43824,10 +43824,10 @@
         </is>
       </c>
       <c r="Q319" t="n">
-        <v>586415</v>
+        <v>586417</v>
       </c>
       <c r="R319" t="n">
-        <v>6311196</v>
+        <v>6311145</v>
       </c>
       <c r="S319" t="n">
         <v>5</v>
@@ -43859,7 +43859,7 @@
       </c>
       <c r="Z319" t="inlineStr">
         <is>
-          <t>23:22</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AA319" t="inlineStr">
@@ -43869,7 +43869,7 @@
       </c>
       <c r="AB319" t="inlineStr">
         <is>
-          <t>23:23</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AC319" t="inlineStr">
@@ -43914,7 +43914,7 @@
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>122254635</v>
+        <v>122254627</v>
       </c>
       <c r="B320" t="n">
         <v>56294</v>
@@ -43968,10 +43968,10 @@
         </is>
       </c>
       <c r="Q320" t="n">
-        <v>586417</v>
+        <v>586306</v>
       </c>
       <c r="R320" t="n">
-        <v>6311145</v>
+        <v>6311131</v>
       </c>
       <c r="S320" t="n">
         <v>5</v>
@@ -44003,7 +44003,7 @@
       </c>
       <c r="Z320" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AA320" t="inlineStr">
@@ -44013,7 +44013,7 @@
       </c>
       <c r="AB320" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AC320" t="inlineStr">
@@ -44058,7 +44058,7 @@
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>122254627</v>
+        <v>122254588</v>
       </c>
       <c r="B321" t="n">
         <v>56294</v>
@@ -44112,10 +44112,10 @@
         </is>
       </c>
       <c r="Q321" t="n">
-        <v>586306</v>
+        <v>586415</v>
       </c>
       <c r="R321" t="n">
-        <v>6311131</v>
+        <v>6311196</v>
       </c>
       <c r="S321" t="n">
         <v>5</v>
@@ -44147,7 +44147,7 @@
       </c>
       <c r="Z321" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>23:22</t>
         </is>
       </c>
       <c r="AA321" t="inlineStr">
@@ -44157,7 +44157,7 @@
       </c>
       <c r="AB321" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>23:23</t>
         </is>
       </c>
       <c r="AC321" t="inlineStr">
@@ -44202,10 +44202,10 @@
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>122254472</v>
+        <v>122254309</v>
       </c>
       <c r="B322" t="n">
-        <v>56275</v>
+        <v>56289</v>
       </c>
       <c r="C322" t="inlineStr">
         <is>
@@ -44214,25 +44214,25 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E322" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
@@ -44256,10 +44256,10 @@
         </is>
       </c>
       <c r="Q322" t="n">
-        <v>586455</v>
+        <v>586456</v>
       </c>
       <c r="R322" t="n">
-        <v>6311159</v>
+        <v>6311158</v>
       </c>
       <c r="S322" t="n">
         <v>5</v>
@@ -44346,10 +44346,10 @@
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>122254585</v>
+        <v>122254472</v>
       </c>
       <c r="B323" t="n">
-        <v>56294</v>
+        <v>56275</v>
       </c>
       <c r="C323" t="inlineStr">
         <is>
@@ -44358,25 +44358,25 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E323" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
@@ -44403,7 +44403,7 @@
         <v>586455</v>
       </c>
       <c r="R323" t="n">
-        <v>6311156</v>
+        <v>6311159</v>
       </c>
       <c r="S323" t="n">
         <v>5</v>
@@ -44490,7 +44490,7 @@
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>122254636</v>
+        <v>122254585</v>
       </c>
       <c r="B324" t="n">
         <v>56294</v>
@@ -44544,10 +44544,10 @@
         </is>
       </c>
       <c r="Q324" t="n">
-        <v>586418</v>
+        <v>586455</v>
       </c>
       <c r="R324" t="n">
-        <v>6311145</v>
+        <v>6311156</v>
       </c>
       <c r="S324" t="n">
         <v>5</v>
@@ -44579,7 +44579,7 @@
       </c>
       <c r="Z324" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AA324" t="inlineStr">
@@ -44589,7 +44589,7 @@
       </c>
       <c r="AB324" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AC324" t="inlineStr">
@@ -44634,10 +44634,10 @@
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>122254309</v>
+        <v>122254636</v>
       </c>
       <c r="B325" t="n">
-        <v>56289</v>
+        <v>56294</v>
       </c>
       <c r="C325" t="inlineStr">
         <is>
@@ -44650,21 +44650,21 @@
         </is>
       </c>
       <c r="E325" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
@@ -44688,10 +44688,10 @@
         </is>
       </c>
       <c r="Q325" t="n">
-        <v>586456</v>
+        <v>586418</v>
       </c>
       <c r="R325" t="n">
-        <v>6311158</v>
+        <v>6311145</v>
       </c>
       <c r="S325" t="n">
         <v>5</v>
@@ -44723,7 +44723,7 @@
       </c>
       <c r="Z325" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AA325" t="inlineStr">
@@ -44733,7 +44733,7 @@
       </c>
       <c r="AB325" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AC325" t="inlineStr">
@@ -46362,10 +46362,10 @@
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>122254341</v>
+        <v>122254513</v>
       </c>
       <c r="B337" t="n">
-        <v>56289</v>
+        <v>56275</v>
       </c>
       <c r="C337" t="inlineStr">
         <is>
@@ -46374,25 +46374,25 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E337" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
@@ -46416,7 +46416,7 @@
         </is>
       </c>
       <c r="Q337" t="n">
-        <v>586415</v>
+        <v>586396</v>
       </c>
       <c r="R337" t="n">
         <v>6311146</v>
@@ -46451,7 +46451,7 @@
       </c>
       <c r="Z337" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AA337" t="inlineStr">
@@ -46461,7 +46461,7 @@
       </c>
       <c r="AB337" t="inlineStr">
         <is>
-          <t>23:03</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AC337" t="inlineStr">
@@ -46506,10 +46506,10 @@
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>122254313</v>
+        <v>122254957</v>
       </c>
       <c r="B338" t="n">
-        <v>56289</v>
+        <v>56282</v>
       </c>
       <c r="C338" t="inlineStr">
         <is>
@@ -46522,21 +46522,21 @@
         </is>
       </c>
       <c r="E338" t="n">
-        <v>100092</v>
+        <v>205992</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
@@ -46560,10 +46560,10 @@
         </is>
       </c>
       <c r="Q338" t="n">
-        <v>586449</v>
+        <v>586444</v>
       </c>
       <c r="R338" t="n">
-        <v>6311155</v>
+        <v>6311160</v>
       </c>
       <c r="S338" t="n">
         <v>5</v>
@@ -46595,7 +46595,7 @@
       </c>
       <c r="Z338" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="AA338" t="inlineStr">
@@ -46605,7 +46605,7 @@
       </c>
       <c r="AB338" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AC338" t="inlineStr">
@@ -46650,10 +46650,10 @@
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>122254373</v>
+        <v>122254499</v>
       </c>
       <c r="B339" t="n">
-        <v>56289</v>
+        <v>56275</v>
       </c>
       <c r="C339" t="inlineStr">
         <is>
@@ -46662,25 +46662,25 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E339" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I339" t="inlineStr">
@@ -46704,10 +46704,10 @@
         </is>
       </c>
       <c r="Q339" t="n">
-        <v>586307</v>
+        <v>586392</v>
       </c>
       <c r="R339" t="n">
-        <v>6311133</v>
+        <v>6311147</v>
       </c>
       <c r="S339" t="n">
         <v>5</v>
@@ -46739,7 +46739,7 @@
       </c>
       <c r="Z339" t="inlineStr">
         <is>
-          <t>22:49</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AA339" t="inlineStr">
@@ -46749,7 +46749,7 @@
       </c>
       <c r="AB339" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AC339" t="inlineStr">
@@ -46794,10 +46794,10 @@
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>122254845</v>
+        <v>122254341</v>
       </c>
       <c r="B340" t="n">
-        <v>56292</v>
+        <v>56289</v>
       </c>
       <c r="C340" t="inlineStr">
         <is>
@@ -46810,21 +46810,21 @@
         </is>
       </c>
       <c r="E340" t="n">
-        <v>100111</v>
+        <v>100092</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
@@ -46848,10 +46848,10 @@
         </is>
       </c>
       <c r="Q340" t="n">
-        <v>586370</v>
+        <v>586415</v>
       </c>
       <c r="R340" t="n">
-        <v>6311139</v>
+        <v>6311146</v>
       </c>
       <c r="S340" t="n">
         <v>5</v>
@@ -46883,7 +46883,7 @@
       </c>
       <c r="Z340" t="inlineStr">
         <is>
-          <t>22:59</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AA340" t="inlineStr">
@@ -46893,7 +46893,7 @@
       </c>
       <c r="AB340" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>23:03</t>
         </is>
       </c>
       <c r="AC340" t="inlineStr">
@@ -46938,10 +46938,10 @@
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>122254856</v>
+        <v>122254313</v>
       </c>
       <c r="B341" t="n">
-        <v>56292</v>
+        <v>56289</v>
       </c>
       <c r="C341" t="inlineStr">
         <is>
@@ -46954,21 +46954,21 @@
         </is>
       </c>
       <c r="E341" t="n">
-        <v>100111</v>
+        <v>100092</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I341" t="inlineStr">
@@ -46992,10 +46992,10 @@
         </is>
       </c>
       <c r="Q341" t="n">
-        <v>586327</v>
+        <v>586449</v>
       </c>
       <c r="R341" t="n">
-        <v>6311118</v>
+        <v>6311155</v>
       </c>
       <c r="S341" t="n">
         <v>5</v>
@@ -47027,7 +47027,7 @@
       </c>
       <c r="Z341" t="inlineStr">
         <is>
-          <t>22:57</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA341" t="inlineStr">
@@ -47037,7 +47037,7 @@
       </c>
       <c r="AB341" t="inlineStr">
         <is>
-          <t>22:58</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC341" t="inlineStr">
@@ -47082,10 +47082,10 @@
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>122254513</v>
+        <v>122254373</v>
       </c>
       <c r="B342" t="n">
-        <v>56275</v>
+        <v>56289</v>
       </c>
       <c r="C342" t="inlineStr">
         <is>
@@ -47094,25 +47094,25 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E342" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
@@ -47136,10 +47136,10 @@
         </is>
       </c>
       <c r="Q342" t="n">
-        <v>586396</v>
+        <v>586307</v>
       </c>
       <c r="R342" t="n">
-        <v>6311146</v>
+        <v>6311133</v>
       </c>
       <c r="S342" t="n">
         <v>5</v>
@@ -47171,7 +47171,7 @@
       </c>
       <c r="Z342" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>22:49</t>
         </is>
       </c>
       <c r="AA342" t="inlineStr">
@@ -47181,7 +47181,7 @@
       </c>
       <c r="AB342" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AC342" t="inlineStr">
@@ -47226,10 +47226,10 @@
     </row>
     <row r="343">
       <c r="A343" t="n">
-        <v>122254957</v>
+        <v>122254845</v>
       </c>
       <c r="B343" t="n">
-        <v>56282</v>
+        <v>56292</v>
       </c>
       <c r="C343" t="inlineStr">
         <is>
@@ -47242,21 +47242,21 @@
         </is>
       </c>
       <c r="E343" t="n">
-        <v>205992</v>
+        <v>100111</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
@@ -47280,10 +47280,10 @@
         </is>
       </c>
       <c r="Q343" t="n">
-        <v>586444</v>
+        <v>586370</v>
       </c>
       <c r="R343" t="n">
-        <v>6311160</v>
+        <v>6311139</v>
       </c>
       <c r="S343" t="n">
         <v>5</v>
@@ -47315,7 +47315,7 @@
       </c>
       <c r="Z343" t="inlineStr">
         <is>
-          <t>23:24</t>
+          <t>22:59</t>
         </is>
       </c>
       <c r="AA343" t="inlineStr">
@@ -47325,7 +47325,7 @@
       </c>
       <c r="AB343" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AC343" t="inlineStr">
@@ -47370,10 +47370,10 @@
     </row>
     <row r="344">
       <c r="A344" t="n">
-        <v>122254499</v>
+        <v>122254856</v>
       </c>
       <c r="B344" t="n">
-        <v>56275</v>
+        <v>56292</v>
       </c>
       <c r="C344" t="inlineStr">
         <is>
@@ -47382,25 +47382,25 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E344" t="n">
-        <v>205998</v>
+        <v>100111</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
@@ -47424,10 +47424,10 @@
         </is>
       </c>
       <c r="Q344" t="n">
-        <v>586392</v>
+        <v>586327</v>
       </c>
       <c r="R344" t="n">
-        <v>6311147</v>
+        <v>6311118</v>
       </c>
       <c r="S344" t="n">
         <v>5</v>
@@ -47459,7 +47459,7 @@
       </c>
       <c r="Z344" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>22:57</t>
         </is>
       </c>
       <c r="AA344" t="inlineStr">
@@ -47469,7 +47469,7 @@
       </c>
       <c r="AB344" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>22:58</t>
         </is>
       </c>
       <c r="AC344" t="inlineStr">
@@ -47514,10 +47514,10 @@
     </row>
     <row r="345">
       <c r="A345" t="n">
-        <v>122254648</v>
+        <v>122254416</v>
       </c>
       <c r="B345" t="n">
-        <v>56294</v>
+        <v>56289</v>
       </c>
       <c r="C345" t="inlineStr">
         <is>
@@ -47530,21 +47530,21 @@
         </is>
       </c>
       <c r="E345" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
@@ -47568,10 +47568,10 @@
         </is>
       </c>
       <c r="Q345" t="n">
-        <v>586418</v>
+        <v>586410</v>
       </c>
       <c r="R345" t="n">
-        <v>6311107</v>
+        <v>6311140</v>
       </c>
       <c r="S345" t="n">
         <v>5</v>
@@ -47603,7 +47603,7 @@
       </c>
       <c r="Z345" t="inlineStr">
         <is>
-          <t>22:36</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="AA345" t="inlineStr">
@@ -47613,7 +47613,7 @@
       </c>
       <c r="AB345" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>22:34</t>
         </is>
       </c>
       <c r="AC345" t="inlineStr">
@@ -47658,10 +47658,10 @@
     </row>
     <row r="346">
       <c r="A346" t="n">
-        <v>122254963</v>
+        <v>122254396</v>
       </c>
       <c r="B346" t="n">
-        <v>56282</v>
+        <v>56289</v>
       </c>
       <c r="C346" t="inlineStr">
         <is>
@@ -47674,21 +47674,21 @@
         </is>
       </c>
       <c r="E346" t="n">
-        <v>205992</v>
+        <v>100092</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
@@ -47712,10 +47712,10 @@
         </is>
       </c>
       <c r="Q346" t="n">
-        <v>586374</v>
+        <v>586408</v>
       </c>
       <c r="R346" t="n">
-        <v>6311140</v>
+        <v>6311124</v>
       </c>
       <c r="S346" t="n">
         <v>5</v>
@@ -47747,7 +47747,7 @@
       </c>
       <c r="Z346" t="inlineStr">
         <is>
-          <t>22:46</t>
+          <t>22:43</t>
         </is>
       </c>
       <c r="AA346" t="inlineStr">
@@ -47757,7 +47757,7 @@
       </c>
       <c r="AB346" t="inlineStr">
         <is>
-          <t>22:47</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AC346" t="inlineStr">
@@ -47802,10 +47802,10 @@
     </row>
     <row r="347">
       <c r="A347" t="n">
-        <v>122254653</v>
+        <v>122254365</v>
       </c>
       <c r="B347" t="n">
-        <v>56294</v>
+        <v>56289</v>
       </c>
       <c r="C347" t="inlineStr">
         <is>
@@ -47818,21 +47818,21 @@
         </is>
       </c>
       <c r="E347" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I347" t="inlineStr">
@@ -47856,10 +47856,10 @@
         </is>
       </c>
       <c r="Q347" t="n">
-        <v>586430</v>
+        <v>586276</v>
       </c>
       <c r="R347" t="n">
-        <v>6311142</v>
+        <v>6311100</v>
       </c>
       <c r="S347" t="n">
         <v>5</v>
@@ -47891,7 +47891,7 @@
       </c>
       <c r="Z347" t="inlineStr">
         <is>
-          <t>22:33</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AA347" t="inlineStr">
@@ -47901,7 +47901,7 @@
       </c>
       <c r="AB347" t="inlineStr">
         <is>
-          <t>22:34</t>
+          <t>22:52</t>
         </is>
       </c>
       <c r="AC347" t="inlineStr">
@@ -47946,10 +47946,10 @@
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>122254609</v>
+        <v>122254315</v>
       </c>
       <c r="B348" t="n">
-        <v>56294</v>
+        <v>56289</v>
       </c>
       <c r="C348" t="inlineStr">
         <is>
@@ -47962,21 +47962,21 @@
         </is>
       </c>
       <c r="E348" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I348" t="inlineStr">
@@ -48000,10 +48000,10 @@
         </is>
       </c>
       <c r="Q348" t="n">
-        <v>586392</v>
+        <v>586441</v>
       </c>
       <c r="R348" t="n">
-        <v>6311147</v>
+        <v>6311155</v>
       </c>
       <c r="S348" t="n">
         <v>5</v>
@@ -48035,7 +48035,7 @@
       </c>
       <c r="Z348" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AA348" t="inlineStr">
@@ -48045,7 +48045,7 @@
       </c>
       <c r="AB348" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AC348" t="inlineStr">
@@ -48090,10 +48090,10 @@
     </row>
     <row r="349">
       <c r="A349" t="n">
-        <v>122254659</v>
+        <v>122254312</v>
       </c>
       <c r="B349" t="n">
-        <v>56294</v>
+        <v>56289</v>
       </c>
       <c r="C349" t="inlineStr">
         <is>
@@ -48106,21 +48106,21 @@
         </is>
       </c>
       <c r="E349" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I349" t="inlineStr">
@@ -48144,10 +48144,10 @@
         </is>
       </c>
       <c r="Q349" t="n">
-        <v>586489</v>
+        <v>586452</v>
       </c>
       <c r="R349" t="n">
-        <v>6311181</v>
+        <v>6311152</v>
       </c>
       <c r="S349" t="n">
         <v>5</v>
@@ -48179,7 +48179,7 @@
       </c>
       <c r="Z349" t="inlineStr">
         <is>
-          <t>22:31</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA349" t="inlineStr">
@@ -48189,7 +48189,7 @@
       </c>
       <c r="AB349" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC349" t="inlineStr">
@@ -48234,10 +48234,10 @@
     </row>
     <row r="350">
       <c r="A350" t="n">
-        <v>122254416</v>
+        <v>122254648</v>
       </c>
       <c r="B350" t="n">
-        <v>56289</v>
+        <v>56294</v>
       </c>
       <c r="C350" t="inlineStr">
         <is>
@@ -48250,21 +48250,21 @@
         </is>
       </c>
       <c r="E350" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I350" t="inlineStr">
@@ -48288,10 +48288,10 @@
         </is>
       </c>
       <c r="Q350" t="n">
-        <v>586410</v>
+        <v>586418</v>
       </c>
       <c r="R350" t="n">
-        <v>6311140</v>
+        <v>6311107</v>
       </c>
       <c r="S350" t="n">
         <v>5</v>
@@ -48323,7 +48323,7 @@
       </c>
       <c r="Z350" t="inlineStr">
         <is>
-          <t>22:33</t>
+          <t>22:36</t>
         </is>
       </c>
       <c r="AA350" t="inlineStr">
@@ -48333,7 +48333,7 @@
       </c>
       <c r="AB350" t="inlineStr">
         <is>
-          <t>22:34</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AC350" t="inlineStr">
@@ -48378,10 +48378,10 @@
     </row>
     <row r="351">
       <c r="A351" t="n">
-        <v>122254396</v>
+        <v>122254963</v>
       </c>
       <c r="B351" t="n">
-        <v>56289</v>
+        <v>56282</v>
       </c>
       <c r="C351" t="inlineStr">
         <is>
@@ -48394,21 +48394,21 @@
         </is>
       </c>
       <c r="E351" t="n">
-        <v>100092</v>
+        <v>205992</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I351" t="inlineStr">
@@ -48432,10 +48432,10 @@
         </is>
       </c>
       <c r="Q351" t="n">
-        <v>586408</v>
+        <v>586374</v>
       </c>
       <c r="R351" t="n">
-        <v>6311124</v>
+        <v>6311140</v>
       </c>
       <c r="S351" t="n">
         <v>5</v>
@@ -48467,7 +48467,7 @@
       </c>
       <c r="Z351" t="inlineStr">
         <is>
-          <t>22:43</t>
+          <t>22:46</t>
         </is>
       </c>
       <c r="AA351" t="inlineStr">
@@ -48477,7 +48477,7 @@
       </c>
       <c r="AB351" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>22:47</t>
         </is>
       </c>
       <c r="AC351" t="inlineStr">
@@ -48522,10 +48522,10 @@
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>122254365</v>
+        <v>122254653</v>
       </c>
       <c r="B352" t="n">
-        <v>56289</v>
+        <v>56294</v>
       </c>
       <c r="C352" t="inlineStr">
         <is>
@@ -48538,21 +48538,21 @@
         </is>
       </c>
       <c r="E352" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I352" t="inlineStr">
@@ -48576,10 +48576,10 @@
         </is>
       </c>
       <c r="Q352" t="n">
-        <v>586276</v>
+        <v>586430</v>
       </c>
       <c r="R352" t="n">
-        <v>6311100</v>
+        <v>6311142</v>
       </c>
       <c r="S352" t="n">
         <v>5</v>
@@ -48611,7 +48611,7 @@
       </c>
       <c r="Z352" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="AA352" t="inlineStr">
@@ -48621,7 +48621,7 @@
       </c>
       <c r="AB352" t="inlineStr">
         <is>
-          <t>22:52</t>
+          <t>22:34</t>
         </is>
       </c>
       <c r="AC352" t="inlineStr">
@@ -48666,10 +48666,10 @@
     </row>
     <row r="353">
       <c r="A353" t="n">
-        <v>122254315</v>
+        <v>122254609</v>
       </c>
       <c r="B353" t="n">
-        <v>56289</v>
+        <v>56294</v>
       </c>
       <c r="C353" t="inlineStr">
         <is>
@@ -48682,21 +48682,21 @@
         </is>
       </c>
       <c r="E353" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I353" t="inlineStr">
@@ -48720,10 +48720,10 @@
         </is>
       </c>
       <c r="Q353" t="n">
-        <v>586441</v>
+        <v>586392</v>
       </c>
       <c r="R353" t="n">
-        <v>6311155</v>
+        <v>6311147</v>
       </c>
       <c r="S353" t="n">
         <v>5</v>
@@ -48755,7 +48755,7 @@
       </c>
       <c r="Z353" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AA353" t="inlineStr">
@@ -48765,7 +48765,7 @@
       </c>
       <c r="AB353" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AC353" t="inlineStr">
@@ -48810,10 +48810,10 @@
     </row>
     <row r="354">
       <c r="A354" t="n">
-        <v>122254312</v>
+        <v>122254659</v>
       </c>
       <c r="B354" t="n">
-        <v>56289</v>
+        <v>56294</v>
       </c>
       <c r="C354" t="inlineStr">
         <is>
@@ -48826,21 +48826,21 @@
         </is>
       </c>
       <c r="E354" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I354" t="inlineStr">
@@ -48864,10 +48864,10 @@
         </is>
       </c>
       <c r="Q354" t="n">
-        <v>586452</v>
+        <v>586489</v>
       </c>
       <c r="R354" t="n">
-        <v>6311152</v>
+        <v>6311181</v>
       </c>
       <c r="S354" t="n">
         <v>5</v>
@@ -48899,7 +48899,7 @@
       </c>
       <c r="Z354" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>22:31</t>
         </is>
       </c>
       <c r="AA354" t="inlineStr">
@@ -48909,7 +48909,7 @@
       </c>
       <c r="AB354" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AC354" t="inlineStr">
@@ -49242,10 +49242,10 @@
     </row>
     <row r="357">
       <c r="A357" t="n">
-        <v>122254610</v>
+        <v>122254317</v>
       </c>
       <c r="B357" t="n">
-        <v>56294</v>
+        <v>56289</v>
       </c>
       <c r="C357" t="inlineStr">
         <is>
@@ -49258,21 +49258,21 @@
         </is>
       </c>
       <c r="E357" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I357" t="inlineStr">
@@ -49296,10 +49296,10 @@
         </is>
       </c>
       <c r="Q357" t="n">
-        <v>586389</v>
+        <v>586438</v>
       </c>
       <c r="R357" t="n">
-        <v>6311141</v>
+        <v>6311222</v>
       </c>
       <c r="S357" t="n">
         <v>5</v>
@@ -49331,7 +49331,7 @@
       </c>
       <c r="Z357" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>23:22</t>
         </is>
       </c>
       <c r="AA357" t="inlineStr">
@@ -49341,7 +49341,7 @@
       </c>
       <c r="AB357" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>23:23</t>
         </is>
       </c>
       <c r="AC357" t="inlineStr">
@@ -49386,10 +49386,10 @@
     </row>
     <row r="358">
       <c r="A358" t="n">
-        <v>122254633</v>
+        <v>122254412</v>
       </c>
       <c r="B358" t="n">
-        <v>56294</v>
+        <v>56289</v>
       </c>
       <c r="C358" t="inlineStr">
         <is>
@@ -49402,21 +49402,21 @@
         </is>
       </c>
       <c r="E358" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H358" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I358" t="inlineStr">
@@ -49440,10 +49440,10 @@
         </is>
       </c>
       <c r="Q358" t="n">
-        <v>586396</v>
+        <v>586424</v>
       </c>
       <c r="R358" t="n">
-        <v>6311146</v>
+        <v>6311135</v>
       </c>
       <c r="S358" t="n">
         <v>5</v>
@@ -49475,7 +49475,7 @@
       </c>
       <c r="Z358" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AA358" t="inlineStr">
@@ -49485,7 +49485,7 @@
       </c>
       <c r="AB358" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>22:38</t>
         </is>
       </c>
       <c r="AC358" t="inlineStr">
@@ -49530,10 +49530,10 @@
     </row>
     <row r="359">
       <c r="A359" t="n">
-        <v>122254511</v>
+        <v>122254415</v>
       </c>
       <c r="B359" t="n">
-        <v>56275</v>
+        <v>56289</v>
       </c>
       <c r="C359" t="inlineStr">
         <is>
@@ -49542,25 +49542,25 @@
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E359" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I359" t="inlineStr">
@@ -49584,10 +49584,10 @@
         </is>
       </c>
       <c r="Q359" t="n">
-        <v>586374</v>
+        <v>586425</v>
       </c>
       <c r="R359" t="n">
-        <v>6311139</v>
+        <v>6311135</v>
       </c>
       <c r="S359" t="n">
         <v>5</v>
@@ -49619,7 +49619,7 @@
       </c>
       <c r="Z359" t="inlineStr">
         <is>
-          <t>22:46</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AA359" t="inlineStr">
@@ -49629,7 +49629,7 @@
       </c>
       <c r="AB359" t="inlineStr">
         <is>
-          <t>22:47</t>
+          <t>22:38</t>
         </is>
       </c>
       <c r="AC359" t="inlineStr">
@@ -49674,7 +49674,7 @@
     </row>
     <row r="360">
       <c r="A360" t="n">
-        <v>122254317</v>
+        <v>122254352</v>
       </c>
       <c r="B360" t="n">
         <v>56289</v>
@@ -49728,10 +49728,10 @@
         </is>
       </c>
       <c r="Q360" t="n">
-        <v>586438</v>
+        <v>586288</v>
       </c>
       <c r="R360" t="n">
-        <v>6311222</v>
+        <v>6311100</v>
       </c>
       <c r="S360" t="n">
         <v>5</v>
@@ -49763,7 +49763,7 @@
       </c>
       <c r="Z360" t="inlineStr">
         <is>
-          <t>23:22</t>
+          <t>22:55</t>
         </is>
       </c>
       <c r="AA360" t="inlineStr">
@@ -49773,7 +49773,7 @@
       </c>
       <c r="AB360" t="inlineStr">
         <is>
-          <t>23:23</t>
+          <t>22:56</t>
         </is>
       </c>
       <c r="AC360" t="inlineStr">
@@ -49818,7 +49818,7 @@
     </row>
     <row r="361">
       <c r="A361" t="n">
-        <v>122254412</v>
+        <v>122254308</v>
       </c>
       <c r="B361" t="n">
         <v>56289</v>
@@ -49872,10 +49872,10 @@
         </is>
       </c>
       <c r="Q361" t="n">
-        <v>586424</v>
+        <v>586455</v>
       </c>
       <c r="R361" t="n">
-        <v>6311135</v>
+        <v>6311159</v>
       </c>
       <c r="S361" t="n">
         <v>5</v>
@@ -49907,7 +49907,7 @@
       </c>
       <c r="Z361" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AA361" t="inlineStr">
@@ -49917,7 +49917,7 @@
       </c>
       <c r="AB361" t="inlineStr">
         <is>
-          <t>22:38</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AC361" t="inlineStr">
@@ -49962,7 +49962,7 @@
     </row>
     <row r="362">
       <c r="A362" t="n">
-        <v>122254415</v>
+        <v>122254417</v>
       </c>
       <c r="B362" t="n">
         <v>56289</v>
@@ -50016,10 +50016,10 @@
         </is>
       </c>
       <c r="Q362" t="n">
-        <v>586425</v>
+        <v>586426</v>
       </c>
       <c r="R362" t="n">
-        <v>6311135</v>
+        <v>6311145</v>
       </c>
       <c r="S362" t="n">
         <v>5</v>
@@ -50051,7 +50051,7 @@
       </c>
       <c r="Z362" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="AA362" t="inlineStr">
@@ -50061,7 +50061,7 @@
       </c>
       <c r="AB362" t="inlineStr">
         <is>
-          <t>22:38</t>
+          <t>22:34</t>
         </is>
       </c>
       <c r="AC362" t="inlineStr">
@@ -50106,10 +50106,10 @@
     </row>
     <row r="363">
       <c r="A363" t="n">
-        <v>122254352</v>
+        <v>122254610</v>
       </c>
       <c r="B363" t="n">
-        <v>56289</v>
+        <v>56294</v>
       </c>
       <c r="C363" t="inlineStr">
         <is>
@@ -50122,21 +50122,21 @@
         </is>
       </c>
       <c r="E363" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I363" t="inlineStr">
@@ -50160,10 +50160,10 @@
         </is>
       </c>
       <c r="Q363" t="n">
-        <v>586288</v>
+        <v>586389</v>
       </c>
       <c r="R363" t="n">
-        <v>6311100</v>
+        <v>6311141</v>
       </c>
       <c r="S363" t="n">
         <v>5</v>
@@ -50195,7 +50195,7 @@
       </c>
       <c r="Z363" t="inlineStr">
         <is>
-          <t>22:55</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA363" t="inlineStr">
@@ -50205,7 +50205,7 @@
       </c>
       <c r="AB363" t="inlineStr">
         <is>
-          <t>22:56</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AC363" t="inlineStr">
@@ -50250,10 +50250,10 @@
     </row>
     <row r="364">
       <c r="A364" t="n">
-        <v>122254308</v>
+        <v>122254633</v>
       </c>
       <c r="B364" t="n">
-        <v>56289</v>
+        <v>56294</v>
       </c>
       <c r="C364" t="inlineStr">
         <is>
@@ -50266,21 +50266,21 @@
         </is>
       </c>
       <c r="E364" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I364" t="inlineStr">
@@ -50304,10 +50304,10 @@
         </is>
       </c>
       <c r="Q364" t="n">
-        <v>586455</v>
+        <v>586396</v>
       </c>
       <c r="R364" t="n">
-        <v>6311159</v>
+        <v>6311146</v>
       </c>
       <c r="S364" t="n">
         <v>5</v>
@@ -50339,7 +50339,7 @@
       </c>
       <c r="Z364" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AA364" t="inlineStr">
@@ -50349,7 +50349,7 @@
       </c>
       <c r="AB364" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AC364" t="inlineStr">
@@ -50394,10 +50394,10 @@
     </row>
     <row r="365">
       <c r="A365" t="n">
-        <v>122254417</v>
+        <v>122254511</v>
       </c>
       <c r="B365" t="n">
-        <v>56289</v>
+        <v>56275</v>
       </c>
       <c r="C365" t="inlineStr">
         <is>
@@ -50406,25 +50406,25 @@
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E365" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I365" t="inlineStr">
@@ -50448,10 +50448,10 @@
         </is>
       </c>
       <c r="Q365" t="n">
-        <v>586426</v>
+        <v>586374</v>
       </c>
       <c r="R365" t="n">
-        <v>6311145</v>
+        <v>6311139</v>
       </c>
       <c r="S365" t="n">
         <v>5</v>
@@ -50483,7 +50483,7 @@
       </c>
       <c r="Z365" t="inlineStr">
         <is>
-          <t>22:33</t>
+          <t>22:46</t>
         </is>
       </c>
       <c r="AA365" t="inlineStr">
@@ -50493,7 +50493,7 @@
       </c>
       <c r="AB365" t="inlineStr">
         <is>
-          <t>22:34</t>
+          <t>22:47</t>
         </is>
       </c>
       <c r="AC365" t="inlineStr">
@@ -52986,10 +52986,10 @@
     </row>
     <row r="383">
       <c r="A383" t="n">
-        <v>122254634</v>
+        <v>122254307</v>
       </c>
       <c r="B383" t="n">
-        <v>56294</v>
+        <v>56289</v>
       </c>
       <c r="C383" t="inlineStr">
         <is>
@@ -53002,21 +53002,21 @@
         </is>
       </c>
       <c r="E383" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I383" t="inlineStr">
@@ -53040,10 +53040,10 @@
         </is>
       </c>
       <c r="Q383" t="n">
-        <v>586415</v>
+        <v>586477</v>
       </c>
       <c r="R383" t="n">
-        <v>6311148</v>
+        <v>6311186</v>
       </c>
       <c r="S383" t="n">
         <v>5</v>
@@ -53075,7 +53075,7 @@
       </c>
       <c r="Z383" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AA383" t="inlineStr">
@@ -53085,7 +53085,7 @@
       </c>
       <c r="AB383" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AC383" t="inlineStr">
@@ -53130,10 +53130,10 @@
     </row>
     <row r="384">
       <c r="A384" t="n">
-        <v>122254654</v>
+        <v>122254394</v>
       </c>
       <c r="B384" t="n">
-        <v>56294</v>
+        <v>56289</v>
       </c>
       <c r="C384" t="inlineStr">
         <is>
@@ -53146,21 +53146,21 @@
         </is>
       </c>
       <c r="E384" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I384" t="inlineStr">
@@ -53184,10 +53184,10 @@
         </is>
       </c>
       <c r="Q384" t="n">
-        <v>586467</v>
+        <v>586419</v>
       </c>
       <c r="R384" t="n">
-        <v>6311178</v>
+        <v>6311142</v>
       </c>
       <c r="S384" t="n">
         <v>5</v>
@@ -53219,7 +53219,7 @@
       </c>
       <c r="Z384" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>22:43</t>
         </is>
       </c>
       <c r="AA384" t="inlineStr">
@@ -53229,7 +53229,7 @@
       </c>
       <c r="AB384" t="inlineStr">
         <is>
-          <t>22:33</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AC384" t="inlineStr">
@@ -53274,10 +53274,10 @@
     </row>
     <row r="385">
       <c r="A385" t="n">
-        <v>122254496</v>
+        <v>122254350</v>
       </c>
       <c r="B385" t="n">
-        <v>56275</v>
+        <v>56289</v>
       </c>
       <c r="C385" t="inlineStr">
         <is>
@@ -53286,25 +53286,25 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E385" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H385" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I385" t="inlineStr">
@@ -53328,10 +53328,10 @@
         </is>
       </c>
       <c r="Q385" t="n">
-        <v>586415</v>
+        <v>586330</v>
       </c>
       <c r="R385" t="n">
-        <v>6311146</v>
+        <v>6311120</v>
       </c>
       <c r="S385" t="n">
         <v>5</v>
@@ -53363,7 +53363,7 @@
       </c>
       <c r="Z385" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>22:57</t>
         </is>
       </c>
       <c r="AA385" t="inlineStr">
@@ -53373,7 +53373,7 @@
       </c>
       <c r="AB385" t="inlineStr">
         <is>
-          <t>23:03</t>
+          <t>22:58</t>
         </is>
       </c>
       <c r="AC385" t="inlineStr">
@@ -53418,10 +53418,10 @@
     </row>
     <row r="386">
       <c r="A386" t="n">
-        <v>122254500</v>
+        <v>122254634</v>
       </c>
       <c r="B386" t="n">
-        <v>56275</v>
+        <v>56294</v>
       </c>
       <c r="C386" t="inlineStr">
         <is>
@@ -53430,25 +53430,25 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E386" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H386" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I386" t="inlineStr">
@@ -53472,10 +53472,10 @@
         </is>
       </c>
       <c r="Q386" t="n">
-        <v>586388</v>
+        <v>586415</v>
       </c>
       <c r="R386" t="n">
-        <v>6311142</v>
+        <v>6311148</v>
       </c>
       <c r="S386" t="n">
         <v>5</v>
@@ -53507,7 +53507,7 @@
       </c>
       <c r="Z386" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AA386" t="inlineStr">
@@ -53517,7 +53517,7 @@
       </c>
       <c r="AB386" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AC386" t="inlineStr">
@@ -53562,10 +53562,10 @@
     </row>
     <row r="387">
       <c r="A387" t="n">
-        <v>122254307</v>
+        <v>122254654</v>
       </c>
       <c r="B387" t="n">
-        <v>56289</v>
+        <v>56294</v>
       </c>
       <c r="C387" t="inlineStr">
         <is>
@@ -53578,21 +53578,21 @@
         </is>
       </c>
       <c r="E387" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I387" t="inlineStr">
@@ -53616,10 +53616,10 @@
         </is>
       </c>
       <c r="Q387" t="n">
-        <v>586477</v>
+        <v>586467</v>
       </c>
       <c r="R387" t="n">
-        <v>6311186</v>
+        <v>6311178</v>
       </c>
       <c r="S387" t="n">
         <v>5</v>
@@ -53651,7 +53651,7 @@
       </c>
       <c r="Z387" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AA387" t="inlineStr">
@@ -53661,7 +53661,7 @@
       </c>
       <c r="AB387" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="AC387" t="inlineStr">
@@ -53706,10 +53706,10 @@
     </row>
     <row r="388">
       <c r="A388" t="n">
-        <v>122254394</v>
+        <v>122254496</v>
       </c>
       <c r="B388" t="n">
-        <v>56289</v>
+        <v>56275</v>
       </c>
       <c r="C388" t="inlineStr">
         <is>
@@ -53718,25 +53718,25 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E388" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H388" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I388" t="inlineStr">
@@ -53760,10 +53760,10 @@
         </is>
       </c>
       <c r="Q388" t="n">
-        <v>586419</v>
+        <v>586415</v>
       </c>
       <c r="R388" t="n">
-        <v>6311142</v>
+        <v>6311146</v>
       </c>
       <c r="S388" t="n">
         <v>5</v>
@@ -53795,7 +53795,7 @@
       </c>
       <c r="Z388" t="inlineStr">
         <is>
-          <t>22:43</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AA388" t="inlineStr">
@@ -53805,7 +53805,7 @@
       </c>
       <c r="AB388" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>23:03</t>
         </is>
       </c>
       <c r="AC388" t="inlineStr">
@@ -53850,10 +53850,10 @@
     </row>
     <row r="389">
       <c r="A389" t="n">
-        <v>122254350</v>
+        <v>122254500</v>
       </c>
       <c r="B389" t="n">
-        <v>56289</v>
+        <v>56275</v>
       </c>
       <c r="C389" t="inlineStr">
         <is>
@@ -53862,25 +53862,25 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E389" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I389" t="inlineStr">
@@ -53904,10 +53904,10 @@
         </is>
       </c>
       <c r="Q389" t="n">
-        <v>586330</v>
+        <v>586388</v>
       </c>
       <c r="R389" t="n">
-        <v>6311120</v>
+        <v>6311142</v>
       </c>
       <c r="S389" t="n">
         <v>5</v>
@@ -53939,7 +53939,7 @@
       </c>
       <c r="Z389" t="inlineStr">
         <is>
-          <t>22:57</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA389" t="inlineStr">
@@ -53949,7 +53949,7 @@
       </c>
       <c r="AB389" t="inlineStr">
         <is>
-          <t>22:58</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AC389" t="inlineStr">

--- a/artfynd/A 36363-2024 artfynd.xlsx
+++ b/artfynd/A 36363-2024 artfynd.xlsx
@@ -37002,7 +37002,7 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>122254411</v>
+        <v>122254343</v>
       </c>
       <c r="B272" t="n">
         <v>56289</v>
@@ -37056,10 +37056,10 @@
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>586414</v>
+        <v>586388</v>
       </c>
       <c r="R272" t="n">
-        <v>6311126</v>
+        <v>6311142</v>
       </c>
       <c r="S272" t="n">
         <v>5</v>
@@ -37091,7 +37091,7 @@
       </c>
       <c r="Z272" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA272" t="inlineStr">
@@ -37101,7 +37101,7 @@
       </c>
       <c r="AB272" t="inlineStr">
         <is>
-          <t>22:38</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AC272" t="inlineStr">
@@ -37146,10 +37146,10 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>122254371</v>
+        <v>122254472</v>
       </c>
       <c r="B273" t="n">
-        <v>56289</v>
+        <v>56275</v>
       </c>
       <c r="C273" t="inlineStr">
         <is>
@@ -37158,25 +37158,25 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E273" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
@@ -37200,10 +37200,10 @@
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>586308</v>
+        <v>586455</v>
       </c>
       <c r="R273" t="n">
-        <v>6311132</v>
+        <v>6311159</v>
       </c>
       <c r="S273" t="n">
         <v>5</v>
@@ -37235,7 +37235,7 @@
       </c>
       <c r="Z273" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AA273" t="inlineStr">
@@ -37245,7 +37245,7 @@
       </c>
       <c r="AB273" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AC273" t="inlineStr">
@@ -37290,10 +37290,10 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>122254838</v>
+        <v>122254496</v>
       </c>
       <c r="B274" t="n">
-        <v>56292</v>
+        <v>56275</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>
@@ -37302,25 +37302,25 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E274" t="n">
-        <v>100111</v>
+        <v>205998</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
@@ -37344,10 +37344,10 @@
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>586448</v>
+        <v>586415</v>
       </c>
       <c r="R274" t="n">
-        <v>6311154</v>
+        <v>6311146</v>
       </c>
       <c r="S274" t="n">
         <v>5</v>
@@ -37379,7 +37379,7 @@
       </c>
       <c r="Z274" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AA274" t="inlineStr">
@@ -37389,7 +37389,7 @@
       </c>
       <c r="AB274" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>23:03</t>
         </is>
       </c>
       <c r="AC274" t="inlineStr">
@@ -37434,10 +37434,10 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>122254950</v>
+        <v>122254317</v>
       </c>
       <c r="B275" t="n">
-        <v>56282</v>
+        <v>56289</v>
       </c>
       <c r="C275" t="inlineStr">
         <is>
@@ -37450,21 +37450,21 @@
         </is>
       </c>
       <c r="E275" t="n">
-        <v>205992</v>
+        <v>100092</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
@@ -37488,10 +37488,10 @@
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>586482</v>
+        <v>586438</v>
       </c>
       <c r="R275" t="n">
-        <v>6311185</v>
+        <v>6311222</v>
       </c>
       <c r="S275" t="n">
         <v>5</v>
@@ -37523,7 +37523,7 @@
       </c>
       <c r="Z275" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:22</t>
         </is>
       </c>
       <c r="AA275" t="inlineStr">
@@ -37533,7 +37533,7 @@
       </c>
       <c r="AB275" t="inlineStr">
         <is>
-          <t>23:31</t>
+          <t>23:23</t>
         </is>
       </c>
       <c r="AC275" t="inlineStr">
@@ -37578,10 +37578,10 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>122254617</v>
+        <v>122254396</v>
       </c>
       <c r="B276" t="n">
-        <v>56294</v>
+        <v>56289</v>
       </c>
       <c r="C276" t="inlineStr">
         <is>
@@ -37594,21 +37594,21 @@
         </is>
       </c>
       <c r="E276" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
@@ -37632,10 +37632,10 @@
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>586317</v>
+        <v>586408</v>
       </c>
       <c r="R276" t="n">
-        <v>6311115</v>
+        <v>6311124</v>
       </c>
       <c r="S276" t="n">
         <v>5</v>
@@ -37667,7 +37667,7 @@
       </c>
       <c r="Z276" t="inlineStr">
         <is>
-          <t>22:57</t>
+          <t>22:43</t>
         </is>
       </c>
       <c r="AA276" t="inlineStr">
@@ -37677,7 +37677,7 @@
       </c>
       <c r="AB276" t="inlineStr">
         <is>
-          <t>22:58</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AC276" t="inlineStr">
@@ -37722,10 +37722,10 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>122254952</v>
+        <v>122254609</v>
       </c>
       <c r="B277" t="n">
-        <v>56282</v>
+        <v>56294</v>
       </c>
       <c r="C277" t="inlineStr">
         <is>
@@ -37738,21 +37738,21 @@
         </is>
       </c>
       <c r="E277" t="n">
-        <v>205992</v>
+        <v>205995</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
@@ -37776,10 +37776,10 @@
         </is>
       </c>
       <c r="Q277" t="n">
-        <v>586455</v>
+        <v>586392</v>
       </c>
       <c r="R277" t="n">
-        <v>6311156</v>
+        <v>6311147</v>
       </c>
       <c r="S277" t="n">
         <v>5</v>
@@ -37811,7 +37811,7 @@
       </c>
       <c r="Z277" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AA277" t="inlineStr">
@@ -37821,7 +37821,7 @@
       </c>
       <c r="AB277" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AC277" t="inlineStr">
@@ -37866,7 +37866,7 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>122254369</v>
+        <v>122254372</v>
       </c>
       <c r="B278" t="n">
         <v>56289</v>
@@ -37920,10 +37920,10 @@
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>586300</v>
+        <v>586306</v>
       </c>
       <c r="R278" t="n">
-        <v>6311112</v>
+        <v>6311131</v>
       </c>
       <c r="S278" t="n">
         <v>5</v>
@@ -38010,7 +38010,7 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>122254625</v>
+        <v>122254612</v>
       </c>
       <c r="B279" t="n">
         <v>56294</v>
@@ -38064,10 +38064,10 @@
         </is>
       </c>
       <c r="Q279" t="n">
-        <v>586309</v>
+        <v>586371</v>
       </c>
       <c r="R279" t="n">
-        <v>6311119</v>
+        <v>6311135</v>
       </c>
       <c r="S279" t="n">
         <v>5</v>
@@ -38099,7 +38099,7 @@
       </c>
       <c r="Z279" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>22:59</t>
         </is>
       </c>
       <c r="AA279" t="inlineStr">
@@ -38109,7 +38109,7 @@
       </c>
       <c r="AB279" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AC279" t="inlineStr">
@@ -38154,10 +38154,10 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>122254608</v>
+        <v>122254953</v>
       </c>
       <c r="B280" t="n">
-        <v>56294</v>
+        <v>56282</v>
       </c>
       <c r="C280" t="inlineStr">
         <is>
@@ -38170,21 +38170,21 @@
         </is>
       </c>
       <c r="E280" t="n">
-        <v>205995</v>
+        <v>205992</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
@@ -38208,10 +38208,10 @@
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>586393</v>
+        <v>586449</v>
       </c>
       <c r="R280" t="n">
-        <v>6311147</v>
+        <v>6311155</v>
       </c>
       <c r="S280" t="n">
         <v>5</v>
@@ -38243,7 +38243,7 @@
       </c>
       <c r="Z280" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA280" t="inlineStr">
@@ -38253,7 +38253,7 @@
       </c>
       <c r="AB280" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC280" t="inlineStr">
@@ -38298,10 +38298,10 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>122254655</v>
+        <v>122254420</v>
       </c>
       <c r="B281" t="n">
-        <v>56294</v>
+        <v>56289</v>
       </c>
       <c r="C281" t="inlineStr">
         <is>
@@ -38314,21 +38314,21 @@
         </is>
       </c>
       <c r="E281" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
@@ -38352,10 +38352,10 @@
         </is>
       </c>
       <c r="Q281" t="n">
-        <v>586475</v>
+        <v>586467</v>
       </c>
       <c r="R281" t="n">
-        <v>6311187</v>
+        <v>6311178</v>
       </c>
       <c r="S281" t="n">
         <v>5</v>
@@ -38442,10 +38442,10 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>122254637</v>
+        <v>122254474</v>
       </c>
       <c r="B282" t="n">
-        <v>56294</v>
+        <v>56275</v>
       </c>
       <c r="C282" t="inlineStr">
         <is>
@@ -38454,25 +38454,25 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E282" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
@@ -38496,10 +38496,10 @@
         </is>
       </c>
       <c r="Q282" t="n">
-        <v>586408</v>
+        <v>586443</v>
       </c>
       <c r="R282" t="n">
-        <v>6311124</v>
+        <v>6311164</v>
       </c>
       <c r="S282" t="n">
         <v>5</v>
@@ -38531,7 +38531,7 @@
       </c>
       <c r="Z282" t="inlineStr">
         <is>
-          <t>22:43</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AA282" t="inlineStr">
@@ -38541,7 +38541,7 @@
       </c>
       <c r="AB282" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AC282" t="inlineStr">
@@ -38586,10 +38586,10 @@
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>122254413</v>
+        <v>122254655</v>
       </c>
       <c r="B283" t="n">
-        <v>56289</v>
+        <v>56294</v>
       </c>
       <c r="C283" t="inlineStr">
         <is>
@@ -38602,21 +38602,21 @@
         </is>
       </c>
       <c r="E283" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
@@ -38640,10 +38640,10 @@
         </is>
       </c>
       <c r="Q283" t="n">
-        <v>586423</v>
+        <v>586475</v>
       </c>
       <c r="R283" t="n">
-        <v>6311137</v>
+        <v>6311187</v>
       </c>
       <c r="S283" t="n">
         <v>5</v>
@@ -38675,7 +38675,7 @@
       </c>
       <c r="Z283" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AA283" t="inlineStr">
@@ -38685,7 +38685,7 @@
       </c>
       <c r="AB283" t="inlineStr">
         <is>
-          <t>22:38</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="AC283" t="inlineStr">
@@ -38730,7 +38730,7 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>122254316</v>
+        <v>122254365</v>
       </c>
       <c r="B284" t="n">
         <v>56289</v>
@@ -38784,10 +38784,10 @@
         </is>
       </c>
       <c r="Q284" t="n">
-        <v>586423</v>
+        <v>586276</v>
       </c>
       <c r="R284" t="n">
-        <v>6311166</v>
+        <v>6311100</v>
       </c>
       <c r="S284" t="n">
         <v>5</v>
@@ -38819,7 +38819,7 @@
       </c>
       <c r="Z284" t="inlineStr">
         <is>
-          <t>23:23</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AA284" t="inlineStr">
@@ -38829,7 +38829,7 @@
       </c>
       <c r="AB284" t="inlineStr">
         <is>
-          <t>23:24</t>
+          <t>22:52</t>
         </is>
       </c>
       <c r="AC284" t="inlineStr">
@@ -38874,10 +38874,10 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>122254393</v>
+        <v>122254648</v>
       </c>
       <c r="B285" t="n">
-        <v>56289</v>
+        <v>56294</v>
       </c>
       <c r="C285" t="inlineStr">
         <is>
@@ -38890,21 +38890,21 @@
         </is>
       </c>
       <c r="E285" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
@@ -38928,10 +38928,10 @@
         </is>
       </c>
       <c r="Q285" t="n">
-        <v>586396</v>
+        <v>586418</v>
       </c>
       <c r="R285" t="n">
-        <v>6311146</v>
+        <v>6311107</v>
       </c>
       <c r="S285" t="n">
         <v>5</v>
@@ -38963,7 +38963,7 @@
       </c>
       <c r="Z285" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>22:36</t>
         </is>
       </c>
       <c r="AA285" t="inlineStr">
@@ -38973,7 +38973,7 @@
       </c>
       <c r="AB285" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AC285" t="inlineStr">
@@ -39018,10 +39018,10 @@
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>122254420</v>
+        <v>122254954</v>
       </c>
       <c r="B286" t="n">
-        <v>56289</v>
+        <v>56282</v>
       </c>
       <c r="C286" t="inlineStr">
         <is>
@@ -39034,21 +39034,21 @@
         </is>
       </c>
       <c r="E286" t="n">
-        <v>100092</v>
+        <v>205992</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
@@ -39072,10 +39072,10 @@
         </is>
       </c>
       <c r="Q286" t="n">
-        <v>586467</v>
+        <v>586442</v>
       </c>
       <c r="R286" t="n">
-        <v>6311178</v>
+        <v>6311152</v>
       </c>
       <c r="S286" t="n">
         <v>5</v>
@@ -39107,7 +39107,7 @@
       </c>
       <c r="Z286" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AA286" t="inlineStr">
@@ -39117,7 +39117,7 @@
       </c>
       <c r="AB286" t="inlineStr">
         <is>
-          <t>22:33</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AC286" t="inlineStr">
@@ -39162,10 +39162,10 @@
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>122254855</v>
+        <v>122254644</v>
       </c>
       <c r="B287" t="n">
-        <v>56292</v>
+        <v>56294</v>
       </c>
       <c r="C287" t="inlineStr">
         <is>
@@ -39178,21 +39178,21 @@
         </is>
       </c>
       <c r="E287" t="n">
-        <v>100111</v>
+        <v>205995</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
@@ -39216,10 +39216,10 @@
         </is>
       </c>
       <c r="Q287" t="n">
-        <v>586330</v>
+        <v>586429</v>
       </c>
       <c r="R287" t="n">
-        <v>6311120</v>
+        <v>6311115</v>
       </c>
       <c r="S287" t="n">
         <v>5</v>
@@ -39251,7 +39251,7 @@
       </c>
       <c r="Z287" t="inlineStr">
         <is>
-          <t>22:57</t>
+          <t>22:36</t>
         </is>
       </c>
       <c r="AA287" t="inlineStr">
@@ -39261,7 +39261,7 @@
       </c>
       <c r="AB287" t="inlineStr">
         <is>
-          <t>22:58</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AC287" t="inlineStr">
@@ -39306,10 +39306,10 @@
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>122254658</v>
+        <v>122254952</v>
       </c>
       <c r="B288" t="n">
-        <v>56294</v>
+        <v>56282</v>
       </c>
       <c r="C288" t="inlineStr">
         <is>
@@ -39322,21 +39322,21 @@
         </is>
       </c>
       <c r="E288" t="n">
-        <v>205995</v>
+        <v>205992</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
@@ -39360,10 +39360,10 @@
         </is>
       </c>
       <c r="Q288" t="n">
-        <v>586491</v>
+        <v>586455</v>
       </c>
       <c r="R288" t="n">
-        <v>6311181</v>
+        <v>6311156</v>
       </c>
       <c r="S288" t="n">
         <v>5</v>
@@ -39395,7 +39395,7 @@
       </c>
       <c r="Z288" t="inlineStr">
         <is>
-          <t>22:31</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AA288" t="inlineStr">
@@ -39405,7 +39405,7 @@
       </c>
       <c r="AB288" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AC288" t="inlineStr">
@@ -39450,10 +39450,10 @@
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>122254612</v>
+        <v>122254514</v>
       </c>
       <c r="B289" t="n">
-        <v>56294</v>
+        <v>56275</v>
       </c>
       <c r="C289" t="inlineStr">
         <is>
@@ -39462,25 +39462,25 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E289" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
@@ -39504,10 +39504,10 @@
         </is>
       </c>
       <c r="Q289" t="n">
-        <v>586371</v>
+        <v>586408</v>
       </c>
       <c r="R289" t="n">
-        <v>6311135</v>
+        <v>6311124</v>
       </c>
       <c r="S289" t="n">
         <v>5</v>
@@ -39539,7 +39539,7 @@
       </c>
       <c r="Z289" t="inlineStr">
         <is>
-          <t>22:59</t>
+          <t>22:43</t>
         </is>
       </c>
       <c r="AA289" t="inlineStr">
@@ -39549,7 +39549,7 @@
       </c>
       <c r="AB289" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AC289" t="inlineStr">
@@ -39594,10 +39594,10 @@
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>122254966</v>
+        <v>122254512</v>
       </c>
       <c r="B290" t="n">
-        <v>56282</v>
+        <v>56275</v>
       </c>
       <c r="C290" t="inlineStr">
         <is>
@@ -39606,25 +39606,25 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E290" t="n">
-        <v>205992</v>
+        <v>205998</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
@@ -39648,10 +39648,10 @@
         </is>
       </c>
       <c r="Q290" t="n">
-        <v>586467</v>
+        <v>586379</v>
       </c>
       <c r="R290" t="n">
-        <v>6311178</v>
+        <v>6311136</v>
       </c>
       <c r="S290" t="n">
         <v>5</v>
@@ -39683,7 +39683,7 @@
       </c>
       <c r="Z290" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AA290" t="inlineStr">
@@ -39693,7 +39693,7 @@
       </c>
       <c r="AB290" t="inlineStr">
         <is>
-          <t>22:33</t>
+          <t>22:46</t>
         </is>
       </c>
       <c r="AC290" t="inlineStr">
@@ -39738,10 +39738,10 @@
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>122254314</v>
+        <v>122254950</v>
       </c>
       <c r="B291" t="n">
-        <v>56289</v>
+        <v>56282</v>
       </c>
       <c r="C291" t="inlineStr">
         <is>
@@ -39754,21 +39754,21 @@
         </is>
       </c>
       <c r="E291" t="n">
-        <v>100092</v>
+        <v>205992</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
@@ -39792,10 +39792,10 @@
         </is>
       </c>
       <c r="Q291" t="n">
-        <v>586443</v>
+        <v>586482</v>
       </c>
       <c r="R291" t="n">
-        <v>6311164</v>
+        <v>6311185</v>
       </c>
       <c r="S291" t="n">
         <v>5</v>
@@ -39827,7 +39827,7 @@
       </c>
       <c r="Z291" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AA291" t="inlineStr">
@@ -39837,7 +39837,7 @@
       </c>
       <c r="AB291" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>23:31</t>
         </is>
       </c>
       <c r="AC291" t="inlineStr">
@@ -39882,10 +39882,10 @@
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>122254476</v>
+        <v>122254951</v>
       </c>
       <c r="B292" t="n">
-        <v>56275</v>
+        <v>56282</v>
       </c>
       <c r="C292" t="inlineStr">
         <is>
@@ -39894,25 +39894,25 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E292" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
@@ -39936,10 +39936,10 @@
         </is>
       </c>
       <c r="Q292" t="n">
-        <v>586418</v>
+        <v>586459</v>
       </c>
       <c r="R292" t="n">
-        <v>6311167</v>
+        <v>6311154</v>
       </c>
       <c r="S292" t="n">
         <v>5</v>
@@ -39971,7 +39971,7 @@
       </c>
       <c r="Z292" t="inlineStr">
         <is>
-          <t>23:23</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AA292" t="inlineStr">
@@ -39981,7 +39981,7 @@
       </c>
       <c r="AB292" t="inlineStr">
         <is>
-          <t>23:24</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AC292" t="inlineStr">
@@ -40026,7 +40026,7 @@
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>122254660</v>
+        <v>122254587</v>
       </c>
       <c r="B293" t="n">
         <v>56294</v>
@@ -40080,10 +40080,10 @@
         </is>
       </c>
       <c r="Q293" t="n">
-        <v>586488</v>
+        <v>586443</v>
       </c>
       <c r="R293" t="n">
-        <v>6311183</v>
+        <v>6311163</v>
       </c>
       <c r="S293" t="n">
         <v>5</v>
@@ -40115,7 +40115,7 @@
       </c>
       <c r="Z293" t="inlineStr">
         <is>
-          <t>22:31</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AA293" t="inlineStr">
@@ -40125,7 +40125,7 @@
       </c>
       <c r="AB293" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AC293" t="inlineStr">
@@ -40170,10 +40170,10 @@
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>122254959</v>
+        <v>122254411</v>
       </c>
       <c r="B294" t="n">
-        <v>56282</v>
+        <v>56289</v>
       </c>
       <c r="C294" t="inlineStr">
         <is>
@@ -40186,21 +40186,21 @@
         </is>
       </c>
       <c r="E294" t="n">
-        <v>205992</v>
+        <v>100092</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
@@ -40224,10 +40224,10 @@
         </is>
       </c>
       <c r="Q294" t="n">
-        <v>586370</v>
+        <v>586414</v>
       </c>
       <c r="R294" t="n">
-        <v>6311139</v>
+        <v>6311126</v>
       </c>
       <c r="S294" t="n">
         <v>5</v>
@@ -40259,7 +40259,7 @@
       </c>
       <c r="Z294" t="inlineStr">
         <is>
-          <t>22:59</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AA294" t="inlineStr">
@@ -40269,7 +40269,7 @@
       </c>
       <c r="AB294" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:38</t>
         </is>
       </c>
       <c r="AC294" t="inlineStr">
@@ -40314,10 +40314,10 @@
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>122254607</v>
+        <v>122254352</v>
       </c>
       <c r="B295" t="n">
-        <v>56294</v>
+        <v>56289</v>
       </c>
       <c r="C295" t="inlineStr">
         <is>
@@ -40330,21 +40330,21 @@
         </is>
       </c>
       <c r="E295" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
@@ -40368,10 +40368,10 @@
         </is>
       </c>
       <c r="Q295" t="n">
-        <v>586415</v>
+        <v>586288</v>
       </c>
       <c r="R295" t="n">
-        <v>6311149</v>
+        <v>6311100</v>
       </c>
       <c r="S295" t="n">
         <v>5</v>
@@ -40403,7 +40403,7 @@
       </c>
       <c r="Z295" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>22:55</t>
         </is>
       </c>
       <c r="AA295" t="inlineStr">
@@ -40413,7 +40413,7 @@
       </c>
       <c r="AB295" t="inlineStr">
         <is>
-          <t>23:03</t>
+          <t>22:56</t>
         </is>
       </c>
       <c r="AC295" t="inlineStr">
@@ -40458,10 +40458,10 @@
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>122254657</v>
+        <v>122254392</v>
       </c>
       <c r="B296" t="n">
-        <v>56294</v>
+        <v>56289</v>
       </c>
       <c r="C296" t="inlineStr">
         <is>
@@ -40474,21 +40474,21 @@
         </is>
       </c>
       <c r="E296" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
@@ -40512,10 +40512,10 @@
         </is>
       </c>
       <c r="Q296" t="n">
-        <v>586488</v>
+        <v>586384</v>
       </c>
       <c r="R296" t="n">
-        <v>6311184</v>
+        <v>6311139</v>
       </c>
       <c r="S296" t="n">
         <v>5</v>
@@ -40547,7 +40547,7 @@
       </c>
       <c r="Z296" t="inlineStr">
         <is>
-          <t>22:31</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AA296" t="inlineStr">
@@ -40557,7 +40557,7 @@
       </c>
       <c r="AB296" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>22:46</t>
         </is>
       </c>
       <c r="AC296" t="inlineStr">
@@ -40602,10 +40602,10 @@
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>122254953</v>
+        <v>122254845</v>
       </c>
       <c r="B297" t="n">
-        <v>56282</v>
+        <v>56292</v>
       </c>
       <c r="C297" t="inlineStr">
         <is>
@@ -40618,21 +40618,21 @@
         </is>
       </c>
       <c r="E297" t="n">
-        <v>205992</v>
+        <v>100111</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
@@ -40656,10 +40656,10 @@
         </is>
       </c>
       <c r="Q297" t="n">
-        <v>586449</v>
+        <v>586370</v>
       </c>
       <c r="R297" t="n">
-        <v>6311155</v>
+        <v>6311139</v>
       </c>
       <c r="S297" t="n">
         <v>5</v>
@@ -40691,7 +40691,7 @@
       </c>
       <c r="Z297" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>22:59</t>
         </is>
       </c>
       <c r="AA297" t="inlineStr">
@@ -40701,7 +40701,7 @@
       </c>
       <c r="AB297" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AC297" t="inlineStr">
@@ -40746,10 +40746,10 @@
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>122254343</v>
+        <v>122254855</v>
       </c>
       <c r="B298" t="n">
-        <v>56289</v>
+        <v>56292</v>
       </c>
       <c r="C298" t="inlineStr">
         <is>
@@ -40762,21 +40762,21 @@
         </is>
       </c>
       <c r="E298" t="n">
-        <v>100092</v>
+        <v>100111</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
@@ -40800,10 +40800,10 @@
         </is>
       </c>
       <c r="Q298" t="n">
-        <v>586388</v>
+        <v>586330</v>
       </c>
       <c r="R298" t="n">
-        <v>6311142</v>
+        <v>6311120</v>
       </c>
       <c r="S298" t="n">
         <v>5</v>
@@ -40835,7 +40835,7 @@
       </c>
       <c r="Z298" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:57</t>
         </is>
       </c>
       <c r="AA298" t="inlineStr">
@@ -40845,7 +40845,7 @@
       </c>
       <c r="AB298" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>22:58</t>
         </is>
       </c>
       <c r="AC298" t="inlineStr">
@@ -40890,10 +40890,10 @@
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>122254367</v>
+        <v>122254475</v>
       </c>
       <c r="B299" t="n">
-        <v>56289</v>
+        <v>56275</v>
       </c>
       <c r="C299" t="inlineStr">
         <is>
@@ -40902,25 +40902,25 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E299" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
@@ -40944,10 +40944,10 @@
         </is>
       </c>
       <c r="Q299" t="n">
-        <v>586280</v>
+        <v>586420</v>
       </c>
       <c r="R299" t="n">
-        <v>6311103</v>
+        <v>6311166</v>
       </c>
       <c r="S299" t="n">
         <v>5</v>
@@ -40979,7 +40979,7 @@
       </c>
       <c r="Z299" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>23:23</t>
         </is>
       </c>
       <c r="AA299" t="inlineStr">
@@ -40989,7 +40989,7 @@
       </c>
       <c r="AB299" t="inlineStr">
         <is>
-          <t>22:52</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="AC299" t="inlineStr">
@@ -41034,10 +41034,10 @@
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>122254310</v>
+        <v>122254513</v>
       </c>
       <c r="B300" t="n">
-        <v>56289</v>
+        <v>56275</v>
       </c>
       <c r="C300" t="inlineStr">
         <is>
@@ -41046,25 +41046,25 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E300" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
@@ -41088,10 +41088,10 @@
         </is>
       </c>
       <c r="Q300" t="n">
-        <v>586452</v>
+        <v>586396</v>
       </c>
       <c r="R300" t="n">
-        <v>6311156</v>
+        <v>6311146</v>
       </c>
       <c r="S300" t="n">
         <v>5</v>
@@ -41123,7 +41123,7 @@
       </c>
       <c r="Z300" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AA300" t="inlineStr">
@@ -41133,7 +41133,7 @@
       </c>
       <c r="AB300" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AC300" t="inlineStr">
@@ -41178,10 +41178,10 @@
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>122254843</v>
+        <v>122254627</v>
       </c>
       <c r="B301" t="n">
-        <v>56292</v>
+        <v>56294</v>
       </c>
       <c r="C301" t="inlineStr">
         <is>
@@ -41194,21 +41194,21 @@
         </is>
       </c>
       <c r="E301" t="n">
-        <v>100111</v>
+        <v>205995</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
@@ -41232,10 +41232,10 @@
         </is>
       </c>
       <c r="Q301" t="n">
-        <v>586389</v>
+        <v>586306</v>
       </c>
       <c r="R301" t="n">
-        <v>6311142</v>
+        <v>6311131</v>
       </c>
       <c r="S301" t="n">
         <v>5</v>
@@ -41267,7 +41267,7 @@
       </c>
       <c r="Z301" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AA301" t="inlineStr">
@@ -41277,7 +41277,7 @@
       </c>
       <c r="AB301" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AC301" t="inlineStr">
@@ -41322,7 +41322,7 @@
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>122254632</v>
+        <v>122254657</v>
       </c>
       <c r="B302" t="n">
         <v>56294</v>
@@ -41376,10 +41376,10 @@
         </is>
       </c>
       <c r="Q302" t="n">
-        <v>586374</v>
+        <v>586488</v>
       </c>
       <c r="R302" t="n">
-        <v>6311140</v>
+        <v>6311184</v>
       </c>
       <c r="S302" t="n">
         <v>5</v>
@@ -41411,7 +41411,7 @@
       </c>
       <c r="Z302" t="inlineStr">
         <is>
-          <t>22:46</t>
+          <t>22:31</t>
         </is>
       </c>
       <c r="AA302" t="inlineStr">
@@ -41421,7 +41421,7 @@
       </c>
       <c r="AB302" t="inlineStr">
         <is>
-          <t>22:47</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AC302" t="inlineStr">
@@ -41466,10 +41466,10 @@
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>122254512</v>
+        <v>122254373</v>
       </c>
       <c r="B303" t="n">
-        <v>56275</v>
+        <v>56289</v>
       </c>
       <c r="C303" t="inlineStr">
         <is>
@@ -41478,25 +41478,25 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E303" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
@@ -41520,10 +41520,10 @@
         </is>
       </c>
       <c r="Q303" t="n">
-        <v>586379</v>
+        <v>586307</v>
       </c>
       <c r="R303" t="n">
-        <v>6311136</v>
+        <v>6311133</v>
       </c>
       <c r="S303" t="n">
         <v>5</v>
@@ -41555,7 +41555,7 @@
       </c>
       <c r="Z303" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>22:49</t>
         </is>
       </c>
       <c r="AA303" t="inlineStr">
@@ -41565,7 +41565,7 @@
       </c>
       <c r="AB303" t="inlineStr">
         <is>
-          <t>22:46</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AC303" t="inlineStr">
@@ -41610,10 +41610,10 @@
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>122254615</v>
+        <v>122254843</v>
       </c>
       <c r="B304" t="n">
-        <v>56294</v>
+        <v>56292</v>
       </c>
       <c r="C304" t="inlineStr">
         <is>
@@ -41626,21 +41626,21 @@
         </is>
       </c>
       <c r="E304" t="n">
-        <v>205995</v>
+        <v>100111</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
@@ -41664,10 +41664,10 @@
         </is>
       </c>
       <c r="Q304" t="n">
-        <v>586329</v>
+        <v>586389</v>
       </c>
       <c r="R304" t="n">
-        <v>6311120</v>
+        <v>6311142</v>
       </c>
       <c r="S304" t="n">
         <v>5</v>
@@ -41699,7 +41699,7 @@
       </c>
       <c r="Z304" t="inlineStr">
         <is>
-          <t>22:57</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA304" t="inlineStr">
@@ -41709,7 +41709,7 @@
       </c>
       <c r="AB304" t="inlineStr">
         <is>
-          <t>22:58</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AC304" t="inlineStr">
@@ -41754,10 +41754,10 @@
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>122254514</v>
+        <v>122254957</v>
       </c>
       <c r="B305" t="n">
-        <v>56275</v>
+        <v>56282</v>
       </c>
       <c r="C305" t="inlineStr">
         <is>
@@ -41766,25 +41766,25 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E305" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
@@ -41808,10 +41808,10 @@
         </is>
       </c>
       <c r="Q305" t="n">
-        <v>586408</v>
+        <v>586444</v>
       </c>
       <c r="R305" t="n">
-        <v>6311124</v>
+        <v>6311160</v>
       </c>
       <c r="S305" t="n">
         <v>5</v>
@@ -41843,7 +41843,7 @@
       </c>
       <c r="Z305" t="inlineStr">
         <is>
-          <t>22:43</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="AA305" t="inlineStr">
@@ -41853,7 +41853,7 @@
       </c>
       <c r="AB305" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AC305" t="inlineStr">
@@ -41898,7 +41898,7 @@
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>122254519</v>
+        <v>122254476</v>
       </c>
       <c r="B306" t="n">
         <v>56275</v>
@@ -41952,10 +41952,10 @@
         </is>
       </c>
       <c r="Q306" t="n">
-        <v>586424</v>
+        <v>586418</v>
       </c>
       <c r="R306" t="n">
-        <v>6311135</v>
+        <v>6311167</v>
       </c>
       <c r="S306" t="n">
         <v>5</v>
@@ -41987,7 +41987,7 @@
       </c>
       <c r="Z306" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>23:23</t>
         </is>
       </c>
       <c r="AA306" t="inlineStr">
@@ -41997,7 +41997,7 @@
       </c>
       <c r="AB306" t="inlineStr">
         <is>
-          <t>22:38</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="AC306" t="inlineStr">
@@ -42042,10 +42042,10 @@
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>122254954</v>
+        <v>122254658</v>
       </c>
       <c r="B307" t="n">
-        <v>56282</v>
+        <v>56294</v>
       </c>
       <c r="C307" t="inlineStr">
         <is>
@@ -42058,21 +42058,21 @@
         </is>
       </c>
       <c r="E307" t="n">
-        <v>205992</v>
+        <v>205995</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
@@ -42096,10 +42096,10 @@
         </is>
       </c>
       <c r="Q307" t="n">
-        <v>586442</v>
+        <v>586491</v>
       </c>
       <c r="R307" t="n">
-        <v>6311152</v>
+        <v>6311181</v>
       </c>
       <c r="S307" t="n">
         <v>5</v>
@@ -42131,7 +42131,7 @@
       </c>
       <c r="Z307" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>22:31</t>
         </is>
       </c>
       <c r="AA307" t="inlineStr">
@@ -42141,7 +42141,7 @@
       </c>
       <c r="AB307" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AC307" t="inlineStr">
@@ -42186,10 +42186,10 @@
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>122254370</v>
+        <v>122254649</v>
       </c>
       <c r="B308" t="n">
-        <v>56289</v>
+        <v>56294</v>
       </c>
       <c r="C308" t="inlineStr">
         <is>
@@ -42202,21 +42202,21 @@
         </is>
       </c>
       <c r="E308" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
@@ -42240,10 +42240,10 @@
         </is>
       </c>
       <c r="Q308" t="n">
-        <v>586309</v>
+        <v>586422</v>
       </c>
       <c r="R308" t="n">
-        <v>6311119</v>
+        <v>6311100</v>
       </c>
       <c r="S308" t="n">
         <v>5</v>
@@ -42275,7 +42275,7 @@
       </c>
       <c r="Z308" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="AA308" t="inlineStr">
@@ -42285,7 +42285,7 @@
       </c>
       <c r="AB308" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>22:36</t>
         </is>
       </c>
       <c r="AC308" t="inlineStr">
@@ -42330,10 +42330,10 @@
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>122254880</v>
+        <v>122254646</v>
       </c>
       <c r="B309" t="n">
-        <v>56292</v>
+        <v>56294</v>
       </c>
       <c r="C309" t="inlineStr">
         <is>
@@ -42346,21 +42346,21 @@
         </is>
       </c>
       <c r="E309" t="n">
-        <v>100111</v>
+        <v>205995</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
@@ -42384,10 +42384,10 @@
         </is>
       </c>
       <c r="Q309" t="n">
-        <v>586303</v>
+        <v>586422</v>
       </c>
       <c r="R309" t="n">
-        <v>6311115</v>
+        <v>6311111</v>
       </c>
       <c r="S309" t="n">
         <v>5</v>
@@ -42419,7 +42419,7 @@
       </c>
       <c r="Z309" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>22:36</t>
         </is>
       </c>
       <c r="AA309" t="inlineStr">
@@ -42429,7 +42429,7 @@
       </c>
       <c r="AB309" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AC309" t="inlineStr">
@@ -42474,10 +42474,10 @@
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>122254372</v>
+        <v>122254963</v>
       </c>
       <c r="B310" t="n">
-        <v>56289</v>
+        <v>56282</v>
       </c>
       <c r="C310" t="inlineStr">
         <is>
@@ -42490,21 +42490,21 @@
         </is>
       </c>
       <c r="E310" t="n">
-        <v>100092</v>
+        <v>205992</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
@@ -42528,10 +42528,10 @@
         </is>
       </c>
       <c r="Q310" t="n">
-        <v>586306</v>
+        <v>586374</v>
       </c>
       <c r="R310" t="n">
-        <v>6311131</v>
+        <v>6311140</v>
       </c>
       <c r="S310" t="n">
         <v>5</v>
@@ -42563,7 +42563,7 @@
       </c>
       <c r="Z310" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>22:46</t>
         </is>
       </c>
       <c r="AA310" t="inlineStr">
@@ -42573,7 +42573,7 @@
       </c>
       <c r="AB310" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>22:47</t>
         </is>
       </c>
       <c r="AC310" t="inlineStr">
@@ -42618,10 +42618,10 @@
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>122254854</v>
+        <v>122254309</v>
       </c>
       <c r="B311" t="n">
-        <v>56292</v>
+        <v>56289</v>
       </c>
       <c r="C311" t="inlineStr">
         <is>
@@ -42634,21 +42634,21 @@
         </is>
       </c>
       <c r="E311" t="n">
-        <v>100111</v>
+        <v>100092</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
@@ -42672,10 +42672,10 @@
         </is>
       </c>
       <c r="Q311" t="n">
-        <v>586329</v>
+        <v>586456</v>
       </c>
       <c r="R311" t="n">
-        <v>6311120</v>
+        <v>6311158</v>
       </c>
       <c r="S311" t="n">
         <v>5</v>
@@ -42707,7 +42707,7 @@
       </c>
       <c r="Z311" t="inlineStr">
         <is>
-          <t>22:57</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AA311" t="inlineStr">
@@ -42717,7 +42717,7 @@
       </c>
       <c r="AB311" t="inlineStr">
         <is>
-          <t>22:58</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AC311" t="inlineStr">
@@ -42762,7 +42762,7 @@
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>122254844</v>
+        <v>122254880</v>
       </c>
       <c r="B312" t="n">
         <v>56292</v>
@@ -42816,10 +42816,10 @@
         </is>
       </c>
       <c r="Q312" t="n">
-        <v>586387</v>
+        <v>586303</v>
       </c>
       <c r="R312" t="n">
-        <v>6311141</v>
+        <v>6311115</v>
       </c>
       <c r="S312" t="n">
         <v>5</v>
@@ -42851,7 +42851,7 @@
       </c>
       <c r="Z312" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AA312" t="inlineStr">
@@ -42861,7 +42861,7 @@
       </c>
       <c r="AB312" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AC312" t="inlineStr">
@@ -42906,10 +42906,10 @@
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>122254651</v>
+        <v>122254854</v>
       </c>
       <c r="B313" t="n">
-        <v>56294</v>
+        <v>56292</v>
       </c>
       <c r="C313" t="inlineStr">
         <is>
@@ -42922,21 +42922,21 @@
         </is>
       </c>
       <c r="E313" t="n">
-        <v>205995</v>
+        <v>100111</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
@@ -42960,10 +42960,10 @@
         </is>
       </c>
       <c r="Q313" t="n">
-        <v>586425</v>
+        <v>586329</v>
       </c>
       <c r="R313" t="n">
-        <v>6311113</v>
+        <v>6311120</v>
       </c>
       <c r="S313" t="n">
         <v>5</v>
@@ -42995,7 +42995,7 @@
       </c>
       <c r="Z313" t="inlineStr">
         <is>
-          <t>22:35</t>
+          <t>22:57</t>
         </is>
       </c>
       <c r="AA313" t="inlineStr">
@@ -43005,7 +43005,7 @@
       </c>
       <c r="AB313" t="inlineStr">
         <is>
-          <t>22:36</t>
+          <t>22:58</t>
         </is>
       </c>
       <c r="AC313" t="inlineStr">
@@ -43050,10 +43050,10 @@
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>122254964</v>
+        <v>122254878</v>
       </c>
       <c r="B314" t="n">
-        <v>56282</v>
+        <v>56292</v>
       </c>
       <c r="C314" t="inlineStr">
         <is>
@@ -43066,21 +43066,21 @@
         </is>
       </c>
       <c r="E314" t="n">
-        <v>205992</v>
+        <v>100111</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
@@ -43104,10 +43104,10 @@
         </is>
       </c>
       <c r="Q314" t="n">
-        <v>586430</v>
+        <v>586280</v>
       </c>
       <c r="R314" t="n">
-        <v>6311142</v>
+        <v>6311103</v>
       </c>
       <c r="S314" t="n">
         <v>5</v>
@@ -43139,7 +43139,7 @@
       </c>
       <c r="Z314" t="inlineStr">
         <is>
-          <t>22:33</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AA314" t="inlineStr">
@@ -43149,7 +43149,7 @@
       </c>
       <c r="AB314" t="inlineStr">
         <is>
-          <t>22:34</t>
+          <t>22:52</t>
         </is>
       </c>
       <c r="AC314" t="inlineStr">
@@ -43194,10 +43194,10 @@
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>122254473</v>
+        <v>122254310</v>
       </c>
       <c r="B315" t="n">
-        <v>56275</v>
+        <v>56289</v>
       </c>
       <c r="C315" t="inlineStr">
         <is>
@@ -43206,25 +43206,25 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E315" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
@@ -43248,10 +43248,10 @@
         </is>
       </c>
       <c r="Q315" t="n">
-        <v>586450</v>
+        <v>586452</v>
       </c>
       <c r="R315" t="n">
-        <v>6311152</v>
+        <v>6311156</v>
       </c>
       <c r="S315" t="n">
         <v>5</v>
@@ -43338,10 +43338,10 @@
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>122254342</v>
+        <v>122254877</v>
       </c>
       <c r="B316" t="n">
-        <v>56289</v>
+        <v>56292</v>
       </c>
       <c r="C316" t="inlineStr">
         <is>
@@ -43354,21 +43354,21 @@
         </is>
       </c>
       <c r="E316" t="n">
-        <v>100092</v>
+        <v>100111</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
@@ -43392,10 +43392,10 @@
         </is>
       </c>
       <c r="Q316" t="n">
-        <v>586389</v>
+        <v>586276</v>
       </c>
       <c r="R316" t="n">
-        <v>6311142</v>
+        <v>6311100</v>
       </c>
       <c r="S316" t="n">
         <v>5</v>
@@ -43427,7 +43427,7 @@
       </c>
       <c r="Z316" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AA316" t="inlineStr">
@@ -43437,7 +43437,7 @@
       </c>
       <c r="AB316" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>22:52</t>
         </is>
       </c>
       <c r="AC316" t="inlineStr">
@@ -43482,10 +43482,10 @@
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>122254390</v>
+        <v>122254633</v>
       </c>
       <c r="B317" t="n">
-        <v>56289</v>
+        <v>56294</v>
       </c>
       <c r="C317" t="inlineStr">
         <is>
@@ -43498,21 +43498,21 @@
         </is>
       </c>
       <c r="E317" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
@@ -43536,10 +43536,10 @@
         </is>
       </c>
       <c r="Q317" t="n">
-        <v>586374</v>
+        <v>586396</v>
       </c>
       <c r="R317" t="n">
-        <v>6311139</v>
+        <v>6311146</v>
       </c>
       <c r="S317" t="n">
         <v>5</v>
@@ -43571,7 +43571,7 @@
       </c>
       <c r="Z317" t="inlineStr">
         <is>
-          <t>22:46</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AA317" t="inlineStr">
@@ -43581,7 +43581,7 @@
       </c>
       <c r="AB317" t="inlineStr">
         <is>
-          <t>22:47</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AC317" t="inlineStr">
@@ -43626,10 +43626,10 @@
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>122254392</v>
+        <v>122254500</v>
       </c>
       <c r="B318" t="n">
-        <v>56289</v>
+        <v>56275</v>
       </c>
       <c r="C318" t="inlineStr">
         <is>
@@ -43638,25 +43638,25 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E318" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
@@ -43680,10 +43680,10 @@
         </is>
       </c>
       <c r="Q318" t="n">
-        <v>586384</v>
+        <v>586388</v>
       </c>
       <c r="R318" t="n">
-        <v>6311139</v>
+        <v>6311142</v>
       </c>
       <c r="S318" t="n">
         <v>5</v>
@@ -43715,7 +43715,7 @@
       </c>
       <c r="Z318" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA318" t="inlineStr">
@@ -43725,7 +43725,7 @@
       </c>
       <c r="AB318" t="inlineStr">
         <is>
-          <t>22:46</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AC318" t="inlineStr">
@@ -43770,10 +43770,10 @@
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>122254635</v>
+        <v>122254318</v>
       </c>
       <c r="B319" t="n">
-        <v>56294</v>
+        <v>56289</v>
       </c>
       <c r="C319" t="inlineStr">
         <is>
@@ -43786,21 +43786,21 @@
         </is>
       </c>
       <c r="E319" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
@@ -43824,10 +43824,10 @@
         </is>
       </c>
       <c r="Q319" t="n">
-        <v>586417</v>
+        <v>586455</v>
       </c>
       <c r="R319" t="n">
-        <v>6311145</v>
+        <v>6311228</v>
       </c>
       <c r="S319" t="n">
         <v>5</v>
@@ -43859,7 +43859,7 @@
       </c>
       <c r="Z319" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>23:22</t>
         </is>
       </c>
       <c r="AA319" t="inlineStr">
@@ -43869,7 +43869,7 @@
       </c>
       <c r="AB319" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>23:23</t>
         </is>
       </c>
       <c r="AC319" t="inlineStr">
@@ -43914,10 +43914,10 @@
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>122254627</v>
+        <v>122254314</v>
       </c>
       <c r="B320" t="n">
-        <v>56294</v>
+        <v>56289</v>
       </c>
       <c r="C320" t="inlineStr">
         <is>
@@ -43930,21 +43930,21 @@
         </is>
       </c>
       <c r="E320" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
@@ -43968,10 +43968,10 @@
         </is>
       </c>
       <c r="Q320" t="n">
-        <v>586306</v>
+        <v>586443</v>
       </c>
       <c r="R320" t="n">
-        <v>6311131</v>
+        <v>6311164</v>
       </c>
       <c r="S320" t="n">
         <v>5</v>
@@ -44003,7 +44003,7 @@
       </c>
       <c r="Z320" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AA320" t="inlineStr">
@@ -44013,7 +44013,7 @@
       </c>
       <c r="AB320" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AC320" t="inlineStr">
@@ -44058,10 +44058,10 @@
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>122254588</v>
+        <v>122254862</v>
       </c>
       <c r="B321" t="n">
-        <v>56294</v>
+        <v>56292</v>
       </c>
       <c r="C321" t="inlineStr">
         <is>
@@ -44074,21 +44074,21 @@
         </is>
       </c>
       <c r="E321" t="n">
-        <v>205995</v>
+        <v>100111</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
@@ -44112,10 +44112,10 @@
         </is>
       </c>
       <c r="Q321" t="n">
-        <v>586415</v>
+        <v>586288</v>
       </c>
       <c r="R321" t="n">
-        <v>6311196</v>
+        <v>6311100</v>
       </c>
       <c r="S321" t="n">
         <v>5</v>
@@ -44147,7 +44147,7 @@
       </c>
       <c r="Z321" t="inlineStr">
         <is>
-          <t>23:22</t>
+          <t>22:55</t>
         </is>
       </c>
       <c r="AA321" t="inlineStr">
@@ -44157,7 +44157,7 @@
       </c>
       <c r="AB321" t="inlineStr">
         <is>
-          <t>23:23</t>
+          <t>22:56</t>
         </is>
       </c>
       <c r="AC321" t="inlineStr">
@@ -44202,7 +44202,7 @@
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>122254309</v>
+        <v>122254413</v>
       </c>
       <c r="B322" t="n">
         <v>56289</v>
@@ -44256,10 +44256,10 @@
         </is>
       </c>
       <c r="Q322" t="n">
-        <v>586456</v>
+        <v>586423</v>
       </c>
       <c r="R322" t="n">
-        <v>6311158</v>
+        <v>6311137</v>
       </c>
       <c r="S322" t="n">
         <v>5</v>
@@ -44291,7 +44291,7 @@
       </c>
       <c r="Z322" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AA322" t="inlineStr">
@@ -44301,7 +44301,7 @@
       </c>
       <c r="AB322" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>22:38</t>
         </is>
       </c>
       <c r="AC322" t="inlineStr">
@@ -44346,10 +44346,10 @@
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>122254472</v>
+        <v>122254416</v>
       </c>
       <c r="B323" t="n">
-        <v>56275</v>
+        <v>56289</v>
       </c>
       <c r="C323" t="inlineStr">
         <is>
@@ -44358,25 +44358,25 @@
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E323" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
@@ -44400,10 +44400,10 @@
         </is>
       </c>
       <c r="Q323" t="n">
-        <v>586455</v>
+        <v>586410</v>
       </c>
       <c r="R323" t="n">
-        <v>6311159</v>
+        <v>6311140</v>
       </c>
       <c r="S323" t="n">
         <v>5</v>
@@ -44435,7 +44435,7 @@
       </c>
       <c r="Z323" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="AA323" t="inlineStr">
@@ -44445,7 +44445,7 @@
       </c>
       <c r="AB323" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>22:34</t>
         </is>
       </c>
       <c r="AC323" t="inlineStr">
@@ -44490,10 +44490,10 @@
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>122254585</v>
+        <v>122254835</v>
       </c>
       <c r="B324" t="n">
-        <v>56294</v>
+        <v>56292</v>
       </c>
       <c r="C324" t="inlineStr">
         <is>
@@ -44506,21 +44506,21 @@
         </is>
       </c>
       <c r="E324" t="n">
-        <v>205995</v>
+        <v>100111</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
@@ -44544,10 +44544,10 @@
         </is>
       </c>
       <c r="Q324" t="n">
-        <v>586455</v>
+        <v>586473</v>
       </c>
       <c r="R324" t="n">
-        <v>6311156</v>
+        <v>6311192</v>
       </c>
       <c r="S324" t="n">
         <v>5</v>
@@ -44579,7 +44579,7 @@
       </c>
       <c r="Z324" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AA324" t="inlineStr">
@@ -44589,7 +44589,7 @@
       </c>
       <c r="AB324" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AC324" t="inlineStr">
@@ -44634,10 +44634,10 @@
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>122254636</v>
+        <v>122254857</v>
       </c>
       <c r="B325" t="n">
-        <v>56294</v>
+        <v>56292</v>
       </c>
       <c r="C325" t="inlineStr">
         <is>
@@ -44650,21 +44650,21 @@
         </is>
       </c>
       <c r="E325" t="n">
-        <v>205995</v>
+        <v>100111</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
@@ -44688,10 +44688,10 @@
         </is>
       </c>
       <c r="Q325" t="n">
-        <v>586418</v>
+        <v>586317</v>
       </c>
       <c r="R325" t="n">
-        <v>6311145</v>
+        <v>6311115</v>
       </c>
       <c r="S325" t="n">
         <v>5</v>
@@ -44723,7 +44723,7 @@
       </c>
       <c r="Z325" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>22:57</t>
         </is>
       </c>
       <c r="AA325" t="inlineStr">
@@ -44733,7 +44733,7 @@
       </c>
       <c r="AB325" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>22:58</t>
         </is>
       </c>
       <c r="AC325" t="inlineStr">
@@ -44778,10 +44778,10 @@
     </row>
     <row r="326">
       <c r="A326" t="n">
-        <v>122254878</v>
+        <v>122254660</v>
       </c>
       <c r="B326" t="n">
-        <v>56292</v>
+        <v>56294</v>
       </c>
       <c r="C326" t="inlineStr">
         <is>
@@ -44794,21 +44794,21 @@
         </is>
       </c>
       <c r="E326" t="n">
-        <v>100111</v>
+        <v>205995</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
@@ -44832,10 +44832,10 @@
         </is>
       </c>
       <c r="Q326" t="n">
-        <v>586280</v>
+        <v>586488</v>
       </c>
       <c r="R326" t="n">
-        <v>6311103</v>
+        <v>6311183</v>
       </c>
       <c r="S326" t="n">
         <v>5</v>
@@ -44867,7 +44867,7 @@
       </c>
       <c r="Z326" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>22:31</t>
         </is>
       </c>
       <c r="AA326" t="inlineStr">
@@ -44877,7 +44877,7 @@
       </c>
       <c r="AB326" t="inlineStr">
         <is>
-          <t>22:52</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AC326" t="inlineStr">
@@ -44922,10 +44922,10 @@
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>122254391</v>
+        <v>122254654</v>
       </c>
       <c r="B327" t="n">
-        <v>56289</v>
+        <v>56294</v>
       </c>
       <c r="C327" t="inlineStr">
         <is>
@@ -44938,21 +44938,21 @@
         </is>
       </c>
       <c r="E327" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
@@ -44976,10 +44976,10 @@
         </is>
       </c>
       <c r="Q327" t="n">
-        <v>586379</v>
+        <v>586467</v>
       </c>
       <c r="R327" t="n">
-        <v>6311136</v>
+        <v>6311178</v>
       </c>
       <c r="S327" t="n">
         <v>5</v>
@@ -45011,7 +45011,7 @@
       </c>
       <c r="Z327" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AA327" t="inlineStr">
@@ -45021,7 +45021,7 @@
       </c>
       <c r="AB327" t="inlineStr">
         <is>
-          <t>22:46</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="AC327" t="inlineStr">
@@ -45066,10 +45066,10 @@
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>122254503</v>
+        <v>122254659</v>
       </c>
       <c r="B328" t="n">
-        <v>56275</v>
+        <v>56294</v>
       </c>
       <c r="C328" t="inlineStr">
         <is>
@@ -45078,25 +45078,25 @@
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E328" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
@@ -45120,10 +45120,10 @@
         </is>
       </c>
       <c r="Q328" t="n">
-        <v>586313</v>
+        <v>586489</v>
       </c>
       <c r="R328" t="n">
-        <v>6311124</v>
+        <v>6311181</v>
       </c>
       <c r="S328" t="n">
         <v>5</v>
@@ -45155,7 +45155,7 @@
       </c>
       <c r="Z328" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>22:31</t>
         </is>
       </c>
       <c r="AA328" t="inlineStr">
@@ -45165,7 +45165,7 @@
       </c>
       <c r="AB328" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AC328" t="inlineStr">
@@ -45210,7 +45210,7 @@
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>122254498</v>
+        <v>122254499</v>
       </c>
       <c r="B329" t="n">
         <v>56275</v>
@@ -45264,7 +45264,7 @@
         </is>
       </c>
       <c r="Q329" t="n">
-        <v>586393</v>
+        <v>586392</v>
       </c>
       <c r="R329" t="n">
         <v>6311147</v>
@@ -45354,7 +45354,7 @@
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>122254318</v>
+        <v>122254393</v>
       </c>
       <c r="B330" t="n">
         <v>56289</v>
@@ -45408,10 +45408,10 @@
         </is>
       </c>
       <c r="Q330" t="n">
-        <v>586455</v>
+        <v>586396</v>
       </c>
       <c r="R330" t="n">
-        <v>6311228</v>
+        <v>6311146</v>
       </c>
       <c r="S330" t="n">
         <v>5</v>
@@ -45443,7 +45443,7 @@
       </c>
       <c r="Z330" t="inlineStr">
         <is>
-          <t>23:22</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AA330" t="inlineStr">
@@ -45453,7 +45453,7 @@
       </c>
       <c r="AB330" t="inlineStr">
         <is>
-          <t>23:23</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AC330" t="inlineStr">
@@ -45498,7 +45498,7 @@
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>122254306</v>
+        <v>122254313</v>
       </c>
       <c r="B331" t="n">
         <v>56289</v>
@@ -45552,10 +45552,10 @@
         </is>
       </c>
       <c r="Q331" t="n">
-        <v>586473</v>
+        <v>586449</v>
       </c>
       <c r="R331" t="n">
-        <v>6311192</v>
+        <v>6311155</v>
       </c>
       <c r="S331" t="n">
         <v>5</v>
@@ -45587,7 +45587,7 @@
       </c>
       <c r="Z331" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA331" t="inlineStr">
@@ -45597,7 +45597,7 @@
       </c>
       <c r="AB331" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC331" t="inlineStr">
@@ -45642,10 +45642,10 @@
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>122254951</v>
+        <v>122254312</v>
       </c>
       <c r="B332" t="n">
-        <v>56282</v>
+        <v>56289</v>
       </c>
       <c r="C332" t="inlineStr">
         <is>
@@ -45658,21 +45658,21 @@
         </is>
       </c>
       <c r="E332" t="n">
-        <v>205992</v>
+        <v>100092</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
@@ -45696,10 +45696,10 @@
         </is>
       </c>
       <c r="Q332" t="n">
-        <v>586459</v>
+        <v>586452</v>
       </c>
       <c r="R332" t="n">
-        <v>6311154</v>
+        <v>6311152</v>
       </c>
       <c r="S332" t="n">
         <v>5</v>
@@ -45731,17 +45731,17 @@
       </c>
       <c r="Z332" t="inlineStr">
         <is>
+          <t>23:27</t>
+        </is>
+      </c>
+      <c r="AA332" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AB332" t="inlineStr">
+        <is>
           <t>23:28</t>
-        </is>
-      </c>
-      <c r="AA332" t="inlineStr">
-        <is>
-          <t>2024-06-26</t>
-        </is>
-      </c>
-      <c r="AB332" t="inlineStr">
-        <is>
-          <t>23:29</t>
         </is>
       </c>
       <c r="AC332" t="inlineStr">
@@ -45786,10 +45786,10 @@
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>122254606</v>
+        <v>122254412</v>
       </c>
       <c r="B333" t="n">
-        <v>56294</v>
+        <v>56289</v>
       </c>
       <c r="C333" t="inlineStr">
         <is>
@@ -45802,21 +45802,21 @@
         </is>
       </c>
       <c r="E333" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
@@ -45840,10 +45840,10 @@
         </is>
       </c>
       <c r="Q333" t="n">
-        <v>586415</v>
+        <v>586424</v>
       </c>
       <c r="R333" t="n">
-        <v>6311146</v>
+        <v>6311135</v>
       </c>
       <c r="S333" t="n">
         <v>5</v>
@@ -45875,7 +45875,7 @@
       </c>
       <c r="Z333" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AA333" t="inlineStr">
@@ -45885,7 +45885,7 @@
       </c>
       <c r="AB333" t="inlineStr">
         <is>
-          <t>23:03</t>
+          <t>22:38</t>
         </is>
       </c>
       <c r="AC333" t="inlineStr">
@@ -45930,10 +45930,10 @@
     </row>
     <row r="334">
       <c r="A334" t="n">
-        <v>122254656</v>
+        <v>122254342</v>
       </c>
       <c r="B334" t="n">
-        <v>56294</v>
+        <v>56289</v>
       </c>
       <c r="C334" t="inlineStr">
         <is>
@@ -45946,21 +45946,21 @@
         </is>
       </c>
       <c r="E334" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
@@ -45984,10 +45984,10 @@
         </is>
       </c>
       <c r="Q334" t="n">
-        <v>586483</v>
+        <v>586389</v>
       </c>
       <c r="R334" t="n">
-        <v>6311186</v>
+        <v>6311142</v>
       </c>
       <c r="S334" t="n">
         <v>5</v>
@@ -46019,7 +46019,7 @@
       </c>
       <c r="Z334" t="inlineStr">
         <is>
-          <t>22:31</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA334" t="inlineStr">
@@ -46029,7 +46029,7 @@
       </c>
       <c r="AB334" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AC334" t="inlineStr">
@@ -46074,10 +46074,10 @@
     </row>
     <row r="335">
       <c r="A335" t="n">
-        <v>122254611</v>
+        <v>122254370</v>
       </c>
       <c r="B335" t="n">
-        <v>56294</v>
+        <v>56289</v>
       </c>
       <c r="C335" t="inlineStr">
         <is>
@@ -46090,21 +46090,21 @@
         </is>
       </c>
       <c r="E335" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I335" t="inlineStr">
@@ -46128,10 +46128,10 @@
         </is>
       </c>
       <c r="Q335" t="n">
-        <v>586370</v>
+        <v>586309</v>
       </c>
       <c r="R335" t="n">
-        <v>6311139</v>
+        <v>6311119</v>
       </c>
       <c r="S335" t="n">
         <v>5</v>
@@ -46163,7 +46163,7 @@
       </c>
       <c r="Z335" t="inlineStr">
         <is>
-          <t>22:59</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AA335" t="inlineStr">
@@ -46173,7 +46173,7 @@
       </c>
       <c r="AB335" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AC335" t="inlineStr">
@@ -46218,10 +46218,10 @@
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>122254836</v>
+        <v>122254956</v>
       </c>
       <c r="B336" t="n">
-        <v>56292</v>
+        <v>56282</v>
       </c>
       <c r="C336" t="inlineStr">
         <is>
@@ -46234,21 +46234,21 @@
         </is>
       </c>
       <c r="E336" t="n">
-        <v>100111</v>
+        <v>205992</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
@@ -46272,10 +46272,10 @@
         </is>
       </c>
       <c r="Q336" t="n">
-        <v>586474</v>
+        <v>586441</v>
       </c>
       <c r="R336" t="n">
-        <v>6311176</v>
+        <v>6311152</v>
       </c>
       <c r="S336" t="n">
         <v>5</v>
@@ -46307,7 +46307,7 @@
       </c>
       <c r="Z336" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AA336" t="inlineStr">
@@ -46317,7 +46317,7 @@
       </c>
       <c r="AB336" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AC336" t="inlineStr">
@@ -46362,7 +46362,7 @@
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>122254513</v>
+        <v>122254511</v>
       </c>
       <c r="B337" t="n">
         <v>56275</v>
@@ -46416,10 +46416,10 @@
         </is>
       </c>
       <c r="Q337" t="n">
-        <v>586396</v>
+        <v>586374</v>
       </c>
       <c r="R337" t="n">
-        <v>6311146</v>
+        <v>6311139</v>
       </c>
       <c r="S337" t="n">
         <v>5</v>
@@ -46451,7 +46451,7 @@
       </c>
       <c r="Z337" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>22:46</t>
         </is>
       </c>
       <c r="AA337" t="inlineStr">
@@ -46461,7 +46461,7 @@
       </c>
       <c r="AB337" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>22:47</t>
         </is>
       </c>
       <c r="AC337" t="inlineStr">
@@ -46506,10 +46506,10 @@
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>122254957</v>
+        <v>122254635</v>
       </c>
       <c r="B338" t="n">
-        <v>56282</v>
+        <v>56294</v>
       </c>
       <c r="C338" t="inlineStr">
         <is>
@@ -46522,21 +46522,21 @@
         </is>
       </c>
       <c r="E338" t="n">
-        <v>205992</v>
+        <v>205995</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
@@ -46560,10 +46560,10 @@
         </is>
       </c>
       <c r="Q338" t="n">
-        <v>586444</v>
+        <v>586417</v>
       </c>
       <c r="R338" t="n">
-        <v>6311160</v>
+        <v>6311145</v>
       </c>
       <c r="S338" t="n">
         <v>5</v>
@@ -46595,7 +46595,7 @@
       </c>
       <c r="Z338" t="inlineStr">
         <is>
-          <t>23:24</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AA338" t="inlineStr">
@@ -46605,7 +46605,7 @@
       </c>
       <c r="AB338" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AC338" t="inlineStr">
@@ -46650,10 +46650,10 @@
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>122254499</v>
+        <v>122254634</v>
       </c>
       <c r="B339" t="n">
-        <v>56275</v>
+        <v>56294</v>
       </c>
       <c r="C339" t="inlineStr">
         <is>
@@ -46662,25 +46662,25 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E339" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I339" t="inlineStr">
@@ -46704,10 +46704,10 @@
         </is>
       </c>
       <c r="Q339" t="n">
-        <v>586392</v>
+        <v>586415</v>
       </c>
       <c r="R339" t="n">
-        <v>6311147</v>
+        <v>6311148</v>
       </c>
       <c r="S339" t="n">
         <v>5</v>
@@ -46739,7 +46739,7 @@
       </c>
       <c r="Z339" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AA339" t="inlineStr">
@@ -46749,7 +46749,7 @@
       </c>
       <c r="AB339" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AC339" t="inlineStr">
@@ -46794,10 +46794,10 @@
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>122254341</v>
+        <v>122254626</v>
       </c>
       <c r="B340" t="n">
-        <v>56289</v>
+        <v>56294</v>
       </c>
       <c r="C340" t="inlineStr">
         <is>
@@ -46810,21 +46810,21 @@
         </is>
       </c>
       <c r="E340" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
@@ -46848,10 +46848,10 @@
         </is>
       </c>
       <c r="Q340" t="n">
-        <v>586415</v>
+        <v>586313</v>
       </c>
       <c r="R340" t="n">
-        <v>6311146</v>
+        <v>6311124</v>
       </c>
       <c r="S340" t="n">
         <v>5</v>
@@ -46883,7 +46883,7 @@
       </c>
       <c r="Z340" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AA340" t="inlineStr">
@@ -46893,7 +46893,7 @@
       </c>
       <c r="AB340" t="inlineStr">
         <is>
-          <t>23:03</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AC340" t="inlineStr">
@@ -46938,7 +46938,7 @@
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>122254313</v>
+        <v>122254341</v>
       </c>
       <c r="B341" t="n">
         <v>56289</v>
@@ -46992,10 +46992,10 @@
         </is>
       </c>
       <c r="Q341" t="n">
-        <v>586449</v>
+        <v>586415</v>
       </c>
       <c r="R341" t="n">
-        <v>6311155</v>
+        <v>6311146</v>
       </c>
       <c r="S341" t="n">
         <v>5</v>
@@ -47027,7 +47027,7 @@
       </c>
       <c r="Z341" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AA341" t="inlineStr">
@@ -47037,7 +47037,7 @@
       </c>
       <c r="AB341" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>23:03</t>
         </is>
       </c>
       <c r="AC341" t="inlineStr">
@@ -47082,7 +47082,7 @@
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>122254373</v>
+        <v>122254350</v>
       </c>
       <c r="B342" t="n">
         <v>56289</v>
@@ -47136,10 +47136,10 @@
         </is>
       </c>
       <c r="Q342" t="n">
-        <v>586307</v>
+        <v>586330</v>
       </c>
       <c r="R342" t="n">
-        <v>6311133</v>
+        <v>6311120</v>
       </c>
       <c r="S342" t="n">
         <v>5</v>
@@ -47171,7 +47171,7 @@
       </c>
       <c r="Z342" t="inlineStr">
         <is>
-          <t>22:49</t>
+          <t>22:57</t>
         </is>
       </c>
       <c r="AA342" t="inlineStr">
@@ -47181,7 +47181,7 @@
       </c>
       <c r="AB342" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>22:58</t>
         </is>
       </c>
       <c r="AC342" t="inlineStr">
@@ -47226,10 +47226,10 @@
     </row>
     <row r="343">
       <c r="A343" t="n">
-        <v>122254845</v>
+        <v>122254586</v>
       </c>
       <c r="B343" t="n">
-        <v>56292</v>
+        <v>56294</v>
       </c>
       <c r="C343" t="inlineStr">
         <is>
@@ -47242,21 +47242,21 @@
         </is>
       </c>
       <c r="E343" t="n">
-        <v>100111</v>
+        <v>205995</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
@@ -47280,10 +47280,10 @@
         </is>
       </c>
       <c r="Q343" t="n">
-        <v>586370</v>
+        <v>586446</v>
       </c>
       <c r="R343" t="n">
-        <v>6311139</v>
+        <v>6311158</v>
       </c>
       <c r="S343" t="n">
         <v>5</v>
@@ -47315,7 +47315,7 @@
       </c>
       <c r="Z343" t="inlineStr">
         <is>
-          <t>22:59</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AA343" t="inlineStr">
@@ -47325,7 +47325,7 @@
       </c>
       <c r="AB343" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AC343" t="inlineStr">
@@ -47370,10 +47370,10 @@
     </row>
     <row r="344">
       <c r="A344" t="n">
-        <v>122254856</v>
+        <v>122254616</v>
       </c>
       <c r="B344" t="n">
-        <v>56292</v>
+        <v>56294</v>
       </c>
       <c r="C344" t="inlineStr">
         <is>
@@ -47386,21 +47386,21 @@
         </is>
       </c>
       <c r="E344" t="n">
-        <v>100111</v>
+        <v>205995</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
@@ -47514,10 +47514,10 @@
     </row>
     <row r="345">
       <c r="A345" t="n">
-        <v>122254416</v>
+        <v>122254964</v>
       </c>
       <c r="B345" t="n">
-        <v>56289</v>
+        <v>56282</v>
       </c>
       <c r="C345" t="inlineStr">
         <is>
@@ -47530,21 +47530,21 @@
         </is>
       </c>
       <c r="E345" t="n">
-        <v>100092</v>
+        <v>205992</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
@@ -47568,10 +47568,10 @@
         </is>
       </c>
       <c r="Q345" t="n">
-        <v>586410</v>
+        <v>586430</v>
       </c>
       <c r="R345" t="n">
-        <v>6311140</v>
+        <v>6311142</v>
       </c>
       <c r="S345" t="n">
         <v>5</v>
@@ -47658,10 +47658,10 @@
     </row>
     <row r="346">
       <c r="A346" t="n">
-        <v>122254396</v>
+        <v>122254643</v>
       </c>
       <c r="B346" t="n">
-        <v>56289</v>
+        <v>56294</v>
       </c>
       <c r="C346" t="inlineStr">
         <is>
@@ -47674,21 +47674,21 @@
         </is>
       </c>
       <c r="E346" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
@@ -47712,10 +47712,10 @@
         </is>
       </c>
       <c r="Q346" t="n">
-        <v>586408</v>
+        <v>586424</v>
       </c>
       <c r="R346" t="n">
-        <v>6311124</v>
+        <v>6311135</v>
       </c>
       <c r="S346" t="n">
         <v>5</v>
@@ -47747,7 +47747,7 @@
       </c>
       <c r="Z346" t="inlineStr">
         <is>
-          <t>22:43</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AA346" t="inlineStr">
@@ -47757,7 +47757,7 @@
       </c>
       <c r="AB346" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>22:38</t>
         </is>
       </c>
       <c r="AC346" t="inlineStr">
@@ -47802,7 +47802,7 @@
     </row>
     <row r="347">
       <c r="A347" t="n">
-        <v>122254365</v>
+        <v>122254316</v>
       </c>
       <c r="B347" t="n">
         <v>56289</v>
@@ -47856,10 +47856,10 @@
         </is>
       </c>
       <c r="Q347" t="n">
-        <v>586276</v>
+        <v>586423</v>
       </c>
       <c r="R347" t="n">
-        <v>6311100</v>
+        <v>6311166</v>
       </c>
       <c r="S347" t="n">
         <v>5</v>
@@ -47891,7 +47891,7 @@
       </c>
       <c r="Z347" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>23:23</t>
         </is>
       </c>
       <c r="AA347" t="inlineStr">
@@ -47901,7 +47901,7 @@
       </c>
       <c r="AB347" t="inlineStr">
         <is>
-          <t>22:52</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="AC347" t="inlineStr">
@@ -47946,7 +47946,7 @@
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>122254315</v>
+        <v>122254308</v>
       </c>
       <c r="B348" t="n">
         <v>56289</v>
@@ -48000,10 +48000,10 @@
         </is>
       </c>
       <c r="Q348" t="n">
-        <v>586441</v>
+        <v>586455</v>
       </c>
       <c r="R348" t="n">
-        <v>6311155</v>
+        <v>6311159</v>
       </c>
       <c r="S348" t="n">
         <v>5</v>
@@ -48035,7 +48035,7 @@
       </c>
       <c r="Z348" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AA348" t="inlineStr">
@@ -48045,7 +48045,7 @@
       </c>
       <c r="AB348" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AC348" t="inlineStr">
@@ -48090,7 +48090,7 @@
     </row>
     <row r="349">
       <c r="A349" t="n">
-        <v>122254312</v>
+        <v>122254390</v>
       </c>
       <c r="B349" t="n">
         <v>56289</v>
@@ -48144,10 +48144,10 @@
         </is>
       </c>
       <c r="Q349" t="n">
-        <v>586452</v>
+        <v>586374</v>
       </c>
       <c r="R349" t="n">
-        <v>6311152</v>
+        <v>6311139</v>
       </c>
       <c r="S349" t="n">
         <v>5</v>
@@ -48179,7 +48179,7 @@
       </c>
       <c r="Z349" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>22:46</t>
         </is>
       </c>
       <c r="AA349" t="inlineStr">
@@ -48189,7 +48189,7 @@
       </c>
       <c r="AB349" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>22:47</t>
         </is>
       </c>
       <c r="AC349" t="inlineStr">
@@ -48234,10 +48234,10 @@
     </row>
     <row r="350">
       <c r="A350" t="n">
-        <v>122254648</v>
+        <v>122254417</v>
       </c>
       <c r="B350" t="n">
-        <v>56294</v>
+        <v>56289</v>
       </c>
       <c r="C350" t="inlineStr">
         <is>
@@ -48250,21 +48250,21 @@
         </is>
       </c>
       <c r="E350" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I350" t="inlineStr">
@@ -48288,10 +48288,10 @@
         </is>
       </c>
       <c r="Q350" t="n">
-        <v>586418</v>
+        <v>586426</v>
       </c>
       <c r="R350" t="n">
-        <v>6311107</v>
+        <v>6311145</v>
       </c>
       <c r="S350" t="n">
         <v>5</v>
@@ -48323,7 +48323,7 @@
       </c>
       <c r="Z350" t="inlineStr">
         <is>
-          <t>22:36</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="AA350" t="inlineStr">
@@ -48333,7 +48333,7 @@
       </c>
       <c r="AB350" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>22:34</t>
         </is>
       </c>
       <c r="AC350" t="inlineStr">
@@ -48378,10 +48378,10 @@
     </row>
     <row r="351">
       <c r="A351" t="n">
-        <v>122254963</v>
+        <v>122254837</v>
       </c>
       <c r="B351" t="n">
-        <v>56282</v>
+        <v>56292</v>
       </c>
       <c r="C351" t="inlineStr">
         <is>
@@ -48394,21 +48394,21 @@
         </is>
       </c>
       <c r="E351" t="n">
-        <v>205992</v>
+        <v>100111</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I351" t="inlineStr">
@@ -48432,10 +48432,10 @@
         </is>
       </c>
       <c r="Q351" t="n">
-        <v>586374</v>
+        <v>586448</v>
       </c>
       <c r="R351" t="n">
-        <v>6311140</v>
+        <v>6311154</v>
       </c>
       <c r="S351" t="n">
         <v>5</v>
@@ -48467,7 +48467,7 @@
       </c>
       <c r="Z351" t="inlineStr">
         <is>
-          <t>22:46</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA351" t="inlineStr">
@@ -48477,7 +48477,7 @@
       </c>
       <c r="AB351" t="inlineStr">
         <is>
-          <t>22:47</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC351" t="inlineStr">
@@ -48522,10 +48522,10 @@
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>122254653</v>
+        <v>122254391</v>
       </c>
       <c r="B352" t="n">
-        <v>56294</v>
+        <v>56289</v>
       </c>
       <c r="C352" t="inlineStr">
         <is>
@@ -48538,21 +48538,21 @@
         </is>
       </c>
       <c r="E352" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I352" t="inlineStr">
@@ -48576,10 +48576,10 @@
         </is>
       </c>
       <c r="Q352" t="n">
-        <v>586430</v>
+        <v>586379</v>
       </c>
       <c r="R352" t="n">
-        <v>6311142</v>
+        <v>6311136</v>
       </c>
       <c r="S352" t="n">
         <v>5</v>
@@ -48611,7 +48611,7 @@
       </c>
       <c r="Z352" t="inlineStr">
         <is>
-          <t>22:33</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AA352" t="inlineStr">
@@ -48621,7 +48621,7 @@
       </c>
       <c r="AB352" t="inlineStr">
         <is>
-          <t>22:34</t>
+          <t>22:46</t>
         </is>
       </c>
       <c r="AC352" t="inlineStr">
@@ -48666,7 +48666,7 @@
     </row>
     <row r="353">
       <c r="A353" t="n">
-        <v>122254609</v>
+        <v>122254617</v>
       </c>
       <c r="B353" t="n">
         <v>56294</v>
@@ -48720,10 +48720,10 @@
         </is>
       </c>
       <c r="Q353" t="n">
-        <v>586392</v>
+        <v>586317</v>
       </c>
       <c r="R353" t="n">
-        <v>6311147</v>
+        <v>6311115</v>
       </c>
       <c r="S353" t="n">
         <v>5</v>
@@ -48755,7 +48755,7 @@
       </c>
       <c r="Z353" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>22:57</t>
         </is>
       </c>
       <c r="AA353" t="inlineStr">
@@ -48765,7 +48765,7 @@
       </c>
       <c r="AB353" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>22:58</t>
         </is>
       </c>
       <c r="AC353" t="inlineStr">
@@ -48810,7 +48810,7 @@
     </row>
     <row r="354">
       <c r="A354" t="n">
-        <v>122254659</v>
+        <v>122254606</v>
       </c>
       <c r="B354" t="n">
         <v>56294</v>
@@ -48864,10 +48864,10 @@
         </is>
       </c>
       <c r="Q354" t="n">
-        <v>586489</v>
+        <v>586415</v>
       </c>
       <c r="R354" t="n">
-        <v>6311181</v>
+        <v>6311146</v>
       </c>
       <c r="S354" t="n">
         <v>5</v>
@@ -48899,7 +48899,7 @@
       </c>
       <c r="Z354" t="inlineStr">
         <is>
-          <t>22:31</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AA354" t="inlineStr">
@@ -48909,7 +48909,7 @@
       </c>
       <c r="AB354" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>23:03</t>
         </is>
       </c>
       <c r="AC354" t="inlineStr">
@@ -48954,10 +48954,10 @@
     </row>
     <row r="355">
       <c r="A355" t="n">
-        <v>122254835</v>
+        <v>122254966</v>
       </c>
       <c r="B355" t="n">
-        <v>56292</v>
+        <v>56282</v>
       </c>
       <c r="C355" t="inlineStr">
         <is>
@@ -48970,21 +48970,21 @@
         </is>
       </c>
       <c r="E355" t="n">
-        <v>100111</v>
+        <v>205992</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I355" t="inlineStr">
@@ -49008,10 +49008,10 @@
         </is>
       </c>
       <c r="Q355" t="n">
-        <v>586473</v>
+        <v>586467</v>
       </c>
       <c r="R355" t="n">
-        <v>6311192</v>
+        <v>6311178</v>
       </c>
       <c r="S355" t="n">
         <v>5</v>
@@ -49043,7 +49043,7 @@
       </c>
       <c r="Z355" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AA355" t="inlineStr">
@@ -49053,7 +49053,7 @@
       </c>
       <c r="AB355" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="AC355" t="inlineStr">
@@ -49098,10 +49098,10 @@
     </row>
     <row r="356">
       <c r="A356" t="n">
-        <v>122254862</v>
+        <v>122254636</v>
       </c>
       <c r="B356" t="n">
-        <v>56292</v>
+        <v>56294</v>
       </c>
       <c r="C356" t="inlineStr">
         <is>
@@ -49114,21 +49114,21 @@
         </is>
       </c>
       <c r="E356" t="n">
-        <v>100111</v>
+        <v>205995</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I356" t="inlineStr">
@@ -49152,10 +49152,10 @@
         </is>
       </c>
       <c r="Q356" t="n">
-        <v>586288</v>
+        <v>586418</v>
       </c>
       <c r="R356" t="n">
-        <v>6311100</v>
+        <v>6311145</v>
       </c>
       <c r="S356" t="n">
         <v>5</v>
@@ -49187,7 +49187,7 @@
       </c>
       <c r="Z356" t="inlineStr">
         <is>
-          <t>22:55</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AA356" t="inlineStr">
@@ -49197,7 +49197,7 @@
       </c>
       <c r="AB356" t="inlineStr">
         <is>
-          <t>22:56</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AC356" t="inlineStr">
@@ -49242,10 +49242,10 @@
     </row>
     <row r="357">
       <c r="A357" t="n">
-        <v>122254317</v>
+        <v>122254584</v>
       </c>
       <c r="B357" t="n">
-        <v>56289</v>
+        <v>56294</v>
       </c>
       <c r="C357" t="inlineStr">
         <is>
@@ -49258,21 +49258,21 @@
         </is>
       </c>
       <c r="E357" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I357" t="inlineStr">
@@ -49296,10 +49296,10 @@
         </is>
       </c>
       <c r="Q357" t="n">
-        <v>586438</v>
+        <v>586473</v>
       </c>
       <c r="R357" t="n">
-        <v>6311222</v>
+        <v>6311192</v>
       </c>
       <c r="S357" t="n">
         <v>5</v>
@@ -49331,7 +49331,7 @@
       </c>
       <c r="Z357" t="inlineStr">
         <is>
-          <t>23:22</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AA357" t="inlineStr">
@@ -49341,7 +49341,7 @@
       </c>
       <c r="AB357" t="inlineStr">
         <is>
-          <t>23:23</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AC357" t="inlineStr">
@@ -49386,10 +49386,10 @@
     </row>
     <row r="358">
       <c r="A358" t="n">
-        <v>122254412</v>
+        <v>122254498</v>
       </c>
       <c r="B358" t="n">
-        <v>56289</v>
+        <v>56275</v>
       </c>
       <c r="C358" t="inlineStr">
         <is>
@@ -49398,25 +49398,25 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E358" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H358" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I358" t="inlineStr">
@@ -49440,10 +49440,10 @@
         </is>
       </c>
       <c r="Q358" t="n">
-        <v>586424</v>
+        <v>586393</v>
       </c>
       <c r="R358" t="n">
-        <v>6311135</v>
+        <v>6311147</v>
       </c>
       <c r="S358" t="n">
         <v>5</v>
@@ -49475,7 +49475,7 @@
       </c>
       <c r="Z358" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AA358" t="inlineStr">
@@ -49485,7 +49485,7 @@
       </c>
       <c r="AB358" t="inlineStr">
         <is>
-          <t>22:38</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AC358" t="inlineStr">
@@ -49530,7 +49530,7 @@
     </row>
     <row r="359">
       <c r="A359" t="n">
-        <v>122254415</v>
+        <v>122254307</v>
       </c>
       <c r="B359" t="n">
         <v>56289</v>
@@ -49584,10 +49584,10 @@
         </is>
       </c>
       <c r="Q359" t="n">
-        <v>586425</v>
+        <v>586477</v>
       </c>
       <c r="R359" t="n">
-        <v>6311135</v>
+        <v>6311186</v>
       </c>
       <c r="S359" t="n">
         <v>5</v>
@@ -49619,7 +49619,7 @@
       </c>
       <c r="Z359" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AA359" t="inlineStr">
@@ -49629,7 +49629,7 @@
       </c>
       <c r="AB359" t="inlineStr">
         <is>
-          <t>22:38</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AC359" t="inlineStr">
@@ -49674,7 +49674,7 @@
     </row>
     <row r="360">
       <c r="A360" t="n">
-        <v>122254352</v>
+        <v>122254315</v>
       </c>
       <c r="B360" t="n">
         <v>56289</v>
@@ -49728,10 +49728,10 @@
         </is>
       </c>
       <c r="Q360" t="n">
-        <v>586288</v>
+        <v>586441</v>
       </c>
       <c r="R360" t="n">
-        <v>6311100</v>
+        <v>6311155</v>
       </c>
       <c r="S360" t="n">
         <v>5</v>
@@ -49763,7 +49763,7 @@
       </c>
       <c r="Z360" t="inlineStr">
         <is>
-          <t>22:55</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AA360" t="inlineStr">
@@ -49773,7 +49773,7 @@
       </c>
       <c r="AB360" t="inlineStr">
         <is>
-          <t>22:56</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AC360" t="inlineStr">
@@ -49818,10 +49818,10 @@
     </row>
     <row r="361">
       <c r="A361" t="n">
-        <v>122254308</v>
+        <v>122254844</v>
       </c>
       <c r="B361" t="n">
-        <v>56289</v>
+        <v>56292</v>
       </c>
       <c r="C361" t="inlineStr">
         <is>
@@ -49834,21 +49834,21 @@
         </is>
       </c>
       <c r="E361" t="n">
-        <v>100092</v>
+        <v>100111</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I361" t="inlineStr">
@@ -49872,10 +49872,10 @@
         </is>
       </c>
       <c r="Q361" t="n">
-        <v>586455</v>
+        <v>586387</v>
       </c>
       <c r="R361" t="n">
-        <v>6311159</v>
+        <v>6311141</v>
       </c>
       <c r="S361" t="n">
         <v>5</v>
@@ -49907,7 +49907,7 @@
       </c>
       <c r="Z361" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA361" t="inlineStr">
@@ -49917,7 +49917,7 @@
       </c>
       <c r="AB361" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AC361" t="inlineStr">
@@ -49962,7 +49962,7 @@
     </row>
     <row r="362">
       <c r="A362" t="n">
-        <v>122254417</v>
+        <v>122254371</v>
       </c>
       <c r="B362" t="n">
         <v>56289</v>
@@ -50016,10 +50016,10 @@
         </is>
       </c>
       <c r="Q362" t="n">
-        <v>586426</v>
+        <v>586308</v>
       </c>
       <c r="R362" t="n">
-        <v>6311145</v>
+        <v>6311132</v>
       </c>
       <c r="S362" t="n">
         <v>5</v>
@@ -50051,7 +50051,7 @@
       </c>
       <c r="Z362" t="inlineStr">
         <is>
-          <t>22:33</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AA362" t="inlineStr">
@@ -50061,7 +50061,7 @@
       </c>
       <c r="AB362" t="inlineStr">
         <is>
-          <t>22:34</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AC362" t="inlineStr">
@@ -50106,7 +50106,7 @@
     </row>
     <row r="363">
       <c r="A363" t="n">
-        <v>122254610</v>
+        <v>122254607</v>
       </c>
       <c r="B363" t="n">
         <v>56294</v>
@@ -50160,10 +50160,10 @@
         </is>
       </c>
       <c r="Q363" t="n">
-        <v>586389</v>
+        <v>586415</v>
       </c>
       <c r="R363" t="n">
-        <v>6311141</v>
+        <v>6311149</v>
       </c>
       <c r="S363" t="n">
         <v>5</v>
@@ -50195,7 +50195,7 @@
       </c>
       <c r="Z363" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AA363" t="inlineStr">
@@ -50205,7 +50205,7 @@
       </c>
       <c r="AB363" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>23:03</t>
         </is>
       </c>
       <c r="AC363" t="inlineStr">
@@ -50250,7 +50250,7 @@
     </row>
     <row r="364">
       <c r="A364" t="n">
-        <v>122254633</v>
+        <v>122254652</v>
       </c>
       <c r="B364" t="n">
         <v>56294</v>
@@ -50304,10 +50304,10 @@
         </is>
       </c>
       <c r="Q364" t="n">
-        <v>586396</v>
+        <v>586432</v>
       </c>
       <c r="R364" t="n">
-        <v>6311146</v>
+        <v>6311118</v>
       </c>
       <c r="S364" t="n">
         <v>5</v>
@@ -50339,7 +50339,7 @@
       </c>
       <c r="Z364" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>22:34</t>
         </is>
       </c>
       <c r="AA364" t="inlineStr">
@@ -50349,7 +50349,7 @@
       </c>
       <c r="AB364" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="AC364" t="inlineStr">
@@ -50394,10 +50394,10 @@
     </row>
     <row r="365">
       <c r="A365" t="n">
-        <v>122254511</v>
+        <v>122254959</v>
       </c>
       <c r="B365" t="n">
-        <v>56275</v>
+        <v>56282</v>
       </c>
       <c r="C365" t="inlineStr">
         <is>
@@ -50406,25 +50406,25 @@
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E365" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I365" t="inlineStr">
@@ -50448,7 +50448,7 @@
         </is>
       </c>
       <c r="Q365" t="n">
-        <v>586374</v>
+        <v>586370</v>
       </c>
       <c r="R365" t="n">
         <v>6311139</v>
@@ -50483,7 +50483,7 @@
       </c>
       <c r="Z365" t="inlineStr">
         <is>
-          <t>22:46</t>
+          <t>22:59</t>
         </is>
       </c>
       <c r="AA365" t="inlineStr">
@@ -50493,7 +50493,7 @@
       </c>
       <c r="AB365" t="inlineStr">
         <is>
-          <t>22:47</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AC365" t="inlineStr">
@@ -50538,10 +50538,10 @@
     </row>
     <row r="366">
       <c r="A366" t="n">
-        <v>122254857</v>
+        <v>122254650</v>
       </c>
       <c r="B366" t="n">
-        <v>56292</v>
+        <v>56294</v>
       </c>
       <c r="C366" t="inlineStr">
         <is>
@@ -50554,21 +50554,21 @@
         </is>
       </c>
       <c r="E366" t="n">
-        <v>100111</v>
+        <v>205995</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I366" t="inlineStr">
@@ -50592,10 +50592,10 @@
         </is>
       </c>
       <c r="Q366" t="n">
-        <v>586317</v>
+        <v>586422</v>
       </c>
       <c r="R366" t="n">
-        <v>6311115</v>
+        <v>6311105</v>
       </c>
       <c r="S366" t="n">
         <v>5</v>
@@ -50627,7 +50627,7 @@
       </c>
       <c r="Z366" t="inlineStr">
         <is>
-          <t>22:57</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="AA366" t="inlineStr">
@@ -50637,7 +50637,7 @@
       </c>
       <c r="AB366" t="inlineStr">
         <is>
-          <t>22:58</t>
+          <t>22:36</t>
         </is>
       </c>
       <c r="AC366" t="inlineStr">
@@ -50682,7 +50682,7 @@
     </row>
     <row r="367">
       <c r="A367" t="n">
-        <v>122254649</v>
+        <v>122254585</v>
       </c>
       <c r="B367" t="n">
         <v>56294</v>
@@ -50736,10 +50736,10 @@
         </is>
       </c>
       <c r="Q367" t="n">
-        <v>586422</v>
+        <v>586455</v>
       </c>
       <c r="R367" t="n">
-        <v>6311100</v>
+        <v>6311156</v>
       </c>
       <c r="S367" t="n">
         <v>5</v>
@@ -50771,7 +50771,7 @@
       </c>
       <c r="Z367" t="inlineStr">
         <is>
-          <t>22:35</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AA367" t="inlineStr">
@@ -50781,7 +50781,7 @@
       </c>
       <c r="AB367" t="inlineStr">
         <is>
-          <t>22:36</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AC367" t="inlineStr">
@@ -50826,10 +50826,10 @@
     </row>
     <row r="368">
       <c r="A368" t="n">
-        <v>122254475</v>
+        <v>122254588</v>
       </c>
       <c r="B368" t="n">
-        <v>56275</v>
+        <v>56294</v>
       </c>
       <c r="C368" t="inlineStr">
         <is>
@@ -50838,25 +50838,25 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E368" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H368" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I368" t="inlineStr">
@@ -50880,10 +50880,10 @@
         </is>
       </c>
       <c r="Q368" t="n">
-        <v>586420</v>
+        <v>586415</v>
       </c>
       <c r="R368" t="n">
-        <v>6311166</v>
+        <v>6311196</v>
       </c>
       <c r="S368" t="n">
         <v>5</v>
@@ -50915,17 +50915,17 @@
       </c>
       <c r="Z368" t="inlineStr">
         <is>
+          <t>23:22</t>
+        </is>
+      </c>
+      <c r="AA368" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AB368" t="inlineStr">
+        <is>
           <t>23:23</t>
-        </is>
-      </c>
-      <c r="AA368" t="inlineStr">
-        <is>
-          <t>2024-06-26</t>
-        </is>
-      </c>
-      <c r="AB368" t="inlineStr">
-        <is>
-          <t>23:24</t>
         </is>
       </c>
       <c r="AC368" t="inlineStr">
@@ -50970,10 +50970,10 @@
     </row>
     <row r="369">
       <c r="A369" t="n">
-        <v>122254474</v>
+        <v>122254421</v>
       </c>
       <c r="B369" t="n">
-        <v>56275</v>
+        <v>56289</v>
       </c>
       <c r="C369" t="inlineStr">
         <is>
@@ -50982,25 +50982,25 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E369" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I369" t="inlineStr">
@@ -51024,10 +51024,10 @@
         </is>
       </c>
       <c r="Q369" t="n">
-        <v>586443</v>
+        <v>586468</v>
       </c>
       <c r="R369" t="n">
-        <v>6311164</v>
+        <v>6311181</v>
       </c>
       <c r="S369" t="n">
         <v>5</v>
@@ -51059,7 +51059,7 @@
       </c>
       <c r="Z369" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AA369" t="inlineStr">
@@ -51069,7 +51069,7 @@
       </c>
       <c r="AB369" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="AC369" t="inlineStr">
@@ -51114,7 +51114,7 @@
     </row>
     <row r="370">
       <c r="A370" t="n">
-        <v>122254650</v>
+        <v>122254610</v>
       </c>
       <c r="B370" t="n">
         <v>56294</v>
@@ -51168,10 +51168,10 @@
         </is>
       </c>
       <c r="Q370" t="n">
-        <v>586422</v>
+        <v>586389</v>
       </c>
       <c r="R370" t="n">
-        <v>6311105</v>
+        <v>6311141</v>
       </c>
       <c r="S370" t="n">
         <v>5</v>
@@ -51203,7 +51203,7 @@
       </c>
       <c r="Z370" t="inlineStr">
         <is>
-          <t>22:35</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA370" t="inlineStr">
@@ -51213,7 +51213,7 @@
       </c>
       <c r="AB370" t="inlineStr">
         <is>
-          <t>22:36</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AC370" t="inlineStr">
@@ -51258,7 +51258,7 @@
     </row>
     <row r="371">
       <c r="A371" t="n">
-        <v>122254644</v>
+        <v>122254611</v>
       </c>
       <c r="B371" t="n">
         <v>56294</v>
@@ -51312,10 +51312,10 @@
         </is>
       </c>
       <c r="Q371" t="n">
-        <v>586429</v>
+        <v>586370</v>
       </c>
       <c r="R371" t="n">
-        <v>6311115</v>
+        <v>6311139</v>
       </c>
       <c r="S371" t="n">
         <v>5</v>
@@ -51347,7 +51347,7 @@
       </c>
       <c r="Z371" t="inlineStr">
         <is>
-          <t>22:36</t>
+          <t>22:59</t>
         </is>
       </c>
       <c r="AA371" t="inlineStr">
@@ -51357,7 +51357,7 @@
       </c>
       <c r="AB371" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AC371" t="inlineStr">
@@ -51402,7 +51402,7 @@
     </row>
     <row r="372">
       <c r="A372" t="n">
-        <v>122254652</v>
+        <v>122254625</v>
       </c>
       <c r="B372" t="n">
         <v>56294</v>
@@ -51456,10 +51456,10 @@
         </is>
       </c>
       <c r="Q372" t="n">
-        <v>586432</v>
+        <v>586309</v>
       </c>
       <c r="R372" t="n">
-        <v>6311118</v>
+        <v>6311119</v>
       </c>
       <c r="S372" t="n">
         <v>5</v>
@@ -51491,7 +51491,7 @@
       </c>
       <c r="Z372" t="inlineStr">
         <is>
-          <t>22:34</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AA372" t="inlineStr">
@@ -51501,7 +51501,7 @@
       </c>
       <c r="AB372" t="inlineStr">
         <is>
-          <t>22:35</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AC372" t="inlineStr">
@@ -51546,10 +51546,10 @@
     </row>
     <row r="373">
       <c r="A373" t="n">
-        <v>122254586</v>
+        <v>122254836</v>
       </c>
       <c r="B373" t="n">
-        <v>56294</v>
+        <v>56292</v>
       </c>
       <c r="C373" t="inlineStr">
         <is>
@@ -51562,21 +51562,21 @@
         </is>
       </c>
       <c r="E373" t="n">
-        <v>205995</v>
+        <v>100111</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H373" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I373" t="inlineStr">
@@ -51600,10 +51600,10 @@
         </is>
       </c>
       <c r="Q373" t="n">
-        <v>586446</v>
+        <v>586474</v>
       </c>
       <c r="R373" t="n">
-        <v>6311158</v>
+        <v>6311176</v>
       </c>
       <c r="S373" t="n">
         <v>5</v>
@@ -51635,7 +51635,7 @@
       </c>
       <c r="Z373" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AA373" t="inlineStr">
@@ -51645,7 +51645,7 @@
       </c>
       <c r="AB373" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AC373" t="inlineStr">
@@ -51690,10 +51690,10 @@
     </row>
     <row r="374">
       <c r="A374" t="n">
-        <v>122254956</v>
+        <v>122254608</v>
       </c>
       <c r="B374" t="n">
-        <v>56282</v>
+        <v>56294</v>
       </c>
       <c r="C374" t="inlineStr">
         <is>
@@ -51706,21 +51706,21 @@
         </is>
       </c>
       <c r="E374" t="n">
-        <v>205992</v>
+        <v>205995</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I374" t="inlineStr">
@@ -51744,10 +51744,10 @@
         </is>
       </c>
       <c r="Q374" t="n">
-        <v>586441</v>
+        <v>586393</v>
       </c>
       <c r="R374" t="n">
-        <v>6311152</v>
+        <v>6311147</v>
       </c>
       <c r="S374" t="n">
         <v>5</v>
@@ -51779,7 +51779,7 @@
       </c>
       <c r="Z374" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AA374" t="inlineStr">
@@ -51789,7 +51789,7 @@
       </c>
       <c r="AB374" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AC374" t="inlineStr">
@@ -51834,10 +51834,10 @@
     </row>
     <row r="375">
       <c r="A375" t="n">
-        <v>122254877</v>
+        <v>122254503</v>
       </c>
       <c r="B375" t="n">
-        <v>56292</v>
+        <v>56275</v>
       </c>
       <c r="C375" t="inlineStr">
         <is>
@@ -51846,25 +51846,25 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E375" t="n">
-        <v>100111</v>
+        <v>205998</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I375" t="inlineStr">
@@ -51888,10 +51888,10 @@
         </is>
       </c>
       <c r="Q375" t="n">
-        <v>586276</v>
+        <v>586313</v>
       </c>
       <c r="R375" t="n">
-        <v>6311100</v>
+        <v>6311124</v>
       </c>
       <c r="S375" t="n">
         <v>5</v>
@@ -51923,17 +51923,17 @@
       </c>
       <c r="Z375" t="inlineStr">
         <is>
+          <t>22:50</t>
+        </is>
+      </c>
+      <c r="AA375" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AB375" t="inlineStr">
+        <is>
           <t>22:51</t>
-        </is>
-      </c>
-      <c r="AA375" t="inlineStr">
-        <is>
-          <t>2024-06-26</t>
-        </is>
-      </c>
-      <c r="AB375" t="inlineStr">
-        <is>
-          <t>22:52</t>
         </is>
       </c>
       <c r="AC375" t="inlineStr">
@@ -51978,7 +51978,7 @@
     </row>
     <row r="376">
       <c r="A376" t="n">
-        <v>122254584</v>
+        <v>122254651</v>
       </c>
       <c r="B376" t="n">
         <v>56294</v>
@@ -52032,10 +52032,10 @@
         </is>
       </c>
       <c r="Q376" t="n">
-        <v>586473</v>
+        <v>586425</v>
       </c>
       <c r="R376" t="n">
-        <v>6311192</v>
+        <v>6311113</v>
       </c>
       <c r="S376" t="n">
         <v>5</v>
@@ -52067,7 +52067,7 @@
       </c>
       <c r="Z376" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="AA376" t="inlineStr">
@@ -52077,7 +52077,7 @@
       </c>
       <c r="AB376" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>22:36</t>
         </is>
       </c>
       <c r="AC376" t="inlineStr">
@@ -52122,7 +52122,7 @@
     </row>
     <row r="377">
       <c r="A377" t="n">
-        <v>122254646</v>
+        <v>122254632</v>
       </c>
       <c r="B377" t="n">
         <v>56294</v>
@@ -52176,10 +52176,10 @@
         </is>
       </c>
       <c r="Q377" t="n">
-        <v>586422</v>
+        <v>586374</v>
       </c>
       <c r="R377" t="n">
-        <v>6311111</v>
+        <v>6311140</v>
       </c>
       <c r="S377" t="n">
         <v>5</v>
@@ -52211,7 +52211,7 @@
       </c>
       <c r="Z377" t="inlineStr">
         <is>
-          <t>22:36</t>
+          <t>22:46</t>
         </is>
       </c>
       <c r="AA377" t="inlineStr">
@@ -52221,7 +52221,7 @@
       </c>
       <c r="AB377" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>22:47</t>
         </is>
       </c>
       <c r="AC377" t="inlineStr">
@@ -52266,10 +52266,10 @@
     </row>
     <row r="378">
       <c r="A378" t="n">
-        <v>122254616</v>
+        <v>122254415</v>
       </c>
       <c r="B378" t="n">
-        <v>56294</v>
+        <v>56289</v>
       </c>
       <c r="C378" t="inlineStr">
         <is>
@@ -52282,21 +52282,21 @@
         </is>
       </c>
       <c r="E378" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I378" t="inlineStr">
@@ -52320,10 +52320,10 @@
         </is>
       </c>
       <c r="Q378" t="n">
-        <v>586327</v>
+        <v>586425</v>
       </c>
       <c r="R378" t="n">
-        <v>6311118</v>
+        <v>6311135</v>
       </c>
       <c r="S378" t="n">
         <v>5</v>
@@ -52355,7 +52355,7 @@
       </c>
       <c r="Z378" t="inlineStr">
         <is>
-          <t>22:57</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AA378" t="inlineStr">
@@ -52365,7 +52365,7 @@
       </c>
       <c r="AB378" t="inlineStr">
         <is>
-          <t>22:58</t>
+          <t>22:38</t>
         </is>
       </c>
       <c r="AC378" t="inlineStr">
@@ -52410,7 +52410,7 @@
     </row>
     <row r="379">
       <c r="A379" t="n">
-        <v>122254643</v>
+        <v>122254653</v>
       </c>
       <c r="B379" t="n">
         <v>56294</v>
@@ -52464,10 +52464,10 @@
         </is>
       </c>
       <c r="Q379" t="n">
-        <v>586424</v>
+        <v>586430</v>
       </c>
       <c r="R379" t="n">
-        <v>6311135</v>
+        <v>6311142</v>
       </c>
       <c r="S379" t="n">
         <v>5</v>
@@ -52499,7 +52499,7 @@
       </c>
       <c r="Z379" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="AA379" t="inlineStr">
@@ -52509,7 +52509,7 @@
       </c>
       <c r="AB379" t="inlineStr">
         <is>
-          <t>22:38</t>
+          <t>22:34</t>
         </is>
       </c>
       <c r="AC379" t="inlineStr">
@@ -52554,7 +52554,7 @@
     </row>
     <row r="380">
       <c r="A380" t="n">
-        <v>122254626</v>
+        <v>122254637</v>
       </c>
       <c r="B380" t="n">
         <v>56294</v>
@@ -52608,7 +52608,7 @@
         </is>
       </c>
       <c r="Q380" t="n">
-        <v>586313</v>
+        <v>586408</v>
       </c>
       <c r="R380" t="n">
         <v>6311124</v>
@@ -52643,7 +52643,7 @@
       </c>
       <c r="Z380" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>22:43</t>
         </is>
       </c>
       <c r="AA380" t="inlineStr">
@@ -52653,7 +52653,7 @@
       </c>
       <c r="AB380" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AC380" t="inlineStr">
@@ -52698,10 +52698,10 @@
     </row>
     <row r="381">
       <c r="A381" t="n">
-        <v>122254587</v>
+        <v>122254856</v>
       </c>
       <c r="B381" t="n">
-        <v>56294</v>
+        <v>56292</v>
       </c>
       <c r="C381" t="inlineStr">
         <is>
@@ -52714,21 +52714,21 @@
         </is>
       </c>
       <c r="E381" t="n">
-        <v>205995</v>
+        <v>100111</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I381" t="inlineStr">
@@ -52752,10 +52752,10 @@
         </is>
       </c>
       <c r="Q381" t="n">
-        <v>586443</v>
+        <v>586327</v>
       </c>
       <c r="R381" t="n">
-        <v>6311163</v>
+        <v>6311118</v>
       </c>
       <c r="S381" t="n">
         <v>5</v>
@@ -52787,7 +52787,7 @@
       </c>
       <c r="Z381" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>22:57</t>
         </is>
       </c>
       <c r="AA381" t="inlineStr">
@@ -52797,7 +52797,7 @@
       </c>
       <c r="AB381" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>22:58</t>
         </is>
       </c>
       <c r="AC381" t="inlineStr">
@@ -52842,10 +52842,10 @@
     </row>
     <row r="382">
       <c r="A382" t="n">
-        <v>122254421</v>
+        <v>122254615</v>
       </c>
       <c r="B382" t="n">
-        <v>56289</v>
+        <v>56294</v>
       </c>
       <c r="C382" t="inlineStr">
         <is>
@@ -52858,21 +52858,21 @@
         </is>
       </c>
       <c r="E382" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H382" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I382" t="inlineStr">
@@ -52896,10 +52896,10 @@
         </is>
       </c>
       <c r="Q382" t="n">
-        <v>586468</v>
+        <v>586329</v>
       </c>
       <c r="R382" t="n">
-        <v>6311181</v>
+        <v>6311120</v>
       </c>
       <c r="S382" t="n">
         <v>5</v>
@@ -52931,7 +52931,7 @@
       </c>
       <c r="Z382" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>22:57</t>
         </is>
       </c>
       <c r="AA382" t="inlineStr">
@@ -52941,7 +52941,7 @@
       </c>
       <c r="AB382" t="inlineStr">
         <is>
-          <t>22:33</t>
+          <t>22:58</t>
         </is>
       </c>
       <c r="AC382" t="inlineStr">
@@ -52986,10 +52986,10 @@
     </row>
     <row r="383">
       <c r="A383" t="n">
-        <v>122254307</v>
+        <v>122254473</v>
       </c>
       <c r="B383" t="n">
-        <v>56289</v>
+        <v>56275</v>
       </c>
       <c r="C383" t="inlineStr">
         <is>
@@ -52998,25 +52998,25 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E383" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I383" t="inlineStr">
@@ -53040,10 +53040,10 @@
         </is>
       </c>
       <c r="Q383" t="n">
-        <v>586477</v>
+        <v>586450</v>
       </c>
       <c r="R383" t="n">
-        <v>6311186</v>
+        <v>6311152</v>
       </c>
       <c r="S383" t="n">
         <v>5</v>
@@ -53075,7 +53075,7 @@
       </c>
       <c r="Z383" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA383" t="inlineStr">
@@ -53085,7 +53085,7 @@
       </c>
       <c r="AB383" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC383" t="inlineStr">
@@ -53130,7 +53130,7 @@
     </row>
     <row r="384">
       <c r="A384" t="n">
-        <v>122254394</v>
+        <v>122254367</v>
       </c>
       <c r="B384" t="n">
         <v>56289</v>
@@ -53184,10 +53184,10 @@
         </is>
       </c>
       <c r="Q384" t="n">
-        <v>586419</v>
+        <v>586280</v>
       </c>
       <c r="R384" t="n">
-        <v>6311142</v>
+        <v>6311103</v>
       </c>
       <c r="S384" t="n">
         <v>5</v>
@@ -53219,7 +53219,7 @@
       </c>
       <c r="Z384" t="inlineStr">
         <is>
-          <t>22:43</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AA384" t="inlineStr">
@@ -53229,7 +53229,7 @@
       </c>
       <c r="AB384" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>22:52</t>
         </is>
       </c>
       <c r="AC384" t="inlineStr">
@@ -53274,7 +53274,7 @@
     </row>
     <row r="385">
       <c r="A385" t="n">
-        <v>122254350</v>
+        <v>122254369</v>
       </c>
       <c r="B385" t="n">
         <v>56289</v>
@@ -53328,10 +53328,10 @@
         </is>
       </c>
       <c r="Q385" t="n">
-        <v>586330</v>
+        <v>586300</v>
       </c>
       <c r="R385" t="n">
-        <v>6311120</v>
+        <v>6311112</v>
       </c>
       <c r="S385" t="n">
         <v>5</v>
@@ -53363,7 +53363,7 @@
       </c>
       <c r="Z385" t="inlineStr">
         <is>
-          <t>22:57</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AA385" t="inlineStr">
@@ -53373,7 +53373,7 @@
       </c>
       <c r="AB385" t="inlineStr">
         <is>
-          <t>22:58</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AC385" t="inlineStr">
@@ -53418,7 +53418,7 @@
     </row>
     <row r="386">
       <c r="A386" t="n">
-        <v>122254634</v>
+        <v>122254656</v>
       </c>
       <c r="B386" t="n">
         <v>56294</v>
@@ -53472,10 +53472,10 @@
         </is>
       </c>
       <c r="Q386" t="n">
-        <v>586415</v>
+        <v>586483</v>
       </c>
       <c r="R386" t="n">
-        <v>6311148</v>
+        <v>6311186</v>
       </c>
       <c r="S386" t="n">
         <v>5</v>
@@ -53507,7 +53507,7 @@
       </c>
       <c r="Z386" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>22:31</t>
         </is>
       </c>
       <c r="AA386" t="inlineStr">
@@ -53517,7 +53517,7 @@
       </c>
       <c r="AB386" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AC386" t="inlineStr">
@@ -53562,10 +53562,10 @@
     </row>
     <row r="387">
       <c r="A387" t="n">
-        <v>122254654</v>
+        <v>122254394</v>
       </c>
       <c r="B387" t="n">
-        <v>56294</v>
+        <v>56289</v>
       </c>
       <c r="C387" t="inlineStr">
         <is>
@@ -53578,21 +53578,21 @@
         </is>
       </c>
       <c r="E387" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I387" t="inlineStr">
@@ -53616,10 +53616,10 @@
         </is>
       </c>
       <c r="Q387" t="n">
-        <v>586467</v>
+        <v>586419</v>
       </c>
       <c r="R387" t="n">
-        <v>6311178</v>
+        <v>6311142</v>
       </c>
       <c r="S387" t="n">
         <v>5</v>
@@ -53651,7 +53651,7 @@
       </c>
       <c r="Z387" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>22:43</t>
         </is>
       </c>
       <c r="AA387" t="inlineStr">
@@ -53661,7 +53661,7 @@
       </c>
       <c r="AB387" t="inlineStr">
         <is>
-          <t>22:33</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AC387" t="inlineStr">
@@ -53706,10 +53706,10 @@
     </row>
     <row r="388">
       <c r="A388" t="n">
-        <v>122254496</v>
+        <v>122254306</v>
       </c>
       <c r="B388" t="n">
-        <v>56275</v>
+        <v>56289</v>
       </c>
       <c r="C388" t="inlineStr">
         <is>
@@ -53718,25 +53718,25 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E388" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H388" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I388" t="inlineStr">
@@ -53760,10 +53760,10 @@
         </is>
       </c>
       <c r="Q388" t="n">
-        <v>586415</v>
+        <v>586473</v>
       </c>
       <c r="R388" t="n">
-        <v>6311146</v>
+        <v>6311192</v>
       </c>
       <c r="S388" t="n">
         <v>5</v>
@@ -53795,7 +53795,7 @@
       </c>
       <c r="Z388" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AA388" t="inlineStr">
@@ -53805,7 +53805,7 @@
       </c>
       <c r="AB388" t="inlineStr">
         <is>
-          <t>23:03</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AC388" t="inlineStr">
@@ -53850,7 +53850,7 @@
     </row>
     <row r="389">
       <c r="A389" t="n">
-        <v>122254500</v>
+        <v>122254519</v>
       </c>
       <c r="B389" t="n">
         <v>56275</v>
@@ -53904,10 +53904,10 @@
         </is>
       </c>
       <c r="Q389" t="n">
-        <v>586388</v>
+        <v>586424</v>
       </c>
       <c r="R389" t="n">
-        <v>6311142</v>
+        <v>6311135</v>
       </c>
       <c r="S389" t="n">
         <v>5</v>
@@ -53939,7 +53939,7 @@
       </c>
       <c r="Z389" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AA389" t="inlineStr">
@@ -53949,7 +53949,7 @@
       </c>
       <c r="AB389" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>22:38</t>
         </is>
       </c>
       <c r="AC389" t="inlineStr">

--- a/artfynd/A 36363-2024 artfynd.xlsx
+++ b/artfynd/A 36363-2024 artfynd.xlsx
@@ -38730,10 +38730,10 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>122254365</v>
+        <v>122254648</v>
       </c>
       <c r="B284" t="n">
-        <v>56289</v>
+        <v>56294</v>
       </c>
       <c r="C284" t="inlineStr">
         <is>
@@ -38746,21 +38746,21 @@
         </is>
       </c>
       <c r="E284" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
@@ -38784,10 +38784,10 @@
         </is>
       </c>
       <c r="Q284" t="n">
-        <v>586276</v>
+        <v>586418</v>
       </c>
       <c r="R284" t="n">
-        <v>6311100</v>
+        <v>6311107</v>
       </c>
       <c r="S284" t="n">
         <v>5</v>
@@ -38819,7 +38819,7 @@
       </c>
       <c r="Z284" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>22:36</t>
         </is>
       </c>
       <c r="AA284" t="inlineStr">
@@ -38829,7 +38829,7 @@
       </c>
       <c r="AB284" t="inlineStr">
         <is>
-          <t>22:52</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AC284" t="inlineStr">
@@ -38874,10 +38874,10 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>122254648</v>
+        <v>122254954</v>
       </c>
       <c r="B285" t="n">
-        <v>56294</v>
+        <v>56282</v>
       </c>
       <c r="C285" t="inlineStr">
         <is>
@@ -38890,21 +38890,21 @@
         </is>
       </c>
       <c r="E285" t="n">
-        <v>205995</v>
+        <v>205992</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
@@ -38928,10 +38928,10 @@
         </is>
       </c>
       <c r="Q285" t="n">
-        <v>586418</v>
+        <v>586442</v>
       </c>
       <c r="R285" t="n">
-        <v>6311107</v>
+        <v>6311152</v>
       </c>
       <c r="S285" t="n">
         <v>5</v>
@@ -38963,7 +38963,7 @@
       </c>
       <c r="Z285" t="inlineStr">
         <is>
-          <t>22:36</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AA285" t="inlineStr">
@@ -38973,7 +38973,7 @@
       </c>
       <c r="AB285" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AC285" t="inlineStr">
@@ -39018,10 +39018,10 @@
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>122254954</v>
+        <v>122254644</v>
       </c>
       <c r="B286" t="n">
-        <v>56282</v>
+        <v>56294</v>
       </c>
       <c r="C286" t="inlineStr">
         <is>
@@ -39034,21 +39034,21 @@
         </is>
       </c>
       <c r="E286" t="n">
-        <v>205992</v>
+        <v>205995</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
@@ -39072,10 +39072,10 @@
         </is>
       </c>
       <c r="Q286" t="n">
-        <v>586442</v>
+        <v>586429</v>
       </c>
       <c r="R286" t="n">
-        <v>6311152</v>
+        <v>6311115</v>
       </c>
       <c r="S286" t="n">
         <v>5</v>
@@ -39107,7 +39107,7 @@
       </c>
       <c r="Z286" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>22:36</t>
         </is>
       </c>
       <c r="AA286" t="inlineStr">
@@ -39117,7 +39117,7 @@
       </c>
       <c r="AB286" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AC286" t="inlineStr">
@@ -39162,10 +39162,10 @@
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>122254644</v>
+        <v>122254952</v>
       </c>
       <c r="B287" t="n">
-        <v>56294</v>
+        <v>56282</v>
       </c>
       <c r="C287" t="inlineStr">
         <is>
@@ -39178,21 +39178,21 @@
         </is>
       </c>
       <c r="E287" t="n">
-        <v>205995</v>
+        <v>205992</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
@@ -39216,10 +39216,10 @@
         </is>
       </c>
       <c r="Q287" t="n">
-        <v>586429</v>
+        <v>586455</v>
       </c>
       <c r="R287" t="n">
-        <v>6311115</v>
+        <v>6311156</v>
       </c>
       <c r="S287" t="n">
         <v>5</v>
@@ -39251,7 +39251,7 @@
       </c>
       <c r="Z287" t="inlineStr">
         <is>
-          <t>22:36</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AA287" t="inlineStr">
@@ -39261,7 +39261,7 @@
       </c>
       <c r="AB287" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AC287" t="inlineStr">
@@ -39306,10 +39306,10 @@
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>122254952</v>
+        <v>122254514</v>
       </c>
       <c r="B288" t="n">
-        <v>56282</v>
+        <v>56275</v>
       </c>
       <c r="C288" t="inlineStr">
         <is>
@@ -39318,25 +39318,25 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E288" t="n">
-        <v>205992</v>
+        <v>205998</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
@@ -39360,10 +39360,10 @@
         </is>
       </c>
       <c r="Q288" t="n">
-        <v>586455</v>
+        <v>586408</v>
       </c>
       <c r="R288" t="n">
-        <v>6311156</v>
+        <v>6311124</v>
       </c>
       <c r="S288" t="n">
         <v>5</v>
@@ -39395,7 +39395,7 @@
       </c>
       <c r="Z288" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>22:43</t>
         </is>
       </c>
       <c r="AA288" t="inlineStr">
@@ -39405,7 +39405,7 @@
       </c>
       <c r="AB288" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AC288" t="inlineStr">
@@ -39450,7 +39450,7 @@
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>122254514</v>
+        <v>122254512</v>
       </c>
       <c r="B289" t="n">
         <v>56275</v>
@@ -39504,10 +39504,10 @@
         </is>
       </c>
       <c r="Q289" t="n">
-        <v>586408</v>
+        <v>586379</v>
       </c>
       <c r="R289" t="n">
-        <v>6311124</v>
+        <v>6311136</v>
       </c>
       <c r="S289" t="n">
         <v>5</v>
@@ -39539,7 +39539,7 @@
       </c>
       <c r="Z289" t="inlineStr">
         <is>
-          <t>22:43</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AA289" t="inlineStr">
@@ -39549,7 +39549,7 @@
       </c>
       <c r="AB289" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>22:46</t>
         </is>
       </c>
       <c r="AC289" t="inlineStr">
@@ -39594,10 +39594,10 @@
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>122254512</v>
+        <v>122254365</v>
       </c>
       <c r="B290" t="n">
-        <v>56275</v>
+        <v>56289</v>
       </c>
       <c r="C290" t="inlineStr">
         <is>
@@ -39606,25 +39606,25 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E290" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
@@ -39648,10 +39648,10 @@
         </is>
       </c>
       <c r="Q290" t="n">
-        <v>586379</v>
+        <v>586276</v>
       </c>
       <c r="R290" t="n">
-        <v>6311136</v>
+        <v>6311100</v>
       </c>
       <c r="S290" t="n">
         <v>5</v>
@@ -39683,7 +39683,7 @@
       </c>
       <c r="Z290" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AA290" t="inlineStr">
@@ -39693,7 +39693,7 @@
       </c>
       <c r="AB290" t="inlineStr">
         <is>
-          <t>22:46</t>
+          <t>22:52</t>
         </is>
       </c>
       <c r="AC290" t="inlineStr">
@@ -40170,10 +40170,10 @@
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>122254411</v>
+        <v>122254845</v>
       </c>
       <c r="B294" t="n">
-        <v>56289</v>
+        <v>56292</v>
       </c>
       <c r="C294" t="inlineStr">
         <is>
@@ -40186,21 +40186,21 @@
         </is>
       </c>
       <c r="E294" t="n">
-        <v>100092</v>
+        <v>100111</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
@@ -40224,10 +40224,10 @@
         </is>
       </c>
       <c r="Q294" t="n">
-        <v>586414</v>
+        <v>586370</v>
       </c>
       <c r="R294" t="n">
-        <v>6311126</v>
+        <v>6311139</v>
       </c>
       <c r="S294" t="n">
         <v>5</v>
@@ -40259,7 +40259,7 @@
       </c>
       <c r="Z294" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>22:59</t>
         </is>
       </c>
       <c r="AA294" t="inlineStr">
@@ -40269,7 +40269,7 @@
       </c>
       <c r="AB294" t="inlineStr">
         <is>
-          <t>22:38</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AC294" t="inlineStr">
@@ -40314,10 +40314,10 @@
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>122254352</v>
+        <v>122254855</v>
       </c>
       <c r="B295" t="n">
-        <v>56289</v>
+        <v>56292</v>
       </c>
       <c r="C295" t="inlineStr">
         <is>
@@ -40330,21 +40330,21 @@
         </is>
       </c>
       <c r="E295" t="n">
-        <v>100092</v>
+        <v>100111</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
@@ -40368,10 +40368,10 @@
         </is>
       </c>
       <c r="Q295" t="n">
-        <v>586288</v>
+        <v>586330</v>
       </c>
       <c r="R295" t="n">
-        <v>6311100</v>
+        <v>6311120</v>
       </c>
       <c r="S295" t="n">
         <v>5</v>
@@ -40403,7 +40403,7 @@
       </c>
       <c r="Z295" t="inlineStr">
         <is>
-          <t>22:55</t>
+          <t>22:57</t>
         </is>
       </c>
       <c r="AA295" t="inlineStr">
@@ -40413,7 +40413,7 @@
       </c>
       <c r="AB295" t="inlineStr">
         <is>
-          <t>22:56</t>
+          <t>22:58</t>
         </is>
       </c>
       <c r="AC295" t="inlineStr">
@@ -40458,7 +40458,7 @@
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>122254392</v>
+        <v>122254411</v>
       </c>
       <c r="B296" t="n">
         <v>56289</v>
@@ -40512,10 +40512,10 @@
         </is>
       </c>
       <c r="Q296" t="n">
-        <v>586384</v>
+        <v>586414</v>
       </c>
       <c r="R296" t="n">
-        <v>6311139</v>
+        <v>6311126</v>
       </c>
       <c r="S296" t="n">
         <v>5</v>
@@ -40547,7 +40547,7 @@
       </c>
       <c r="Z296" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AA296" t="inlineStr">
@@ -40557,7 +40557,7 @@
       </c>
       <c r="AB296" t="inlineStr">
         <is>
-          <t>22:46</t>
+          <t>22:38</t>
         </is>
       </c>
       <c r="AC296" t="inlineStr">
@@ -40602,10 +40602,10 @@
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>122254845</v>
+        <v>122254352</v>
       </c>
       <c r="B297" t="n">
-        <v>56292</v>
+        <v>56289</v>
       </c>
       <c r="C297" t="inlineStr">
         <is>
@@ -40618,21 +40618,21 @@
         </is>
       </c>
       <c r="E297" t="n">
-        <v>100111</v>
+        <v>100092</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
@@ -40656,10 +40656,10 @@
         </is>
       </c>
       <c r="Q297" t="n">
-        <v>586370</v>
+        <v>586288</v>
       </c>
       <c r="R297" t="n">
-        <v>6311139</v>
+        <v>6311100</v>
       </c>
       <c r="S297" t="n">
         <v>5</v>
@@ -40691,7 +40691,7 @@
       </c>
       <c r="Z297" t="inlineStr">
         <is>
-          <t>22:59</t>
+          <t>22:55</t>
         </is>
       </c>
       <c r="AA297" t="inlineStr">
@@ -40701,7 +40701,7 @@
       </c>
       <c r="AB297" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:56</t>
         </is>
       </c>
       <c r="AC297" t="inlineStr">
@@ -40746,10 +40746,10 @@
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>122254855</v>
+        <v>122254392</v>
       </c>
       <c r="B298" t="n">
-        <v>56292</v>
+        <v>56289</v>
       </c>
       <c r="C298" t="inlineStr">
         <is>
@@ -40762,21 +40762,21 @@
         </is>
       </c>
       <c r="E298" t="n">
-        <v>100111</v>
+        <v>100092</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
@@ -40800,10 +40800,10 @@
         </is>
       </c>
       <c r="Q298" t="n">
-        <v>586330</v>
+        <v>586384</v>
       </c>
       <c r="R298" t="n">
-        <v>6311120</v>
+        <v>6311139</v>
       </c>
       <c r="S298" t="n">
         <v>5</v>
@@ -40835,7 +40835,7 @@
       </c>
       <c r="Z298" t="inlineStr">
         <is>
-          <t>22:57</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AA298" t="inlineStr">
@@ -40845,7 +40845,7 @@
       </c>
       <c r="AB298" t="inlineStr">
         <is>
-          <t>22:58</t>
+          <t>22:46</t>
         </is>
       </c>
       <c r="AC298" t="inlineStr">
@@ -40890,10 +40890,10 @@
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>122254475</v>
+        <v>122254627</v>
       </c>
       <c r="B299" t="n">
-        <v>56275</v>
+        <v>56294</v>
       </c>
       <c r="C299" t="inlineStr">
         <is>
@@ -40902,25 +40902,25 @@
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E299" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
@@ -40944,10 +40944,10 @@
         </is>
       </c>
       <c r="Q299" t="n">
-        <v>586420</v>
+        <v>586306</v>
       </c>
       <c r="R299" t="n">
-        <v>6311166</v>
+        <v>6311131</v>
       </c>
       <c r="S299" t="n">
         <v>5</v>
@@ -40979,7 +40979,7 @@
       </c>
       <c r="Z299" t="inlineStr">
         <is>
-          <t>23:23</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AA299" t="inlineStr">
@@ -40989,7 +40989,7 @@
       </c>
       <c r="AB299" t="inlineStr">
         <is>
-          <t>23:24</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AC299" t="inlineStr">
@@ -41034,10 +41034,10 @@
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>122254513</v>
+        <v>122254657</v>
       </c>
       <c r="B300" t="n">
-        <v>56275</v>
+        <v>56294</v>
       </c>
       <c r="C300" t="inlineStr">
         <is>
@@ -41046,25 +41046,25 @@
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E300" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
@@ -41088,10 +41088,10 @@
         </is>
       </c>
       <c r="Q300" t="n">
-        <v>586396</v>
+        <v>586488</v>
       </c>
       <c r="R300" t="n">
-        <v>6311146</v>
+        <v>6311184</v>
       </c>
       <c r="S300" t="n">
         <v>5</v>
@@ -41123,7 +41123,7 @@
       </c>
       <c r="Z300" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>22:31</t>
         </is>
       </c>
       <c r="AA300" t="inlineStr">
@@ -41133,7 +41133,7 @@
       </c>
       <c r="AB300" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AC300" t="inlineStr">
@@ -41178,10 +41178,10 @@
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>122254627</v>
+        <v>122254475</v>
       </c>
       <c r="B301" t="n">
-        <v>56294</v>
+        <v>56275</v>
       </c>
       <c r="C301" t="inlineStr">
         <is>
@@ -41190,25 +41190,25 @@
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E301" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
@@ -41232,10 +41232,10 @@
         </is>
       </c>
       <c r="Q301" t="n">
-        <v>586306</v>
+        <v>586420</v>
       </c>
       <c r="R301" t="n">
-        <v>6311131</v>
+        <v>6311166</v>
       </c>
       <c r="S301" t="n">
         <v>5</v>
@@ -41267,7 +41267,7 @@
       </c>
       <c r="Z301" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>23:23</t>
         </is>
       </c>
       <c r="AA301" t="inlineStr">
@@ -41277,7 +41277,7 @@
       </c>
       <c r="AB301" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="AC301" t="inlineStr">
@@ -41322,10 +41322,10 @@
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>122254657</v>
+        <v>122254513</v>
       </c>
       <c r="B302" t="n">
-        <v>56294</v>
+        <v>56275</v>
       </c>
       <c r="C302" t="inlineStr">
         <is>
@@ -41334,25 +41334,25 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E302" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
@@ -41376,10 +41376,10 @@
         </is>
       </c>
       <c r="Q302" t="n">
-        <v>586488</v>
+        <v>586396</v>
       </c>
       <c r="R302" t="n">
-        <v>6311184</v>
+        <v>6311146</v>
       </c>
       <c r="S302" t="n">
         <v>5</v>
@@ -41411,7 +41411,7 @@
       </c>
       <c r="Z302" t="inlineStr">
         <is>
-          <t>22:31</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AA302" t="inlineStr">
@@ -41421,7 +41421,7 @@
       </c>
       <c r="AB302" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AC302" t="inlineStr">
@@ -41754,10 +41754,10 @@
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>122254957</v>
+        <v>122254476</v>
       </c>
       <c r="B305" t="n">
-        <v>56282</v>
+        <v>56275</v>
       </c>
       <c r="C305" t="inlineStr">
         <is>
@@ -41766,25 +41766,25 @@
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E305" t="n">
-        <v>205992</v>
+        <v>205998</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
@@ -41808,10 +41808,10 @@
         </is>
       </c>
       <c r="Q305" t="n">
-        <v>586444</v>
+        <v>586418</v>
       </c>
       <c r="R305" t="n">
-        <v>6311160</v>
+        <v>6311167</v>
       </c>
       <c r="S305" t="n">
         <v>5</v>
@@ -41843,17 +41843,17 @@
       </c>
       <c r="Z305" t="inlineStr">
         <is>
+          <t>23:23</t>
+        </is>
+      </c>
+      <c r="AA305" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AB305" t="inlineStr">
+        <is>
           <t>23:24</t>
-        </is>
-      </c>
-      <c r="AA305" t="inlineStr">
-        <is>
-          <t>2024-06-26</t>
-        </is>
-      </c>
-      <c r="AB305" t="inlineStr">
-        <is>
-          <t>23:25</t>
         </is>
       </c>
       <c r="AC305" t="inlineStr">
@@ -41898,10 +41898,10 @@
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>122254476</v>
+        <v>122254658</v>
       </c>
       <c r="B306" t="n">
-        <v>56275</v>
+        <v>56294</v>
       </c>
       <c r="C306" t="inlineStr">
         <is>
@@ -41910,25 +41910,25 @@
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E306" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
@@ -41952,10 +41952,10 @@
         </is>
       </c>
       <c r="Q306" t="n">
-        <v>586418</v>
+        <v>586491</v>
       </c>
       <c r="R306" t="n">
-        <v>6311167</v>
+        <v>6311181</v>
       </c>
       <c r="S306" t="n">
         <v>5</v>
@@ -41987,7 +41987,7 @@
       </c>
       <c r="Z306" t="inlineStr">
         <is>
-          <t>23:23</t>
+          <t>22:31</t>
         </is>
       </c>
       <c r="AA306" t="inlineStr">
@@ -41997,7 +41997,7 @@
       </c>
       <c r="AB306" t="inlineStr">
         <is>
-          <t>23:24</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AC306" t="inlineStr">
@@ -42042,10 +42042,10 @@
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>122254658</v>
+        <v>122254957</v>
       </c>
       <c r="B307" t="n">
-        <v>56294</v>
+        <v>56282</v>
       </c>
       <c r="C307" t="inlineStr">
         <is>
@@ -42058,21 +42058,21 @@
         </is>
       </c>
       <c r="E307" t="n">
-        <v>205995</v>
+        <v>205992</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
@@ -42096,10 +42096,10 @@
         </is>
       </c>
       <c r="Q307" t="n">
-        <v>586491</v>
+        <v>586444</v>
       </c>
       <c r="R307" t="n">
-        <v>6311181</v>
+        <v>6311160</v>
       </c>
       <c r="S307" t="n">
         <v>5</v>
@@ -42131,7 +42131,7 @@
       </c>
       <c r="Z307" t="inlineStr">
         <is>
-          <t>22:31</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="AA307" t="inlineStr">
@@ -42141,7 +42141,7 @@
       </c>
       <c r="AB307" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AC307" t="inlineStr">
@@ -42186,10 +42186,10 @@
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>122254649</v>
+        <v>122254309</v>
       </c>
       <c r="B308" t="n">
-        <v>56294</v>
+        <v>56289</v>
       </c>
       <c r="C308" t="inlineStr">
         <is>
@@ -42202,21 +42202,21 @@
         </is>
       </c>
       <c r="E308" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
@@ -42240,10 +42240,10 @@
         </is>
       </c>
       <c r="Q308" t="n">
-        <v>586422</v>
+        <v>586456</v>
       </c>
       <c r="R308" t="n">
-        <v>6311100</v>
+        <v>6311158</v>
       </c>
       <c r="S308" t="n">
         <v>5</v>
@@ -42275,7 +42275,7 @@
       </c>
       <c r="Z308" t="inlineStr">
         <is>
-          <t>22:35</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AA308" t="inlineStr">
@@ -42285,7 +42285,7 @@
       </c>
       <c r="AB308" t="inlineStr">
         <is>
-          <t>22:36</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AC308" t="inlineStr">
@@ -42330,7 +42330,7 @@
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>122254646</v>
+        <v>122254649</v>
       </c>
       <c r="B309" t="n">
         <v>56294</v>
@@ -42387,7 +42387,7 @@
         <v>586422</v>
       </c>
       <c r="R309" t="n">
-        <v>6311111</v>
+        <v>6311100</v>
       </c>
       <c r="S309" t="n">
         <v>5</v>
@@ -42419,17 +42419,17 @@
       </c>
       <c r="Z309" t="inlineStr">
         <is>
+          <t>22:35</t>
+        </is>
+      </c>
+      <c r="AA309" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AB309" t="inlineStr">
+        <is>
           <t>22:36</t>
-        </is>
-      </c>
-      <c r="AA309" t="inlineStr">
-        <is>
-          <t>2024-06-26</t>
-        </is>
-      </c>
-      <c r="AB309" t="inlineStr">
-        <is>
-          <t>22:37</t>
         </is>
       </c>
       <c r="AC309" t="inlineStr">
@@ -42474,10 +42474,10 @@
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>122254963</v>
+        <v>122254646</v>
       </c>
       <c r="B310" t="n">
-        <v>56282</v>
+        <v>56294</v>
       </c>
       <c r="C310" t="inlineStr">
         <is>
@@ -42490,21 +42490,21 @@
         </is>
       </c>
       <c r="E310" t="n">
-        <v>205992</v>
+        <v>205995</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
@@ -42528,10 +42528,10 @@
         </is>
       </c>
       <c r="Q310" t="n">
-        <v>586374</v>
+        <v>586422</v>
       </c>
       <c r="R310" t="n">
-        <v>6311140</v>
+        <v>6311111</v>
       </c>
       <c r="S310" t="n">
         <v>5</v>
@@ -42563,7 +42563,7 @@
       </c>
       <c r="Z310" t="inlineStr">
         <is>
-          <t>22:46</t>
+          <t>22:36</t>
         </is>
       </c>
       <c r="AA310" t="inlineStr">
@@ -42573,7 +42573,7 @@
       </c>
       <c r="AB310" t="inlineStr">
         <is>
-          <t>22:47</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AC310" t="inlineStr">
@@ -42618,10 +42618,10 @@
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>122254309</v>
+        <v>122254963</v>
       </c>
       <c r="B311" t="n">
-        <v>56289</v>
+        <v>56282</v>
       </c>
       <c r="C311" t="inlineStr">
         <is>
@@ -42634,21 +42634,21 @@
         </is>
       </c>
       <c r="E311" t="n">
-        <v>100092</v>
+        <v>205992</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
@@ -42672,10 +42672,10 @@
         </is>
       </c>
       <c r="Q311" t="n">
-        <v>586456</v>
+        <v>586374</v>
       </c>
       <c r="R311" t="n">
-        <v>6311158</v>
+        <v>6311140</v>
       </c>
       <c r="S311" t="n">
         <v>5</v>
@@ -42707,7 +42707,7 @@
       </c>
       <c r="Z311" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>22:46</t>
         </is>
       </c>
       <c r="AA311" t="inlineStr">
@@ -42717,7 +42717,7 @@
       </c>
       <c r="AB311" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>22:47</t>
         </is>
       </c>
       <c r="AC311" t="inlineStr">
@@ -43770,7 +43770,7 @@
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>122254318</v>
+        <v>122254413</v>
       </c>
       <c r="B319" t="n">
         <v>56289</v>
@@ -43824,10 +43824,10 @@
         </is>
       </c>
       <c r="Q319" t="n">
-        <v>586455</v>
+        <v>586423</v>
       </c>
       <c r="R319" t="n">
-        <v>6311228</v>
+        <v>6311137</v>
       </c>
       <c r="S319" t="n">
         <v>5</v>
@@ -43859,7 +43859,7 @@
       </c>
       <c r="Z319" t="inlineStr">
         <is>
-          <t>23:22</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AA319" t="inlineStr">
@@ -43869,7 +43869,7 @@
       </c>
       <c r="AB319" t="inlineStr">
         <is>
-          <t>23:23</t>
+          <t>22:38</t>
         </is>
       </c>
       <c r="AC319" t="inlineStr">
@@ -43914,7 +43914,7 @@
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>122254314</v>
+        <v>122254416</v>
       </c>
       <c r="B320" t="n">
         <v>56289</v>
@@ -43968,10 +43968,10 @@
         </is>
       </c>
       <c r="Q320" t="n">
-        <v>586443</v>
+        <v>586410</v>
       </c>
       <c r="R320" t="n">
-        <v>6311164</v>
+        <v>6311140</v>
       </c>
       <c r="S320" t="n">
         <v>5</v>
@@ -44003,7 +44003,7 @@
       </c>
       <c r="Z320" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="AA320" t="inlineStr">
@@ -44013,7 +44013,7 @@
       </c>
       <c r="AB320" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>22:34</t>
         </is>
       </c>
       <c r="AC320" t="inlineStr">
@@ -44058,10 +44058,10 @@
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>122254862</v>
+        <v>122254318</v>
       </c>
       <c r="B321" t="n">
-        <v>56292</v>
+        <v>56289</v>
       </c>
       <c r="C321" t="inlineStr">
         <is>
@@ -44074,21 +44074,21 @@
         </is>
       </c>
       <c r="E321" t="n">
-        <v>100111</v>
+        <v>100092</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
@@ -44112,10 +44112,10 @@
         </is>
       </c>
       <c r="Q321" t="n">
-        <v>586288</v>
+        <v>586455</v>
       </c>
       <c r="R321" t="n">
-        <v>6311100</v>
+        <v>6311228</v>
       </c>
       <c r="S321" t="n">
         <v>5</v>
@@ -44147,7 +44147,7 @@
       </c>
       <c r="Z321" t="inlineStr">
         <is>
-          <t>22:55</t>
+          <t>23:22</t>
         </is>
       </c>
       <c r="AA321" t="inlineStr">
@@ -44157,7 +44157,7 @@
       </c>
       <c r="AB321" t="inlineStr">
         <is>
-          <t>22:56</t>
+          <t>23:23</t>
         </is>
       </c>
       <c r="AC321" t="inlineStr">
@@ -44202,7 +44202,7 @@
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>122254413</v>
+        <v>122254314</v>
       </c>
       <c r="B322" t="n">
         <v>56289</v>
@@ -44256,10 +44256,10 @@
         </is>
       </c>
       <c r="Q322" t="n">
-        <v>586423</v>
+        <v>586443</v>
       </c>
       <c r="R322" t="n">
-        <v>6311137</v>
+        <v>6311164</v>
       </c>
       <c r="S322" t="n">
         <v>5</v>
@@ -44291,7 +44291,7 @@
       </c>
       <c r="Z322" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AA322" t="inlineStr">
@@ -44301,7 +44301,7 @@
       </c>
       <c r="AB322" t="inlineStr">
         <is>
-          <t>22:38</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AC322" t="inlineStr">
@@ -44346,10 +44346,10 @@
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>122254416</v>
+        <v>122254862</v>
       </c>
       <c r="B323" t="n">
-        <v>56289</v>
+        <v>56292</v>
       </c>
       <c r="C323" t="inlineStr">
         <is>
@@ -44362,21 +44362,21 @@
         </is>
       </c>
       <c r="E323" t="n">
-        <v>100092</v>
+        <v>100111</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
@@ -44400,10 +44400,10 @@
         </is>
       </c>
       <c r="Q323" t="n">
-        <v>586410</v>
+        <v>586288</v>
       </c>
       <c r="R323" t="n">
-        <v>6311140</v>
+        <v>6311100</v>
       </c>
       <c r="S323" t="n">
         <v>5</v>
@@ -44435,7 +44435,7 @@
       </c>
       <c r="Z323" t="inlineStr">
         <is>
-          <t>22:33</t>
+          <t>22:55</t>
         </is>
       </c>
       <c r="AA323" t="inlineStr">
@@ -44445,7 +44445,7 @@
       </c>
       <c r="AB323" t="inlineStr">
         <is>
-          <t>22:34</t>
+          <t>22:56</t>
         </is>
       </c>
       <c r="AC323" t="inlineStr">
@@ -44490,10 +44490,10 @@
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>122254835</v>
+        <v>122254660</v>
       </c>
       <c r="B324" t="n">
-        <v>56292</v>
+        <v>56294</v>
       </c>
       <c r="C324" t="inlineStr">
         <is>
@@ -44506,21 +44506,21 @@
         </is>
       </c>
       <c r="E324" t="n">
-        <v>100111</v>
+        <v>205995</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
@@ -44544,10 +44544,10 @@
         </is>
       </c>
       <c r="Q324" t="n">
-        <v>586473</v>
+        <v>586488</v>
       </c>
       <c r="R324" t="n">
-        <v>6311192</v>
+        <v>6311183</v>
       </c>
       <c r="S324" t="n">
         <v>5</v>
@@ -44579,7 +44579,7 @@
       </c>
       <c r="Z324" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>22:31</t>
         </is>
       </c>
       <c r="AA324" t="inlineStr">
@@ -44589,7 +44589,7 @@
       </c>
       <c r="AB324" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AC324" t="inlineStr">
@@ -44634,10 +44634,10 @@
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>122254857</v>
+        <v>122254654</v>
       </c>
       <c r="B325" t="n">
-        <v>56292</v>
+        <v>56294</v>
       </c>
       <c r="C325" t="inlineStr">
         <is>
@@ -44650,21 +44650,21 @@
         </is>
       </c>
       <c r="E325" t="n">
-        <v>100111</v>
+        <v>205995</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
@@ -44688,10 +44688,10 @@
         </is>
       </c>
       <c r="Q325" t="n">
-        <v>586317</v>
+        <v>586467</v>
       </c>
       <c r="R325" t="n">
-        <v>6311115</v>
+        <v>6311178</v>
       </c>
       <c r="S325" t="n">
         <v>5</v>
@@ -44723,7 +44723,7 @@
       </c>
       <c r="Z325" t="inlineStr">
         <is>
-          <t>22:57</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AA325" t="inlineStr">
@@ -44733,7 +44733,7 @@
       </c>
       <c r="AB325" t="inlineStr">
         <is>
-          <t>22:58</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="AC325" t="inlineStr">
@@ -44778,7 +44778,7 @@
     </row>
     <row r="326">
       <c r="A326" t="n">
-        <v>122254660</v>
+        <v>122254659</v>
       </c>
       <c r="B326" t="n">
         <v>56294</v>
@@ -44832,10 +44832,10 @@
         </is>
       </c>
       <c r="Q326" t="n">
-        <v>586488</v>
+        <v>586489</v>
       </c>
       <c r="R326" t="n">
-        <v>6311183</v>
+        <v>6311181</v>
       </c>
       <c r="S326" t="n">
         <v>5</v>
@@ -44922,10 +44922,10 @@
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>122254654</v>
+        <v>122254499</v>
       </c>
       <c r="B327" t="n">
-        <v>56294</v>
+        <v>56275</v>
       </c>
       <c r="C327" t="inlineStr">
         <is>
@@ -44934,25 +44934,25 @@
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E327" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
@@ -44976,10 +44976,10 @@
         </is>
       </c>
       <c r="Q327" t="n">
-        <v>586467</v>
+        <v>586392</v>
       </c>
       <c r="R327" t="n">
-        <v>6311178</v>
+        <v>6311147</v>
       </c>
       <c r="S327" t="n">
         <v>5</v>
@@ -45011,7 +45011,7 @@
       </c>
       <c r="Z327" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AA327" t="inlineStr">
@@ -45021,7 +45021,7 @@
       </c>
       <c r="AB327" t="inlineStr">
         <is>
-          <t>22:33</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AC327" t="inlineStr">
@@ -45066,10 +45066,10 @@
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>122254659</v>
+        <v>122254393</v>
       </c>
       <c r="B328" t="n">
-        <v>56294</v>
+        <v>56289</v>
       </c>
       <c r="C328" t="inlineStr">
         <is>
@@ -45082,21 +45082,21 @@
         </is>
       </c>
       <c r="E328" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
@@ -45120,10 +45120,10 @@
         </is>
       </c>
       <c r="Q328" t="n">
-        <v>586489</v>
+        <v>586396</v>
       </c>
       <c r="R328" t="n">
-        <v>6311181</v>
+        <v>6311146</v>
       </c>
       <c r="S328" t="n">
         <v>5</v>
@@ -45155,7 +45155,7 @@
       </c>
       <c r="Z328" t="inlineStr">
         <is>
-          <t>22:31</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AA328" t="inlineStr">
@@ -45165,7 +45165,7 @@
       </c>
       <c r="AB328" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AC328" t="inlineStr">
@@ -45210,10 +45210,10 @@
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>122254499</v>
+        <v>122254313</v>
       </c>
       <c r="B329" t="n">
-        <v>56275</v>
+        <v>56289</v>
       </c>
       <c r="C329" t="inlineStr">
         <is>
@@ -45222,25 +45222,25 @@
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E329" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
@@ -45264,10 +45264,10 @@
         </is>
       </c>
       <c r="Q329" t="n">
-        <v>586392</v>
+        <v>586449</v>
       </c>
       <c r="R329" t="n">
-        <v>6311147</v>
+        <v>6311155</v>
       </c>
       <c r="S329" t="n">
         <v>5</v>
@@ -45299,7 +45299,7 @@
       </c>
       <c r="Z329" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA329" t="inlineStr">
@@ -45309,7 +45309,7 @@
       </c>
       <c r="AB329" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC329" t="inlineStr">
@@ -45354,7 +45354,7 @@
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>122254393</v>
+        <v>122254312</v>
       </c>
       <c r="B330" t="n">
         <v>56289</v>
@@ -45408,10 +45408,10 @@
         </is>
       </c>
       <c r="Q330" t="n">
-        <v>586396</v>
+        <v>586452</v>
       </c>
       <c r="R330" t="n">
-        <v>6311146</v>
+        <v>6311152</v>
       </c>
       <c r="S330" t="n">
         <v>5</v>
@@ -45443,7 +45443,7 @@
       </c>
       <c r="Z330" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA330" t="inlineStr">
@@ -45453,7 +45453,7 @@
       </c>
       <c r="AB330" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC330" t="inlineStr">
@@ -45498,10 +45498,10 @@
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>122254313</v>
+        <v>122254835</v>
       </c>
       <c r="B331" t="n">
-        <v>56289</v>
+        <v>56292</v>
       </c>
       <c r="C331" t="inlineStr">
         <is>
@@ -45514,21 +45514,21 @@
         </is>
       </c>
       <c r="E331" t="n">
-        <v>100092</v>
+        <v>100111</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I331" t="inlineStr">
@@ -45552,10 +45552,10 @@
         </is>
       </c>
       <c r="Q331" t="n">
-        <v>586449</v>
+        <v>586473</v>
       </c>
       <c r="R331" t="n">
-        <v>6311155</v>
+        <v>6311192</v>
       </c>
       <c r="S331" t="n">
         <v>5</v>
@@ -45587,7 +45587,7 @@
       </c>
       <c r="Z331" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AA331" t="inlineStr">
@@ -45597,7 +45597,7 @@
       </c>
       <c r="AB331" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AC331" t="inlineStr">
@@ -45642,10 +45642,10 @@
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>122254312</v>
+        <v>122254857</v>
       </c>
       <c r="B332" t="n">
-        <v>56289</v>
+        <v>56292</v>
       </c>
       <c r="C332" t="inlineStr">
         <is>
@@ -45658,21 +45658,21 @@
         </is>
       </c>
       <c r="E332" t="n">
-        <v>100092</v>
+        <v>100111</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
@@ -45696,10 +45696,10 @@
         </is>
       </c>
       <c r="Q332" t="n">
-        <v>586452</v>
+        <v>586317</v>
       </c>
       <c r="R332" t="n">
-        <v>6311152</v>
+        <v>6311115</v>
       </c>
       <c r="S332" t="n">
         <v>5</v>
@@ -45731,7 +45731,7 @@
       </c>
       <c r="Z332" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>22:57</t>
         </is>
       </c>
       <c r="AA332" t="inlineStr">
@@ -45741,7 +45741,7 @@
       </c>
       <c r="AB332" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>22:58</t>
         </is>
       </c>
       <c r="AC332" t="inlineStr">
@@ -46938,10 +46938,10 @@
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>122254341</v>
+        <v>122254586</v>
       </c>
       <c r="B341" t="n">
-        <v>56289</v>
+        <v>56294</v>
       </c>
       <c r="C341" t="inlineStr">
         <is>
@@ -46954,21 +46954,21 @@
         </is>
       </c>
       <c r="E341" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I341" t="inlineStr">
@@ -46992,10 +46992,10 @@
         </is>
       </c>
       <c r="Q341" t="n">
-        <v>586415</v>
+        <v>586446</v>
       </c>
       <c r="R341" t="n">
-        <v>6311146</v>
+        <v>6311158</v>
       </c>
       <c r="S341" t="n">
         <v>5</v>
@@ -47027,7 +47027,7 @@
       </c>
       <c r="Z341" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AA341" t="inlineStr">
@@ -47037,7 +47037,7 @@
       </c>
       <c r="AB341" t="inlineStr">
         <is>
-          <t>23:03</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AC341" t="inlineStr">
@@ -47082,10 +47082,10 @@
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>122254350</v>
+        <v>122254616</v>
       </c>
       <c r="B342" t="n">
-        <v>56289</v>
+        <v>56294</v>
       </c>
       <c r="C342" t="inlineStr">
         <is>
@@ -47098,21 +47098,21 @@
         </is>
       </c>
       <c r="E342" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
@@ -47136,10 +47136,10 @@
         </is>
       </c>
       <c r="Q342" t="n">
-        <v>586330</v>
+        <v>586327</v>
       </c>
       <c r="R342" t="n">
-        <v>6311120</v>
+        <v>6311118</v>
       </c>
       <c r="S342" t="n">
         <v>5</v>
@@ -47226,10 +47226,10 @@
     </row>
     <row r="343">
       <c r="A343" t="n">
-        <v>122254586</v>
+        <v>122254964</v>
       </c>
       <c r="B343" t="n">
-        <v>56294</v>
+        <v>56282</v>
       </c>
       <c r="C343" t="inlineStr">
         <is>
@@ -47242,21 +47242,21 @@
         </is>
       </c>
       <c r="E343" t="n">
-        <v>205995</v>
+        <v>205992</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
@@ -47280,10 +47280,10 @@
         </is>
       </c>
       <c r="Q343" t="n">
-        <v>586446</v>
+        <v>586430</v>
       </c>
       <c r="R343" t="n">
-        <v>6311158</v>
+        <v>6311142</v>
       </c>
       <c r="S343" t="n">
         <v>5</v>
@@ -47315,7 +47315,7 @@
       </c>
       <c r="Z343" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="AA343" t="inlineStr">
@@ -47325,7 +47325,7 @@
       </c>
       <c r="AB343" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>22:34</t>
         </is>
       </c>
       <c r="AC343" t="inlineStr">
@@ -47370,10 +47370,10 @@
     </row>
     <row r="344">
       <c r="A344" t="n">
-        <v>122254616</v>
+        <v>122254341</v>
       </c>
       <c r="B344" t="n">
-        <v>56294</v>
+        <v>56289</v>
       </c>
       <c r="C344" t="inlineStr">
         <is>
@@ -47386,21 +47386,21 @@
         </is>
       </c>
       <c r="E344" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
@@ -47424,10 +47424,10 @@
         </is>
       </c>
       <c r="Q344" t="n">
-        <v>586327</v>
+        <v>586415</v>
       </c>
       <c r="R344" t="n">
-        <v>6311118</v>
+        <v>6311146</v>
       </c>
       <c r="S344" t="n">
         <v>5</v>
@@ -47459,7 +47459,7 @@
       </c>
       <c r="Z344" t="inlineStr">
         <is>
-          <t>22:57</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AA344" t="inlineStr">
@@ -47469,7 +47469,7 @@
       </c>
       <c r="AB344" t="inlineStr">
         <is>
-          <t>22:58</t>
+          <t>23:03</t>
         </is>
       </c>
       <c r="AC344" t="inlineStr">
@@ -47514,10 +47514,10 @@
     </row>
     <row r="345">
       <c r="A345" t="n">
-        <v>122254964</v>
+        <v>122254350</v>
       </c>
       <c r="B345" t="n">
-        <v>56282</v>
+        <v>56289</v>
       </c>
       <c r="C345" t="inlineStr">
         <is>
@@ -47530,21 +47530,21 @@
         </is>
       </c>
       <c r="E345" t="n">
-        <v>205992</v>
+        <v>100092</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
@@ -47568,10 +47568,10 @@
         </is>
       </c>
       <c r="Q345" t="n">
-        <v>586430</v>
+        <v>586330</v>
       </c>
       <c r="R345" t="n">
-        <v>6311142</v>
+        <v>6311120</v>
       </c>
       <c r="S345" t="n">
         <v>5</v>
@@ -47603,7 +47603,7 @@
       </c>
       <c r="Z345" t="inlineStr">
         <is>
-          <t>22:33</t>
+          <t>22:57</t>
         </is>
       </c>
       <c r="AA345" t="inlineStr">
@@ -47613,7 +47613,7 @@
       </c>
       <c r="AB345" t="inlineStr">
         <is>
-          <t>22:34</t>
+          <t>22:58</t>
         </is>
       </c>
       <c r="AC345" t="inlineStr">
@@ -47658,10 +47658,10 @@
     </row>
     <row r="346">
       <c r="A346" t="n">
-        <v>122254643</v>
+        <v>122254316</v>
       </c>
       <c r="B346" t="n">
-        <v>56294</v>
+        <v>56289</v>
       </c>
       <c r="C346" t="inlineStr">
         <is>
@@ -47674,21 +47674,21 @@
         </is>
       </c>
       <c r="E346" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
@@ -47712,10 +47712,10 @@
         </is>
       </c>
       <c r="Q346" t="n">
-        <v>586424</v>
+        <v>586423</v>
       </c>
       <c r="R346" t="n">
-        <v>6311135</v>
+        <v>6311166</v>
       </c>
       <c r="S346" t="n">
         <v>5</v>
@@ -47747,7 +47747,7 @@
       </c>
       <c r="Z346" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>23:23</t>
         </is>
       </c>
       <c r="AA346" t="inlineStr">
@@ -47757,7 +47757,7 @@
       </c>
       <c r="AB346" t="inlineStr">
         <is>
-          <t>22:38</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="AC346" t="inlineStr">
@@ -47802,10 +47802,10 @@
     </row>
     <row r="347">
       <c r="A347" t="n">
-        <v>122254316</v>
+        <v>122254643</v>
       </c>
       <c r="B347" t="n">
-        <v>56289</v>
+        <v>56294</v>
       </c>
       <c r="C347" t="inlineStr">
         <is>
@@ -47818,21 +47818,21 @@
         </is>
       </c>
       <c r="E347" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I347" t="inlineStr">
@@ -47856,10 +47856,10 @@
         </is>
       </c>
       <c r="Q347" t="n">
-        <v>586423</v>
+        <v>586424</v>
       </c>
       <c r="R347" t="n">
-        <v>6311166</v>
+        <v>6311135</v>
       </c>
       <c r="S347" t="n">
         <v>5</v>
@@ -47891,7 +47891,7 @@
       </c>
       <c r="Z347" t="inlineStr">
         <is>
-          <t>23:23</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AA347" t="inlineStr">
@@ -47901,7 +47901,7 @@
       </c>
       <c r="AB347" t="inlineStr">
         <is>
-          <t>23:24</t>
+          <t>22:38</t>
         </is>
       </c>
       <c r="AC347" t="inlineStr">
@@ -47946,7 +47946,7 @@
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>122254308</v>
+        <v>122254391</v>
       </c>
       <c r="B348" t="n">
         <v>56289</v>
@@ -48000,10 +48000,10 @@
         </is>
       </c>
       <c r="Q348" t="n">
-        <v>586455</v>
+        <v>586379</v>
       </c>
       <c r="R348" t="n">
-        <v>6311159</v>
+        <v>6311136</v>
       </c>
       <c r="S348" t="n">
         <v>5</v>
@@ -48035,7 +48035,7 @@
       </c>
       <c r="Z348" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AA348" t="inlineStr">
@@ -48045,7 +48045,7 @@
       </c>
       <c r="AB348" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>22:46</t>
         </is>
       </c>
       <c r="AC348" t="inlineStr">
@@ -48090,10 +48090,10 @@
     </row>
     <row r="349">
       <c r="A349" t="n">
-        <v>122254390</v>
+        <v>122254617</v>
       </c>
       <c r="B349" t="n">
-        <v>56289</v>
+        <v>56294</v>
       </c>
       <c r="C349" t="inlineStr">
         <is>
@@ -48106,21 +48106,21 @@
         </is>
       </c>
       <c r="E349" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I349" t="inlineStr">
@@ -48144,10 +48144,10 @@
         </is>
       </c>
       <c r="Q349" t="n">
-        <v>586374</v>
+        <v>586317</v>
       </c>
       <c r="R349" t="n">
-        <v>6311139</v>
+        <v>6311115</v>
       </c>
       <c r="S349" t="n">
         <v>5</v>
@@ -48179,7 +48179,7 @@
       </c>
       <c r="Z349" t="inlineStr">
         <is>
-          <t>22:46</t>
+          <t>22:57</t>
         </is>
       </c>
       <c r="AA349" t="inlineStr">
@@ -48189,7 +48189,7 @@
       </c>
       <c r="AB349" t="inlineStr">
         <is>
-          <t>22:47</t>
+          <t>22:58</t>
         </is>
       </c>
       <c r="AC349" t="inlineStr">
@@ -48234,10 +48234,10 @@
     </row>
     <row r="350">
       <c r="A350" t="n">
-        <v>122254417</v>
+        <v>122254606</v>
       </c>
       <c r="B350" t="n">
-        <v>56289</v>
+        <v>56294</v>
       </c>
       <c r="C350" t="inlineStr">
         <is>
@@ -48250,21 +48250,21 @@
         </is>
       </c>
       <c r="E350" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I350" t="inlineStr">
@@ -48288,10 +48288,10 @@
         </is>
       </c>
       <c r="Q350" t="n">
-        <v>586426</v>
+        <v>586415</v>
       </c>
       <c r="R350" t="n">
-        <v>6311145</v>
+        <v>6311146</v>
       </c>
       <c r="S350" t="n">
         <v>5</v>
@@ -48323,7 +48323,7 @@
       </c>
       <c r="Z350" t="inlineStr">
         <is>
-          <t>22:33</t>
+          <t>23:02</t>
         </is>
       </c>
       <c r="AA350" t="inlineStr">
@@ -48333,7 +48333,7 @@
       </c>
       <c r="AB350" t="inlineStr">
         <is>
-          <t>22:34</t>
+          <t>23:03</t>
         </is>
       </c>
       <c r="AC350" t="inlineStr">
@@ -48378,10 +48378,10 @@
     </row>
     <row r="351">
       <c r="A351" t="n">
-        <v>122254837</v>
+        <v>122254308</v>
       </c>
       <c r="B351" t="n">
-        <v>56292</v>
+        <v>56289</v>
       </c>
       <c r="C351" t="inlineStr">
         <is>
@@ -48394,21 +48394,21 @@
         </is>
       </c>
       <c r="E351" t="n">
-        <v>100111</v>
+        <v>100092</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I351" t="inlineStr">
@@ -48432,10 +48432,10 @@
         </is>
       </c>
       <c r="Q351" t="n">
-        <v>586448</v>
+        <v>586455</v>
       </c>
       <c r="R351" t="n">
-        <v>6311154</v>
+        <v>6311159</v>
       </c>
       <c r="S351" t="n">
         <v>5</v>
@@ -48467,7 +48467,7 @@
       </c>
       <c r="Z351" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AA351" t="inlineStr">
@@ -48477,7 +48477,7 @@
       </c>
       <c r="AB351" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AC351" t="inlineStr">
@@ -48522,7 +48522,7 @@
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>122254391</v>
+        <v>122254390</v>
       </c>
       <c r="B352" t="n">
         <v>56289</v>
@@ -48576,10 +48576,10 @@
         </is>
       </c>
       <c r="Q352" t="n">
-        <v>586379</v>
+        <v>586374</v>
       </c>
       <c r="R352" t="n">
-        <v>6311136</v>
+        <v>6311139</v>
       </c>
       <c r="S352" t="n">
         <v>5</v>
@@ -48611,7 +48611,7 @@
       </c>
       <c r="Z352" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>22:46</t>
         </is>
       </c>
       <c r="AA352" t="inlineStr">
@@ -48621,7 +48621,7 @@
       </c>
       <c r="AB352" t="inlineStr">
         <is>
-          <t>22:46</t>
+          <t>22:47</t>
         </is>
       </c>
       <c r="AC352" t="inlineStr">
@@ -48666,10 +48666,10 @@
     </row>
     <row r="353">
       <c r="A353" t="n">
-        <v>122254617</v>
+        <v>122254417</v>
       </c>
       <c r="B353" t="n">
-        <v>56294</v>
+        <v>56289</v>
       </c>
       <c r="C353" t="inlineStr">
         <is>
@@ -48682,21 +48682,21 @@
         </is>
       </c>
       <c r="E353" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I353" t="inlineStr">
@@ -48720,10 +48720,10 @@
         </is>
       </c>
       <c r="Q353" t="n">
-        <v>586317</v>
+        <v>586426</v>
       </c>
       <c r="R353" t="n">
-        <v>6311115</v>
+        <v>6311145</v>
       </c>
       <c r="S353" t="n">
         <v>5</v>
@@ -48755,7 +48755,7 @@
       </c>
       <c r="Z353" t="inlineStr">
         <is>
-          <t>22:57</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="AA353" t="inlineStr">
@@ -48765,7 +48765,7 @@
       </c>
       <c r="AB353" t="inlineStr">
         <is>
-          <t>22:58</t>
+          <t>22:34</t>
         </is>
       </c>
       <c r="AC353" t="inlineStr">
@@ -48810,10 +48810,10 @@
     </row>
     <row r="354">
       <c r="A354" t="n">
-        <v>122254606</v>
+        <v>122254837</v>
       </c>
       <c r="B354" t="n">
-        <v>56294</v>
+        <v>56292</v>
       </c>
       <c r="C354" t="inlineStr">
         <is>
@@ -48826,21 +48826,21 @@
         </is>
       </c>
       <c r="E354" t="n">
-        <v>205995</v>
+        <v>100111</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I354" t="inlineStr">
@@ -48864,10 +48864,10 @@
         </is>
       </c>
       <c r="Q354" t="n">
-        <v>586415</v>
+        <v>586448</v>
       </c>
       <c r="R354" t="n">
-        <v>6311146</v>
+        <v>6311154</v>
       </c>
       <c r="S354" t="n">
         <v>5</v>
@@ -48899,7 +48899,7 @@
       </c>
       <c r="Z354" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>23:27</t>
         </is>
       </c>
       <c r="AA354" t="inlineStr">
@@ -48909,7 +48909,7 @@
       </c>
       <c r="AB354" t="inlineStr">
         <is>
-          <t>23:03</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AC354" t="inlineStr">
@@ -50394,10 +50394,10 @@
     </row>
     <row r="365">
       <c r="A365" t="n">
-        <v>122254959</v>
+        <v>122254650</v>
       </c>
       <c r="B365" t="n">
-        <v>56282</v>
+        <v>56294</v>
       </c>
       <c r="C365" t="inlineStr">
         <is>
@@ -50410,21 +50410,21 @@
         </is>
       </c>
       <c r="E365" t="n">
-        <v>205992</v>
+        <v>205995</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I365" t="inlineStr">
@@ -50448,10 +50448,10 @@
         </is>
       </c>
       <c r="Q365" t="n">
-        <v>586370</v>
+        <v>586422</v>
       </c>
       <c r="R365" t="n">
-        <v>6311139</v>
+        <v>6311105</v>
       </c>
       <c r="S365" t="n">
         <v>5</v>
@@ -50483,7 +50483,7 @@
       </c>
       <c r="Z365" t="inlineStr">
         <is>
-          <t>22:59</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="AA365" t="inlineStr">
@@ -50493,7 +50493,7 @@
       </c>
       <c r="AB365" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:36</t>
         </is>
       </c>
       <c r="AC365" t="inlineStr">
@@ -50538,7 +50538,7 @@
     </row>
     <row r="366">
       <c r="A366" t="n">
-        <v>122254650</v>
+        <v>122254585</v>
       </c>
       <c r="B366" t="n">
         <v>56294</v>
@@ -50592,10 +50592,10 @@
         </is>
       </c>
       <c r="Q366" t="n">
-        <v>586422</v>
+        <v>586455</v>
       </c>
       <c r="R366" t="n">
-        <v>6311105</v>
+        <v>6311156</v>
       </c>
       <c r="S366" t="n">
         <v>5</v>
@@ -50627,7 +50627,7 @@
       </c>
       <c r="Z366" t="inlineStr">
         <is>
-          <t>22:35</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AA366" t="inlineStr">
@@ -50637,7 +50637,7 @@
       </c>
       <c r="AB366" t="inlineStr">
         <is>
-          <t>22:36</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AC366" t="inlineStr">
@@ -50682,10 +50682,10 @@
     </row>
     <row r="367">
       <c r="A367" t="n">
-        <v>122254585</v>
+        <v>122254959</v>
       </c>
       <c r="B367" t="n">
-        <v>56294</v>
+        <v>56282</v>
       </c>
       <c r="C367" t="inlineStr">
         <is>
@@ -50698,21 +50698,21 @@
         </is>
       </c>
       <c r="E367" t="n">
-        <v>205995</v>
+        <v>205992</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I367" t="inlineStr">
@@ -50736,10 +50736,10 @@
         </is>
       </c>
       <c r="Q367" t="n">
-        <v>586455</v>
+        <v>586370</v>
       </c>
       <c r="R367" t="n">
-        <v>6311156</v>
+        <v>6311139</v>
       </c>
       <c r="S367" t="n">
         <v>5</v>
@@ -50771,7 +50771,7 @@
       </c>
       <c r="Z367" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>22:59</t>
         </is>
       </c>
       <c r="AA367" t="inlineStr">
@@ -50781,7 +50781,7 @@
       </c>
       <c r="AB367" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AC367" t="inlineStr">
@@ -51978,10 +51978,10 @@
     </row>
     <row r="376">
       <c r="A376" t="n">
-        <v>122254651</v>
+        <v>122254415</v>
       </c>
       <c r="B376" t="n">
-        <v>56294</v>
+        <v>56289</v>
       </c>
       <c r="C376" t="inlineStr">
         <is>
@@ -51994,21 +51994,21 @@
         </is>
       </c>
       <c r="E376" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H376" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I376" t="inlineStr">
@@ -52035,7 +52035,7 @@
         <v>586425</v>
       </c>
       <c r="R376" t="n">
-        <v>6311113</v>
+        <v>6311135</v>
       </c>
       <c r="S376" t="n">
         <v>5</v>
@@ -52067,7 +52067,7 @@
       </c>
       <c r="Z376" t="inlineStr">
         <is>
-          <t>22:35</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AA376" t="inlineStr">
@@ -52077,7 +52077,7 @@
       </c>
       <c r="AB376" t="inlineStr">
         <is>
-          <t>22:36</t>
+          <t>22:38</t>
         </is>
       </c>
       <c r="AC376" t="inlineStr">
@@ -52122,7 +52122,7 @@
     </row>
     <row r="377">
       <c r="A377" t="n">
-        <v>122254632</v>
+        <v>122254651</v>
       </c>
       <c r="B377" t="n">
         <v>56294</v>
@@ -52176,10 +52176,10 @@
         </is>
       </c>
       <c r="Q377" t="n">
-        <v>586374</v>
+        <v>586425</v>
       </c>
       <c r="R377" t="n">
-        <v>6311140</v>
+        <v>6311113</v>
       </c>
       <c r="S377" t="n">
         <v>5</v>
@@ -52211,7 +52211,7 @@
       </c>
       <c r="Z377" t="inlineStr">
         <is>
-          <t>22:46</t>
+          <t>22:35</t>
         </is>
       </c>
       <c r="AA377" t="inlineStr">
@@ -52221,7 +52221,7 @@
       </c>
       <c r="AB377" t="inlineStr">
         <is>
-          <t>22:47</t>
+          <t>22:36</t>
         </is>
       </c>
       <c r="AC377" t="inlineStr">
@@ -52266,10 +52266,10 @@
     </row>
     <row r="378">
       <c r="A378" t="n">
-        <v>122254415</v>
+        <v>122254632</v>
       </c>
       <c r="B378" t="n">
-        <v>56289</v>
+        <v>56294</v>
       </c>
       <c r="C378" t="inlineStr">
         <is>
@@ -52282,21 +52282,21 @@
         </is>
       </c>
       <c r="E378" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I378" t="inlineStr">
@@ -52320,10 +52320,10 @@
         </is>
       </c>
       <c r="Q378" t="n">
-        <v>586425</v>
+        <v>586374</v>
       </c>
       <c r="R378" t="n">
-        <v>6311135</v>
+        <v>6311140</v>
       </c>
       <c r="S378" t="n">
         <v>5</v>
@@ -52355,7 +52355,7 @@
       </c>
       <c r="Z378" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>22:46</t>
         </is>
       </c>
       <c r="AA378" t="inlineStr">
@@ -52365,7 +52365,7 @@
       </c>
       <c r="AB378" t="inlineStr">
         <is>
-          <t>22:38</t>
+          <t>22:47</t>
         </is>
       </c>
       <c r="AC378" t="inlineStr">
@@ -52698,10 +52698,10 @@
     </row>
     <row r="381">
       <c r="A381" t="n">
-        <v>122254856</v>
+        <v>122254615</v>
       </c>
       <c r="B381" t="n">
-        <v>56292</v>
+        <v>56294</v>
       </c>
       <c r="C381" t="inlineStr">
         <is>
@@ -52714,21 +52714,21 @@
         </is>
       </c>
       <c r="E381" t="n">
-        <v>100111</v>
+        <v>205995</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I381" t="inlineStr">
@@ -52752,10 +52752,10 @@
         </is>
       </c>
       <c r="Q381" t="n">
-        <v>586327</v>
+        <v>586329</v>
       </c>
       <c r="R381" t="n">
-        <v>6311118</v>
+        <v>6311120</v>
       </c>
       <c r="S381" t="n">
         <v>5</v>
@@ -52842,10 +52842,10 @@
     </row>
     <row r="382">
       <c r="A382" t="n">
-        <v>122254615</v>
+        <v>122254856</v>
       </c>
       <c r="B382" t="n">
-        <v>56294</v>
+        <v>56292</v>
       </c>
       <c r="C382" t="inlineStr">
         <is>
@@ -52858,21 +52858,21 @@
         </is>
       </c>
       <c r="E382" t="n">
-        <v>205995</v>
+        <v>100111</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H382" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I382" t="inlineStr">
@@ -52896,10 +52896,10 @@
         </is>
       </c>
       <c r="Q382" t="n">
-        <v>586329</v>
+        <v>586327</v>
       </c>
       <c r="R382" t="n">
-        <v>6311120</v>
+        <v>6311118</v>
       </c>
       <c r="S382" t="n">
         <v>5</v>
@@ -53130,10 +53130,10 @@
     </row>
     <row r="384">
       <c r="A384" t="n">
-        <v>122254367</v>
+        <v>122254656</v>
       </c>
       <c r="B384" t="n">
-        <v>56289</v>
+        <v>56294</v>
       </c>
       <c r="C384" t="inlineStr">
         <is>
@@ -53146,21 +53146,21 @@
         </is>
       </c>
       <c r="E384" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I384" t="inlineStr">
@@ -53184,10 +53184,10 @@
         </is>
       </c>
       <c r="Q384" t="n">
-        <v>586280</v>
+        <v>586483</v>
       </c>
       <c r="R384" t="n">
-        <v>6311103</v>
+        <v>6311186</v>
       </c>
       <c r="S384" t="n">
         <v>5</v>
@@ -53219,7 +53219,7 @@
       </c>
       <c r="Z384" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>22:31</t>
         </is>
       </c>
       <c r="AA384" t="inlineStr">
@@ -53229,7 +53229,7 @@
       </c>
       <c r="AB384" t="inlineStr">
         <is>
-          <t>22:52</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AC384" t="inlineStr">
@@ -53274,7 +53274,7 @@
     </row>
     <row r="385">
       <c r="A385" t="n">
-        <v>122254369</v>
+        <v>122254394</v>
       </c>
       <c r="B385" t="n">
         <v>56289</v>
@@ -53328,10 +53328,10 @@
         </is>
       </c>
       <c r="Q385" t="n">
-        <v>586300</v>
+        <v>586419</v>
       </c>
       <c r="R385" t="n">
-        <v>6311112</v>
+        <v>6311142</v>
       </c>
       <c r="S385" t="n">
         <v>5</v>
@@ -53363,7 +53363,7 @@
       </c>
       <c r="Z385" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>22:43</t>
         </is>
       </c>
       <c r="AA385" t="inlineStr">
@@ -53373,7 +53373,7 @@
       </c>
       <c r="AB385" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AC385" t="inlineStr">
@@ -53418,10 +53418,10 @@
     </row>
     <row r="386">
       <c r="A386" t="n">
-        <v>122254656</v>
+        <v>122254306</v>
       </c>
       <c r="B386" t="n">
-        <v>56294</v>
+        <v>56289</v>
       </c>
       <c r="C386" t="inlineStr">
         <is>
@@ -53434,21 +53434,21 @@
         </is>
       </c>
       <c r="E386" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H386" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I386" t="inlineStr">
@@ -53472,10 +53472,10 @@
         </is>
       </c>
       <c r="Q386" t="n">
-        <v>586483</v>
+        <v>586473</v>
       </c>
       <c r="R386" t="n">
-        <v>6311186</v>
+        <v>6311192</v>
       </c>
       <c r="S386" t="n">
         <v>5</v>
@@ -53507,7 +53507,7 @@
       </c>
       <c r="Z386" t="inlineStr">
         <is>
-          <t>22:31</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AA386" t="inlineStr">
@@ -53517,7 +53517,7 @@
       </c>
       <c r="AB386" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AC386" t="inlineStr">
@@ -53562,7 +53562,7 @@
     </row>
     <row r="387">
       <c r="A387" t="n">
-        <v>122254394</v>
+        <v>122254367</v>
       </c>
       <c r="B387" t="n">
         <v>56289</v>
@@ -53616,10 +53616,10 @@
         </is>
       </c>
       <c r="Q387" t="n">
-        <v>586419</v>
+        <v>586280</v>
       </c>
       <c r="R387" t="n">
-        <v>6311142</v>
+        <v>6311103</v>
       </c>
       <c r="S387" t="n">
         <v>5</v>
@@ -53651,7 +53651,7 @@
       </c>
       <c r="Z387" t="inlineStr">
         <is>
-          <t>22:43</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AA387" t="inlineStr">
@@ -53661,7 +53661,7 @@
       </c>
       <c r="AB387" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>22:52</t>
         </is>
       </c>
       <c r="AC387" t="inlineStr">
@@ -53706,7 +53706,7 @@
     </row>
     <row r="388">
       <c r="A388" t="n">
-        <v>122254306</v>
+        <v>122254369</v>
       </c>
       <c r="B388" t="n">
         <v>56289</v>
@@ -53760,10 +53760,10 @@
         </is>
       </c>
       <c r="Q388" t="n">
-        <v>586473</v>
+        <v>586300</v>
       </c>
       <c r="R388" t="n">
-        <v>6311192</v>
+        <v>6311112</v>
       </c>
       <c r="S388" t="n">
         <v>5</v>
@@ -53795,7 +53795,7 @@
       </c>
       <c r="Z388" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AA388" t="inlineStr">
@@ -53805,7 +53805,7 @@
       </c>
       <c r="AB388" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AC388" t="inlineStr">

--- a/artfynd/A 36363-2024 artfynd.xlsx
+++ b/artfynd/A 36363-2024 artfynd.xlsx
@@ -37002,7 +37002,7 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>122254343</v>
+        <v>122254371</v>
       </c>
       <c r="B272" t="n">
         <v>56289</v>
@@ -37056,10 +37056,10 @@
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>586388</v>
+        <v>586308</v>
       </c>
       <c r="R272" t="n">
-        <v>6311142</v>
+        <v>6311132</v>
       </c>
       <c r="S272" t="n">
         <v>5</v>
@@ -37091,7 +37091,7 @@
       </c>
       <c r="Z272" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AA272" t="inlineStr">
@@ -37101,7 +37101,7 @@
       </c>
       <c r="AB272" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AC272" t="inlineStr">
@@ -37146,10 +37146,10 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>122254472</v>
+        <v>122254838</v>
       </c>
       <c r="B273" t="n">
-        <v>56275</v>
+        <v>56292</v>
       </c>
       <c r="C273" t="inlineStr">
         <is>
@@ -37158,25 +37158,25 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E273" t="n">
-        <v>205998</v>
+        <v>100111</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
@@ -37200,10 +37200,10 @@
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>586455</v>
+        <v>586448</v>
       </c>
       <c r="R273" t="n">
-        <v>6311159</v>
+        <v>6311154</v>
       </c>
       <c r="S273" t="n">
         <v>5</v>
@@ -37235,17 +37235,17 @@
       </c>
       <c r="Z273" t="inlineStr">
         <is>
+          <t>23:27</t>
+        </is>
+      </c>
+      <c r="AA273" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AB273" t="inlineStr">
+        <is>
           <t>23:28</t>
-        </is>
-      </c>
-      <c r="AA273" t="inlineStr">
-        <is>
-          <t>2024-06-26</t>
-        </is>
-      </c>
-      <c r="AB273" t="inlineStr">
-        <is>
-          <t>23:29</t>
         </is>
       </c>
       <c r="AC273" t="inlineStr">
@@ -37290,10 +37290,10 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>122254496</v>
+        <v>122254412</v>
       </c>
       <c r="B274" t="n">
-        <v>56275</v>
+        <v>56289</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>
@@ -37302,25 +37302,25 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E274" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
@@ -37344,10 +37344,10 @@
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>586415</v>
+        <v>586424</v>
       </c>
       <c r="R274" t="n">
-        <v>6311146</v>
+        <v>6311135</v>
       </c>
       <c r="S274" t="n">
         <v>5</v>
@@ -37379,7 +37379,7 @@
       </c>
       <c r="Z274" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AA274" t="inlineStr">
@@ -37389,7 +37389,7 @@
       </c>
       <c r="AB274" t="inlineStr">
         <is>
-          <t>23:03</t>
+          <t>22:38</t>
         </is>
       </c>
       <c r="AC274" t="inlineStr">
@@ -37434,7 +37434,7 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>122254317</v>
+        <v>122254390</v>
       </c>
       <c r="B275" t="n">
         <v>56289</v>
@@ -37488,10 +37488,10 @@
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>586438</v>
+        <v>586374</v>
       </c>
       <c r="R275" t="n">
-        <v>6311222</v>
+        <v>6311139</v>
       </c>
       <c r="S275" t="n">
         <v>5</v>
@@ -37523,7 +37523,7 @@
       </c>
       <c r="Z275" t="inlineStr">
         <is>
-          <t>23:22</t>
+          <t>22:46</t>
         </is>
       </c>
       <c r="AA275" t="inlineStr">
@@ -37533,7 +37533,7 @@
       </c>
       <c r="AB275" t="inlineStr">
         <is>
-          <t>23:23</t>
+          <t>22:47</t>
         </is>
       </c>
       <c r="AC275" t="inlineStr">
@@ -37578,10 +37578,10 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>122254396</v>
+        <v>122254625</v>
       </c>
       <c r="B276" t="n">
-        <v>56289</v>
+        <v>56294</v>
       </c>
       <c r="C276" t="inlineStr">
         <is>
@@ -37594,21 +37594,21 @@
         </is>
       </c>
       <c r="E276" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
@@ -37632,10 +37632,10 @@
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>586408</v>
+        <v>586309</v>
       </c>
       <c r="R276" t="n">
-        <v>6311124</v>
+        <v>6311119</v>
       </c>
       <c r="S276" t="n">
         <v>5</v>
@@ -37667,7 +37667,7 @@
       </c>
       <c r="Z276" t="inlineStr">
         <is>
-          <t>22:43</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AA276" t="inlineStr">
@@ -37677,7 +37677,7 @@
       </c>
       <c r="AB276" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AC276" t="inlineStr">
@@ -37722,7 +37722,7 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>122254609</v>
+        <v>122254635</v>
       </c>
       <c r="B277" t="n">
         <v>56294</v>
@@ -37776,10 +37776,10 @@
         </is>
       </c>
       <c r="Q277" t="n">
-        <v>586392</v>
+        <v>586417</v>
       </c>
       <c r="R277" t="n">
-        <v>6311147</v>
+        <v>6311145</v>
       </c>
       <c r="S277" t="n">
         <v>5</v>
@@ -37811,7 +37811,7 @@
       </c>
       <c r="Z277" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AA277" t="inlineStr">
@@ -37821,7 +37821,7 @@
       </c>
       <c r="AB277" t="inlineStr">
         <is>
-          <t>23:02</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="AC277" t="inlineStr">
@@ -37866,10 +37866,10 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>122254372</v>
+        <v>122254475</v>
       </c>
       <c r="B278" t="n">
-        <v>56289</v>
+        <v>56275</v>
       </c>
       <c r="C278" t="inlineStr">
         <is>
@@ -37878,25 +37878,25 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E278" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
@@ -37920,10 +37920,10 @@
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>586306</v>
+        <v>586420</v>
       </c>
       <c r="R278" t="n">
-        <v>6311131</v>
+        <v>6311166</v>
       </c>
       <c r="S278" t="n">
         <v>5</v>
@@ -37955,7 +37955,7 @@
       </c>
       <c r="Z278" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>23:23</t>
         </is>
       </c>
       <c r="AA278" t="inlineStr">
@@ -37965,7 +37965,7 @@
       </c>
       <c r="AB278" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="AC278" t="inlineStr">
@@ -38010,7 +38010,7 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>122254612</v>
+        <v>122254637</v>
       </c>
       <c r="B279" t="n">
         <v>56294</v>
@@ -38064,10 +38064,10 @@
         </is>
       </c>
       <c r="Q279" t="n">
-        <v>586371</v>
+        <v>586408</v>
       </c>
       <c r="R279" t="n">
-        <v>6311135</v>
+        <v>6311124</v>
       </c>
       <c r="S279" t="n">
         <v>5</v>
@@ -38099,7 +38099,7 @@
       </c>
       <c r="Z279" t="inlineStr">
         <is>
-          <t>22:59</t>
+          <t>22:43</t>
         </is>
       </c>
       <c r="AA279" t="inlineStr">
@@ -38109,7 +38109,7 @@
       </c>
       <c r="AB279" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:44</t>
         </is>
       </c>
       <c r="AC279" t="inlineStr">
@@ -38154,7 +38154,7 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>122254953</v>
+        <v>122254957</v>
       </c>
       <c r="B280" t="n">
         <v>56282</v>
@@ -38208,10 +38208,10 @@
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>586449</v>
+        <v>586444</v>
       </c>
       <c r="R280" t="n">
-        <v>6311155</v>
+        <v>6311160</v>
       </c>
       <c r="S280" t="n">
         <v>5</v>
@@ -38243,7 +38243,7 @@
       </c>
       <c r="Z280" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>23:24</t>
         </is>
       </c>
       <c r="AA280" t="inlineStr">
@@ -38253,7 +38253,7 @@
       </c>
       <c r="AB280" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AC280" t="inlineStr">
@@ -38298,10 +38298,10 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>122254420</v>
+        <v>122254843</v>
       </c>
       <c r="B281" t="n">
-        <v>56289</v>
+        <v>56292</v>
       </c>
       <c r="C281" t="inlineStr">
         <is>
@@ -38314,21 +38314,21 @@
         </is>
       </c>
       <c r="E281" t="n">
-        <v>100092</v>
+        <v>100111</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
@@ -38352,10 +38352,10 @@
         </is>
       </c>
       <c r="Q281" t="n">
-        <v>586467</v>
+        <v>586389</v>
       </c>
       <c r="R281" t="n">
-        <v>6311178</v>
+        <v>6311142</v>
       </c>
       <c r="S281" t="n">
         <v>5</v>
@@ -38387,7 +38387,7 @@
       </c>
       <c r="Z281" t="inlineStr">
         <is>
-          <t>22:32</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA281" t="inlineStr">
@@ -38397,7 +38397,7 @@
       </c>
       <c r="AB281" t="inlineStr">
         <is>
-          <t>22:33</t>
+          <t>23:01</t>
         </is>
       </c>
       <c r="AC281" t="inlineStr">
@@ -38442,10 +38442,10 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>122254474</v>
+        <v>122254308</v>
       </c>
       <c r="B282" t="n">
-        <v>56275</v>
+        <v>56289</v>
       </c>
       <c r="C282" t="inlineStr">
         <is>
@@ -38454,25 +38454,25 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E282" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
@@ -38496,10 +38496,10 @@
         </is>
       </c>
       <c r="Q282" t="n">
-        <v>586443</v>
+        <v>586455</v>
       </c>
       <c r="R282" t="n">
-        <v>6311164</v>
+        <v>6311159</v>
       </c>
       <c r="S282" t="n">
         <v>5</v>
@@ -38531,7 +38531,7 @@
       </c>
       <c r="Z282" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AA282" t="inlineStr">
@@ -38541,7 +38541,7 @@
       </c>
       <c r="AB282" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AC282" t="inlineStr">
@@ -38586,10 +38586,10 @@
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>122254655</v>
+        <v>122254420</v>
       </c>
       <c r="B283" t="n">
-        <v>56294</v>
+        <v>56289</v>
       </c>
       <c r="C283" t="inlineStr">
         <is>
@@ -38602,21 +38602,21 @@
         </is>
       </c>
       <c r="E283" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
@@ -38640,10 +38640,10 @@
         </is>
       </c>
       <c r="Q283" t="n">
-        <v>586475</v>
+        <v>586467</v>
       </c>
       <c r="R283" t="n">
-        <v>6311187</v>
+        <v>6311178</v>
       </c>
       <c r="S283" t="n">
         <v>5</v>
@@ -38730,7 +38730,7 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>122254648</v>
+        <v>122254660</v>
       </c>
       <c r="B284" t="n">
         <v>56294</v>
@@ -38784,10 +38784,10 @@
         </is>
       </c>
       <c r="Q284" t="n">
-        <v>586418</v>
+        <v>586488</v>
       </c>
       <c r="R284" t="n">
-        <v>6311107</v>
+        <v>6311183</v>
       </c>
       <c r="S284" t="n">
         <v>5</v>
@@ -38819,7 +38819,7 @@
       </c>
       <c r="Z284" t="inlineStr">
         <is>
-          <t>22:36</t>
+          <t>22:31</t>
         </is>
       </c>
       <c r="AA284" t="inlineStr">
@@ -38829,7 +38829,7 @@
       </c>
       <c r="AB284" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AC284" t="inlineStr">
@@ -38874,10 +38874,10 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>122254954</v>
+        <v>122254585</v>
       </c>
       <c r="B285" t="n">
-        <v>56282</v>
+        <v>56294</v>
       </c>
       <c r="C285" t="inlineStr">
         <is>
@@ -38890,21 +38890,21 @@
         </is>
       </c>
       <c r="E285" t="n">
-        <v>205992</v>
+        <v>205995</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
@@ -38928,10 +38928,10 @@
         </is>
       </c>
       <c r="Q285" t="n">
-        <v>586442</v>
+        <v>586455</v>
       </c>
       <c r="R285" t="n">
-        <v>6311152</v>
+        <v>6311156</v>
       </c>
       <c r="S285" t="n">
         <v>5</v>
@@ -38963,7 +38963,7 @@
       </c>
       <c r="Z285" t="inlineStr">
         <is>
-          <t>23:25</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AA285" t="inlineStr">
@@ -38973,7 +38973,7 @@
       </c>
       <c r="AB285" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AC285" t="inlineStr">
@@ -39018,7 +39018,7 @@
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>122254644</v>
+        <v>122254646</v>
       </c>
       <c r="B286" t="n">
         <v>56294</v>
@@ -39072,10 +39072,10 @@
         </is>
       </c>
       <c r="Q286" t="n">
-        <v>586429</v>
+        <v>586422</v>
       </c>
       <c r="R286" t="n">
-        <v>6311115</v>
+        <v>6311111</v>
       </c>
       <c r="S286" t="n">
         <v>5</v>
@@ -39162,10 +39162,10 @@
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>122254952</v>
+        <v>122254659</v>
       </c>
       <c r="B287" t="n">
-        <v>56282</v>
+        <v>56294</v>
       </c>
       <c r="C287" t="inlineStr">
         <is>
@@ -39178,21 +39178,21 @@
         </is>
       </c>
       <c r="E287" t="n">
-        <v>205992</v>
+        <v>205995</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
@@ -39216,10 +39216,10 @@
         </is>
       </c>
       <c r="Q287" t="n">
-        <v>586455</v>
+        <v>586489</v>
       </c>
       <c r="R287" t="n">
-        <v>6311156</v>
+        <v>6311181</v>
       </c>
       <c r="S287" t="n">
         <v>5</v>
@@ -39251,7 +39251,7 @@
       </c>
       <c r="Z287" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>22:31</t>
         </is>
       </c>
       <c r="AA287" t="inlineStr">
@@ -39261,7 +39261,7 @@
       </c>
       <c r="AB287" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AC287" t="inlineStr">
@@ -39306,10 +39306,10 @@
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>122254514</v>
+        <v>122254862</v>
       </c>
       <c r="B288" t="n">
-        <v>56275</v>
+        <v>56292</v>
       </c>
       <c r="C288" t="inlineStr">
         <is>
@@ -39318,25 +39318,25 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E288" t="n">
-        <v>205998</v>
+        <v>100111</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
@@ -39360,10 +39360,10 @@
         </is>
       </c>
       <c r="Q288" t="n">
-        <v>586408</v>
+        <v>586288</v>
       </c>
       <c r="R288" t="n">
-        <v>6311124</v>
+        <v>6311100</v>
       </c>
       <c r="S288" t="n">
         <v>5</v>
@@ -39395,7 +39395,7 @@
       </c>
       <c r="Z288" t="inlineStr">
         <is>
-          <t>22:43</t>
+          <t>22:55</t>
         </is>
       </c>
       <c r="AA288" t="inlineStr">
@@ -39405,7 +39405,7 @@
       </c>
       <c r="AB288" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>22:56</t>
         </is>
       </c>
       <c r="AC288" t="inlineStr">
@@ -39450,10 +39450,10 @@
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>122254512</v>
+        <v>122254372</v>
       </c>
       <c r="B289" t="n">
-        <v>56275</v>
+        <v>56289</v>
       </c>
       <c r="C289" t="inlineStr">
         <is>
@@ -39462,25 +39462,25 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E289" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
@@ -39504,10 +39504,10 @@
         </is>
       </c>
       <c r="Q289" t="n">
-        <v>586379</v>
+        <v>586306</v>
       </c>
       <c r="R289" t="n">
-        <v>6311136</v>
+        <v>6311131</v>
       </c>
       <c r="S289" t="n">
         <v>5</v>
@@ -39539,7 +39539,7 @@
       </c>
       <c r="Z289" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AA289" t="inlineStr">
@@ -39549,7 +39549,7 @@
       </c>
       <c r="AB289" t="inlineStr">
         <is>
-          <t>22:46</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="AC289" t="inlineStr">
@@ -39594,7 +39594,7 @@
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>122254365</v>
+        <v>122254411</v>
       </c>
       <c r="B290" t="n">
         <v>56289</v>
@@ -39648,10 +39648,10 @@
         </is>
       </c>
       <c r="Q290" t="n">
-        <v>586276</v>
+        <v>586414</v>
       </c>
       <c r="R290" t="n">
-        <v>6311100</v>
+        <v>6311126</v>
       </c>
       <c r="S290" t="n">
         <v>5</v>
@@ -39683,7 +39683,7 @@
       </c>
       <c r="Z290" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AA290" t="inlineStr">
@@ -39693,7 +39693,7 @@
       </c>
       <c r="AB290" t="inlineStr">
         <is>
-          <t>22:52</t>
+          <t>22:38</t>
         </is>
       </c>
       <c r="AC290" t="inlineStr">
@@ -39738,10 +39738,10 @@
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>122254950</v>
+        <v>122254421</v>
       </c>
       <c r="B291" t="n">
-        <v>56282</v>
+        <v>56289</v>
       </c>
       <c r="C291" t="inlineStr">
         <is>
@@ -39754,21 +39754,21 @@
         </is>
       </c>
       <c r="E291" t="n">
-        <v>205992</v>
+        <v>100092</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
@@ -39792,10 +39792,10 @@
         </is>
       </c>
       <c r="Q291" t="n">
-        <v>586482</v>
+        <v>586468</v>
       </c>
       <c r="R291" t="n">
-        <v>6311185</v>
+        <v>6311181</v>
       </c>
       <c r="S291" t="n">
         <v>5</v>
@@ -39827,7 +39827,7 @@
       </c>
       <c r="Z291" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AA291" t="inlineStr">
@@ -39837,7 +39837,7 @@
       </c>
       <c r="AB291" t="inlineStr">
         <is>
-          <t>23:31</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="AC291" t="inlineStr">
@@ -39882,10 +39882,10 @@
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>122254951</v>
+        <v>122254413</v>
       </c>
       <c r="B292" t="n">
-        <v>56282</v>
+        <v>56289</v>
       </c>
       <c r="C292" t="inlineStr">
         <is>
@@ -39898,21 +39898,21 @@
         </is>
       </c>
       <c r="E292" t="n">
-        <v>205992</v>
+        <v>100092</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
@@ -39936,10 +39936,10 @@
         </is>
       </c>
       <c r="Q292" t="n">
-        <v>586459</v>
+        <v>586423</v>
       </c>
       <c r="R292" t="n">
-        <v>6311154</v>
+        <v>6311137</v>
       </c>
       <c r="S292" t="n">
         <v>5</v>
@@ -39971,7 +39971,7 @@
       </c>
       <c r="Z292" t="inlineStr">
         <is>
-          <t>23:28</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="AA292" t="inlineStr">
@@ -39981,7 +39981,7 @@
       </c>
       <c r="AB292" t="inlineStr">
         <is>
-          <t>23:29</t>
+          <t>22:38</t>
         </is>
       </c>
       <c r="AC292" t="inlineStr">
@@ -40026,10 +40026,10 @@
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>122254587</v>
+        <v>122254966</v>
       </c>
       <c r="B293" t="n">
-        <v>56294</v>
+        <v>56282</v>
       </c>
       <c r="C293" t="inlineStr">
         <is>
@@ -40042,21 +40042,21 @@
         </is>
       </c>
       <c r="E293" t="n">
-        <v>205995</v>
+        <v>205992</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
@@ -40080,10 +40080,10 @@
         </is>
       </c>
       <c r="Q293" t="n">
-        <v>586443</v>
+        <v>586467</v>
       </c>
       <c r="R293" t="n">
-        <v>6311163</v>
+        <v>6311178</v>
       </c>
       <c r="S293" t="n">
         <v>5</v>
@@ -40115,7 +40115,7 @@
       </c>
       <c r="Z293" t="inlineStr">
         <is>
-          <t>23:26</t>
+          <t>22:32</t>
         </is>
       </c>
       <c r="AA293" t="inlineStr">
@@ -40125,7 +40125,7 @@
       </c>
       <c r="AB293" t="inlineStr">
         <is>
-          <t>23:27</t>
+          <t>22:33</t>
         </is>
       </c>
       <c r="AC293" t="inlineStr">
@@ -40170,10 +40170,10 @@
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>122254845</v>
+        <v>122254954</v>
       </c>
       <c r="B294" t="n">
-        <v>56292</v>
+        <v>56282</v>
       </c>
       <c r="C294" t="inlineStr">
         <is>
@@ -40186,21 +40186,21 @@
         </is>
       </c>
       <c r="E294" t="n">
-        <v>100111</v>
+        <v>205992</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
@@ -40224,10 +40224,10 @@
         </is>
       </c>
       <c r="Q294" t="n">
-        <v>586370</v>
+        <v>586442</v>
       </c>
       <c r="R294" t="n">
-        <v>6311139</v>
+        <v>6311152</v>
       </c>
       <c r="S294" t="n">
         <v>5</v>
@@ -40259,7 +40259,7 @@
       </c>
       <c r="Z294" t="inlineStr">
         <is>
-          <t>22:59</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="AA294" t="inlineStr">
@@ -40269,7 +40269,7 @@
       </c>
       <c r="AB294" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>23:26</t>
         </is>
       </c>
       <c r="AC294" t="inlineStr">
@@ -40314,10 +40314,10 @@
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>122254855</v>
+        <v>122254951</v>
       </c>
       <c r="B295" t="n">
-        <v>56292</v>
+        <v>56282</v>
       </c>
       <c r="C295" t="inlineStr">
         <is>
@@ -40330,21 +40330,21 @@
         </is>
       </c>
       <c r="E295" t="n">
-        <v>100111</v>
+        <v>205992</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
@@ -40368,10 +40368,10 @@
         </is>
       </c>
       <c r="Q295" t="n">
-        <v>586330</v>
+        <v>586459</v>
       </c>
       <c r="R295" t="n">
-        <v>6311120</v>
+        <v>6311154</v>
       </c>
       <c r="S295" t="n">
         <v>5</v>
@@ -40403,7 +40403,7 @@
       </c>
       <c r="Z295" t="inlineStr">
         <is>
-          <t>22:57</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AA295" t="inlineStr">
@@ -40413,7 +40413,7 @@
       </c>
       <c r="AB295" t="inlineStr">
         <is>
-          <t>22:58</t>
+          <t>23:29</t>
         </is>
       </c>
       <c r="AC295" t="inlineStr">
@@ -40458,10 +40458,10 @@
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>122254411</v>
+        <v>122254500</v>
       </c>
       <c r="B296" t="n">
-        <v>56289</v>
+        <v>56275</v>
       </c>
       <c r="C296" t="inlineStr">
         <is>
@@ -40470,25 +40470,25 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E296" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
@@ -40512,10 +40512,10 @@